--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -461,25 +461,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="53" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="210" customWidth="1" min="5" max="5"/>
-    <col width="35" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="25" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" min="15" max="15"/>
-    <col width="19" customWidth="1" min="16" max="16"/>
+    <col width="67" customWidth="1" min="3" max="3"/>
+    <col width="77" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="19" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -500,65 +501,70 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Research Topics</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Tenure Track</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Deadline</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Salary</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Summary (Gemini)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Link</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Date Added</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Last Verified</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Latitude</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Longitude</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
@@ -567,59 +573,59 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Civil, Construction and Environmental Engineering -TransportationEngineering -AssistantProfessor</t>
+          <t>Assistant Professor of Transportation Engineering</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Transportation Engineering</t>
+          <t>University of Alabama</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Transportation Engineering</t>
+          <t>Department of Civil, Construction and Environmental Engineering</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Transportation Engineering, Civil Engineering, Transportation Systems</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor University of Alabama Civil, Construction and Environmental Engineering Tuscaloosa, Alabama United States Date Posted Nov. 3, 2025 Deadline Open until filled Position Starts Aug. 16, 2026</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Review begins immediately / Open</t>
+          <t>Tuscaloosa, AL</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>Civil, Construction and Environmental Engineering - Transportation Engineering - Assistant Professor University of Alabama Civil, Construction and Environmental Engineering Tuscaloosa, Alabama United ...</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>The Department of Civil, Construction and Environmental Engineering at the University of Alabama is hiring a tenure-track Assistant Professor in Transportation Engineering, requiring an earned doctorate in civil engineering or a closely related field. | Research Topics: Transportation Engineering, Civil Engineering, Transportation Systems</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
         <is>
           <t>https://engineering.academickeys.com/job/s9z6epb3/Civil-Construction-and-Environmental-Engineering--Transportation-Engineering--Assistant-Professor</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>AcademicKeys</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
@@ -627,16 +633,21 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="N2" s="2" t="n">
-        <v>39.0691039</v>
-      </c>
       <c r="O2" s="2" t="n">
-        <v>-108.5607374</v>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
+        <v>33.2120822</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>-87.53967350000001</v>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>daabd65ea8fe188a</t>
         </is>
@@ -645,59 +656,59 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Postdoctoral Scholar</t>
+          <t>Assistant Professor of Transportation Engineering</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>AcademicKeys Listed Institution</t>
+          <t>South Dakota State University</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Transportation Engineering</t>
+          <t>Civil and Environmental Engineering</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Transportation Engineering, Civil Infrastructure, Traffic Engineering</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Review begins immediately / Open</t>
+          <t>Brookings, SD</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>Postdoctoral Scholar Michigan Technological University Civil, Environmental, and Geospatial Engineering Houghton, Michigan United States Date Posted Jul. 13, 2026 Deadline Aug. 1, 2026 Position Starts...</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>https://engineering.academickeys.com/job/7yb6uoel/Postdoctoral-Scholar</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>South Dakota State University invites applications for a tenure-track Assistant Professor of Transportation Engineering in the Department of Civil and Environmental Engineering, requiring a Ph.D. in Civil Engineering or a closely related field. | Research Topics: Transportation Engineering, Civil Infrastructure, Traffic Engineering</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>https://engineering.academickeys.com/job/m4lk5asr/Assistant-Professor-of-Transportation-Engineering</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>AcademicKeys</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
@@ -705,73 +716,82 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr"/>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>aa223cc351175091</t>
+      <c r="O3" s="2" t="n">
+        <v>44.344449</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>-96.79823709999999</v>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>9b7d5de4753a514b</t>
         </is>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>AssistantProfessorofTransportationEngineering</t>
+          <t>Assistant/Associate Professor of Civil Engineering (Transportation)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>AcademicKeys Listed Institution</t>
+          <t>Trine University</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Transportation Engineering</t>
+          <t>Allen School of Engineering &amp; Computing</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>Transportation Engineering, Civil Infrastructure, Traffic Systems</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>Unspecified</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Review begins immediately / Open</t>
+          <t>Angola, IN</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>Assistant Professor of Transportation Engineering South Dakota State University Civil and Environmental Engineering Brookings, South Dakota United States Date Posted Jul. 2, 2026 Deadline Aug. 16, 202...</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>https://engineering.academickeys.com/job/m4lk5asr/Assistant-Professor-of-Transportation-Engineering</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Trine University invites applications for an Assistant or Associate Professor of Civil Engineering specializing in transportation, requiring a Ph.D. in Civil Engineering or a closely related field. | Research Topics: Transportation Engineering, Civil Infrastructure, Traffic Systems</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>https://engineering.academickeys.com/job/e8akh47s/AssistantAssociate-Professor--Civil-Engineering-Transportation</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>AcademicKeys</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
@@ -779,73 +799,78 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="2" t="inlineStr"/>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>9b7d5de4753a514b</t>
+      <c r="O4" s="2" t="n">
+        <v>41.6311141</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>-85.0105982</v>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>87a4115bef0ef2e7</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Research Fellow (TransportationEngineering)</t>
+          <t>Civil, Construction and Environmental Engineering - Assistant Professor</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>AcademicKeys Listed Institution</t>
+          <t>University of Alabama</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Transportation Engineering</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+          <t>Transportation / Civil Engineering</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Unspecified</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Review begins immediately / Open</t>
+          <t>Tuscaloosa, Alabama</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>Research Fellow ( Transportation Engineering) Nanyang Technological University School of Civil and Environmental Engineering Singapore Singapore Date Posted Jun. 1, 2026 Deadline Open untill filled Po...</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>https://engineering.academickeys.com/job/liz1ks87/Research-Fellow-Transportation-Engineering</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Civil, Construction and Environmental Engineering - Assistant Professor University of Alabama Civil, Construction and Environmental Engineering Tuscaloosa, Alabama United States Date Posted Jul. 29, 2</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>https://engineering.academickeys.com/job/02ixzgls/Civil-Construction-and-Environmental-Engineering--Assistant-Professor</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>AcademicKeys</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
@@ -853,73 +878,82 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr"/>
-      <c r="O5" s="2" t="inlineStr"/>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>dfaed26f70dd7232</t>
+      <c r="O5" s="2" t="n">
+        <v>33.2120822</v>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>-87.53967350000001</v>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>f80ad2336a210f82</t>
         </is>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Project Officer (TransportationEngineering)</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>AcademicKeys Listed Institution</t>
+          <t>University of Alabama</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Transportation Engineering</t>
+          <t>Department of Civil, Construction and Environmental Engineering</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Civil Engineering, Construction Engineering, Environmental Engineering</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Tenured</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Review begins immediately / Open</t>
+          <t>Tuscaloosa, AL</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>Project Officer ( Transportation Engineering) Nanyang Technological University School of Civil and Environmental Engineering Singapore Singapore Date Posted May 8, 2026 Deadline Open untill filled Pos...</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>https://engineering.academickeys.com/job/in7p6mzx/Project-Officer-Transportation-Engineering</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>The University of Alabama seeks an Associate Professor in Civil, Construction, and Environmental Engineering holding a PhD in a related field. | Research Topics: Civil Engineering, Construction Engineering, Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>https://engineering.academickeys.com/job/w1r7nesq/Civil-Construction-and-Environmental-Engineering--Associate-Professor</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>AcademicKeys</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
@@ -927,46 +961,55 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" s="2" t="inlineStr"/>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>63eb9266e453efe9</t>
+      <c r="O6" s="2" t="n">
+        <v>33.2120822</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>-87.53967350000001</v>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>1b5f034d56841a04</t>
         </is>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Assistant/Associate Professor of Civil Engineering</t>
+          <t>Assistant Professor of Urban Planning/Geography</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Cedarville University</t>
+          <t>Loyola Marymount University</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Civil &amp; Environmental / Transportation Engineering</t>
+          <t>Department of Urban and Environmental Studies</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Urban Planning, Geography, Environmental Studies</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Cedarville, OH</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Open until filled</t>
+          <t>Los Angeles, CA</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -974,24 +1017,24 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>Assistant/Associate Professor of Civil Engineering Cedarville University Cedarville, OH Civil and Environmental Engineering Posted 10 days ago Priority</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179544290&amp;Title=Assistant%2FAssociate%20Professor%20of%20Civil%20Engineering</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>HigherEdJobs</t>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>$92,000</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Loyola Marymount University seeks a tenure-track Assistant Professor of Urban Planning/Geography with a relevant Ph.D. to conduct research and teach in the Department of Urban and Environmental Studies. | Research Topics: Urban Planning, Geography, Environmental Studies</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.chronicle.com/job/38031694/assistant-professor-of-urban-planning-geography/</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1001,50 +1044,55 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="N7" s="2" t="n">
-        <v>39.7540491</v>
-      </c>
       <c r="O7" s="2" t="n">
-        <v>-83.8170518</v>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>751c7406865a2787</t>
+        <v>33.9687824</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>-118.4182021</v>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>c13b0c3f0cf09a9e</t>
         </is>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Assistant Professor of Urban Economics</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>University of Texas at Arlington</t>
+          <t>Harvard University</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Civil &amp; Environmental / Transportation Engineering</t>
+          <t>Harvard Kennedy School of Government</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Urban Economics, Regional Economics, Urban Policy</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Arlington, TX</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Open until filled</t>
+          <t>Cambridge, MA</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1052,24 +1100,24 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>Assistant Professor University of Texas at Arlington Arlington, TX Public Administration and Policy Posted Today</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179553472&amp;Title=Assistant%20Professor</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>HigherEdJobs</t>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>$165,000 - $185,000</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>The Harvard Kennedy School invites applications for a tenure-track Assistant Professor with a PhD in economics or a related field to study urgent issues affecting U.S. cities and regions. | Research Topics: Urban Economics, Regional Economics, Urban Policy</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.chronicle.com/job/38032116/assistant-professor-urban-economics-/</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1079,75 +1127,80 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="N8" s="2" t="n">
-        <v>32.7315155</v>
-      </c>
       <c r="O8" s="2" t="n">
-        <v>-97.1171533</v>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>85da23cbf7841060</t>
+        <v>42.3657432</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>-71.12221390000001</v>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>93251b0fa8170f49</t>
         </is>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor, English (Film Studies and Contemporary U.S. Literature)</t>
+          <t>Assistant/Associate Professor of Civil Engineering (Transportation)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>University of Nevada Reno</t>
+          <t>Trine University</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Civil &amp; Environmental / Transportation Engineering</t>
+          <t>Reiners Department of Civil and Environmental Engineering</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>Transportation Engineering, Civil Engineering, Infrastructure Systems</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>Unspecified</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Reno, NV</t>
-        </is>
-      </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
+          <t>Angola, IN</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
           <t>Open until filled</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>Assistant Professor, English (Film Studies and Contemporary U.S. Literature) University of Nevada Reno Reno, NV $68,000 - $73,000 per year English and Literature Posted Today</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179553229&amp;Title=Assistant%20Professor%2C%20English%20%28Film%20Studies%20and%20Contemporary%20U%2ES%2E%20Literature%29</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>HigherEdJobs</t>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Based on qualifications</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Trine University is hiring a full-time Assistant or Associate Professor in Civil Engineering with a focus on transportation engineering, requiring a doctorate in civil engineering or a related field. | Research Topics: Transportation Engineering, Civil Engineering, Infrastructure Systems</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.chronicle.com/job/38028401/assistant-associate-professor-civil-engineering-transportation-/</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1157,50 +1210,55 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="N9" s="2" t="n">
-        <v>39.5442688</v>
-      </c>
       <c r="O9" s="2" t="n">
-        <v>-119.8163105</v>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>187a8dd6f5651753</t>
+        <v>41.6311141</v>
+      </c>
+      <c r="P9" s="2" t="n">
+        <v>-85.0105982</v>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>9f9cc58aa59ccd96</t>
         </is>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Pharmaceutical Sciences - Drug Delivery</t>
+          <t>Adjunct Faculty - Transportation Engineering</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>University of Wisconsin - Madison</t>
+          <t>Morgan State University</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Civil &amp; Environmental / Transportation Engineering</t>
+          <t>School of Engineering</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Transportation Engineering, Traffic Flow, Transportation Systems</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Madison, WI</t>
+          <t>Non-Tenure Track</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Open until filled</t>
+          <t>Baltimore, MD</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1208,24 +1266,24 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>Assistant Professor of Pharmaceutical Sciences - Drug Delivery University of Wisconsin - Madison Madison, WI Pharmacy and Pharmacology Posted Today Military</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179553111&amp;Title=Assistant%20Professor%20of%20Pharmaceutical%20Sciences%20%2D%20Drug%20Delivery</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>HigherEdJobs</t>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Competitive Salary</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Morgan State University is seeking an Adjunct Faculty member to teach courses in Transportation Engineering, requiring at least a Master's or Ph.D. in a related discipline. | Research Topics: Transportation Engineering, Traffic Flow, Transportation Systems</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.chronicle.com/job/37974518/adjunct-faculty-transportation-engineering/</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1235,50 +1293,55 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="N10" s="2" t="n">
-        <v>43.0802745</v>
-      </c>
       <c r="O10" s="2" t="n">
-        <v>-89.43095870000001</v>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>88a52598cec129d3</t>
+        <v>39.3446663</v>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>-76.5836094</v>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>3df6fb24b156d70b</t>
         </is>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Assistant/Associate Professor of Metallurgical, Materials and Biomedical Engineering</t>
+          <t>Advanced Transportation Technology Instructor, Part-time Adjunct</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>University of Texas at El Paso</t>
+          <t>Kern Community College District</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Civil &amp; Environmental / Transportation Engineering</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Advanced Transportation Technology, Automotive Technology, Vehicle Systems</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>El Paso, TX</t>
+          <t>Non-Tenure Track</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Open until filled</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1286,24 +1349,24 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>Assistant/Associate Professor of Metallurgical, Materials and Biomedical Engineering University of Texas at El Paso El Paso, TX Biological and Biomedical Engineering Posted Today</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179552602&amp;Title=Assistant%2FAssociate%20Professor%20of%20Metallurgical%2C%20Materials%20and%20Biomedical%20Engineering</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>HigherEdJobs</t>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>$65.00 Hourly</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Kern Community College District is seeking a Part-time Adjunct Instructor to teach advanced transportation technology courses. | Research Topics: Advanced Transportation Technology, Automotive Technology, Vehicle Systems</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.chronicle.com/job/38026829/advanced-transportation-technology-instructor-part-time-adjunct/</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1313,75 +1376,80 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="N11" s="2" t="n">
-        <v>31.7601001</v>
-      </c>
       <c r="O11" s="2" t="n">
-        <v>-106.4870476</v>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>a28cca356b9385b7</t>
+        <v>37.8719</v>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>-122.2585</v>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>36f117729bac62c9</t>
         </is>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Urban Planning/Geography</t>
+          <t>Assistant/Associate/Full Professor, Transportation Engineering and Systems</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Chronicle Listed University</t>
+          <t>University of Cincinnati</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Transportation / Civil Engineering</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Transportation Engineering, Transportation Systems, Systems Engineering</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>See full listing</t>
+          <t>Cincinnati, OH</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>Assistant Professor of Urban Planning/Geography Los Angeles, California (US) 92000 Loyola Marymount University Who We Are   The Department of Urban and Environmental Studies at Loyola Marymount Univer...</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>https://jobs.chronicle.com/job/38031694/assistant-professor-of-urban-planning-geography/</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>Chronicle</t>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>The University of Cincinnati seeks an open-rank faculty member in Transportation Engineering and Systems, requiring a Ph.D. in civil engineering or a related field. | Research Topics: Transportation Engineering, Transportation Systems, Systems Engineering</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/assistant-associate-full-professor-transportation-engineering-and-systems-at-university-of-cincinnati-4416744025</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1391,71 +1459,80 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr"/>
-      <c r="O12" s="2" t="inlineStr"/>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>c13b0c3f0cf09a9e</t>
+      <c r="O12" s="2" t="n">
+        <v>39.1318888</v>
+      </c>
+      <c r="P12" s="2" t="n">
+        <v>-84.51578309999999</v>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>6aa8ab000bc6f6c0</t>
         </is>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor (Urban Economics)</t>
+          <t>Assistant/Associate Professor of Civil, Architectural and Environmental Engineering</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Chronicle Listed University</t>
+          <t>Missouri University of Science and Technology</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Transportation / Civil Engineering</t>
+          <t>Department of Civil, Architectural and Environmental Engineering</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Civil Engineering, Architectural Engineering, Environmental Engineering</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>See full listing</t>
+          <t>Rolla, MO</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>Assistant Professor (Urban Economics) Cambridge, Massachusetts 165k - 185k Harvard Kennedy School of Government The Harvard Kennedy School invites applications for a junior economist who studies urgen...</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>https://jobs.chronicle.com/job/38032116/assistant-professor-urban-economics-/</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>Chronicle</t>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>Missouri University of Science and Technology invites applications for an Assistant/Associate Professor in Civil, Architectural and Environmental Engineering requiring a Ph.D. in a related engineering discipline. | Research Topics: Civil Engineering, Architectural Engineering, Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/assistant-associate-professor-civil-architectural-and-environmental-engineering-%2300096512-at-missouri-university-of-science-and-technology-4442271248</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1465,71 +1542,76 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr"/>
-      <c r="O13" s="2" t="inlineStr"/>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>93251b0fa8170f49</t>
+      <c r="O13" s="2" t="n">
+        <v>37.9532435</v>
+      </c>
+      <c r="P13" s="2" t="n">
+        <v>-91.7742667</v>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>4fad8c46021c1243</t>
         </is>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Assistant/Associate Professor - Civil Engineering (Transportation)</t>
+          <t>Assistant Professor – Urban Policy and Planning Dept., School of Arts and Sciences (Hunter College)</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Chronicle Listed University</t>
+          <t>Hunter College</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Transportation / Civil Engineering</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+          <t>Transportation Engineering</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Unspecified</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>See full listing</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
+          <t>Posted 2 months ago</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>Assistant/Associate Professor - Civil Engineering (Transportation) Angola, Indiana Rank and salary will be based on qualifications. Trine University The Reiners Department of Civil and Environmental E...</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>https://jobs.chronicle.com/job/38028401/assistant-associate-professor-civil-engineering-transportation-/</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>Chronicle</t>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assistant Professor – Urban Policy and Planning Dept., School of Arts and Sciences (Hunter College) Assistant Professor – Urban Policy and Planning Dept., School of Arts and Sciences (Hunter College) </t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-%E2%80%93-urban-policy-and-planning-dept-school-of-arts-and-sciences-hunter-college-at-hunter-college-4438624127</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1539,75 +1621,76 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr"/>
-      <c r="O14" s="2" t="inlineStr"/>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>9f9cc58aa59ccd96</t>
+      <c r="O14" s="2" t="n">
+        <v>40.7683107</v>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>-73.964406</v>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>e4e18ed629103a27</t>
         </is>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Transportation Driver</t>
+          <t>Research Assistant Professor - CYBER-CARE Consortium</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Chronicle Listed University</t>
+          <t>University of Houston</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Transportation / Civil Engineering</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+          <t>Transportation Engineering</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr"/>
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Unspecified</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>See full listing</t>
+          <t>Houston, TX</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
+          <t>Posted 4 months ago</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>Transportation Driver Massachusetts, United States Salary Not specified College of the Holy Cross Transportation Driver
-College of the Holy Cross
-Part Time
-JREQ-000628
-At Holy Cross, we are focused ...</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>https://jobs.chronicle.com/job/38025514/transportation-driver/</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>Chronicle</t>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>Research Assistant Professor - CYBER-CARE Consortium Research Assistant Professor - CYBER-CARE Consortium University of Houston Houston, TX Be an early applicant 4 months ago</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/research-assistant-professor-cyber-care-consortium-at-university-of-houston-4404319276</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1617,73 +1700,76 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="N15" s="2" t="inlineStr"/>
-      <c r="O15" s="2" t="inlineStr"/>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>3d9a59d2266115bd</t>
+      <c r="O15" s="2" t="n">
+        <v>29.7207902</v>
+      </c>
+      <c r="P15" s="2" t="n">
+        <v>-95.34406269999999</v>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>c6ee2c0289357949</t>
         </is>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Transportation Driver (Temporary)</t>
+          <t>Tenure-Track Faculty Position with a focus on Air Transportation Systems, Daytona Beach Campus</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Chronicle Listed University</t>
+          <t>Embry-Riddle Aeronautical University</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Transportation / Civil Engineering</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+          <t>Transportation Engineering</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr"/>
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Unspecified</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>See full listing</t>
+          <t>Daytona Beach, FL</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>Posted 1 month ago</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>Transportation Driver (Temporary) Lancaster, California, United States Competitive Salary Antelope Valley College DESCRIPTION
-Under the direction of the Supervisor of Campus Events and/or
-designee pr...</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>https://jobs.chronicle.com/job/37882967/transportation-driver-temporary-/</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>Chronicle</t>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>Tenure-Track Faculty Position with a focus on Air Transportation Systems, Daytona Beach Campus Tenure-Track Faculty Position with a focus on Air Transportation Systems, Daytona Beach Campus Embry-Ridd</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/tenure-track-faculty-position-with-a-focus-on-air-transportation-systems-daytona-beach-campus-at-embry-riddle-aeronautical-university-4434897662</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -1693,402 +1779,21 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr"/>
-      <c r="O16" s="2" t="inlineStr"/>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>04d2e04a6ec65549</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Assistant/Associate/Full Professor, Transportation Engineering and Systems</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>University of Cincinnati</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Transportation Engineering</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Unspecified</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Cincinnati, OH</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Posted 3 months ago</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>Assistant/Associate/Full Professor, Transportation Engineering and Systems Assistant/Associate/Full Professor, Transportation Engineering and Systems University of Cincinnati Cincinnati, OH 3 months a...</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-associate-full-professor-transportation-engineering-and-systems-at-university-of-cincinnati-4416744025</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="n">
-        <v>39.1318888</v>
-      </c>
-      <c r="O17" s="2" t="n">
-        <v>-84.51578309999999</v>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>6aa8ab000bc6f6c0</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>ASSISTANT/ASSOCIATE PROFESSOR - Civil, Architectural and Environmental Engineering #00096512</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Missouri University of Science and Technology</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Transportation Engineering</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Unspecified</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Rolla, MO</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Posted 1 week ago</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>ASSISTANT/ASSOCIATE PROFESSOR - Civil, Architectural and Environmental Engineering #00096512 ASSISTANT/ASSOCIATE PROFESSOR - Civil, Architectural and Environmental Engineering #00096512 Missouri Unive...</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-associate-professor-civil-architectural-and-environmental-engineering-%2300096512-at-missouri-university-of-science-and-technology-4442271248</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="n">
-        <v>37.9532435</v>
-      </c>
-      <c r="O18" s="2" t="n">
-        <v>-91.7742667</v>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>4fad8c46021c1243</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Assistant Professor – Urban Policy and Planning Dept., School of Arts and Sciences (Hunter College)</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Hunter College</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Transportation Engineering</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Unspecified</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>New York, NY</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Posted 2 months ago</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>Assistant Professor – Urban Policy and Planning Dept., School of Arts and Sciences (Hunter College) Assistant Professor – Urban Policy and Planning Dept., School of Arts and Sciences (Hunter College) ...</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-%E2%80%93-urban-policy-and-planning-dept-school-of-arts-and-sciences-hunter-college-at-hunter-college-4438624127</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="n">
-        <v>40.7683107</v>
-      </c>
-      <c r="O19" s="2" t="n">
-        <v>-73.964406</v>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>e4e18ed629103a27</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Research Assistant Professor - CYBER-CARE Consortium</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>University of Houston</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Transportation Engineering</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Unspecified</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Houston, TX</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Posted 4 months ago</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>Research Assistant Professor - CYBER-CARE Consortium Research Assistant Professor - CYBER-CARE Consortium University of Houston Houston, TX Be an early applicant 4 months ago</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/research-assistant-professor-cyber-care-consortium-at-university-of-houston-4404319276</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="n">
-        <v>29.7207902</v>
-      </c>
-      <c r="O20" s="2" t="n">
-        <v>-95.34406269999999</v>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>c6ee2c0289357949</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Tenure-Track Faculty Position with a focus on Air Transportation Systems, Daytona Beach Campus</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Embry-Riddle Aeronautical University</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Transportation Engineering</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Unspecified</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Daytona Beach, FL</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Posted 1 month ago</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>Tenure-Track Faculty Position with a focus on Air Transportation Systems, Daytona Beach Campus Tenure-Track Faculty Position with a focus on Air Transportation Systems, Daytona Beach Campus Embry-Ridd...</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/tenure-track-faculty-position-with-a-focus-on-air-transportation-systems-daytona-beach-campus-at-embry-riddle-aeronautical-university-4434897662</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="n">
+      <c r="O16" s="2" t="n">
         <v>33.8082375</v>
       </c>
-      <c r="O21" s="2" t="n">
+      <c r="P16" s="2" t="n">
         <v>-118.1344224</v>
       </c>
-      <c r="P21" s="2" t="inlineStr">
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>b3c177958e0ab7a7</t>
         </is>
@@ -2096,26 +1801,21 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -461,24 +461,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:Q65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="67" customWidth="1" min="3" max="3"/>
+    <col width="68" customWidth="1" min="3" max="3"/>
     <col width="77" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="31" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="25" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
     <col width="15" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
   </cols>
@@ -633,7 +633,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assistant Professor – Urban Policy and Planning Dept., School of Arts and Sciences (Hunter College) Assistant Professor – Urban Policy and Planning Dept., School of Arts and Sciences (Hunter College) </t>
+          <t>Assistant Professor – Urban Policy and Planning Dept., School of Arts and Sciences (Hunter College) Assistant Professor – Urban Policy and Planning Dept., School of Arts and Sciences (Hunter College)</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1796,6 +1796,3949 @@
       <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>b3c177958e0ab7a7</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Renewable Contract Full Professor of Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>University of Alabama</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Department of Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Mechanical Engineering, Thermal-Fluid Systems, Mechanical Systems</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Non-Tenure Track</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Tuscaloosa, AL</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>The Department of Mechanical Engineering at the University of Alabama is seeking a Renewable Contract Full Professor, requiring a PhD in Mechanical Engineering or a related field. | Research Topics: Mechanical Engineering, Thermal-Fluid Systems, Mechanical Systems</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>https://engineering.academickeys.com/job/xjyhz108/Mechanical-Engineering--Renewable-Contract-Full-Professor</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>AcademicKeys</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="n">
+        <v>33.2120822</v>
+      </c>
+      <c r="P17" s="2" t="n">
+        <v>-87.53967350000001</v>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>5bd795b72f025512</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Professor / Associate Professor in Maritime Studies</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Nanyang Technological University</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>School of Civil and Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Maritime Studies, Maritime Logistics, Port Operations, Shipping</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Tenure-Track</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>Nanyang Technological University invites applications for tenure-track and practice-track faculty positions in Maritime Studies within the School of Civil and Environmental Engineering, requiring a PhD in a relevant discipline. | Research Topics: Maritime Studies, Maritime Logistics, Port Operations, Shipping</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>https://engineering.academickeys.com/job/m80x7utf/Assistant-Professor--Associate-Professor-TenureTrack-Associate-Professor-PracticeTrack-in-Maritime-Studies</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>AcademicKeys</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v>1.357107</v>
+      </c>
+      <c r="P18" s="2" t="n">
+        <v>103.8194992</v>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>6736da1a934c5c83</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Professor / Associate Professor in Civil and Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Nanyang Technological University</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Civil and Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Civil Engineering, Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Tenure-Track</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>Nanyang Technological University seeks candidates for a tenure-track Assistant or Associate Professor position in Civil and Environmental Engineering, requiring a PhD in a relevant field. | Research Topics: Civil Engineering, Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>https://engineering.academickeys.com/job/dhzin0q4/Assistant-Professor--Associate-Professor-TenureTrack-in-Civil-and-Environmental-Engineering</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>AcademicKeys</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="n">
+        <v>1.357107</v>
+      </c>
+      <c r="P19" s="2" t="n">
+        <v>103.8194992</v>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>3fa57c30724444e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Montana State University</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Mechanical and Industrial Engineering</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Mechanical Engineering, Industrial Engineering</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Tenure-Track</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Bozeman, MT</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>Montana State University seeks an Assistant Professor of Mechanical Engineering within the Department of Mechanical and Industrial Engineering, requiring a Ph.D. in a related field. | Research Topics: Mechanical Engineering, Industrial Engineering</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>https://engineering.academickeys.com/job/ruoe4wlz/Assistant-Professor-of-Mechanical-Engineering</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>AcademicKeys</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v>45.6639222</v>
+      </c>
+      <c r="P20" s="2" t="n">
+        <v>-111.079277</v>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>735f106baf0ccc18</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Assistant / Associate / Full Professor of Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Auburn University</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Department of Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Mechanical Engineering, Systems Engineering, Dynamics and Controls</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Auburn, AL</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>Auburn University invites applications for an open-rank faculty position in Mechanical Engineering starting August 2026, requiring a Ph.D. in Mechanical Engineering or a related field. | Research Topics: Mechanical Engineering, Systems Engineering, Dynamics and Controls</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>https://engineering.academickeys.com/job/f320isty/AssistantAssociateFull-Professor</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>AcademicKeys</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="n">
+        <v>32.5919529</v>
+      </c>
+      <c r="P21" s="2" t="n">
+        <v>-85.4959775</v>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>c08698a4bf95171b</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Assistant / Associate / Full Professor</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Auburn University</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Department of Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Mechanical Engineering, Systems Engineering</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Tenure-Track</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Auburn, AL</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>Auburn University invites applications for an open-rank faculty position in Mechanical Engineering starting August 2026, requiring a Ph.D. in a relevant engineering discipline. | Research Topics: Mechanical Engineering, Systems Engineering</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>https://engineering.academickeys.com/job/uypo7ria/AssistantAssociateFull-Professor</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>AcademicKeys</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v>32.5919529</v>
+      </c>
+      <c r="P22" s="2" t="n">
+        <v>-85.4959775</v>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>ba0c2e06d99f3d36</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Assistant / Associate Professor, Industrial and Systems Engineering</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>University of Washington</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Industrial &amp; Systems Engineering</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Systems Engineering, Industrial Engineering, Operations Research</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Tenure-Track</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>The University of Washington invites applications for a faculty position in Industrial and Systems Engineering with a focus on systems engineering, requiring a PhD in industrial engineering, systems engineering, or a closely related field. | Research Topics: Systems Engineering, Industrial Engineering, Operations Research</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>https://engineering.academickeys.com/job/g4m97a60/AssistantAssociate-Professor-Industrial-and-Systems-Engineering-Systems-Engineering-Focus</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>AcademicKeys</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="n">
+        <v>47.6553</v>
+      </c>
+      <c r="P23" s="2" t="n">
+        <v>-122.3035</v>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>9d5682cf4dbca334</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Tenure-Track Faculty (Open Rank)</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>University of Notre Dame</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Department of Aerospace and Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Aerospace Engineering, Mechanical Engineering, Systems Engineering</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Tenure-Track</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Notre Dame, IN</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>The University of Notre Dame invites applications for an open-rank, tenure-track faculty position across all areas of aerospace and mechanical engineering, requiring an earned Ph.D. in engineering or a closely related field. | Research Topics: Aerospace Engineering, Mechanical Engineering, Systems Engineering</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>http://engineering.academickeys.com/job/b59jfimr/TenureTrack-Faculty-Open-Rank--all-areas</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>AcademicKeys</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="n">
+        <v>41.7045677</v>
+      </c>
+      <c r="P24" s="2" t="n">
+        <v>-86.23822029999999</v>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>8f71db0119b0789c</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Small-scale Engineering</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>ETH Zurich</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Department of Mechanical and Process Engineering</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Small-scale Engineering, Mechanical Engineering, Process Engineering</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Tenure-Track</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Zurich, Switzerland</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>ETH Zurich seeks a tenure-track Assistant Professor of Small-scale Engineering in the Department of Mechanical and Process Engineering, requiring a doctorate in a related field. | Research Topics: Small-scale Engineering, Mechanical Engineering, Process Engineering</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>http://engineering.academickeys.com/job/cj6ipqsy/Assistant-Professor-Tenure-Track-of-Smallscale-Engineering</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>AcademicKeys</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="n">
+        <v>47.3744489</v>
+      </c>
+      <c r="P25" s="2" t="n">
+        <v>8.5410422</v>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>a793ffff0ac6ae95</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Professor &amp; Department Chair</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>University of Pittsburgh</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Department of Electrical and Computer Engineering</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Electrical Engineering, Computer Engineering</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Tenured</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>The University of Pittsburgh seeks a Professor &amp; Department Chair to lead the Department of Electrical and Computer Engineering, requiring a Ph.D. in a relevant discipline. | Research Topics: Electrical Engineering, Computer Engineering</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>http://engineering.academickeys.com/job/vhlo0w6p/Professor--Department-Chair--Electrical-and-Computer-Engineering</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>AcademicKeys</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="n">
+        <v>40.444153</v>
+      </c>
+      <c r="P26" s="2" t="n">
+        <v>-79.962461</v>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>17acd4b4e7207871</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Senior Lecturer (Biomedical Engineering)</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>University of Western Australia</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>School of Engineering</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Biomedical Engineering, Biomechanics, Medical Devices</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Perth, Australia</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>The University of Western Australia invites applications for a Senior Lecturer in Biomedical Engineering position requiring a PhD in Biomedical Engineering or a related discipline. | Research Topics: Biomedical Engineering, Biomechanics, Medical Devices</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>http://engineering.academickeys.com/job/sxjqk9ic/Senior-Lecturer-Biomedical-Engineering</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>AcademicKeys</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="n">
+        <v>-31.9558967</v>
+      </c>
+      <c r="P27" s="2" t="n">
+        <v>115.8605784</v>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>520bf89b522e2bfe</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Lecturer in Discipline or Senior Lecturer in Discipline</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Columbia University</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Department of Industrial Engineering and Operations Research</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Industrial Engineering, Operations Research</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Non-Tenure Track</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>Columbia University's Department of Industrial Engineering and Operations Research invites applications for a teaching-focused Lecturer in Discipline position requiring a Ph.D. or equivalent doctoral degree. | Research Topics: Industrial Engineering, Operations Research</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>http://engineering.academickeys.com/job/arsy3jqh/Open-Rank-Lecturer-in-Discipline-or-Senior-Lecturer-in-Discipline</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>AcademicKeys</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="n">
+        <v>40.8077507</v>
+      </c>
+      <c r="P28" s="2" t="n">
+        <v>-73.9624901</v>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>f11b4a4e74422ae3</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Assistant/Associate Professor of Civil Engineering</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Cedarville University</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Civil and Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Civil Engineering, Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Cedarville, OH</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>Cedarville University invites applications for an Assistant/Associate Professor of Civil Engineering position, typically requiring a Ph.D. in civil engineering or a related field. | Research Topics: Civil Engineering, Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179544290&amp;Title=Assistant%2FAssociate%20Professor%20of%20Civil%20Engineering</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>HigherEdJobs</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="n">
+        <v>39.7540491</v>
+      </c>
+      <c r="P29" s="2" t="n">
+        <v>-83.8170518</v>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>751c7406865a2787</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Professor</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>University of Texas at Arlington</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Department of Public Administration and Policy</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Public Administration, Public Policy, Transportation Policy</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Tenure-Track</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Arlington, TX</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>The University of Texas at Arlington invites applications for an Assistant Professor position in Public Administration and Policy, requiring a Ph.D. in a relevant discipline. | Research Topics: Public Administration, Public Policy, Transportation Policy</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179553472&amp;Title=Assistant%20Professor</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>HigherEdJobs</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="n">
+        <v>32.7315155</v>
+      </c>
+      <c r="P30" s="2" t="n">
+        <v>-97.1171533</v>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>85da23cbf7841060</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Professor, English (Film Studies and Contemporary U.S. Literature)</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>University of Nevada, Reno</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Department of English</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Film Studies, Contemporary U.S. Literature</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Tenure-Track</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Reno, NV</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>$68,000 - $73,000 per year</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>The University of Nevada, Reno is hiring an Assistant Professor of English focused on Film Studies and Contemporary U.S. Literature, requiring a doctorate in English or a closely related discipline. | Research Topics: Film Studies, Contemporary U.S. Literature</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179553229&amp;Title=Assistant%20Professor%2C%20English%20%28Film%20Studies%20and%20Contemporary%20U%2ES%2E%20Literature%29</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>HigherEdJobs</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="n">
+        <v>39.5442688</v>
+      </c>
+      <c r="P31" s="2" t="n">
+        <v>-119.8163105</v>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>187a8dd6f5651753</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Pharmaceutical Sciences - Drug Delivery</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>University of Wisconsin - Madison</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacy and Pharmacology</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Drug Delivery, Pharmaceutical Sciences, Pharmacology</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Tenure-Track</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Madison, WI</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>The University of Wisconsin - Madison is seeking an Assistant Professor focused on pharmaceutical sciences and drug delivery, requiring a PhD or equivalent doctoral degree. | Research Topics: Drug Delivery, Pharmaceutical Sciences, Pharmacology</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179553111&amp;Title=Assistant%20Professor%20of%20Pharmaceutical%20Sciences%20%2D%20Drug%20Delivery</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>HigherEdJobs</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="n">
+        <v>43.0802745</v>
+      </c>
+      <c r="P32" s="2" t="n">
+        <v>-89.43095870000001</v>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>88a52598cec129d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Assistant/Associate Professor of Metallurgical, Materials and Biomedical Engineering</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>University of Texas at El Paso</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Department of Metallurgical, Materials and Biomedical Engineering</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Metallurgical Engineering, Materials Engineering, Biomedical Engineering</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Tenure-Track</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>El Paso, TX</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>The University of Texas at El Paso invites applications for an Assistant or Associate Professor position in Metallurgical, Materials, and Biomedical Engineering requiring a Ph.D. in a related field. | Research Topics: Metallurgical Engineering, Materials Engineering, Biomedical Engineering</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179552602&amp;Title=Assistant%2FAssociate%20Professor%20of%20Metallurgical%2C%20Materials%20and%20Biomedical%20Engineering</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>HigherEdJobs</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="n">
+        <v>31.7601001</v>
+      </c>
+      <c r="P33" s="2" t="n">
+        <v>-106.4870476</v>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>a28cca356b9385b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Professor - IDS (Supply Chain &amp; Operations Management)</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>University of Illinois Chicago</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Information and Decision Sciences</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Management, Operations Management, Decision Sciences</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Tenure-Track</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Chicago, IL</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>The University of Illinois Chicago is recruiting an Assistant Professor in Information and Decision Sciences focusing on Supply Chain &amp; Operations Management, requiring a doctorate in a related discipline. | Research Topics: Supply Chain Management, Operations Management, Decision Sciences</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179552436&amp;Title=Assistant%20Professor%20%2D%20IDS%20%28Supply%20Chain%20%26%20Operations%20Management%29</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>HigherEdJobs</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="n">
+        <v>41.8748613</v>
+      </c>
+      <c r="P34" s="2" t="n">
+        <v>-87.6519866</v>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>77e0632bd4e74eae</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Tenured/Tenure-Track Faculty Position</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>New York University</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Rory Meyers College of Nursing</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Nursing, Healthcare, Health Sciences</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Tenure-Track</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>$107,228 - $167,228 per year</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>New York University invites applications for a tenured or tenure-track faculty position in the Rory Meyers College of Nursing, requiring a research doctorate (PhD or equivalent) in nursing or a related field. | Research Topics: Nursing, Healthcare, Health Sciences</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179550658&amp;Title=NYU%20Rory%20Meyers%20College%20of%20Nursing%20%2D%20Tenured%2FTenure%2DTrack%20Faculty%20Position%5FAY%202026%2D2027</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>HigherEdJobs</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="n">
+        <v>40.7292053</v>
+      </c>
+      <c r="P35" s="2" t="n">
+        <v>-73.99501480000001</v>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>3b38c37b905c5dbe</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Professor, Associate Professor, or Assistant Professor of Industrial and Systems Engineering</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Auburn University</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Department of Industrial and Systems Engineering</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Industrial Engineering, Systems Engineering, Manufacturing Engineering</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Tenure-Track</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Auburn, AL</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>$80,000 - $180,000 per year</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>Auburn University is seeking candidates for an open-rank faculty position in Industrial and Systems Engineering, requiring a doctorate in industrial engineering or a related field. | Research Topics: Industrial Engineering, Systems Engineering, Manufacturing Engineering</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179548357&amp;Title=Professor%2C%20Associate%20Professor%2C%20Assistant%20Professor%20%2D%20Industrial%20and%20Systems%20Engineering</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>HigherEdJobs</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="n">
+        <v>32.5919529</v>
+      </c>
+      <c r="P36" s="2" t="n">
+        <v>-85.4959775</v>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>d0f23a527bf71c22</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Teaching Assistant Professor or Lecturer, Construction Engineering and Management</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>University of Tennessee, Knoxville</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Civil and Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Construction Engineering, Construction Management, Civil Engineering</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Non-Tenure Track</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Knoxville, TN</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>The Department of Civil and Environmental Engineering at the University of Tennessee, Knoxville invites applications for a teaching-focused faculty position in Construction Engineering and Management beginning Spring 2027. | Research Topics: Construction Engineering, Construction Management, Civil Engineering</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179547216&amp;Title=Teaching%20Assistant%20Professor%20or%20Lecturer%2C%20Construction%20Engineering%20and%20Management%2C%20Spring%202027</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>HigherEdJobs</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="n">
+        <v>35.9516352</v>
+      </c>
+      <c r="P37" s="2" t="n">
+        <v>-83.9308819</v>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>947b5e96db5e6c60</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Assistant/Associate/Full Professor, Dublin Innovation Institute</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Northeastern University</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Civil &amp; Environmental / Transportation Engineering</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Boston, MA</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>Assistant/Associate/Full Professor, Dublin Innovation Institute Northeastern University Boston, MA Political Science Posted 9 days ago</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179547014&amp;Title=Assistant%2FAssociate%2FFull%20Professor%2C%20Dublin%20Innovation%20Institute</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>HigherEdJobs</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="n">
+        <v>42.3351065</v>
+      </c>
+      <c r="P38" s="2" t="n">
+        <v>-71.0892575</v>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>b017a7af093b678d</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Professor, English</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>University of Nevada Reno</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Civil &amp; Environmental / Transportation Engineering</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr"/>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Reno, NV</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>Assistant Professor, English University of Nevada Reno Reno, NV $68,000 - $73,000 per year English and Literature Posted 9 days ago</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179546765&amp;Title=Assistant%20Professor%2C%20English</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>HigherEdJobs</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="n">
+        <v>39.5442688</v>
+      </c>
+      <c r="P39" s="2" t="n">
+        <v>-119.8163105</v>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>5e48ceadc81def6f</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Bilingual Education  (Teacher Preparation Faculty – BLE)</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Heritage University</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Civil &amp; Environmental / Transportation Engineering</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr"/>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Toppenish, WA</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Bilingual Education  (Teacher Preparation Faculty – BLE) Heritage University Toppenish, WA $69,519 - $72,519 per year Teacher Education Posted 10 days ago</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179545717&amp;Title=Assistant%20Professor%20of%20Bilingual%20Education%20%20%28Teacher%20Preparation%20Faculty%20%E2%80%93%20BLE%29</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>HigherEdJobs</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="n">
+        <v>46.3741532</v>
+      </c>
+      <c r="P40" s="2" t="n">
+        <v>-120.3942755</v>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>b150880d7bf70d02</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Tenure-Track Assistant Professor of Industrial and Systems Engineering, Fall 2027 (1/3)</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>University of Tennessee, Knoxville</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Civil &amp; Environmental / Transportation Engineering</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr"/>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Knoxville, TN</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>Tenure-Track Assistant Professor of Industrial and Systems Engineering, Fall 2027 (1/3) University of Tennessee, Knoxville Knoxville, TN Industrial and Manufacturing Engineering Posted 10 days ago</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179545449&amp;Title=Tenure%2DTrack%20Assistant%20Professor%20of%20Industrial%20and%20Systems%20Engineering%2C%20Fall%202027%20%281%2F3%29</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>HigherEdJobs</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="n">
+        <v>35.9516352</v>
+      </c>
+      <c r="P41" s="2" t="n">
+        <v>-83.9308819</v>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>ecd34777430b7c8d</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Civil Engineering</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>McNeese State University</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Civil &amp; Environmental / Transportation Engineering</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr"/>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Lake Charles, LA</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Civil Engineering McNeese State University Lake Charles, LA $76,000 per year Civil and Environmental Engineering Posted 10 days ago</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179545361&amp;Title=Assistant%20Professor%20of%20Civil%20Engineering</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>HigherEdJobs</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="n">
+        <v>30.1751363</v>
+      </c>
+      <c r="P42" s="2" t="n">
+        <v>-93.2112786</v>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>bd292fb9f52ac2e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="24" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Montana State University</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Civil &amp; Environmental / Transportation Engineering</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr"/>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Bozeman, MT</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Mechanical Engineering Montana State University Bozeman, MT Salary commensurate with experience, education, and qualifications Mechanical Engineering Posted 11 days ago</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179544064&amp;Title=Assistant%20Professor%20of%20Mechanical%20Engineering</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>HigherEdJobs</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="n">
+        <v>45.6639222</v>
+      </c>
+      <c r="P43" s="2" t="n">
+        <v>-111.079277</v>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>55cafc053dd408d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="24" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Construction Science and Management for Advanced Manufacturing for Affordable Building Construction - Research Assistant/Associate/Full Professor</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>University of Tennessee, Knoxville</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Civil &amp; Environmental / Transportation Engineering</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Knoxville, TN</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>Construction Science and Management for Advanced Manufacturing for Affordable Building Construction - Research Assistant/Associate/Full Professor University of Tennessee, Knoxville Knoxville, TN Const</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179543068&amp;Title=Construction%20Science%20and%20Management%20for%20Advanced%20Manufacturing%20for%20Affordable%20Building%20Construction%20%2D%20Research%20Assistant%2FAssociate%2FFull%20Professor</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>HigherEdJobs</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="n">
+        <v>35.9516352</v>
+      </c>
+      <c r="P44" s="2" t="n">
+        <v>-83.9308819</v>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>e0804d6b64754a04</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="24" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Robotics and Automation for Advanced Manufacturing for Affordable Building Construction - Research Assistant/Associate/Full Professor</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>University of Tennessee, Knoxville</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Civil &amp; Environmental / Transportation Engineering</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr"/>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Knoxville, TN</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>Robotics and Automation for Advanced Manufacturing for Affordable Building Construction - Research Assistant/Associate/Full Professor University of Tennessee, Knoxville Knoxville, TN Industrial and Ma</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179543067&amp;Title=Robotics%20and%20Automation%20for%20Advanced%20Manufacturing%20for%20Affordable%20Building%20Construction%20%2D%20Research%20Assistant%2FAssociate%2FFull%20Professor</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>HigherEdJobs</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="n">
+        <v>35.9516352</v>
+      </c>
+      <c r="P45" s="2" t="n">
+        <v>-83.9308819</v>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>67e7cb2c4f0d9666</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="24" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Professor - Aerospace Engineering</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>University of Kansas</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Civil &amp; Environmental / Transportation Engineering</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr"/>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Lawrence, KS</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>Assistant Professor - Aerospace Engineering University of Kansas Lawrence, KS Aerospace Engineering Posted 15 days ago</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179541995&amp;Title=Assistant%20Professor%20%2D%20Aerospace%20Engineering</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>HigherEdJobs</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="n">
+        <v>38.9535052</v>
+      </c>
+      <c r="P46" s="2" t="n">
+        <v>-95.263093</v>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>ab72a079a661c8d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="24" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Teaching Assistant Professor</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>University of Arkansas</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Civil &amp; Environmental / Transportation Engineering</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr"/>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Fayetteville, AR</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>Teaching Assistant Professor University of Arkansas Fayetteville, AR Commensurate with education and experience Accounting Posted 15 days ago</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179541925&amp;Title=Teaching%20Assistant%20Professor</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>HigherEdJobs</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="n">
+        <v>36.0970389</v>
+      </c>
+      <c r="P47" s="2" t="n">
+        <v>-94.1703322</v>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>8b28f5b58e7e3607</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="24" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Political Science</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Wellesley College</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Civil &amp; Environmental / Transportation Engineering</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr"/>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Wellesley, MA</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Political Science Wellesley College Wellesley, MA Starting at $103,000 per year Political Science Posted 15 days ago</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179541568&amp;Title=Assistant%20Professor%20of%20Political%20Science</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>HigherEdJobs</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="n">
+        <v>42.2895485</v>
+      </c>
+      <c r="P48" s="2" t="n">
+        <v>-71.3144942</v>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>7c6e64c1e90a63e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="24" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Faculty Recruitment Announcement – Department of Civil Engineering, National Taiwan University</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Chronicle Listed University</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Transportation / Civil Engineering</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr"/>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>See full listing</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>Faculty Recruitment Announcement – Department of Civil Engineering, National Taiwan University Taipei, Taiwan Monthly salary: NT$83,720–137,370, depending on academic rank, qualifications, experience,</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.chronicle.com/job/38034402/faculty-recruitment-announcement-department-of-civil-engineering-national-taiwan-university/</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>Chronicle</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr"/>
+      <c r="P49" s="2" t="inlineStr"/>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>f056997ace2e1de7</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="24" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Tenure-Track Faculty Position with a focus on Air Transportation Systems, Daytona Beach Campus</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Chronicle Listed University</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Transportation / Civil Engineering</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr"/>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>See full listing</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>Tenure-Track Faculty Position with a focus on Air Transportation Systems, Daytona Beach Campus Daytona Beach, Florida, United States Competitive Salary Embry-Riddle Aeronautical University Job Descrip</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.chronicle.com/job/38012134/tenure-track-faculty-position-with-a-focus-on-air-transportation-systems-daytona-beach-campus/</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>Chronicle</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr"/>
+      <c r="P50" s="2" t="inlineStr"/>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>52969a207999417a</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="24" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Professional Practice Assistant Professor - Air Traffic Control</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Utah State University</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Transportation Engineering</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr"/>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Logan, UT</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Posted 1 week ago</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>Professional Practice Assistant Professor - Air Traffic Control Professional Practice Assistant Professor - Air Traffic Control Utah State University Logan, UT Be an early applicant 1 week ago</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/professional-practice-assistant-professor-air-traffic-control-at-utah-state-university-4462897860</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="n">
+        <v>41.7526959</v>
+      </c>
+      <c r="P51" s="2" t="n">
+        <v>-111.808733</v>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>02b944bc9d0177ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="24" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Teaching</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Florida Atlantic University</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Transportation Engineering</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr"/>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Boca Raton, FL</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Posted 4 months ago</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Teaching Assistant Professor of Teaching Florida Atlantic University Boca Raton, FL 4 months ago</t>
+        </is>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-of-teaching-at-florida-atlantic-university-4414964381</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="n">
+        <v>26.1194058</v>
+      </c>
+      <c r="P52" s="2" t="n">
+        <v>-80.14167999999999</v>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>7bdaa996cf64d1f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="24" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Tenure Track Assistant Professor of Meteorology, Applied Aviation Sciences, College of Aviation, Daytona Beach Campus</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Embry-Riddle Aeronautical University</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Transportation Engineering</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr"/>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Daytona Beach, FL</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Posted 1 week ago</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>Tenure Track Assistant Professor of Meteorology, Applied Aviation Sciences, College of Aviation, Daytona Beach Campus Tenure Track Assistant Professor of Meteorology, Applied Aviation Sciences, Colleg</t>
+        </is>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/tenure-track-assistant-professor-of-meteorology-applied-aviation-sciences-college-of-aviation-daytona-beach-campus-at-embry-riddle-aeronautical-university-4461419176</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="n">
+        <v>33.8082375</v>
+      </c>
+      <c r="P53" s="2" t="n">
+        <v>-118.1344224</v>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>2f2314fa17a45e15</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="24" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Assistant or Associate Professor (Open Rank)</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>University of Arkansas ­- Sam M. Walton College of Business</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Transportation Engineering</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr"/>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Fayetteville, AR</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Posted 2 weeks ago</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>Assistant or Associate Professor (Open Rank) Assistant or Associate Professor (Open Rank) University of Arkansas ­- Sam M. Walton College of Business Fayetteville, AR Be an early applicant 2 weeks ago</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/assistant-or-associate-professor-open-rank-at-university-of-arkansas-%C2%AD-sam-m-walton-college-of-business-4460111187</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="n">
+        <v>36.0625843</v>
+      </c>
+      <c r="P54" s="2" t="n">
+        <v>-94.1574328</v>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>c16a694d5f7f68d4</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="24" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Professor - Aerospace Engineering</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>The University of Kansas</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Transportation Engineering</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr"/>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Lawrence, KS</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Posted 10 hours ago</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>Assistant Professor - Aerospace Engineering Assistant Professor - Aerospace Engineering The University of Kansas Lawrence, KS Be an early applicant 10 hours ago</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-aerospace-engineering-at-the-university-of-kansas-4460398978</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="n">
+        <v>39.0559267</v>
+      </c>
+      <c r="P55" s="2" t="n">
+        <v>-94.6090332</v>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>4a53cfad86712a72</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="24" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Electrical and Computer Engineering</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>The University of Texas at El Paso</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Transportation Engineering</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr"/>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>El Paso, TX</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Posted 2 days ago</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Electrical and Computer Engineering Assistant Professor of Electrical and Computer Engineering The University of Texas at El Paso El Paso, TX Be an early applicant 2 days ago</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-of-electrical-and-computer-engineering-at-the-university-of-texas-at-el-paso-4465369446</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="n">
+        <v>31.7757794</v>
+      </c>
+      <c r="P56" s="2" t="n">
+        <v>-106.5078652</v>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>8b1761788d4a46f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="24" customHeight="1">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Tenure-Track: Assistant or Associate Professor (Dynamics &amp; Control)</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Texas A&amp;M University</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Transportation Engineering</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr"/>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>College Station, TX</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Posted 20 hours ago</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>Tenure-Track: Assistant or Associate Professor (Dynamics &amp; Control) Tenure-Track: Assistant or Associate Professor (Dynamics &amp; Control) Texas A&amp;M University College Station, TX Be an early applicant 2</t>
+        </is>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/tenure-track-assistant-or-associate-professor-dynamics-control-at-texas-a-m-university-4457057729</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="n">
+        <v>30.6187</v>
+      </c>
+      <c r="P57" s="2" t="n">
+        <v>-96.3365</v>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>669ed2b0fff91e2f</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="24" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>ASSISTANT/ASSOCIATE/FULL PROFESSOR - Industrial &amp; Systems Engineering</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>University of Florida</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Transportation Engineering</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr"/>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Gainesville, FL</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Posted 9 months ago</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>ASSISTANT/ASSOCIATE/FULL PROFESSOR - Industrial &amp; Systems Engineering ASSISTANT/ASSOCIATE/FULL PROFESSOR - Industrial &amp; Systems Engineering University of Florida Gainesville, FL Actively Hiring 9 mont</t>
+        </is>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/assistant-associate-full-professor-industrial-systems-engineering-at-university-of-florida-4323668785</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="n">
+        <v>29.6436</v>
+      </c>
+      <c r="P58" s="2" t="n">
+        <v>-82.3549</v>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>56d501f448e77e05</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="24" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Professor (Two Open Positions)</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>University of Arkansas ­- Sam M. Walton College of Business</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Transportation Engineering</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr"/>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Fayetteville, AR</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Posted 2 weeks ago</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>Assistant Professor (Two Open Positions) Assistant Professor (Two Open Positions) University of Arkansas ­- Sam M. Walton College of Business Fayetteville, AR Be an early applicant 2 weeks ago</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-two-open-positions-at-university-of-arkansas-%C2%AD-sam-m-walton-college-of-business-4460109211</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="n">
+        <v>36.0625843</v>
+      </c>
+      <c r="P59" s="2" t="n">
+        <v>-94.1574328</v>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>8b974c86c7dfa1c1</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="24" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Professor in Supply Chain Management</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Iowa State University - Ivy College of Business</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Transportation Engineering</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr"/>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Ames, IA</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>Posted 1 month ago</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>Assistant Professor in Supply Chain Management Assistant Professor in Supply Chain Management Iowa State University - Ivy College of Business Ames, IA Be an early applicant 1 month ago</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-in-supply-chain-management-at-iowa-state-university-ivy-college-of-business-4440811209</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="n">
+        <v>42.0267567</v>
+      </c>
+      <c r="P60" s="2" t="n">
+        <v>-93.6170448</v>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>e994e392d38b77ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="24" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Professor - Aerospace Engineering</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Center for Public Partnerships &amp; Research</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Transportation Engineering</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr"/>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>Topeka Metropolitan Area</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>Posted 2 weeks ago</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>Assistant Professor - Aerospace Engineering Assistant Professor - Aerospace Engineering Center for Public Partnerships &amp; Research Topeka Metropolitan Area Be an early applicant 2 weeks ago</t>
+        </is>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-aerospace-engineering-at-center-for-public-partnerships-research-4460516009</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr"/>
+      <c r="P61" s="2" t="inlineStr"/>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>2a4d376b988084d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="24" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Professor - Air Traffic Control</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Tulsa Community College</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Transportation Engineering</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr"/>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Tulsa, OK</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Posted 2 weeks ago</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>Assistant Professor - Air Traffic Control Assistant Professor - Air Traffic Control Tulsa Community College Tulsa, OK Be an early applicant 2 weeks ago</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-air-traffic-control-at-tulsa-community-college-4458672005</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="n">
+        <v>36.1946011</v>
+      </c>
+      <c r="P62" s="2" t="n">
+        <v>-95.9374648</v>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>283b856ef808fa3c</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="24" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Professor – IDS (Supply Chain &amp; Operations Management)</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>University of Illinois Chicago</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Transportation Engineering</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr"/>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>Chicago, IL</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>Posted 1 week ago</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>Assistant Professor – IDS (Supply Chain &amp; Operations Management) Assistant Professor – IDS (Supply Chain &amp; Operations Management) University of Illinois Chicago Chicago, IL Be an early applicant 1 wee</t>
+        </is>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-%E2%80%93-ids-supply-chain-operations-management-at-university-of-illinois-chicago-4463632919</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="n">
+        <v>41.8748613</v>
+      </c>
+      <c r="P63" s="2" t="n">
+        <v>-87.6519866</v>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>d58da246ce5b68ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="24" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Professor</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>The University of Texas at Arlington</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Transportation Engineering</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr"/>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Arlington, TX</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>Posted 1 week ago</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>Assistant Professor Assistant Professor The University of Texas at Arlington Arlington, TX 1 week ago</t>
+        </is>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-at-the-university-of-texas-at-arlington-4397332037</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="n">
+        <v>32.7284713</v>
+      </c>
+      <c r="P64" s="2" t="n">
+        <v>-97.11202129999999</v>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>8f5d66dcdfbbc7fd</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="24" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Public Policy (Market-Based Solutions to Societal Challenges)</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>UW-Madison College of Letters &amp; Science</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Transportation Engineering</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr"/>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>Madison, WI</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Posted 1 week ago</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assistant Professor of Public Policy (Market-Based Solutions to Societal Challenges) Assistant Professor of Public Policy (Market-Based Solutions to Societal Challenges) UW-Madison College of Letters </t>
+        </is>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-of-public-policy-market-based-solutions-to-societal-challenges-at-uw-madison-college-of-letters-science-4435310692</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="n">
+        <v>43.07469</v>
+      </c>
+      <c r="P65" s="2" t="n">
+        <v>-89.3841663</v>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>886b76b05d362fdc</t>
         </is>
       </c>
     </row>
@@ -1816,6 +5759,55 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J65" r:id="rId64"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S33"/>
+  <dimension ref="A1:S39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -503,7 +503,7 @@
     <col width="32" customWidth="1" min="5" max="5"/>
     <col width="151" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
     <col width="83" customWidth="1" min="9" max="9"/>
     <col width="47" customWidth="1" min="10" max="10"/>
     <col width="42" customWidth="1" min="11" max="11"/>
@@ -685,7 +685,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="P2" s="5" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="P3" s="5" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="P5" s="5" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="P6" s="5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="P7" s="5" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="P8" s="5" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="P9" s="5" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="P10" s="5" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="P11" s="5" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="P12" s="5" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="P15" s="5" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="P16" s="5" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="P17" s="5" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="P18" s="5" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="P20" s="5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="P21" s="5" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="P22" s="5" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="P23" s="5" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="P24" s="5" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="P25" s="5" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="P27" s="5" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="P28" s="5" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="P30" s="5" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="P33" s="5" t="inlineStr">
@@ -3523,6 +3523,552 @@
       <c r="S33" s="2" t="inlineStr">
         <is>
           <t>886b76b05d362fdc</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Civil, Construction and Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>University of Alabama</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Civil, Construction and Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Broad Civil, Construction and Environmental Engineering faculty search where transportation is a potential sub-discipline within the department.</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Civil Engineering, Construction Engineering, Environmental Engineering, Transportation Engineering</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>Tenure-Track</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Tuscaloosa, AL</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>Assistant Professor position in the Department of Civil, Construction and Environmental Engineering at the University of Alabama. | Research Topics: Civil Engineering, Construction Engineering, Environmental Engineering, Transportation Engineering</t>
+        </is>
+      </c>
+      <c r="L34" s="6" t="inlineStr">
+        <is>
+          <t>https://engineering.academickeys.com/job/02ixzgls/Civil-Construction-and-Environmental-Engineering--Assistant-Professor</t>
+        </is>
+      </c>
+      <c r="M34" s="5" t="inlineStr">
+        <is>
+          <t>AcademicKeys</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="P34" s="5" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="n">
+        <v>33.2120822</v>
+      </c>
+      <c r="R34" s="2" t="n">
+        <v>-87.53967350000001</v>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>f80ad2336a210f82</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="26" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Associate Professor of Civil, Construction and Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>University of Alabama</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Department of Civil, Construction and Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Moderate fit: Broad Civil, Construction, and Environmental Engineering Associate Professor opening without an explicitly specified sub-discipline.</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Civil Engineering, Construction Engineering, Environmental Engineering, Transportation Infrastructure</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Tenured</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Tuscaloosa, AL</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>The University of Alabama invites applications for an Associate Professor position in Civil, Construction, and Environmental Engineering requiring a Ph.D. in civil engineering or a closely related field. | Research Topics: Civil Engineering, Construction Engineering, Environmental Engineering, Transportation Infrastructure</t>
+        </is>
+      </c>
+      <c r="L35" s="6" t="inlineStr">
+        <is>
+          <t>https://engineering.academickeys.com/job/w1r7nesq/Civil-Construction-and-Environmental-Engineering--Associate-Professor</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>AcademicKeys</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="P35" s="5" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="n">
+        <v>33.2120822</v>
+      </c>
+      <c r="R35" s="2" t="n">
+        <v>-87.53967350000001</v>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>1b5f034d56841a04</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="26" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Professor / Associate Professor (Tenure-Track) in Civil and Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Nanyang Technological University</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>School of Civil and Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>Moderate fit: broad Civil and Environmental Engineering search where Transportation Engineering is a potential sub-discipline, though specific subfield requirements are not detailed in the snippet.</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Civil and Environmental Engineering, Transportation Systems, Infrastructure Systems, Smart Cities</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>Tenure-Track</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Singapore, Singapore</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>Tenure-track Assistant or Associate Professor position in Civil and Environmental Engineering requiring an earned doctorate in civil engineering or a closely related discipline. | Research Topics: Civil and Environmental Engineering, Transportation Systems, Infrastructure Systems, Smart Cities</t>
+        </is>
+      </c>
+      <c r="L36" s="6" t="inlineStr">
+        <is>
+          <t>https://engineering.academickeys.com/job/dhzin0q4/Assistant-Professor--Associate-Professor-TenureTrack-in-Civil-and-Environmental-Engineering</t>
+        </is>
+      </c>
+      <c r="M36" s="5" t="inlineStr">
+        <is>
+          <t>AcademicKeys</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="P36" s="5" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="n">
+        <v>1.2899175</v>
+      </c>
+      <c r="R36" s="2" t="n">
+        <v>103.8519072</v>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>3fa57c30724444e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="26" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Multiple Faculty Positions in Computer Science and Engineering</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Texas A&amp;M University</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Department of Computer Science and Engineering</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Moderate fit: open faculty search in Computer Science and Engineering without explicit specialization in transportation or mobility systems.</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Computer Science, Computer Engineering, Artificial Intelligence, Data Science</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>College Station, TX</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>Texas A&amp;M University invites applications for multiple faculty positions in Computer Science and Engineering, requiring a Ph.D. in a relevant discipline. | Research Topics: Computer Science, Computer Engineering, Artificial Intelligence, Data Science</t>
+        </is>
+      </c>
+      <c r="L37" s="6" t="inlineStr">
+        <is>
+          <t>http://engineering.academickeys.com/job/rh7lvag4/CSE--TAMU-Multiple-Faculty-Positions</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>AcademicKeys</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="P37" s="5" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="n">
+        <v>30.6187</v>
+      </c>
+      <c r="R37" s="2" t="n">
+        <v>-96.3365</v>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>7d5d844d65485b4b</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="26" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Civil Engineering</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>McNeese State University</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Civil and Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>Moderate fit: broad Civil Engineering search where transportation is not explicitly prioritized in the snippet.</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Civil Engineering, Engineering Education</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Lake Charles, LA</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>$76,000 per year</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>Assistant Professor position in Civil and Environmental Engineering at McNeese State University with a salary of $76,000 per year. | Research Topics: Civil Engineering, Engineering Education</t>
+        </is>
+      </c>
+      <c r="L38" s="6" t="inlineStr">
+        <is>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179545361&amp;Title=Assistant%20Professor%20of%20Civil%20Engineering</t>
+        </is>
+      </c>
+      <c r="M38" s="5" t="inlineStr">
+        <is>
+          <t>HigherEdJobs</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="P38" s="5" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="n">
+        <v>30.1751363</v>
+      </c>
+      <c r="R38" s="2" t="n">
+        <v>-93.2112786</v>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>bd292fb9f52ac2e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="26" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Tenure-Track Faculty Positions in Transportation Engineering</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>National Taiwan University</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Department of Civil Engineering</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>Core match: seeks multiple tenure-track faculty positions specifically in the Transportation track within a Department of Civil Engineering.</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Transportation Engineering, Mobility Systems, Transit Planning</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>Tenure-Track</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Taipei, Taiwan</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>NT$83,720–137,370 monthly</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>The Department of Civil Engineering at National Taiwan University invites applications for multiple tenure-track faculty positions in Transportation Engineering. | Research Topics: Transportation Engineering, Mobility Systems, Transit Planning</t>
+        </is>
+      </c>
+      <c r="L39" s="6" t="inlineStr">
+        <is>
+          <t>https://jobs.chronicle.com/job/38034402/faculty-recruitment-announcement-department-of-civil-engineering-national-taiwan-university/</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>Chronicle</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="P39" s="5" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="n">
+        <v>25.0375198</v>
+      </c>
+      <c r="R39" s="2" t="n">
+        <v>121.5636796</v>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>f056997ace2e1de7</t>
         </is>
       </c>
     </row>
@@ -3560,6 +4106,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId38"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -37,12 +37,6 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00276A3C"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
       <color rgb="000563C1"/>
       <sz val="10"/>
       <u val="single"/>
@@ -50,6 +44,12 @@
     <font>
       <name val="Calibri"/>
       <color rgb="001F497D"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00276A3C"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -68,14 +68,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-        <bgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00EDF2F8"/>
+        <bgColor rgb="00EDF2F8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EDF2F8"/>
-        <bgColor rgb="00EDF2F8"/>
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -113,17 +113,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S39"/>
+  <dimension ref="A1:S35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -617,45 +617,45 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Transportation Engineering</t>
+          <t>Tenure-Track Faculty Position in Air Transportation Systems</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>University of Alabama</t>
+          <t>Chronicle Listed University</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Civil, Construction and Environmental Engineering</t>
+          <t>Air Transportation Systems (Daytona Beach Campus)</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>Core match: position is explicitly for an Assistant Professor of Transportation Engineering.</t>
+          <t>Low fit: position focuses specifically on air transportation and aviation systems rather than ground transportation, transit, or mobility systems.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Transportation Engineering, Traffic Operations, Intelligent Transportation Systems, Travel Behavior</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="inlineStr">
+          <t>Air Transportation Systems, Aviation, Transportation Management</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Tuscaloosa, AL</t>
-        </is>
-      </c>
-      <c r="I2" s="5" t="inlineStr">
-        <is>
-          <t>Open until filled</t>
+          <t>Daytona Beach, FL</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -665,22 +665,22 @@
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>The University of Alabama seeks a tenure-track Assistant Professor of Transportation Engineering requiring a Ph.D. in civil engineering or a closely related field. | Research Topics: Transportation Engineering, Traffic Operations, Intelligent Transportation Systems, Travel Behavior</t>
-        </is>
-      </c>
-      <c r="L2" s="6" t="inlineStr">
-        <is>
-          <t>https://engineering.academickeys.com/job/s9z6epb3/Civil-Construction-and-Environmental-Engineering--Transportation-Engineering--Assistant-Professor</t>
-        </is>
-      </c>
-      <c r="M2" s="5" t="inlineStr">
-        <is>
-          <t>AcademicKeys</t>
+          <t>This is a tenure-track faculty position focusing on air transportation systems at the Daytona Beach campus requiring an appropriate terminal degree. | Research Topics: Air Transportation Systems, Aviation, Transportation Management</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>https://jobs.chronicle.com/job/38012134/tenure-track-faculty-position-with-a-focus-on-air-transportation-systems-daytona-beach-campus/</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -688,63 +688,63 @@
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="P2" s="5" t="inlineStr">
+      <c r="P2" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>33.2120822</v>
+        <v>29.2108147</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>-87.53967350000001</v>
+        <v>-81.0228331</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>daabd65ea8fe188a</t>
+          <t>52969a207999417a</t>
         </is>
       </c>
     </row>
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Transportation Engineering</t>
+          <t>Assistant Professor of Civil, Construction and Environmental Engineering</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>South Dakota State University</t>
+          <t>University of Alabama</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Department of Civil and Environmental Engineering</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>10</v>
+          <t>Civil, Construction and Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>6</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Core match: direct faculty position in Transportation Engineering aligning perfectly with the candidate's core field.</t>
+          <t>Broad Civil, Construction and Environmental Engineering faculty search where transportation is a potential sub-discipline within the department.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Transportation Engineering, Traffic Systems, Infrastructure Planning, Smart Mobility</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
+          <t>Civil Engineering, Construction Engineering, Environmental Engineering, Transportation Engineering</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Brookings, SD</t>
-        </is>
-      </c>
-      <c r="I3" s="5" t="inlineStr">
+          <t>Tuscaloosa, AL</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>Open until filled</t>
         </is>
@@ -756,22 +756,22 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>Assistant Professor position in Transportation Engineering requiring a Ph.D. in civil engineering or a closely related field to teach, advise, and conduct sponsored research. | Research Topics: Transportation Engineering, Traffic Systems, Infrastructure Planning, Smart Mobility</t>
-        </is>
-      </c>
-      <c r="L3" s="6" t="inlineStr">
-        <is>
-          <t>https://engineering.academickeys.com/job/m4lk5asr/Assistant-Professor-of-Transportation-Engineering</t>
-        </is>
-      </c>
-      <c r="M3" s="5" t="inlineStr">
+          <t>Assistant Professor position in the Department of Civil, Construction and Environmental Engineering at the University of Alabama. | Research Topics: Civil Engineering, Construction Engineering, Environmental Engineering, Transportation Engineering</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>https://engineering.academickeys.com/job/02ixzgls/Civil-Construction-and-Environmental-Engineering--Assistant-Professor</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>AcademicKeys</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
@@ -779,63 +779,63 @@
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="P3" s="5" t="inlineStr">
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>44.344449</v>
+        <v>33.2120822</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-96.79823709999999</v>
+        <v>-87.53967350000001</v>
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>9b7d5de4753a514b</t>
+          <t>f80ad2336a210f82</t>
         </is>
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Assistant/Associate Professor of Civil Engineering (Transportation)</t>
+          <t>Assistant Professor of Transportation Engineering</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Trine University</t>
+          <t>South Dakota State University</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>8</v>
+          <t>Department of Civil and Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>10</v>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Strong match for a tenure-track faculty position specifically in Civil Engineering with a focus on Transportation.</t>
+          <t>Core match: direct faculty position in Transportation Engineering aligning perfectly with the candidate's core field.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Transportation Engineering, Civil Engineering Education, Mobility Systems</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
+          <t>Transportation Engineering, Traffic Systems, Infrastructure Planning, Smart Mobility</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Angola, IN</t>
-        </is>
-      </c>
-      <c r="I4" s="5" t="inlineStr">
+          <t>Brookings, SD</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Open until filled</t>
         </is>
@@ -847,15 +847,15 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>The role seeks a faculty member to teach and mentor undergraduate and graduate students in transportation engineering within a civil engineering department. | Research Topics: Transportation Engineering, Civil Engineering Education, Mobility Systems</t>
-        </is>
-      </c>
-      <c r="L4" s="6" t="inlineStr">
-        <is>
-          <t>https://engineering.academickeys.com/job/e8akh47s/AssistantAssociate-Professor--Civil-Engineering-Transportation</t>
-        </is>
-      </c>
-      <c r="M4" s="5" t="inlineStr">
+          <t>Assistant Professor position in Transportation Engineering requiring a Ph.D. in civil engineering or a closely related field to teach, advise, and conduct sponsored research. | Research Topics: Transportation Engineering, Traffic Systems, Infrastructure Planning, Smart Mobility</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>https://engineering.academickeys.com/job/m4lk5asr/Assistant-Professor-of-Transportation-Engineering</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>AcademicKeys</t>
         </is>
@@ -867,86 +867,86 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="P4" s="5" t="inlineStr">
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>41.6311141</v>
+        <v>44.344449</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>-85.0105982</v>
+        <v>-96.79823709999999</v>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>87a4115bef0ef2e7</t>
+          <t>9b7d5de4753a514b</t>
         </is>
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Urban Planning/Geography</t>
+          <t>Assistant/Associate Professor of Civil Engineering (Transportation)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Loyola Marymount University</t>
+          <t>Trine University</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Department of Urban Planning</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Strong interdisciplinary match in urban planning and geography with potential focus on urban mobility and transit systems.</t>
+          <t>Strong match for a faculty position specifically dedicated to transportation engineering within a civil engineering program.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Urban Planning, Geography, Mobility Systems, Urban Analytics</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
+          <t>Transportation Engineering, Civil Engineering Education, Intelligent Transportation Systems</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Los Angeles, CA</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
+          <t>Angola, IN</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>Open until filled</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>$92,000</t>
+          <t>Based on qualifications</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>Assistant Professor position in urban planning and geography requiring a terminal degree in a relevant field to teach and conduct research. | Research Topics: Urban Planning, Geography, Mobility Systems, Urban Analytics</t>
-        </is>
-      </c>
-      <c r="L5" s="6" t="inlineStr">
-        <is>
-          <t>https://jobs.chronicle.com/job/38031694/assistant-professor-of-urban-planning-geography/</t>
-        </is>
-      </c>
-      <c r="M5" s="5" t="inlineStr">
+          <t>This is a faculty position seeking a transportation engineering specialist to teach undergraduate and graduate civil engineering courses and mentor students. | Research Topics: Transportation Engineering, Civil Engineering Education, Intelligent Transportation Systems</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>https://jobs.chronicle.com/job/38028401/assistant-associate-professor-civil-engineering-transportation-/</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>Chronicle</t>
         </is>
@@ -961,83 +961,83 @@
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="P5" s="5" t="inlineStr">
+      <c r="P5" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>33.9687824</v>
+        <v>41.6311141</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-118.4182021</v>
+        <v>-85.0105982</v>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>c13b0c3f0cf09a9e</t>
+          <t>9f9cc58aa59ccd96</t>
         </is>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Urban Economics</t>
+          <t>Assistant Professor of Urban Planning/Geography</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Harvard University</t>
+          <t>Loyola Marymount University</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Department of Economics / Graduate School of Design</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="n">
-        <v>5</v>
+          <t>Department of Urban Planning</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>7</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Moderate fit: urban economics position focusing on economic analysis rather than core transportation engineering and travel behavior.</t>
+          <t>Strong interdisciplinary match in urban planning and geography with potential focus on urban mobility and transit systems.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Urban Economics, Spatial Economics, Urban Analytics, Real Estate and Housing</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
+          <t>Urban Planning, Geography, Mobility Systems, Urban Analytics</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Cambridge, MA</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
+          <t>Los Angeles, CA</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>Open until filled</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>$165,000 - $185,000</t>
+          <t>$92,000</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>This is a tenure-track faculty role in urban economics requiring a Ph.D. in economics, public policy, or a closely related field with a focus on urban systems. | Research Topics: Urban Economics, Spatial Economics, Urban Analytics, Real Estate and Housing</t>
-        </is>
-      </c>
-      <c r="L6" s="6" t="inlineStr">
-        <is>
-          <t>https://jobs.chronicle.com/job/38032116/assistant-professor-urban-economics-/</t>
-        </is>
-      </c>
-      <c r="M6" s="5" t="inlineStr">
+          <t>Assistant Professor position in urban planning and geography requiring a terminal degree in a relevant field to teach and conduct research. | Research Topics: Urban Planning, Geography, Mobility Systems, Urban Analytics</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>https://jobs.chronicle.com/job/38031694/assistant-professor-of-urban-planning-geography/</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>Chronicle</t>
         </is>
@@ -1052,83 +1052,83 @@
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="P6" s="5" t="inlineStr">
+      <c r="P6" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>42.3657432</v>
+        <v>33.9687824</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-71.12221390000001</v>
+        <v>-118.4182021</v>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>93251b0fa8170f49</t>
+          <t>c13b0c3f0cf09a9e</t>
         </is>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Assistant/Associate Professor of Civil Engineering (Transportation)</t>
+          <t>Assistant Professor of Urban Economics</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Trine University</t>
+          <t>Harvard University</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>8</v>
+          <t>Department of Economics / Graduate School of Design</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>5</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Strong match for a faculty position specifically dedicated to transportation engineering within a civil engineering program.</t>
+          <t>Moderate fit: urban economics position focusing on economic analysis rather than core transportation engineering and travel behavior.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Transportation Engineering, Civil Engineering Education, Intelligent Transportation Systems</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
+          <t>Urban Economics, Spatial Economics, Urban Analytics, Real Estate and Housing</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Angola, IN</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
+          <t>Cambridge, MA</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>Open until filled</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Based on qualifications</t>
+          <t>$165,000 - $185,000</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>This is a faculty position seeking a transportation engineering specialist to teach undergraduate and graduate civil engineering courses and mentor students. | Research Topics: Transportation Engineering, Civil Engineering Education, Intelligent Transportation Systems</t>
-        </is>
-      </c>
-      <c r="L7" s="6" t="inlineStr">
-        <is>
-          <t>https://jobs.chronicle.com/job/38028401/assistant-associate-professor-civil-engineering-transportation-/</t>
-        </is>
-      </c>
-      <c r="M7" s="5" t="inlineStr">
+          <t>This is a tenure-track faculty role in urban economics requiring a Ph.D. in economics, public policy, or a closely related field with a focus on urban systems. | Research Topics: Urban Economics, Spatial Economics, Urban Analytics, Real Estate and Housing</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>https://jobs.chronicle.com/job/38032116/assistant-professor-urban-economics-/</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
         <is>
           <t>Chronicle</t>
         </is>
@@ -1143,20 +1143,20 @@
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="P7" s="5" t="inlineStr">
+      <c r="P7" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>41.6311141</v>
+        <v>42.3657432</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-85.0105982</v>
+        <v>-71.12221390000001</v>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9f9cc58aa59ccd96</t>
+          <t>93251b0fa8170f49</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
           <t>Civil and Environmental Engineering</t>
         </is>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="7" t="n">
         <v>9</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -1189,7 +1189,7 @@
           <t>Transportation Engineering, Transit Planning, Traffic Systems</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>Non-Tenure Track</t>
         </is>
@@ -1199,7 +1199,7 @@
           <t>Baltimore, MD</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>Open until filled</t>
         </is>
@@ -1214,12 +1214,12 @@
           <t>The role seeks an adjunct faculty member to teach transportation engineering courses within the civil and environmental engineering department, requiring a relevant graduate degree. | Research Topics: Transportation Engineering, Transit Planning, Traffic Systems</t>
         </is>
       </c>
-      <c r="L8" s="6" t="inlineStr">
+      <c r="L8" s="5" t="inlineStr">
         <is>
           <t>https://jobs.chronicle.com/job/37974518/adjunct-faculty-transportation-engineering/</t>
         </is>
       </c>
-      <c r="M8" s="5" t="inlineStr">
+      <c r="M8" s="3" t="inlineStr">
         <is>
           <t>Chronicle</t>
         </is>
@@ -1234,7 +1234,7 @@
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="P8" s="5" t="inlineStr">
+      <c r="P8" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -1267,7 +1267,7 @@
           <t>Advanced Transportation Technology</t>
         </is>
       </c>
-      <c r="D9" s="7" t="n">
+      <c r="D9" s="6" t="n">
         <v>5</v>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -1280,7 +1280,7 @@
           <t>Advanced Transportation Technology, Vehicle Technologies, Transportation Education</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>Non-Tenure Track</t>
         </is>
@@ -1290,7 +1290,7 @@
           <t>California</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>Open until filled</t>
         </is>
@@ -1305,12 +1305,12 @@
           <t>Part-time adjunct instructor role teaching advanced transportation technology courses at a community college district. | Research Topics: Advanced Transportation Technology, Vehicle Technologies, Transportation Education</t>
         </is>
       </c>
-      <c r="L9" s="6" t="inlineStr">
+      <c r="L9" s="5" t="inlineStr">
         <is>
           <t>https://jobs.chronicle.com/job/38026829/advanced-transportation-technology-instructor-part-time-adjunct/</t>
         </is>
       </c>
-      <c r="M9" s="5" t="inlineStr">
+      <c r="M9" s="3" t="inlineStr">
         <is>
           <t>Chronicle</t>
         </is>
@@ -1325,7 +1325,7 @@
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="P9" s="5" t="inlineStr">
+      <c r="P9" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -1358,7 +1358,7 @@
           <t>Department of Civil and Architectural Engineering and Construction Management</t>
         </is>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D10" s="7" t="n">
         <v>10</v>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -1371,7 +1371,7 @@
           <t>Transportation Engineering, Transportation Systems, Transit Planning, Mobility Systems</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>Tenure-Track</t>
         </is>
@@ -1381,7 +1381,7 @@
           <t>Cincinnati, OH</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>Open until filled</t>
         </is>
@@ -1396,12 +1396,12 @@
           <t>The Department of Civil and Architectural Engineering and Construction Management at the University of Cincinnati is seeking an open-rank faculty member specializing in transportation engineering and systems. | Research Topics: Transportation Engineering, Transportation Systems, Transit Planning, Mobility Systems</t>
         </is>
       </c>
-      <c r="L10" s="6" t="inlineStr">
+      <c r="L10" s="5" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/assistant-associate-full-professor-transportation-engineering-and-systems-at-university-of-cincinnati-4416744025</t>
         </is>
       </c>
-      <c r="M10" s="5" t="inlineStr">
+      <c r="M10" s="3" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
@@ -1416,7 +1416,7 @@
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="P10" s="5" t="inlineStr">
+      <c r="P10" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -1449,7 +1449,7 @@
           <t>Civil, Architectural and Environmental Engineering</t>
         </is>
       </c>
-      <c r="D11" s="7" t="n">
+      <c r="D11" s="6" t="n">
         <v>6</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1462,7 +1462,7 @@
           <t>Civil Engineering, Architectural Engineering, Environmental Engineering</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>Tenure-Track</t>
         </is>
@@ -1472,7 +1472,7 @@
           <t>Rolla, MO</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>Open until filled</t>
         </is>
@@ -1487,12 +1487,12 @@
           <t>The position seeks an Assistant or Associate Professor in the Department of Civil, Architectural and Environmental Engineering, requiring a Ph.D. in a relevant discipline. | Research Topics: Civil Engineering, Architectural Engineering, Environmental Engineering</t>
         </is>
       </c>
-      <c r="L11" s="6" t="inlineStr">
+      <c r="L11" s="5" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/assistant-associate-professor-civil-architectural-and-environmental-engineering-%2300096512-at-missouri-university-of-science-and-technology-4442271248</t>
         </is>
       </c>
-      <c r="M11" s="5" t="inlineStr">
+      <c r="M11" s="3" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
@@ -1507,7 +1507,7 @@
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="P11" s="5" t="inlineStr">
+      <c r="P11" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -1540,7 +1540,7 @@
           <t>Department of Urban Policy and Planning, School of Arts and Sciences</t>
         </is>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" s="7" t="n">
         <v>8</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -1553,7 +1553,7 @@
           <t>Transportation Policy, Transit Accessibility, Transportation Equity, Community-Engaged Research</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>Tenure-Track</t>
         </is>
@@ -1563,7 +1563,7 @@
           <t>New York, NY</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>Open until filled (Review begins Oct. 1, 2025)</t>
         </is>
@@ -1578,12 +1578,12 @@
           <t>Hunter College seeks a tenure-track Assistant Professor in transportation policy requiring a Ph.D. in policy, planning, or a related field to teach applied policy research and develop a robust research agenda. | Research Topics: Transportation Policy, Transit Accessibility, Transportation Equity, Community-Engaged Research</t>
         </is>
       </c>
-      <c r="L12" s="6" t="inlineStr">
+      <c r="L12" s="5" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/assistant-professor-%E2%80%93-urban-policy-and-planning-dept-school-of-arts-and-sciences-hunter-college-at-hunter-college-4438624127</t>
         </is>
       </c>
-      <c r="M12" s="5" t="inlineStr">
+      <c r="M12" s="3" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
@@ -1598,7 +1598,7 @@
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="P12" s="5" t="inlineStr">
+      <c r="P12" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -1631,7 +1631,7 @@
           <t>Information Science Technology (CYBER-CARE Consortium)</t>
         </is>
       </c>
-      <c r="D13" s="7" t="n">
+      <c r="D13" s="6" t="n">
         <v>6</v>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -1644,7 +1644,7 @@
           <t>Connected and Automated Vehicle Cybersecurity, Transportation Data Security, Advanced Traffic Management Systems, Intelligent Transportation Systems</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>Non-Tenure Track</t>
         </is>
@@ -1654,7 +1654,7 @@
           <t>Houston, TX</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>Open until filled</t>
         </is>
@@ -1669,12 +1669,12 @@
           <t>The University of Houston seeks a non-tenure track Research Assistant Professor for the CYBER-CARE consortium to conduct research on transportation cybersecurity and AI applications, requiring a doctoral degree in Transportation Engineering or a closely related field. | Research Topics: Connected and Automated Vehicle Cybersecurity, Transportation Data Security, Advanced Traffic Management Systems, Intelligent Transportation Systems</t>
         </is>
       </c>
-      <c r="L13" s="6" t="inlineStr">
+      <c r="L13" s="5" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/research-assistant-professor-cyber-care-consortium-at-university-of-houston-4404319276</t>
         </is>
       </c>
-      <c r="M13" s="5" t="inlineStr">
+      <c r="M13" s="3" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
@@ -1689,7 +1689,7 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="P13" s="5" t="inlineStr">
+      <c r="P13" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -1722,7 +1722,7 @@
           <t>School of Graduate Studies in the College of Aviation</t>
         </is>
       </c>
-      <c r="D14" s="5" t="n">
+      <c r="D14" s="3" t="n">
         <v>4</v>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -1735,7 +1735,7 @@
           <t>Air Transportation Systems, Advanced Air Mobility, UAS Traffic Management, Machine Learning/AI in Aviation</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>Tenure-Track</t>
         </is>
@@ -1745,7 +1745,7 @@
           <t>Daytona Beach, FL</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>Review begins immediately; Priority given to applications received by 2026-08-31</t>
         </is>
@@ -1760,12 +1760,12 @@
           <t>This tenure-track faculty position requires a doctorate in air transportation systems, advanced air mobility, or a related area to teach graduate courses and conduct AI/machine learning research in aviation. | Research Topics: Air Transportation Systems, Advanced Air Mobility, UAS Traffic Management, Machine Learning/AI in Aviation</t>
         </is>
       </c>
-      <c r="L14" s="6" t="inlineStr">
+      <c r="L14" s="5" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/tenure-track-faculty-position-with-a-focus-on-air-transportation-systems-daytona-beach-campus-at-embry-riddle-aeronautical-university-4434897662</t>
         </is>
       </c>
-      <c r="M14" s="5" t="inlineStr">
+      <c r="M14" s="3" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
@@ -1780,7 +1780,7 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="P14" s="5" t="inlineStr">
+      <c r="P14" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -1800,7 +1800,7 @@
     <row r="15" ht="26" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor / Associate Professor in Maritime Studies</t>
+          <t>Assistant Professor / Associate Professor (Tenure-Track) in Civil and Environmental Engineering</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1813,30 +1813,30 @@
           <t>School of Civil and Environmental Engineering</t>
         </is>
       </c>
-      <c r="D15" s="7" t="n">
+      <c r="D15" s="6" t="n">
         <v>5</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Moderate fit: maritime studies includes ports and logistics, but the focus is broader than the candidate's core transportation engineering specialization.</t>
+          <t>Moderate fit: broad Civil and Environmental Engineering search where Transportation Engineering is a potential sub-discipline, though specific subfield requirements are not detailed in the snippet.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Maritime Studies, Port Logistics, Transportation Systems, Supply Chain</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
+          <t>Civil and Environmental Engineering, Transportation Systems, Infrastructure Systems, Smart Cities</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Singapore</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
+          <t>Singapore, Singapore</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>Open until filled</t>
         </is>
@@ -1848,22 +1848,22 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>This is a faculty position focusing on maritime studies and port-related systems, requiring a relevant Ph.D. degree. | Research Topics: Maritime Studies, Port Logistics, Transportation Systems, Supply Chain</t>
-        </is>
-      </c>
-      <c r="L15" s="6" t="inlineStr">
-        <is>
-          <t>https://engineering.academickeys.com/job/m80x7utf/Assistant-Professor--Associate-Professor-TenureTrack-Associate-Professor-PracticeTrack-in-Maritime-Studies</t>
-        </is>
-      </c>
-      <c r="M15" s="5" t="inlineStr">
+          <t>Tenure-track Assistant or Associate Professor position in Civil and Environmental Engineering requiring an earned doctorate in civil engineering or a closely related discipline. | Research Topics: Civil and Environmental Engineering, Transportation Systems, Infrastructure Systems, Smart Cities</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>https://engineering.academickeys.com/job/dhzin0q4/Assistant-Professor--Associate-Professor-TenureTrack-in-Civil-and-Environmental-Engineering</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
         <is>
           <t>AcademicKeys</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -1871,20 +1871,20 @@
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="P15" s="5" t="inlineStr">
+      <c r="P15" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
       <c r="Q15" s="2" t="n">
-        <v>1.357107</v>
+        <v>1.2899175</v>
       </c>
       <c r="R15" s="2" t="n">
-        <v>103.8194992</v>
+        <v>103.8519072</v>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6736da1a934c5c83</t>
+          <t>3fa57c30724444e8</t>
         </is>
       </c>
     </row>
@@ -1904,7 +1904,7 @@
           <t>Department of Mechanical Engineering</t>
         </is>
       </c>
-      <c r="D16" s="5" t="n">
+      <c r="D16" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -1917,7 +1917,7 @@
           <t>Mechanical Engineering, Thermal/Fluids or Mechanical Systems</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>Tenure-Track</t>
         </is>
@@ -1927,7 +1927,7 @@
           <t>Auburn, AL</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
@@ -1942,12 +1942,12 @@
           <t>An open-rank faculty position in mechanical engineering requiring a Ph.D. in mechanical engineering or a closely related field. | Research Topics: Mechanical Engineering, Thermal/Fluids or Mechanical Systems</t>
         </is>
       </c>
-      <c r="L16" s="6" t="inlineStr">
+      <c r="L16" s="5" t="inlineStr">
         <is>
           <t>https://engineering.academickeys.com/job/f320isty/AssistantAssociateFull-Professor</t>
         </is>
       </c>
-      <c r="M16" s="5" t="inlineStr">
+      <c r="M16" s="3" t="inlineStr">
         <is>
           <t>AcademicKeys</t>
         </is>
@@ -1962,7 +1962,7 @@
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="P16" s="5" t="inlineStr">
+      <c r="P16" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -1995,7 +1995,7 @@
           <t>Industrial and Systems Engineering</t>
         </is>
       </c>
-      <c r="D17" s="7" t="n">
+      <c r="D17" s="6" t="n">
         <v>7</v>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -2008,7 +2008,7 @@
           <t>Industrial and Systems Engineering, Mobility Systems, Systems Optimization</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>Tenure-Track</t>
         </is>
@@ -2018,7 +2018,7 @@
           <t>Seattle, WA</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>Unspecified</t>
         </is>
@@ -2033,12 +2033,12 @@
           <t>Assistant or Associate Professor position in Industrial and Systems Engineering requiring a Ph.D. in a relevant engineering or analytical discipline. | Research Topics: Industrial and Systems Engineering, Mobility Systems, Systems Optimization</t>
         </is>
       </c>
-      <c r="L17" s="6" t="inlineStr">
+      <c r="L17" s="5" t="inlineStr">
         <is>
           <t>https://engineering.academickeys.com/job/g4m97a60/AssistantAssociate-Professor-Industrial-and-Systems-Engineering-Systems-Engineering-Focus</t>
         </is>
       </c>
-      <c r="M17" s="5" t="inlineStr">
+      <c r="M17" s="3" t="inlineStr">
         <is>
           <t>AcademicKeys</t>
         </is>
@@ -2053,7 +2053,7 @@
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="P17" s="5" t="inlineStr">
+      <c r="P17" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -2086,7 +2086,7 @@
           <t>Department of Civil and Environmental Engineering</t>
         </is>
       </c>
-      <c r="D18" s="5" t="n">
+      <c r="D18" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -2099,7 +2099,7 @@
           <t>Civil Engineering, Environmental Engineering, Academic Leadership, Departmental Administration</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>Tenured</t>
         </is>
@@ -2109,7 +2109,7 @@
           <t>Pittsburgh, PA</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="I18" s="3" t="inlineStr">
         <is>
           <t>Open until filled</t>
         </is>
@@ -2124,12 +2124,12 @@
           <t>Strictly 1 concise sentence summarizing the primary focus of the role and minimum degree qualification. | Research Topics: Civil Engineering, Environmental Engineering, Academic Leadership, Departmental Administration</t>
         </is>
       </c>
-      <c r="L18" s="6" t="inlineStr">
+      <c r="L18" s="5" t="inlineStr">
         <is>
           <t>http://engineering.academickeys.com/job/vhlo0w6p/Professor--Department-Chair--Electrical-and-Computer-Engineering</t>
         </is>
       </c>
-      <c r="M18" s="5" t="inlineStr">
+      <c r="M18" s="3" t="inlineStr">
         <is>
           <t>AcademicKeys</t>
         </is>
@@ -2144,7 +2144,7 @@
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="P18" s="5" t="inlineStr">
+      <c r="P18" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -2177,7 +2177,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="D19" s="7" t="n">
+      <c r="D19" s="6" t="n">
         <v>6</v>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -2190,7 +2190,7 @@
           <t>Higher Education, Instruction, Academic Teaching</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>Non-Tenure Track</t>
         </is>
@@ -2200,7 +2200,7 @@
           <t>New York, NY</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
@@ -2215,12 +2215,12 @@
           <t>This is a faculty teaching role at Columbia University, though the specific academic department and subject focus are missing from the current snippet. | Research Topics: Higher Education, Instruction, Academic Teaching</t>
         </is>
       </c>
-      <c r="L19" s="6" t="inlineStr">
+      <c r="L19" s="5" t="inlineStr">
         <is>
           <t>http://engineering.academickeys.com/job/arsy3jqh/Open-Rank-Lecturer-in-Discipline-or-Senior-Lecturer-in-Discipline</t>
         </is>
       </c>
-      <c r="M19" s="5" t="inlineStr">
+      <c r="M19" s="3" t="inlineStr">
         <is>
           <t>AcademicKeys</t>
         </is>
@@ -2235,7 +2235,7 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="P19" s="5" t="inlineStr">
+      <c r="P19" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -2268,7 +2268,7 @@
           <t>Department of Civil Engineering</t>
         </is>
       </c>
-      <c r="D20" s="7" t="n">
+      <c r="D20" s="6" t="n">
         <v>5</v>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -2281,7 +2281,7 @@
           <t>Civil Engineering, Transportation Engineering, Infrastructure Systems</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>Tenure-Track</t>
         </is>
@@ -2291,7 +2291,7 @@
           <t>Cedarville, OH</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
@@ -2306,12 +2306,12 @@
           <t>A faculty position in civil engineering requiring a Ph.D. to teach undergraduate courses and engage in scholarly activity. | Research Topics: Civil Engineering, Transportation Engineering, Infrastructure Systems</t>
         </is>
       </c>
-      <c r="L20" s="6" t="inlineStr">
+      <c r="L20" s="5" t="inlineStr">
         <is>
           <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179544290&amp;Title=Assistant%2FAssociate%20Professor%20of%20Civil%20Engineering</t>
         </is>
       </c>
-      <c r="M20" s="5" t="inlineStr">
+      <c r="M20" s="3" t="inlineStr">
         <is>
           <t>HigherEdJobs</t>
         </is>
@@ -2326,7 +2326,7 @@
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="P20" s="5" t="inlineStr">
+      <c r="P20" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -2359,7 +2359,7 @@
           <t>Information and Decision Sciences (IDS)</t>
         </is>
       </c>
-      <c r="D21" s="5" t="n">
+      <c r="D21" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -2372,7 +2372,7 @@
           <t>Supply Chain Management, Operations Management, Decision Sciences</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>Tenure-Track</t>
         </is>
@@ -2382,7 +2382,7 @@
           <t>Chicago, IL</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="I21" s="3" t="inlineStr">
         <is>
           <t>Open until filled</t>
         </is>
@@ -2397,12 +2397,12 @@
           <t>This is a tenure-track Assistant Professor role in Supply Chain and Operations Management requiring a Ph.D. in a relevant business or analytical discipline. | Research Topics: Supply Chain Management, Operations Management, Decision Sciences</t>
         </is>
       </c>
-      <c r="L21" s="6" t="inlineStr">
+      <c r="L21" s="5" t="inlineStr">
         <is>
           <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179552436&amp;Title=Assistant%20Professor%20%2D%20IDS%20%28Supply%20Chain%20%26%20Operations%20Management%29</t>
         </is>
       </c>
-      <c r="M21" s="5" t="inlineStr">
+      <c r="M21" s="3" t="inlineStr">
         <is>
           <t>HigherEdJobs</t>
         </is>
@@ -2417,7 +2417,7 @@
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="P21" s="5" t="inlineStr">
+      <c r="P21" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -2450,7 +2450,7 @@
           <t>Department of Industrial and Systems Engineering</t>
         </is>
       </c>
-      <c r="D22" s="7" t="n">
+      <c r="D22" s="6" t="n">
         <v>6</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -2463,7 +2463,7 @@
           <t>Industrial Engineering, Systems Engineering, Operations Research</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>Tenure-Track</t>
         </is>
@@ -2473,7 +2473,7 @@
           <t>Auburn, AL</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>Open until filled</t>
         </is>
@@ -2488,12 +2488,12 @@
           <t>Open-rank faculty position in Industrial and Systems Engineering requiring a Ph.D. in industrial engineering, systems engineering, or a closely related field. | Research Topics: Industrial Engineering, Systems Engineering, Operations Research</t>
         </is>
       </c>
-      <c r="L22" s="6" t="inlineStr">
+      <c r="L22" s="5" t="inlineStr">
         <is>
           <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179548357&amp;Title=Professor%2C%20Associate%20Professor%2C%20Assistant%20Professor%20%2D%20Industrial%20and%20Systems%20Engineering</t>
         </is>
       </c>
-      <c r="M22" s="5" t="inlineStr">
+      <c r="M22" s="3" t="inlineStr">
         <is>
           <t>HigherEdJobs</t>
         </is>
@@ -2508,7 +2508,7 @@
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="P22" s="5" t="inlineStr">
+      <c r="P22" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -2541,7 +2541,7 @@
           <t>Department of Industrial and Systems Engineering</t>
         </is>
       </c>
-      <c r="D23" s="7" t="n">
+      <c r="D23" s="6" t="n">
         <v>7</v>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -2554,7 +2554,7 @@
           <t>Industrial Engineering, Mobility Systems, Systems Engineering</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>Tenure-Track</t>
         </is>
@@ -2564,7 +2564,7 @@
           <t>Knoxville, TN</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="I23" s="3" t="inlineStr">
         <is>
           <t>Open until filled</t>
         </is>
@@ -2579,12 +2579,12 @@
           <t>Tenure-track Assistant Professor position in Industrial and Systems Engineering focusing on mobility systems, requiring a Ph.D. in industrial engineering, systems engineering, or a closely related field. | Research Topics: Industrial Engineering, Mobility Systems, Systems Engineering</t>
         </is>
       </c>
-      <c r="L23" s="6" t="inlineStr">
+      <c r="L23" s="5" t="inlineStr">
         <is>
           <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179545449&amp;Title=Tenure%2DTrack%20Assistant%20Professor%20of%20Industrial%20and%20Systems%20Engineering%2C%20Fall%202027%20%281%2F3%29</t>
         </is>
       </c>
-      <c r="M23" s="5" t="inlineStr">
+      <c r="M23" s="3" t="inlineStr">
         <is>
           <t>HigherEdJobs</t>
         </is>
@@ -2599,7 +2599,7 @@
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="P23" s="5" t="inlineStr">
+      <c r="P23" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -2632,7 +2632,7 @@
           <t>Civil Engineering</t>
         </is>
       </c>
-      <c r="D24" s="7" t="n">
+      <c r="D24" s="6" t="n">
         <v>5</v>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -2645,7 +2645,7 @@
           <t>Civil Engineering Education, Transportation Engineering</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>Non-Tenure Track</t>
         </is>
@@ -2655,7 +2655,7 @@
           <t>Fayetteville, AR</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="I24" s="3" t="inlineStr">
         <is>
           <t>Open until filled</t>
         </is>
@@ -2670,12 +2670,12 @@
           <t>A teaching-focused assistant professor position in civil engineering requiring a Ph.D. in civil engineering or a closely related field. | Research Topics: Civil Engineering Education, Transportation Engineering</t>
         </is>
       </c>
-      <c r="L24" s="6" t="inlineStr">
+      <c r="L24" s="5" t="inlineStr">
         <is>
           <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179541925&amp;Title=Teaching%20Assistant%20Professor</t>
         </is>
       </c>
-      <c r="M24" s="5" t="inlineStr">
+      <c r="M24" s="3" t="inlineStr">
         <is>
           <t>HigherEdJobs</t>
         </is>
@@ -2690,7 +2690,7 @@
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="P24" s="5" t="inlineStr">
+      <c r="P24" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -2710,65 +2710,65 @@
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Tenure-Track Faculty Position in Air Transportation Systems</t>
+          <t>Assistant Professor of Teaching</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Chronicle Listed University</t>
+          <t>Florida Atlantic University</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Air Transportation Systems (Daytona Beach Campus)</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>3</v>
+          <t>Department of Civil, Environmental &amp; Geomatics Engineering</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>5</v>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Low fit: position focuses specifically on air transportation and aviation systems rather than ground transportation, transit, or mobility systems.</t>
+          <t>Moderate fit: it is a Civil Engineering teaching position in a department with transportation research centers, but requires teaching structural analysis and design-related classes alongside a P.E. license.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Air Transportation Systems, Aviation, Transportation Management</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>Tenure-Track</t>
+          <t>Civil Engineering Education, Applied Transportation Problems, Infrastructure and Sustainability</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Non-Tenure Track</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>Not specified</t>
+          <t>Boca Raton, FL</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>Open until filled</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Commensurate with Experience</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>This is a tenure-track faculty position focusing on air transportation systems at the Daytona Beach campus requiring an appropriate terminal degree. | Research Topics: Air Transportation Systems, Aviation, Transportation Management</t>
-        </is>
-      </c>
-      <c r="L25" s="6" t="inlineStr">
-        <is>
-          <t>https://jobs.chronicle.com/job/38012134/tenure-track-faculty-position-with-a-focus-on-air-transportation-systems-daytona-beach-campus/</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>Chronicle</t>
+          <t>This is a non-tenure-track Assistant Teaching Professor position in civil engineering requiring a Ph.D. and P.E. license to teach undergraduate and graduate courses including structural analysis and design. | Research Topics: Civil Engineering Education, Applied Transportation Problems, Infrastructure and Sustainability</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-of-teaching-at-florida-atlantic-university-4414964381</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2778,86 +2778,86 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="P25" s="5" t="inlineStr">
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
       <c r="Q25" s="2" t="n">
-        <v>29.2108147</v>
+        <v>26.1194058</v>
       </c>
       <c r="R25" s="2" t="n">
-        <v>-81.0228331</v>
+        <v>-80.14167999999999</v>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>52969a207999417a</t>
+          <t>7bdaa996cf64d1f6</t>
         </is>
       </c>
     </row>
     <row r="26" ht="26" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Teaching</t>
+          <t>Assistant or Associate Professor in Supply Chain Management</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Florida Atlantic University</t>
+          <t>University of Arkansas</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Department of Civil, Environmental &amp; Geomatics Engineering</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="n">
-        <v>5</v>
+          <t>J.B. Hunt Transport Department of Supply Chain Management</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Moderate fit: it is a Civil Engineering teaching position in a department with transportation research centers, but requires teaching structural analysis and design-related classes alongside a P.E. license.</t>
+          <t>Low fit: this is a faculty position in Supply Chain Management within a Business School rather than Transportation Engineering.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Civil Engineering Education, Applied Transportation Problems, Infrastructure and Sustainability</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>Non-Tenure Track</t>
+          <t>Supply Chain Management, Logistics, Operations Research</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Boca Raton, FL</t>
-        </is>
-      </c>
-      <c r="I26" s="5" t="inlineStr">
-        <is>
-          <t>Open until filled</t>
+          <t>Fayetteville, AR</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>Commensurate with Experience</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>This is a non-tenure-track Assistant Teaching Professor position in civil engineering requiring a Ph.D. and P.E. license to teach undergraduate and graduate courses including structural analysis and design. | Research Topics: Civil Engineering Education, Applied Transportation Problems, Infrastructure and Sustainability</t>
-        </is>
-      </c>
-      <c r="L26" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-of-teaching-at-florida-atlantic-university-4414964381</t>
-        </is>
-      </c>
-      <c r="M26" s="5" t="inlineStr">
+          <t>This is a tenure-track Assistant or Associate Professor position in Supply Chain Management requiring a strong research record in leading peer-reviewed journals. | Research Topics: Supply Chain Management, Logistics, Operations Research</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/assistant-or-associate-professor-open-rank-at-university-of-arkansas-%C2%AD-sam-m-walton-college-of-business-4460111187</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
@@ -2869,68 +2869,68 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="P26" s="5" t="inlineStr">
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>26.1194058</v>
+        <v>36.0625843</v>
       </c>
       <c r="R26" s="2" t="n">
-        <v>-80.14167999999999</v>
+        <v>-94.1574328</v>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>7bdaa996cf64d1f6</t>
+          <t>c16a694d5f7f68d4</t>
         </is>
       </c>
     </row>
     <row r="27" ht="26" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Assistant or Associate Professor in Supply Chain Management</t>
+          <t>Assistant Professor of Aerospace Engineering</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>University of Arkansas</t>
+          <t>The University of Kansas</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>J.B. Hunt Transport Department of Supply Chain Management</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="n">
+          <t>Department of Aerospace Engineering</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Low fit: this is a faculty position in Supply Chain Management within a Business School rather than Transportation Engineering.</t>
+          <t>The position is specifically for Aerospace Engineering focusing on aircraft and space systems, where the candidate's core transportation engineering expertise is not the primary requirement.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Management, Logistics, Operations Research</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
+          <t>Unmanned aircraft, Advanced air mobility, Aerospace autonomy, Space systems engineering</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Fayetteville, AR</t>
-        </is>
-      </c>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>2026-11-01</t>
+          <t>Lawrence, KS</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -2940,15 +2940,15 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>This is a tenure-track Assistant or Associate Professor position in Supply Chain Management requiring a strong research record in leading peer-reviewed journals. | Research Topics: Supply Chain Management, Logistics, Operations Research</t>
-        </is>
-      </c>
-      <c r="L27" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-or-associate-professor-open-rank-at-university-of-arkansas-%C2%AD-sam-m-walton-college-of-business-4460111187</t>
-        </is>
-      </c>
-      <c r="M27" s="5" t="inlineStr">
+          <t>This is a tenure-track faculty position in Aerospace Engineering requiring a doctorate in Aerospace Engineering or a closely related field, focusing on aviation and space-related research. | Research Topics: Unmanned aircraft, Advanced air mobility, Aerospace autonomy, Space systems engineering</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-aerospace-engineering-at-the-university-of-kansas-4460398978</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
@@ -2963,83 +2963,83 @@
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="P27" s="5" t="inlineStr">
+      <c r="P27" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
       <c r="Q27" s="2" t="n">
-        <v>36.0625843</v>
+        <v>39.0559267</v>
       </c>
       <c r="R27" s="2" t="n">
-        <v>-94.1574328</v>
+        <v>-94.6090332</v>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>c16a694d5f7f68d4</t>
+          <t>4a53cfad86712a72</t>
         </is>
       </c>
     </row>
     <row r="28" ht="26" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Aerospace Engineering</t>
+          <t>Assistant/Associate/Full Professor in Industrial and Systems Engineering</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>The University of Kansas</t>
+          <t>University of Florida</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Department of Aerospace Engineering</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>3</v>
+          <t>Department of Industrial and Systems Engineering</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>The position is specifically for Aerospace Engineering focusing on aircraft and space systems, where the candidate's core transportation engineering expertise is not the primary requirement.</t>
+          <t>Moderate fit: while housed in Industrial and Systems Engineering with a broad mention of transportation applications, the primary departmental focus and hiring emphasis is strictly on Industrialized Construction.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Unmanned aircraft, Advanced air mobility, Aerospace autonomy, Space systems engineering</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
+          <t>Industrialized Construction, Operations Research, Artificial Intelligence, Digital Twins</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
         <is>
           <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Lawrence, KS</t>
-        </is>
-      </c>
-      <c r="I28" s="5" t="inlineStr">
+          <t>Gainesville, FL</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>This is a tenure-track faculty position in Aerospace Engineering requiring a doctorate in Aerospace Engineering or a closely related field, focusing on aviation and space-related research. | Research Topics: Unmanned aircraft, Advanced air mobility, Aerospace autonomy, Space systems engineering</t>
-        </is>
-      </c>
-      <c r="L28" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-aerospace-engineering-at-the-university-of-kansas-4460398978</t>
-        </is>
-      </c>
-      <c r="M28" s="5" t="inlineStr">
+          <t>The Department of Industrial and Systems Engineering at the University of Florida seeks a tenured/tenure-track faculty member specializing in Industrialized Construction with a PhD in ISE, Manufacturing Engineering, Civil Engineering, Mechanical Engineering, or a closely related field. | Research Topics: Industrialized Construction, Operations Research, Artificial Intelligence, Digital Twins</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/assistant-associate-full-professor-industrial-systems-engineering-at-university-of-florida-4323668785</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
@@ -3051,68 +3051,68 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="P28" s="5" t="inlineStr">
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
       <c r="Q28" s="2" t="n">
-        <v>39.0559267</v>
+        <v>29.6436</v>
       </c>
       <c r="R28" s="2" t="n">
-        <v>-94.6090332</v>
+        <v>-82.3549</v>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4a53cfad86712a72</t>
+          <t>56d501f448e77e05</t>
         </is>
       </c>
     </row>
     <row r="29" ht="26" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Assistant/Associate/Full Professor in Industrial and Systems Engineering</t>
+          <t>Assistant Professor in Supply Chain Management</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>University of Florida</t>
+          <t>University of Arkansas</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Department of Industrial and Systems Engineering</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>4</v>
+          <t>J.B. Hunt Transport Department of Supply Chain Management, Sam M. Walton College of Business</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Moderate fit: while housed in Industrial and Systems Engineering with a broad mention of transportation applications, the primary departmental focus and hiring emphasis is strictly on Industrialized Construction.</t>
+          <t>Low fit: Business school faculty position focused entirely on defense-relevant supply chain management and contested logistics, which falls outside transportation engineering.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Industrialized Construction, Operations Research, Artificial Intelligence, Digital Twins</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
+          <t>Supply Chain Management, Contested Logistics, Military and Defense Logistics, National Security Supply Chains</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Gainesville, FL</t>
-        </is>
-      </c>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>Open until filled</t>
+          <t>Fayetteville, AR</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3122,15 +3122,15 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>The Department of Industrial and Systems Engineering at the University of Florida seeks a tenured/tenure-track faculty member specializing in Industrialized Construction with a PhD in ISE, Manufacturing Engineering, Civil Engineering, Mechanical Engineering, or a closely related field. | Research Topics: Industrialized Construction, Operations Research, Artificial Intelligence, Digital Twins</t>
-        </is>
-      </c>
-      <c r="L29" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-associate-full-professor-industrial-systems-engineering-at-university-of-florida-4323668785</t>
-        </is>
-      </c>
-      <c r="M29" s="5" t="inlineStr">
+          <t>The Sam M. Walton College of Business at the University of Arkansas seeks two tenure-track Assistant Professors in Supply Chain Management as part of a faculty cluster hire focused on contested logistics and defense-relevant supply chains. | Research Topics: Supply Chain Management, Contested Logistics, Military and Defense Logistics, National Security Supply Chains</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-two-open-positions-at-university-of-arkansas-%C2%AD-sam-m-walton-college-of-business-4460109211</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
@@ -3142,23 +3142,23 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="P29" s="5" t="inlineStr">
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
       <c r="Q29" s="2" t="n">
-        <v>29.6436</v>
+        <v>36.0625843</v>
       </c>
       <c r="R29" s="2" t="n">
-        <v>-82.3549</v>
+        <v>-94.1574328</v>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>56d501f448e77e05</t>
+          <t>8b974c86c7dfa1c1</t>
         </is>
       </c>
     </row>
@@ -3170,40 +3170,40 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>University of Arkansas</t>
+          <t>Iowa State University</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>J.B. Hunt Transport Department of Supply Chain Management, Sam M. Walton College of Business</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="n">
-        <v>3</v>
+          <t>Department of Supply Chain Management, Ivy College of Business</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>6</v>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Low fit: Business school faculty position focused entirely on defense-relevant supply chain management and contested logistics, which falls outside transportation engineering.</t>
+          <t>Moderate fit: the role is in a business school supply chain department rather than engineering or planning, though it accepts transportation as a related specialization.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Management, Contested Logistics, Military and Defense Logistics, National Security Supply Chains</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
+          <t>Supply Chain Management, Transportation, Logistics, Operations</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
         <is>
           <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Fayetteville, AR</t>
-        </is>
-      </c>
-      <c r="I30" s="5" t="inlineStr">
-        <is>
-          <t>2026-11-01</t>
+          <t>Ames, IA</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>Open until filled</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3213,15 +3213,15 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>The Sam M. Walton College of Business at the University of Arkansas seeks two tenure-track Assistant Professors in Supply Chain Management as part of a faculty cluster hire focused on contested logistics and defense-relevant supply chains. | Research Topics: Supply Chain Management, Contested Logistics, Military and Defense Logistics, National Security Supply Chains</t>
-        </is>
-      </c>
-      <c r="L30" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-two-open-positions-at-university-of-arkansas-%C2%AD-sam-m-walton-college-of-business-4460109211</t>
-        </is>
-      </c>
-      <c r="M30" s="5" t="inlineStr">
+          <t>The Ivy College of Business at Iowa State University seeks a tenure-track Assistant Professor in Supply Chain Management to conduct research and teach across undergraduate, master's, and Ph.D. levels, requiring a Ph.D. in business administration or a related field such as transportation or logistics. | Research Topics: Supply Chain Management, Transportation, Logistics, Operations</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-in-supply-chain-management-at-iowa-state-university-ivy-college-of-business-4440811209</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
@@ -3233,86 +3233,86 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="P30" s="5" t="inlineStr">
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
       <c r="Q30" s="2" t="n">
-        <v>36.0625843</v>
+        <v>42.0267567</v>
       </c>
       <c r="R30" s="2" t="n">
-        <v>-94.1574328</v>
+        <v>-93.6170448</v>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>8b974c86c7dfa1c1</t>
+          <t>e994e392d38b77ce</t>
         </is>
       </c>
     </row>
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor in Supply Chain Management</t>
+          <t>Assistant Professor in Operations Management</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Iowa State University</t>
+          <t>University of Illinois Chicago</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Department of Supply Chain Management, Ivy College of Business</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="n">
-        <v>6</v>
+          <t>Department of Information and Decision Sciences, College of Business Administration</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>7</v>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Moderate fit: the role is in a business school supply chain department rather than engineering or planning, though it accepts transportation as a related specialization.</t>
+          <t>Strong interdisciplinary match in a Business School department that explicitly prioritizes transportation and AI in supply chain management as a preferred research domain.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Management, Transportation, Logistics, Operations</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
+          <t>Operations Management, Transportation, Supply Chain Management, Artificial Intelligence and Analytics</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Ames, IA</t>
-        </is>
-      </c>
-      <c r="I31" s="5" t="inlineStr">
-        <is>
-          <t>Open until filled</t>
+          <t>Chicago, IL</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>$185,000 - $220,000 annually</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>The Ivy College of Business at Iowa State University seeks a tenure-track Assistant Professor in Supply Chain Management to conduct research and teach across undergraduate, master's, and Ph.D. levels, requiring a Ph.D. in business administration or a related field such as transportation or logistics. | Research Topics: Supply Chain Management, Transportation, Logistics, Operations</t>
-        </is>
-      </c>
-      <c r="L31" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-in-supply-chain-management-at-iowa-state-university-ivy-college-of-business-4440811209</t>
-        </is>
-      </c>
-      <c r="M31" s="5" t="inlineStr">
+          <t>The Department of Information and Decision Sciences seeks a tenure-track Assistant Professor in Operations Management with a preferred research focus on transportation and AI-driven supply chain management, requiring a Ph.D. in Management Science, Operations Management, Operations Research, or a closely related field. | Research Topics: Operations Management, Transportation, Supply Chain Management, Artificial Intelligence and Analytics</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-%E2%80%93-ids-supply-chain-operations-management-at-university-of-illinois-chicago-4463632919</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
@@ -3327,83 +3327,83 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="P31" s="5" t="inlineStr">
+      <c r="P31" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
       <c r="Q31" s="2" t="n">
-        <v>42.0267567</v>
+        <v>41.8748613</v>
       </c>
       <c r="R31" s="2" t="n">
-        <v>-93.6170448</v>
+        <v>-87.6519866</v>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>e994e392d38b77ce</t>
+          <t>d58da246ce5b68ab</t>
         </is>
       </c>
     </row>
     <row r="32" ht="26" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor in Operations Management</t>
+          <t>Assistant Professor of Public Policy (Market-Based Solutions to Societal Challenges)</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>University of Illinois Chicago</t>
+          <t>University of Wisconsin-Madison</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Department of Information and Decision Sciences, College of Business Administration</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="n">
-        <v>7</v>
+          <t>La Follette School of Public Affairs, College of Letters &amp; Science</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Strong interdisciplinary match in a Business School department that explicitly prioritizes transportation and AI in supply chain management as a preferred research domain.</t>
+          <t>Low fit: Public policy and economics faculty position focused on market-based solutions, though transportation and infrastructure finance is listed as one of many broad application areas.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Operations Management, Transportation, Supply Chain Management, Artificial Intelligence and Analytics</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="inlineStr">
+          <t>Market-based institutions, Public policy analysis, Transportation and infrastructure finance, Institutional design</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
         <is>
           <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
-        </is>
-      </c>
-      <c r="I32" s="5" t="inlineStr">
-        <is>
-          <t>2026-12-06</t>
+          <t>Madison, WI</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>Open until filled</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>$185,000 - $220,000 annually</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>The Department of Information and Decision Sciences seeks a tenure-track Assistant Professor in Operations Management with a preferred research focus on transportation and AI-driven supply chain management, requiring a Ph.D. in Management Science, Operations Management, Operations Research, or a closely related field. | Research Topics: Operations Management, Transportation, Supply Chain Management, Artificial Intelligence and Analytics</t>
-        </is>
-      </c>
-      <c r="L32" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-%E2%80%93-ids-supply-chain-operations-management-at-university-of-illinois-chicago-4463632919</t>
-        </is>
-      </c>
-      <c r="M32" s="5" t="inlineStr">
+          <t>The La Follette School of Public Affairs at UW-Madison seeks a tenure-track assistant professor to conduct theoretically grounded research on market-based solutions and incentive-compatible policy design across various domains. | Research Topics: Market-based institutions, Public policy analysis, Transportation and infrastructure finance, Institutional design</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-of-public-policy-market-based-solutions-to-societal-challenges-at-uw-madison-college-of-letters-science-4435310692</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
@@ -3415,66 +3415,66 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="P32" s="5" t="inlineStr">
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>41.8748613</v>
+        <v>43.07469</v>
       </c>
       <c r="R32" s="2" t="n">
-        <v>-87.6519866</v>
+        <v>-89.3841663</v>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>d58da246ce5b68ab</t>
+          <t>886b76b05d362fdc</t>
         </is>
       </c>
     </row>
     <row r="33" ht="26" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Public Policy (Market-Based Solutions to Societal Challenges)</t>
+          <t>Multiple Faculty Positions in Computer Science and Engineering</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>University of Wisconsin-Madison</t>
+          <t>Texas A&amp;M University</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>La Follette School of Public Affairs, College of Letters &amp; Science</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="n">
-        <v>3</v>
+          <t>Department of Computer Science and Engineering</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Low fit: Public policy and economics faculty position focused on market-based solutions, though transportation and infrastructure finance is listed as one of many broad application areas.</t>
+          <t>Moderate fit: open faculty search in Computer Science and Engineering without explicit specialization in transportation or mobility systems.</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Market-based institutions, Public policy analysis, Transportation and infrastructure finance, Institutional design</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>Tenure-Track</t>
+          <t>Computer Science, Computer Engineering, Artificial Intelligence, Data Science</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Madison, WI</t>
-        </is>
-      </c>
-      <c r="I33" s="5" t="inlineStr">
+          <t>College Station, TX</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
         <is>
           <t>Open until filled</t>
         </is>
@@ -3486,22 +3486,22 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>The La Follette School of Public Affairs at UW-Madison seeks a tenure-track assistant professor to conduct theoretically grounded research on market-based solutions and incentive-compatible policy design across various domains. | Research Topics: Market-based institutions, Public policy analysis, Transportation and infrastructure finance, Institutional design</t>
-        </is>
-      </c>
-      <c r="L33" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-of-public-policy-market-based-solutions-to-societal-challenges-at-uw-madison-college-of-letters-science-4435310692</t>
-        </is>
-      </c>
-      <c r="M33" s="5" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
+          <t>Texas A&amp;M University invites applications for multiple faculty positions in Computer Science and Engineering, requiring a Ph.D. in a relevant discipline. | Research Topics: Computer Science, Computer Engineering, Artificial Intelligence, Data Science</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>http://engineering.academickeys.com/job/rh7lvag4/CSE--TAMU-Multiple-Faculty-Positions</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>AcademicKeys</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
@@ -3509,85 +3509,85 @@
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="P33" s="5" t="inlineStr">
+      <c r="P33" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
       <c r="Q33" s="2" t="n">
-        <v>43.07469</v>
+        <v>30.6187</v>
       </c>
       <c r="R33" s="2" t="n">
-        <v>-89.3841663</v>
+        <v>-96.3365</v>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>886b76b05d362fdc</t>
+          <t>7d5d844d65485b4b</t>
         </is>
       </c>
     </row>
     <row r="34" ht="26" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Civil, Construction and Environmental Engineering</t>
+          <t>Assistant Professor of Civil Engineering</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>University of Alabama</t>
+          <t>McNeese State University</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Civil, Construction and Environmental Engineering</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="n">
-        <v>6</v>
+          <t>Civil and Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>5</v>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Broad Civil, Construction and Environmental Engineering faculty search where transportation is a potential sub-discipline within the department.</t>
+          <t>Moderate fit: broad Civil Engineering search where transportation is not explicitly prioritized in the snippet.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Civil Engineering, Construction Engineering, Environmental Engineering, Transportation Engineering</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>Tenure-Track</t>
+          <t>Civil Engineering, Engineering Education</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Tuscaloosa, AL</t>
-        </is>
-      </c>
-      <c r="I34" s="5" t="inlineStr">
+          <t>Lake Charles, LA</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
         <is>
           <t>Open until filled</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>$76,000 per year</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>Assistant Professor position in the Department of Civil, Construction and Environmental Engineering at the University of Alabama. | Research Topics: Civil Engineering, Construction Engineering, Environmental Engineering, Transportation Engineering</t>
-        </is>
-      </c>
-      <c r="L34" s="6" t="inlineStr">
-        <is>
-          <t>https://engineering.academickeys.com/job/02ixzgls/Civil-Construction-and-Environmental-Engineering--Assistant-Professor</t>
-        </is>
-      </c>
-      <c r="M34" s="5" t="inlineStr">
-        <is>
-          <t>AcademicKeys</t>
+          <t>Assistant Professor position in Civil and Environmental Engineering at McNeese State University with a salary of $76,000 per year. | Research Topics: Civil Engineering, Engineering Education</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179545361&amp;Title=Assistant%20Professor%20of%20Civil%20Engineering</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3600,85 +3600,85 @@
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="P34" s="5" t="inlineStr">
+      <c r="P34" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
       <c r="Q34" s="2" t="n">
-        <v>33.2120822</v>
+        <v>30.1751363</v>
       </c>
       <c r="R34" s="2" t="n">
-        <v>-87.53967350000001</v>
+        <v>-93.2112786</v>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>f80ad2336a210f82</t>
+          <t>bd292fb9f52ac2e9</t>
         </is>
       </c>
     </row>
     <row r="35" ht="26" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Associate Professor of Civil, Construction and Environmental Engineering</t>
+          <t>Tenure-Track Faculty Positions in Transportation Engineering</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>University of Alabama</t>
+          <t>National Taiwan University</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Department of Civil, Construction and Environmental Engineering</t>
+          <t>Department of Civil Engineering</t>
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Moderate fit: Broad Civil, Construction, and Environmental Engineering Associate Professor opening without an explicitly specified sub-discipline.</t>
+          <t>Core match: seeks multiple tenure-track faculty positions specifically in the Transportation track within a Department of Civil Engineering.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Civil Engineering, Construction Engineering, Environmental Engineering, Transportation Infrastructure</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="inlineStr">
-        <is>
-          <t>Tenured</t>
+          <t>Transportation Engineering, Mobility Systems, Transit Planning</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Tuscaloosa, AL</t>
-        </is>
-      </c>
-      <c r="I35" s="5" t="inlineStr">
-        <is>
-          <t>Open until filled</t>
+          <t>Taipei, Taiwan</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>NT$83,720–137,370 monthly</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>The University of Alabama invites applications for an Associate Professor position in Civil, Construction, and Environmental Engineering requiring a Ph.D. in civil engineering or a closely related field. | Research Topics: Civil Engineering, Construction Engineering, Environmental Engineering, Transportation Infrastructure</t>
-        </is>
-      </c>
-      <c r="L35" s="6" t="inlineStr">
-        <is>
-          <t>https://engineering.academickeys.com/job/w1r7nesq/Civil-Construction-and-Environmental-Engineering--Associate-Professor</t>
-        </is>
-      </c>
-      <c r="M35" s="5" t="inlineStr">
-        <is>
-          <t>AcademicKeys</t>
+          <t>The Department of Civil Engineering at National Taiwan University invites applications for multiple tenure-track faculty positions in Transportation Engineering. | Research Topics: Transportation Engineering, Mobility Systems, Transit Planning</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>https://jobs.chronicle.com/job/38034402/faculty-recruitment-announcement-department-of-civil-engineering-national-taiwan-university/</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3691,382 +3691,18 @@
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="P35" s="5" t="inlineStr">
+      <c r="P35" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
       <c r="Q35" s="2" t="n">
-        <v>33.2120822</v>
+        <v>25.0375198</v>
       </c>
       <c r="R35" s="2" t="n">
-        <v>-87.53967350000001</v>
+        <v>121.5636796</v>
       </c>
       <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>1b5f034d56841a04</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="26" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Assistant Professor / Associate Professor (Tenure-Track) in Civil and Environmental Engineering</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Nanyang Technological University</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>School of Civil and Environmental Engineering</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>Moderate fit: broad Civil and Environmental Engineering search where Transportation Engineering is a potential sub-discipline, though specific subfield requirements are not detailed in the snippet.</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Civil and Environmental Engineering, Transportation Systems, Infrastructure Systems, Smart Cities</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>Tenure-Track</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>Singapore, Singapore</t>
-        </is>
-      </c>
-      <c r="I36" s="5" t="inlineStr">
-        <is>
-          <t>Open until filled</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="K36" s="4" t="inlineStr">
-        <is>
-          <t>Tenure-track Assistant or Associate Professor position in Civil and Environmental Engineering requiring an earned doctorate in civil engineering or a closely related discipline. | Research Topics: Civil and Environmental Engineering, Transportation Systems, Infrastructure Systems, Smart Cities</t>
-        </is>
-      </c>
-      <c r="L36" s="6" t="inlineStr">
-        <is>
-          <t>https://engineering.academickeys.com/job/dhzin0q4/Assistant-Professor--Associate-Professor-TenureTrack-in-Civil-and-Environmental-Engineering</t>
-        </is>
-      </c>
-      <c r="M36" s="5" t="inlineStr">
-        <is>
-          <t>AcademicKeys</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="P36" s="5" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="n">
-        <v>1.2899175</v>
-      </c>
-      <c r="R36" s="2" t="n">
-        <v>103.8519072</v>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>3fa57c30724444e8</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="26" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>Multiple Faculty Positions in Computer Science and Engineering</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>Texas A&amp;M University</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Department of Computer Science and Engineering</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>Moderate fit: open faculty search in Computer Science and Engineering without explicit specialization in transportation or mobility systems.</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Computer Science, Computer Engineering, Artificial Intelligence, Data Science</t>
-        </is>
-      </c>
-      <c r="G37" s="5" t="inlineStr">
-        <is>
-          <t>Unspecified</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>College Station, TX</t>
-        </is>
-      </c>
-      <c r="I37" s="5" t="inlineStr">
-        <is>
-          <t>Open until filled</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="K37" s="4" t="inlineStr">
-        <is>
-          <t>Texas A&amp;M University invites applications for multiple faculty positions in Computer Science and Engineering, requiring a Ph.D. in a relevant discipline. | Research Topics: Computer Science, Computer Engineering, Artificial Intelligence, Data Science</t>
-        </is>
-      </c>
-      <c r="L37" s="6" t="inlineStr">
-        <is>
-          <t>http://engineering.academickeys.com/job/rh7lvag4/CSE--TAMU-Multiple-Faculty-Positions</t>
-        </is>
-      </c>
-      <c r="M37" s="5" t="inlineStr">
-        <is>
-          <t>AcademicKeys</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="P37" s="5" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="n">
-        <v>30.6187</v>
-      </c>
-      <c r="R37" s="2" t="n">
-        <v>-96.3365</v>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>7d5d844d65485b4b</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="26" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Assistant Professor of Civil Engineering</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>McNeese State University</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Civil and Environmental Engineering</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>Moderate fit: broad Civil Engineering search where transportation is not explicitly prioritized in the snippet.</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Civil Engineering, Engineering Education</t>
-        </is>
-      </c>
-      <c r="G38" s="5" t="inlineStr">
-        <is>
-          <t>Unspecified</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>Lake Charles, LA</t>
-        </is>
-      </c>
-      <c r="I38" s="5" t="inlineStr">
-        <is>
-          <t>Open until filled</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>$76,000 per year</t>
-        </is>
-      </c>
-      <c r="K38" s="4" t="inlineStr">
-        <is>
-          <t>Assistant Professor position in Civil and Environmental Engineering at McNeese State University with a salary of $76,000 per year. | Research Topics: Civil Engineering, Engineering Education</t>
-        </is>
-      </c>
-      <c r="L38" s="6" t="inlineStr">
-        <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179545361&amp;Title=Assistant%20Professor%20of%20Civil%20Engineering</t>
-        </is>
-      </c>
-      <c r="M38" s="5" t="inlineStr">
-        <is>
-          <t>HigherEdJobs</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="P38" s="5" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="n">
-        <v>30.1751363</v>
-      </c>
-      <c r="R38" s="2" t="n">
-        <v>-93.2112786</v>
-      </c>
-      <c r="S38" s="2" t="inlineStr">
-        <is>
-          <t>bd292fb9f52ac2e9</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="26" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>Tenure-Track Faculty Positions in Transportation Engineering</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>National Taiwan University</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Department of Civil Engineering</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>Core match: seeks multiple tenure-track faculty positions specifically in the Transportation track within a Department of Civil Engineering.</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>Transportation Engineering, Mobility Systems, Transit Planning</t>
-        </is>
-      </c>
-      <c r="G39" s="5" t="inlineStr">
-        <is>
-          <t>Tenure-Track</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>Taipei, Taiwan</t>
-        </is>
-      </c>
-      <c r="I39" s="5" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>NT$83,720–137,370 monthly</t>
-        </is>
-      </c>
-      <c r="K39" s="4" t="inlineStr">
-        <is>
-          <t>The Department of Civil Engineering at National Taiwan University invites applications for multiple tenure-track faculty positions in Transportation Engineering. | Research Topics: Transportation Engineering, Mobility Systems, Transit Planning</t>
-        </is>
-      </c>
-      <c r="L39" s="6" t="inlineStr">
-        <is>
-          <t>https://jobs.chronicle.com/job/38034402/faculty-recruitment-announcement-department-of-civil-engineering-national-taiwan-university/</t>
-        </is>
-      </c>
-      <c r="M39" s="5" t="inlineStr">
-        <is>
-          <t>Chronicle</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="P39" s="5" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="Q39" s="2" t="n">
-        <v>25.0375198</v>
-      </c>
-      <c r="R39" s="2" t="n">
-        <v>121.5636796</v>
-      </c>
-      <c r="S39" s="2" t="inlineStr">
         <is>
           <t>f056997ace2e1de7</t>
         </is>
@@ -4108,10 +3744,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId38"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -2232,7 +2232,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -43,13 +43,13 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="001F497D"/>
+      <b val="1"/>
+      <color rgb="00276A3C"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00276A3C"/>
+      <color rgb="001F497D"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -68,14 +68,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EDF2F8"/>
-        <bgColor rgb="00EDF2F8"/>
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-        <bgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00EDF2F8"/>
+        <bgColor rgb="00EDF2F8"/>
       </patternFill>
     </fill>
   </fills>
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S35"/>
+  <dimension ref="A1:S47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -505,7 +505,7 @@
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="83" customWidth="1" min="9" max="9"/>
-    <col width="47" customWidth="1" min="10" max="10"/>
+    <col width="96" customWidth="1" min="10" max="10"/>
     <col width="42" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
@@ -708,65 +708,65 @@
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Civil, Construction and Environmental Engineering</t>
+          <t>Lecturer - Continuing Education</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>University of Alabama</t>
+          <t>City Colleges of Chicago</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Civil, Construction and Environmental Engineering</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="n">
-        <v>6</v>
+          <t>Continuing Education</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Broad Civil, Construction and Environmental Engineering faculty search where transportation is a potential sub-discipline within the department.</t>
+          <t>Low fit: general continuing education lecturing position at a community college system without a focus on transportation engineering research or faculty track.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Civil Engineering, Construction Engineering, Environmental Engineering, Transportation Engineering</t>
+          <t>Continuing Education, Community College Instruction, Adult Education</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Non-Tenure Track</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Tuscaloosa, AL</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Open until filled</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Competitive Salary</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>Assistant Professor position in the Department of Civil, Construction and Environmental Engineering at the University of Alabama. | Research Topics: Civil Engineering, Construction Engineering, Environmental Engineering, Transportation Engineering</t>
+          <t>This continuing education lecturer role provides instruction for adult learners within the City Colleges of Chicago system. | Research Topics: Continuing Education, Community College Instruction, Adult Education</t>
         </is>
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>https://engineering.academickeys.com/job/02ixzgls/Civil-Construction-and-Environmental-Engineering--Assistant-Professor</t>
+          <t>https://jobs.chronicle.com/job/37994648/lecturer-continuing-education/</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>AcademicKeys</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -785,59 +785,59 @@
         </is>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>33.2120822</v>
+        <v>32.898417</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-87.53967350000001</v>
+        <v>-80.05262430000001</v>
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>f80ad2336a210f82</t>
+          <t>aca94749a7e8bf9e</t>
         </is>
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Transportation Engineering</t>
+          <t>Professor / Associate Professor / Assistant Professor</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>South Dakota State University</t>
+          <t>The Hong Kong Polytechnic University</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Department of Civil and Environmental Engineering</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="n">
-        <v>10</v>
+          <t>Department of Aeronautical and Aviation Engineering</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Core match: direct faculty position in Transportation Engineering aligning perfectly with the candidate's core field.</t>
+          <t>Low fit: position is in Aeronautical and Aviation Engineering, which falls outside the candidate's core transportation engineering and planning track.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Transportation Engineering, Traffic Systems, Infrastructure Planning, Smart Mobility</t>
+          <t>Aeronautical Engineering, Aviation Engineering</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Unspecified</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Brookings, SD</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>Open until filled</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -847,22 +847,22 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>Assistant Professor position in Transportation Engineering requiring a Ph.D. in civil engineering or a closely related field to teach, advise, and conduct sponsored research. | Research Topics: Transportation Engineering, Traffic Systems, Infrastructure Planning, Smart Mobility</t>
+          <t>Faculty position in the Department of Aeronautical and Aviation Engineering at The Hong Kong Polytechnic University. | Research Topics: Aeronautical Engineering, Aviation Engineering</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>https://engineering.academickeys.com/job/m4lk5asr/Assistant-Professor-of-Transportation-Engineering</t>
+          <t>https://jobs.chronicle.com/job/38028368/professor-associate-professor-assistant-professor/</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>AcademicKeys</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -876,54 +876,54 @@
         </is>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>44.344449</v>
+        <v>22.3492361</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>-96.79823709999999</v>
+        <v>114.1857778</v>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9b7d5de4753a514b</t>
+          <t>09d04da628fd08f9</t>
         </is>
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Assistant/Associate Professor of Civil Engineering (Transportation)</t>
+          <t>Assistant Professor of Teaching of Urban Planning</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Trine University</t>
+          <t>University of California, Los Angeles (UCLA)</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="n">
+          <t>Meyer and Renee Luskin School of Public Affairs, Department of Urban Planning</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="n">
         <v>8</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Strong match for a faculty position specifically dedicated to transportation engineering within a civil engineering program.</t>
+          <t>Strong interdisciplinary match for a faculty position in urban planning within the candidate's target department scope.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Transportation Engineering, Civil Engineering Education, Intelligent Transportation Systems</t>
+          <t>Urban Planning, Teaching Mission, Mobility and Transportation Planning</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Non-Tenure Track</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Angola, IN</t>
+          <t>Los Angeles, CA</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -933,17 +933,17 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Based on qualifications</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>This is a faculty position seeking a transportation engineering specialist to teach undergraduate and graduate civil engineering courses and mentor students. | Research Topics: Transportation Engineering, Civil Engineering Education, Intelligent Transportation Systems</t>
+          <t>UCLA seeks an Assistant Professor of Teaching in Urban Planning to contribute primarily to the department's teaching mission. | Research Topics: Urban Planning, Teaching Mission, Mobility and Transportation Planning</t>
         </is>
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38028401/assistant-associate-professor-civil-engineering-transportation-/</t>
+          <t>https://jobs.chronicle.com/job/38020965/assistant-professor-of-teaching-of-urban-planning/</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -967,74 +967,74 @@
         </is>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>41.6311141</v>
+        <v>34.0536909</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-85.0105982</v>
+        <v>-118.242766</v>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9f9cc58aa59ccd96</t>
+          <t>fb7ba0794bd02172</t>
         </is>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Urban Planning/Geography</t>
+          <t>Clinical Assistant Professor</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Loyola Marymount University</t>
+          <t>Georgia State University</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Department of Urban Planning</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>7</v>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Strong interdisciplinary match in urban planning and geography with potential focus on urban mobility and transit systems.</t>
+          <t>Low fit: the job snippet lacks specific department and topic details beyond a generic clinical assistant professor title at Georgia State University.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Urban Planning, Geography, Mobility Systems, Urban Analytics</t>
+          <t>Higher Education, Clinical Faculty, Not specified</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Non-Tenure Track</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Los Angeles, CA</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>Open until filled</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>$92,000</t>
+          <t>Competitive Salary</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>Assistant Professor position in urban planning and geography requiring a terminal degree in a relevant field to teach and conduct research. | Research Topics: Urban Planning, Geography, Mobility Systems, Urban Analytics</t>
+          <t>This is a clinical assistant professor position at Georgia State University, but the specific academic discipline and research focus are not provided in the text. | Research Topics: Higher Education, Clinical Faculty, Not specified</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38031694/assistant-professor-of-urban-planning-geography/</t>
+          <t>https://jobs.chronicle.com/job/38022215/clinical-assistant-professor-non-tenure-tack/</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1058,44 +1058,44 @@
         </is>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>33.9687824</v>
+        <v>33.7535889</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-118.4182021</v>
+        <v>-84.3854209</v>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>c13b0c3f0cf09a9e</t>
+          <t>f39f14cbaaf9d6f7</t>
         </is>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Urban Economics</t>
+          <t>Assistant Professor of Public Policy (Market-Based Solutions to Societal Challenges)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Harvard University</t>
+          <t>University of Wisconsin-Madison</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Department of Economics / Graduate School of Design</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>5</v>
+          <t>Department of Public Policy / La Follette School of Public Affairs</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Moderate fit: urban economics position focusing on economic analysis rather than core transportation engineering and travel behavior.</t>
+          <t>Low fit: public policy position focused on market-based solutions rather than core transportation engineering or mobility systems.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Urban Economics, Spatial Economics, Urban Analytics, Real Estate and Housing</t>
+          <t>Public Policy, Market-Based Solutions, Societal Challenges</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Cambridge, MA</t>
+          <t>Madison, WI</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -1115,17 +1115,17 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>$165,000 - $185,000</t>
+          <t>Competitive Salary</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>This is a tenure-track faculty role in urban economics requiring a Ph.D. in economics, public policy, or a closely related field with a focus on urban systems. | Research Topics: Urban Economics, Spatial Economics, Urban Analytics, Real Estate and Housing</t>
+          <t>An assistant professor position in public policy focusing on market-based solutions to societal challenges requiring a Ph.D. or equivalent. | Research Topics: Public Policy, Market-Based Solutions, Societal Challenges</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38032116/assistant-professor-urban-economics-/</t>
+          <t>https://jobs.chronicle.com/job/38008254/assistant-professor-of-public-policy-market-based-solutions-to-societal-challenges-/</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1149,74 +1149,74 @@
         </is>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>42.3657432</v>
+        <v>43.0802745</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-71.12221390000001</v>
+        <v>-89.43095870000001</v>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>93251b0fa8170f49</t>
+          <t>51857534b7308d30</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Adjunct Faculty - Transportation Engineering</t>
+          <t>Assistant Professor in Industrial Engineering</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Morgan State University</t>
+          <t>California Polytechnic State University - San Luis Obispo</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Civil and Environmental Engineering</t>
+          <t>Industrial and Manufacturing Engineering (IME) Department</t>
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Core match: directly seeks faculty expertise in Transportation Engineering.</t>
+          <t>Moderate fit: An Industrial Engineering faculty position at Cal Poly, which falls into a target department but lacks specific mention of transportation or mobility systems in the brief snippet.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Transportation Engineering, Transit Planning, Traffic Systems</t>
+          <t>Industrial Engineering, Systems Engineering, Manufacturing Engineering</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Non-Tenure Track</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Baltimore, MD</t>
+          <t>San Luis Obispo, CA</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>Open until filled</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Competitive Salary</t>
+          <t>$106,000 - $117,000 per year</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>The role seeks an adjunct faculty member to teach transportation engineering courses within the civil and environmental engineering department, requiring a relevant graduate degree. | Research Topics: Transportation Engineering, Transit Planning, Traffic Systems</t>
+          <t>Full-time Assistant Professor in Industrial Engineering at California Polytechnic State University starting August 12th. | Research Topics: Industrial Engineering, Systems Engineering, Manufacturing Engineering</t>
         </is>
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/37974518/adjunct-faculty-transportation-engineering/</t>
+          <t>https://jobs.chronicle.com/job/38018328/assistant-professor-industrial-engineering/</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1240,74 +1240,74 @@
         </is>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>39.3446663</v>
+        <v>35.3074623</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-76.5836094</v>
+        <v>-120.6646483</v>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3df6fb24b156d70b</t>
+          <t>78cbe3317d3f9c95</t>
         </is>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Advanced Transportation Technology Instructor, Part-time Adjunct</t>
+          <t>Assistant Professor in Urban and Regional Planning</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Kern Community College District</t>
+          <t>Louisiana State University New Orleans</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Advanced Transportation Technology</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>5</v>
+          <t>Planning and Urban Studies</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>7</v>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Moderate fit: community college instructor position in advanced transportation technology, but lacks tenure-track research focus.</t>
+          <t>Strong interdisciplinary match for an Assistant Professor position in Urban and Regional Planning, which aligns with the candidate's mobility and urban planning target track.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Advanced Transportation Technology, Vehicle Technologies, Transportation Education</t>
+          <t>Urban and Regional Planning, Urban Studies, Mobility Systems</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Non-Tenure Track</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>New Orleans, LA</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Open until filled</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>$65.00 Hourly</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>Part-time adjunct instructor role teaching advanced transportation technology courses at a community college district. | Research Topics: Advanced Transportation Technology, Vehicle Technologies, Transportation Education</t>
+          <t>Louisiana State University New Orleans invites applications for a tenure-track Assistant Professor position in Urban and Regional Planning. | Research Topics: Urban and Regional Planning, Urban Studies, Mobility Systems</t>
         </is>
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38026829/advanced-transportation-technology-instructor-part-time-adjunct/</t>
+          <t>https://jobs.chronicle.com/job/38025681/assistant-professor-planning-and-urban-studies-/</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1331,44 +1331,44 @@
         </is>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>37.8719</v>
+        <v>29.9911944</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>-122.2585</v>
+        <v>-90.0835067</v>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>36f117729bac62c9</t>
+          <t>f373f0209d1c2577</t>
         </is>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Assistant/Associate/Full Professor, Transportation Engineering and Systems</t>
+          <t>Assistant Professor of Technology and Social Change</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>University of Cincinnati</t>
+          <t>The Ohio State University</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Department of Civil and Architectural Engineering and Construction Management</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="n">
-        <v>10</v>
+          <t>Department of Sociology</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Core match: explicitly seeks a faculty member in Transportation Engineering and Systems within a Civil Engineering department.</t>
+          <t>Low fit: position is in the Department of Sociology focusing on technology and social change rather than transportation engineering or mobility.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Transportation Engineering, Transportation Systems, Transit Planning, Mobility Systems</t>
+          <t>Technology and Social Change, Sociology of Technology</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1378,37 +1378,37 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Cincinnati, OH</t>
+          <t>Columbus, OH</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>Open until filled</t>
+          <t>Unspecified</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Commensurate with education and experience</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>The Department of Civil and Architectural Engineering and Construction Management at the University of Cincinnati is seeking an open-rank faculty member specializing in transportation engineering and systems. | Research Topics: Transportation Engineering, Transportation Systems, Transit Planning, Mobility Systems</t>
+          <t>The Department of Sociology at The Ohio State University seeks a tenure-track Assistant Professor in Technology and Social Change. | Research Topics: Technology and Social Change, Sociology of Technology</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-associate-full-professor-transportation-engineering-and-systems-at-university-of-cincinnati-4416744025</t>
+          <t>https://jobs.chronicle.com/job/38029743/assistant-professor-of-technology-and-social-change/</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1422,54 +1422,54 @@
         </is>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>39.1318888</v>
+        <v>40.0067</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>-84.51578309999999</v>
+        <v>-83.0305</v>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6aa8ab000bc6f6c0</t>
+          <t>66008413c6bf1b19</t>
         </is>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Assistant/Associate Professor of Civil, Architectural and Environmental Engineering</t>
+          <t>Full/Associate/Assistant Professor in Modern Civil Engineering</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Missouri University of Science and Technology</t>
+          <t>University of Macau</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Civil, Architectural and Environmental Engineering</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>6</v>
+          <t>Faculty of Engineering</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>5</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Moderate fit: a broad Civil, Architectural and Environmental Engineering department search that may include transportation, though the specific sub-discipline focus in the provided snippet is unspecified.</t>
+          <t>Moderate fit: broad modern civil engineering position at the University of Macau in Macau, but outside the target geographic scope (Mainland China / SAR region not in preferred US/EU/East Asia target list) and lacking specific focus on transportation.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Civil Engineering, Architectural Engineering, Environmental Engineering</t>
+          <t>Modern Civil Engineering, Infrastructure, Engineering Education</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Unspecified</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Rolla, MO</t>
+          <t>Macau</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1479,27 +1479,27 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Commensurate with the applicants’ academic qualification and relevant professional experience</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>The position seeks an Assistant or Associate Professor in the Department of Civil, Architectural and Environmental Engineering, requiring a Ph.D. in a relevant discipline. | Research Topics: Civil Engineering, Architectural Engineering, Environmental Engineering</t>
+          <t>The University of Macau invites applications for a faculty position in Modern Civil Engineering within the Faculty of Engineering. | Research Topics: Modern Civil Engineering, Infrastructure, Engineering Education</t>
         </is>
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-associate-professor-civil-architectural-and-environmental-engineering-%2300096512-at-missouri-university-of-science-and-technology-4442271248</t>
+          <t>https://jobs.chronicle.com/job/38020589/full-associate-assistant-professor-in-modern-civil-engineering/</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1513,44 +1513,44 @@
         </is>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>37.9532435</v>
+        <v>22.1757605</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>-91.7742667</v>
+        <v>113.5514142</v>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4fad8c46021c1243</t>
+          <t>f5ea2aadd95a9b14</t>
         </is>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor in Transportation Policy</t>
+          <t>Tenure-Track Assistant Professor of Statistics</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Hunter College</t>
+          <t>Haverford College</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Department of Urban Policy and Planning, School of Arts and Sciences</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="n">
-        <v>8</v>
+          <t>Department of Mathematics and Statistics</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Strong interdisciplinary match in an Urban Policy and Planning department specifically seeking expertise in transportation policy, accessibility, and equity.</t>
+          <t>Low fit: position is in Statistics rather than Transportation Engineering or Mobility Systems.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Transportation Policy, Transit Accessibility, Transportation Equity, Community-Engaged Research</t>
+          <t>Statistics, Data Analysis, Mathematics</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -1560,37 +1560,37 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Haverford, PA</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>Open until filled (Review begins Oct. 1, 2025)</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>$77,092 - $91,922 (plus scheduled increases)</t>
+          <t>Competitive Salary</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>Hunter College seeks a tenure-track Assistant Professor in transportation policy requiring a Ph.D. in policy, planning, or a related field to teach applied policy research and develop a robust research agenda. | Research Topics: Transportation Policy, Transit Accessibility, Transportation Equity, Community-Engaged Research</t>
+          <t>Haverford College seeks a tenure-track Assistant Professor of Statistics to begin in fall 2027 within the Department of Mathematics and Statistics. | Research Topics: Statistics, Data Analysis, Mathematics</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-%E2%80%93-urban-policy-and-planning-dept-school-of-arts-and-sciences-hunter-college-at-hunter-college-4438624127</t>
+          <t>https://jobs.chronicle.com/job/38017766/tenure-track-assistant-professor-of-statistics/</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1604,89 +1604,89 @@
         </is>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>40.7683107</v>
+        <v>40.0071506</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>-73.964406</v>
+        <v>-75.3069423</v>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>e4e18ed629103a27</t>
+          <t>139bc27f2f7867a0</t>
         </is>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Research Assistant Professor</t>
+          <t>Assistant Professor of Operations Management</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>University of Houston</t>
+          <t>University of Illinois - Chicago</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Information Science Technology (CYBER-CARE Consortium)</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>6</v>
+          <t>Information and Decision Sciences (IDS) Department</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Moderate fit: the role is a Research Assistant Professor position in transportation engineering, but heavily emphasizes cybersecurity and connected/automated vehicles rather than the candidate's core focus on travel behavior and transit planning.</t>
+          <t>Low fit: position is in Supply Chain and Operations Management within a business/IDS department rather than transportation engineering or urban planning.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Connected and Automated Vehicle Cybersecurity, Transportation Data Security, Advanced Traffic Management Systems, Intelligent Transportation Systems</t>
+          <t>Operations Management, Supply Chain Management</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Non-Tenure Track</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Houston, TX</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>Open until filled</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>Commensurate with experience</t>
+          <t>DOE</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>The University of Houston seeks a non-tenure track Research Assistant Professor for the CYBER-CARE consortium to conduct research on transportation cybersecurity and AI applications, requiring a doctoral degree in Transportation Engineering or a closely related field. | Research Topics: Connected and Automated Vehicle Cybersecurity, Transportation Data Security, Advanced Traffic Management Systems, Intelligent Transportation Systems</t>
+          <t>The Information and Decision Sciences department invites applications for a tenure-track assistant professor position in Operations Management starting in the 2027-2028 academic year. | Research Topics: Operations Management, Supply Chain Management</t>
         </is>
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/research-assistant-professor-cyber-care-consortium-at-university-of-houston-4404319276</t>
+          <t>https://jobs.chronicle.com/job/38035040/assistant-professor-ids-supply-chain-and-operations-management-/</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
@@ -1695,44 +1695,44 @@
         </is>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>29.7207902</v>
+        <v>41.8748613</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>-95.34406269999999</v>
+        <v>-87.6519866</v>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>c6ee2c0289357949</t>
+          <t>c1e8cde424bc7afa</t>
         </is>
       </c>
     </row>
     <row r="14" ht="26" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Tenure-Track Assistant/Associate Professor of Air Transportation Systems</t>
+          <t>Tenure-track Assistant Professor of Industrial and Systems Engineering</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Embry-Riddle Aeronautical University</t>
+          <t>University of Tennessee, Knoxville</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>School of Graduate Studies in the College of Aviation</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>4</v>
+          <t>Department of Industrial and Systems Engineering</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>6</v>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Moderate-low fit: the position focuses specifically on aviation and aerospace systems (air transportation, advanced air mobility, UAS) rather than surface transportation engineering or mobility.</t>
+          <t>Moderate fit: Assistant Professor position in Industrial and Systems Engineering which can align with mobility systems, though the snippet lacks specific details.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Air Transportation Systems, Advanced Air Mobility, UAS Traffic Management, Machine Learning/AI in Aviation</t>
+          <t>Industrial Engineering, Systems Engineering, Mobility Systems</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1742,42 +1742,42 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL</t>
+          <t>Knoxville, TN</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>Review begins immediately; Priority given to applications received by 2026-08-31</t>
+          <t>Open until filled</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Competitive Salary</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>This tenure-track faculty position requires a doctorate in air transportation systems, advanced air mobility, or a related area to teach graduate courses and conduct AI/machine learning research in aviation. | Research Topics: Air Transportation Systems, Advanced Air Mobility, UAS Traffic Management, Machine Learning/AI in Aviation</t>
+          <t>The University of Tennessee, Knoxville is seeking three tenure-track Assistant Professors in the Department of Industrial and Systems Engineering. | Research Topics: Industrial Engineering, Systems Engineering, Mobility Systems</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/tenure-track-faculty-position-with-a-focus-on-air-transportation-systems-daytona-beach-campus-at-embry-riddle-aeronautical-university-4434897662</t>
+          <t>https://jobs.chronicle.com/job/38032334/tenure-track-assistant-professor-of-industrial-and-systems-engineering-fall-2027-1-3-/</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
@@ -1786,44 +1786,44 @@
         </is>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>33.8082375</v>
+        <v>35.9516352</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>-118.1344224</v>
+        <v>-83.9308819</v>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>b3c177958e0ab7a7</t>
+          <t>a40790e93b28a33d</t>
         </is>
       </c>
     </row>
     <row r="15" ht="26" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor / Associate Professor (Tenure-Track) in Civil and Environmental Engineering</t>
+          <t>Assistant Professor of Civil, Construction and Environmental Engineering</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Nanyang Technological University</t>
+          <t>University of Alabama</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>School of Civil and Environmental Engineering</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>5</v>
+          <t>Civil, Construction and Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>6</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Moderate fit: broad Civil and Environmental Engineering search where Transportation Engineering is a potential sub-discipline, though specific subfield requirements are not detailed in the snippet.</t>
+          <t>Broad Civil, Construction and Environmental Engineering faculty search where transportation is a potential sub-discipline within the department.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Civil and Environmental Engineering, Transportation Systems, Infrastructure Systems, Smart Cities</t>
+          <t>Civil Engineering, Construction Engineering, Environmental Engineering, Transportation Engineering</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Singapore, Singapore</t>
+          <t>Tuscaloosa, AL</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -1848,12 +1848,12 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>Tenure-track Assistant or Associate Professor position in Civil and Environmental Engineering requiring an earned doctorate in civil engineering or a closely related discipline. | Research Topics: Civil and Environmental Engineering, Transportation Systems, Infrastructure Systems, Smart Cities</t>
+          <t>Assistant Professor position in the Department of Civil, Construction and Environmental Engineering at the University of Alabama. | Research Topics: Civil Engineering, Construction Engineering, Environmental Engineering, Transportation Engineering</t>
         </is>
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>https://engineering.academickeys.com/job/dhzin0q4/Assistant-Professor--Associate-Professor-TenureTrack-in-Civil-and-Environmental-Engineering</t>
+          <t>https://engineering.academickeys.com/job/02ixzgls/Civil-Construction-and-Environmental-Engineering--Assistant-Professor</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -1877,44 +1877,44 @@
         </is>
       </c>
       <c r="Q15" s="2" t="n">
-        <v>1.2899175</v>
+        <v>33.2120822</v>
       </c>
       <c r="R15" s="2" t="n">
-        <v>103.8519072</v>
+        <v>-87.53967350000001</v>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3fa57c30724444e8</t>
+          <t>f80ad2336a210f82</t>
         </is>
       </c>
     </row>
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Assistant / Associate / Full Professor of Mechanical Engineering</t>
+          <t>Assistant Professor of Transportation Engineering</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Auburn University</t>
+          <t>South Dakota State University</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Department of Mechanical Engineering</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>3</v>
+          <t>Department of Civil and Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>10</v>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Low fit: position is in Mechanical Engineering and lacks description details, which does not align with the candidate's transportation engineering and planning profile.</t>
+          <t>Core match: direct faculty position in Transportation Engineering aligning perfectly with the candidate's core field.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Mechanical Engineering, Thermal/Fluids or Mechanical Systems</t>
+          <t>Transportation Engineering, Traffic Systems, Infrastructure Planning, Smart Mobility</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -1924,27 +1924,27 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Auburn, AL</t>
+          <t>Brookings, SD</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>An open-rank faculty position in mechanical engineering requiring a Ph.D. in mechanical engineering or a closely related field. | Research Topics: Mechanical Engineering, Thermal/Fluids or Mechanical Systems</t>
+          <t>Assistant Professor position in Transportation Engineering requiring a Ph.D. in civil engineering or a closely related field to teach, advise, and conduct sponsored research. | Research Topics: Transportation Engineering, Traffic Systems, Infrastructure Planning, Smart Mobility</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>https://engineering.academickeys.com/job/f320isty/AssistantAssociateFull-Professor</t>
+          <t>https://engineering.academickeys.com/job/m4lk5asr/Assistant-Professor-of-Transportation-Engineering</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -1968,44 +1968,44 @@
         </is>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>32.5919529</v>
+        <v>44.344449</v>
       </c>
       <c r="R16" s="2" t="n">
-        <v>-85.4959775</v>
+        <v>-96.79823709999999</v>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>c08698a4bf95171b</t>
+          <t>9b7d5de4753a514b</t>
         </is>
       </c>
     </row>
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Assistant / Associate Professor of Industrial and Systems Engineering</t>
+          <t>Assistant/Associate Professor of Civil Engineering (Transportation)</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>University of Washington</t>
+          <t>Trine University</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Industrial and Systems Engineering</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Strong interdisciplinary match: industrial and systems engineering position in a target department, though specific mobility focus depends on the full department scope.</t>
+          <t>Strong match for a faculty position specifically dedicated to transportation engineering within a civil engineering program.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Industrial and Systems Engineering, Mobility Systems, Systems Optimization</t>
+          <t>Transportation Engineering, Civil Engineering Education, Intelligent Transportation Systems</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -2015,37 +2015,37 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Angola, IN</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Open until filled</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Based on qualifications</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>Assistant or Associate Professor position in Industrial and Systems Engineering requiring a Ph.D. in a relevant engineering or analytical discipline. | Research Topics: Industrial and Systems Engineering, Mobility Systems, Systems Optimization</t>
+          <t>This is a faculty position seeking a transportation engineering specialist to teach undergraduate and graduate civil engineering courses and mentor students. | Research Topics: Transportation Engineering, Civil Engineering Education, Intelligent Transportation Systems</t>
         </is>
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>https://engineering.academickeys.com/job/g4m97a60/AssistantAssociate-Professor-Industrial-and-Systems-Engineering-Systems-Engineering-Focus</t>
+          <t>https://jobs.chronicle.com/job/38028401/assistant-associate-professor-civil-engineering-transportation-/</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>AcademicKeys</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2059,54 +2059,54 @@
         </is>
       </c>
       <c r="Q17" s="2" t="n">
-        <v>47.6553</v>
+        <v>41.6311141</v>
       </c>
       <c r="R17" s="2" t="n">
-        <v>-122.3035</v>
+        <v>-85.0105982</v>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9d5682cf4dbca334</t>
+          <t>9f9cc58aa59ccd96</t>
         </is>
       </c>
     </row>
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Professor &amp; Department Chair</t>
+          <t>Assistant Professor of Urban Planning/Geography</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>University of Pittsburgh</t>
+          <t>Loyola Marymount University</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Department of Civil and Environmental Engineering</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>3</v>
+          <t>Department of Urban Planning</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>7</v>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Low fit: departmental leadership position for a broad Civil and Environmental Engineering department rather than a dedicated transportation research faculty role.</t>
+          <t>Strong interdisciplinary match in urban planning and geography with potential focus on urban mobility and transit systems.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Civil Engineering, Environmental Engineering, Academic Leadership, Departmental Administration</t>
+          <t>Urban Planning, Geography, Mobility Systems, Urban Analytics</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Tenured</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA</t>
+          <t>Los Angeles, CA</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
@@ -2116,27 +2116,27 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>$92,000</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>Strictly 1 concise sentence summarizing the primary focus of the role and minimum degree qualification. | Research Topics: Civil Engineering, Environmental Engineering, Academic Leadership, Departmental Administration</t>
+          <t>Assistant Professor position in urban planning and geography requiring a terminal degree in a relevant field to teach and conduct research. | Research Topics: Urban Planning, Geography, Mobility Systems, Urban Analytics</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>http://engineering.academickeys.com/job/vhlo0w6p/Professor--Department-Chair--Electrical-and-Computer-Engineering</t>
+          <t>https://jobs.chronicle.com/job/38031694/assistant-professor-of-urban-planning-geography/</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>AcademicKeys</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2150,84 +2150,84 @@
         </is>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>40.444153</v>
+        <v>33.9687824</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>-79.962461</v>
+        <v>-118.4182021</v>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>17acd4b4e7207871</t>
+          <t>c13b0c3f0cf09a9e</t>
         </is>
       </c>
     </row>
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Lecturer in Discipline or Senior Lecturer in Discipline</t>
+          <t>Assistant Professor of Urban Economics</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Columbia University</t>
+          <t>Harvard University</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>6</v>
+          <t>Department of Economics / Graduate School of Design</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>5</v>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Moderate fit: general lecturer position at Columbia University in an unspecified discipline, requiring further text details to confirm a transportation focus.</t>
+          <t>Moderate fit: urban economics position focusing on economic analysis rather than core transportation engineering and travel behavior.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Higher Education, Instruction, Academic Teaching</t>
+          <t>Urban Economics, Spatial Economics, Urban Analytics, Real Estate and Housing</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Non-Tenure Track</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Cambridge, MA</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Open until filled</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>$165,000 - $185,000</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>This is a faculty teaching role at Columbia University, though the specific academic department and subject focus are missing from the current snippet. | Research Topics: Higher Education, Instruction, Academic Teaching</t>
+          <t>This is a tenure-track faculty role in urban economics requiring a Ph.D. in economics, public policy, or a closely related field with a focus on urban systems. | Research Topics: Urban Economics, Spatial Economics, Urban Analytics, Real Estate and Housing</t>
         </is>
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>http://engineering.academickeys.com/job/arsy3jqh/Open-Rank-Lecturer-in-Discipline-or-Senior-Lecturer-in-Discipline</t>
+          <t>https://jobs.chronicle.com/job/38032116/assistant-professor-urban-economics-/</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>AcademicKeys</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2241,84 +2241,84 @@
         </is>
       </c>
       <c r="Q19" s="2" t="n">
-        <v>40.8077507</v>
+        <v>42.3657432</v>
       </c>
       <c r="R19" s="2" t="n">
-        <v>-73.9624901</v>
+        <v>-71.12221390000001</v>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>f11b4a4e74422ae3</t>
+          <t>93251b0fa8170f49</t>
         </is>
       </c>
     </row>
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Assistant/Associate Professor of Civil Engineering</t>
+          <t>Adjunct Faculty - Transportation Engineering</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Cedarville University</t>
+          <t>Morgan State University</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Department of Civil Engineering</t>
+          <t>Civil and Environmental Engineering</t>
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Moderate fit: broad Civil Engineering search where transportation may be acceptable, but lacks a dedicated job description snippet for precise evaluation.</t>
+          <t>Core match: directly seeks faculty expertise in Transportation Engineering.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Civil Engineering, Transportation Engineering, Infrastructure Systems</t>
+          <t>Transportation Engineering, Transit Planning, Traffic Systems</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Non-Tenure Track</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Cedarville, OH</t>
+          <t>Baltimore, MD</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Open until filled</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Competitive Salary</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>A faculty position in civil engineering requiring a Ph.D. to teach undergraduate courses and engage in scholarly activity. | Research Topics: Civil Engineering, Transportation Engineering, Infrastructure Systems</t>
+          <t>The role seeks an adjunct faculty member to teach transportation engineering courses within the civil and environmental engineering department, requiring a relevant graduate degree. | Research Topics: Transportation Engineering, Transit Planning, Traffic Systems</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179544290&amp;Title=Assistant%2FAssociate%20Professor%20of%20Civil%20Engineering</t>
+          <t>https://jobs.chronicle.com/job/37974518/adjunct-faculty-transportation-engineering/</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>HigherEdJobs</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2332,54 +2332,54 @@
         </is>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>39.7540491</v>
+        <v>39.3446663</v>
       </c>
       <c r="R20" s="2" t="n">
-        <v>-83.8170518</v>
+        <v>-76.5836094</v>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>751c7406865a2787</t>
+          <t>3df6fb24b156d70b</t>
         </is>
       </c>
     </row>
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Information and Decision Sciences (Supply Chain &amp; Operations Management)</t>
+          <t>Advanced Transportation Technology Instructor, Part-time Adjunct</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>University of Illinois Chicago</t>
+          <t>Kern Community College District</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Information and Decision Sciences (IDS)</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>3</v>
+          <t>Advanced Transportation Technology</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>5</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Low fit: position is in Supply Chain and Operations Management within a business school, which falls outside the candidate's core transportation engineering and mobility systems profile.</t>
+          <t>Moderate fit: community college instructor position in advanced transportation technology, but lacks tenure-track research focus.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Management, Operations Management, Decision Sciences</t>
+          <t>Advanced Transportation Technology, Vehicle Technologies, Transportation Education</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Non-Tenure Track</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>California</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -2389,27 +2389,27 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>$65.00 Hourly</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>This is a tenure-track Assistant Professor role in Supply Chain and Operations Management requiring a Ph.D. in a relevant business or analytical discipline. | Research Topics: Supply Chain Management, Operations Management, Decision Sciences</t>
+          <t>Part-time adjunct instructor role teaching advanced transportation technology courses at a community college district. | Research Topics: Advanced Transportation Technology, Vehicle Technologies, Transportation Education</t>
         </is>
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179552436&amp;Title=Assistant%20Professor%20%2D%20IDS%20%28Supply%20Chain%20%26%20Operations%20Management%29</t>
+          <t>https://jobs.chronicle.com/job/38026829/advanced-transportation-technology-instructor-part-time-adjunct/</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>HigherEdJobs</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -2423,44 +2423,44 @@
         </is>
       </c>
       <c r="Q21" s="2" t="n">
-        <v>41.8748613</v>
+        <v>37.8719</v>
       </c>
       <c r="R21" s="2" t="n">
-        <v>-87.6519866</v>
+        <v>-122.2585</v>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>77e0632bd4e74eae</t>
+          <t>36f117729bac62c9</t>
         </is>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Professor, Associate Professor, or Assistant Professor of Industrial and Systems Engineering</t>
+          <t>Assistant/Associate/Full Professor, Transportation Engineering and Systems</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Auburn University</t>
+          <t>University of Cincinnati</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Department of Industrial and Systems Engineering</t>
+          <t>Department of Civil and Architectural Engineering and Construction Management</t>
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Moderate fit: Industrial and Systems Engineering faculty position at Auburn University, but the job description text was missing to confirm a specific focus on mobility systems.</t>
+          <t>Core match: explicitly seeks a faculty member in Transportation Engineering and Systems within a Civil Engineering department.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Industrial Engineering, Systems Engineering, Operations Research</t>
+          <t>Transportation Engineering, Transportation Systems, Transit Planning, Mobility Systems</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Auburn, AL</t>
+          <t>Cincinnati, OH</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
@@ -2480,27 +2480,27 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>$80,000 - $180,000 per year</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>Open-rank faculty position in Industrial and Systems Engineering requiring a Ph.D. in industrial engineering, systems engineering, or a closely related field. | Research Topics: Industrial Engineering, Systems Engineering, Operations Research</t>
+          <t>The Department of Civil and Architectural Engineering and Construction Management at the University of Cincinnati is seeking an open-rank faculty member specializing in transportation engineering and systems. | Research Topics: Transportation Engineering, Transportation Systems, Transit Planning, Mobility Systems</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179548357&amp;Title=Professor%2C%20Associate%20Professor%2C%20Assistant%20Professor%20%2D%20Industrial%20and%20Systems%20Engineering</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-associate-full-professor-transportation-engineering-and-systems-at-university-of-cincinnati-4416744025</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>HigherEdJobs</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2514,44 +2514,44 @@
         </is>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>32.5919529</v>
+        <v>39.1318888</v>
       </c>
       <c r="R22" s="2" t="n">
-        <v>-85.4959775</v>
+        <v>-84.51578309999999</v>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>d0f23a527bf71c22</t>
+          <t>6aa8ab000bc6f6c0</t>
         </is>
       </c>
     </row>
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Tenure-Track Assistant Professor of Industrial and Systems Engineering</t>
+          <t>Assistant/Associate Professor of Civil, Architectural and Environmental Engineering</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>University of Tennessee, Knoxville</t>
+          <t>Missouri University of Science and Technology</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Department of Industrial and Systems Engineering</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>7</v>
+          <t>Civil, Architectural and Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>6</v>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Strong interdisciplinary match in Industrial and Systems Engineering with a focus on mobility systems aligned with the candidate's target departments.</t>
+          <t>Moderate fit: a broad Civil, Architectural and Environmental Engineering department search that may include transportation, though the specific sub-discipline focus in the provided snippet is unspecified.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Industrial Engineering, Mobility Systems, Systems Engineering</t>
+          <t>Civil Engineering, Architectural Engineering, Environmental Engineering</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Knoxville, TN</t>
+          <t>Rolla, MO</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -2576,22 +2576,22 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>Tenure-track Assistant Professor position in Industrial and Systems Engineering focusing on mobility systems, requiring a Ph.D. in industrial engineering, systems engineering, or a closely related field. | Research Topics: Industrial Engineering, Mobility Systems, Systems Engineering</t>
+          <t>The position seeks an Assistant or Associate Professor in the Department of Civil, Architectural and Environmental Engineering, requiring a Ph.D. in a relevant discipline. | Research Topics: Civil Engineering, Architectural Engineering, Environmental Engineering</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179545449&amp;Title=Tenure%2DTrack%20Assistant%20Professor%20of%20Industrial%20and%20Systems%20Engineering%2C%20Fall%202027%20%281%2F3%29</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-associate-professor-civil-architectural-and-environmental-engineering-%2300096512-at-missouri-university-of-science-and-technology-4442271248</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>HigherEdJobs</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2605,84 +2605,84 @@
         </is>
       </c>
       <c r="Q23" s="2" t="n">
-        <v>35.9516352</v>
+        <v>37.9532435</v>
       </c>
       <c r="R23" s="2" t="n">
-        <v>-83.9308819</v>
+        <v>-91.7742667</v>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>ecd34777430b7c8d</t>
+          <t>4fad8c46021c1243</t>
         </is>
       </c>
     </row>
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Teaching Assistant Professor</t>
+          <t>Assistant Professor in Transportation Policy</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>University of Arkansas</t>
+          <t>Hunter College</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Department of Urban Policy and Planning, School of Arts and Sciences</t>
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Moderate fit: Broad Civil Engineering faculty search where transportation is only one of multiple acceptable sub-disciplines.</t>
+          <t>Strong interdisciplinary match in an Urban Policy and Planning department specifically seeking expertise in transportation policy, accessibility, and equity.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Civil Engineering Education, Transportation Engineering</t>
+          <t>Transportation Policy, Transit Accessibility, Transportation Equity, Community-Engaged Research</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Non-Tenure Track</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Fayetteville, AR</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>Open until filled</t>
+          <t>Open until filled (Review begins Oct. 1, 2025)</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>$77,092 - $91,922 (plus scheduled increases)</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>A teaching-focused assistant professor position in civil engineering requiring a Ph.D. in civil engineering or a closely related field. | Research Topics: Civil Engineering Education, Transportation Engineering</t>
+          <t>Hunter College seeks a tenure-track Assistant Professor in transportation policy requiring a Ph.D. in policy, planning, or a related field to teach applied policy research and develop a robust research agenda. | Research Topics: Transportation Policy, Transit Accessibility, Transportation Equity, Community-Engaged Research</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179541925&amp;Title=Teaching%20Assistant%20Professor</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-%E2%80%93-urban-policy-and-planning-dept-school-of-arts-and-sciences-hunter-college-at-hunter-college-4438624127</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>HigherEdJobs</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -2696,44 +2696,44 @@
         </is>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>36.0970389</v>
+        <v>40.7683107</v>
       </c>
       <c r="R24" s="2" t="n">
-        <v>-94.1703322</v>
+        <v>-73.964406</v>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8b28f5b58e7e3607</t>
+          <t>e4e18ed629103a27</t>
         </is>
       </c>
     </row>
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Teaching</t>
+          <t>Research Assistant Professor</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Florida Atlantic University</t>
+          <t>University of Houston</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Department of Civil, Environmental &amp; Geomatics Engineering</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="n">
-        <v>5</v>
+          <t>Information Science Technology (CYBER-CARE Consortium)</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>6</v>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Moderate fit: it is a Civil Engineering teaching position in a department with transportation research centers, but requires teaching structural analysis and design-related classes alongside a P.E. license.</t>
+          <t>Moderate fit: the role is a Research Assistant Professor position in transportation engineering, but heavily emphasizes cybersecurity and connected/automated vehicles rather than the candidate's core focus on travel behavior and transit planning.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Civil Engineering Education, Applied Transportation Problems, Infrastructure and Sustainability</t>
+          <t>Connected and Automated Vehicle Cybersecurity, Transportation Data Security, Advanced Traffic Management Systems, Intelligent Transportation Systems</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Boca Raton, FL</t>
+          <t>Houston, TX</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -2753,17 +2753,17 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>Commensurate with Experience</t>
+          <t>Commensurate with experience</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>This is a non-tenure-track Assistant Teaching Professor position in civil engineering requiring a Ph.D. and P.E. license to teach undergraduate and graduate courses including structural analysis and design. | Research Topics: Civil Engineering Education, Applied Transportation Problems, Infrastructure and Sustainability</t>
+          <t>The University of Houston seeks a non-tenure track Research Assistant Professor for the CYBER-CARE consortium to conduct research on transportation cybersecurity and AI applications, requiring a doctoral degree in Transportation Engineering or a closely related field. | Research Topics: Connected and Automated Vehicle Cybersecurity, Transportation Data Security, Advanced Traffic Management Systems, Intelligent Transportation Systems</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-of-teaching-at-florida-atlantic-university-4414964381</t>
+          <t>https://www.linkedin.com/jobs/view/research-assistant-professor-cyber-care-consortium-at-university-of-houston-4404319276</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
@@ -2773,58 +2773,58 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
       <c r="Q25" s="2" t="n">
-        <v>26.1194058</v>
+        <v>29.7207902</v>
       </c>
       <c r="R25" s="2" t="n">
-        <v>-80.14167999999999</v>
+        <v>-95.34406269999999</v>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7bdaa996cf64d1f6</t>
+          <t>c6ee2c0289357949</t>
         </is>
       </c>
     </row>
     <row r="26" ht="26" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Assistant or Associate Professor in Supply Chain Management</t>
+          <t>Tenure-Track Assistant/Associate Professor of Air Transportation Systems</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>University of Arkansas</t>
+          <t>Embry-Riddle Aeronautical University</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>J.B. Hunt Transport Department of Supply Chain Management</t>
+          <t>School of Graduate Studies in the College of Aviation</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Low fit: this is a faculty position in Supply Chain Management within a Business School rather than Transportation Engineering.</t>
+          <t>Moderate-low fit: the position focuses specifically on aviation and aerospace systems (air transportation, advanced air mobility, UAS) rather than surface transportation engineering or mobility.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Management, Logistics, Operations Research</t>
+          <t>Air Transportation Systems, Advanced Air Mobility, UAS Traffic Management, Machine Learning/AI in Aviation</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -2834,12 +2834,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Fayetteville, AR</t>
+          <t>Daytona Beach, FL</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>Review begins immediately; Priority given to applications received by 2026-08-31</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>This is a tenure-track Assistant or Associate Professor position in Supply Chain Management requiring a strong research record in leading peer-reviewed journals. | Research Topics: Supply Chain Management, Logistics, Operations Research</t>
+          <t>This tenure-track faculty position requires a doctorate in air transportation systems, advanced air mobility, or a related area to teach graduate courses and conduct AI/machine learning research in aviation. | Research Topics: Air Transportation Systems, Advanced Air Mobility, UAS Traffic Management, Machine Learning/AI in Aviation</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-or-associate-professor-open-rank-at-university-of-arkansas-%C2%AD-sam-m-walton-college-of-business-4460111187</t>
+          <t>https://www.linkedin.com/jobs/view/tenure-track-faculty-position-with-a-focus-on-air-transportation-systems-daytona-beach-campus-at-embry-riddle-aeronautical-university-4434897662</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
@@ -2864,58 +2864,58 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>36.0625843</v>
+        <v>33.8082375</v>
       </c>
       <c r="R26" s="2" t="n">
-        <v>-94.1574328</v>
+        <v>-118.1344224</v>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>c16a694d5f7f68d4</t>
+          <t>b3c177958e0ab7a7</t>
         </is>
       </c>
     </row>
     <row r="27" ht="26" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Aerospace Engineering</t>
+          <t>Assistant Professor / Associate Professor (Tenure-Track) in Civil and Environmental Engineering</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>The University of Kansas</t>
+          <t>Nanyang Technological University</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Department of Aerospace Engineering</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>3</v>
+          <t>School of Civil and Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>5</v>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>The position is specifically for Aerospace Engineering focusing on aircraft and space systems, where the candidate's core transportation engineering expertise is not the primary requirement.</t>
+          <t>Moderate fit: broad Civil and Environmental Engineering search where Transportation Engineering is a potential sub-discipline, though specific subfield requirements are not detailed in the snippet.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Unmanned aircraft, Advanced air mobility, Aerospace autonomy, Space systems engineering</t>
+          <t>Civil and Environmental Engineering, Transportation Systems, Infrastructure Systems, Smart Cities</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -2925,37 +2925,37 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Lawrence, KS</t>
+          <t>Singapore, Singapore</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>This is a tenure-track faculty position in Aerospace Engineering requiring a doctorate in Aerospace Engineering or a closely related field, focusing on aviation and space-related research. | Research Topics: Unmanned aircraft, Advanced air mobility, Aerospace autonomy, Space systems engineering</t>
+          <t>Tenure-track Assistant or Associate Professor position in Civil and Environmental Engineering requiring an earned doctorate in civil engineering or a closely related discipline. | Research Topics: Civil and Environmental Engineering, Transportation Systems, Infrastructure Systems, Smart Cities</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-aerospace-engineering-at-the-university-of-kansas-4460398978</t>
+          <t>https://engineering.academickeys.com/job/dhzin0q4/Assistant-Professor--Associate-Professor-TenureTrack-in-Civil-and-Environmental-Engineering</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>AcademicKeys</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
@@ -2969,44 +2969,44 @@
         </is>
       </c>
       <c r="Q27" s="2" t="n">
-        <v>39.0559267</v>
+        <v>1.2899175</v>
       </c>
       <c r="R27" s="2" t="n">
-        <v>-94.6090332</v>
+        <v>103.8519072</v>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>4a53cfad86712a72</t>
+          <t>3fa57c30724444e8</t>
         </is>
       </c>
     </row>
     <row r="28" ht="26" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Assistant/Associate/Full Professor in Industrial and Systems Engineering</t>
+          <t>Assistant / Associate / Full Professor of Mechanical Engineering</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>University of Florida</t>
+          <t>Auburn University</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Department of Industrial and Systems Engineering</t>
+          <t>Department of Mechanical Engineering</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Moderate fit: while housed in Industrial and Systems Engineering with a broad mention of transportation applications, the primary departmental focus and hiring emphasis is strictly on Industrialized Construction.</t>
+          <t>Low fit: position is in Mechanical Engineering and lacks description details, which does not align with the candidate's transportation engineering and planning profile.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Industrialized Construction, Operations Research, Artificial Intelligence, Digital Twins</t>
+          <t>Mechanical Engineering, Thermal/Fluids or Mechanical Systems</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -3016,12 +3016,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Gainesville, FL</t>
+          <t>Auburn, AL</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>Open until filled</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3031,17 +3031,17 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>The Department of Industrial and Systems Engineering at the University of Florida seeks a tenured/tenure-track faculty member specializing in Industrialized Construction with a PhD in ISE, Manufacturing Engineering, Civil Engineering, Mechanical Engineering, or a closely related field. | Research Topics: Industrialized Construction, Operations Research, Artificial Intelligence, Digital Twins</t>
+          <t>An open-rank faculty position in mechanical engineering requiring a Ph.D. in mechanical engineering or a closely related field. | Research Topics: Mechanical Engineering, Thermal/Fluids or Mechanical Systems</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-associate-full-professor-industrial-systems-engineering-at-university-of-florida-4323668785</t>
+          <t>https://engineering.academickeys.com/job/f320isty/AssistantAssociateFull-Professor</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>AcademicKeys</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
@@ -3060,44 +3060,44 @@
         </is>
       </c>
       <c r="Q28" s="2" t="n">
-        <v>29.6436</v>
+        <v>32.5919529</v>
       </c>
       <c r="R28" s="2" t="n">
-        <v>-82.3549</v>
+        <v>-85.4959775</v>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>56d501f448e77e05</t>
+          <t>c08698a4bf95171b</t>
         </is>
       </c>
     </row>
     <row r="29" ht="26" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor in Supply Chain Management</t>
+          <t>Assistant / Associate Professor of Industrial and Systems Engineering</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>University of Arkansas</t>
+          <t>University of Washington</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>J.B. Hunt Transport Department of Supply Chain Management, Sam M. Walton College of Business</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>3</v>
+          <t>Industrial and Systems Engineering</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>7</v>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Low fit: Business school faculty position focused entirely on defense-relevant supply chain management and contested logistics, which falls outside transportation engineering.</t>
+          <t>Strong interdisciplinary match: industrial and systems engineering position in a target department, though specific mobility focus depends on the full department scope.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Management, Contested Logistics, Military and Defense Logistics, National Security Supply Chains</t>
+          <t>Industrial and Systems Engineering, Mobility Systems, Systems Optimization</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Fayetteville, AR</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>Unspecified</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3122,17 +3122,17 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>The Sam M. Walton College of Business at the University of Arkansas seeks two tenure-track Assistant Professors in Supply Chain Management as part of a faculty cluster hire focused on contested logistics and defense-relevant supply chains. | Research Topics: Supply Chain Management, Contested Logistics, Military and Defense Logistics, National Security Supply Chains</t>
+          <t>Assistant or Associate Professor position in Industrial and Systems Engineering requiring a Ph.D. in a relevant engineering or analytical discipline. | Research Topics: Industrial and Systems Engineering, Mobility Systems, Systems Optimization</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-two-open-positions-at-university-of-arkansas-%C2%AD-sam-m-walton-college-of-business-4460109211</t>
+          <t>https://engineering.academickeys.com/job/g4m97a60/AssistantAssociate-Professor-Industrial-and-Systems-Engineering-Systems-Engineering-Focus</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>AcademicKeys</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3151,54 +3151,54 @@
         </is>
       </c>
       <c r="Q29" s="2" t="n">
-        <v>36.0625843</v>
+        <v>47.6553</v>
       </c>
       <c r="R29" s="2" t="n">
-        <v>-94.1574328</v>
+        <v>-122.3035</v>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>8b974c86c7dfa1c1</t>
+          <t>9d5682cf4dbca334</t>
         </is>
       </c>
     </row>
     <row r="30" ht="26" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor in Supply Chain Management</t>
+          <t>Professor &amp; Department Chair</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Iowa State University</t>
+          <t>University of Pittsburgh</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Department of Supply Chain Management, Ivy College of Business</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="n">
-        <v>6</v>
+          <t>Department of Civil and Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Moderate fit: the role is in a business school supply chain department rather than engineering or planning, though it accepts transportation as a related specialization.</t>
+          <t>Low fit: departmental leadership position for a broad Civil and Environmental Engineering department rather than a dedicated transportation research faculty role.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Management, Transportation, Logistics, Operations</t>
+          <t>Civil Engineering, Environmental Engineering, Academic Leadership, Departmental Administration</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Tenured</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Ames, IA</t>
+          <t>Pittsburgh, PA</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -3213,17 +3213,17 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>The Ivy College of Business at Iowa State University seeks a tenure-track Assistant Professor in Supply Chain Management to conduct research and teach across undergraduate, master's, and Ph.D. levels, requiring a Ph.D. in business administration or a related field such as transportation or logistics. | Research Topics: Supply Chain Management, Transportation, Logistics, Operations</t>
+          <t>Strictly 1 concise sentence summarizing the primary focus of the role and minimum degree qualification. | Research Topics: Civil Engineering, Environmental Engineering, Academic Leadership, Departmental Administration</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-in-supply-chain-management-at-iowa-state-university-ivy-college-of-business-4440811209</t>
+          <t>http://engineering.academickeys.com/job/vhlo0w6p/Professor--Department-Chair--Electrical-and-Computer-Engineering</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>AcademicKeys</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
@@ -3242,79 +3242,79 @@
         </is>
       </c>
       <c r="Q30" s="2" t="n">
-        <v>42.0267567</v>
+        <v>40.444153</v>
       </c>
       <c r="R30" s="2" t="n">
-        <v>-93.6170448</v>
+        <v>-79.962461</v>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>e994e392d38b77ce</t>
+          <t>17acd4b4e7207871</t>
         </is>
       </c>
     </row>
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor in Operations Management</t>
+          <t>Lecturer in Discipline or Senior Lecturer in Discipline</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>University of Illinois Chicago</t>
+          <t>Columbia University</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Department of Information and Decision Sciences, College of Business Administration</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="n">
-        <v>7</v>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="n">
+        <v>6</v>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Strong interdisciplinary match in a Business School department that explicitly prioritizes transportation and AI in supply chain management as a preferred research domain.</t>
+          <t>Moderate fit: general lecturer position at Columbia University in an unspecified discipline, requiring further text details to confirm a transportation focus.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Operations Management, Transportation, Supply Chain Management, Artificial Intelligence and Analytics</t>
+          <t>Higher Education, Instruction, Academic Teaching</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Non-Tenure Track</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>$185,000 - $220,000 annually</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>The Department of Information and Decision Sciences seeks a tenure-track Assistant Professor in Operations Management with a preferred research focus on transportation and AI-driven supply chain management, requiring a Ph.D. in Management Science, Operations Management, Operations Research, or a closely related field. | Research Topics: Operations Management, Transportation, Supply Chain Management, Artificial Intelligence and Analytics</t>
+          <t>This is a faculty teaching role at Columbia University, though the specific academic department and subject focus are missing from the current snippet. | Research Topics: Higher Education, Instruction, Academic Teaching</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-%E2%80%93-ids-supply-chain-operations-management-at-university-of-illinois-chicago-4463632919</t>
+          <t>http://engineering.academickeys.com/job/arsy3jqh/Open-Rank-Lecturer-in-Discipline-or-Senior-Lecturer-in-Discipline</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>AcademicKeys</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3324,7 +3324,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
@@ -3333,44 +3333,44 @@
         </is>
       </c>
       <c r="Q31" s="2" t="n">
-        <v>41.8748613</v>
+        <v>40.8077507</v>
       </c>
       <c r="R31" s="2" t="n">
-        <v>-87.6519866</v>
+        <v>-73.9624901</v>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>d58da246ce5b68ab</t>
+          <t>f11b4a4e74422ae3</t>
         </is>
       </c>
     </row>
     <row r="32" ht="26" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Public Policy (Market-Based Solutions to Societal Challenges)</t>
+          <t>Assistant/Associate Professor of Civil Engineering</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>University of Wisconsin-Madison</t>
+          <t>Cedarville University</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>La Follette School of Public Affairs, College of Letters &amp; Science</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>3</v>
+          <t>Department of Civil Engineering</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>5</v>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Low fit: Public policy and economics faculty position focused on market-based solutions, though transportation and infrastructure finance is listed as one of many broad application areas.</t>
+          <t>Moderate fit: broad Civil Engineering search where transportation may be acceptable, but lacks a dedicated job description snippet for precise evaluation.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Market-based institutions, Public policy analysis, Transportation and infrastructure finance, Institutional design</t>
+          <t>Civil Engineering, Transportation Engineering, Infrastructure Systems</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Madison, WI</t>
+          <t>Cedarville, OH</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>Open until filled</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3395,17 +3395,17 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>The La Follette School of Public Affairs at UW-Madison seeks a tenure-track assistant professor to conduct theoretically grounded research on market-based solutions and incentive-compatible policy design across various domains. | Research Topics: Market-based institutions, Public policy analysis, Transportation and infrastructure finance, Institutional design</t>
+          <t>A faculty position in civil engineering requiring a Ph.D. to teach undergraduate courses and engage in scholarly activity. | Research Topics: Civil Engineering, Transportation Engineering, Infrastructure Systems</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-of-public-policy-market-based-solutions-to-societal-challenges-at-uw-madison-college-of-letters-science-4435310692</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179544290&amp;Title=Assistant%2FAssociate%20Professor%20of%20Civil%20Engineering</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3424,54 +3424,54 @@
         </is>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>43.07469</v>
+        <v>39.7540491</v>
       </c>
       <c r="R32" s="2" t="n">
-        <v>-89.3841663</v>
+        <v>-83.8170518</v>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>886b76b05d362fdc</t>
+          <t>751c7406865a2787</t>
         </is>
       </c>
     </row>
     <row r="33" ht="26" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Multiple Faculty Positions in Computer Science and Engineering</t>
+          <t>Assistant Professor of Information and Decision Sciences (Supply Chain &amp; Operations Management)</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University</t>
+          <t>University of Illinois Chicago</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Department of Computer Science and Engineering</t>
+          <t>Information and Decision Sciences (IDS)</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Moderate fit: open faculty search in Computer Science and Engineering without explicit specialization in transportation or mobility systems.</t>
+          <t>Low fit: position is in Supply Chain and Operations Management within a business school, which falls outside the candidate's core transportation engineering and mobility systems profile.</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Computer Science, Computer Engineering, Artificial Intelligence, Data Science</t>
+          <t>Supply Chain Management, Operations Management, Decision Sciences</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>College Station, TX</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -3486,22 +3486,22 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University invites applications for multiple faculty positions in Computer Science and Engineering, requiring a Ph.D. in a relevant discipline. | Research Topics: Computer Science, Computer Engineering, Artificial Intelligence, Data Science</t>
+          <t>This is a tenure-track Assistant Professor role in Supply Chain and Operations Management requiring a Ph.D. in a relevant business or analytical discipline. | Research Topics: Supply Chain Management, Operations Management, Decision Sciences</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>http://engineering.academickeys.com/job/rh7lvag4/CSE--TAMU-Multiple-Faculty-Positions</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179552436&amp;Title=Assistant%20Professor%20%2D%20IDS%20%28Supply%20Chain%20%26%20Operations%20Management%29</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>AcademicKeys</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
@@ -3515,54 +3515,54 @@
         </is>
       </c>
       <c r="Q33" s="2" t="n">
-        <v>30.6187</v>
+        <v>41.8748613</v>
       </c>
       <c r="R33" s="2" t="n">
-        <v>-96.3365</v>
+        <v>-87.6519866</v>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>7d5d844d65485b4b</t>
+          <t>77e0632bd4e74eae</t>
         </is>
       </c>
     </row>
     <row r="34" ht="26" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Civil Engineering</t>
+          <t>Professor, Associate Professor, or Assistant Professor of Industrial and Systems Engineering</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>McNeese State University</t>
+          <t>Auburn University</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Civil and Environmental Engineering</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="n">
-        <v>5</v>
+          <t>Department of Industrial and Systems Engineering</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>6</v>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Moderate fit: broad Civil Engineering search where transportation is not explicitly prioritized in the snippet.</t>
+          <t>Moderate fit: Industrial and Systems Engineering faculty position at Auburn University, but the job description text was missing to confirm a specific focus on mobility systems.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Civil Engineering, Engineering Education</t>
+          <t>Industrial Engineering, Systems Engineering, Operations Research</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Lake Charles, LA</t>
+          <t>Auburn, AL</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
@@ -3572,17 +3572,17 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>$76,000 per year</t>
+          <t>$80,000 - $180,000 per year</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>Assistant Professor position in Civil and Environmental Engineering at McNeese State University with a salary of $76,000 per year. | Research Topics: Civil Engineering, Engineering Education</t>
+          <t>Open-rank faculty position in Industrial and Systems Engineering requiring a Ph.D. in industrial engineering, systems engineering, or a closely related field. | Research Topics: Industrial Engineering, Systems Engineering, Operations Research</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179545361&amp;Title=Assistant%20Professor%20of%20Civil%20Engineering</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179548357&amp;Title=Professor%2C%20Associate%20Professor%2C%20Assistant%20Professor%20%2D%20Industrial%20and%20Systems%20Engineering</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -3606,105 +3606,1197 @@
         </is>
       </c>
       <c r="Q34" s="2" t="n">
-        <v>30.1751363</v>
+        <v>32.5919529</v>
       </c>
       <c r="R34" s="2" t="n">
-        <v>-93.2112786</v>
+        <v>-85.4959775</v>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>bd292fb9f52ac2e9</t>
+          <t>d0f23a527bf71c22</t>
         </is>
       </c>
     </row>
     <row r="35" ht="26" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>Teaching Assistant Professor</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>University of Arkansas</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Civil Engineering</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Moderate fit: Broad Civil Engineering faculty search where transportation is only one of multiple acceptable sub-disciplines.</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Civil Engineering Education, Transportation Engineering</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>Non-Tenure Track</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Fayetteville, AR</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>A teaching-focused assistant professor position in civil engineering requiring a Ph.D. in civil engineering or a closely related field. | Research Topics: Civil Engineering Education, Transportation Engineering</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179541925&amp;Title=Teaching%20Assistant%20Professor</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>HigherEdJobs</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="n">
+        <v>36.0970389</v>
+      </c>
+      <c r="R35" s="2" t="n">
+        <v>-94.1703322</v>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>8b28f5b58e7e3607</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="26" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Teaching</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Florida Atlantic University</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Department of Civil, Environmental &amp; Geomatics Engineering</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>Moderate fit: it is a Civil Engineering teaching position in a department with transportation research centers, but requires teaching structural analysis and design-related classes alongside a P.E. license.</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Civil Engineering Education, Applied Transportation Problems, Infrastructure and Sustainability</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>Non-Tenure Track</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Boca Raton, FL</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>Commensurate with Experience</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>This is a non-tenure-track Assistant Teaching Professor position in civil engineering requiring a Ph.D. and P.E. license to teach undergraduate and graduate courses including structural analysis and design. | Research Topics: Civil Engineering Education, Applied Transportation Problems, Infrastructure and Sustainability</t>
+        </is>
+      </c>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-of-teaching-at-florida-atlantic-university-4414964381</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="n">
+        <v>26.1194058</v>
+      </c>
+      <c r="R36" s="2" t="n">
+        <v>-80.14167999999999</v>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>7bdaa996cf64d1f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="26" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Assistant or Associate Professor in Supply Chain Management</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>University of Arkansas</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>J.B. Hunt Transport Department of Supply Chain Management</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Low fit: this is a faculty position in Supply Chain Management within a Business School rather than Transportation Engineering.</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Management, Logistics, Operations Research</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>Tenure-Track</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Fayetteville, AR</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>This is a tenure-track Assistant or Associate Professor position in Supply Chain Management requiring a strong research record in leading peer-reviewed journals. | Research Topics: Supply Chain Management, Logistics, Operations Research</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/assistant-or-associate-professor-open-rank-at-university-of-arkansas-%C2%AD-sam-m-walton-college-of-business-4460111187</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="n">
+        <v>36.0625843</v>
+      </c>
+      <c r="R37" s="2" t="n">
+        <v>-94.1574328</v>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>c16a694d5f7f68d4</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="26" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Aerospace Engineering</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>The University of Kansas</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Department of Aerospace Engineering</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>The position is specifically for Aerospace Engineering focusing on aircraft and space systems, where the candidate's core transportation engineering expertise is not the primary requirement.</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Unmanned aircraft, Advanced air mobility, Aerospace autonomy, Space systems engineering</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>Tenure-Track</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Lawrence, KS</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>This is a tenure-track faculty position in Aerospace Engineering requiring a doctorate in Aerospace Engineering or a closely related field, focusing on aviation and space-related research. | Research Topics: Unmanned aircraft, Advanced air mobility, Aerospace autonomy, Space systems engineering</t>
+        </is>
+      </c>
+      <c r="L38" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-aerospace-engineering-at-the-university-of-kansas-4460398978</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="n">
+        <v>39.0559267</v>
+      </c>
+      <c r="R38" s="2" t="n">
+        <v>-94.6090332</v>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>4a53cfad86712a72</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="26" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Assistant/Associate/Full Professor in Industrial and Systems Engineering</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>University of Florida</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Department of Industrial and Systems Engineering</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>Moderate fit: while housed in Industrial and Systems Engineering with a broad mention of transportation applications, the primary departmental focus and hiring emphasis is strictly on Industrialized Construction.</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Industrialized Construction, Operations Research, Artificial Intelligence, Digital Twins</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>Tenure-Track</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Gainesville, FL</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>The Department of Industrial and Systems Engineering at the University of Florida seeks a tenured/tenure-track faculty member specializing in Industrialized Construction with a PhD in ISE, Manufacturing Engineering, Civil Engineering, Mechanical Engineering, or a closely related field. | Research Topics: Industrialized Construction, Operations Research, Artificial Intelligence, Digital Twins</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/assistant-associate-full-professor-industrial-systems-engineering-at-university-of-florida-4323668785</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="n">
+        <v>29.6436</v>
+      </c>
+      <c r="R39" s="2" t="n">
+        <v>-82.3549</v>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>56d501f448e77e05</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="26" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Professor in Supply Chain Management</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>University of Arkansas</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>J.B. Hunt Transport Department of Supply Chain Management, Sam M. Walton College of Business</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>Low fit: Business school faculty position focused entirely on defense-relevant supply chain management and contested logistics, which falls outside transportation engineering.</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Management, Contested Logistics, Military and Defense Logistics, National Security Supply Chains</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>Tenure-Track</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Fayetteville, AR</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>The Sam M. Walton College of Business at the University of Arkansas seeks two tenure-track Assistant Professors in Supply Chain Management as part of a faculty cluster hire focused on contested logistics and defense-relevant supply chains. | Research Topics: Supply Chain Management, Contested Logistics, Military and Defense Logistics, National Security Supply Chains</t>
+        </is>
+      </c>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-two-open-positions-at-university-of-arkansas-%C2%AD-sam-m-walton-college-of-business-4460109211</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="n">
+        <v>36.0625843</v>
+      </c>
+      <c r="R40" s="2" t="n">
+        <v>-94.1574328</v>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>8b974c86c7dfa1c1</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="26" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Professor in Supply Chain Management</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Iowa State University</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Department of Supply Chain Management, Ivy College of Business</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>Moderate fit: the role is in a business school supply chain department rather than engineering or planning, though it accepts transportation as a related specialization.</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Management, Transportation, Logistics, Operations</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>Tenure-Track</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Ames, IA</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>The Ivy College of Business at Iowa State University seeks a tenure-track Assistant Professor in Supply Chain Management to conduct research and teach across undergraduate, master's, and Ph.D. levels, requiring a Ph.D. in business administration or a related field such as transportation or logistics. | Research Topics: Supply Chain Management, Transportation, Logistics, Operations</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-in-supply-chain-management-at-iowa-state-university-ivy-college-of-business-4440811209</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="n">
+        <v>42.0267567</v>
+      </c>
+      <c r="R41" s="2" t="n">
+        <v>-93.6170448</v>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>e994e392d38b77ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="26" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Professor in Operations Management</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>University of Illinois Chicago</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Department of Information and Decision Sciences, College of Business Administration</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>Strong interdisciplinary match in a Business School department that explicitly prioritizes transportation and AI in supply chain management as a preferred research domain.</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Operations Management, Transportation, Supply Chain Management, Artificial Intelligence and Analytics</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>Tenure-Track</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Chicago, IL</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>2026-12-06</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>$185,000 - $220,000 annually</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>The Department of Information and Decision Sciences seeks a tenure-track Assistant Professor in Operations Management with a preferred research focus on transportation and AI-driven supply chain management, requiring a Ph.D. in Management Science, Operations Management, Operations Research, or a closely related field. | Research Topics: Operations Management, Transportation, Supply Chain Management, Artificial Intelligence and Analytics</t>
+        </is>
+      </c>
+      <c r="L42" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-%E2%80%93-ids-supply-chain-operations-management-at-university-of-illinois-chicago-4463632919</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="n">
+        <v>41.8748613</v>
+      </c>
+      <c r="R42" s="2" t="n">
+        <v>-87.6519866</v>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>d58da246ce5b68ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="26" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Public Policy (Market-Based Solutions to Societal Challenges)</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>University of Wisconsin-Madison</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>La Follette School of Public Affairs, College of Letters &amp; Science</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>Low fit: Public policy and economics faculty position focused on market-based solutions, though transportation and infrastructure finance is listed as one of many broad application areas.</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Market-based institutions, Public policy analysis, Transportation and infrastructure finance, Institutional design</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>Tenure-Track</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Madison, WI</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="K43" s="4" t="inlineStr">
+        <is>
+          <t>The La Follette School of Public Affairs at UW-Madison seeks a tenure-track assistant professor to conduct theoretically grounded research on market-based solutions and incentive-compatible policy design across various domains. | Research Topics: Market-based institutions, Public policy analysis, Transportation and infrastructure finance, Institutional design</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-of-public-policy-market-based-solutions-to-societal-challenges-at-uw-madison-college-of-letters-science-4435310692</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="n">
+        <v>43.07469</v>
+      </c>
+      <c r="R43" s="2" t="n">
+        <v>-89.3841663</v>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>886b76b05d362fdc</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="26" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Multiple Faculty Positions in Computer Science and Engineering</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Texas A&amp;M University</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Department of Computer Science and Engineering</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>Moderate fit: open faculty search in Computer Science and Engineering without explicit specialization in transportation or mobility systems.</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Computer Science, Computer Engineering, Artificial Intelligence, Data Science</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>College Station, TX</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="K44" s="4" t="inlineStr">
+        <is>
+          <t>Texas A&amp;M University invites applications for multiple faculty positions in Computer Science and Engineering, requiring a Ph.D. in a relevant discipline. | Research Topics: Computer Science, Computer Engineering, Artificial Intelligence, Data Science</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="inlineStr">
+        <is>
+          <t>http://engineering.academickeys.com/job/rh7lvag4/CSE--TAMU-Multiple-Faculty-Positions</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>AcademicKeys</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="n">
+        <v>30.6187</v>
+      </c>
+      <c r="R44" s="2" t="n">
+        <v>-96.3365</v>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>7d5d844d65485b4b</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="26" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Civil Engineering</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>McNeese State University</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Civil and Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>Moderate fit: broad Civil Engineering search where transportation is not explicitly prioritized in the snippet.</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Civil Engineering, Engineering Education</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Lake Charles, LA</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>$76,000 per year</t>
+        </is>
+      </c>
+      <c r="K45" s="4" t="inlineStr">
+        <is>
+          <t>Assistant Professor position in Civil and Environmental Engineering at McNeese State University with a salary of $76,000 per year. | Research Topics: Civil Engineering, Engineering Education</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179545361&amp;Title=Assistant%20Professor%20of%20Civil%20Engineering</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>HigherEdJobs</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="n">
+        <v>30.1751363</v>
+      </c>
+      <c r="R45" s="2" t="n">
+        <v>-93.2112786</v>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>bd292fb9f52ac2e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="26" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
           <t>Tenure-Track Faculty Positions in Transportation Engineering</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>National Taiwan University</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>Department of Civil Engineering</t>
         </is>
       </c>
-      <c r="D35" s="7" t="n">
+      <c r="D46" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="E46" s="4" t="inlineStr">
         <is>
           <t>Core match: seeks multiple tenure-track faculty positions specifically in the Transportation track within a Department of Civil Engineering.</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Transportation Engineering, Mobility Systems, Transit Planning</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="G46" s="3" t="inlineStr">
         <is>
           <t>Tenure-Track</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>Taipei, Taiwan</t>
         </is>
       </c>
-      <c r="I35" s="3" t="inlineStr">
+      <c r="I46" s="3" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="J46" s="2" t="inlineStr">
         <is>
           <t>NT$83,720–137,370 monthly</t>
         </is>
       </c>
-      <c r="K35" s="4" t="inlineStr">
+      <c r="K46" s="4" t="inlineStr">
         <is>
           <t>The Department of Civil Engineering at National Taiwan University invites applications for multiple tenure-track faculty positions in Transportation Engineering. | Research Topics: Transportation Engineering, Mobility Systems, Transit Planning</t>
         </is>
       </c>
-      <c r="L35" s="5" t="inlineStr">
+      <c r="L46" s="5" t="inlineStr">
         <is>
           <t>https://jobs.chronicle.com/job/38034402/faculty-recruitment-announcement-department-of-civil-engineering-national-taiwan-university/</t>
         </is>
       </c>
-      <c r="M35" s="3" t="inlineStr">
+      <c r="M46" s="3" t="inlineStr">
         <is>
           <t>Chronicle</t>
         </is>
       </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="P35" s="3" t="inlineStr">
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="Q35" s="2" t="n">
+      <c r="Q46" s="2" t="n">
         <v>25.0375198</v>
       </c>
-      <c r="R35" s="2" t="n">
+      <c r="R46" s="2" t="n">
         <v>121.5636796</v>
       </c>
-      <c r="S35" s="2" t="inlineStr">
+      <c r="S46" s="2" t="inlineStr">
         <is>
           <t>f056997ace2e1de7</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="26" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Public Policy and Administration</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>University of Texas at Arlington</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Department of Public Affairs &amp; Planning</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>Moderate fit: Assistant Professor in Public Affairs &amp; Planning focused on public policy and urban studies, offering potential interdisciplinary overlap despite lacking a specific transportation mandate.</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Public Policy, Urban Studies, Public Infrastructure, Interdisciplinary Public Administration</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>Tenure-Track</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>Arlington, TX</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="K47" s="4" t="inlineStr">
+        <is>
+          <t>The University of Texas at Arlington seeks a tenure-track Assistant Professor in Public Policy &amp; Planning to conduct policy research, secure external funding, and teach public administration courses requiring a Ph.D. | Research Topics: Public Policy, Urban Studies, Public Infrastructure, Interdisciplinary Public Administration</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-at-excel-campus-activities-4464851831</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="P47" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="n">
+        <v>32.7315155</v>
+      </c>
+      <c r="R47" s="2" t="n">
+        <v>-97.1171533</v>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>15704bb25858281c</t>
         </is>
       </c>
     </row>
@@ -3744,6 +4836,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId46"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -493,12 +493,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S47"/>
+  <dimension ref="A1:S43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="95" customWidth="1" min="3" max="3"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="32" customWidth="1" min="5" max="5"/>
     <col width="151" customWidth="1" min="6" max="6"/>
@@ -3438,30 +3438,30 @@
     <row r="33" ht="26" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Information and Decision Sciences (Supply Chain &amp; Operations Management)</t>
+          <t>Professor, Associate Professor, or Assistant Professor of Industrial and Systems Engineering</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>University of Illinois Chicago</t>
+          <t>Auburn University</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Information and Decision Sciences (IDS)</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>3</v>
+          <t>Department of Industrial and Systems Engineering</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="n">
+        <v>6</v>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Low fit: position is in Supply Chain and Operations Management within a business school, which falls outside the candidate's core transportation engineering and mobility systems profile.</t>
+          <t>Moderate fit: Industrial and Systems Engineering faculty position at Auburn University, but the job description text was missing to confirm a specific focus on mobility systems.</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Management, Operations Management, Decision Sciences</t>
+          <t>Industrial Engineering, Systems Engineering, Operations Research</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>Auburn, AL</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -3481,17 +3481,17 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>$80,000 - $180,000 per year</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>This is a tenure-track Assistant Professor role in Supply Chain and Operations Management requiring a Ph.D. in a relevant business or analytical discipline. | Research Topics: Supply Chain Management, Operations Management, Decision Sciences</t>
+          <t>Open-rank faculty position in Industrial and Systems Engineering requiring a Ph.D. in industrial engineering, systems engineering, or a closely related field. | Research Topics: Industrial Engineering, Systems Engineering, Operations Research</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179552436&amp;Title=Assistant%20Professor%20%2D%20IDS%20%28Supply%20Chain%20%26%20Operations%20Management%29</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179548357&amp;Title=Professor%2C%20Associate%20Professor%2C%20Assistant%20Professor%20%2D%20Industrial%20and%20Systems%20Engineering</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
@@ -3515,54 +3515,54 @@
         </is>
       </c>
       <c r="Q33" s="2" t="n">
-        <v>41.8748613</v>
+        <v>32.5919529</v>
       </c>
       <c r="R33" s="2" t="n">
-        <v>-87.6519866</v>
+        <v>-85.4959775</v>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>77e0632bd4e74eae</t>
+          <t>d0f23a527bf71c22</t>
         </is>
       </c>
     </row>
     <row r="34" ht="26" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Professor, Associate Professor, or Assistant Professor of Industrial and Systems Engineering</t>
+          <t>Teaching Assistant Professor</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Auburn University</t>
+          <t>University of Arkansas</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Department of Industrial and Systems Engineering</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="D34" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Moderate fit: Industrial and Systems Engineering faculty position at Auburn University, but the job description text was missing to confirm a specific focus on mobility systems.</t>
+          <t>Moderate fit: Broad Civil Engineering faculty search where transportation is only one of multiple acceptable sub-disciplines.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Industrial Engineering, Systems Engineering, Operations Research</t>
+          <t>Civil Engineering Education, Transportation Engineering</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Non-Tenure Track</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Auburn, AL</t>
+          <t>Fayetteville, AR</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
@@ -3572,17 +3572,17 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>$80,000 - $180,000 per year</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>Open-rank faculty position in Industrial and Systems Engineering requiring a Ph.D. in industrial engineering, systems engineering, or a closely related field. | Research Topics: Industrial Engineering, Systems Engineering, Operations Research</t>
+          <t>A teaching-focused assistant professor position in civil engineering requiring a Ph.D. in civil engineering or a closely related field. | Research Topics: Civil Engineering Education, Transportation Engineering</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179548357&amp;Title=Professor%2C%20Associate%20Professor%2C%20Assistant%20Professor%20%2D%20Industrial%20and%20Systems%20Engineering</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179541925&amp;Title=Teaching%20Assistant%20Professor</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
@@ -3606,31 +3606,31 @@
         </is>
       </c>
       <c r="Q34" s="2" t="n">
-        <v>32.5919529</v>
+        <v>36.0970389</v>
       </c>
       <c r="R34" s="2" t="n">
-        <v>-85.4959775</v>
+        <v>-94.1703322</v>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>d0f23a527bf71c22</t>
+          <t>8b28f5b58e7e3607</t>
         </is>
       </c>
     </row>
     <row r="35" ht="26" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Teaching Assistant Professor</t>
+          <t>Assistant Professor of Teaching</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>University of Arkansas</t>
+          <t>Florida Atlantic University</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Department of Civil, Environmental &amp; Geomatics Engineering</t>
         </is>
       </c>
       <c r="D35" s="7" t="n">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Moderate fit: Broad Civil Engineering faculty search where transportation is only one of multiple acceptable sub-disciplines.</t>
+          <t>Moderate fit: it is a Civil Engineering teaching position in a department with transportation research centers, but requires teaching structural analysis and design-related classes alongside a P.E. license.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Civil Engineering Education, Transportation Engineering</t>
+          <t>Civil Engineering Education, Applied Transportation Problems, Infrastructure and Sustainability</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Fayetteville, AR</t>
+          <t>Boca Raton, FL</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
@@ -3663,22 +3663,22 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Commensurate with Experience</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>A teaching-focused assistant professor position in civil engineering requiring a Ph.D. in civil engineering or a closely related field. | Research Topics: Civil Engineering Education, Transportation Engineering</t>
+          <t>This is a non-tenure-track Assistant Teaching Professor position in civil engineering requiring a Ph.D. and P.E. license to teach undergraduate and graduate courses including structural analysis and design. | Research Topics: Civil Engineering Education, Applied Transportation Problems, Infrastructure and Sustainability</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179541925&amp;Title=Teaching%20Assistant%20Professor</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-of-teaching-at-florida-atlantic-university-4414964381</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>HigherEdJobs</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
@@ -3697,74 +3697,74 @@
         </is>
       </c>
       <c r="Q35" s="2" t="n">
-        <v>36.0970389</v>
+        <v>26.1194058</v>
       </c>
       <c r="R35" s="2" t="n">
-        <v>-94.1703322</v>
+        <v>-80.14167999999999</v>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>8b28f5b58e7e3607</t>
+          <t>7bdaa996cf64d1f6</t>
         </is>
       </c>
     </row>
     <row r="36" ht="26" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Teaching</t>
+          <t>Assistant or Associate Professor in Supply Chain Management</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Florida Atlantic University</t>
+          <t>University of Arkansas</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Department of Civil, Environmental &amp; Geomatics Engineering</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="n">
-        <v>5</v>
+          <t>J.B. Hunt Transport Department of Supply Chain Management</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Moderate fit: it is a Civil Engineering teaching position in a department with transportation research centers, but requires teaching structural analysis and design-related classes alongside a P.E. license.</t>
+          <t>Low fit: this is a faculty position in Supply Chain Management within a Business School rather than Transportation Engineering.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Civil Engineering Education, Applied Transportation Problems, Infrastructure and Sustainability</t>
+          <t>Supply Chain Management, Logistics, Operations Research</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>Non-Tenure Track</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Boca Raton, FL</t>
+          <t>Fayetteville, AR</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>Open until filled</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>Commensurate with Experience</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>This is a non-tenure-track Assistant Teaching Professor position in civil engineering requiring a Ph.D. and P.E. license to teach undergraduate and graduate courses including structural analysis and design. | Research Topics: Civil Engineering Education, Applied Transportation Problems, Infrastructure and Sustainability</t>
+          <t>This is a tenure-track Assistant or Associate Professor position in Supply Chain Management requiring a strong research record in leading peer-reviewed journals. | Research Topics: Supply Chain Management, Logistics, Operations Research</t>
         </is>
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-of-teaching-at-florida-atlantic-university-4414964381</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-or-associate-professor-open-rank-at-university-of-arkansas-%C2%AD-sam-m-walton-college-of-business-4460111187</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
@@ -3779,7 +3779,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
@@ -3788,31 +3788,31 @@
         </is>
       </c>
       <c r="Q36" s="2" t="n">
-        <v>26.1194058</v>
+        <v>36.0625843</v>
       </c>
       <c r="R36" s="2" t="n">
-        <v>-80.14167999999999</v>
+        <v>-94.1574328</v>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>7bdaa996cf64d1f6</t>
+          <t>c16a694d5f7f68d4</t>
         </is>
       </c>
     </row>
     <row r="37" ht="26" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Assistant or Associate Professor in Supply Chain Management</t>
+          <t>Assistant Professor of Aerospace Engineering</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>University of Arkansas</t>
+          <t>The University of Kansas</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>J.B. Hunt Transport Department of Supply Chain Management</t>
+          <t>Department of Aerospace Engineering</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Low fit: this is a faculty position in Supply Chain Management within a Business School rather than Transportation Engineering.</t>
+          <t>The position is specifically for Aerospace Engineering focusing on aircraft and space systems, where the candidate's core transportation engineering expertise is not the primary requirement.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Management, Logistics, Operations Research</t>
+          <t>Unmanned aircraft, Advanced air mobility, Aerospace autonomy, Space systems engineering</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Fayetteville, AR</t>
+          <t>Lawrence, KS</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>This is a tenure-track Assistant or Associate Professor position in Supply Chain Management requiring a strong research record in leading peer-reviewed journals. | Research Topics: Supply Chain Management, Logistics, Operations Research</t>
+          <t>This is a tenure-track faculty position in Aerospace Engineering requiring a doctorate in Aerospace Engineering or a closely related field, focusing on aviation and space-related research. | Research Topics: Unmanned aircraft, Advanced air mobility, Aerospace autonomy, Space systems engineering</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-or-associate-professor-open-rank-at-university-of-arkansas-%C2%AD-sam-m-walton-college-of-business-4460111187</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-aerospace-engineering-at-the-university-of-kansas-4460398978</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
@@ -3879,44 +3879,44 @@
         </is>
       </c>
       <c r="Q37" s="2" t="n">
-        <v>36.0625843</v>
+        <v>39.0559267</v>
       </c>
       <c r="R37" s="2" t="n">
-        <v>-94.1574328</v>
+        <v>-94.6090332</v>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>c16a694d5f7f68d4</t>
+          <t>4a53cfad86712a72</t>
         </is>
       </c>
     </row>
     <row r="38" ht="26" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Aerospace Engineering</t>
+          <t>Assistant/Associate/Full Professor in Industrial and Systems Engineering</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>The University of Kansas</t>
+          <t>University of Florida</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Department of Aerospace Engineering</t>
+          <t>Department of Industrial and Systems Engineering</t>
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>The position is specifically for Aerospace Engineering focusing on aircraft and space systems, where the candidate's core transportation engineering expertise is not the primary requirement.</t>
+          <t>Moderate fit: while housed in Industrial and Systems Engineering with a broad mention of transportation applications, the primary departmental focus and hiring emphasis is strictly on Industrialized Construction.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Unmanned aircraft, Advanced air mobility, Aerospace autonomy, Space systems engineering</t>
+          <t>Industrialized Construction, Operations Research, Artificial Intelligence, Digital Twins</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -3926,27 +3926,27 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Lawrence, KS</t>
+          <t>Gainesville, FL</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>This is a tenure-track faculty position in Aerospace Engineering requiring a doctorate in Aerospace Engineering or a closely related field, focusing on aviation and space-related research. | Research Topics: Unmanned aircraft, Advanced air mobility, Aerospace autonomy, Space systems engineering</t>
+          <t>The Department of Industrial and Systems Engineering at the University of Florida seeks a tenured/tenure-track faculty member specializing in Industrialized Construction with a PhD in ISE, Manufacturing Engineering, Civil Engineering, Mechanical Engineering, or a closely related field. | Research Topics: Industrialized Construction, Operations Research, Artificial Intelligence, Digital Twins</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-aerospace-engineering-at-the-university-of-kansas-4460398978</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-associate-full-professor-industrial-systems-engineering-at-university-of-florida-4323668785</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
@@ -3970,44 +3970,44 @@
         </is>
       </c>
       <c r="Q38" s="2" t="n">
-        <v>39.0559267</v>
+        <v>29.6436</v>
       </c>
       <c r="R38" s="2" t="n">
-        <v>-94.6090332</v>
+        <v>-82.3549</v>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>4a53cfad86712a72</t>
+          <t>56d501f448e77e05</t>
         </is>
       </c>
     </row>
     <row r="39" ht="26" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Assistant/Associate/Full Professor in Industrial and Systems Engineering</t>
+          <t>Assistant Professor in Supply Chain Management</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>University of Florida</t>
+          <t>Iowa State University</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Department of Industrial and Systems Engineering</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>4</v>
+          <t>Department of Supply Chain Management, Ivy College of Business</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="n">
+        <v>6</v>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Moderate fit: while housed in Industrial and Systems Engineering with a broad mention of transportation applications, the primary departmental focus and hiring emphasis is strictly on Industrialized Construction.</t>
+          <t>Moderate fit: the role is in a business school supply chain department rather than engineering or planning, though it accepts transportation as a related specialization.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Industrialized Construction, Operations Research, Artificial Intelligence, Digital Twins</t>
+          <t>Supply Chain Management, Transportation, Logistics, Operations</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Gainesville, FL</t>
+          <t>Ames, IA</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>The Department of Industrial and Systems Engineering at the University of Florida seeks a tenured/tenure-track faculty member specializing in Industrialized Construction with a PhD in ISE, Manufacturing Engineering, Civil Engineering, Mechanical Engineering, or a closely related field. | Research Topics: Industrialized Construction, Operations Research, Artificial Intelligence, Digital Twins</t>
+          <t>The Ivy College of Business at Iowa State University seeks a tenure-track Assistant Professor in Supply Chain Management to conduct research and teach across undergraduate, master's, and Ph.D. levels, requiring a Ph.D. in business administration or a related field such as transportation or logistics. | Research Topics: Supply Chain Management, Transportation, Logistics, Operations</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-associate-full-professor-industrial-systems-engineering-at-university-of-florida-4323668785</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-in-supply-chain-management-at-iowa-state-university-ivy-college-of-business-4440811209</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
@@ -4061,59 +4061,59 @@
         </is>
       </c>
       <c r="Q39" s="2" t="n">
-        <v>29.6436</v>
+        <v>42.0267567</v>
       </c>
       <c r="R39" s="2" t="n">
-        <v>-82.3549</v>
+        <v>-93.6170448</v>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>56d501f448e77e05</t>
+          <t>e994e392d38b77ce</t>
         </is>
       </c>
     </row>
     <row r="40" ht="26" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor in Supply Chain Management</t>
+          <t>Multiple Faculty Positions in Computer Science and Engineering</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>University of Arkansas</t>
+          <t>Texas A&amp;M University</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>J.B. Hunt Transport Department of Supply Chain Management, Sam M. Walton College of Business</t>
+          <t>Department of Computer Science and Engineering</t>
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Low fit: Business school faculty position focused entirely on defense-relevant supply chain management and contested logistics, which falls outside transportation engineering.</t>
+          <t>Moderate fit: open faculty search in Computer Science and Engineering without explicit specialization in transportation or mobility systems.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Management, Contested Logistics, Military and Defense Logistics, National Security Supply Chains</t>
+          <t>Computer Science, Computer Engineering, Artificial Intelligence, Data Science</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Unspecified</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Fayetteville, AR</t>
+          <t>College Station, TX</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>Open until filled</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4123,22 +4123,22 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>The Sam M. Walton College of Business at the University of Arkansas seeks two tenure-track Assistant Professors in Supply Chain Management as part of a faculty cluster hire focused on contested logistics and defense-relevant supply chains. | Research Topics: Supply Chain Management, Contested Logistics, Military and Defense Logistics, National Security Supply Chains</t>
+          <t>Texas A&amp;M University invites applications for multiple faculty positions in Computer Science and Engineering, requiring a Ph.D. in a relevant discipline. | Research Topics: Computer Science, Computer Engineering, Artificial Intelligence, Data Science</t>
         </is>
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-two-open-positions-at-university-of-arkansas-%C2%AD-sam-m-walton-college-of-business-4460109211</t>
+          <t>http://engineering.academickeys.com/job/rh7lvag4/CSE--TAMU-Multiple-Faculty-Positions</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>AcademicKeys</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -4152,54 +4152,54 @@
         </is>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>36.0625843</v>
+        <v>30.6187</v>
       </c>
       <c r="R40" s="2" t="n">
-        <v>-94.1574328</v>
+        <v>-96.3365</v>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>8b974c86c7dfa1c1</t>
+          <t>7d5d844d65485b4b</t>
         </is>
       </c>
     </row>
     <row r="41" ht="26" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor in Supply Chain Management</t>
+          <t>Assistant Professor of Civil Engineering</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Iowa State University</t>
+          <t>McNeese State University</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Department of Supply Chain Management, Ivy College of Business</t>
+          <t>Civil and Environmental Engineering</t>
         </is>
       </c>
       <c r="D41" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Moderate fit: the role is in a business school supply chain department rather than engineering or planning, though it accepts transportation as a related specialization.</t>
+          <t>Moderate fit: broad Civil Engineering search where transportation is not explicitly prioritized in the snippet.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Management, Transportation, Logistics, Operations</t>
+          <t>Civil Engineering, Engineering Education</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Unspecified</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Ames, IA</t>
+          <t>Lake Charles, LA</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>$76,000 per year</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>The Ivy College of Business at Iowa State University seeks a tenure-track Assistant Professor in Supply Chain Management to conduct research and teach across undergraduate, master's, and Ph.D. levels, requiring a Ph.D. in business administration or a related field such as transportation or logistics. | Research Topics: Supply Chain Management, Transportation, Logistics, Operations</t>
+          <t>Assistant Professor position in Civil and Environmental Engineering at McNeese State University with a salary of $76,000 per year. | Research Topics: Civil Engineering, Engineering Education</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-in-supply-chain-management-at-iowa-state-university-ivy-college-of-business-4440811209</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179545361&amp;Title=Assistant%20Professor%20of%20Civil%20Engineering</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
@@ -4243,44 +4243,44 @@
         </is>
       </c>
       <c r="Q41" s="2" t="n">
-        <v>42.0267567</v>
+        <v>30.1751363</v>
       </c>
       <c r="R41" s="2" t="n">
-        <v>-93.6170448</v>
+        <v>-93.2112786</v>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>e994e392d38b77ce</t>
+          <t>bd292fb9f52ac2e9</t>
         </is>
       </c>
     </row>
     <row r="42" ht="26" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor in Operations Management</t>
+          <t>Tenure-Track Faculty Positions in Transportation Engineering</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>University of Illinois Chicago</t>
+          <t>National Taiwan University</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Department of Information and Decision Sciences, College of Business Administration</t>
-        </is>
-      </c>
-      <c r="D42" s="7" t="n">
-        <v>7</v>
+          <t>Department of Civil Engineering</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="n">
+        <v>9</v>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Strong interdisciplinary match in a Business School department that explicitly prioritizes transportation and AI in supply chain management as a preferred research domain.</t>
+          <t>Core match: seeks multiple tenure-track faculty positions specifically in the Transportation track within a Department of Civil Engineering.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Operations Management, Transportation, Supply Chain Management, Artificial Intelligence and Analytics</t>
+          <t>Transportation Engineering, Mobility Systems, Transit Planning</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -4290,42 +4290,42 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>Taipei, Taiwan</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>$185,000 - $220,000 annually</t>
+          <t>NT$83,720–137,370 monthly</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>The Department of Information and Decision Sciences seeks a tenure-track Assistant Professor in Operations Management with a preferred research focus on transportation and AI-driven supply chain management, requiring a Ph.D. in Management Science, Operations Management, Operations Research, or a closely related field. | Research Topics: Operations Management, Transportation, Supply Chain Management, Artificial Intelligence and Analytics</t>
+          <t>The Department of Civil Engineering at National Taiwan University invites applications for multiple tenure-track faculty positions in Transportation Engineering. | Research Topics: Transportation Engineering, Mobility Systems, Transit Planning</t>
         </is>
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-%E2%80%93-ids-supply-chain-operations-management-at-university-of-illinois-chicago-4463632919</t>
+          <t>https://jobs.chronicle.com/job/38034402/faculty-recruitment-announcement-department-of-civil-engineering-national-taiwan-university/</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
@@ -4334,44 +4334,44 @@
         </is>
       </c>
       <c r="Q42" s="2" t="n">
-        <v>41.8748613</v>
+        <v>25.0375198</v>
       </c>
       <c r="R42" s="2" t="n">
-        <v>-87.6519866</v>
+        <v>121.5636796</v>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>d58da246ce5b68ab</t>
+          <t>f056997ace2e1de7</t>
         </is>
       </c>
     </row>
     <row r="43" ht="26" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Public Policy (Market-Based Solutions to Societal Challenges)</t>
+          <t>Assistant Professor of Public Policy and Administration</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>University of Wisconsin-Madison</t>
+          <t>University of Texas at Arlington</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>La Follette School of Public Affairs, College of Letters &amp; Science</t>
+          <t>Department of Public Affairs &amp; Planning</t>
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Low fit: Public policy and economics faculty position focused on market-based solutions, though transportation and infrastructure finance is listed as one of many broad application areas.</t>
+          <t>Moderate fit: Assistant Professor in Public Affairs &amp; Planning focused on public policy and urban studies, offering potential interdisciplinary overlap despite lacking a specific transportation mandate.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Market-based institutions, Public policy analysis, Transportation and infrastructure finance, Institutional design</t>
+          <t>Public Policy, Urban Studies, Public Infrastructure, Interdisciplinary Public Administration</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Madison, WI</t>
+          <t>Arlington, TX</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>The La Follette School of Public Affairs at UW-Madison seeks a tenure-track assistant professor to conduct theoretically grounded research on market-based solutions and incentive-compatible policy design across various domains. | Research Topics: Market-based institutions, Public policy analysis, Transportation and infrastructure finance, Institutional design</t>
+          <t>The University of Texas at Arlington seeks a tenure-track Assistant Professor in Public Policy &amp; Planning to conduct policy research, secure external funding, and teach public administration courses requiring a Ph.D. | Research Topics: Public Policy, Urban Studies, Public Infrastructure, Interdisciplinary Public Administration</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-of-public-policy-market-based-solutions-to-societal-challenges-at-uw-madison-college-of-letters-science-4435310692</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-at-excel-campus-activities-4464851831</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
@@ -4425,376 +4425,12 @@
         </is>
       </c>
       <c r="Q43" s="2" t="n">
-        <v>43.07469</v>
+        <v>32.7315155</v>
       </c>
       <c r="R43" s="2" t="n">
-        <v>-89.3841663</v>
+        <v>-97.1171533</v>
       </c>
       <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>886b76b05d362fdc</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="26" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>Multiple Faculty Positions in Computer Science and Engineering</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>Texas A&amp;M University</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Department of Computer Science and Engineering</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>Moderate fit: open faculty search in Computer Science and Engineering without explicit specialization in transportation or mobility systems.</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Computer Science, Computer Engineering, Artificial Intelligence, Data Science</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t>Unspecified</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>College Station, TX</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t>Open until filled</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="K44" s="4" t="inlineStr">
-        <is>
-          <t>Texas A&amp;M University invites applications for multiple faculty positions in Computer Science and Engineering, requiring a Ph.D. in a relevant discipline. | Research Topics: Computer Science, Computer Engineering, Artificial Intelligence, Data Science</t>
-        </is>
-      </c>
-      <c r="L44" s="5" t="inlineStr">
-        <is>
-          <t>http://engineering.academickeys.com/job/rh7lvag4/CSE--TAMU-Multiple-Faculty-Positions</t>
-        </is>
-      </c>
-      <c r="M44" s="3" t="inlineStr">
-        <is>
-          <t>AcademicKeys</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="P44" s="3" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="n">
-        <v>30.6187</v>
-      </c>
-      <c r="R44" s="2" t="n">
-        <v>-96.3365</v>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t>7d5d844d65485b4b</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="26" customHeight="1">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>Assistant Professor of Civil Engineering</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>McNeese State University</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Civil and Environmental Engineering</t>
-        </is>
-      </c>
-      <c r="D45" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>Moderate fit: broad Civil Engineering search where transportation is not explicitly prioritized in the snippet.</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>Civil Engineering, Engineering Education</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t>Unspecified</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>Lake Charles, LA</t>
-        </is>
-      </c>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t>Open until filled</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>$76,000 per year</t>
-        </is>
-      </c>
-      <c r="K45" s="4" t="inlineStr">
-        <is>
-          <t>Assistant Professor position in Civil and Environmental Engineering at McNeese State University with a salary of $76,000 per year. | Research Topics: Civil Engineering, Engineering Education</t>
-        </is>
-      </c>
-      <c r="L45" s="5" t="inlineStr">
-        <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179545361&amp;Title=Assistant%20Professor%20of%20Civil%20Engineering</t>
-        </is>
-      </c>
-      <c r="M45" s="3" t="inlineStr">
-        <is>
-          <t>HigherEdJobs</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="P45" s="3" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="Q45" s="2" t="n">
-        <v>30.1751363</v>
-      </c>
-      <c r="R45" s="2" t="n">
-        <v>-93.2112786</v>
-      </c>
-      <c r="S45" s="2" t="inlineStr">
-        <is>
-          <t>bd292fb9f52ac2e9</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="26" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>Tenure-Track Faculty Positions in Transportation Engineering</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>National Taiwan University</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Department of Civil Engineering</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>Core match: seeks multiple tenure-track faculty positions specifically in the Transportation track within a Department of Civil Engineering.</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>Transportation Engineering, Mobility Systems, Transit Planning</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t>Tenure-Track</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>Taipei, Taiwan</t>
-        </is>
-      </c>
-      <c r="I46" s="3" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>NT$83,720–137,370 monthly</t>
-        </is>
-      </c>
-      <c r="K46" s="4" t="inlineStr">
-        <is>
-          <t>The Department of Civil Engineering at National Taiwan University invites applications for multiple tenure-track faculty positions in Transportation Engineering. | Research Topics: Transportation Engineering, Mobility Systems, Transit Planning</t>
-        </is>
-      </c>
-      <c r="L46" s="5" t="inlineStr">
-        <is>
-          <t>https://jobs.chronicle.com/job/38034402/faculty-recruitment-announcement-department-of-civil-engineering-national-taiwan-university/</t>
-        </is>
-      </c>
-      <c r="M46" s="3" t="inlineStr">
-        <is>
-          <t>Chronicle</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="P46" s="3" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="n">
-        <v>25.0375198</v>
-      </c>
-      <c r="R46" s="2" t="n">
-        <v>121.5636796</v>
-      </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t>f056997ace2e1de7</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="26" customHeight="1">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>Assistant Professor of Public Policy and Administration</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>University of Texas at Arlington</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>Department of Public Affairs &amp; Planning</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>Moderate fit: Assistant Professor in Public Affairs &amp; Planning focused on public policy and urban studies, offering potential interdisciplinary overlap despite lacking a specific transportation mandate.</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>Public Policy, Urban Studies, Public Infrastructure, Interdisciplinary Public Administration</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr">
-        <is>
-          <t>Tenure-Track</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>Arlington, TX</t>
-        </is>
-      </c>
-      <c r="I47" s="3" t="inlineStr">
-        <is>
-          <t>Open until filled</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="K47" s="4" t="inlineStr">
-        <is>
-          <t>The University of Texas at Arlington seeks a tenure-track Assistant Professor in Public Policy &amp; Planning to conduct policy research, secure external funding, and teach public administration courses requiring a Ph.D. | Research Topics: Public Policy, Urban Studies, Public Infrastructure, Interdisciplinary Public Administration</t>
-        </is>
-      </c>
-      <c r="L47" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-at-excel-campus-activities-4464851831</t>
-        </is>
-      </c>
-      <c r="M47" s="3" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="O47" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="P47" s="3" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="Q47" s="2" t="n">
-        <v>32.7315155</v>
-      </c>
-      <c r="R47" s="2" t="n">
-        <v>-97.1171533</v>
-      </c>
-      <c r="S47" s="2" t="inlineStr">
         <is>
           <t>15704bb25858281c</t>
         </is>
@@ -4844,10 +4480,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId46"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -622,7 +622,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Chronicle Listed University</t>
+          <t>Embry-Riddle Aeronautical University</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -694,10 +694,10 @@
         </is>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>29.2108147</v>
+        <v>29.1895</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>-81.0228331</v>
+        <v>-81.04940000000001</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
@@ -785,10 +785,10 @@
         </is>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>32.898417</v>
+        <v>41.8837</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-80.05262430000001</v>
+        <v>-87.6324</v>
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S43"/>
+  <dimension ref="A1:S42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -504,7 +504,7 @@
     <col width="151" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="83" customWidth="1" min="9" max="9"/>
+    <col width="49" customWidth="1" min="9" max="9"/>
     <col width="96" customWidth="1" min="10" max="10"/>
     <col width="42" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
@@ -928,7 +928,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Open until filled</t>
+          <t>Priority: 2026-09-15 / Final: 2026-11-01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>Open until filled</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2801,30 +2801,30 @@
     <row r="26" ht="26" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Tenure-Track Assistant/Associate Professor of Air Transportation Systems</t>
+          <t>Assistant Professor / Associate Professor (Tenure-Track) in Civil and Environmental Engineering</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Embry-Riddle Aeronautical University</t>
+          <t>Nanyang Technological University</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>School of Graduate Studies in the College of Aviation</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>4</v>
+          <t>School of Civil and Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>5</v>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Moderate-low fit: the position focuses specifically on aviation and aerospace systems (air transportation, advanced air mobility, UAS) rather than surface transportation engineering or mobility.</t>
+          <t>Moderate fit: broad Civil and Environmental Engineering search where Transportation Engineering is a potential sub-discipline, though specific subfield requirements are not detailed in the snippet.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Air Transportation Systems, Advanced Air Mobility, UAS Traffic Management, Machine Learning/AI in Aviation</t>
+          <t>Civil and Environmental Engineering, Transportation Systems, Infrastructure Systems, Smart Cities</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -2834,12 +2834,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL</t>
+          <t>Singapore, Singapore</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>Review begins immediately; Priority given to applications received by 2026-08-31</t>
+          <t>Open until filled</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2849,27 +2849,27 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>This tenure-track faculty position requires a doctorate in air transportation systems, advanced air mobility, or a related area to teach graduate courses and conduct AI/machine learning research in aviation. | Research Topics: Air Transportation Systems, Advanced Air Mobility, UAS Traffic Management, Machine Learning/AI in Aviation</t>
+          <t>Tenure-track Assistant or Associate Professor position in Civil and Environmental Engineering requiring an earned doctorate in civil engineering or a closely related discipline. | Research Topics: Civil and Environmental Engineering, Transportation Systems, Infrastructure Systems, Smart Cities</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/tenure-track-faculty-position-with-a-focus-on-air-transportation-systems-daytona-beach-campus-at-embry-riddle-aeronautical-university-4434897662</t>
+          <t>https://engineering.academickeys.com/job/dhzin0q4/Assistant-Professor--Associate-Professor-TenureTrack-in-Civil-and-Environmental-Engineering</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>AcademicKeys</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
@@ -2878,44 +2878,44 @@
         </is>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>33.8082375</v>
+        <v>1.2899175</v>
       </c>
       <c r="R26" s="2" t="n">
-        <v>-118.1344224</v>
+        <v>103.8519072</v>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>b3c177958e0ab7a7</t>
+          <t>3fa57c30724444e8</t>
         </is>
       </c>
     </row>
     <row r="27" ht="26" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor / Associate Professor (Tenure-Track) in Civil and Environmental Engineering</t>
+          <t>Assistant / Associate / Full Professor of Mechanical Engineering</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Nanyang Technological University</t>
+          <t>Auburn University</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>School of Civil and Environmental Engineering</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="n">
-        <v>5</v>
+          <t>Department of Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Moderate fit: broad Civil and Environmental Engineering search where Transportation Engineering is a potential sub-discipline, though specific subfield requirements are not detailed in the snippet.</t>
+          <t>Low fit: position is in Mechanical Engineering and lacks description details, which does not align with the candidate's transportation engineering and planning profile.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Civil and Environmental Engineering, Transportation Systems, Infrastructure Systems, Smart Cities</t>
+          <t>Mechanical Engineering, Thermal/Fluids or Mechanical Systems</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Singapore, Singapore</t>
+          <t>Auburn, AL</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>Open until filled</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>Tenure-track Assistant or Associate Professor position in Civil and Environmental Engineering requiring an earned doctorate in civil engineering or a closely related discipline. | Research Topics: Civil and Environmental Engineering, Transportation Systems, Infrastructure Systems, Smart Cities</t>
+          <t>An open-rank faculty position in mechanical engineering requiring a Ph.D. in mechanical engineering or a closely related field. | Research Topics: Mechanical Engineering, Thermal/Fluids or Mechanical Systems</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>https://engineering.academickeys.com/job/dhzin0q4/Assistant-Professor--Associate-Professor-TenureTrack-in-Civil-and-Environmental-Engineering</t>
+          <t>https://engineering.academickeys.com/job/f320isty/AssistantAssociateFull-Professor</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
@@ -2969,44 +2969,44 @@
         </is>
       </c>
       <c r="Q27" s="2" t="n">
-        <v>1.2899175</v>
+        <v>32.5919529</v>
       </c>
       <c r="R27" s="2" t="n">
-        <v>103.8519072</v>
+        <v>-85.4959775</v>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>3fa57c30724444e8</t>
+          <t>c08698a4bf95171b</t>
         </is>
       </c>
     </row>
     <row r="28" ht="26" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Assistant / Associate / Full Professor of Mechanical Engineering</t>
+          <t>Assistant / Associate Professor of Industrial and Systems Engineering</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Auburn University</t>
+          <t>University of Washington</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Department of Mechanical Engineering</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>3</v>
+          <t>Industrial and Systems Engineering</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>7</v>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Low fit: position is in Mechanical Engineering and lacks description details, which does not align with the candidate's transportation engineering and planning profile.</t>
+          <t>Strong interdisciplinary match: industrial and systems engineering position in a target department, though specific mobility focus depends on the full department scope.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Mechanical Engineering, Thermal/Fluids or Mechanical Systems</t>
+          <t>Industrial and Systems Engineering, Mobility Systems, Systems Optimization</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -3016,27 +3016,27 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Auburn, AL</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>An open-rank faculty position in mechanical engineering requiring a Ph.D. in mechanical engineering or a closely related field. | Research Topics: Mechanical Engineering, Thermal/Fluids or Mechanical Systems</t>
+          <t>Assistant or Associate Professor position in Industrial and Systems Engineering requiring a Ph.D. in a relevant engineering or analytical discipline. | Research Topics: Industrial and Systems Engineering, Mobility Systems, Systems Optimization</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>https://engineering.academickeys.com/job/f320isty/AssistantAssociateFull-Professor</t>
+          <t>https://engineering.academickeys.com/job/g4m97a60/AssistantAssociate-Professor-Industrial-and-Systems-Engineering-Systems-Engineering-Focus</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
@@ -3060,59 +3060,59 @@
         </is>
       </c>
       <c r="Q28" s="2" t="n">
-        <v>32.5919529</v>
+        <v>47.6553</v>
       </c>
       <c r="R28" s="2" t="n">
-        <v>-85.4959775</v>
+        <v>-122.3035</v>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>c08698a4bf95171b</t>
+          <t>9d5682cf4dbca334</t>
         </is>
       </c>
     </row>
     <row r="29" ht="26" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Assistant / Associate Professor of Industrial and Systems Engineering</t>
+          <t>Professor &amp; Department Chair</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>University of Washington</t>
+          <t>University of Pittsburgh</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Industrial and Systems Engineering</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="n">
-        <v>7</v>
+          <t>Department of Civil and Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Strong interdisciplinary match: industrial and systems engineering position in a target department, though specific mobility focus depends on the full department scope.</t>
+          <t>Low fit: departmental leadership position for a broad Civil and Environmental Engineering department rather than a dedicated transportation research faculty role.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Industrial and Systems Engineering, Mobility Systems, Systems Optimization</t>
+          <t>Civil Engineering, Environmental Engineering, Academic Leadership, Departmental Administration</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Tenured</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Pittsburgh, PA</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Open until filled</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3122,12 +3122,12 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>Assistant or Associate Professor position in Industrial and Systems Engineering requiring a Ph.D. in a relevant engineering or analytical discipline. | Research Topics: Industrial and Systems Engineering, Mobility Systems, Systems Optimization</t>
+          <t>Strictly 1 concise sentence summarizing the primary focus of the role and minimum degree qualification. | Research Topics: Civil Engineering, Environmental Engineering, Academic Leadership, Departmental Administration</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>https://engineering.academickeys.com/job/g4m97a60/AssistantAssociate-Professor-Industrial-and-Systems-Engineering-Systems-Engineering-Focus</t>
+          <t>http://engineering.academickeys.com/job/vhlo0w6p/Professor--Department-Chair--Electrical-and-Computer-Engineering</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
@@ -3151,59 +3151,59 @@
         </is>
       </c>
       <c r="Q29" s="2" t="n">
-        <v>47.6553</v>
+        <v>40.444153</v>
       </c>
       <c r="R29" s="2" t="n">
-        <v>-122.3035</v>
+        <v>-79.962461</v>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>9d5682cf4dbca334</t>
+          <t>17acd4b4e7207871</t>
         </is>
       </c>
     </row>
     <row r="30" ht="26" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Professor &amp; Department Chair</t>
+          <t>Lecturer in Discipline or Senior Lecturer in Discipline</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>University of Pittsburgh</t>
+          <t>Columbia University</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Department of Civil and Environmental Engineering</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="n">
-        <v>3</v>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>6</v>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Low fit: departmental leadership position for a broad Civil and Environmental Engineering department rather than a dedicated transportation research faculty role.</t>
+          <t>Moderate fit: general lecturer position at Columbia University in an unspecified discipline, requiring further text details to confirm a transportation focus.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Civil Engineering, Environmental Engineering, Academic Leadership, Departmental Administration</t>
+          <t>Higher Education, Instruction, Academic Teaching</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Tenured</t>
+          <t>Non-Tenure Track</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>Open until filled</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3213,12 +3213,12 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>Strictly 1 concise sentence summarizing the primary focus of the role and minimum degree qualification. | Research Topics: Civil Engineering, Environmental Engineering, Academic Leadership, Departmental Administration</t>
+          <t>This is a faculty teaching role at Columbia University, though the specific academic department and subject focus are missing from the current snippet. | Research Topics: Higher Education, Instruction, Academic Teaching</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>http://engineering.academickeys.com/job/vhlo0w6p/Professor--Department-Chair--Electrical-and-Computer-Engineering</t>
+          <t>http://engineering.academickeys.com/job/arsy3jqh/Open-Rank-Lecturer-in-Discipline-or-Senior-Lecturer-in-Discipline</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
@@ -3242,79 +3242,79 @@
         </is>
       </c>
       <c r="Q30" s="2" t="n">
-        <v>40.444153</v>
+        <v>40.8077507</v>
       </c>
       <c r="R30" s="2" t="n">
-        <v>-79.962461</v>
+        <v>-73.9624901</v>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>17acd4b4e7207871</t>
+          <t>f11b4a4e74422ae3</t>
         </is>
       </c>
     </row>
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Lecturer in Discipline or Senior Lecturer in Discipline</t>
+          <t>Assistant/Associate Professor of Civil Engineering</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Columbia University</t>
+          <t>Cedarville University</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>Department of Civil Engineering</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Moderate fit: broad Civil Engineering search where transportation may be acceptable, but lacks a dedicated job description snippet for precise evaluation.</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Civil Engineering, Transportation Engineering, Infrastructure Systems</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>Tenure-Track</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Cedarville, OH</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="D31" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>Moderate fit: general lecturer position at Columbia University in an unspecified discipline, requiring further text details to confirm a transportation focus.</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>Higher Education, Instruction, Academic Teaching</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>Non-Tenure Track</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>New York, NY</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>This is a faculty teaching role at Columbia University, though the specific academic department and subject focus are missing from the current snippet. | Research Topics: Higher Education, Instruction, Academic Teaching</t>
+          <t>A faculty position in civil engineering requiring a Ph.D. to teach undergraduate courses and engage in scholarly activity. | Research Topics: Civil Engineering, Transportation Engineering, Infrastructure Systems</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>http://engineering.academickeys.com/job/arsy3jqh/Open-Rank-Lecturer-in-Discipline-or-Senior-Lecturer-in-Discipline</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179544290&amp;Title=Assistant%2FAssociate%20Professor%20of%20Civil%20Engineering</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>AcademicKeys</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3333,44 +3333,44 @@
         </is>
       </c>
       <c r="Q31" s="2" t="n">
-        <v>40.8077507</v>
+        <v>39.7540491</v>
       </c>
       <c r="R31" s="2" t="n">
-        <v>-73.9624901</v>
+        <v>-83.8170518</v>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>f11b4a4e74422ae3</t>
+          <t>751c7406865a2787</t>
         </is>
       </c>
     </row>
     <row r="32" ht="26" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Assistant/Associate Professor of Civil Engineering</t>
+          <t>Professor, Associate Professor, or Assistant Professor of Industrial and Systems Engineering</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Cedarville University</t>
+          <t>Auburn University</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Department of Civil Engineering</t>
+          <t>Department of Industrial and Systems Engineering</t>
         </is>
       </c>
       <c r="D32" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Moderate fit: broad Civil Engineering search where transportation may be acceptable, but lacks a dedicated job description snippet for precise evaluation.</t>
+          <t>Moderate fit: Industrial and Systems Engineering faculty position at Auburn University, but the job description text was missing to confirm a specific focus on mobility systems.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Civil Engineering, Transportation Engineering, Infrastructure Systems</t>
+          <t>Industrial Engineering, Systems Engineering, Operations Research</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -3380,27 +3380,27 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Cedarville, OH</t>
+          <t>Auburn, AL</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Open until filled</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>$80,000 - $180,000 per year</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>A faculty position in civil engineering requiring a Ph.D. to teach undergraduate courses and engage in scholarly activity. | Research Topics: Civil Engineering, Transportation Engineering, Infrastructure Systems</t>
+          <t>Open-rank faculty position in Industrial and Systems Engineering requiring a Ph.D. in industrial engineering, systems engineering, or a closely related field. | Research Topics: Industrial Engineering, Systems Engineering, Operations Research</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179544290&amp;Title=Assistant%2FAssociate%20Professor%20of%20Civil%20Engineering</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179548357&amp;Title=Professor%2C%20Associate%20Professor%2C%20Assistant%20Professor%20%2D%20Industrial%20and%20Systems%20Engineering</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
@@ -3424,54 +3424,54 @@
         </is>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>39.7540491</v>
+        <v>32.5919529</v>
       </c>
       <c r="R32" s="2" t="n">
-        <v>-83.8170518</v>
+        <v>-85.4959775</v>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>751c7406865a2787</t>
+          <t>d0f23a527bf71c22</t>
         </is>
       </c>
     </row>
     <row r="33" ht="26" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Professor, Associate Professor, or Assistant Professor of Industrial and Systems Engineering</t>
+          <t>Teaching Assistant Professor</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Auburn University</t>
+          <t>University of Arkansas</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Department of Industrial and Systems Engineering</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="D33" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Moderate fit: Industrial and Systems Engineering faculty position at Auburn University, but the job description text was missing to confirm a specific focus on mobility systems.</t>
+          <t>Moderate fit: Broad Civil Engineering faculty search where transportation is only one of multiple acceptable sub-disciplines.</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Industrial Engineering, Systems Engineering, Operations Research</t>
+          <t>Civil Engineering Education, Transportation Engineering</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Non-Tenure Track</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Auburn, AL</t>
+          <t>Fayetteville, AR</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -3481,17 +3481,17 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>$80,000 - $180,000 per year</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>Open-rank faculty position in Industrial and Systems Engineering requiring a Ph.D. in industrial engineering, systems engineering, or a closely related field. | Research Topics: Industrial Engineering, Systems Engineering, Operations Research</t>
+          <t>A teaching-focused assistant professor position in civil engineering requiring a Ph.D. in civil engineering or a closely related field. | Research Topics: Civil Engineering Education, Transportation Engineering</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179548357&amp;Title=Professor%2C%20Associate%20Professor%2C%20Assistant%20Professor%20%2D%20Industrial%20and%20Systems%20Engineering</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179541925&amp;Title=Teaching%20Assistant%20Professor</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
@@ -3515,31 +3515,31 @@
         </is>
       </c>
       <c r="Q33" s="2" t="n">
-        <v>32.5919529</v>
+        <v>36.0970389</v>
       </c>
       <c r="R33" s="2" t="n">
-        <v>-85.4959775</v>
+        <v>-94.1703322</v>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>d0f23a527bf71c22</t>
+          <t>8b28f5b58e7e3607</t>
         </is>
       </c>
     </row>
     <row r="34" ht="26" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Teaching Assistant Professor</t>
+          <t>Assistant Professor of Teaching</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>University of Arkansas</t>
+          <t>Florida Atlantic University</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Department of Civil, Environmental &amp; Geomatics Engineering</t>
         </is>
       </c>
       <c r="D34" s="7" t="n">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Moderate fit: Broad Civil Engineering faculty search where transportation is only one of multiple acceptable sub-disciplines.</t>
+          <t>Moderate fit: it is a Civil Engineering teaching position in a department with transportation research centers, but requires teaching structural analysis and design-related classes alongside a P.E. license.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Civil Engineering Education, Transportation Engineering</t>
+          <t>Civil Engineering Education, Applied Transportation Problems, Infrastructure and Sustainability</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Fayetteville, AR</t>
+          <t>Boca Raton, FL</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
@@ -3572,22 +3572,22 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Commensurate with Experience</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>A teaching-focused assistant professor position in civil engineering requiring a Ph.D. in civil engineering or a closely related field. | Research Topics: Civil Engineering Education, Transportation Engineering</t>
+          <t>This is a non-tenure-track Assistant Teaching Professor position in civil engineering requiring a Ph.D. and P.E. license to teach undergraduate and graduate courses including structural analysis and design. | Research Topics: Civil Engineering Education, Applied Transportation Problems, Infrastructure and Sustainability</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179541925&amp;Title=Teaching%20Assistant%20Professor</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-of-teaching-at-florida-atlantic-university-4414964381</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>HigherEdJobs</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
@@ -3606,74 +3606,74 @@
         </is>
       </c>
       <c r="Q34" s="2" t="n">
-        <v>36.0970389</v>
+        <v>26.1194058</v>
       </c>
       <c r="R34" s="2" t="n">
-        <v>-94.1703322</v>
+        <v>-80.14167999999999</v>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>8b28f5b58e7e3607</t>
+          <t>7bdaa996cf64d1f6</t>
         </is>
       </c>
     </row>
     <row r="35" ht="26" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Teaching</t>
+          <t>Assistant or Associate Professor in Supply Chain Management</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Florida Atlantic University</t>
+          <t>University of Arkansas</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Department of Civil, Environmental &amp; Geomatics Engineering</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="n">
-        <v>5</v>
+          <t>J.B. Hunt Transport Department of Supply Chain Management</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Moderate fit: it is a Civil Engineering teaching position in a department with transportation research centers, but requires teaching structural analysis and design-related classes alongside a P.E. license.</t>
+          <t>Low fit: this is a faculty position in Supply Chain Management within a Business School rather than Transportation Engineering.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Civil Engineering Education, Applied Transportation Problems, Infrastructure and Sustainability</t>
+          <t>Supply Chain Management, Logistics, Operations Research</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>Non-Tenure Track</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Boca Raton, FL</t>
+          <t>Fayetteville, AR</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>Open until filled</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>Commensurate with Experience</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>This is a non-tenure-track Assistant Teaching Professor position in civil engineering requiring a Ph.D. and P.E. license to teach undergraduate and graduate courses including structural analysis and design. | Research Topics: Civil Engineering Education, Applied Transportation Problems, Infrastructure and Sustainability</t>
+          <t>This is a tenure-track Assistant or Associate Professor position in Supply Chain Management requiring a strong research record in leading peer-reviewed journals. | Research Topics: Supply Chain Management, Logistics, Operations Research</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-of-teaching-at-florida-atlantic-university-4414964381</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-or-associate-professor-open-rank-at-university-of-arkansas-%C2%AD-sam-m-walton-college-of-business-4460111187</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
@@ -3697,31 +3697,31 @@
         </is>
       </c>
       <c r="Q35" s="2" t="n">
-        <v>26.1194058</v>
+        <v>36.0625843</v>
       </c>
       <c r="R35" s="2" t="n">
-        <v>-80.14167999999999</v>
+        <v>-94.1574328</v>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>7bdaa996cf64d1f6</t>
+          <t>c16a694d5f7f68d4</t>
         </is>
       </c>
     </row>
     <row r="36" ht="26" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Assistant or Associate Professor in Supply Chain Management</t>
+          <t>Assistant Professor of Aerospace Engineering</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>University of Arkansas</t>
+          <t>The University of Kansas</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>J.B. Hunt Transport Department of Supply Chain Management</t>
+          <t>Department of Aerospace Engineering</t>
         </is>
       </c>
       <c r="D36" s="3" t="n">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Low fit: this is a faculty position in Supply Chain Management within a Business School rather than Transportation Engineering.</t>
+          <t>The position is specifically for Aerospace Engineering focusing on aircraft and space systems, where the candidate's core transportation engineering expertise is not the primary requirement.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Management, Logistics, Operations Research</t>
+          <t>Unmanned aircraft, Advanced air mobility, Aerospace autonomy, Space systems engineering</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Fayetteville, AR</t>
+          <t>Lawrence, KS</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>This is a tenure-track Assistant or Associate Professor position in Supply Chain Management requiring a strong research record in leading peer-reviewed journals. | Research Topics: Supply Chain Management, Logistics, Operations Research</t>
+          <t>This is a tenure-track faculty position in Aerospace Engineering requiring a doctorate in Aerospace Engineering or a closely related field, focusing on aviation and space-related research. | Research Topics: Unmanned aircraft, Advanced air mobility, Aerospace autonomy, Space systems engineering</t>
         </is>
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-or-associate-professor-open-rank-at-university-of-arkansas-%C2%AD-sam-m-walton-college-of-business-4460111187</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-aerospace-engineering-at-the-university-of-kansas-4460398978</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
@@ -3788,44 +3788,44 @@
         </is>
       </c>
       <c r="Q36" s="2" t="n">
-        <v>36.0625843</v>
+        <v>39.0559267</v>
       </c>
       <c r="R36" s="2" t="n">
-        <v>-94.1574328</v>
+        <v>-94.6090332</v>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>c16a694d5f7f68d4</t>
+          <t>4a53cfad86712a72</t>
         </is>
       </c>
     </row>
     <row r="37" ht="26" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Aerospace Engineering</t>
+          <t>Assistant/Associate/Full Professor in Industrial and Systems Engineering</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>The University of Kansas</t>
+          <t>University of Florida</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Department of Aerospace Engineering</t>
+          <t>Department of Industrial and Systems Engineering</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>The position is specifically for Aerospace Engineering focusing on aircraft and space systems, where the candidate's core transportation engineering expertise is not the primary requirement.</t>
+          <t>Moderate fit: while housed in Industrial and Systems Engineering with a broad mention of transportation applications, the primary departmental focus and hiring emphasis is strictly on Industrialized Construction.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Unmanned aircraft, Advanced air mobility, Aerospace autonomy, Space systems engineering</t>
+          <t>Industrialized Construction, Operations Research, Artificial Intelligence, Digital Twins</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -3835,27 +3835,27 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Lawrence, KS</t>
+          <t>Gainesville, FL</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>This is a tenure-track faculty position in Aerospace Engineering requiring a doctorate in Aerospace Engineering or a closely related field, focusing on aviation and space-related research. | Research Topics: Unmanned aircraft, Advanced air mobility, Aerospace autonomy, Space systems engineering</t>
+          <t>The Department of Industrial and Systems Engineering at the University of Florida seeks a tenured/tenure-track faculty member specializing in Industrialized Construction with a PhD in ISE, Manufacturing Engineering, Civil Engineering, Mechanical Engineering, or a closely related field. | Research Topics: Industrialized Construction, Operations Research, Artificial Intelligence, Digital Twins</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-aerospace-engineering-at-the-university-of-kansas-4460398978</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-associate-full-professor-industrial-systems-engineering-at-university-of-florida-4323668785</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
@@ -3879,44 +3879,44 @@
         </is>
       </c>
       <c r="Q37" s="2" t="n">
-        <v>39.0559267</v>
+        <v>29.6436</v>
       </c>
       <c r="R37" s="2" t="n">
-        <v>-94.6090332</v>
+        <v>-82.3549</v>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>4a53cfad86712a72</t>
+          <t>56d501f448e77e05</t>
         </is>
       </c>
     </row>
     <row r="38" ht="26" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Assistant/Associate/Full Professor in Industrial and Systems Engineering</t>
+          <t>Assistant Professor in Supply Chain Management</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>University of Florida</t>
+          <t>Iowa State University</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Department of Industrial and Systems Engineering</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="n">
-        <v>4</v>
+          <t>Department of Supply Chain Management, Ivy College of Business</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>6</v>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Moderate fit: while housed in Industrial and Systems Engineering with a broad mention of transportation applications, the primary departmental focus and hiring emphasis is strictly on Industrialized Construction.</t>
+          <t>Moderate fit: the role is in a business school supply chain department rather than engineering or planning, though it accepts transportation as a related specialization.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Industrialized Construction, Operations Research, Artificial Intelligence, Digital Twins</t>
+          <t>Supply Chain Management, Transportation, Logistics, Operations</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Gainesville, FL</t>
+          <t>Ames, IA</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>The Department of Industrial and Systems Engineering at the University of Florida seeks a tenured/tenure-track faculty member specializing in Industrialized Construction with a PhD in ISE, Manufacturing Engineering, Civil Engineering, Mechanical Engineering, or a closely related field. | Research Topics: Industrialized Construction, Operations Research, Artificial Intelligence, Digital Twins</t>
+          <t>The Ivy College of Business at Iowa State University seeks a tenure-track Assistant Professor in Supply Chain Management to conduct research and teach across undergraduate, master's, and Ph.D. levels, requiring a Ph.D. in business administration or a related field such as transportation or logistics. | Research Topics: Supply Chain Management, Transportation, Logistics, Operations</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-associate-full-professor-industrial-systems-engineering-at-university-of-florida-4323668785</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-in-supply-chain-management-at-iowa-state-university-ivy-college-of-business-4440811209</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
@@ -3970,54 +3970,54 @@
         </is>
       </c>
       <c r="Q38" s="2" t="n">
-        <v>29.6436</v>
+        <v>42.0267567</v>
       </c>
       <c r="R38" s="2" t="n">
-        <v>-82.3549</v>
+        <v>-93.6170448</v>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>56d501f448e77e05</t>
+          <t>e994e392d38b77ce</t>
         </is>
       </c>
     </row>
     <row r="39" ht="26" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor in Supply Chain Management</t>
+          <t>Multiple Faculty Positions in Computer Science and Engineering</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Iowa State University</t>
+          <t>Texas A&amp;M University</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Department of Supply Chain Management, Ivy College of Business</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="n">
-        <v>6</v>
+          <t>Department of Computer Science and Engineering</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Moderate fit: the role is in a business school supply chain department rather than engineering or planning, though it accepts transportation as a related specialization.</t>
+          <t>Moderate fit: open faculty search in Computer Science and Engineering without explicit specialization in transportation or mobility systems.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Management, Transportation, Logistics, Operations</t>
+          <t>Computer Science, Computer Engineering, Artificial Intelligence, Data Science</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Unspecified</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Ames, IA</t>
+          <t>College Station, TX</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
@@ -4032,27 +4032,27 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>The Ivy College of Business at Iowa State University seeks a tenure-track Assistant Professor in Supply Chain Management to conduct research and teach across undergraduate, master's, and Ph.D. levels, requiring a Ph.D. in business administration or a related field such as transportation or logistics. | Research Topics: Supply Chain Management, Transportation, Logistics, Operations</t>
+          <t>Texas A&amp;M University invites applications for multiple faculty positions in Computer Science and Engineering, requiring a Ph.D. in a relevant discipline. | Research Topics: Computer Science, Computer Engineering, Artificial Intelligence, Data Science</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-in-supply-chain-management-at-iowa-state-university-ivy-college-of-business-4440811209</t>
+          <t>http://engineering.academickeys.com/job/rh7lvag4/CSE--TAMU-Multiple-Faculty-Positions</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>AcademicKeys</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
@@ -4061,44 +4061,44 @@
         </is>
       </c>
       <c r="Q39" s="2" t="n">
-        <v>42.0267567</v>
+        <v>30.6187</v>
       </c>
       <c r="R39" s="2" t="n">
-        <v>-93.6170448</v>
+        <v>-96.3365</v>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>e994e392d38b77ce</t>
+          <t>7d5d844d65485b4b</t>
         </is>
       </c>
     </row>
     <row r="40" ht="26" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Multiple Faculty Positions in Computer Science and Engineering</t>
+          <t>Assistant Professor of Civil Engineering</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University</t>
+          <t>McNeese State University</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Department of Computer Science and Engineering</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="n">
-        <v>4</v>
+          <t>Civil and Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>5</v>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Moderate fit: open faculty search in Computer Science and Engineering without explicit specialization in transportation or mobility systems.</t>
+          <t>Moderate fit: broad Civil Engineering search where transportation is not explicitly prioritized in the snippet.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Computer Science, Computer Engineering, Artificial Intelligence, Data Science</t>
+          <t>Civil Engineering, Engineering Education</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>College Station, TX</t>
+          <t>Lake Charles, LA</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
@@ -4118,22 +4118,22 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>$76,000 per year</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University invites applications for multiple faculty positions in Computer Science and Engineering, requiring a Ph.D. in a relevant discipline. | Research Topics: Computer Science, Computer Engineering, Artificial Intelligence, Data Science</t>
+          <t>Assistant Professor position in Civil and Environmental Engineering at McNeese State University with a salary of $76,000 per year. | Research Topics: Civil Engineering, Engineering Education</t>
         </is>
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>http://engineering.academickeys.com/job/rh7lvag4/CSE--TAMU-Multiple-Faculty-Positions</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179545361&amp;Title=Assistant%20Professor%20of%20Civil%20Engineering</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>AcademicKeys</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4152,79 +4152,79 @@
         </is>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>30.6187</v>
+        <v>30.1751363</v>
       </c>
       <c r="R40" s="2" t="n">
-        <v>-96.3365</v>
+        <v>-93.2112786</v>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>7d5d844d65485b4b</t>
+          <t>bd292fb9f52ac2e9</t>
         </is>
       </c>
     </row>
     <row r="41" ht="26" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Civil Engineering</t>
+          <t>Tenure-Track Faculty Positions in Transportation Engineering</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>McNeese State University</t>
+          <t>National Taiwan University</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Civil and Environmental Engineering</t>
-        </is>
-      </c>
-      <c r="D41" s="7" t="n">
-        <v>5</v>
+          <t>Department of Civil Engineering</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="n">
+        <v>9</v>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Moderate fit: broad Civil Engineering search where transportation is not explicitly prioritized in the snippet.</t>
+          <t>Core match: seeks multiple tenure-track faculty positions specifically in the Transportation track within a Department of Civil Engineering.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Civil Engineering, Engineering Education</t>
+          <t>Transportation Engineering, Mobility Systems, Transit Planning</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Lake Charles, LA</t>
+          <t>Taipei, Taiwan</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>Open until filled</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>$76,000 per year</t>
+          <t>NT$83,720–137,370 monthly</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>Assistant Professor position in Civil and Environmental Engineering at McNeese State University with a salary of $76,000 per year. | Research Topics: Civil Engineering, Engineering Education</t>
+          <t>The Department of Civil Engineering at National Taiwan University invites applications for multiple tenure-track faculty positions in Transportation Engineering. | Research Topics: Transportation Engineering, Mobility Systems, Transit Planning</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179545361&amp;Title=Assistant%20Professor%20of%20Civil%20Engineering</t>
+          <t>https://jobs.chronicle.com/job/38034402/faculty-recruitment-announcement-department-of-civil-engineering-national-taiwan-university/</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>HigherEdJobs</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4243,44 +4243,44 @@
         </is>
       </c>
       <c r="Q41" s="2" t="n">
-        <v>30.1751363</v>
+        <v>25.0375198</v>
       </c>
       <c r="R41" s="2" t="n">
-        <v>-93.2112786</v>
+        <v>121.5636796</v>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>bd292fb9f52ac2e9</t>
+          <t>f056997ace2e1de7</t>
         </is>
       </c>
     </row>
     <row r="42" ht="26" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Tenure-Track Faculty Positions in Transportation Engineering</t>
+          <t>Assistant Professor of Public Policy and Administration</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>National Taiwan University</t>
+          <t>University of Texas at Arlington</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Department of Civil Engineering</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="n">
-        <v>9</v>
+          <t>Department of Public Affairs &amp; Planning</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Core match: seeks multiple tenure-track faculty positions specifically in the Transportation track within a Department of Civil Engineering.</t>
+          <t>Moderate fit: Assistant Professor in Public Affairs &amp; Planning focused on public policy and urban studies, offering potential interdisciplinary overlap despite lacking a specific transportation mandate.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Transportation Engineering, Mobility Systems, Transit Planning</t>
+          <t>Public Policy, Urban Studies, Public Infrastructure, Interdisciplinary Public Administration</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -4290,32 +4290,32 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Taipei, Taiwan</t>
+          <t>Arlington, TX</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>NT$83,720–137,370 monthly</t>
-        </is>
-      </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>The Department of Civil Engineering at National Taiwan University invites applications for multiple tenure-track faculty positions in Transportation Engineering. | Research Topics: Transportation Engineering, Mobility Systems, Transit Planning</t>
+          <t>The University of Texas at Arlington seeks a tenure-track Assistant Professor in Public Policy &amp; Planning to conduct policy research, secure external funding, and teach public administration courses requiring a Ph.D. | Research Topics: Public Policy, Urban Studies, Public Infrastructure, Interdisciplinary Public Administration</t>
         </is>
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38034402/faculty-recruitment-announcement-department-of-civil-engineering-national-taiwan-university/</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-at-excel-campus-activities-4464851831</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -4334,103 +4334,12 @@
         </is>
       </c>
       <c r="Q42" s="2" t="n">
-        <v>25.0375198</v>
+        <v>32.7315155</v>
       </c>
       <c r="R42" s="2" t="n">
-        <v>121.5636796</v>
+        <v>-97.1171533</v>
       </c>
       <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>f056997ace2e1de7</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="26" customHeight="1">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Assistant Professor of Public Policy and Administration</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>University of Texas at Arlington</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Department of Public Affairs &amp; Planning</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>Moderate fit: Assistant Professor in Public Affairs &amp; Planning focused on public policy and urban studies, offering potential interdisciplinary overlap despite lacking a specific transportation mandate.</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>Public Policy, Urban Studies, Public Infrastructure, Interdisciplinary Public Administration</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t>Tenure-Track</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>Arlington, TX</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t>Open until filled</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="K43" s="4" t="inlineStr">
-        <is>
-          <t>The University of Texas at Arlington seeks a tenure-track Assistant Professor in Public Policy &amp; Planning to conduct policy research, secure external funding, and teach public administration courses requiring a Ph.D. | Research Topics: Public Policy, Urban Studies, Public Infrastructure, Interdisciplinary Public Administration</t>
-        </is>
-      </c>
-      <c r="L43" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-at-excel-campus-activities-4464851831</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="P43" s="3" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="n">
-        <v>32.7315155</v>
-      </c>
-      <c r="R43" s="2" t="n">
-        <v>-97.1171533</v>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
         <is>
           <t>15704bb25858281c</t>
         </is>
@@ -4479,7 +4388,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId42"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -493,12 +493,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S42"/>
+  <dimension ref="A1:S43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="80" customWidth="1" min="3" max="3"/>
+    <col width="95" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="32" customWidth="1" min="5" max="5"/>
     <col width="151" customWidth="1" min="6" max="6"/>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Department of Public Policy / La Follette School of Public Affairs</t>
+          <t>La Follette School of Public Affairs, College of Letters &amp; Science</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Low fit: public policy position focused on market-based solutions rather than core transportation engineering or mobility systems.</t>
+          <t>Low fit: Assistant Professor position in public policy focusing on market-based economic solutions and public administration rather than transportation engineering.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Public Policy, Market-Based Solutions, Societal Challenges</t>
+          <t>Public Policy, Market-Based Institutions, Incentive-Compatible Policy Design</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1115,32 +1115,32 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Competitive Salary</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>An assistant professor position in public policy focusing on market-based solutions to societal challenges requiring a Ph.D. or equivalent. | Research Topics: Public Policy, Market-Based Solutions, Societal Challenges</t>
+          <t>The La Follette School of Public Affairs seeks an Assistant Professor to conduct research on market-based institutions and incentive-compatible policy design, requiring an advanced degree in a relevant social science discipline. | Research Topics: Public Policy, Market-Based Institutions, Incentive-Compatible Policy Design</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38008254/assistant-professor-of-public-policy-market-based-solutions-to-societal-challenges-/</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-of-public-policy-market-based-solutions-to-societal-challenges-at-uw-madison-college-of-letters-science-4435310692</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>51857534b7308d30</t>
+          <t>886b76b05d362fdc</t>
         </is>
       </c>
     </row>
@@ -1618,7 +1618,7 @@
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Operations Management</t>
+          <t>Assistant Professor of Information and Decision Sciences (Supply Chain &amp; Operations Management)</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Information and Decision Sciences (IDS) Department</t>
+          <t>Information and Decision Sciences (IDS)</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
@@ -1636,12 +1636,12 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Low fit: position is in Supply Chain and Operations Management within a business/IDS department rather than transportation engineering or urban planning.</t>
+          <t>Low fit: position is in Supply Chain and Operations Management within a business school rather than transportation engineering or urban planning.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Operations Management, Supply Chain Management</t>
+          <t>Supply Chain Management, Operations Management, Decision Sciences</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1656,37 +1656,37 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>DOE</t>
-        </is>
-      </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>The Information and Decision Sciences department invites applications for a tenure-track assistant professor position in Operations Management starting in the 2027-2028 academic year. | Research Topics: Operations Management, Supply Chain Management</t>
+          <t>Assistant Professor role focusing on supply chain and operations management within a business school environment. | Research Topics: Supply Chain Management, Operations Management, Decision Sciences</t>
         </is>
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38035040/assistant-professor-ids-supply-chain-and-operations-management-/</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179552436&amp;Title=Assistant%20Professor%20%2D%20IDS%20%28Supply%20Chain%20%26%20Operations%20Management%29</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
@@ -1702,14 +1702,14 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>c1e8cde424bc7afa</t>
+          <t>77e0632bd4e74eae</t>
         </is>
       </c>
     </row>
     <row r="14" ht="26" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Tenure-track Assistant Professor of Industrial and Systems Engineering</t>
+          <t>Assistant Professor of Industrial and Systems Engineering</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1722,17 +1722,17 @@
           <t>Department of Industrial and Systems Engineering</t>
         </is>
       </c>
-      <c r="D14" s="7" t="n">
-        <v>6</v>
+      <c r="D14" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Moderate fit: Assistant Professor position in Industrial and Systems Engineering which can align with mobility systems, though the snippet lacks specific details.</t>
+          <t>Moderate fit: general Industrial and Systems Engineering tenure-track faculty position without an explicit focus on transportation systems specified in the snippet.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Industrial Engineering, Systems Engineering, Mobility Systems</t>
+          <t>Industrial and Systems Engineering, Manufacturing Engineering, Systems Optimization, Operations Research</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1752,32 +1752,32 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Competitive Salary</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>The University of Tennessee, Knoxville is seeking three tenure-track Assistant Professors in the Department of Industrial and Systems Engineering. | Research Topics: Industrial Engineering, Systems Engineering, Mobility Systems</t>
+          <t>Tenure-track Assistant Professor opening in Industrial and Systems Engineering requiring a Ph.D. in industrial engineering, systems engineering, or a closely related discipline. | Research Topics: Industrial and Systems Engineering, Manufacturing Engineering, Systems Optimization, Operations Research</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38032334/tenure-track-assistant-professor-of-industrial-and-systems-engineering-fall-2027-1-3-/</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179545449&amp;Title=Tenure%2DTrack%20Assistant%20Professor%20of%20Industrial%20and%20Systems%20Engineering%2C%20Fall%202027%20%281%2F3%29</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
@@ -1793,14 +1793,14 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>a40790e93b28a33d</t>
+          <t>ecd34777430b7c8d</t>
         </is>
       </c>
     </row>
     <row r="15" ht="26" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Civil, Construction and Environmental Engineering</t>
+          <t>Assistant Professor in Transportation Engineering</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1813,17 +1813,17 @@
           <t>Civil, Construction and Environmental Engineering</t>
         </is>
       </c>
-      <c r="D15" s="7" t="n">
-        <v>6</v>
+      <c r="D15" s="6" t="n">
+        <v>10</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Broad Civil, Construction and Environmental Engineering faculty search where transportation is a potential sub-discipline within the department.</t>
+          <t>Core match: seeks an Assistant Professor specifically in Transportation Engineering within Civil, Construction and Environmental Engineering.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Civil Engineering, Construction Engineering, Environmental Engineering, Transportation Engineering</t>
+          <t>Transportation Engineering, Civil Engineering, Transportation Systems</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1848,12 +1848,12 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>Assistant Professor position in the Department of Civil, Construction and Environmental Engineering at the University of Alabama. | Research Topics: Civil Engineering, Construction Engineering, Environmental Engineering, Transportation Engineering</t>
+          <t>The University of Alabama seeks a tenure-track Assistant Professor in Transportation Engineering within the Department of Civil, Construction and Environmental Engineering. | Research Topics: Transportation Engineering, Civil Engineering, Transportation Systems</t>
         </is>
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>https://engineering.academickeys.com/job/02ixzgls/Civil-Construction-and-Environmental-Engineering--Assistant-Professor</t>
+          <t>https://engineering.academickeys.com/job/s9z6epb3/Civil-Construction-and-Environmental-Engineering--Transportation-Engineering--Assistant-Professor</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -1863,12 +1863,12 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>f80ad2336a210f82</t>
+          <t>daabd65ea8fe188a</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
@@ -3324,7 +3324,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
@@ -3620,7 +3620,7 @@
     <row r="35" ht="26" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Assistant or Associate Professor in Supply Chain Management</t>
+          <t>Assistant Professor of Supply Chain Management</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>J.B. Hunt Transport Department of Supply Chain Management</t>
+          <t>J.B. Hunt Transport Department of Supply Chain Management, Sam M. Walton College of Business</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Low fit: this is a faculty position in Supply Chain Management within a Business School rather than Transportation Engineering.</t>
+          <t>Low fit: Business school position focused on supply chain management and contested logistics rather than transportation engineering or urban planning.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Management, Logistics, Operations Research</t>
+          <t>Supply Chain Management, Contested Logistics, Defense Logistics, National Security Supply Chains</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -3668,12 +3668,12 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>This is a tenure-track Assistant or Associate Professor position in Supply Chain Management requiring a strong research record in leading peer-reviewed journals. | Research Topics: Supply Chain Management, Logistics, Operations Research</t>
+          <t>The Sam M. Walton College of Business at the University of Arkansas seeks two tenure-track Assistant Professors in Supply Chain Management specializing in contested logistics and defense-relevant supply chain research. | Research Topics: Supply Chain Management, Contested Logistics, Defense Logistics, National Security Supply Chains</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-or-associate-professor-open-rank-at-university-of-arkansas-%C2%AD-sam-m-walton-college-of-business-4460111187</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-two-open-positions-at-university-of-arkansas-%C2%AD-sam-m-walton-college-of-business-4460109211</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
@@ -3683,12 +3683,12 @@
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
@@ -3697,14 +3697,14 @@
         </is>
       </c>
       <c r="Q35" s="2" t="n">
-        <v>36.0625843</v>
+        <v>36.0970389</v>
       </c>
       <c r="R35" s="2" t="n">
-        <v>-94.1574328</v>
+        <v>-94.1703322</v>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>c16a694d5f7f68d4</t>
+          <t>8b974c86c7dfa1c1</t>
         </is>
       </c>
     </row>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
@@ -4342,6 +4342,97 @@
       <c r="S42" s="2" t="inlineStr">
         <is>
           <t>15704bb25858281c</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="26" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Professor</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>The University of Texas at Arlington</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Civil and Environmental Engineering (Unspecified)</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>Moderate fit: The scraped text snippet only provides a generic Assistant Professor title and location without department or research details, requiring assumption of a potential broad Civil Engineering or Transportation opening.</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Transportation Engineering, Civil Engineering, Urban Planning</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>Tenure-Track</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Arlington, TX</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="K43" s="4" t="inlineStr">
+        <is>
+          <t>This is a faculty position at The University of Texas at Arlington, though specific departmental focus and qualifications require further details from the full posting. | Research Topics: Transportation Engineering, Civil Engineering, Urban Planning</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-at-the-university-of-texas-at-arlington-4397332037</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="n">
+        <v>32.7284713</v>
+      </c>
+      <c r="R43" s="2" t="n">
+        <v>-97.11202129999999</v>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>8f5d66dcdfbbc7fd</t>
         </is>
       </c>
     </row>
@@ -4388,6 +4479,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId42"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S43"/>
+  <dimension ref="A1:S46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
@@ -1082,20 +1082,20 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>La Follette School of Public Affairs, College of Letters &amp; Science</t>
+          <t>La Follette School of Public Affairs, College of Letters and Science</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Low fit: Assistant Professor position in public policy focusing on market-based economic solutions and public administration rather than transportation engineering.</t>
+          <t>Moderate borderline fit: the position is in public policy and economics rather than transportation engineering, though it lists transportation and infrastructure finance as a potential application area.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Public Policy, Market-Based Institutions, Incentive-Compatible Policy Design</t>
+          <t>Market-based institutions and policy design, Transportation and infrastructure finance, Applied microeconomics and regulatory policy</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1110,37 +1110,37 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Open until filled</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Competitive / Negotiable</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>The La Follette School of Public Affairs seeks an Assistant Professor to conduct research on market-based institutions and incentive-compatible policy design, requiring an advanced degree in a relevant social science discipline. | Research Topics: Public Policy, Market-Based Institutions, Incentive-Compatible Policy Design</t>
+          <t>The La Follette School of Public Affairs at UW-Madison seeks an assistant professor specializing in market-based institutions and policy design with a Ph.D. in Public Policy, Economics, Political Science, Law, or a related field. | Research Topics: Market-based institutions and policy design, Transportation and infrastructure finance, Applied microeconomics and regulatory policy</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-of-public-policy-market-based-solutions-to-societal-challenges-at-uw-madison-college-of-letters-science-4435310692</t>
+          <t>https://jobs.chronicle.com/job/38008254/assistant-professor-of-public-policy-market-based-solutions-to-societal-challenges-/</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>886b76b05d362fdc</t>
+          <t>51857534b7308d30</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
@@ -1800,7 +1800,7 @@
     <row r="15" ht="26" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor in Transportation Engineering</t>
+          <t>Assistant Professor of Civil, Construction and Environmental Engineering</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1813,17 +1813,17 @@
           <t>Civil, Construction and Environmental Engineering</t>
         </is>
       </c>
-      <c r="D15" s="6" t="n">
-        <v>10</v>
+      <c r="D15" s="7" t="n">
+        <v>5</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Core match: seeks an Assistant Professor specifically in Transportation Engineering within Civil, Construction and Environmental Engineering.</t>
+          <t>Moderate fit: Broad Civil, Construction and Environmental Engineering faculty search where transportation is only one of multiple potential sub-disciplines.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Transportation Engineering, Civil Engineering, Transportation Systems</t>
+          <t>Civil Engineering, Construction Engineering, Environmental Engineering, Transportation Engineering</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1848,12 +1848,12 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>The University of Alabama seeks a tenure-track Assistant Professor in Transportation Engineering within the Department of Civil, Construction and Environmental Engineering. | Research Topics: Transportation Engineering, Civil Engineering, Transportation Systems</t>
+          <t>Assistant Professor position in Civil, Construction and Environmental Engineering seeking qualified faculty candidates with a relevant doctoral degree. | Research Topics: Civil Engineering, Construction Engineering, Environmental Engineering, Transportation Engineering</t>
         </is>
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>https://engineering.academickeys.com/job/s9z6epb3/Civil-Construction-and-Environmental-Engineering--Transportation-Engineering--Assistant-Professor</t>
+          <t>https://engineering.academickeys.com/job/02ixzgls/Civil-Construction-and-Environmental-Engineering--Assistant-Professor</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -1863,12 +1863,12 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>daabd65ea8fe188a</t>
+          <t>f80ad2336a210f82</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
@@ -3324,7 +3324,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
@@ -3620,7 +3620,7 @@
     <row r="35" ht="26" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Supply Chain Management</t>
+          <t>Assistant or Associate Professor of Supply Chain Management</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Low fit: Business school position focused on supply chain management and contested logistics rather than transportation engineering or urban planning.</t>
+          <t>Low fit: position is in Supply Chain Management within a Business School rather than Transportation Engineering or Urban Planning.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Management, Contested Logistics, Defense Logistics, National Security Supply Chains</t>
+          <t>Supply Chain Management, Logistics, Operations</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -3668,12 +3668,12 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>The Sam M. Walton College of Business at the University of Arkansas seeks two tenure-track Assistant Professors in Supply Chain Management specializing in contested logistics and defense-relevant supply chain research. | Research Topics: Supply Chain Management, Contested Logistics, Defense Logistics, National Security Supply Chains</t>
+          <t>The Sam M. Walton College of Business seeks a tenure-track Assistant or Associate Professor in Supply Chain Management to conduct high-quality research and teach in the department. | Research Topics: Supply Chain Management, Logistics, Operations</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-two-open-positions-at-university-of-arkansas-%C2%AD-sam-m-walton-college-of-business-4460109211</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-or-associate-professor-open-rank-at-university-of-arkansas-%C2%AD-sam-m-walton-college-of-business-4460111187</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
@@ -3683,12 +3683,12 @@
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>8b974c86c7dfa1c1</t>
+          <t>c16a694d5f7f68d4</t>
         </is>
       </c>
     </row>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
@@ -4257,7 +4257,7 @@
     <row r="42" ht="26" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Public Policy and Administration</t>
+          <t>Assistant Professor of Public Administration and Policy</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -4267,20 +4267,20 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Department of Public Affairs &amp; Planning</t>
+          <t>Department of Public Administration and Policy</t>
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Moderate fit: Assistant Professor in Public Affairs &amp; Planning focused on public policy and urban studies, offering potential interdisciplinary overlap despite lacking a specific transportation mandate.</t>
+          <t>Low fit: Public administration and policy position, lacking a focus on transportation engineering or mobility systems.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Public Policy, Urban Studies, Public Infrastructure, Interdisciplinary Public Administration</t>
+          <t>Public Administration, Public Policy, Governance</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -4305,27 +4305,27 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>The University of Texas at Arlington seeks a tenure-track Assistant Professor in Public Policy &amp; Planning to conduct policy research, secure external funding, and teach public administration courses requiring a Ph.D. | Research Topics: Public Policy, Urban Studies, Public Infrastructure, Interdisciplinary Public Administration</t>
+          <t>Assistant Professor position in Public Administration and Policy requiring a relevant terminal degree. | Research Topics: Public Administration, Public Policy, Governance</t>
         </is>
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-at-excel-campus-activities-4464851831</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179553472&amp;Title=Assistant%20Professor</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>15704bb25858281c</t>
+          <t>85da23cbf7841060</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
@@ -4433,6 +4433,279 @@
       <c r="S43" s="2" t="inlineStr">
         <is>
           <t>8f5d66dcdfbbc7fd</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="26" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Montana State University</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Mechanical and Industrial Engineering</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>Low fit: position is in Mechanical Engineering rather than Transportation Engineering or related target departments.</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Mechanical Engineering, Thermal/Fluid Sciences or Solid Mechanics</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>Tenure-Track</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Bozeman, MT</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="K44" s="4" t="inlineStr">
+        <is>
+          <t>Assistant Professor role in Mechanical Engineering requiring a Ph.D. in mechanical engineering or a closely related field. | Research Topics: Mechanical Engineering, Thermal/Fluid Sciences or Solid Mechanics</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="inlineStr">
+        <is>
+          <t>http://engineering.academickeys.com/job/ruoe4wlz/Assistant-Professor-of-Mechanical-Engineering</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>AcademicKeys</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="n">
+        <v>45.6639222</v>
+      </c>
+      <c r="R44" s="2" t="n">
+        <v>-111.079277</v>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>ec871122feab7986</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="26" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Data Analytics</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Ohio Wesleyan University</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>Moderate fit: general data analytics faculty position at a liberal arts college with no explicit focus on transportation engineering or mobility.</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Data Analytics, Data Science, Quantitative Methods</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>Tenure-Track</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Delaware, OH</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="K45" s="4" t="inlineStr">
+        <is>
+          <t>Assistant professor position in data analytics focusing on data science teaching and research, requiring a relevant graduate degree. | Research Topics: Data Analytics, Data Science, Quantitative Methods</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179549847&amp;Title=Assistant%20Professor%20of%20Data%20Analytics</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>HigherEdJobs</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="n">
+        <v>40.292858</v>
+      </c>
+      <c r="R45" s="2" t="n">
+        <v>-83.0642763</v>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>99e733f7138cdcde</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="26" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Professor</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Georgia Institute of Technology</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>Low fit: the job description snippet only lists the general title and institution without department or subfield details, requiring careful manual verification.</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Transportation Engineering, Civil Engineering, Mobility Systems</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>Tenure-Track</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="K46" s="4" t="inlineStr">
+        <is>
+          <t>The snippet lacks specific department or research details for this faculty position at Georgia Institute of Technology. | Research Topics: Transportation Engineering, Civil Engineering, Mobility Systems</t>
+        </is>
+      </c>
+      <c r="L46" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-at-georgia-institute-of-technology-4467296351</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="n">
+        <v>33.7756</v>
+      </c>
+      <c r="R46" s="2" t="n">
+        <v>-84.3963</v>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>1b7278bf60327029</t>
         </is>
       </c>
     </row>
@@ -4480,6 +4753,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId45"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S46"/>
+  <dimension ref="A1:S47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
@@ -1800,7 +1800,7 @@
     <row r="15" ht="26" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Civil, Construction and Environmental Engineering</t>
+          <t>Assistant Professor of Transportation Engineering</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1813,17 +1813,17 @@
           <t>Civil, Construction and Environmental Engineering</t>
         </is>
       </c>
-      <c r="D15" s="7" t="n">
-        <v>5</v>
+      <c r="D15" s="6" t="n">
+        <v>10</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Moderate fit: Broad Civil, Construction and Environmental Engineering faculty search where transportation is only one of multiple potential sub-disciplines.</t>
+          <t>Core match: direct faculty position in Transportation Engineering within a Civil, Construction, and Environmental Engineering department.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Civil Engineering, Construction Engineering, Environmental Engineering, Transportation Engineering</t>
+          <t>Transportation Engineering, Traffic Operations, Transportation Systems</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1848,12 +1848,12 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>Assistant Professor position in Civil, Construction and Environmental Engineering seeking qualified faculty candidates with a relevant doctoral degree. | Research Topics: Civil Engineering, Construction Engineering, Environmental Engineering, Transportation Engineering</t>
+          <t>Assistant Professor position in transportation engineering focusing on research, teaching, and service within the Department of Civil, Construction and Environmental Engineering. | Research Topics: Transportation Engineering, Traffic Operations, Transportation Systems</t>
         </is>
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>https://engineering.academickeys.com/job/02ixzgls/Civil-Construction-and-Environmental-Engineering--Assistant-Professor</t>
+          <t>https://engineering.academickeys.com/job/s9z6epb3/Civil-Construction-and-Environmental-Engineering--Transportation-Engineering--Assistant-Professor</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -1863,12 +1863,12 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>f80ad2336a210f82</t>
+          <t>daabd65ea8fe188a</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
@@ -3324,7 +3324,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
@@ -3620,7 +3620,7 @@
     <row r="35" ht="26" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Assistant or Associate Professor of Supply Chain Management</t>
+          <t>Assistant Professor of Supply Chain Management</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Low fit: position is in Supply Chain Management within a Business School rather than Transportation Engineering or Urban Planning.</t>
+          <t>Low fit: position is in a Supply Chain Management department focusing on contested logistics and defense supply chains, outside the candidate's core transportation engineering field.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Management, Logistics, Operations</t>
+          <t>Supply Chain Management, Contested Logistics, Defense Logistics, National Security Supply Chains</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -3668,12 +3668,12 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>The Sam M. Walton College of Business seeks a tenure-track Assistant or Associate Professor in Supply Chain Management to conduct high-quality research and teach in the department. | Research Topics: Supply Chain Management, Logistics, Operations</t>
+          <t>The Sam M. Walton College of Business at the University of Arkansas invites applications for two tenure-track Assistant Professor positions in Supply Chain Management specializing in contested logistics and defense-relevant supply chain research. | Research Topics: Supply Chain Management, Contested Logistics, Defense Logistics, National Security Supply Chains</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-or-associate-professor-open-rank-at-university-of-arkansas-%C2%AD-sam-m-walton-college-of-business-4460111187</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-two-open-positions-at-university-of-arkansas-%C2%AD-sam-m-walton-college-of-business-4460109211</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
@@ -3683,12 +3683,12 @@
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>c16a694d5f7f68d4</t>
+          <t>8b974c86c7dfa1c1</t>
         </is>
       </c>
     </row>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
@@ -4439,30 +4439,30 @@
     <row r="44" ht="26" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Mechanical Engineering</t>
+          <t>Assistant Professor of Data Analytics</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Montana State University</t>
+          <t>Ohio Wesleyan University</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Mechanical and Industrial Engineering</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="n">
-        <v>3</v>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>5</v>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Low fit: position is in Mechanical Engineering rather than Transportation Engineering or related target departments.</t>
+          <t>Moderate fit: general data analytics faculty position at a liberal arts college with no explicit focus on transportation engineering or mobility.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Mechanical Engineering, Thermal/Fluid Sciences or Solid Mechanics</t>
+          <t>Data Analytics, Data Science, Quantitative Methods</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Bozeman, MT</t>
+          <t>Delaware, OH</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
@@ -4487,17 +4487,17 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>Assistant Professor role in Mechanical Engineering requiring a Ph.D. in mechanical engineering or a closely related field. | Research Topics: Mechanical Engineering, Thermal/Fluid Sciences or Solid Mechanics</t>
+          <t>Assistant professor position in data analytics focusing on data science teaching and research, requiring a relevant graduate degree. | Research Topics: Data Analytics, Data Science, Quantitative Methods</t>
         </is>
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>http://engineering.academickeys.com/job/ruoe4wlz/Assistant-Professor-of-Mechanical-Engineering</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179549847&amp;Title=Assistant%20Professor%20of%20Data%20Analytics</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>AcademicKeys</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -4516,31 +4516,31 @@
         </is>
       </c>
       <c r="Q44" s="2" t="n">
-        <v>45.6639222</v>
+        <v>40.292858</v>
       </c>
       <c r="R44" s="2" t="n">
-        <v>-111.079277</v>
+        <v>-83.0642763</v>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>ec871122feab7986</t>
+          <t>99e733f7138cdcde</t>
         </is>
       </c>
     </row>
     <row r="45" ht="26" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Data Analytics</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Ohio Wesleyan University</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>Unspecified</t>
         </is>
       </c>
       <c r="D45" s="7" t="n">
@@ -4548,12 +4548,12 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Moderate fit: general data analytics faculty position at a liberal arts college with no explicit focus on transportation engineering or mobility.</t>
+          <t>Low fit: the job description snippet only lists the general title and institution without department or subfield details, requiring careful manual verification.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Data Analytics, Data Science, Quantitative Methods</t>
+          <t>Transportation Engineering, Civil Engineering, Mobility Systems</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Delaware, OH</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
@@ -4578,17 +4578,17 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>Assistant professor position in data analytics focusing on data science teaching and research, requiring a relevant graduate degree. | Research Topics: Data Analytics, Data Science, Quantitative Methods</t>
+          <t>The snippet lacks specific department or research details for this faculty position at Georgia Institute of Technology. | Research Topics: Transportation Engineering, Civil Engineering, Mobility Systems</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179549847&amp;Title=Assistant%20Professor%20of%20Data%20Analytics</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-at-georgia-institute-of-technology-4467296351</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>HigherEdJobs</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -4607,44 +4607,44 @@
         </is>
       </c>
       <c r="Q45" s="2" t="n">
-        <v>40.292858</v>
+        <v>33.7756</v>
       </c>
       <c r="R45" s="2" t="n">
-        <v>-83.0642763</v>
+        <v>-84.3963</v>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>99e733f7138cdcde</t>
+          <t>1b7278bf60327029</t>
         </is>
       </c>
     </row>
     <row r="46" ht="26" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Assistant Professor/Associate Professor of Mechanical Engineering</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>Wayne State University</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Unspecified</t>
-        </is>
-      </c>
-      <c r="D46" s="7" t="n">
-        <v>5</v>
+          <t>Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>Low fit: the job description snippet only lists the general title and institution without department or subfield details, requiring careful manual verification.</t>
+          <t>Low fit: position is in Mechanical Engineering rather than Transportation Engineering or Civil and Environmental Engineering.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Transportation Engineering, Civil Engineering, Mobility Systems</t>
+          <t>Mechanical Engineering</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Detroit, MI</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
@@ -4669,43 +4669,134 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>The snippet lacks specific department or research details for this faculty position at Georgia Institute of Technology. | Research Topics: Transportation Engineering, Civil Engineering, Mobility Systems</t>
+          <t>Wayne State University seeks an Assistant or Associate Professor in Mechanical Engineering requiring a Ph.D. in mechanical engineering or a closely related field. | Research Topics: Mechanical Engineering</t>
         </is>
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-at-georgia-institute-of-technology-4467296351</t>
+          <t>http://engineering.academickeys.com/job/ag72sclk/Assistant-ProfessorAssociate-Professor</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
+          <t>AcademicKeys</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="n">
+        <v>42.3571895</v>
+      </c>
+      <c r="R46" s="2" t="n">
+        <v>-83.07094360000001</v>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>dc3c583beddaae82</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="26" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Assistant/Associate Professor of Public Administration &amp; MPA Coordinator</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>University of New Orleans (UNO Transportation Institute)</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Department of Public Administration</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>Low fit: position focuses on public administration and management rather than transportation engineering or planning.</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Public Administration, Public Policy, Program Management</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>Tenure-Track</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>New Orleans, LA</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="K47" s="4" t="inlineStr">
+        <is>
+          <t>Assistant or Associate Professor position in Public Administration serving as Master of Public Administration Coordinator. | Research Topics: Public Administration, Public Policy, Program Management</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/assistant-associate-professor-public-administration-master-of-public-administration-coordinator-at-uno-transportation-institute-4466545068</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="P46" s="3" t="inlineStr">
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="P47" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="Q46" s="2" t="n">
-        <v>33.7756</v>
-      </c>
-      <c r="R46" s="2" t="n">
-        <v>-84.3963</v>
-      </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t>1b7278bf60327029</t>
+      <c r="Q47" s="2" t="n">
+        <v>29.9561422</v>
+      </c>
+      <c r="R47" s="2" t="n">
+        <v>-90.0733934</v>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>0bd357a7efab4a73</t>
         </is>
       </c>
     </row>
@@ -4756,6 +4847,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId46"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S47"/>
+  <dimension ref="A1:S49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
@@ -1072,7 +1072,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Public Policy (Market-Based Solutions to Societal Challenges)</t>
+          <t>Assistant Professor of Public Policy</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -1082,20 +1082,20 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>La Follette School of Public Affairs, College of Letters and Science</t>
+          <t>La Follette School of Public Affairs, College of Letters &amp; Science</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Moderate borderline fit: the position is in public policy and economics rather than transportation engineering, though it lists transportation and infrastructure finance as a potential application area.</t>
+          <t>Low fit: Public policy faculty position focused on market-based solutions and economic regulation, with only incidental mention of transportation infrastructure finance.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Market-based institutions and policy design, Transportation and infrastructure finance, Applied microeconomics and regulatory policy</t>
+          <t>Market-Based Solutions, Public Policy Analysis, Regulatory Policy, Transportation and Infrastructure Finance</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1110,37 +1110,37 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>Open until filled</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Competitive / Negotiable</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>The La Follette School of Public Affairs at UW-Madison seeks an assistant professor specializing in market-based institutions and policy design with a Ph.D. in Public Policy, Economics, Political Science, Law, or a related field. | Research Topics: Market-based institutions and policy design, Transportation and infrastructure finance, Applied microeconomics and regulatory policy</t>
+          <t>The La Follette School of Public Affairs seeks a tenure-track Assistant Professor of Public Policy specializing in market-based institutions, economic policy, and incentive-compatible regulatory design. | Research Topics: Market-Based Solutions, Public Policy Analysis, Regulatory Policy, Transportation and Infrastructure Finance</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38008254/assistant-professor-of-public-policy-market-based-solutions-to-societal-challenges-/</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-of-public-policy-market-based-solutions-to-societal-challenges-at-uw-madison-college-of-letters-science-4435310692</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>51857534b7308d30</t>
+          <t>886b76b05d362fdc</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
@@ -1800,7 +1800,7 @@
     <row r="15" ht="26" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Transportation Engineering</t>
+          <t>Assistant Professor of Civil, Construction and Environmental Engineering</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1810,20 +1810,20 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Civil, Construction and Environmental Engineering</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>10</v>
+          <t>Department of Civil, Construction and Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>5</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Core match: direct faculty position in Transportation Engineering within a Civil, Construction, and Environmental Engineering department.</t>
+          <t>Moderate fit: Broad Civil, Construction and Environmental Engineering department search where transportation may be considered, but the job text lacks specific details.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Transportation Engineering, Traffic Operations, Transportation Systems</t>
+          <t>Civil Engineering, Construction Engineering, Environmental Engineering, Transportation Engineering</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1848,12 +1848,12 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>Assistant Professor position in transportation engineering focusing on research, teaching, and service within the Department of Civil, Construction and Environmental Engineering. | Research Topics: Transportation Engineering, Traffic Operations, Transportation Systems</t>
+          <t>Assistant Professor position in Civil, Construction and Environmental Engineering requiring a Ph.D. in a relevant discipline. | Research Topics: Civil Engineering, Construction Engineering, Environmental Engineering, Transportation Engineering</t>
         </is>
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>https://engineering.academickeys.com/job/s9z6epb3/Civil-Construction-and-Environmental-Engineering--Transportation-Engineering--Assistant-Professor</t>
+          <t>https://engineering.academickeys.com/job/02ixzgls/Civil-Construction-and-Environmental-Engineering--Assistant-Professor</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -1863,12 +1863,12 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>daabd65ea8fe188a</t>
+          <t>f80ad2336a210f82</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
@@ -3324,7 +3324,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
@@ -3620,7 +3620,7 @@
     <row r="35" ht="26" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Supply Chain Management</t>
+          <t>Assistant or Associate Professor of Supply Chain Management</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Low fit: position is in a Supply Chain Management department focusing on contested logistics and defense supply chains, outside the candidate's core transportation engineering field.</t>
+          <t>Low fit: position is in Supply Chain Management within a business school, which falls outside the candidate's core transportation engineering and planning profile.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Management, Contested Logistics, Defense Logistics, National Security Supply Chains</t>
+          <t>Supply Chain Management, Logistics, Operations</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -3668,12 +3668,12 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>The Sam M. Walton College of Business at the University of Arkansas invites applications for two tenure-track Assistant Professor positions in Supply Chain Management specializing in contested logistics and defense-relevant supply chain research. | Research Topics: Supply Chain Management, Contested Logistics, Defense Logistics, National Security Supply Chains</t>
+          <t>Seeking an Assistant or Associate Professor in Supply Chain Management to conduct research and publish in leading peer-reviewed journals, requiring a Ph.D. in a relevant discipline. | Research Topics: Supply Chain Management, Logistics, Operations</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-two-open-positions-at-university-of-arkansas-%C2%AD-sam-m-walton-college-of-business-4460109211</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-or-associate-professor-open-rank-at-university-of-arkansas-%C2%AD-sam-m-walton-college-of-business-4460111187</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
@@ -3683,12 +3683,12 @@
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>8b974c86c7dfa1c1</t>
+          <t>c16a694d5f7f68d4</t>
         </is>
       </c>
     </row>
@@ -4052,7 +4052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
@@ -4257,7 +4257,7 @@
     <row r="42" ht="26" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Public Administration and Policy</t>
+          <t>Assistant Professor of Public Policy</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -4267,20 +4267,20 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Department of Public Administration and Policy</t>
+          <t>Department of Public Affairs &amp; Planning</t>
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Low fit: Public administration and policy position, lacking a focus on transportation engineering or mobility systems.</t>
+          <t>Moderate-to-low fit: position is in public policy and planning rather than transportation engineering and planning, despite potential overlaps in urban infrastructure.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Public Administration, Public Policy, Governance</t>
+          <t>Public Policy, Urban Studies, Public Infrastructure, Energy &amp; Environment</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -4305,27 +4305,27 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>Assistant Professor position in Public Administration and Policy requiring a relevant terminal degree. | Research Topics: Public Administration, Public Policy, Governance</t>
+          <t>The Department of Public Affairs and Planning seeks a full-time tenure-track Assistant Professor specializing in public policy or related areas with a Ph.D. required by appointment. | Research Topics: Public Policy, Urban Studies, Public Infrastructure, Energy &amp; Environment</t>
         </is>
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179553472&amp;Title=Assistant%20Professor</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-at-excel-campus-activities-4464851831</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>HigherEdJobs</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>85da23cbf7841060</t>
+          <t>15704bb25858281c</t>
         </is>
       </c>
     </row>
@@ -4797,6 +4797,188 @@
       <c r="S47" s="2" t="inlineStr">
         <is>
           <t>0bd357a7efab4a73</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="26" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Tenure-track Assistant Professor – AI for Automotive and Mobility Systems</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>The Ohio State University</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Department of Mechanical and Aerospace Engineering</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>Moderate fit: Assistant Professor position focused on AI for mobility systems, but housed in Mechanical and Aerospace Engineering rather than Civil and Environmental Engineering.</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence, Automotive Systems, Mobility Systems, Connected and Automated Vehicles</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>Tenure-Track</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Columbus, OH</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="K48" s="4" t="inlineStr">
+        <is>
+          <t>The Ohio State University seeks a tenure-track Assistant Professor in Mechanical and Aerospace Engineering specializing in AI applications for automotive and mobility systems, requiring a Ph.D. in a relevant engineering discipline. | Research Topics: Artificial Intelligence, Automotive Systems, Mobility Systems, Connected and Automated Vehicles</t>
+        </is>
+      </c>
+      <c r="L48" s="5" t="inlineStr">
+        <is>
+          <t>https://engineering.academickeys.com/job/vd0ur9k4/Tenuretrack-Assistant-Professor--AI-for-Automotive-and-Mobility-Systems</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>AcademicKeys</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="P48" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="n">
+        <v>40.0067</v>
+      </c>
+      <c r="R48" s="2" t="n">
+        <v>-83.0305</v>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>dd476bd66d0aeb1e</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="26" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Professional Practice Assistant Professor - Air Traffic Control</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Utah State University</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Department of Civil and Environmental Engineering or related aviation/transportation program</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>Moderate fit: Faculty position in professional practice focusing on air traffic control, which is related to aviation transportation but lacks direct alignment with the candidate's core specialties in surface transit, travel behavior, and discrete choice modeling.</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Air Traffic Control, Aviation Transportation, Transportation Operations</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>Non-Tenure Track</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>Logan, UT</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="K49" s="4" t="inlineStr">
+        <is>
+          <t>This role seeks a professional practice faculty member to teach and lead instruction in air traffic control operations. | Research Topics: Air Traffic Control, Aviation Transportation, Transportation Operations</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/professional-practice-assistant-professor-air-traffic-control-at-utah-state-university-4462897860</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="P49" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="n">
+        <v>41.7526959</v>
+      </c>
+      <c r="R49" s="2" t="n">
+        <v>-111.808733</v>
+      </c>
+      <c r="S49" s="2" t="inlineStr">
+        <is>
+          <t>02b944bc9d0177ba</t>
         </is>
       </c>
     </row>
@@ -4848,6 +5030,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId48"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S49"/>
+  <dimension ref="A1:S50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -503,7 +503,7 @@
     <col width="32" customWidth="1" min="5" max="5"/>
     <col width="151" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
     <col width="49" customWidth="1" min="9" max="9"/>
     <col width="96" customWidth="1" min="10" max="10"/>
     <col width="42" customWidth="1" min="11" max="11"/>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>La Follette School of Public Affairs, College of Letters &amp; Science</t>
+          <t>La Follette School of Public Affairs</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Low fit: Public policy faculty position focused on market-based solutions and economic regulation, with only incidental mention of transportation infrastructure finance.</t>
+          <t>Low fit: Public policy faculty position focused on market-based solutions and economic regulation, whereas candidate's profile is in transportation engineering and planning.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Market-Based Solutions, Public Policy Analysis, Regulatory Policy, Transportation and Infrastructure Finance</t>
+          <t>Market-based institutions, Public policy analysis, Regulatory policy and incentive-compatible design</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1110,37 +1110,37 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Open until filled</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Competitive Salary</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>The La Follette School of Public Affairs seeks a tenure-track Assistant Professor of Public Policy specializing in market-based institutions, economic policy, and incentive-compatible regulatory design. | Research Topics: Market-Based Solutions, Public Policy Analysis, Regulatory Policy, Transportation and Infrastructure Finance</t>
+          <t>Assistant professor role in public policy requiring a Ph.D. in Public Policy, Economics, Political Science, Law, or a related field to research market-based solutions and institutional design. | Research Topics: Market-based institutions, Public policy analysis, Regulatory policy and incentive-compatible design</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-of-public-policy-market-based-solutions-to-societal-challenges-at-uw-madison-college-of-letters-science-4435310692</t>
+          <t>https://jobs.chronicle.com/job/38008254/assistant-professor-of-public-policy-market-based-solutions-to-societal-challenges-/</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>886b76b05d362fdc</t>
+          <t>51857534b7308d30</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
@@ -1800,7 +1800,7 @@
     <row r="15" ht="26" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Civil, Construction and Environmental Engineering</t>
+          <t>Assistant Professor in Transportation Engineering</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1810,20 +1810,20 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Department of Civil, Construction and Environmental Engineering</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="n">
-        <v>5</v>
+          <t>Civil, Construction and Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>10</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Moderate fit: Broad Civil, Construction and Environmental Engineering department search where transportation may be considered, but the job text lacks specific details.</t>
+          <t>Core match: explicitly seeks an Assistant Professor in Transportation Engineering within the Civil, Construction and Environmental Engineering department.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Civil Engineering, Construction Engineering, Environmental Engineering, Transportation Engineering</t>
+          <t>Transportation Engineering, Traffic Operations, Mobility Systems, Civil Engineering</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1848,12 +1848,12 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>Assistant Professor position in Civil, Construction and Environmental Engineering requiring a Ph.D. in a relevant discipline. | Research Topics: Civil Engineering, Construction Engineering, Environmental Engineering, Transportation Engineering</t>
+          <t>Tenure-track Assistant Professor position in Transportation Engineering within the Department of Civil, Construction and Environmental Engineering. | Research Topics: Transportation Engineering, Traffic Operations, Mobility Systems, Civil Engineering</t>
         </is>
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>https://engineering.academickeys.com/job/02ixzgls/Civil-Construction-and-Environmental-Engineering--Assistant-Professor</t>
+          <t>https://engineering.academickeys.com/job/s9z6epb3/Civil-Construction-and-Environmental-Engineering--Transportation-Engineering--Assistant-Professor</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -1863,12 +1863,12 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>f80ad2336a210f82</t>
+          <t>daabd65ea8fe188a</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
@@ -2801,7 +2801,7 @@
     <row r="26" ht="26" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor / Associate Professor (Tenure-Track) in Civil and Environmental Engineering</t>
+          <t>Assistant Professor / Associate Professor in Maritime Studies</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -2815,16 +2815,16 @@
         </is>
       </c>
       <c r="D26" s="7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Moderate fit: broad Civil and Environmental Engineering search where Transportation Engineering is a potential sub-discipline, though specific subfield requirements are not detailed in the snippet.</t>
+          <t>Strong interdisciplinary match: position at NTU School of Civil and Environmental Engineering in Maritime Studies aligns with transportation systems and port/freight mobility.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Civil and Environmental Engineering, Transportation Systems, Infrastructure Systems, Smart Cities</t>
+          <t>Maritime Studies, Transportation Systems, Logistics and Mobility, Network Analysis</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Singapore, Singapore</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>Tenure-track Assistant or Associate Professor position in Civil and Environmental Engineering requiring an earned doctorate in civil engineering or a closely related discipline. | Research Topics: Civil and Environmental Engineering, Transportation Systems, Infrastructure Systems, Smart Cities</t>
+          <t>Faculty position in Maritime Studies within the School of Civil and Environmental Engineering at Nanyang Technological University focusing on maritime transportation and related systems. | Research Topics: Maritime Studies, Transportation Systems, Logistics and Mobility, Network Analysis</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>https://engineering.academickeys.com/job/dhzin0q4/Assistant-Professor--Associate-Professor-TenureTrack-in-Civil-and-Environmental-Engineering</t>
+          <t>https://engineering.academickeys.com/job/m80x7utf/Assistant-Professor--Associate-Professor-TenureTrack-Associate-Professor-PracticeTrack-in-Maritime-Studies</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
@@ -2878,14 +2878,14 @@
         </is>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>1.2899175</v>
+        <v>1.3484104</v>
       </c>
       <c r="R26" s="2" t="n">
-        <v>103.8519072</v>
+        <v>103.6829332</v>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3fa57c30724444e8</t>
+          <t>6736da1a934c5c83</t>
         </is>
       </c>
     </row>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
@@ -3620,7 +3620,7 @@
     <row r="35" ht="26" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Assistant or Associate Professor of Supply Chain Management</t>
+          <t>Assistant Professor in Supply Chain Management</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Low fit: position is in Supply Chain Management within a business school, which falls outside the candidate's core transportation engineering and planning profile.</t>
+          <t>Low relevance: position is in Supply Chain Management within a Business School focusing on contested logistics and defense supply chains, which falls outside transportation engineering and planning.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Management, Logistics, Operations</t>
+          <t>Supply Chain Management, Contested Logistics, Defense-Relevant Supply Chain Research</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -3668,12 +3668,12 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>Seeking an Assistant or Associate Professor in Supply Chain Management to conduct research and publish in leading peer-reviewed journals, requiring a Ph.D. in a relevant discipline. | Research Topics: Supply Chain Management, Logistics, Operations</t>
+          <t>The Sam M. Walton College of Business at the University of Arkansas invites applications for two tenure-track Assistant Professor positions in Supply Chain Management focused on contested logistics and national security supply chains. | Research Topics: Supply Chain Management, Contested Logistics, Defense-Relevant Supply Chain Research</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-or-associate-professor-open-rank-at-university-of-arkansas-%C2%AD-sam-m-walton-college-of-business-4460111187</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-two-open-positions-at-university-of-arkansas-%C2%AD-sam-m-walton-college-of-business-4460109211</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
@@ -3683,12 +3683,12 @@
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>c16a694d5f7f68d4</t>
+          <t>8b974c86c7dfa1c1</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
@@ -4813,20 +4813,20 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Department of Mechanical and Aerospace Engineering</t>
+          <t>Mechanical Engineering</t>
         </is>
       </c>
       <c r="D48" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Moderate fit: Assistant Professor position focused on AI for mobility systems, but housed in Mechanical and Aerospace Engineering rather than Civil and Environmental Engineering.</t>
+          <t>Strong interdisciplinary match focused on AI for mobility systems, though housed in a mechanical engineering department.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Artificial Intelligence, Automotive Systems, Mobility Systems, Connected and Automated Vehicles</t>
+          <t>Artificial Intelligence, Automotive Systems, Mobility Systems</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -4851,27 +4851,27 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>The Ohio State University seeks a tenure-track Assistant Professor in Mechanical and Aerospace Engineering specializing in AI applications for automotive and mobility systems, requiring a Ph.D. in a relevant engineering discipline. | Research Topics: Artificial Intelligence, Automotive Systems, Mobility Systems, Connected and Automated Vehicles</t>
+          <t>The position seeks a tenure-track Assistant Professor specializing in AI for automotive and mobility systems, requiring a Ph.D. in a relevant engineering discipline. | Research Topics: Artificial Intelligence, Automotive Systems, Mobility Systems</t>
         </is>
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>https://engineering.academickeys.com/job/vd0ur9k4/Tenuretrack-Assistant-Professor--AI-for-Automotive-and-Mobility-Systems</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179558778&amp;Title=Tenure%2Dtrack%20Assistant%20Professor%20%E2%80%93%20AI%20for%20Automotive%20and%20Mobility%20Systems</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>AcademicKeys</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="P48" s="3" t="inlineStr">
@@ -4887,24 +4887,24 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>dd476bd66d0aeb1e</t>
+          <t>4e4fa974f5d3f2a4</t>
         </is>
       </c>
     </row>
     <row r="49" ht="26" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Professional Practice Assistant Professor - Air Traffic Control</t>
+          <t>Assistant, Associate, or Full Professor of Mechanical and Industrial Engineering</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Utah State University</t>
+          <t>Northeastern University</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Department of Civil and Environmental Engineering or related aviation/transportation program</t>
+          <t>Department of Mechanical and Industrial Engineering</t>
         </is>
       </c>
       <c r="D49" s="7" t="n">
@@ -4912,22 +4912,22 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Moderate fit: Faculty position in professional practice focusing on air traffic control, which is related to aviation transportation but lacks direct alignment with the candidate's core specialties in surface transit, travel behavior, and discrete choice modeling.</t>
+          <t>Moderate fit: An open-rank industrial engineering search where transportation systems focus is possible but not explicitly guaranteed.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Air Traffic Control, Aviation Transportation, Transportation Operations</t>
+          <t>Industrial Engineering, Systems Engineering, Operations Research</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>Non-Tenure Track</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Logan, UT</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
@@ -4937,32 +4937,32 @@
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>$101,000 - $215,000 per year</t>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>This role seeks a professional practice faculty member to teach and lead instruction in air traffic control operations. | Research Topics: Air Traffic Control, Aviation Transportation, Transportation Operations</t>
+          <t>Open-rank faculty position in mechanical and industrial engineering requiring a Ph.D. in a relevant engineering discipline. | Research Topics: Industrial Engineering, Systems Engineering, Operations Research</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/professional-practice-assistant-professor-air-traffic-control-at-utah-state-university-4462897860</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179560354&amp;Title=Assistant%2C%20Associate%2C%20Full%20Professor%20%2D%20College%20of%20Engineering%20%2D%20Mechanical%20and%20Industrial%20Engineering%20%2D%20Boston</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="P49" s="3" t="inlineStr">
@@ -4971,14 +4971,105 @@
         </is>
       </c>
       <c r="Q49" s="2" t="n">
-        <v>41.7526959</v>
+        <v>42.3351065</v>
       </c>
       <c r="R49" s="2" t="n">
-        <v>-111.808733</v>
+        <v>-71.0892575</v>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>02b944bc9d0177ba</t>
+          <t>e1042bf3b6aa8057</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="26" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Civil Engineering</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>The College of New Jersey</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Civil and Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>Moderate fit: Broad Civil Engineering search where transportation is only one of several potential sub-disciplines.</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Civil Engineering, Infrastructure, Transportation Systems</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>Tenure-Track</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Ewing, NJ</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>$108,433.95 - $116,469.62 per year</t>
+        </is>
+      </c>
+      <c r="K50" s="4" t="inlineStr">
+        <is>
+          <t>Assistant Professor position in Civil and Environmental Engineering requiring a Ph.D. in civil engineering or a closely related field to teach undergraduate courses and build an active research program. | Research Topics: Civil Engineering, Infrastructure, Transportation Systems</t>
+        </is>
+      </c>
+      <c r="L50" s="5" t="inlineStr">
+        <is>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179559500&amp;Title=Assistant%20Professor%2DCivil%20Engineering</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>HigherEdJobs</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="P50" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="n">
+        <v>40.2685516</v>
+      </c>
+      <c r="R50" s="2" t="n">
+        <v>-74.7779768</v>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>f8f163ed02e700ff</t>
         </is>
       </c>
     </row>
@@ -5032,6 +5123,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="rId49"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S50"/>
+  <dimension ref="A1:S51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
@@ -1082,20 +1082,20 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>La Follette School of Public Affairs</t>
+          <t>La Follette School of Public Affairs, College of Letters &amp; Science</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Low fit: Public policy faculty position focused on market-based solutions and economic regulation, whereas candidate's profile is in transportation engineering and planning.</t>
+          <t>Low fit: Public policy and economics position focused on market-based solutions and institutional design, rather than engineering-based transportation systems or planning.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Market-based institutions, Public policy analysis, Regulatory policy and incentive-compatible design</t>
+          <t>Market-Based Solutions, Public Policy, Transportation and Infrastructure Finance, Regulatory Policy</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1110,37 +1110,37 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>Open until filled</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Competitive Salary</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>Assistant professor role in public policy requiring a Ph.D. in Public Policy, Economics, Political Science, Law, or a related field to research market-based solutions and institutional design. | Research Topics: Market-based institutions, Public policy analysis, Regulatory policy and incentive-compatible design</t>
+          <t>The La Follette School of Public Affairs seeks an Assistant Professor to conduct research on market-based institutions, competitive structures, and incentive-compatible policy design. | Research Topics: Market-Based Solutions, Public Policy, Transportation and Infrastructure Finance, Regulatory Policy</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38008254/assistant-professor-of-public-policy-market-based-solutions-to-societal-challenges-/</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-of-public-policy-market-based-solutions-to-societal-challenges-at-uw-madison-college-of-letters-science-4435310692</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>51857534b7308d30</t>
+          <t>886b76b05d362fdc</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
@@ -1800,7 +1800,7 @@
     <row r="15" ht="26" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor in Transportation Engineering</t>
+          <t>Assistant Professor of Civil, Construction and Environmental Engineering</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1813,17 +1813,17 @@
           <t>Civil, Construction and Environmental Engineering</t>
         </is>
       </c>
-      <c r="D15" s="6" t="n">
-        <v>10</v>
+      <c r="D15" s="7" t="n">
+        <v>6</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Core match: explicitly seeks an Assistant Professor in Transportation Engineering within the Civil, Construction and Environmental Engineering department.</t>
+          <t>Moderate fit: broad Civil and Environmental Engineering search where transportation is only one of multiple potential sub-disciplines.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Transportation Engineering, Traffic Operations, Mobility Systems, Civil Engineering</t>
+          <t>Civil Engineering, Transportation Engineering, Construction Engineering, Environmental Engineering</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1848,12 +1848,12 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>Tenure-track Assistant Professor position in Transportation Engineering within the Department of Civil, Construction and Environmental Engineering. | Research Topics: Transportation Engineering, Traffic Operations, Mobility Systems, Civil Engineering</t>
+          <t>Assistant professor position in civil, construction, and environmental engineering requiring a Ph.D. in a relevant discipline. | Research Topics: Civil Engineering, Transportation Engineering, Construction Engineering, Environmental Engineering</t>
         </is>
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>https://engineering.academickeys.com/job/s9z6epb3/Civil-Construction-and-Environmental-Engineering--Transportation-Engineering--Assistant-Professor</t>
+          <t>https://engineering.academickeys.com/job/02ixzgls/Civil-Construction-and-Environmental-Engineering--Assistant-Professor</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -1863,12 +1863,12 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>daabd65ea8fe188a</t>
+          <t>f80ad2336a210f82</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
@@ -2801,7 +2801,7 @@
     <row r="26" ht="26" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor / Associate Professor in Maritime Studies</t>
+          <t>Assistant Professor / Associate Professor in Civil and Environmental Engineering</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -2811,20 +2811,20 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>School of Civil and Environmental Engineering</t>
+          <t>Civil and Environmental Engineering</t>
         </is>
       </c>
       <c r="D26" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Strong interdisciplinary match: position at NTU School of Civil and Environmental Engineering in Maritime Studies aligns with transportation systems and port/freight mobility.</t>
+          <t>Broad Civil and Environmental Engineering faculty search at a target institution, though the exact subfield is unspecified in the snippet.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Maritime Studies, Transportation Systems, Logistics and Mobility, Network Analysis</t>
+          <t>Civil Engineering, Environmental Engineering, Transportation Engineering</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>Faculty position in Maritime Studies within the School of Civil and Environmental Engineering at Nanyang Technological University focusing on maritime transportation and related systems. | Research Topics: Maritime Studies, Transportation Systems, Logistics and Mobility, Network Analysis</t>
+          <t>Tenure-track faculty position in Civil and Environmental Engineering requiring a Ph.D. for teaching and research. | Research Topics: Civil Engineering, Environmental Engineering, Transportation Engineering</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>https://engineering.academickeys.com/job/m80x7utf/Assistant-Professor--Associate-Professor-TenureTrack-Associate-Professor-PracticeTrack-in-Maritime-Studies</t>
+          <t>https://engineering.academickeys.com/job/dhzin0q4/Assistant-Professor--Associate-Professor-TenureTrack-in-Civil-and-Environmental-Engineering</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6736da1a934c5c83</t>
+          <t>3fa57c30724444e8</t>
         </is>
       </c>
     </row>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
@@ -3620,7 +3620,7 @@
     <row r="35" ht="26" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor in Supply Chain Management</t>
+          <t>Assistant or Associate Professor in Supply Chain Management</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Low relevance: position is in Supply Chain Management within a Business School focusing on contested logistics and defense supply chains, which falls outside transportation engineering and planning.</t>
+          <t>Low fit: position is in Supply Chain Management within a business school rather than Transportation Engineering or Systems Engineering.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Management, Contested Logistics, Defense-Relevant Supply Chain Research</t>
+          <t>Supply Chain Management, Logistics, Operations</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -3668,12 +3668,12 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>The Sam M. Walton College of Business at the University of Arkansas invites applications for two tenure-track Assistant Professor positions in Supply Chain Management focused on contested logistics and national security supply chains. | Research Topics: Supply Chain Management, Contested Logistics, Defense-Relevant Supply Chain Research</t>
+          <t>The Sam M. Walton College of Business at the University of Arkansas seeks a tenure-track Assistant or Associate Professor in Supply Chain Management to advance research and teaching in supply chain topics. | Research Topics: Supply Chain Management, Logistics, Operations</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-two-open-positions-at-university-of-arkansas-%C2%AD-sam-m-walton-college-of-business-4460109211</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-or-associate-professor-open-rank-at-university-of-arkansas-%C2%AD-sam-m-walton-college-of-business-4460111187</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
@@ -3683,12 +3683,12 @@
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>8b974c86c7dfa1c1</t>
+          <t>c16a694d5f7f68d4</t>
         </is>
       </c>
     </row>
@@ -4052,7 +4052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
@@ -4813,15 +4813,15 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Mechanical Engineering</t>
+          <t>Department of Mechanical and Aerospace Engineering</t>
         </is>
       </c>
       <c r="D48" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Strong interdisciplinary match focused on AI for mobility systems, though housed in a mechanical engineering department.</t>
+          <t>Moderate fit: Assistant Professor position in Mechanical and Aerospace Engineering focusing on automotive and mobility systems, which is somewhat adjacent to transportation engineering.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -4851,27 +4851,27 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>The position seeks a tenure-track Assistant Professor specializing in AI for automotive and mobility systems, requiring a Ph.D. in a relevant engineering discipline. | Research Topics: Artificial Intelligence, Automotive Systems, Mobility Systems</t>
+          <t>The Department of Mechanical and Aerospace Engineering at The Ohio State University is seeking a tenure-track Assistant Professor specializing in AI for automotive and mobility systems. | Research Topics: Artificial Intelligence, Automotive Systems, Mobility Systems</t>
         </is>
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179558778&amp;Title=Tenure%2Dtrack%20Assistant%20Professor%20%E2%80%93%20AI%20for%20Automotive%20and%20Mobility%20Systems</t>
+          <t>https://engineering.academickeys.com/job/vd0ur9k4/Tenuretrack-Assistant-Professor--AI-for-Automotive-and-Mobility-Systems</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>HigherEdJobs</t>
+          <t>AcademicKeys</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="P48" s="3" t="inlineStr">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>4e4fa974f5d3f2a4</t>
+          <t>dd476bd66d0aeb1e</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="P49" s="3" t="inlineStr">
@@ -5053,7 +5053,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="P50" s="3" t="inlineStr">
@@ -5070,6 +5070,97 @@
       <c r="S50" s="2" t="inlineStr">
         <is>
           <t>f8f163ed02e700ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="26" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Tenure-Track Professor of Land Use and Resilience (Open Rank)</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>University of Michigan</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>Moderate fit: broader land use and resilience search at a target institution, though lacking explicit focus on transportation engineering or travel behavior.</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Land Use, Resilience, Urban Systems</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>Tenure-Track</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Ann Arbor, MI</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="K51" s="4" t="inlineStr">
+        <is>
+          <t>Open rank tenure-track faculty position focusing on land use and resilience requiring a Ph.D. or terminal degree. | Research Topics: Land Use, Resilience, Urban Systems</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/tenure-track-professor-of-land-use-and-resilience-open-rank-at-university-of-michigan-4422103936</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="n">
+        <v>42.278</v>
+      </c>
+      <c r="R51" s="2" t="n">
+        <v>-83.73820000000001</v>
+      </c>
+      <c r="S51" s="2" t="inlineStr">
+        <is>
+          <t>6d685e6e729ffedd</t>
         </is>
       </c>
     </row>
@@ -5124,6 +5215,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L51" r:id="rId50"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Assistant Professor Jobs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assistant Professor Jobs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -100,19 +97,13 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
     </border>
     <border>
       <left style="thin">
@@ -134,31 +125,31 @@
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -526,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T34"/>
+  <dimension ref="A1:T40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -536,7 +527,7 @@
     <col width="32" customWidth="1" min="5" max="5"/>
     <col width="137" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="29" customWidth="1" min="8" max="8"/>
     <col width="50" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="78" customWidth="1" min="11" max="11"/>
@@ -1232,30 +1223,30 @@
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Data Analytics</t>
+          <t>Assistant Professor in Regional and Urban Planning</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Ohio Wesleyan University</t>
+          <t>University College Dublin</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Data Analytics Program</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>4</v>
+          <t>UCD School of Architecture, Planning and Environmental Policy</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>7</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>While data analytics aligns with the candidate's quantitative skills, this liberal arts data analytics position lacks a specific focus on transportation engineering, urban mobility, or civil systems.</t>
+          <t>This Assistant Professor position in Regional and Urban Planning aligns well with the candidate's B.S. and M.S. background in Urban Planning.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Data Analytics, Interdisciplinary Data Science, Big Data Ethics, Data Visualization</t>
+          <t>Regional and Urban Planning, Urban Systems, Spatial Planning</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -1265,47 +1256,47 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Delaware, OH</t>
+          <t>Dublin, Ireland</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>£57,454.37 to £90,980.66 per annum</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>Ohio Wesleyan University seeks a tenure-track Assistant Professor of Data Analytics to teach undergraduate courses, advise students, and maintain an active research agenda requiring a Ph.D. or Master's degree in analytics, data science, or a related field. | Research Topics: Data Analytics, Interdisciplinary Data Science, Big Data Ethics, Data Visualization</t>
+          <t>This is an Assistant Professor role in regional and urban planning at University College Dublin requiring relevant graduate qualifications. | Research Topics: Regional and Urban Planning, Urban Systems, Spatial Planning</t>
         </is>
       </c>
       <c r="M8" s="6" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179549847&amp;Title=Assistant%20Professor%20of%20Data%20Analytics</t>
+          <t>https://www.jobs.ac.uk/job/DSY140/assistant-professor-in-regional-and-urban-planning</t>
         </is>
       </c>
       <c r="N8" s="5" t="inlineStr">
         <is>
-          <t>HigherEdJobs</t>
+          <t>Jobs.ac.uk</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="Q8" s="7" t="inlineStr">
@@ -1314,31 +1305,31 @@
         </is>
       </c>
       <c r="R8" s="2" t="n">
-        <v>40.292858</v>
+        <v>53.3082</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>-83.0642763</v>
+        <v>-6.2238</v>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>99e733f7138cdcde</t>
+          <t>d042d0e38cf2b00a</t>
         </is>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Tenure-Track Professor of Land Use and Resilience (Open Rank)</t>
+          <t>Assistant Professor of Data Analytics</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>University of Michigan</t>
+          <t>Ohio Wesleyan University</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Urban and Regional Planning Program, Taubman College of Architecture and Urban Planning</t>
+          <t>Data Analytics Program</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -1346,12 +1337,12 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>While the candidate has a background in urban planning, this position focuses specifically on land use and climate resilience planning rather than the candidate's core expertise in transportation engineering, transit planning, or travel behavior.</t>
+          <t>While data analytics aligns with the candidate's quantitative skills, this liberal arts data analytics position lacks a specific focus on transportation engineering, urban mobility, or civil systems.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Land Use Planning, Climate Resilience, Urban and Regional Planning, Environmental Disparities</t>
+          <t>Data Analytics, Interdisciplinary Data Science, Big Data Ethics, Data Visualization</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -1361,17 +1352,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI</t>
+          <t>Delaware, OH</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1381,27 +1372,27 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>The University of Michigan seeks an open-rank tenure-track faculty member in land use and resilience planning within the Urban and Regional Planning Program, requiring a terminal degree in planning or a related discipline. | Research Topics: Land Use Planning, Climate Resilience, Urban and Regional Planning, Environmental Disparities</t>
+          <t>Ohio Wesleyan University seeks a tenure-track Assistant Professor of Data Analytics to teach undergraduate courses, advise students, and maintain an active research agenda requiring a Ph.D. or Master's degree in analytics, data science, or a related field. | Research Topics: Data Analytics, Interdisciplinary Data Science, Big Data Ethics, Data Visualization</t>
         </is>
       </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/tenure-track-professor-of-land-use-and-resilience-open-rank-at-university-of-michigan-4422103936</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179549847&amp;Title=Assistant%20Professor%20of%20Data%20Analytics</t>
         </is>
       </c>
       <c r="N9" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="Q9" s="7" t="inlineStr">
@@ -1410,44 +1401,44 @@
         </is>
       </c>
       <c r="R9" s="2" t="n">
-        <v>42.278</v>
+        <v>40.292858</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>-83.73820000000001</v>
+        <v>-83.0642763</v>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6d685e6e729ffedd</t>
+          <t>99e733f7138cdcde</t>
         </is>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Assistant/Associate Professor of Public Administration &amp; MPA Coordinator</t>
+          <t>Tenure-Track Professor of Land Use and Resilience (Open Rank)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>University of New Orleans</t>
+          <t>University of Michigan</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Department of Political Science / Division of Planning and Public Affairs</t>
+          <t>Urban and Regional Planning Program, Taubman College of Architecture and Urban Planning</t>
         </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>The position is for an Assistant/Associate Professor of Public Administration and MPA Coordinator in a political science and public affairs division, which does not align with the candidate's core transportation engineering and travel behavior research profile.</t>
+          <t>While the candidate has a background in urban planning, this position focuses specifically on land use and climate resilience planning rather than the candidate's core expertise in transportation engineering, transit planning, or travel behavior.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Public Administration, Public Policy, Nonprofit Management, Emergency Management</t>
+          <t>Land Use Planning, Climate Resilience, Urban and Regional Planning, Environmental Disparities</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -1457,17 +1448,17 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>New Orleans, LA</t>
+          <t>Ann Arbor, MI</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>Priority: 2026-10-19 / Final: Open until filled</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1477,12 +1468,12 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>The Department of Political Science seeks a tenure-track Assistant or Associate Professor of Public Administration to teach graduate MPA courses, serve as Program Coordinator, and maintain an active research agenda requiring a Ph.D. in Public Administration, Political Science, or a closely related field. | Research Topics: Public Administration, Public Policy, Nonprofit Management, Emergency Management</t>
+          <t>The University of Michigan seeks an open-rank tenure-track faculty member in land use and resilience planning within the Urban and Regional Planning Program, requiring a terminal degree in planning or a related discipline. | Research Topics: Land Use Planning, Climate Resilience, Urban and Regional Planning, Environmental Disparities</t>
         </is>
       </c>
       <c r="M10" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-associate-professor-public-administration-master-of-public-administration-coordinator-at-uno-transportation-institute-4466545068</t>
+          <t>https://www.linkedin.com/jobs/view/tenure-track-professor-of-land-use-and-resilience-open-rank-at-university-of-michigan-4422103936</t>
         </is>
       </c>
       <c r="N10" s="5" t="inlineStr">
@@ -1492,12 +1483,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="Q10" s="7" t="inlineStr">
@@ -1506,44 +1497,44 @@
         </is>
       </c>
       <c r="R10" s="2" t="n">
-        <v>29.9561422</v>
+        <v>42.278</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>-90.0733934</v>
+        <v>-83.73820000000001</v>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>0bd357a7efab4a73</t>
+          <t>6d685e6e729ffedd</t>
         </is>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Urban Economics</t>
+          <t>Assistant/Associate Professor of Public Administration &amp; MPA Coordinator</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Harvard University</t>
+          <t>University of New Orleans</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Harvard Kennedy School of Government</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>5</v>
+          <t>Department of Political Science / Division of Planning and Public Affairs</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>While transportation is listed among the acceptable research areas, this is an urban economics position in a public policy school preferring junior economists rather than a core engineering or mobility planning appointment.</t>
+          <t>The position is for an Assistant/Associate Professor of Public Administration and MPA Coordinator in a political science and public affairs division, which does not align with the candidate's core transportation engineering and travel behavior research profile.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Urban Economics, Housing, Transportation, Infrastructure</t>
+          <t>Public Administration, Public Policy, Nonprofit Management, Emergency Management</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1553,47 +1544,47 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Cambridge, MA</t>
+          <t>New Orleans, LA</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>Priority: 2026-10-19 / Final: Open until filled</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>165k - 185k</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>The Harvard Kennedy School seeks a junior economist to study urban issues including housing, transportation, and infrastructure, requiring a Ph.D. by June 2027. | Research Topics: Urban Economics, Housing, Transportation, Infrastructure</t>
+          <t>The Department of Political Science seeks a tenure-track Assistant or Associate Professor of Public Administration to teach graduate MPA courses, serve as Program Coordinator, and maintain an active research agenda requiring a Ph.D. in Public Administration, Political Science, or a closely related field. | Research Topics: Public Administration, Public Policy, Nonprofit Management, Emergency Management</t>
         </is>
       </c>
       <c r="M11" s="6" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38032116/assistant-professor-urban-economics-/</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-associate-professor-public-administration-master-of-public-administration-coordinator-at-uno-transportation-institute-4466545068</t>
         </is>
       </c>
       <c r="N11" s="5" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="Q11" s="7" t="inlineStr">
@@ -1602,44 +1593,44 @@
         </is>
       </c>
       <c r="R11" s="2" t="n">
-        <v>42.3657432</v>
+        <v>29.9561422</v>
       </c>
       <c r="S11" s="2" t="n">
-        <v>-71.12221390000001</v>
+        <v>-90.0733934</v>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>93251b0fa8170f49</t>
+          <t>0bd357a7efab4a73</t>
         </is>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Assistant or Associate Professor in Supply Chain Management</t>
+          <t>Assistant Professor (Tenure-Track)</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>University of Arkansas</t>
+          <t>Johns Hopkins University</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>J.B. Hunt Transport Department of Supply Chain Management, Sam M. Walton College of Business</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>3</v>
+          <t>School of Government and Policy</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>7</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>This is a tenure-track position in Supply Chain Management housed within a business school, which has limited overlap with the candidate's core transportation engineering and travel behavior profile.</t>
+          <t>Strong interdisciplinary fit as JHU's new School of Government and Policy explicitly solicits candidates with civil engineering and urban planning backgrounds working on transportation and land use, smart city innovation, and AI governance.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Management, Logistics, Operations and Business Research</t>
+          <t>Transportation and Land Use, Urban Innovation and State Capacity, Frontier AI in Government, Public-Sector Technology Adoption</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1649,47 +1640,43 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Fayetteville, AR</t>
+          <t>Washington, DC</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
-        </is>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>2026-11-01</t>
-        </is>
-      </c>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>$100,000 - $200,000 per year</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>The University of Arkansas invites applications for a tenure-track Assistant or Associate Professor in Supply Chain Management starting in August 2027. | Research Topics: Supply Chain Management, Logistics, Operations and Business Research</t>
+          <t>Johns Hopkins University seeks multiple tenure-track Assistant Professors in civil engineering, urban planning, and related fields with research interests in transportation, land use, and AI policy, requiring a Ph.D. or J.D. by the start date. | Research Topics: Transportation and Land Use, Urban Innovation and State Capacity, Frontier AI in Government, Public-Sector Technology Adoption</t>
         </is>
       </c>
       <c r="M12" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-or-associate-professor-open-rank-at-university-of-arkansas-%C2%AD-sam-m-walton-college-of-business-4460111187</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179560444&amp;Title=Assistant%20Professor</t>
         </is>
       </c>
       <c r="N12" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="Q12" s="7" t="inlineStr">
@@ -1698,59 +1685,59 @@
         </is>
       </c>
       <c r="R12" s="2" t="n">
-        <v>36.0970389</v>
+        <v>38.9086858</v>
       </c>
       <c r="S12" s="2" t="n">
-        <v>-94.1703322</v>
+        <v>-77.0395355</v>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>c16a694d5f7f68d4</t>
+          <t>3e8b915493d9b1ef</t>
         </is>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Teaching of Urban Planning</t>
+          <t>Assistant Professor of Urban Economics</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>University of California, Los Angeles (UCLA)</t>
+          <t>Harvard University</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Department of Urban Planning, Luskin School of Public Affairs</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>3</v>
+          <t>Harvard Kennedy School of Government</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>5</v>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>While located in an urban planning department, the role specifically requires teaching and research focused primarily on contexts outside of North America (e.g., Asia, the Middle East, or Africa) for a Master of Global Public Affairs program, which does not align with the candidate's core profile.</t>
+          <t>While transportation is listed among the acceptable research areas, this is an urban economics position in a public policy school preferring junior economists rather than a core engineering or mobility planning appointment.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Global Public Affairs, Comparative Urbanization, International Policy Analysis</t>
+          <t>Urban Economics, Housing, Transportation, Infrastructure</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Non-Tenure Track</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Los Angeles, CA</t>
+          <t>Cambridge, MA</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>Open until filled</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
@@ -1760,17 +1747,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>DOE</t>
+          <t>165k - 185k</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>UCLA seeks an Assistant Professor of Teaching in Urban Planning primarily focused on global public affairs and contexts outside North America, requiring a policy-relevant research agenda and master's/undergraduate instruction. | Research Topics: Global Public Affairs, Comparative Urbanization, International Policy Analysis</t>
+          <t>The Harvard Kennedy School seeks a junior economist to study urban issues including housing, transportation, and infrastructure, requiring a Ph.D. by June 2027. | Research Topics: Urban Economics, Housing, Transportation, Infrastructure</t>
         </is>
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38020965/assistant-professor-of-teaching-of-urban-planning/</t>
+          <t>https://jobs.chronicle.com/job/38032116/assistant-professor-urban-economics-/</t>
         </is>
       </c>
       <c r="N13" s="5" t="inlineStr">
@@ -1780,12 +1767,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="Q13" s="7" t="inlineStr">
@@ -1794,44 +1781,44 @@
         </is>
       </c>
       <c r="R13" s="2" t="n">
-        <v>34.0536909</v>
+        <v>42.3657432</v>
       </c>
       <c r="S13" s="2" t="n">
-        <v>-118.242766</v>
+        <v>-71.12221390000001</v>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>fb7ba0794bd02172</t>
+          <t>93251b0fa8170f49</t>
         </is>
       </c>
     </row>
     <row r="14" ht="26" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Professor, Associate Professor, or Assistant Professor of Industrial and Systems Engineering</t>
+          <t>Assistant or Associate Professor in Supply Chain Management</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Auburn University</t>
+          <t>University of Arkansas</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Department of Industrial &amp; Systems Engineering</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>7</v>
+          <t>J.B. Hunt Transport Department of Supply Chain Management, Sam M. Walton College of Business</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Assistant Professor position in Industrial and Systems Engineering with potential interdisciplinary intersections in transportation systems and human systems integration.</t>
+          <t>This is a tenure-track position in Supply Chain Management housed within a business school, which has limited overlap with the candidate's core transportation engineering and travel behavior profile.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Industrial and Systems Engineering, Human Systems Integration, Operations Research, Systems Engineering</t>
+          <t>Supply Chain Management, Logistics, Operations and Business Research</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -1841,42 +1828,42 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Auburn, AL</t>
+          <t>Fayetteville, AR</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>$80,000 - $180,000 per year</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>An open-rank tenure-track faculty position in Industrial and Systems Engineering requiring an earned doctorate in ISE or a closely related discipline, with research and teaching responsibilities spanning advanced manufacturing, operations research, human systems integration, and systems engineering. | Research Topics: Industrial and Systems Engineering, Human Systems Integration, Operations Research, Systems Engineering</t>
+          <t>The University of Arkansas invites applications for a tenure-track Assistant or Associate Professor in Supply Chain Management starting in August 2027. | Research Topics: Supply Chain Management, Logistics, Operations and Business Research</t>
         </is>
       </c>
       <c r="M14" s="6" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179548357&amp;Title=Professor%2C%20Associate%20Professor%2C%20Assistant%20Professor%20%2D%20Industrial%20and%20Systems%20Engineering</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-or-associate-professor-open-rank-at-university-of-arkansas-%C2%AD-sam-m-walton-college-of-business-4460111187</t>
         </is>
       </c>
       <c r="N14" s="5" t="inlineStr">
         <is>
-          <t>HigherEdJobs</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1890,94 +1877,94 @@
         </is>
       </c>
       <c r="R14" s="2" t="n">
-        <v>32.5919529</v>
+        <v>36.0970389</v>
       </c>
       <c r="S14" s="2" t="n">
-        <v>-85.4959775</v>
+        <v>-94.1703322</v>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>d0f23a527bf71c22</t>
+          <t>c16a694d5f7f68d4</t>
         </is>
       </c>
     </row>
     <row r="15" ht="26" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Civil Engineering (Transportation Engineering)</t>
+          <t>Assistant Professor of Teaching of Urban Planning</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>The College of New Jersey</t>
+          <t>University of California, Los Angeles (UCLA)</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Department of Civil Engineering</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="n">
-        <v>10</v>
+          <t>Department of Urban Planning, Luskin School of Public Affairs</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>This tenure-track Assistant Professor position in Transportation Engineering is a dedicated core match for the candidate's background in transportation systems analysis, travel behavior, and transit planning.</t>
+          <t>While located in an urban planning department, the role specifically requires teaching and research focused primarily on contexts outside of North America (e.g., Asia, the Middle East, or Africa) for a Master of Global Public Affairs program, which does not align with the candidate's core profile.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Transportation Systems Analysis, Transportation Planning, Traffic Operations, Intelligent Transportation Systems</t>
+          <t>Global Public Affairs, Comparative Urbanization, International Policy Analysis</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Non-Tenure Track</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Ewing, NJ</t>
+          <t>Los Angeles, CA</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>Open until filled</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>$108,433.95 - $116,469.62 per year</t>
+          <t>DOE</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>The College of New Jersey seeks a tenure-track Assistant Professor in Transportation Engineering to teach undergraduate coursework, advise senior design projects, and establish an active scholarly research program, requiring an earned doctorate in Civil Engineering or a closely related field. | Research Topics: Transportation Systems Analysis, Transportation Planning, Traffic Operations, Intelligent Transportation Systems</t>
+          <t>UCLA seeks an Assistant Professor of Teaching in Urban Planning primarily focused on global public affairs and contexts outside North America, requiring a policy-relevant research agenda and master's/undergraduate instruction. | Research Topics: Global Public Affairs, Comparative Urbanization, International Policy Analysis</t>
         </is>
       </c>
       <c r="M15" s="6" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179559500&amp;Title=Assistant%20Professor%2DCivil%20Engineering</t>
+          <t>https://jobs.chronicle.com/job/38020965/assistant-professor-of-teaching-of-urban-planning/</t>
         </is>
       </c>
       <c r="N15" s="5" t="inlineStr">
         <is>
-          <t>HigherEdJobs</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Q15" s="7" t="inlineStr">
@@ -1986,31 +1973,31 @@
         </is>
       </c>
       <c r="R15" s="2" t="n">
-        <v>40.2685516</v>
+        <v>34.0536909</v>
       </c>
       <c r="S15" s="2" t="n">
-        <v>-74.7779768</v>
+        <v>-118.242766</v>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>f8f163ed02e700ff</t>
+          <t>fb7ba0794bd02172</t>
         </is>
       </c>
     </row>
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Information and Decision Sciences (Supply Chain &amp; Operations Management)</t>
+          <t>Professor, Associate Professor, or Assistant Professor of Industrial and Systems Engineering</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>University of Illinois Chicago</t>
+          <t>Auburn University</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Department of Information and Decision Sciences, College of Business Administration</t>
+          <t>Department of Industrial &amp; Systems Engineering</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
@@ -2018,12 +2005,12 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Strong interdisciplinary business school fit as the position explicitly prioritizes transportation as a preferred applied research domain for operations management.</t>
+          <t>Assistant Professor position in Industrial and Systems Engineering with potential interdisciplinary intersections in transportation systems and human systems integration.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Operations Management, Supply Chain Management, Transportation, Artificial Intelligence</t>
+          <t>Industrial and Systems Engineering, Human Systems Integration, Operations Research, Systems Engineering</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -2033,32 +2020,32 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>Auburn, AL</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>Priority: 2026-10-20 / Final: 2026-12-06</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>$185,000 - $220,000 annually</t>
+          <t>$80,000 - $180,000 per year</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>This tenure-track assistant professor role in operations management seeks candidates with a Ph.D. in a related field and explicitly prefers research focused on transportation and AI-integrated supply chain management. | Research Topics: Operations Management, Supply Chain Management, Transportation, Artificial Intelligence</t>
+          <t>An open-rank tenure-track faculty position in Industrial and Systems Engineering requiring an earned doctorate in ISE or a closely related discipline, with research and teaching responsibilities spanning advanced manufacturing, operations research, human systems integration, and systems engineering. | Research Topics: Industrial and Systems Engineering, Human Systems Integration, Operations Research, Systems Engineering</t>
         </is>
       </c>
       <c r="M16" s="6" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179552436&amp;Title=Assistant%20Professor%20%2D%20IDS%20%28Supply%20Chain%20%26%20Operations%20Management%29</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179548357&amp;Title=Professor%2C%20Associate%20Professor%2C%20Assistant%20Professor%20%2D%20Industrial%20and%20Systems%20Engineering</t>
         </is>
       </c>
       <c r="N16" s="5" t="inlineStr">
@@ -2068,12 +2055,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="Q16" s="7" t="inlineStr">
@@ -2082,26 +2069,26 @@
         </is>
       </c>
       <c r="R16" s="2" t="n">
-        <v>41.8748613</v>
+        <v>32.5919529</v>
       </c>
       <c r="S16" s="2" t="n">
-        <v>-87.6519866</v>
+        <v>-85.4959775</v>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>77e0632bd4e74eae</t>
+          <t>d0f23a527bf71c22</t>
         </is>
       </c>
     </row>
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Tenure-Track Faculty Positions in Transportation Engineering</t>
+          <t>Assistant Professor of Civil Engineering (Transportation Engineering)</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>National Taiwan University</t>
+          <t>The College of New Jersey</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2109,17 +2096,17 @@
           <t>Department of Civil Engineering</t>
         </is>
       </c>
-      <c r="D17" s="3" t="n">
-        <v>7</v>
+      <c r="D17" s="8" t="n">
+        <v>10</v>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>This is a civil engineering faculty search at National Taiwan University that explicitly includes Public Transportation and Intelligent Transportation Systems as preferred research areas.</t>
+          <t>This tenure-track Assistant Professor position in Transportation Engineering is a dedicated core match for the candidate's background in transportation systems analysis, travel behavior, and transit planning.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Intelligent Transportation Systems, Public Transportation, Transportation Economics</t>
+          <t>Transportation Systems Analysis, Transportation Planning, Traffic Operations, Intelligent Transportation Systems</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -2129,47 +2116,47 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Taipei, Taiwan</t>
+          <t>Ewing, NJ</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Monthly salary: NT$83,720–137,370</t>
+          <t>$108,433.95 - $116,469.62 per year</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>National Taiwan University seeks multiple tenure-track faculty members in transportation engineering and surveying, requiring a Ph.D. and the ability to teach in English. | Research Topics: Intelligent Transportation Systems, Public Transportation, Transportation Economics</t>
+          <t>The College of New Jersey seeks a tenure-track Assistant Professor in Transportation Engineering to teach undergraduate coursework, advise senior design projects, and establish an active scholarly research program, requiring an earned doctorate in Civil Engineering or a closely related field. | Research Topics: Transportation Systems Analysis, Transportation Planning, Traffic Operations, Intelligent Transportation Systems</t>
         </is>
       </c>
       <c r="M17" s="6" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38034402/faculty-recruitment-announcement-department-of-civil-engineering-national-taiwan-university/</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179559500&amp;Title=Assistant%20Professor%2DCivil%20Engineering</t>
         </is>
       </c>
       <c r="N17" s="5" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="Q17" s="7" t="inlineStr">
@@ -2178,94 +2165,94 @@
         </is>
       </c>
       <c r="R17" s="2" t="n">
-        <v>25.0375198</v>
+        <v>40.2685516</v>
       </c>
       <c r="S17" s="2" t="n">
-        <v>121.5636796</v>
+        <v>-74.7779768</v>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>f056997ace2e1de7</t>
+          <t>f8f163ed02e700ff</t>
         </is>
       </c>
     </row>
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Lecturer in Discipline or Senior Lecturer in Discipline</t>
+          <t>Assistant Professor of Public Policy (Market-Based Solutions to Societal Challenges)</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Columbia University</t>
+          <t>University of Wisconsin-Madison</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Department of Industrial Engineering and Operations Research</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>7</v>
+          <t>La Follette School of Public Affairs, College of Letters &amp; Science</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>This is a full-time career-track lecturer role in Industrial Engineering and Operations Research at Columbia University focused on Artificial Intelligence and data science applications, which aligns well with the candidate's strong machine learning and data-driven modeling expertise.</t>
+          <t>While transportation and infrastructure finance is listed as a potential application area, this position is centered on public policy, economics, and market-based policy design rather than transportation engineering and planning.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Artificial Intelligence, Operations Research, Data Science, Machine Learning Applications</t>
+          <t>Market-Based Public Policy, Transportation and Infrastructure Finance, Regulatory Policy and Microeconomics, Institutional Design</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Non-Tenure Track</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Madison, WI</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>2027-01-01</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>2027-01-01</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Lecturer in Discipline: 106K-129K; Senior Lecturer in Discipline: 125K-162K</t>
+          <t>Negotiable</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>Columbia University seeks a full-time Lecturer or Senior Lecturer in the Department of Industrial Engineering and Operations Research to teach AI and data science courses, requiring a Ph.D. in a related quantitative discipline. | Research Topics: Artificial Intelligence, Operations Research, Data Science, Machine Learning Applications</t>
+          <t>The La Follette School of Public Affairs seeks a tenure-track Assistant Professor researching market-based institutions and incentive-compatible policy design across societal challenges, requiring a Ph.D. in Public Policy, Economics, Political Science, or a related field. | Research Topics: Market-Based Public Policy, Transportation and Infrastructure Finance, Regulatory Policy and Microeconomics, Institutional Design</t>
         </is>
       </c>
       <c r="M18" s="6" t="inlineStr">
         <is>
-          <t>http://engineering.academickeys.com/job/arsy3jqh/Open-Rank-Lecturer-in-Discipline-or-Senior-Lecturer-in-Discipline</t>
+          <t>https://jobs.chronicle.com/job/38008254/assistant-professor-of-public-policy-market-based-solutions-to-societal-challenges-/</t>
         </is>
       </c>
       <c r="N18" s="5" t="inlineStr">
         <is>
-          <t>AcademicKeys</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="Q18" s="7" t="inlineStr">
@@ -2274,44 +2261,44 @@
         </is>
       </c>
       <c r="R18" s="2" t="n">
-        <v>40.8077507</v>
+        <v>43.0802745</v>
       </c>
       <c r="S18" s="2" t="n">
-        <v>-73.9624901</v>
+        <v>-89.43095870000001</v>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>f11b4a4e74422ae3</t>
+          <t>51857534b7308d30</t>
         </is>
       </c>
     </row>
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Assistant/Associate/Full Professor, Transportation Engineering and Systems</t>
+          <t>Assistant Professor of Information and Decision Sciences (Supply Chain &amp; Operations Management)</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>University of Cincinnati</t>
+          <t>University of Illinois Chicago</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Department of Civil and Architectural Engineering and Construction Management (CAECM)</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="n">
-        <v>9</v>
+          <t>Department of Information and Decision Sciences, College of Business Administration</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>7</v>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>This is a dedicated Assistant/Associate/Full Professor position in Transportation Engineering and Systems perfectly aligned with the candidate's core research profile.</t>
+          <t>Strong interdisciplinary business school fit as the position explicitly prioritizes transportation as a preferred applied research domain for operations management.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Transportation Engineering, Transportation Systems, Transit Planning</t>
+          <t>Operations Management, Supply Chain Management, Transportation, Artificial Intelligence</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
@@ -2321,38 +2308,42 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Cincinnati, OH</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>Open until filled</t>
-        </is>
-      </c>
-      <c r="J19" s="5" t="inlineStr"/>
+          <t>Priority: 2026-10-20 / Final: 2026-12-06</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>2026-12-06</t>
+        </is>
+      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>$185,000 - $220,000 annually</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>This role seeks a faculty member in transportation engineering and systems within an R1 urban research university setting requiring an appropriate terminal degree. | Research Topics: Transportation Engineering, Transportation Systems, Transit Planning</t>
+          <t>This tenure-track assistant professor role in operations management seeks candidates with a Ph.D. in a related field and explicitly prefers research focused on transportation and AI-integrated supply chain management. | Research Topics: Operations Management, Supply Chain Management, Transportation, Artificial Intelligence</t>
         </is>
       </c>
       <c r="M19" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-associate-full-professor-transportation-engineering-and-systems-at-university-of-cincinnati-4416744025</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179552436&amp;Title=Assistant%20Professor%20%2D%20IDS%20%28Supply%20Chain%20%26%20Operations%20Management%29</t>
         </is>
       </c>
       <c r="N19" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2366,44 +2357,44 @@
         </is>
       </c>
       <c r="R19" s="2" t="n">
-        <v>39.1318888</v>
+        <v>41.8748613</v>
       </c>
       <c r="S19" s="2" t="n">
-        <v>-84.51578309999999</v>
+        <v>-87.6519866</v>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6aa8ab000bc6f6c0</t>
+          <t>77e0632bd4e74eae</t>
         </is>
       </c>
     </row>
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Tenure-Track Faculty Positions in Transportation Engineering</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>National Taiwan University</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>School of City and Regional Planning</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="n">
-        <v>8</v>
+          <t>Department of Civil Engineering</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>7</v>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>This is an Assistant Professor position within the School of City and Regional Planning, matching the candidate's background in urban planning and transportation mobility research.</t>
+          <t>This is a civil engineering faculty search at National Taiwan University that explicitly includes Public Transportation and Intelligent Transportation Systems as preferred research areas.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Urban Planning and Spatial Analytics, Sustainable and Resilient Communities, Mobility Analytics</t>
+          <t>Intelligent Transportation Systems, Public Transportation, Transportation Economics</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
@@ -2413,43 +2404,47 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Taipei, Taiwan</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>Open until filled</t>
-        </is>
-      </c>
-      <c r="J20" s="5" t="inlineStr"/>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Monthly salary: NT$83,720–137,370</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology seeks a tenure-track Assistant Professor in the School of City and Regional Planning to advance research and teaching in urban planning, spatial analytics, and sustainable communities. | Research Topics: Urban Planning and Spatial Analytics, Sustainable and Resilient Communities, Mobility Analytics</t>
+          <t>National Taiwan University seeks multiple tenure-track faculty members in transportation engineering and surveying, requiring a Ph.D. and the ability to teach in English. | Research Topics: Intelligent Transportation Systems, Public Transportation, Transportation Economics</t>
         </is>
       </c>
       <c r="M20" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-at-georgia-institute-of-technology-4467296351</t>
+          <t>https://jobs.chronicle.com/job/38034402/faculty-recruitment-announcement-department-of-civil-engineering-national-taiwan-university/</t>
         </is>
       </c>
       <c r="N20" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Q20" s="7" t="inlineStr">
@@ -2458,80 +2453,84 @@
         </is>
       </c>
       <c r="R20" s="2" t="n">
-        <v>33.7756</v>
+        <v>25.0375198</v>
       </c>
       <c r="S20" s="2" t="n">
-        <v>-84.3963</v>
+        <v>121.5636796</v>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1b7278bf60327029</t>
+          <t>f056997ace2e1de7</t>
         </is>
       </c>
     </row>
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Assistant/Associate Professor of Civil Engineering</t>
+          <t>Lecturer in Discipline or Senior Lecturer in Discipline</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Cedarville University</t>
+          <t>Columbia University</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>School of Engineering and Computer Science</t>
+          <t>Department of Industrial Engineering and Operations Research</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>This is a broad civil engineering faculty search where transportation is explicitly listed as one of the acceptable sub-disciplines.</t>
+          <t>This is a full-time career-track lecturer role in Industrial Engineering and Operations Research at Columbia University focused on Artificial Intelligence and data science applications, which aligns well with the candidate's strong machine learning and data-driven modeling expertise.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Transportation Engineering, Civil Engineering Education, Undergraduate Mentoring</t>
+          <t>Artificial Intelligence, Operations Research, Data Science, Machine Learning Applications</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Non-Tenure Track</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Cedarville, OH</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>Open until filled</t>
-        </is>
-      </c>
-      <c r="J21" s="5" t="inlineStr"/>
+          <t>2027-01-01</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>2027-01-01</t>
+        </is>
+      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Lecturer in Discipline: 106K-129K; Senior Lecturer in Discipline: 125K-162K</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>This position seeks an Assistant or Associate Professor in Civil Engineering to teach undergraduate courses and mentor students across disciplines including transportation, requiring a Ph.D. in Civil Engineering or related field. | Research Topics: Transportation Engineering, Civil Engineering Education, Undergraduate Mentoring</t>
+          <t>Columbia University seeks a full-time Lecturer or Senior Lecturer in the Department of Industrial Engineering and Operations Research to teach AI and data science courses, requiring a Ph.D. in a related quantitative discipline. | Research Topics: Artificial Intelligence, Operations Research, Data Science, Machine Learning Applications</t>
         </is>
       </c>
       <c r="M21" s="6" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179544290&amp;Title=Assistant%2FAssociate%20Professor%20of%20Civil%20Engineering</t>
+          <t>http://engineering.academickeys.com/job/arsy3jqh/Open-Rank-Lecturer-in-Discipline-or-Senior-Lecturer-in-Discipline</t>
         </is>
       </c>
       <c r="N21" s="5" t="inlineStr">
         <is>
-          <t>HigherEdJobs</t>
+          <t>AcademicKeys</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -2541,7 +2540,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="Q21" s="7" t="inlineStr">
@@ -2550,44 +2549,44 @@
         </is>
       </c>
       <c r="R21" s="2" t="n">
-        <v>39.7540491</v>
+        <v>40.8077507</v>
       </c>
       <c r="S21" s="2" t="n">
-        <v>-83.8170518</v>
+        <v>-73.9624901</v>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>751c7406865a2787</t>
+          <t>f11b4a4e74422ae3</t>
         </is>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Civil Engineering</t>
+          <t>Assistant/Associate/Full Professor, Transportation Engineering and Systems</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>McNeese State University</t>
+          <t>University of Cincinnati</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Department of Engineering and Computer Science</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="n">
-        <v>6</v>
+          <t>Department of Civil and Architectural Engineering and Construction Management (CAECM)</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>9</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>This is a broad civil engineering faculty search that explicitly welcomes transportation engineering alongside other sub-disciplines.</t>
+          <t>This is a dedicated Assistant/Associate/Full Professor position in Transportation Engineering and Systems perfectly aligned with the candidate's core research profile.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Civil Engineering, Transportation Engineering, Water Resources and Hydraulic Engineering, Structural and Geotechnical Engineering</t>
+          <t>Transportation Engineering, Transportation Systems, Transit Planning</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -2597,7 +2596,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Lake Charles, LA</t>
+          <t>Cincinnati, OH</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
@@ -2608,32 +2607,32 @@
       <c r="J22" s="5" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>$76,000 per year</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>McNeese State University seeks a full-time, tenure-track Assistant Professor of Civil Engineering to teach, advise students, and conduct research, requiring a Ph.D. in Civil Engineering. | Research Topics: Civil Engineering, Transportation Engineering, Water Resources and Hydraulic Engineering, Structural and Geotechnical Engineering</t>
+          <t>This role seeks a faculty member in transportation engineering and systems within an R1 urban research university setting requiring an appropriate terminal degree. | Research Topics: Transportation Engineering, Transportation Systems, Transit Planning</t>
         </is>
       </c>
       <c r="M22" s="6" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179545361&amp;Title=Assistant%20Professor%20of%20Civil%20Engineering</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-associate-full-professor-transportation-engineering-and-systems-at-university-of-cincinnati-4416744025</t>
         </is>
       </c>
       <c r="N22" s="5" t="inlineStr">
         <is>
-          <t>HigherEdJobs</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="Q22" s="7" t="inlineStr">
@@ -2642,44 +2641,44 @@
         </is>
       </c>
       <c r="R22" s="2" t="n">
-        <v>30.1751363</v>
+        <v>39.1318888</v>
       </c>
       <c r="S22" s="2" t="n">
-        <v>-93.2112786</v>
+        <v>-84.51578309999999</v>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>bd292fb9f52ac2e9</t>
+          <t>6aa8ab000bc6f6c0</t>
         </is>
       </c>
     </row>
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor / Associate Professor (Tenure-Track) in Civil and Environmental Engineering</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Nanyang Technological University</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>School of Civil and Environmental Engineering, College of Engineering</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="n">
-        <v>6</v>
+          <t>School of City and Regional Planning</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="n">
+        <v>8</v>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>This is an open-rank Civil and Environmental Engineering search at a top international university where transportation is one of several potential engineering domains.</t>
+          <t>This is an Assistant Professor position within the School of City and Regional Planning, matching the candidate's background in urban planning and transportation mobility research.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Civil and Environmental Engineering, Geospatial Technologies, Infrastructure Systems</t>
+          <t>Urban Planning and Spatial Analytics, Sustainable and Resilient Communities, Mobility Analytics</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
@@ -2689,7 +2688,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
@@ -2700,32 +2699,32 @@
       <c r="J23" s="5" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>Highly competitive</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>Nanyang Technological University seeks tenure-track faculty across areas of civil and environmental engineering requiring a Ph.D. in a related field. | Research Topics: Civil and Environmental Engineering, Geospatial Technologies, Infrastructure Systems</t>
+          <t>Georgia Institute of Technology seeks a tenure-track Assistant Professor in the School of City and Regional Planning to advance research and teaching in urban planning, spatial analytics, and sustainable communities. | Research Topics: Urban Planning and Spatial Analytics, Sustainable and Resilient Communities, Mobility Analytics</t>
         </is>
       </c>
       <c r="M23" s="6" t="inlineStr">
         <is>
-          <t>https://engineering.academickeys.com/job/dhzin0q4/Assistant-Professor--Associate-Professor-TenureTrack-in-Civil-and-Environmental-Engineering</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-at-georgia-institute-of-technology-4467296351</t>
         </is>
       </c>
       <c r="N23" s="5" t="inlineStr">
         <is>
-          <t>AcademicKeys</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="Q23" s="7" t="inlineStr">
@@ -2734,54 +2733,54 @@
         </is>
       </c>
       <c r="R23" s="2" t="n">
-        <v>1.3484104</v>
+        <v>33.7756</v>
       </c>
       <c r="S23" s="2" t="n">
-        <v>103.6829332</v>
+        <v>-84.3963</v>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3fa57c30724444e8</t>
+          <t>1b7278bf60327029</t>
         </is>
       </c>
     </row>
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor in Low-Altitude Economy</t>
+          <t>Assistant or Associate Professor in Complex Systems and Urban &amp; Regional Modelling</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>The Hong Kong Polytechnic University</t>
+          <t>Maastricht University</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Faculty of Science and Engineering</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>The position focuses on the low-altitude economy, which aligns with advanced mobility and transportation systems, though it is based in Europe despite the institution being in Hong Kong.</t>
+          <t>This Assistant or Associate Professor role in complex systems and urban and regional modelling aligns well with the candidate's strong computational and urban modelling expertise.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Low-Altitude Economy, Advanced Air Mobility, Transportation Systems, Mobility Management</t>
+          <t>Urban and Regional Modelling, Complex Systems Theory, Urban Sustainability, Spatial Modelling</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Unspecified</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Maastricht, Netherlands</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
@@ -2797,17 +2796,17 @@
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>This tenure-track Assistant Professor position focuses on research and teaching within the low-altitude economy and advanced mobility sectors, requiring a relevant doctoral degree. | Research Topics: Low-Altitude Economy, Advanced Air Mobility, Transportation Systems, Mobility Management</t>
+          <t>Maastricht University seeks an Assistant or Associate Professor to build a new research line in urban and regional modelling, requiring a PhD in a relevant technical or computational field. | Research Topics: Urban and Regional Modelling, Complex Systems Theory, Urban Sustainability, Spatial Modelling</t>
         </is>
       </c>
       <c r="M24" s="6" t="inlineStr">
         <is>
-          <t>https://www.jobs.ac.uk/job/DSJ402/assistant-professor-in-low-altitude-economy</t>
+          <t>https://nl.linkedin.com/jobs/view/assistant-or-associate-professor-in-complex-systems-and-urban-regional-modelling-at-maastricht-university-faculty-of-science-and-engineering-4452765174</t>
         </is>
       </c>
       <c r="N24" s="5" t="inlineStr">
         <is>
-          <t>Jobs.ac.uk</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -2826,31 +2825,31 @@
         </is>
       </c>
       <c r="R24" s="2" t="n">
-        <v>22.3044867</v>
+        <v>50.8472117</v>
       </c>
       <c r="S24" s="2" t="n">
-        <v>114.1796935</v>
+        <v>5.6859518</v>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>ce4ae0a91b9988f7</t>
+          <t>321ee686ffad2403</t>
         </is>
       </c>
     </row>
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Assistant/Associate Professor of Civil Engineering (Transportation)</t>
+          <t>Assistant/Associate Professor of Civil Engineering</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Trine University</t>
+          <t>Cedarville University</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Reiners Department of Civil and Environmental Engineering</t>
+          <t>School of Engineering and Computer Science</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
@@ -2858,22 +2857,22 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>This is a broad Civil Engineering assistant/associate professor position at a teaching-focused institution where transportation engineering is explicitly listed as a primary teaching and curricular requirement.</t>
+          <t>This is a broad civil engineering faculty search where transportation is explicitly listed as one of the acceptable sub-disciplines.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Transportation Engineering, Undergraduate Engineering Education, Geographic Information Systems (GIS), Civil Engineering Curriculum</t>
+          <t>Transportation Engineering, Civil Engineering Education, Undergraduate Mentoring</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Unspecified</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Angola, IN</t>
+          <t>Cedarville, OH</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
@@ -2884,32 +2883,32 @@
       <c r="J25" s="5" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Based on qualifications</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>Trine University seeks a full-time Assistant or Associate Professor of Civil Engineering with a specialization in transportation to teach undergraduate courses, engage students in applied projects, and support program accreditation, requiring a Ph.D. in Civil Engineering or a closely related field. | Research Topics: Transportation Engineering, Undergraduate Engineering Education, Geographic Information Systems (GIS), Civil Engineering Curriculum</t>
+          <t>This position seeks an Assistant or Associate Professor in Civil Engineering to teach undergraduate courses and mentor students across disciplines including transportation, requiring a Ph.D. in Civil Engineering or related field. | Research Topics: Transportation Engineering, Civil Engineering Education, Undergraduate Mentoring</t>
         </is>
       </c>
       <c r="M25" s="6" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38028401/assistant-associate-professor-civil-engineering-transportation-/</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179544290&amp;Title=Assistant%2FAssociate%20Professor%20of%20Civil%20Engineering</t>
         </is>
       </c>
       <c r="N25" s="5" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="Q25" s="7" t="inlineStr">
@@ -2918,44 +2917,44 @@
         </is>
       </c>
       <c r="R25" s="2" t="n">
-        <v>41.6311141</v>
+        <v>39.7540491</v>
       </c>
       <c r="S25" s="2" t="n">
-        <v>-85.0105982</v>
+        <v>-83.8170518</v>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9f9cc58aa59ccd96</t>
+          <t>751c7406865a2787</t>
         </is>
       </c>
     </row>
     <row r="26" ht="26" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Public Policy</t>
+          <t>Assistant Professor of Civil Engineering</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>University of Texas at Arlington</t>
+          <t>McNeese State University</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Department of Public Affairs &amp; Planning</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="n">
-        <v>4</v>
+          <t>Department of Engineering and Computer Science</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>The position is for an Assistant Professor of Public Policy in a public affairs department, which falls outside the candidate's core expertise in transportation engineering, travel behavior, and mobility systems.</t>
+          <t>This is a broad civil engineering faculty search that explicitly welcomes transportation engineering alongside other sub-disciplines.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Public Policy, Urban Studies, Public Infrastructure, Public Administration</t>
+          <t>Civil Engineering, Transportation Engineering, Water Resources and Hydraulic Engineering, Structural and Geotechnical Engineering</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
@@ -2965,7 +2964,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Arlington, TX</t>
+          <t>Lake Charles, LA</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
@@ -2976,78 +2975,78 @@
       <c r="J26" s="5" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>$76,000 per year</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>The University of Texas at Arlington seeks a tenure-track Assistant Professor of Public Policy in the Department of Public Affairs and Planning requiring a Ph.D. in public policy or a related social science discipline. | Research Topics: Public Policy, Urban Studies, Public Infrastructure, Public Administration</t>
+          <t>McNeese State University seeks a full-time, tenure-track Assistant Professor of Civil Engineering to teach, advise students, and conduct research, requiring a Ph.D. in Civil Engineering. | Research Topics: Civil Engineering, Transportation Engineering, Water Resources and Hydraulic Engineering, Structural and Geotechnical Engineering</t>
         </is>
       </c>
       <c r="M26" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-at-excel-campus-activities-4464851831</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179545361&amp;Title=Assistant%20Professor%20of%20Civil%20Engineering</t>
         </is>
       </c>
       <c r="N26" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
       <c r="Q26" s="7" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
       <c r="R26" s="2" t="n">
-        <v>32.7315155</v>
+        <v>30.1751363</v>
       </c>
       <c r="S26" s="2" t="n">
-        <v>-97.1171533</v>
+        <v>-93.2112786</v>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>15704bb25858281c</t>
+          <t>bd292fb9f52ac2e9</t>
         </is>
       </c>
     </row>
     <row r="27" ht="26" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor in Supply Chain Management</t>
+          <t>Assistant Professor / Associate Professor (Tenure-Track) in Civil and Environmental Engineering</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Iowa State University</t>
+          <t>Nanyang Technological University</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Department of Supply Chain Management, Ivy College of Business</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>3</v>
+          <t>School of Civil and Environmental Engineering, College of Engineering</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>This is a business school position focused on supply chain management rather than transportation engineering or urban mobility systems.</t>
+          <t>This is an open-rank Civil and Environmental Engineering search at a top international university where transportation is one of several potential engineering domains.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Management, Logistics, Operations</t>
+          <t>Civil and Environmental Engineering, Geospatial Technologies, Infrastructure Systems</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -3057,7 +3056,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Ames, IA</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
@@ -3068,32 +3067,32 @@
       <c r="J27" s="5" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Highly competitive</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>Iowa State University seeks a tenure-track Assistant Professor in Supply Chain Management to conduct research and teach courses at the undergraduate, master's, and Ph.D. levels, requiring a doctorate in business administration, supply chain, transportation, logistics, operations, or a related field. | Research Topics: Supply Chain Management, Logistics, Operations</t>
+          <t>Nanyang Technological University seeks tenure-track faculty across areas of civil and environmental engineering requiring a Ph.D. in a related field. | Research Topics: Civil and Environmental Engineering, Geospatial Technologies, Infrastructure Systems</t>
         </is>
       </c>
       <c r="M27" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-in-supply-chain-management-at-iowa-state-university-ivy-college-of-business-4440811209</t>
+          <t>https://engineering.academickeys.com/job/dhzin0q4/Assistant-Professor--Associate-Professor-TenureTrack-in-Civil-and-Environmental-Engineering</t>
         </is>
       </c>
       <c r="N27" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>AcademicKeys</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="Q27" s="7" t="inlineStr">
@@ -3102,44 +3101,44 @@
         </is>
       </c>
       <c r="R27" s="2" t="n">
-        <v>42.0267567</v>
+        <v>1.3484104</v>
       </c>
       <c r="S27" s="2" t="n">
-        <v>-93.6170448</v>
+        <v>103.6829332</v>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>e994e392d38b77ce</t>
+          <t>3fa57c30724444e8</t>
         </is>
       </c>
     </row>
     <row r="28" ht="26" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Assistant/Associate/Full Professor in Industrial and Systems Engineering</t>
+          <t>Assistant Professor / Associate Professor in Civil and Environmental Engineering</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>University of Florida</t>
+          <t>Nanyang Technological University Singapore</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Department of Industrial and Systems Engineering</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>3</v>
+          <t>School of Civil and Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Although transportation is mentioned as a potential application area, the primary focus of this Industrial and Systems Engineering position is on Industrialized Construction and 3D construction printing rather than core transportation engineering, mobility, or travel behavior.</t>
+          <t>This is an open-rank faculty search in Civil and Environmental Engineering where transportation is a potential fit among broader infrastructure domains.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Industrialized Construction, Artificial Intelligence, Digital Twins, Operations Research</t>
+          <t>Civil Engineering, Geospatial Technologies, Digital Construction, Infrastructure Systems</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
@@ -3149,7 +3148,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Gainesville, FL</t>
+          <t>Singapore, Singapore</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
@@ -3160,17 +3159,17 @@
       <c r="J28" s="5" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Salary is commensurate with education and experience.</t>
+          <t>Highly competitive</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>This full-time tenured or tenure-track faculty position in Industrial and Systems Engineering at the University of Florida seeks expertise in industrialized construction and related technologies, requiring a Ph.D. in ISE, Manufacturing Engineering, Civil Engineering, Mechanical Engineering, or a closely related field. | Research Topics: Industrialized Construction, Artificial Intelligence, Digital Twins, Operations Research</t>
+          <t>Nanyang Technological University seeks tenure-track faculty across all areas of Civil and Environmental Engineering requiring a Ph.D. in a relevant field. | Research Topics: Civil Engineering, Geospatial Technologies, Digital Construction, Infrastructure Systems</t>
         </is>
       </c>
       <c r="M28" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-associate-full-professor-industrial-systems-engineering-at-university-of-florida-4323668785</t>
+          <t>https://sg.linkedin.com/jobs/view/assistant-professor-associate-professor-tenure-track-in-civil-and-environmental-engineering-at-nanyang-technological-university-singapore-4432357834</t>
         </is>
       </c>
       <c r="N28" s="5" t="inlineStr">
@@ -3180,12 +3179,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="Q28" s="7" t="inlineStr">
@@ -3194,44 +3193,44 @@
         </is>
       </c>
       <c r="R28" s="2" t="n">
-        <v>29.6436</v>
+        <v>1.3483</v>
       </c>
       <c r="S28" s="2" t="n">
-        <v>-82.3549</v>
+        <v>103.6831</v>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>56d501f448e77e05</t>
+          <t>ce5f34eaef46b041</t>
         </is>
       </c>
     </row>
     <row r="29" ht="26" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Public Policy</t>
+          <t>Assistant Professor in Low-Altitude Economy</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>University of Wisconsin-Madison</t>
+          <t>The Hong Kong Polytechnic University</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>La Follette School of Public Affairs</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>3</v>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Although the position lists transportation finance as one of many sub-areas, it is primarily a public policy and economics faculty role focused on market institutions rather than transportation engineering or travel behavior.</t>
+          <t>The position focuses on the low-altitude economy, which aligns with advanced mobility and transportation systems, though it is based in Europe despite the institution being in Hong Kong.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Public Policy, Market-Based Institutions, Transportation and Infrastructure Finance, Regulatory Policy</t>
+          <t>Low-Altitude Economy, Advanced Air Mobility, Transportation Systems, Mobility Management</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -3241,7 +3240,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Madison, WI</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
@@ -3257,27 +3256,27 @@
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>The La Follette School of Public Affairs seeks a tenure-track Assistant Professor of Public Policy specializing in market-based institutions and incentive-compatible policy design. | Research Topics: Public Policy, Market-Based Institutions, Transportation and Infrastructure Finance, Regulatory Policy</t>
+          <t>This tenure-track Assistant Professor position focuses on research and teaching within the low-altitude economy and advanced mobility sectors, requiring a relevant doctoral degree. | Research Topics: Low-Altitude Economy, Advanced Air Mobility, Transportation Systems, Mobility Management</t>
         </is>
       </c>
       <c r="M29" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-of-public-policy-market-based-solutions-to-societal-challenges-at-uw-madison-college-of-letters-science-4435310692</t>
+          <t>https://www.jobs.ac.uk/job/DSJ402/assistant-professor-in-low-altitude-economy</t>
         </is>
       </c>
       <c r="N29" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Jobs.ac.uk</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="Q29" s="7" t="inlineStr">
@@ -3286,31 +3285,31 @@
         </is>
       </c>
       <c r="R29" s="2" t="n">
-        <v>43.0802745</v>
+        <v>22.3044867</v>
       </c>
       <c r="S29" s="2" t="n">
-        <v>-89.43095870000001</v>
+        <v>114.1796935</v>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>886b76b05d362fdc</t>
+          <t>ce4ae0a91b9988f7</t>
         </is>
       </c>
     </row>
     <row r="30" ht="26" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Assistant / Associate Professor of Industrial and Systems Engineering</t>
+          <t>Assistant/Associate Professor of Civil Engineering (Transportation)</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>University of Washington</t>
+          <t>Trine University</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Industrial &amp; Systems Engineering</t>
+          <t>Reiners Department of Civil and Environmental Engineering</t>
         </is>
       </c>
       <c r="D30" s="3" t="n">
@@ -3318,12 +3317,12 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Assistant Professor position in Systems Engineering that aligns with the candidate's expertise in AI-enabled systems and smart mobility through the lens of cyber-physical and autonomous systems.</t>
+          <t>This is a broad Civil Engineering assistant/associate professor position at a teaching-focused institution where transportation engineering is explicitly listed as a primary teaching and curricular requirement.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Systems Engineering, Autonomous Systems, Cyber-Physical Systems, AI-Enabled Systems Engineering</t>
+          <t>Transportation Engineering, Undergraduate Engineering Education, Geographic Information Systems (GIS), Civil Engineering Curriculum</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
@@ -3333,47 +3332,43 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Angola, IN</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>Priority: 2026-09-15 / Open until filled</t>
-        </is>
-      </c>
-      <c r="J30" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>$12,000 – $17,000 per month (9-month service period)</t>
+          <t>Based on qualifications</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>The Department of Industrial and Systems Engineering at the University of Washington seeks an Assistant or Associate Professor specializing in Systems Engineering, requiring a Ph.D. in Systems Engineering, Industrial Engineering, or a related discipline. | Research Topics: Systems Engineering, Autonomous Systems, Cyber-Physical Systems, AI-Enabled Systems Engineering</t>
+          <t>Trine University seeks a full-time Assistant or Associate Professor of Civil Engineering with a specialization in transportation to teach undergraduate courses, engage students in applied projects, and support program accreditation, requiring a Ph.D. in Civil Engineering or a closely related field. | Research Topics: Transportation Engineering, Undergraduate Engineering Education, Geographic Information Systems (GIS), Civil Engineering Curriculum</t>
         </is>
       </c>
       <c r="M30" s="6" t="inlineStr">
         <is>
-          <t>https://engineering.academickeys.com/job/g4m97a60/AssistantAssociate-Professor-Industrial-and-Systems-Engineering-Systems-Engineering-Focus</t>
+          <t>https://jobs.chronicle.com/job/38028401/assistant-associate-professor-civil-engineering-transportation-/</t>
         </is>
       </c>
       <c r="N30" s="5" t="inlineStr">
         <is>
-          <t>AcademicKeys</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Q30" s="7" t="inlineStr">
@@ -3382,44 +3377,44 @@
         </is>
       </c>
       <c r="R30" s="2" t="n">
-        <v>47.6553</v>
+        <v>41.6311141</v>
       </c>
       <c r="S30" s="2" t="n">
-        <v>-122.3035</v>
+        <v>-85.0105982</v>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>9d5682cf4dbca334</t>
+          <t>9f9cc58aa59ccd96</t>
         </is>
       </c>
     </row>
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Tenure-Track Assistant/Associate Professor of Air Transportation Systems</t>
+          <t>Faculty Position in Civil Engineering (Transportation and Traffic Engineering)</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Embry-Riddle Aeronautical University</t>
+          <t>University of New Brunswick</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>School of Graduate Studies, College of Aviation</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>3</v>
+          <t>Faculty of Engineering</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>The position focuses specifically on air transportation systems, advanced air mobility, and aviation, which falls outside the candidate's core background in ground-based transportation engineering and public transit planning.</t>
+          <t>This is a broad Civil Engineering faculty position that explicitly covers traffic engineering and transportation operations, aligning with the candidate's core subfield.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Air Transportation Systems, Advanced Air Mobility, UAS Traffic Management, Machine Learning/AI in Aviation</t>
+          <t>Traffic studies and analysis, Traffic control devices, Intersections and interchanges operations, Traffic accident studies</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -3429,47 +3424,43 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL</t>
+          <t>Fredericton, New Brunswick</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>Priority: 2026-08-31 / Open until filled</t>
-        </is>
-      </c>
-      <c r="J31" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>Competitive Salary</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>Embry-Riddle Aeronautical University seeks a tenure-track faculty member in air transportation systems and advanced air mobility requiring a doctorate and relevant experience. | Research Topics: Air Transportation Systems, Advanced Air Mobility, UAS Traffic Management, Machine Learning/AI in Aviation</t>
+          <t>The University of New Brunswick seeks a faculty member in Civil Engineering specializing in traffic characteristics, traffic studies, and intersection operations, requiring a Master's or Ph.D. in Civil Engineering or a closely related area. | Research Topics: Traffic studies and analysis, Traffic control devices, Intersections and interchanges operations, Traffic accident studies</t>
         </is>
       </c>
       <c r="M31" s="6" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38012134/tenure-track-faculty-position-with-a-focus-on-air-transportation-systems-daytona-beach-campus/</t>
+          <t>https://ca.linkedin.com/jobs/view/engineering-faculty-of-at-university-of-new-brunswick-4451582209</t>
         </is>
       </c>
       <c r="N31" s="5" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="Q31" s="7" t="inlineStr">
@@ -3478,44 +3469,44 @@
         </is>
       </c>
       <c r="R31" s="2" t="n">
-        <v>29.1895</v>
+        <v>45.9455202</v>
       </c>
       <c r="S31" s="2" t="n">
-        <v>-81.04940000000001</v>
+        <v>-66.64018609999999</v>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>52969a207999417a</t>
+          <t>77b43c5491345e72</t>
         </is>
       </c>
     </row>
     <row r="32" ht="26" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Transportation Engineering</t>
+          <t>Assistant/Associate Professor of Civil, Architectural and Environmental Engineering</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>South Dakota State University</t>
+          <t>Missouri University of Science and Technology</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Department of Civil and Environmental Engineering</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="n">
-        <v>9</v>
+          <t>Department of Civil, Architectural and Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>This is a tenure-track Assistant Professor position in Transportation Engineering within a Civil and Environmental Engineering department, perfectly aligning with the candidate's core research profile.</t>
+          <t>This is a general Civil, Architectural and Environmental Engineering faculty opening without an explicitly stated specialization in transportation engineering or transit planning.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Intelligent Transportation Systems, Transportation Data Analytics, Traffic Operations, Resilient Transportation Systems</t>
+          <t>Civil Engineering, Architectural Engineering, Environmental Engineering</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
@@ -3525,80 +3516,76 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Brookings, SD</t>
+          <t>Rolla, MO</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="J32" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>Starting at $92,000</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>South Dakota State University seeks a tenure-track Assistant Professor in Transportation Engineering to teach undergraduate and graduate courses, advise students, and develop an externally funded research program requiring a Ph.D. in Civil Engineering or a closely related field. | Research Topics: Intelligent Transportation Systems, Transportation Data Analytics, Traffic Operations, Resilient Transportation Systems</t>
+          <t>Missouri University of Science and Technology invites applications for an Assistant or Associate Professor position in Civil, Architectural, and Environmental Engineering requiring a relevant doctoral degree. | Research Topics: Civil Engineering, Architectural Engineering, Environmental Engineering</t>
         </is>
       </c>
       <c r="M32" s="6" t="inlineStr">
         <is>
-          <t>https://engineering.academickeys.com/job/m4lk5asr/Assistant-Professor-of-Transportation-Engineering</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-associate-professor-civil-architectural-and-environmental-engineering-%2300096512-at-missouri-university-of-science-and-technology-4442271248</t>
         </is>
       </c>
       <c r="N32" s="5" t="inlineStr">
         <is>
-          <t>AcademicKeys</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="Q32" s="9" t="inlineStr">
-        <is>
-          <t>Past Due</t>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="Q32" s="7" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
       <c r="R32" s="2" t="n">
-        <v>44.344449</v>
+        <v>37.9532435</v>
       </c>
       <c r="S32" s="2" t="n">
-        <v>-96.79823709999999</v>
+        <v>-91.7742667</v>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>9b7d5de4753a514b</t>
+          <t>4fad8c46021c1243</t>
         </is>
       </c>
     </row>
     <row r="33" ht="26" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Clinical Assistant Professor</t>
+          <t>Assistant Professor of Public Policy</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Georgia State University</t>
+          <t>University of Texas at Arlington</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Department of Public Management and Policy</t>
+          <t>Department of Public Affairs &amp; Planning</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
@@ -3606,172 +3593,736 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>This is a non-tenure-track clinical position in public management and policy focusing on teaching data analytics and urban planning, which is a poor fit for a candidate targeting research-active tenure-track positions in transportation engineering.</t>
+          <t>The position is for an Assistant Professor of Public Policy in a public affairs department, which falls outside the candidate's core expertise in transportation engineering, travel behavior, and mobility systems.</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Policy Analytics, Urban Planning, Data Visualization, GIS Applications</t>
+          <t>Public Policy, Urban Studies, Public Infrastructure, Public Administration</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Non-Tenure Track</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Arlington, TX</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="J33" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>$80,000-$90,000</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>A non-tenure-track clinical assistant professor position focusing on teaching policy analytics, urban planning, and GIS, requiring a Ph.D. in a related field and university teaching experience. | Research Topics: Policy Analytics, Urban Planning, Data Visualization, GIS Applications</t>
+          <t>The University of Texas at Arlington seeks a tenure-track Assistant Professor of Public Policy in the Department of Public Affairs and Planning requiring a Ph.D. in public policy or a related social science discipline. | Research Topics: Public Policy, Urban Studies, Public Infrastructure, Public Administration</t>
         </is>
       </c>
       <c r="M33" s="6" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38022215/clinical-assistant-professor-non-tenure-tack/</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-at-excel-campus-activities-4464851831</t>
         </is>
       </c>
       <c r="N33" s="5" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="Q33" s="9" t="inlineStr">
-        <is>
-          <t>Past Due</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Q33" s="7" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
       <c r="R33" s="2" t="n">
-        <v>33.7535889</v>
+        <v>32.7315155</v>
       </c>
       <c r="S33" s="2" t="n">
-        <v>-84.3854209</v>
+        <v>-97.1171533</v>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>f39f14cbaaf9d6f7</t>
+          <t>15704bb25858281c</t>
         </is>
       </c>
     </row>
     <row r="34" ht="26" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>Assistant Professor in Supply Chain Management</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Iowa State University</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Department of Supply Chain Management, Ivy College of Business</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>This is a business school position focused on supply chain management rather than transportation engineering or urban mobility systems.</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Management, Logistics, Operations</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>Tenure-Track</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Ames, IA</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>Iowa State University seeks a tenure-track Assistant Professor in Supply Chain Management to conduct research and teach courses at the undergraduate, master's, and Ph.D. levels, requiring a doctorate in business administration, supply chain, transportation, logistics, operations, or a related field. | Research Topics: Supply Chain Management, Logistics, Operations</t>
+        </is>
+      </c>
+      <c r="M34" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-in-supply-chain-management-at-iowa-state-university-ivy-college-of-business-4440811209</t>
+        </is>
+      </c>
+      <c r="N34" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Q34" s="7" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="n">
+        <v>42.0267567</v>
+      </c>
+      <c r="S34" s="2" t="n">
+        <v>-93.6170448</v>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>e994e392d38b77ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="26" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Assistant/Associate/Full Professor in Industrial and Systems Engineering</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>University of Florida</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Department of Industrial and Systems Engineering</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Although transportation is mentioned as a potential application area, the primary focus of this Industrial and Systems Engineering position is on Industrialized Construction and 3D construction printing rather than core transportation engineering, mobility, or travel behavior.</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Industrialized Construction, Artificial Intelligence, Digital Twins, Operations Research</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Tenure-Track</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Gainesville, FL</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>Salary is commensurate with education and experience.</t>
+        </is>
+      </c>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>This full-time tenured or tenure-track faculty position in Industrial and Systems Engineering at the University of Florida seeks expertise in industrialized construction and related technologies, requiring a Ph.D. in ISE, Manufacturing Engineering, Civil Engineering, Mechanical Engineering, or a closely related field. | Research Topics: Industrialized Construction, Artificial Intelligence, Digital Twins, Operations Research</t>
+        </is>
+      </c>
+      <c r="M35" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/assistant-associate-full-professor-industrial-systems-engineering-at-university-of-florida-4323668785</t>
+        </is>
+      </c>
+      <c r="N35" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Q35" s="7" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="n">
+        <v>29.6436</v>
+      </c>
+      <c r="S35" s="2" t="n">
+        <v>-82.3549</v>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>56d501f448e77e05</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="26" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Assistant / Associate Professor of Industrial and Systems Engineering</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>University of Washington</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Industrial &amp; Systems Engineering</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>Assistant Professor position in Systems Engineering that aligns with the candidate's expertise in AI-enabled systems and smart mobility through the lens of cyber-physical and autonomous systems.</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Systems Engineering, Autonomous Systems, Cyber-Physical Systems, AI-Enabled Systems Engineering</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>Tenure-Track</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>Priority: 2026-09-15 / Open until filled</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>$12,000 – $17,000 per month (9-month service period)</t>
+        </is>
+      </c>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>The Department of Industrial and Systems Engineering at the University of Washington seeks an Assistant or Associate Professor specializing in Systems Engineering, requiring a Ph.D. in Systems Engineering, Industrial Engineering, or a related discipline. | Research Topics: Systems Engineering, Autonomous Systems, Cyber-Physical Systems, AI-Enabled Systems Engineering</t>
+        </is>
+      </c>
+      <c r="M36" s="6" t="inlineStr">
+        <is>
+          <t>https://engineering.academickeys.com/job/g4m97a60/AssistantAssociate-Professor-Industrial-and-Systems-Engineering-Systems-Engineering-Focus</t>
+        </is>
+      </c>
+      <c r="N36" s="5" t="inlineStr">
+        <is>
+          <t>AcademicKeys</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Q36" s="7" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="n">
+        <v>47.6553</v>
+      </c>
+      <c r="S36" s="2" t="n">
+        <v>-122.3035</v>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>9d5682cf4dbca334</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="26" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Tenure-Track Assistant/Associate Professor of Air Transportation Systems</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Embry-Riddle Aeronautical University</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>School of Graduate Studies, College of Aviation</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>The position focuses specifically on air transportation systems, advanced air mobility, and aviation, which falls outside the candidate's core background in ground-based transportation engineering and public transit planning.</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Air Transportation Systems, Advanced Air Mobility, UAS Traffic Management, Machine Learning/AI in Aviation</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Tenure-Track</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Daytona Beach, FL</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>Priority: 2026-08-31 / Open until filled</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>Competitive Salary</t>
+        </is>
+      </c>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>Embry-Riddle Aeronautical University seeks a tenure-track faculty member in air transportation systems and advanced air mobility requiring a doctorate and relevant experience. | Research Topics: Air Transportation Systems, Advanced Air Mobility, UAS Traffic Management, Machine Learning/AI in Aviation</t>
+        </is>
+      </c>
+      <c r="M37" s="6" t="inlineStr">
+        <is>
+          <t>https://jobs.chronicle.com/job/38012134/tenure-track-faculty-position-with-a-focus-on-air-transportation-systems-daytona-beach-campus/</t>
+        </is>
+      </c>
+      <c r="N37" s="5" t="inlineStr">
+        <is>
+          <t>Chronicle</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Q37" s="7" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="n">
+        <v>29.1895</v>
+      </c>
+      <c r="S37" s="2" t="n">
+        <v>-81.04940000000001</v>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>52969a207999417a</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="26" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Transportation Engineering</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>South Dakota State University</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Department of Civil and Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>This is a tenure-track Assistant Professor position in Transportation Engineering within a Civil and Environmental Engineering department, perfectly aligning with the candidate's core research profile.</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Intelligent Transportation Systems, Transportation Data Analytics, Traffic Operations, Resilient Transportation Systems</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>Tenure-Track</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Brookings, SD</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>Starting at $92,000</t>
+        </is>
+      </c>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>South Dakota State University seeks a tenure-track Assistant Professor in Transportation Engineering to teach undergraduate and graduate courses, advise students, and develop an externally funded research program requiring a Ph.D. in Civil Engineering or a closely related field. | Research Topics: Intelligent Transportation Systems, Transportation Data Analytics, Traffic Operations, Resilient Transportation Systems</t>
+        </is>
+      </c>
+      <c r="M38" s="6" t="inlineStr">
+        <is>
+          <t>https://engineering.academickeys.com/job/m4lk5asr/Assistant-Professor-of-Transportation-Engineering</t>
+        </is>
+      </c>
+      <c r="N38" s="5" t="inlineStr">
+        <is>
+          <t>AcademicKeys</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Q38" s="9" t="inlineStr">
+        <is>
+          <t>Past Due</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="n">
+        <v>44.344449</v>
+      </c>
+      <c r="S38" s="2" t="n">
+        <v>-96.79823709999999</v>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>9b7d5de4753a514b</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="26" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Clinical Assistant Professor</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Georgia State University</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Department of Public Management and Policy</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>This is a non-tenure-track clinical position in public management and policy focusing on teaching data analytics and urban planning, which is a poor fit for a candidate targeting research-active tenure-track positions in transportation engineering.</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Policy Analytics, Urban Planning, Data Visualization, GIS Applications</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>Non-Tenure Track</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>$80,000-$90,000</t>
+        </is>
+      </c>
+      <c r="L39" s="4" t="inlineStr">
+        <is>
+          <t>A non-tenure-track clinical assistant professor position focusing on teaching policy analytics, urban planning, and GIS, requiring a Ph.D. in a related field and university teaching experience. | Research Topics: Policy Analytics, Urban Planning, Data Visualization, GIS Applications</t>
+        </is>
+      </c>
+      <c r="M39" s="6" t="inlineStr">
+        <is>
+          <t>https://jobs.chronicle.com/job/38022215/clinical-assistant-professor-non-tenure-tack/</t>
+        </is>
+      </c>
+      <c r="N39" s="5" t="inlineStr">
+        <is>
+          <t>Chronicle</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Q39" s="9" t="inlineStr">
+        <is>
+          <t>Past Due</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="n">
+        <v>33.7535889</v>
+      </c>
+      <c r="S39" s="2" t="n">
+        <v>-84.3854209</v>
+      </c>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>f39f14cbaaf9d6f7</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="26" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
           <t>Assistant Professor in Transportation Policy</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>Hunter College</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>Department of Urban Policy and Planning</t>
         </is>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="E40" s="4" t="inlineStr">
         <is>
           <t>Strong interdisciplinary fit for an Assistant Professor position focusing on transportation policy and planning within an urban policy department.</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Transportation Policy, Transportation Advocacy &amp; Accessibility, Community-Engaged Research, Urban Planning</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>Tenure-Track</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
       </c>
-      <c r="I34" s="5" t="inlineStr">
+      <c r="I40" s="5" t="inlineStr">
         <is>
           <t>Open until filled</t>
         </is>
       </c>
-      <c r="J34" s="5" t="inlineStr">
+      <c r="J40" s="5" t="inlineStr">
         <is>
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="K40" s="2" t="inlineStr">
         <is>
           <t>$77,092 - $91,922</t>
         </is>
       </c>
-      <c r="L34" s="4" t="inlineStr">
+      <c r="L40" s="4" t="inlineStr">
         <is>
           <t>Hunter College seeks a tenure-track Assistant Professor in transportation policy to teach graduate students and conduct community-engaged research, requiring a Ph.D. in policy, planning, or a related field specializing in transportation. | Research Topics: Transportation Policy, Transportation Advocacy &amp; Accessibility, Community-Engaged Research, Urban Planning</t>
         </is>
       </c>
-      <c r="M34" s="6" t="inlineStr">
+      <c r="M40" s="6" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/assistant-professor-%E2%80%93-urban-policy-and-planning-dept-school-of-arts-and-sciences-hunter-college-at-hunter-college-4438624127</t>
         </is>
       </c>
-      <c r="N34" s="5" t="inlineStr">
+      <c r="N40" s="5" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="O34" s="2" t="inlineStr">
+      <c r="O40" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="P34" s="2" t="inlineStr">
+      <c r="P40" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
       </c>
-      <c r="Q34" s="7" t="inlineStr">
+      <c r="Q40" s="7" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="R34" s="2" t="n">
+      <c r="R40" s="2" t="n">
         <v>40.7683107</v>
       </c>
-      <c r="S34" s="2" t="n">
+      <c r="S40" s="2" t="n">
         <v>-73.964406</v>
       </c>
-      <c r="T34" s="2" t="inlineStr">
+      <c r="T40" s="2" t="inlineStr">
         <is>
           <t>e4e18ed629103a27</t>
         </is>
@@ -3812,6 +4363,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId39"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T40"/>
+  <dimension ref="A1:T41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -525,7 +525,7 @@
     <col width="95" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="32" customWidth="1" min="5" max="5"/>
-    <col width="137" customWidth="1" min="6" max="6"/>
+    <col width="138" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="29" customWidth="1" min="8" max="8"/>
     <col width="50" customWidth="1" min="9" max="9"/>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q8" s="7" t="inlineStr">
@@ -1648,7 +1648,11 @@
           <t>2026-10-25</t>
         </is>
       </c>
-      <c r="J12" s="5" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
           <t>$100,000 - $200,000 per year</t>
@@ -1676,7 +1680,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q12" s="7" t="inlineStr">
@@ -1772,7 +1776,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q13" s="7" t="inlineStr">
@@ -2252,7 +2256,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q18" s="7" t="inlineStr">
@@ -2348,7 +2352,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q19" s="7" t="inlineStr">
@@ -2632,7 +2636,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q22" s="7" t="inlineStr">
@@ -2816,7 +2820,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q24" s="7" t="inlineStr">
@@ -3023,17 +3027,17 @@
     <row r="27" ht="26" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor / Associate Professor (Tenure-Track) in Civil and Environmental Engineering</t>
+          <t>Assistant Professor / Associate Professor in Civil and Environmental Engineering</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Nanyang Technological University</t>
+          <t>Nanyang Technological University Singapore</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>School of Civil and Environmental Engineering, College of Engineering</t>
+          <t>School of Civil and Environmental Engineering</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
@@ -3041,12 +3045,12 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>This is an open-rank Civil and Environmental Engineering search at a top international university where transportation is one of several potential engineering domains.</t>
+          <t>This is an open-rank faculty search in Civil and Environmental Engineering where transportation is a potential fit among broader infrastructure domains.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Civil and Environmental Engineering, Geospatial Technologies, Infrastructure Systems</t>
+          <t>Civil Engineering, Geospatial Technologies, Digital Construction, Infrastructure Systems</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -3056,7 +3060,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Singapore, Singapore</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
@@ -3072,27 +3076,27 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>Nanyang Technological University seeks tenure-track faculty across areas of civil and environmental engineering requiring a Ph.D. in a related field. | Research Topics: Civil and Environmental Engineering, Geospatial Technologies, Infrastructure Systems</t>
+          <t>Nanyang Technological University seeks tenure-track faculty across all areas of Civil and Environmental Engineering requiring a Ph.D. in a relevant field. | Research Topics: Civil Engineering, Geospatial Technologies, Digital Construction, Infrastructure Systems</t>
         </is>
       </c>
       <c r="M27" s="6" t="inlineStr">
         <is>
-          <t>https://engineering.academickeys.com/job/dhzin0q4/Assistant-Professor--Associate-Professor-TenureTrack-in-Civil-and-Environmental-Engineering</t>
+          <t>https://sg.linkedin.com/jobs/view/assistant-professor-associate-professor-tenure-track-in-civil-and-environmental-engineering-at-nanyang-technological-university-singapore-4432357834</t>
         </is>
       </c>
       <c r="N27" s="5" t="inlineStr">
         <is>
-          <t>AcademicKeys</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q27" s="7" t="inlineStr">
@@ -3101,31 +3105,31 @@
         </is>
       </c>
       <c r="R27" s="2" t="n">
-        <v>1.3484104</v>
+        <v>1.3483</v>
       </c>
       <c r="S27" s="2" t="n">
-        <v>103.6829332</v>
+        <v>103.6831</v>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>3fa57c30724444e8</t>
+          <t>ce5f34eaef46b041</t>
         </is>
       </c>
     </row>
     <row r="28" ht="26" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor / Associate Professor in Civil and Environmental Engineering</t>
+          <t>Assistant/Associate Professor of Civil Engineering (Transportation)</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Nanyang Technological University Singapore</t>
+          <t>Trine University</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>School of Civil and Environmental Engineering</t>
+          <t>Reiners Department of Civil and Environmental Engineering</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
@@ -3133,12 +3137,12 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>This is an open-rank faculty search in Civil and Environmental Engineering where transportation is a potential fit among broader infrastructure domains.</t>
+          <t>This is a broad Civil Engineering assistant/associate professor position at a teaching-focused institution where transportation engineering is explicitly listed as a primary teaching and curricular requirement.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Civil Engineering, Geospatial Technologies, Digital Construction, Infrastructure Systems</t>
+          <t>Transportation Engineering, Undergraduate Engineering Education, Geographic Information Systems (GIS), Civil Engineering Curriculum</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
@@ -3148,7 +3152,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Singapore, Singapore</t>
+          <t>Angola, IN</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
@@ -3159,32 +3163,32 @@
       <c r="J28" s="5" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Highly competitive</t>
+          <t>Based on qualifications</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>Nanyang Technological University seeks tenure-track faculty across all areas of Civil and Environmental Engineering requiring a Ph.D. in a relevant field. | Research Topics: Civil Engineering, Geospatial Technologies, Digital Construction, Infrastructure Systems</t>
+          <t>Trine University seeks a full-time Assistant or Associate Professor of Civil Engineering with a specialization in transportation to teach undergraduate courses, engage students in applied projects, and support program accreditation, requiring a Ph.D. in Civil Engineering or a closely related field. | Research Topics: Transportation Engineering, Undergraduate Engineering Education, Geographic Information Systems (GIS), Civil Engineering Curriculum</t>
         </is>
       </c>
       <c r="M28" s="6" t="inlineStr">
         <is>
-          <t>https://sg.linkedin.com/jobs/view/assistant-professor-associate-professor-tenure-track-in-civil-and-environmental-engineering-at-nanyang-technological-university-singapore-4432357834</t>
+          <t>https://jobs.chronicle.com/job/38028401/assistant-associate-professor-civil-engineering-transportation-/</t>
         </is>
       </c>
       <c r="N28" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Q28" s="7" t="inlineStr">
@@ -3193,31 +3197,31 @@
         </is>
       </c>
       <c r="R28" s="2" t="n">
-        <v>1.3483</v>
+        <v>41.6311141</v>
       </c>
       <c r="S28" s="2" t="n">
-        <v>103.6831</v>
+        <v>-85.0105982</v>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>ce5f34eaef46b041</t>
+          <t>9f9cc58aa59ccd96</t>
         </is>
       </c>
     </row>
     <row r="29" ht="26" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor in Low-Altitude Economy</t>
+          <t>Faculty Position in Civil Engineering (Transportation and Traffic Engineering)</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>The Hong Kong Polytechnic University</t>
+          <t>University of New Brunswick</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Faculty of Engineering</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
@@ -3225,12 +3229,12 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>The position focuses on the low-altitude economy, which aligns with advanced mobility and transportation systems, though it is based in Europe despite the institution being in Hong Kong.</t>
+          <t>This is a broad Civil Engineering faculty position that explicitly covers traffic engineering and transportation operations, aligning with the candidate's core subfield.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Low-Altitude Economy, Advanced Air Mobility, Transportation Systems, Mobility Management</t>
+          <t>Traffic studies and analysis, Traffic control devices, Intersections and interchanges operations, Traffic accident studies</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -3240,7 +3244,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Fredericton, New Brunswick</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
@@ -3256,17 +3260,17 @@
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>This tenure-track Assistant Professor position focuses on research and teaching within the low-altitude economy and advanced mobility sectors, requiring a relevant doctoral degree. | Research Topics: Low-Altitude Economy, Advanced Air Mobility, Transportation Systems, Mobility Management</t>
+          <t>The University of New Brunswick seeks a faculty member in Civil Engineering specializing in traffic characteristics, traffic studies, and intersection operations, requiring a Master's or Ph.D. in Civil Engineering or a closely related area. | Research Topics: Traffic studies and analysis, Traffic control devices, Intersections and interchanges operations, Traffic accident studies</t>
         </is>
       </c>
       <c r="M29" s="6" t="inlineStr">
         <is>
-          <t>https://www.jobs.ac.uk/job/DSJ402/assistant-professor-in-low-altitude-economy</t>
+          <t>https://ca.linkedin.com/jobs/view/engineering-faculty-of-at-university-of-new-brunswick-4451582209</t>
         </is>
       </c>
       <c r="N29" s="5" t="inlineStr">
         <is>
-          <t>Jobs.ac.uk</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -3276,7 +3280,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q29" s="7" t="inlineStr">
@@ -3285,44 +3289,44 @@
         </is>
       </c>
       <c r="R29" s="2" t="n">
-        <v>22.3044867</v>
+        <v>45.9455202</v>
       </c>
       <c r="S29" s="2" t="n">
-        <v>114.1796935</v>
+        <v>-66.64018609999999</v>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>ce4ae0a91b9988f7</t>
+          <t>77b43c5491345e72</t>
         </is>
       </c>
     </row>
     <row r="30" ht="26" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Assistant/Associate Professor of Civil Engineering (Transportation)</t>
+          <t>Assistant/Associate Professor of Civil, Architectural and Environmental Engineering</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Trine University</t>
+          <t>Missouri University of Science and Technology</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Reiners Department of Civil and Environmental Engineering</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="n">
-        <v>6</v>
+          <t>Department of Civil, Architectural and Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>This is a broad Civil Engineering assistant/associate professor position at a teaching-focused institution where transportation engineering is explicitly listed as a primary teaching and curricular requirement.</t>
+          <t>This is a general Civil, Architectural and Environmental Engineering faculty opening without an explicitly stated specialization in transportation engineering or transit planning.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Transportation Engineering, Undergraduate Engineering Education, Geographic Information Systems (GIS), Civil Engineering Curriculum</t>
+          <t>Civil Engineering, Architectural Engineering, Environmental Engineering</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
@@ -3332,7 +3336,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Angola, IN</t>
+          <t>Rolla, MO</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
@@ -3343,32 +3347,32 @@
       <c r="J30" s="5" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>Based on qualifications</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>Trine University seeks a full-time Assistant or Associate Professor of Civil Engineering with a specialization in transportation to teach undergraduate courses, engage students in applied projects, and support program accreditation, requiring a Ph.D. in Civil Engineering or a closely related field. | Research Topics: Transportation Engineering, Undergraduate Engineering Education, Geographic Information Systems (GIS), Civil Engineering Curriculum</t>
+          <t>Missouri University of Science and Technology invites applications for an Assistant or Associate Professor position in Civil, Architectural, and Environmental Engineering requiring a relevant doctoral degree. | Research Topics: Civil Engineering, Architectural Engineering, Environmental Engineering</t>
         </is>
       </c>
       <c r="M30" s="6" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38028401/assistant-associate-professor-civil-engineering-transportation-/</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-associate-professor-civil-architectural-and-environmental-engineering-%2300096512-at-missouri-university-of-science-and-technology-4442271248</t>
         </is>
       </c>
       <c r="N30" s="5" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q30" s="7" t="inlineStr">
@@ -3377,44 +3381,44 @@
         </is>
       </c>
       <c r="R30" s="2" t="n">
-        <v>41.6311141</v>
+        <v>37.9532435</v>
       </c>
       <c r="S30" s="2" t="n">
-        <v>-85.0105982</v>
+        <v>-91.7742667</v>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>9f9cc58aa59ccd96</t>
+          <t>4fad8c46021c1243</t>
         </is>
       </c>
     </row>
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Faculty Position in Civil Engineering (Transportation and Traffic Engineering)</t>
+          <t>Assistant Professor of Public Policy</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>University of New Brunswick</t>
+          <t>University of Texas at Arlington</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Faculty of Engineering</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="n">
-        <v>6</v>
+          <t>Department of Public Affairs &amp; Planning</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>This is a broad Civil Engineering faculty position that explicitly covers traffic engineering and transportation operations, aligning with the candidate's core subfield.</t>
+          <t>The position is for an Assistant Professor of Public Policy in a public affairs department, which falls outside the candidate's core expertise in transportation engineering, travel behavior, and mobility systems.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Traffic studies and analysis, Traffic control devices, Intersections and interchanges operations, Traffic accident studies</t>
+          <t>Public Policy, Urban Studies, Public Infrastructure, Public Administration</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -3424,7 +3428,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Fredericton, New Brunswick</t>
+          <t>Arlington, TX</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
@@ -3440,12 +3444,12 @@
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>The University of New Brunswick seeks a faculty member in Civil Engineering specializing in traffic characteristics, traffic studies, and intersection operations, requiring a Master's or Ph.D. in Civil Engineering or a closely related area. | Research Topics: Traffic studies and analysis, Traffic control devices, Intersections and interchanges operations, Traffic accident studies</t>
+          <t>The University of Texas at Arlington seeks a tenure-track Assistant Professor of Public Policy in the Department of Public Affairs and Planning requiring a Ph.D. in public policy or a related social science discipline. | Research Topics: Public Policy, Urban Studies, Public Infrastructure, Public Administration</t>
         </is>
       </c>
       <c r="M31" s="6" t="inlineStr">
         <is>
-          <t>https://ca.linkedin.com/jobs/view/engineering-faculty-of-at-university-of-new-brunswick-4451582209</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-at-excel-campus-activities-4464851831</t>
         </is>
       </c>
       <c r="N31" s="5" t="inlineStr">
@@ -3455,12 +3459,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="Q31" s="7" t="inlineStr">
@@ -3469,44 +3473,44 @@
         </is>
       </c>
       <c r="R31" s="2" t="n">
-        <v>45.9455202</v>
+        <v>32.7315155</v>
       </c>
       <c r="S31" s="2" t="n">
-        <v>-66.64018609999999</v>
+        <v>-97.1171533</v>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>77b43c5491345e72</t>
+          <t>15704bb25858281c</t>
         </is>
       </c>
     </row>
     <row r="32" ht="26" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Assistant/Associate Professor of Civil, Architectural and Environmental Engineering</t>
+          <t>Assistant Professor in Supply Chain Management</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Missouri University of Science and Technology</t>
+          <t>Iowa State University</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Department of Civil, Architectural and Environmental Engineering</t>
+          <t>Department of Supply Chain Management, Ivy College of Business</t>
         </is>
       </c>
       <c r="D32" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>This is a general Civil, Architectural and Environmental Engineering faculty opening without an explicitly stated specialization in transportation engineering or transit planning.</t>
+          <t>This is a business school position focused on supply chain management rather than transportation engineering or urban mobility systems.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Civil Engineering, Architectural Engineering, Environmental Engineering</t>
+          <t>Supply Chain Management, Logistics, Operations</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
@@ -3516,7 +3520,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Rolla, MO</t>
+          <t>Ames, IA</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
@@ -3532,12 +3536,12 @@
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>Missouri University of Science and Technology invites applications for an Assistant or Associate Professor position in Civil, Architectural, and Environmental Engineering requiring a relevant doctoral degree. | Research Topics: Civil Engineering, Architectural Engineering, Environmental Engineering</t>
+          <t>Iowa State University seeks a tenure-track Assistant Professor in Supply Chain Management to conduct research and teach courses at the undergraduate, master's, and Ph.D. levels, requiring a doctorate in business administration, supply chain, transportation, logistics, operations, or a related field. | Research Topics: Supply Chain Management, Logistics, Operations</t>
         </is>
       </c>
       <c r="M32" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-associate-professor-civil-architectural-and-environmental-engineering-%2300096512-at-missouri-university-of-science-and-technology-4442271248</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-in-supply-chain-management-at-iowa-state-university-ivy-college-of-business-4440811209</t>
         </is>
       </c>
       <c r="N32" s="5" t="inlineStr">
@@ -3547,12 +3551,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="Q32" s="7" t="inlineStr">
@@ -3561,44 +3565,44 @@
         </is>
       </c>
       <c r="R32" s="2" t="n">
-        <v>37.9532435</v>
+        <v>42.0267567</v>
       </c>
       <c r="S32" s="2" t="n">
-        <v>-91.7742667</v>
+        <v>-93.6170448</v>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4fad8c46021c1243</t>
+          <t>e994e392d38b77ce</t>
         </is>
       </c>
     </row>
     <row r="33" ht="26" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Public Policy</t>
+          <t>Assistant Professor / Associate Professor (Tenure-Track) in Maritime Studies</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>University of Texas at Arlington</t>
+          <t>Nanyang Technological University</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Department of Public Affairs &amp; Planning</t>
+          <t>School of Civil and Environmental Engineering</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>The position is for an Assistant Professor of Public Policy in a public affairs department, which falls outside the candidate's core expertise in transportation engineering, travel behavior, and mobility systems.</t>
+          <t>While housed in the School of Civil and Environmental Engineering, this position specifically targets Maritime Studies, shipping decarbonization, and port logistics, diverging from the candidate's core expertise in urban public transit and travel behavior modeling.</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Public Policy, Urban Studies, Public Infrastructure, Public Administration</t>
+          <t>Sustainable Shipping and Decarbonization, Port Operations and Logistics, Maritime Economics and Digitalisation, Supply Chain Resilience</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -3608,7 +3612,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Arlington, TX</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
@@ -3624,12 +3628,12 @@
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>The University of Texas at Arlington seeks a tenure-track Assistant Professor of Public Policy in the Department of Public Affairs and Planning requiring a Ph.D. in public policy or a related social science discipline. | Research Topics: Public Policy, Urban Studies, Public Infrastructure, Public Administration</t>
+          <t>Nanyang Technological University seeks tenure-track faculty at all ranks in Maritime Studies within the School of Civil and Environmental Engineering, requiring a Ph.D. in Maritime Studies or a closely related field. | Research Topics: Sustainable Shipping and Decarbonization, Port Operations and Logistics, Maritime Economics and Digitalisation, Supply Chain Resilience</t>
         </is>
       </c>
       <c r="M33" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-at-excel-campus-activities-4464851831</t>
+          <t>https://sg.linkedin.com/jobs/view/assistant-professor-associate-professor-tenure-track-associate-professor-practice-track-in-maritime-studies-at-nanyang-technological-university-singapore-4432368242</t>
         </is>
       </c>
       <c r="N33" s="5" t="inlineStr">
@@ -3639,12 +3643,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q33" s="7" t="inlineStr">
@@ -3653,31 +3657,31 @@
         </is>
       </c>
       <c r="R33" s="2" t="n">
-        <v>32.7315155</v>
+        <v>1.3483</v>
       </c>
       <c r="S33" s="2" t="n">
-        <v>-97.1171533</v>
+        <v>103.6831</v>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>15704bb25858281c</t>
+          <t>1e0a7536f9329af5</t>
         </is>
       </c>
     </row>
     <row r="34" ht="26" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor in Supply Chain Management</t>
+          <t>Faculty Openings in Engineering (Open Rank)</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Iowa State University</t>
+          <t>Singapore Institute of Technology</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Department of Supply Chain Management, Ivy College of Business</t>
+          <t>Engineering Cluster</t>
         </is>
       </c>
       <c r="D34" s="5" t="n">
@@ -3685,22 +3689,22 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>This is a business school position focused on supply chain management rather than transportation engineering or urban mobility systems.</t>
+          <t>While open rank and located in target Singapore, the engineering openings focus on construction materials, tunneling, infrastructure asset maintenance, and power systems rather than transportation planning or travel demand modeling.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Management, Logistics, Operations</t>
+          <t>Transport Infrastructure Asset Management, Tunnel Engineering, Construction Technologies, Power and Systems Engineering</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Unspecified</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Ames, IA</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
@@ -3716,12 +3720,12 @@
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>Iowa State University seeks a tenure-track Assistant Professor in Supply Chain Management to conduct research and teach courses at the undergraduate, master's, and Ph.D. levels, requiring a doctorate in business administration, supply chain, transportation, logistics, operations, or a related field. | Research Topics: Supply Chain Management, Logistics, Operations</t>
+          <t>Singapore Institute of Technology is seeking faculty at all ranks across civil, electrical, mechanical, and systems engineering disciplines to support applied learning and translational industry research. | Research Topics: Transport Infrastructure Asset Management, Tunnel Engineering, Construction Technologies, Power and Systems Engineering</t>
         </is>
       </c>
       <c r="M34" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-in-supply-chain-management-at-iowa-state-university-ivy-college-of-business-4440811209</t>
+          <t>https://sg.linkedin.com/jobs/view/faculty-openings-in-engineering-at-singapore-institute-of-technology-4273859333</t>
         </is>
       </c>
       <c r="N34" s="5" t="inlineStr">
@@ -3731,12 +3735,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q34" s="7" t="inlineStr">
@@ -3745,14 +3749,14 @@
         </is>
       </c>
       <c r="R34" s="2" t="n">
-        <v>42.0267567</v>
+        <v>1.4123197</v>
       </c>
       <c r="S34" s="2" t="n">
-        <v>-93.6170448</v>
+        <v>103.9094621</v>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>e994e392d38b77ce</t>
+          <t>f21dc0b6a181929c</t>
         </is>
       </c>
     </row>
@@ -4325,6 +4329,98 @@
       <c r="T40" s="2" t="inlineStr">
         <is>
           <t>e4e18ed629103a27</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="26" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Full/Associate/Assistant Professor in Modern Civil Engineering</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>University of Macau</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Department of Civil and Environmental Engineering (CEE)</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>The posting is an open-rank faculty search in modern civil engineering which may encompass transportation, but lacks sufficient departmental subfield details in the short snippet.</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Modern Civil Engineering, Transportation Engineering, Urban Systems</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Macao</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>£87,465.51 to £127,834.20 starting salary</t>
+        </is>
+      </c>
+      <c r="L41" s="4" t="inlineStr">
+        <is>
+          <t>The University of Macau seeks a faculty member in modern civil engineering within the Department of Civil and Environmental Engineering. | Research Topics: Modern Civil Engineering, Transportation Engineering, Urban Systems</t>
+        </is>
+      </c>
+      <c r="M41" s="6" t="inlineStr">
+        <is>
+          <t>https://www.jobs.ac.uk/job/DSL575/full-associate-assistant-professor-in-modern-civil-engineering</t>
+        </is>
+      </c>
+      <c r="N41" s="5" t="inlineStr">
+        <is>
+          <t>Jobs.ac.uk</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Q41" s="7" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="n">
+        <v>22.1285</v>
+      </c>
+      <c r="S41" s="2" t="n">
+        <v>113.5438</v>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>600dff84e8f0a0b2</t>
         </is>
       </c>
     </row>
@@ -4369,6 +4465,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T41"/>
+  <dimension ref="A1:T42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -935,30 +935,30 @@
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Tenure-track Assistant Professor – AI for Automotive and Mobility Systems</t>
+          <t>Assistant Professor of Civil, Construction and Environmental Engineering (Transportation Engineering Domain)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>The Ohio State University</t>
+          <t>University of Alabama</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Department of Mechanical and Aerospace Engineering</t>
+          <t>Department of Civil, Construction and Environmental Engineering</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>This is a strong interdisciplinary Assistant Professor search in Mechanical Engineering focusing on AI for ground transportation and mobility systems, aligning with Dr. Baek's expertise in travel behavior, machine learning, and smart urban mobility.</t>
+          <t>This is an open-rank Civil, Construction and Environmental Engineering faculty position where Transportation Engineering is explicitly listed as one of the target domain areas.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Artificial Intelligence for Mobility, Ground Transportation Systems, Machine Learning Applications, Intelligent Transportation Systems</t>
+          <t>Transportation Engineering, Network Analysis / Data Science, Connected and Autonomous Vehicles, Multimodal Transportation Planning</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Columbus, OH</t>
+          <t>Tuscaloosa, AL</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -988,12 +988,12 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>The Department of Mechanical and Aerospace Engineering at The Ohio State University invites applications for a tenure-track Assistant Professor position focusing on artificial intelligence and machine learning for ground transportation and mobility systems, requiring a doctorate by May 2027. | Research Topics: Artificial Intelligence for Mobility, Ground Transportation Systems, Machine Learning Applications, Intelligent Transportation Systems</t>
+          <t>The University of Alabama seeks a tenure-track Assistant Professor in Transportation Engineering within the Department of Civil, Construction and Environmental Engineering, requiring an earned Ph.D. in a closely related discipline. | Research Topics: Transportation Engineering, Network Analysis / Data Science, Connected and Autonomous Vehicles, Multimodal Transportation Planning</t>
         </is>
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
-          <t>https://engineering.academickeys.com/job/vd0ur9k4/Tenuretrack-Assistant-Professor--AI-for-Automotive-and-Mobility-Systems</t>
+          <t>https://engineering.academickeys.com/job/02ixzgls/Civil-Construction-and-Environmental-Engineering--Assistant-Professor</t>
         </is>
       </c>
       <c r="N5" s="5" t="inlineStr">
@@ -1017,44 +1017,44 @@
         </is>
       </c>
       <c r="R5" s="2" t="n">
-        <v>40.0067</v>
+        <v>33.2120822</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>-83.0305</v>
+        <v>-87.53967350000001</v>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>dd476bd66d0aeb1e</t>
+          <t>f80ad2336a210f82</t>
         </is>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Civil, Construction and Environmental Engineering (Transportation Engineering Domain)</t>
+          <t>Assistant Professor of Industrial and Systems Engineering</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>University of Alabama</t>
+          <t>University of Tennessee, Knoxville</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Department of Civil, Construction and Environmental Engineering</t>
+          <t>Department of Industrial and Systems Engineering (ISE)</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>This is an open-rank Civil, Construction and Environmental Engineering faculty position where Transportation Engineering is explicitly listed as one of the target domain areas.</t>
+          <t>The position is a tenure-track Assistant Professor role in Industrial and Systems Engineering with stated departmental strengths in logistics, transportation, data analytics, and machine learning, aligning well with the candidate's quantitative and optimization background.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Transportation Engineering, Network Analysis / Data Science, Connected and Autonomous Vehicles, Multimodal Transportation Planning</t>
+          <t>Logistics and Transportation, Data Analytics and Machine Learning, Optimization, Supply Chain</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -1064,17 +1064,17 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Tuscaloosa, AL</t>
+          <t>Knoxville, TN</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>Priority: 2026-10-01 / Final: Open until filled</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1084,27 +1084,27 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>The University of Alabama seeks a tenure-track Assistant Professor in Transportation Engineering within the Department of Civil, Construction and Environmental Engineering, requiring an earned Ph.D. in a closely related discipline. | Research Topics: Transportation Engineering, Network Analysis / Data Science, Connected and Autonomous Vehicles, Multimodal Transportation Planning</t>
+          <t>The University of Tennessee, Knoxville seeks a tenure-track Assistant Professor in Industrial and Systems Engineering requiring a Ph.D. in Industrial Engineering, Systems Engineering, Operations Research, or a closely related field. | Research Topics: Logistics and Transportation, Data Analytics and Machine Learning, Optimization, Supply Chain</t>
         </is>
       </c>
       <c r="M6" s="6" t="inlineStr">
         <is>
-          <t>https://engineering.academickeys.com/job/02ixzgls/Civil-Construction-and-Environmental-Engineering--Assistant-Professor</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179545449&amp;Title=Tenure%2DTrack%20Assistant%20Professor%20of%20Industrial%20and%20Systems%20Engineering%2C%20Fall%202027%20%281%2F3%29</t>
         </is>
       </c>
       <c r="N6" s="5" t="inlineStr">
         <is>
-          <t>AcademicKeys</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="Q6" s="7" t="inlineStr">
@@ -1113,31 +1113,31 @@
         </is>
       </c>
       <c r="R6" s="2" t="n">
-        <v>33.2120822</v>
+        <v>35.9516352</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>-87.53967350000001</v>
+        <v>-83.9308819</v>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>f80ad2336a210f82</t>
+          <t>ecd34777430b7c8d</t>
         </is>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Industrial and Systems Engineering</t>
+          <t>Assistant Professor in Regional and Urban Planning</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>University of Tennessee, Knoxville</t>
+          <t>University College Dublin</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Department of Industrial and Systems Engineering (ISE)</t>
+          <t>UCD School of Architecture, Planning and Environmental Policy</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>The position is a tenure-track Assistant Professor role in Industrial and Systems Engineering with stated departmental strengths in logistics, transportation, data analytics, and machine learning, aligning well with the candidate's quantitative and optimization background.</t>
+          <t>This Assistant Professor position in Regional and Urban Planning aligns well with the candidate's B.S. and M.S. background in Urban Planning.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Logistics and Transportation, Data Analytics and Machine Learning, Optimization, Supply Chain</t>
+          <t>Regional and Urban Planning, Urban Systems, Spatial Planning</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -1160,47 +1160,47 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Knoxville, TN</t>
+          <t>Dublin, Ireland</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>£57,454.37 to £90,980.66 per annum</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>The University of Tennessee, Knoxville seeks a tenure-track Assistant Professor in Industrial and Systems Engineering requiring a Ph.D. in Industrial Engineering, Systems Engineering, Operations Research, or a closely related field. | Research Topics: Logistics and Transportation, Data Analytics and Machine Learning, Optimization, Supply Chain</t>
+          <t>This is an Assistant Professor role in regional and urban planning at University College Dublin requiring relevant graduate qualifications. | Research Topics: Regional and Urban Planning, Urban Systems, Spatial Planning</t>
         </is>
       </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179545449&amp;Title=Tenure%2DTrack%20Assistant%20Professor%20of%20Industrial%20and%20Systems%20Engineering%2C%20Fall%202027%20%281%2F3%29</t>
+          <t>https://www.jobs.ac.uk/job/DSY140/assistant-professor-in-regional-and-urban-planning</t>
         </is>
       </c>
       <c r="N7" s="5" t="inlineStr">
         <is>
-          <t>HigherEdJobs</t>
+          <t>Jobs.ac.uk</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q7" s="7" t="inlineStr">
@@ -1209,44 +1209,44 @@
         </is>
       </c>
       <c r="R7" s="2" t="n">
-        <v>35.9516352</v>
+        <v>53.3082</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>-83.9308819</v>
+        <v>-6.2238</v>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>ecd34777430b7c8d</t>
+          <t>d042d0e38cf2b00a</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor in Regional and Urban Planning</t>
+          <t>Assistant Professor of Data Analytics</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>University College Dublin</t>
+          <t>Ohio Wesleyan University</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>UCD School of Architecture, Planning and Environmental Policy</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>7</v>
+          <t>Data Analytics Program</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>This Assistant Professor position in Regional and Urban Planning aligns well with the candidate's B.S. and M.S. background in Urban Planning.</t>
+          <t>While data analytics aligns with the candidate's quantitative skills, this liberal arts data analytics position lacks a specific focus on transportation engineering, urban mobility, or civil systems.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Regional and Urban Planning, Urban Systems, Spatial Planning</t>
+          <t>Data Analytics, Interdisciplinary Data Science, Big Data Ethics, Data Visualization</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -1256,47 +1256,47 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Dublin, Ireland</t>
+          <t>Delaware, OH</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>£57,454.37 to £90,980.66 per annum</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>This is an Assistant Professor role in regional and urban planning at University College Dublin requiring relevant graduate qualifications. | Research Topics: Regional and Urban Planning, Urban Systems, Spatial Planning</t>
+          <t>Ohio Wesleyan University seeks a tenure-track Assistant Professor of Data Analytics to teach undergraduate courses, advise students, and maintain an active research agenda requiring a Ph.D. or Master's degree in analytics, data science, or a related field. | Research Topics: Data Analytics, Interdisciplinary Data Science, Big Data Ethics, Data Visualization</t>
         </is>
       </c>
       <c r="M8" s="6" t="inlineStr">
         <is>
-          <t>https://www.jobs.ac.uk/job/DSY140/assistant-professor-in-regional-and-urban-planning</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179549847&amp;Title=Assistant%20Professor%20of%20Data%20Analytics</t>
         </is>
       </c>
       <c r="N8" s="5" t="inlineStr">
         <is>
-          <t>Jobs.ac.uk</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="Q8" s="7" t="inlineStr">
@@ -1305,31 +1305,31 @@
         </is>
       </c>
       <c r="R8" s="2" t="n">
-        <v>53.3082</v>
+        <v>40.292858</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>-6.2238</v>
+        <v>-83.0642763</v>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>d042d0e38cf2b00a</t>
+          <t>99e733f7138cdcde</t>
         </is>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Data Analytics</t>
+          <t>Tenure-Track Professor of Land Use and Resilience (Open Rank)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Ohio Wesleyan University</t>
+          <t>University of Michigan</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Data Analytics Program</t>
+          <t>Urban and Regional Planning Program, Taubman College of Architecture and Urban Planning</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>While data analytics aligns with the candidate's quantitative skills, this liberal arts data analytics position lacks a specific focus on transportation engineering, urban mobility, or civil systems.</t>
+          <t>While the candidate has a background in urban planning, this position focuses specifically on land use and climate resilience planning rather than the candidate's core expertise in transportation engineering, transit planning, or travel behavior.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Data Analytics, Interdisciplinary Data Science, Big Data Ethics, Data Visualization</t>
+          <t>Land Use Planning, Climate Resilience, Urban and Regional Planning, Environmental Disparities</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -1352,17 +1352,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Delaware, OH</t>
+          <t>Ann Arbor, MI</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1372,27 +1372,27 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>Ohio Wesleyan University seeks a tenure-track Assistant Professor of Data Analytics to teach undergraduate courses, advise students, and maintain an active research agenda requiring a Ph.D. or Master's degree in analytics, data science, or a related field. | Research Topics: Data Analytics, Interdisciplinary Data Science, Big Data Ethics, Data Visualization</t>
+          <t>The University of Michigan seeks an open-rank tenure-track faculty member in land use and resilience planning within the Urban and Regional Planning Program, requiring a terminal degree in planning or a related discipline. | Research Topics: Land Use Planning, Climate Resilience, Urban and Regional Planning, Environmental Disparities</t>
         </is>
       </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179549847&amp;Title=Assistant%20Professor%20of%20Data%20Analytics</t>
+          <t>https://www.linkedin.com/jobs/view/tenure-track-professor-of-land-use-and-resilience-open-rank-at-university-of-michigan-4422103936</t>
         </is>
       </c>
       <c r="N9" s="5" t="inlineStr">
         <is>
-          <t>HigherEdJobs</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="Q9" s="7" t="inlineStr">
@@ -1401,44 +1401,44 @@
         </is>
       </c>
       <c r="R9" s="2" t="n">
-        <v>40.292858</v>
+        <v>42.278</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>-83.0642763</v>
+        <v>-83.73820000000001</v>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>99e733f7138cdcde</t>
+          <t>6d685e6e729ffedd</t>
         </is>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Tenure-Track Professor of Land Use and Resilience (Open Rank)</t>
+          <t>Assistant/Associate Professor of Public Administration &amp; MPA Coordinator</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>University of Michigan</t>
+          <t>University of New Orleans</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Urban and Regional Planning Program, Taubman College of Architecture and Urban Planning</t>
+          <t>Department of Political Science / Division of Planning and Public Affairs</t>
         </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>While the candidate has a background in urban planning, this position focuses specifically on land use and climate resilience planning rather than the candidate's core expertise in transportation engineering, transit planning, or travel behavior.</t>
+          <t>The position is for an Assistant/Associate Professor of Public Administration and MPA Coordinator in a political science and public affairs division, which does not align with the candidate's core transportation engineering and travel behavior research profile.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Land Use Planning, Climate Resilience, Urban and Regional Planning, Environmental Disparities</t>
+          <t>Public Administration, Public Policy, Nonprofit Management, Emergency Management</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -1448,17 +1448,17 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI</t>
+          <t>New Orleans, LA</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>Priority: 2026-10-19 / Final: Open until filled</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>The University of Michigan seeks an open-rank tenure-track faculty member in land use and resilience planning within the Urban and Regional Planning Program, requiring a terminal degree in planning or a related discipline. | Research Topics: Land Use Planning, Climate Resilience, Urban and Regional Planning, Environmental Disparities</t>
+          <t>The Department of Political Science seeks a tenure-track Assistant or Associate Professor of Public Administration to teach graduate MPA courses, serve as Program Coordinator, and maintain an active research agenda requiring a Ph.D. in Public Administration, Political Science, or a closely related field. | Research Topics: Public Administration, Public Policy, Nonprofit Management, Emergency Management</t>
         </is>
       </c>
       <c r="M10" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/tenure-track-professor-of-land-use-and-resilience-open-rank-at-university-of-michigan-4422103936</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-associate-professor-public-administration-master-of-public-administration-coordinator-at-uno-transportation-institute-4466545068</t>
         </is>
       </c>
       <c r="N10" s="5" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="Q10" s="7" t="inlineStr">
@@ -1497,44 +1497,44 @@
         </is>
       </c>
       <c r="R10" s="2" t="n">
-        <v>42.278</v>
+        <v>29.9561422</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>-83.73820000000001</v>
+        <v>-90.0733934</v>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6d685e6e729ffedd</t>
+          <t>0bd357a7efab4a73</t>
         </is>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Assistant/Associate Professor of Public Administration &amp; MPA Coordinator</t>
+          <t>Assistant Professor (Tenure-Track)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>University of New Orleans</t>
+          <t>Johns Hopkins University</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Department of Political Science / Division of Planning and Public Affairs</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>3</v>
+          <t>School of Government and Policy</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>7</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>The position is for an Assistant/Associate Professor of Public Administration and MPA Coordinator in a political science and public affairs division, which does not align with the candidate's core transportation engineering and travel behavior research profile.</t>
+          <t>Strong interdisciplinary fit as JHU's new School of Government and Policy explicitly solicits candidates with civil engineering and urban planning backgrounds working on transportation and land use, smart city innovation, and AI governance.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Public Administration, Public Policy, Nonprofit Management, Emergency Management</t>
+          <t>Transportation and Land Use, Urban Innovation and State Capacity, Frontier AI in Government, Public-Sector Technology Adoption</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1544,47 +1544,47 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>New Orleans, LA</t>
+          <t>Washington, DC</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>Priority: 2026-10-19 / Final: Open until filled</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>$100,000 - $200,000 per year</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>The Department of Political Science seeks a tenure-track Assistant or Associate Professor of Public Administration to teach graduate MPA courses, serve as Program Coordinator, and maintain an active research agenda requiring a Ph.D. in Public Administration, Political Science, or a closely related field. | Research Topics: Public Administration, Public Policy, Nonprofit Management, Emergency Management</t>
+          <t>Johns Hopkins University seeks multiple tenure-track Assistant Professors in civil engineering, urban planning, and related fields with research interests in transportation, land use, and AI policy, requiring a Ph.D. or J.D. by the start date. | Research Topics: Transportation and Land Use, Urban Innovation and State Capacity, Frontier AI in Government, Public-Sector Technology Adoption</t>
         </is>
       </c>
       <c r="M11" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-associate-professor-public-administration-master-of-public-administration-coordinator-at-uno-transportation-institute-4466545068</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179560444&amp;Title=Assistant%20Professor</t>
         </is>
       </c>
       <c r="N11" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q11" s="7" t="inlineStr">
@@ -1593,44 +1593,44 @@
         </is>
       </c>
       <c r="R11" s="2" t="n">
-        <v>29.9561422</v>
+        <v>38.9086858</v>
       </c>
       <c r="S11" s="2" t="n">
-        <v>-90.0733934</v>
+        <v>-77.0395355</v>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>0bd357a7efab4a73</t>
+          <t>3e8b915493d9b1ef</t>
         </is>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor (Tenure-Track)</t>
+          <t>Assistant Professor of Urban Economics</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Johns Hopkins University</t>
+          <t>Harvard University</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>School of Government and Policy</t>
+          <t>Harvard Kennedy School of Government</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Strong interdisciplinary fit as JHU's new School of Government and Policy explicitly solicits candidates with civil engineering and urban planning backgrounds working on transportation and land use, smart city innovation, and AI governance.</t>
+          <t>While transportation is listed among the acceptable research areas, this is an urban economics position in a public policy school preferring junior economists rather than a core engineering or mobility planning appointment.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Transportation and Land Use, Urban Innovation and State Capacity, Frontier AI in Government, Public-Sector Technology Adoption</t>
+          <t>Urban Economics, Housing, Transportation, Infrastructure</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1640,47 +1640,47 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Washington, DC</t>
+          <t>Cambridge, MA</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>$100,000 - $200,000 per year</t>
+          <t>165k - 185k</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>Johns Hopkins University seeks multiple tenure-track Assistant Professors in civil engineering, urban planning, and related fields with research interests in transportation, land use, and AI policy, requiring a Ph.D. or J.D. by the start date. | Research Topics: Transportation and Land Use, Urban Innovation and State Capacity, Frontier AI in Government, Public-Sector Technology Adoption</t>
+          <t>The Harvard Kennedy School seeks a junior economist to study urban issues including housing, transportation, and infrastructure, requiring a Ph.D. by June 2027. | Research Topics: Urban Economics, Housing, Transportation, Infrastructure</t>
         </is>
       </c>
       <c r="M12" s="6" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179560444&amp;Title=Assistant%20Professor</t>
+          <t>https://jobs.chronicle.com/job/38032116/assistant-professor-urban-economics-/</t>
         </is>
       </c>
       <c r="N12" s="5" t="inlineStr">
         <is>
-          <t>HigherEdJobs</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q12" s="7" t="inlineStr">
@@ -1689,44 +1689,44 @@
         </is>
       </c>
       <c r="R12" s="2" t="n">
-        <v>38.9086858</v>
+        <v>42.3657432</v>
       </c>
       <c r="S12" s="2" t="n">
-        <v>-77.0395355</v>
+        <v>-71.12221390000001</v>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3e8b915493d9b1ef</t>
+          <t>93251b0fa8170f49</t>
         </is>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Urban Economics</t>
+          <t>Assistant or Associate Professor in Supply Chain Management</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Harvard University</t>
+          <t>University of Arkansas</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Harvard Kennedy School of Government</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>5</v>
+          <t>J.B. Hunt Transport Department of Supply Chain Management, Sam M. Walton College of Business</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>While transportation is listed among the acceptable research areas, this is an urban economics position in a public policy school preferring junior economists rather than a core engineering or mobility planning appointment.</t>
+          <t>This is a tenure-track position in Supply Chain Management housed within a business school, which has limited overlap with the candidate's core transportation engineering and travel behavior profile.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Urban Economics, Housing, Transportation, Infrastructure</t>
+          <t>Supply Chain Management, Logistics, Operations and Business Research</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Cambridge, MA</t>
+          <t>Fayetteville, AR</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -1751,32 +1751,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>165k - 185k</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>The Harvard Kennedy School seeks a junior economist to study urban issues including housing, transportation, and infrastructure, requiring a Ph.D. by June 2027. | Research Topics: Urban Economics, Housing, Transportation, Infrastructure</t>
+          <t>The University of Arkansas invites applications for a tenure-track Assistant or Associate Professor in Supply Chain Management starting in August 2027. | Research Topics: Supply Chain Management, Logistics, Operations and Business Research</t>
         </is>
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38032116/assistant-professor-urban-economics-/</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-or-associate-professor-open-rank-at-university-of-arkansas-%C2%AD-sam-m-walton-college-of-business-4460111187</t>
         </is>
       </c>
       <c r="N13" s="5" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="Q13" s="7" t="inlineStr">
@@ -1785,31 +1785,31 @@
         </is>
       </c>
       <c r="R13" s="2" t="n">
-        <v>42.3657432</v>
+        <v>36.0970389</v>
       </c>
       <c r="S13" s="2" t="n">
-        <v>-71.12221390000001</v>
+        <v>-94.1703322</v>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>93251b0fa8170f49</t>
+          <t>c16a694d5f7f68d4</t>
         </is>
       </c>
     </row>
     <row r="14" ht="26" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Assistant or Associate Professor in Supply Chain Management</t>
+          <t>Assistant Professor of Teaching of Urban Planning</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>University of Arkansas</t>
+          <t>University of California, Los Angeles (UCLA)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>J.B. Hunt Transport Department of Supply Chain Management, Sam M. Walton College of Business</t>
+          <t>Department of Urban Planning, Luskin School of Public Affairs</t>
         </is>
       </c>
       <c r="D14" s="5" t="n">
@@ -1817,62 +1817,62 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>This is a tenure-track position in Supply Chain Management housed within a business school, which has limited overlap with the candidate's core transportation engineering and travel behavior profile.</t>
+          <t>While located in an urban planning department, the role specifically requires teaching and research focused primarily on contexts outside of North America (e.g., Asia, the Middle East, or Africa) for a Master of Global Public Affairs program, which does not align with the candidate's core profile.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Management, Logistics, Operations and Business Research</t>
+          <t>Global Public Affairs, Comparative Urbanization, International Policy Analysis</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Non-Tenure Track</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Fayetteville, AR</t>
+          <t>Los Angeles, CA</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
           <t>2026-11-01</t>
         </is>
       </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>2026-11-01</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>DOE</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>The University of Arkansas invites applications for a tenure-track Assistant or Associate Professor in Supply Chain Management starting in August 2027. | Research Topics: Supply Chain Management, Logistics, Operations and Business Research</t>
+          <t>UCLA seeks an Assistant Professor of Teaching in Urban Planning primarily focused on global public affairs and contexts outside North America, requiring a policy-relevant research agenda and master's/undergraduate instruction. | Research Topics: Global Public Affairs, Comparative Urbanization, International Policy Analysis</t>
         </is>
       </c>
       <c r="M14" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-or-associate-professor-open-rank-at-university-of-arkansas-%C2%AD-sam-m-walton-college-of-business-4460111187</t>
+          <t>https://jobs.chronicle.com/job/38020965/assistant-professor-of-teaching-of-urban-planning/</t>
         </is>
       </c>
       <c r="N14" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Q14" s="7" t="inlineStr">
@@ -1881,94 +1881,94 @@
         </is>
       </c>
       <c r="R14" s="2" t="n">
-        <v>36.0970389</v>
+        <v>34.0536909</v>
       </c>
       <c r="S14" s="2" t="n">
-        <v>-94.1703322</v>
+        <v>-118.242766</v>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>c16a694d5f7f68d4</t>
+          <t>fb7ba0794bd02172</t>
         </is>
       </c>
     </row>
     <row r="15" ht="26" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Teaching of Urban Planning</t>
+          <t>Professor, Associate Professor, or Assistant Professor of Industrial and Systems Engineering</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>University of California, Los Angeles (UCLA)</t>
+          <t>Auburn University</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Department of Urban Planning, Luskin School of Public Affairs</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>3</v>
+          <t>Department of Industrial &amp; Systems Engineering</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>7</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>While located in an urban planning department, the role specifically requires teaching and research focused primarily on contexts outside of North America (e.g., Asia, the Middle East, or Africa) for a Master of Global Public Affairs program, which does not align with the candidate's core profile.</t>
+          <t>Assistant Professor position in Industrial and Systems Engineering with potential interdisciplinary intersections in transportation systems and human systems integration.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Global Public Affairs, Comparative Urbanization, International Policy Analysis</t>
+          <t>Industrial and Systems Engineering, Human Systems Integration, Operations Research, Systems Engineering</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Non-Tenure Track</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Los Angeles, CA</t>
+          <t>Auburn, AL</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>Open until filled</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>DOE</t>
+          <t>$80,000 - $180,000 per year</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>UCLA seeks an Assistant Professor of Teaching in Urban Planning primarily focused on global public affairs and contexts outside North America, requiring a policy-relevant research agenda and master's/undergraduate instruction. | Research Topics: Global Public Affairs, Comparative Urbanization, International Policy Analysis</t>
+          <t>An open-rank tenure-track faculty position in Industrial and Systems Engineering requiring an earned doctorate in ISE or a closely related discipline, with research and teaching responsibilities spanning advanced manufacturing, operations research, human systems integration, and systems engineering. | Research Topics: Industrial and Systems Engineering, Human Systems Integration, Operations Research, Systems Engineering</t>
         </is>
       </c>
       <c r="M15" s="6" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38020965/assistant-professor-of-teaching-of-urban-planning/</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179548357&amp;Title=Professor%2C%20Associate%20Professor%2C%20Assistant%20Professor%20%2D%20Industrial%20and%20Systems%20Engineering</t>
         </is>
       </c>
       <c r="N15" s="5" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="Q15" s="7" t="inlineStr">
@@ -1977,44 +1977,44 @@
         </is>
       </c>
       <c r="R15" s="2" t="n">
-        <v>34.0536909</v>
+        <v>32.5919529</v>
       </c>
       <c r="S15" s="2" t="n">
-        <v>-118.242766</v>
+        <v>-85.4959775</v>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>fb7ba0794bd02172</t>
+          <t>d0f23a527bf71c22</t>
         </is>
       </c>
     </row>
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Professor, Associate Professor, or Assistant Professor of Industrial and Systems Engineering</t>
+          <t>Assistant Professor of Civil Engineering (Transportation Engineering)</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Auburn University</t>
+          <t>The College of New Jersey</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Department of Industrial &amp; Systems Engineering</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>7</v>
+          <t>Department of Civil Engineering</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>10</v>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Assistant Professor position in Industrial and Systems Engineering with potential interdisciplinary intersections in transportation systems and human systems integration.</t>
+          <t>This tenure-track Assistant Professor position in Transportation Engineering is a dedicated core match for the candidate's background in transportation systems analysis, travel behavior, and transit planning.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Industrial and Systems Engineering, Human Systems Integration, Operations Research, Systems Engineering</t>
+          <t>Transportation Systems Analysis, Transportation Planning, Traffic Operations, Intelligent Transportation Systems</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -2024,32 +2024,32 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Auburn, AL</t>
+          <t>Ewing, NJ</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>$80,000 - $180,000 per year</t>
+          <t>$108,433.95 - $116,469.62 per year</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>An open-rank tenure-track faculty position in Industrial and Systems Engineering requiring an earned doctorate in ISE or a closely related discipline, with research and teaching responsibilities spanning advanced manufacturing, operations research, human systems integration, and systems engineering. | Research Topics: Industrial and Systems Engineering, Human Systems Integration, Operations Research, Systems Engineering</t>
+          <t>The College of New Jersey seeks a tenure-track Assistant Professor in Transportation Engineering to teach undergraduate coursework, advise senior design projects, and establish an active scholarly research program, requiring an earned doctorate in Civil Engineering or a closely related field. | Research Topics: Transportation Systems Analysis, Transportation Planning, Traffic Operations, Intelligent Transportation Systems</t>
         </is>
       </c>
       <c r="M16" s="6" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179548357&amp;Title=Professor%2C%20Associate%20Professor%2C%20Assistant%20Professor%20%2D%20Industrial%20and%20Systems%20Engineering</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179559500&amp;Title=Assistant%20Professor%2DCivil%20Engineering</t>
         </is>
       </c>
       <c r="N16" s="5" t="inlineStr">
@@ -2059,12 +2059,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q16" s="7" t="inlineStr">
@@ -2073,44 +2073,44 @@
         </is>
       </c>
       <c r="R16" s="2" t="n">
-        <v>32.5919529</v>
+        <v>40.2685516</v>
       </c>
       <c r="S16" s="2" t="n">
-        <v>-85.4959775</v>
+        <v>-74.7779768</v>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>d0f23a527bf71c22</t>
+          <t>f8f163ed02e700ff</t>
         </is>
       </c>
     </row>
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Civil Engineering (Transportation Engineering)</t>
+          <t>Assistant Professor of Public Policy (Market-Based Solutions to Societal Challenges)</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>The College of New Jersey</t>
+          <t>University of Wisconsin-Madison</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Department of Civil Engineering</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="n">
-        <v>10</v>
+          <t>La Follette School of Public Affairs, College of Letters &amp; Science</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>This tenure-track Assistant Professor position in Transportation Engineering is a dedicated core match for the candidate's background in transportation systems analysis, travel behavior, and transit planning.</t>
+          <t>While transportation and infrastructure finance is listed as a potential application area, this position is centered on public policy, economics, and market-based policy design rather than transportation engineering and planning.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Transportation Systems Analysis, Transportation Planning, Traffic Operations, Intelligent Transportation Systems</t>
+          <t>Market-Based Public Policy, Transportation and Infrastructure Finance, Regulatory Policy and Microeconomics, Institutional Design</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -2120,47 +2120,47 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Ewing, NJ</t>
+          <t>Madison, WI</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>$108,433.95 - $116,469.62 per year</t>
+          <t>Negotiable</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>The College of New Jersey seeks a tenure-track Assistant Professor in Transportation Engineering to teach undergraduate coursework, advise senior design projects, and establish an active scholarly research program, requiring an earned doctorate in Civil Engineering or a closely related field. | Research Topics: Transportation Systems Analysis, Transportation Planning, Traffic Operations, Intelligent Transportation Systems</t>
+          <t>The La Follette School of Public Affairs seeks a tenure-track Assistant Professor researching market-based institutions and incentive-compatible policy design across societal challenges, requiring a Ph.D. in Public Policy, Economics, Political Science, or a related field. | Research Topics: Market-Based Public Policy, Transportation and Infrastructure Finance, Regulatory Policy and Microeconomics, Institutional Design</t>
         </is>
       </c>
       <c r="M17" s="6" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179559500&amp;Title=Assistant%20Professor%2DCivil%20Engineering</t>
+          <t>https://jobs.chronicle.com/job/38008254/assistant-professor-of-public-policy-market-based-solutions-to-societal-challenges-/</t>
         </is>
       </c>
       <c r="N17" s="5" t="inlineStr">
         <is>
-          <t>HigherEdJobs</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q17" s="7" t="inlineStr">
@@ -2169,44 +2169,44 @@
         </is>
       </c>
       <c r="R17" s="2" t="n">
-        <v>40.2685516</v>
+        <v>43.0802745</v>
       </c>
       <c r="S17" s="2" t="n">
-        <v>-74.7779768</v>
+        <v>-89.43095870000001</v>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>f8f163ed02e700ff</t>
+          <t>51857534b7308d30</t>
         </is>
       </c>
     </row>
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Public Policy (Market-Based Solutions to Societal Challenges)</t>
+          <t>Assistant Professor of Information and Decision Sciences (Supply Chain &amp; Operations Management)</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>University of Wisconsin-Madison</t>
+          <t>University of Illinois Chicago</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>La Follette School of Public Affairs, College of Letters &amp; Science</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v>3</v>
+          <t>Department of Information and Decision Sciences, College of Business Administration</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>7</v>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>While transportation and infrastructure finance is listed as a potential application area, this position is centered on public policy, economics, and market-based policy design rather than transportation engineering and planning.</t>
+          <t>Strong interdisciplinary business school fit as the position explicitly prioritizes transportation as a preferred applied research domain for operations management.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Market-Based Public Policy, Transportation and Infrastructure Finance, Regulatory Policy and Microeconomics, Institutional Design</t>
+          <t>Operations Management, Supply Chain Management, Transportation, Artificial Intelligence</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -2216,42 +2216,42 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Madison, WI</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>Priority: 2026-10-20 / Final: 2026-12-06</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Negotiable</t>
+          <t>$185,000 - $220,000 annually</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>The La Follette School of Public Affairs seeks a tenure-track Assistant Professor researching market-based institutions and incentive-compatible policy design across societal challenges, requiring a Ph.D. in Public Policy, Economics, Political Science, or a related field. | Research Topics: Market-Based Public Policy, Transportation and Infrastructure Finance, Regulatory Policy and Microeconomics, Institutional Design</t>
+          <t>This tenure-track assistant professor role in operations management seeks candidates with a Ph.D. in a related field and explicitly prefers research focused on transportation and AI-integrated supply chain management. | Research Topics: Operations Management, Supply Chain Management, Transportation, Artificial Intelligence</t>
         </is>
       </c>
       <c r="M18" s="6" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38008254/assistant-professor-of-public-policy-market-based-solutions-to-societal-challenges-/</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179552436&amp;Title=Assistant%20Professor%20%2D%20IDS%20%28Supply%20Chain%20%26%20Operations%20Management%29</t>
         </is>
       </c>
       <c r="N18" s="5" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2265,31 +2265,31 @@
         </is>
       </c>
       <c r="R18" s="2" t="n">
-        <v>43.0802745</v>
+        <v>41.8748613</v>
       </c>
       <c r="S18" s="2" t="n">
-        <v>-89.43095870000001</v>
+        <v>-87.6519866</v>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>51857534b7308d30</t>
+          <t>77e0632bd4e74eae</t>
         </is>
       </c>
     </row>
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Information and Decision Sciences (Supply Chain &amp; Operations Management)</t>
+          <t>Tenure-Track Faculty Positions in Transportation Engineering</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>University of Illinois Chicago</t>
+          <t>National Taiwan University</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Department of Information and Decision Sciences, College of Business Administration</t>
+          <t>Department of Civil Engineering</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
@@ -2297,12 +2297,12 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Strong interdisciplinary business school fit as the position explicitly prioritizes transportation as a preferred applied research domain for operations management.</t>
+          <t>This is a civil engineering faculty search at National Taiwan University that explicitly includes Public Transportation and Intelligent Transportation Systems as preferred research areas.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Operations Management, Supply Chain Management, Transportation, Artificial Intelligence</t>
+          <t>Intelligent Transportation Systems, Public Transportation, Transportation Economics</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
@@ -2312,47 +2312,47 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>Taipei, Taiwan</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>Priority: 2026-10-20 / Final: 2026-12-06</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>$185,000 - $220,000 annually</t>
+          <t>Monthly salary: NT$83,720–137,370</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>This tenure-track assistant professor role in operations management seeks candidates with a Ph.D. in a related field and explicitly prefers research focused on transportation and AI-integrated supply chain management. | Research Topics: Operations Management, Supply Chain Management, Transportation, Artificial Intelligence</t>
+          <t>National Taiwan University seeks multiple tenure-track faculty members in transportation engineering and surveying, requiring a Ph.D. and the ability to teach in English. | Research Topics: Intelligent Transportation Systems, Public Transportation, Transportation Economics</t>
         </is>
       </c>
       <c r="M19" s="6" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179552436&amp;Title=Assistant%20Professor%20%2D%20IDS%20%28Supply%20Chain%20%26%20Operations%20Management%29</t>
+          <t>https://jobs.chronicle.com/job/38034402/faculty-recruitment-announcement-department-of-civil-engineering-national-taiwan-university/</t>
         </is>
       </c>
       <c r="N19" s="5" t="inlineStr">
         <is>
-          <t>HigherEdJobs</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Q19" s="7" t="inlineStr">
@@ -2361,31 +2361,31 @@
         </is>
       </c>
       <c r="R19" s="2" t="n">
-        <v>41.8748613</v>
+        <v>25.0375198</v>
       </c>
       <c r="S19" s="2" t="n">
-        <v>-87.6519866</v>
+        <v>121.5636796</v>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>77e0632bd4e74eae</t>
+          <t>f056997ace2e1de7</t>
         </is>
       </c>
     </row>
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Tenure-Track Faculty Positions in Transportation Engineering</t>
+          <t>Lecturer in Discipline or Senior Lecturer in Discipline</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>National Taiwan University</t>
+          <t>Columbia University</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Department of Civil Engineering</t>
+          <t>Department of Industrial Engineering and Operations Research</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
@@ -2393,62 +2393,62 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>This is a civil engineering faculty search at National Taiwan University that explicitly includes Public Transportation and Intelligent Transportation Systems as preferred research areas.</t>
+          <t>This is a full-time career-track lecturer role in Industrial Engineering and Operations Research at Columbia University focused on Artificial Intelligence and data science applications, which aligns well with the candidate's strong machine learning and data-driven modeling expertise.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Intelligent Transportation Systems, Public Transportation, Transportation Economics</t>
+          <t>Artificial Intelligence, Operations Research, Data Science, Machine Learning Applications</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Non-Tenure Track</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Taipei, Taiwan</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-01-01</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-01-01</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Monthly salary: NT$83,720–137,370</t>
+          <t>Lecturer in Discipline: 106K-129K; Senior Lecturer in Discipline: 125K-162K</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>National Taiwan University seeks multiple tenure-track faculty members in transportation engineering and surveying, requiring a Ph.D. and the ability to teach in English. | Research Topics: Intelligent Transportation Systems, Public Transportation, Transportation Economics</t>
+          <t>Columbia University seeks a full-time Lecturer or Senior Lecturer in the Department of Industrial Engineering and Operations Research to teach AI and data science courses, requiring a Ph.D. in a related quantitative discipline. | Research Topics: Artificial Intelligence, Operations Research, Data Science, Machine Learning Applications</t>
         </is>
       </c>
       <c r="M20" s="6" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38034402/faculty-recruitment-announcement-department-of-civil-engineering-national-taiwan-university/</t>
+          <t>http://engineering.academickeys.com/job/arsy3jqh/Open-Rank-Lecturer-in-Discipline-or-Senior-Lecturer-in-Discipline</t>
         </is>
       </c>
       <c r="N20" s="5" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>AcademicKeys</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="Q20" s="7" t="inlineStr">
@@ -2457,94 +2457,90 @@
         </is>
       </c>
       <c r="R20" s="2" t="n">
-        <v>25.0375198</v>
+        <v>40.8077507</v>
       </c>
       <c r="S20" s="2" t="n">
-        <v>121.5636796</v>
+        <v>-73.9624901</v>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>f056997ace2e1de7</t>
+          <t>f11b4a4e74422ae3</t>
         </is>
       </c>
     </row>
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Lecturer in Discipline or Senior Lecturer in Discipline</t>
+          <t>Assistant/Associate/Full Professor, Transportation Engineering and Systems</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Columbia University</t>
+          <t>University of Cincinnati</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Department of Industrial Engineering and Operations Research</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>7</v>
+          <t>Department of Civil and Architectural Engineering and Construction Management (CAECM)</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>9</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>This is a full-time career-track lecturer role in Industrial Engineering and Operations Research at Columbia University focused on Artificial Intelligence and data science applications, which aligns well with the candidate's strong machine learning and data-driven modeling expertise.</t>
+          <t>This is a dedicated Assistant/Associate/Full Professor position in Transportation Engineering and Systems perfectly aligned with the candidate's core research profile.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Artificial Intelligence, Operations Research, Data Science, Machine Learning Applications</t>
+          <t>Transportation Engineering, Transportation Systems, Transit Planning</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Non-Tenure Track</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Cincinnati, OH</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>2027-01-01</t>
-        </is>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>2027-01-01</t>
-        </is>
-      </c>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>Lecturer in Discipline: 106K-129K; Senior Lecturer in Discipline: 125K-162K</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>Columbia University seeks a full-time Lecturer or Senior Lecturer in the Department of Industrial Engineering and Operations Research to teach AI and data science courses, requiring a Ph.D. in a related quantitative discipline. | Research Topics: Artificial Intelligence, Operations Research, Data Science, Machine Learning Applications</t>
+          <t>This role seeks a faculty member in transportation engineering and systems within an R1 urban research university setting requiring an appropriate terminal degree. | Research Topics: Transportation Engineering, Transportation Systems, Transit Planning</t>
         </is>
       </c>
       <c r="M21" s="6" t="inlineStr">
         <is>
-          <t>http://engineering.academickeys.com/job/arsy3jqh/Open-Rank-Lecturer-in-Discipline-or-Senior-Lecturer-in-Discipline</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-associate-full-professor-transportation-engineering-and-systems-at-university-of-cincinnati-4416744025</t>
         </is>
       </c>
       <c r="N21" s="5" t="inlineStr">
         <is>
-          <t>AcademicKeys</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q21" s="7" t="inlineStr">
@@ -2553,44 +2549,44 @@
         </is>
       </c>
       <c r="R21" s="2" t="n">
-        <v>40.8077507</v>
+        <v>39.1318888</v>
       </c>
       <c r="S21" s="2" t="n">
-        <v>-73.9624901</v>
+        <v>-84.51578309999999</v>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>f11b4a4e74422ae3</t>
+          <t>6aa8ab000bc6f6c0</t>
         </is>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Assistant/Associate/Full Professor, Transportation Engineering and Systems</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>University of Cincinnati</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Department of Civil and Architectural Engineering and Construction Management (CAECM)</t>
+          <t>School of City and Regional Planning</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>This is a dedicated Assistant/Associate/Full Professor position in Transportation Engineering and Systems perfectly aligned with the candidate's core research profile.</t>
+          <t>This is an Assistant Professor position within the School of City and Regional Planning, matching the candidate's background in urban planning and transportation mobility research.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Transportation Engineering, Transportation Systems, Transit Planning</t>
+          <t>Urban Planning and Spatial Analytics, Sustainable and Resilient Communities, Mobility Analytics</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -2600,7 +2596,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Cincinnati, OH</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
@@ -2616,12 +2612,12 @@
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>This role seeks a faculty member in transportation engineering and systems within an R1 urban research university setting requiring an appropriate terminal degree. | Research Topics: Transportation Engineering, Transportation Systems, Transit Planning</t>
+          <t>Georgia Institute of Technology seeks a tenure-track Assistant Professor in the School of City and Regional Planning to advance research and teaching in urban planning, spatial analytics, and sustainable communities. | Research Topics: Urban Planning and Spatial Analytics, Sustainable and Resilient Communities, Mobility Analytics</t>
         </is>
       </c>
       <c r="M22" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-associate-full-professor-transportation-engineering-and-systems-at-university-of-cincinnati-4416744025</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-at-georgia-institute-of-technology-4467296351</t>
         </is>
       </c>
       <c r="N22" s="5" t="inlineStr">
@@ -2631,12 +2627,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="Q22" s="7" t="inlineStr">
@@ -2645,54 +2641,54 @@
         </is>
       </c>
       <c r="R22" s="2" t="n">
-        <v>39.1318888</v>
+        <v>33.7756</v>
       </c>
       <c r="S22" s="2" t="n">
-        <v>-84.51578309999999</v>
+        <v>-84.3963</v>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6aa8ab000bc6f6c0</t>
+          <t>1b7278bf60327029</t>
         </is>
       </c>
     </row>
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Assistant or Associate Professor in Complex Systems and Urban &amp; Regional Modelling</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>Maastricht University</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>School of City and Regional Planning</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="n">
-        <v>8</v>
+          <t>Faculty of Science and Engineering</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>7</v>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>This is an Assistant Professor position within the School of City and Regional Planning, matching the candidate's background in urban planning and transportation mobility research.</t>
+          <t>This Assistant or Associate Professor role in complex systems and urban and regional modelling aligns well with the candidate's strong computational and urban modelling expertise.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Urban Planning and Spatial Analytics, Sustainable and Resilient Communities, Mobility Analytics</t>
+          <t>Urban and Regional Modelling, Complex Systems Theory, Urban Sustainability, Spatial Modelling</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Unspecified</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Maastricht, Netherlands</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
@@ -2708,12 +2704,12 @@
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology seeks a tenure-track Assistant Professor in the School of City and Regional Planning to advance research and teaching in urban planning, spatial analytics, and sustainable communities. | Research Topics: Urban Planning and Spatial Analytics, Sustainable and Resilient Communities, Mobility Analytics</t>
+          <t>Maastricht University seeks an Assistant or Associate Professor to build a new research line in urban and regional modelling, requiring a PhD in a relevant technical or computational field. | Research Topics: Urban and Regional Modelling, Complex Systems Theory, Urban Sustainability, Spatial Modelling</t>
         </is>
       </c>
       <c r="M23" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-at-georgia-institute-of-technology-4467296351</t>
+          <t>https://nl.linkedin.com/jobs/view/assistant-or-associate-professor-in-complex-systems-and-urban-regional-modelling-at-maastricht-university-faculty-of-science-and-engineering-4452765174</t>
         </is>
       </c>
       <c r="N23" s="5" t="inlineStr">
@@ -2723,12 +2719,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q23" s="7" t="inlineStr">
@@ -2737,31 +2733,31 @@
         </is>
       </c>
       <c r="R23" s="2" t="n">
-        <v>33.7756</v>
+        <v>50.8472117</v>
       </c>
       <c r="S23" s="2" t="n">
-        <v>-84.3963</v>
+        <v>5.6859518</v>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1b7278bf60327029</t>
+          <t>321ee686ffad2403</t>
         </is>
       </c>
     </row>
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Assistant or Associate Professor in Complex Systems and Urban &amp; Regional Modelling</t>
+          <t>Tenure-track Assistant Professor – AI for Automotive and Mobility Systems</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Maastricht University</t>
+          <t>The Ohio State University</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Faculty of Science and Engineering</t>
+          <t>Department of Mechanical Engineering</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
@@ -2769,22 +2765,22 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>This Assistant or Associate Professor role in complex systems and urban and regional modelling aligns well with the candidate's strong computational and urban modelling expertise.</t>
+          <t>The position focuses on AI and mobility systems, which aligns well with the candidate's background in machine learning applications and smart mobility, though situated within Mechanical Engineering.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Urban and Regional Modelling, Complex Systems Theory, Urban Sustainability, Spatial Modelling</t>
+          <t>AI in Transportation and Mobility, Automotive and Mobility Systems, Smart Urban Mobility, Machine Learning Applications</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Maastricht, Netherlands</t>
+          <t>Columbus, OH</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
@@ -2800,27 +2796,27 @@
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>Maastricht University seeks an Assistant or Associate Professor to build a new research line in urban and regional modelling, requiring a PhD in a relevant technical or computational field. | Research Topics: Urban and Regional Modelling, Complex Systems Theory, Urban Sustainability, Spatial Modelling</t>
+          <t>The Ohio State University invites applications for a tenure-track Assistant Professor in Mechanical Engineering specializing in AI for automotive and mobility systems, requiring a Ph.D. in a related engineering discipline. | Research Topics: AI in Transportation and Mobility, Automotive and Mobility Systems, Smart Urban Mobility, Machine Learning Applications</t>
         </is>
       </c>
       <c r="M24" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/assistant-or-associate-professor-in-complex-systems-and-urban-regional-modelling-at-maastricht-university-faculty-of-science-and-engineering-4452765174</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179558778&amp;Title=Tenure%2Dtrack%20Assistant%20Professor%20%E2%80%93%20AI%20for%20Automotive%20and%20Mobility%20Systems</t>
         </is>
       </c>
       <c r="N24" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q24" s="7" t="inlineStr">
@@ -2829,14 +2825,14 @@
         </is>
       </c>
       <c r="R24" s="2" t="n">
-        <v>50.8472117</v>
+        <v>40.0067</v>
       </c>
       <c r="S24" s="2" t="n">
-        <v>5.6859518</v>
+        <v>-83.0305</v>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>321ee686ffad2403</t>
+          <t>4e4fa974f5d3f2a4</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3092,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q27" s="7" t="inlineStr">
@@ -3280,7 +3276,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q29" s="7" t="inlineStr">
@@ -3372,7 +3368,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q30" s="7" t="inlineStr">
@@ -3648,7 +3644,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q33" s="7" t="inlineStr">
@@ -3740,7 +3736,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q34" s="7" t="inlineStr">
@@ -4376,7 +4372,11 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="J41" s="5" t="inlineStr"/>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
           <t>£87,465.51 to £127,834.20 starting salary</t>
@@ -4404,12 +4404,12 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q41" s="7" t="inlineStr">
-        <is>
-          <t>Active</t>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Q41" s="9" t="inlineStr">
+        <is>
+          <t>Past Due</t>
         </is>
       </c>
       <c r="R41" s="2" t="n">
@@ -4421,6 +4421,98 @@
       <c r="T41" s="2" t="inlineStr">
         <is>
           <t>600dff84e8f0a0b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="26" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Professor in Low-Altitude Economy</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>The Hong Kong Polytechnic University</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Department of Aeronautical and Aviation Engineering</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>Although located in Hong Kong, the position is in Aeronautical and Aviation Engineering focusing on the Low-Altitude Economy rather than traditional transportation engineering or public transit planning.</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Low-Altitude Economy, Aeronautical Engineering, Aviation Systems</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>Tenure-Track</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="L42" s="4" t="inlineStr">
+        <is>
+          <t>The role seeks an Assistant Professor in Low-Altitude Economy within the Department of Aeronautical and Aviation Engineering, requiring relevant expertise in aviation or aerospace systems. | Research Topics: Low-Altitude Economy, Aeronautical Engineering, Aviation Systems</t>
+        </is>
+      </c>
+      <c r="M42" s="6" t="inlineStr">
+        <is>
+          <t>https://www.jobs.ac.uk/job/DSJ402/assistant-professor-in-low-altitude-economy</t>
+        </is>
+      </c>
+      <c r="N42" s="5" t="inlineStr">
+        <is>
+          <t>Jobs.ac.uk</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Q42" s="7" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="n">
+        <v>22.3045</v>
+      </c>
+      <c r="S42" s="2" t="n">
+        <v>114.1797</v>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>ce4ae0a91b9988f7</t>
         </is>
       </c>
     </row>
@@ -4466,6 +4558,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId41"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T42"/>
+  <dimension ref="A1:T43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Q7" s="7" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Q11" s="7" t="inlineStr">
@@ -1607,30 +1607,30 @@
     <row r="12" ht="26" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Urban Economics</t>
+          <t>Associate Professor or DTU Tenure Track Assistant Professor in Sustainable Travel Behaviour</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Harvard University</t>
+          <t>Technical University of Denmark</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Harvard Kennedy School of Government</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>5</v>
+          <t>DTU Management</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>10</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>While transportation is listed among the acceptable research areas, this is an urban economics position in a public policy school preferring junior economists rather than a core engineering or mobility planning appointment.</t>
+          <t>The position is a direct core match for an Assistant or Associate Professor in Sustainable Travel Behaviour, perfectly aligning with the candidate's core expertise in travel behavior analysis.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Urban Economics, Housing, Transportation, Infrastructure</t>
+          <t>Sustainable Travel Behaviour, Travel Behavior Analysis, Transportation Planning</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1640,47 +1640,47 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Cambridge, MA</t>
+          <t>Lyngby, Denmark</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>165k - 185k</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>The Harvard Kennedy School seeks a junior economist to study urban issues including housing, transportation, and infrastructure, requiring a Ph.D. by June 2027. | Research Topics: Urban Economics, Housing, Transportation, Infrastructure</t>
+          <t>This faculty position at Technical University of Denmark focuses on sustainable travel behavior research and teaching within DTU Management. | Research Topics: Sustainable Travel Behaviour, Travel Behavior Analysis, Transportation Planning</t>
         </is>
       </c>
       <c r="M12" s="6" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38032116/assistant-professor-urban-economics-/</t>
+          <t>https://www.jobs.ac.uk/job/DTA266/associate-professor-or-dtu-tenure-track-assistant-professor-in-sustainable-travel-behaviour</t>
         </is>
       </c>
       <c r="N12" s="5" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>Jobs.ac.uk</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Q12" s="7" t="inlineStr">
@@ -1689,44 +1689,44 @@
         </is>
       </c>
       <c r="R12" s="2" t="n">
-        <v>42.3657432</v>
+        <v>55.7856</v>
       </c>
       <c r="S12" s="2" t="n">
-        <v>-71.12221390000001</v>
+        <v>12.5218</v>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>93251b0fa8170f49</t>
+          <t>22581fb6f9f6fea0</t>
         </is>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Assistant or Associate Professor in Supply Chain Management</t>
+          <t>Assistant Professor of Urban Economics</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>University of Arkansas</t>
+          <t>Harvard University</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>J.B. Hunt Transport Department of Supply Chain Management, Sam M. Walton College of Business</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>3</v>
+          <t>Harvard Kennedy School of Government</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>5</v>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>This is a tenure-track position in Supply Chain Management housed within a business school, which has limited overlap with the candidate's core transportation engineering and travel behavior profile.</t>
+          <t>While transportation is listed among the acceptable research areas, this is an urban economics position in a public policy school preferring junior economists rather than a core engineering or mobility planning appointment.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Management, Logistics, Operations and Business Research</t>
+          <t>Urban Economics, Housing, Transportation, Infrastructure</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Fayetteville, AR</t>
+          <t>Cambridge, MA</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -1751,32 +1751,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>165k - 185k</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>The University of Arkansas invites applications for a tenure-track Assistant or Associate Professor in Supply Chain Management starting in August 2027. | Research Topics: Supply Chain Management, Logistics, Operations and Business Research</t>
+          <t>The Harvard Kennedy School seeks a junior economist to study urban issues including housing, transportation, and infrastructure, requiring a Ph.D. by June 2027. | Research Topics: Urban Economics, Housing, Transportation, Infrastructure</t>
         </is>
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-or-associate-professor-open-rank-at-university-of-arkansas-%C2%AD-sam-m-walton-college-of-business-4460111187</t>
+          <t>https://jobs.chronicle.com/job/38032116/assistant-professor-urban-economics-/</t>
         </is>
       </c>
       <c r="N13" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Q13" s="7" t="inlineStr">
@@ -1785,31 +1785,31 @@
         </is>
       </c>
       <c r="R13" s="2" t="n">
-        <v>36.0970389</v>
+        <v>42.3657432</v>
       </c>
       <c r="S13" s="2" t="n">
-        <v>-94.1703322</v>
+        <v>-71.12221390000001</v>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>c16a694d5f7f68d4</t>
+          <t>93251b0fa8170f49</t>
         </is>
       </c>
     </row>
     <row r="14" ht="26" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Teaching of Urban Planning</t>
+          <t>Assistant or Associate Professor in Supply Chain Management</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>University of California, Los Angeles (UCLA)</t>
+          <t>University of Arkansas</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Department of Urban Planning, Luskin School of Public Affairs</t>
+          <t>J.B. Hunt Transport Department of Supply Chain Management, Sam M. Walton College of Business</t>
         </is>
       </c>
       <c r="D14" s="5" t="n">
@@ -1817,27 +1817,27 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>While located in an urban planning department, the role specifically requires teaching and research focused primarily on contexts outside of North America (e.g., Asia, the Middle East, or Africa) for a Master of Global Public Affairs program, which does not align with the candidate's core profile.</t>
+          <t>This is a tenure-track position in Supply Chain Management housed within a business school, which has limited overlap with the candidate's core transportation engineering and travel behavior profile.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Global Public Affairs, Comparative Urbanization, International Policy Analysis</t>
+          <t>Supply Chain Management, Logistics, Operations and Business Research</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Non-Tenure Track</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Los Angeles, CA</t>
+          <t>Fayetteville, AR</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>Open until filled</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
@@ -1847,32 +1847,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>DOE</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>UCLA seeks an Assistant Professor of Teaching in Urban Planning primarily focused on global public affairs and contexts outside North America, requiring a policy-relevant research agenda and master's/undergraduate instruction. | Research Topics: Global Public Affairs, Comparative Urbanization, International Policy Analysis</t>
+          <t>The University of Arkansas invites applications for a tenure-track Assistant or Associate Professor in Supply Chain Management starting in August 2027. | Research Topics: Supply Chain Management, Logistics, Operations and Business Research</t>
         </is>
       </c>
       <c r="M14" s="6" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38020965/assistant-professor-of-teaching-of-urban-planning/</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-or-associate-professor-open-rank-at-university-of-arkansas-%C2%AD-sam-m-walton-college-of-business-4460111187</t>
         </is>
       </c>
       <c r="N14" s="5" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="Q14" s="7" t="inlineStr">
@@ -1881,94 +1881,94 @@
         </is>
       </c>
       <c r="R14" s="2" t="n">
-        <v>34.0536909</v>
+        <v>36.0970389</v>
       </c>
       <c r="S14" s="2" t="n">
-        <v>-118.242766</v>
+        <v>-94.1703322</v>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>fb7ba0794bd02172</t>
+          <t>c16a694d5f7f68d4</t>
         </is>
       </c>
     </row>
     <row r="15" ht="26" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Professor, Associate Professor, or Assistant Professor of Industrial and Systems Engineering</t>
+          <t>Assistant Professor of Teaching of Urban Planning</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Auburn University</t>
+          <t>University of California, Los Angeles (UCLA)</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Department of Industrial &amp; Systems Engineering</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>7</v>
+          <t>Department of Urban Planning, Luskin School of Public Affairs</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Assistant Professor position in Industrial and Systems Engineering with potential interdisciplinary intersections in transportation systems and human systems integration.</t>
+          <t>While located in an urban planning department, the role specifically requires teaching and research focused primarily on contexts outside of North America (e.g., Asia, the Middle East, or Africa) for a Master of Global Public Affairs program, which does not align with the candidate's core profile.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Industrial and Systems Engineering, Human Systems Integration, Operations Research, Systems Engineering</t>
+          <t>Global Public Affairs, Comparative Urbanization, International Policy Analysis</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Non-Tenure Track</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Auburn, AL</t>
+          <t>Los Angeles, CA</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>Open until filled</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>$80,000 - $180,000 per year</t>
+          <t>DOE</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>An open-rank tenure-track faculty position in Industrial and Systems Engineering requiring an earned doctorate in ISE or a closely related discipline, with research and teaching responsibilities spanning advanced manufacturing, operations research, human systems integration, and systems engineering. | Research Topics: Industrial and Systems Engineering, Human Systems Integration, Operations Research, Systems Engineering</t>
+          <t>UCLA seeks an Assistant Professor of Teaching in Urban Planning primarily focused on global public affairs and contexts outside North America, requiring a policy-relevant research agenda and master's/undergraduate instruction. | Research Topics: Global Public Affairs, Comparative Urbanization, International Policy Analysis</t>
         </is>
       </c>
       <c r="M15" s="6" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179548357&amp;Title=Professor%2C%20Associate%20Professor%2C%20Assistant%20Professor%20%2D%20Industrial%20and%20Systems%20Engineering</t>
+          <t>https://jobs.chronicle.com/job/38020965/assistant-professor-of-teaching-of-urban-planning/</t>
         </is>
       </c>
       <c r="N15" s="5" t="inlineStr">
         <is>
-          <t>HigherEdJobs</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Q15" s="7" t="inlineStr">
@@ -1977,44 +1977,44 @@
         </is>
       </c>
       <c r="R15" s="2" t="n">
-        <v>32.5919529</v>
+        <v>34.0536909</v>
       </c>
       <c r="S15" s="2" t="n">
-        <v>-85.4959775</v>
+        <v>-118.242766</v>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>d0f23a527bf71c22</t>
+          <t>fb7ba0794bd02172</t>
         </is>
       </c>
     </row>
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Civil Engineering (Transportation Engineering)</t>
+          <t>Professor, Associate Professor, or Assistant Professor of Industrial and Systems Engineering</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>The College of New Jersey</t>
+          <t>Auburn University</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Department of Civil Engineering</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="n">
-        <v>10</v>
+          <t>Department of Industrial &amp; Systems Engineering</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>7</v>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>This tenure-track Assistant Professor position in Transportation Engineering is a dedicated core match for the candidate's background in transportation systems analysis, travel behavior, and transit planning.</t>
+          <t>Assistant Professor position in Industrial and Systems Engineering with potential interdisciplinary intersections in transportation systems and human systems integration.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Transportation Systems Analysis, Transportation Planning, Traffic Operations, Intelligent Transportation Systems</t>
+          <t>Industrial and Systems Engineering, Human Systems Integration, Operations Research, Systems Engineering</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -2024,32 +2024,32 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Ewing, NJ</t>
+          <t>Auburn, AL</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>$108,433.95 - $116,469.62 per year</t>
+          <t>$80,000 - $180,000 per year</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>The College of New Jersey seeks a tenure-track Assistant Professor in Transportation Engineering to teach undergraduate coursework, advise senior design projects, and establish an active scholarly research program, requiring an earned doctorate in Civil Engineering or a closely related field. | Research Topics: Transportation Systems Analysis, Transportation Planning, Traffic Operations, Intelligent Transportation Systems</t>
+          <t>An open-rank tenure-track faculty position in Industrial and Systems Engineering requiring an earned doctorate in ISE or a closely related discipline, with research and teaching responsibilities spanning advanced manufacturing, operations research, human systems integration, and systems engineering. | Research Topics: Industrial and Systems Engineering, Human Systems Integration, Operations Research, Systems Engineering</t>
         </is>
       </c>
       <c r="M16" s="6" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179559500&amp;Title=Assistant%20Professor%2DCivil%20Engineering</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179548357&amp;Title=Professor%2C%20Associate%20Professor%2C%20Assistant%20Professor%20%2D%20Industrial%20and%20Systems%20Engineering</t>
         </is>
       </c>
       <c r="N16" s="5" t="inlineStr">
@@ -2059,12 +2059,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="Q16" s="7" t="inlineStr">
@@ -2073,44 +2073,44 @@
         </is>
       </c>
       <c r="R16" s="2" t="n">
-        <v>40.2685516</v>
+        <v>32.5919529</v>
       </c>
       <c r="S16" s="2" t="n">
-        <v>-74.7779768</v>
+        <v>-85.4959775</v>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>f8f163ed02e700ff</t>
+          <t>d0f23a527bf71c22</t>
         </is>
       </c>
     </row>
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Public Policy (Market-Based Solutions to Societal Challenges)</t>
+          <t>Assistant Professor of Civil Engineering (Transportation Engineering)</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>University of Wisconsin-Madison</t>
+          <t>The College of New Jersey</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>La Follette School of Public Affairs, College of Letters &amp; Science</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>3</v>
+          <t>Department of Civil Engineering</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>10</v>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>While transportation and infrastructure finance is listed as a potential application area, this position is centered on public policy, economics, and market-based policy design rather than transportation engineering and planning.</t>
+          <t>This tenure-track Assistant Professor position in Transportation Engineering is a dedicated core match for the candidate's background in transportation systems analysis, travel behavior, and transit planning.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Market-Based Public Policy, Transportation and Infrastructure Finance, Regulatory Policy and Microeconomics, Institutional Design</t>
+          <t>Transportation Systems Analysis, Transportation Planning, Traffic Operations, Intelligent Transportation Systems</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -2120,47 +2120,47 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Madison, WI</t>
+          <t>Ewing, NJ</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Negotiable</t>
+          <t>$108,433.95 - $116,469.62 per year</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>The La Follette School of Public Affairs seeks a tenure-track Assistant Professor researching market-based institutions and incentive-compatible policy design across societal challenges, requiring a Ph.D. in Public Policy, Economics, Political Science, or a related field. | Research Topics: Market-Based Public Policy, Transportation and Infrastructure Finance, Regulatory Policy and Microeconomics, Institutional Design</t>
+          <t>The College of New Jersey seeks a tenure-track Assistant Professor in Transportation Engineering to teach undergraduate coursework, advise senior design projects, and establish an active scholarly research program, requiring an earned doctorate in Civil Engineering or a closely related field. | Research Topics: Transportation Systems Analysis, Transportation Planning, Traffic Operations, Intelligent Transportation Systems</t>
         </is>
       </c>
       <c r="M17" s="6" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38008254/assistant-professor-of-public-policy-market-based-solutions-to-societal-challenges-/</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179559500&amp;Title=Assistant%20Professor%2DCivil%20Engineering</t>
         </is>
       </c>
       <c r="N17" s="5" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Q17" s="7" t="inlineStr">
@@ -2169,44 +2169,44 @@
         </is>
       </c>
       <c r="R17" s="2" t="n">
-        <v>43.0802745</v>
+        <v>40.2685516</v>
       </c>
       <c r="S17" s="2" t="n">
-        <v>-89.43095870000001</v>
+        <v>-74.7779768</v>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>51857534b7308d30</t>
+          <t>f8f163ed02e700ff</t>
         </is>
       </c>
     </row>
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Information and Decision Sciences (Supply Chain &amp; Operations Management)</t>
+          <t>Assistant Professor of Public Policy (Market-Based Solutions to Societal Challenges)</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>University of Illinois Chicago</t>
+          <t>University of Wisconsin-Madison</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Department of Information and Decision Sciences, College of Business Administration</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>7</v>
+          <t>La Follette School of Public Affairs, College of Letters &amp; Science</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Strong interdisciplinary business school fit as the position explicitly prioritizes transportation as a preferred applied research domain for operations management.</t>
+          <t>While transportation and infrastructure finance is listed as a potential application area, this position is centered on public policy, economics, and market-based policy design rather than transportation engineering and planning.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Operations Management, Supply Chain Management, Transportation, Artificial Intelligence</t>
+          <t>Market-Based Public Policy, Transportation and Infrastructure Finance, Regulatory Policy and Microeconomics, Institutional Design</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -2216,47 +2216,47 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>Madison, WI</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>Priority: 2026-10-20 / Final: 2026-12-06</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>$185,000 - $220,000 annually</t>
+          <t>Negotiable</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>This tenure-track assistant professor role in operations management seeks candidates with a Ph.D. in a related field and explicitly prefers research focused on transportation and AI-integrated supply chain management. | Research Topics: Operations Management, Supply Chain Management, Transportation, Artificial Intelligence</t>
+          <t>The La Follette School of Public Affairs seeks a tenure-track Assistant Professor researching market-based institutions and incentive-compatible policy design across societal challenges, requiring a Ph.D. in Public Policy, Economics, Political Science, or a related field. | Research Topics: Market-Based Public Policy, Transportation and Infrastructure Finance, Regulatory Policy and Microeconomics, Institutional Design</t>
         </is>
       </c>
       <c r="M18" s="6" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179552436&amp;Title=Assistant%20Professor%20%2D%20IDS%20%28Supply%20Chain%20%26%20Operations%20Management%29</t>
+          <t>https://jobs.chronicle.com/job/38008254/assistant-professor-of-public-policy-market-based-solutions-to-societal-challenges-/</t>
         </is>
       </c>
       <c r="N18" s="5" t="inlineStr">
         <is>
-          <t>HigherEdJobs</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Q18" s="7" t="inlineStr">
@@ -2265,31 +2265,31 @@
         </is>
       </c>
       <c r="R18" s="2" t="n">
-        <v>41.8748613</v>
+        <v>43.0802745</v>
       </c>
       <c r="S18" s="2" t="n">
-        <v>-87.6519866</v>
+        <v>-89.43095870000001</v>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>77e0632bd4e74eae</t>
+          <t>51857534b7308d30</t>
         </is>
       </c>
     </row>
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Tenure-Track Faculty Positions in Transportation Engineering</t>
+          <t>Assistant Professor of Information and Decision Sciences (Supply Chain &amp; Operations Management)</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>National Taiwan University</t>
+          <t>University of Illinois Chicago</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Department of Civil Engineering</t>
+          <t>Department of Information and Decision Sciences, College of Business Administration</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
@@ -2297,12 +2297,12 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>This is a civil engineering faculty search at National Taiwan University that explicitly includes Public Transportation and Intelligent Transportation Systems as preferred research areas.</t>
+          <t>Strong interdisciplinary business school fit as the position explicitly prioritizes transportation as a preferred applied research domain for operations management.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Intelligent Transportation Systems, Public Transportation, Transportation Economics</t>
+          <t>Operations Management, Supply Chain Management, Transportation, Artificial Intelligence</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
@@ -2312,47 +2312,47 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Taipei, Taiwan</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>Priority: 2026-10-20 / Final: 2026-12-06</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Monthly salary: NT$83,720–137,370</t>
+          <t>$185,000 - $220,000 annually</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>National Taiwan University seeks multiple tenure-track faculty members in transportation engineering and surveying, requiring a Ph.D. and the ability to teach in English. | Research Topics: Intelligent Transportation Systems, Public Transportation, Transportation Economics</t>
+          <t>This tenure-track assistant professor role in operations management seeks candidates with a Ph.D. in a related field and explicitly prefers research focused on transportation and AI-integrated supply chain management. | Research Topics: Operations Management, Supply Chain Management, Transportation, Artificial Intelligence</t>
         </is>
       </c>
       <c r="M19" s="6" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38034402/faculty-recruitment-announcement-department-of-civil-engineering-national-taiwan-university/</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179552436&amp;Title=Assistant%20Professor%20%2D%20IDS%20%28Supply%20Chain%20%26%20Operations%20Management%29</t>
         </is>
       </c>
       <c r="N19" s="5" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q19" s="7" t="inlineStr">
@@ -2361,31 +2361,31 @@
         </is>
       </c>
       <c r="R19" s="2" t="n">
-        <v>25.0375198</v>
+        <v>41.8748613</v>
       </c>
       <c r="S19" s="2" t="n">
-        <v>121.5636796</v>
+        <v>-87.6519866</v>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>f056997ace2e1de7</t>
+          <t>77e0632bd4e74eae</t>
         </is>
       </c>
     </row>
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Lecturer in Discipline or Senior Lecturer in Discipline</t>
+          <t>Tenure-Track Faculty Positions in Transportation Engineering</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Columbia University</t>
+          <t>National Taiwan University</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Department of Industrial Engineering and Operations Research</t>
+          <t>Department of Civil Engineering</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
@@ -2393,62 +2393,62 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>This is a full-time career-track lecturer role in Industrial Engineering and Operations Research at Columbia University focused on Artificial Intelligence and data science applications, which aligns well with the candidate's strong machine learning and data-driven modeling expertise.</t>
+          <t>This is a civil engineering faculty search at National Taiwan University that explicitly includes Public Transportation and Intelligent Transportation Systems as preferred research areas.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Artificial Intelligence, Operations Research, Data Science, Machine Learning Applications</t>
+          <t>Intelligent Transportation Systems, Public Transportation, Transportation Economics</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Non-Tenure Track</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Taipei, Taiwan</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>2027-01-01</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>2027-01-01</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Lecturer in Discipline: 106K-129K; Senior Lecturer in Discipline: 125K-162K</t>
+          <t>Monthly salary: NT$83,720–137,370</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>Columbia University seeks a full-time Lecturer or Senior Lecturer in the Department of Industrial Engineering and Operations Research to teach AI and data science courses, requiring a Ph.D. in a related quantitative discipline. | Research Topics: Artificial Intelligence, Operations Research, Data Science, Machine Learning Applications</t>
+          <t>National Taiwan University seeks multiple tenure-track faculty members in transportation engineering and surveying, requiring a Ph.D. and the ability to teach in English. | Research Topics: Intelligent Transportation Systems, Public Transportation, Transportation Economics</t>
         </is>
       </c>
       <c r="M20" s="6" t="inlineStr">
         <is>
-          <t>http://engineering.academickeys.com/job/arsy3jqh/Open-Rank-Lecturer-in-Discipline-or-Senior-Lecturer-in-Discipline</t>
+          <t>https://jobs.chronicle.com/job/38034402/faculty-recruitment-announcement-department-of-civil-engineering-national-taiwan-university/</t>
         </is>
       </c>
       <c r="N20" s="5" t="inlineStr">
         <is>
-          <t>AcademicKeys</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Q20" s="7" t="inlineStr">
@@ -2457,90 +2457,94 @@
         </is>
       </c>
       <c r="R20" s="2" t="n">
-        <v>40.8077507</v>
+        <v>25.0375198</v>
       </c>
       <c r="S20" s="2" t="n">
-        <v>-73.9624901</v>
+        <v>121.5636796</v>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>f11b4a4e74422ae3</t>
+          <t>f056997ace2e1de7</t>
         </is>
       </c>
     </row>
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Assistant/Associate/Full Professor, Transportation Engineering and Systems</t>
+          <t>Lecturer in Discipline or Senior Lecturer in Discipline</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>University of Cincinnati</t>
+          <t>Columbia University</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Department of Civil and Architectural Engineering and Construction Management (CAECM)</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="n">
-        <v>9</v>
+          <t>Department of Industrial Engineering and Operations Research</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>7</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>This is a dedicated Assistant/Associate/Full Professor position in Transportation Engineering and Systems perfectly aligned with the candidate's core research profile.</t>
+          <t>This is a full-time career-track lecturer role in Industrial Engineering and Operations Research at Columbia University focused on Artificial Intelligence and data science applications, which aligns well with the candidate's strong machine learning and data-driven modeling expertise.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Transportation Engineering, Transportation Systems, Transit Planning</t>
+          <t>Artificial Intelligence, Operations Research, Data Science, Machine Learning Applications</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Non-Tenure Track</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Cincinnati, OH</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>Open until filled</t>
-        </is>
-      </c>
-      <c r="J21" s="5" t="inlineStr"/>
+          <t>2027-01-01</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>2027-01-01</t>
+        </is>
+      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Lecturer in Discipline: 106K-129K; Senior Lecturer in Discipline: 125K-162K</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>This role seeks a faculty member in transportation engineering and systems within an R1 urban research university setting requiring an appropriate terminal degree. | Research Topics: Transportation Engineering, Transportation Systems, Transit Planning</t>
+          <t>Columbia University seeks a full-time Lecturer or Senior Lecturer in the Department of Industrial Engineering and Operations Research to teach AI and data science courses, requiring a Ph.D. in a related quantitative discipline. | Research Topics: Artificial Intelligence, Operations Research, Data Science, Machine Learning Applications</t>
         </is>
       </c>
       <c r="M21" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-associate-full-professor-transportation-engineering-and-systems-at-university-of-cincinnati-4416744025</t>
+          <t>http://engineering.academickeys.com/job/arsy3jqh/Open-Rank-Lecturer-in-Discipline-or-Senior-Lecturer-in-Discipline</t>
         </is>
       </c>
       <c r="N21" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>AcademicKeys</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="Q21" s="7" t="inlineStr">
@@ -2549,44 +2553,44 @@
         </is>
       </c>
       <c r="R21" s="2" t="n">
-        <v>39.1318888</v>
+        <v>40.8077507</v>
       </c>
       <c r="S21" s="2" t="n">
-        <v>-84.51578309999999</v>
+        <v>-73.9624901</v>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>6aa8ab000bc6f6c0</t>
+          <t>f11b4a4e74422ae3</t>
         </is>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Assistant/Associate/Full Professor, Transportation Engineering and Systems</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>University of Cincinnati</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>School of City and Regional Planning</t>
+          <t>Department of Civil and Architectural Engineering and Construction Management (CAECM)</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>This is an Assistant Professor position within the School of City and Regional Planning, matching the candidate's background in urban planning and transportation mobility research.</t>
+          <t>This is a dedicated Assistant/Associate/Full Professor position in Transportation Engineering and Systems perfectly aligned with the candidate's core research profile.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Urban Planning and Spatial Analytics, Sustainable and Resilient Communities, Mobility Analytics</t>
+          <t>Transportation Engineering, Transportation Systems, Transit Planning</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -2596,7 +2600,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Cincinnati, OH</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
@@ -2612,12 +2616,12 @@
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology seeks a tenure-track Assistant Professor in the School of City and Regional Planning to advance research and teaching in urban planning, spatial analytics, and sustainable communities. | Research Topics: Urban Planning and Spatial Analytics, Sustainable and Resilient Communities, Mobility Analytics</t>
+          <t>This role seeks a faculty member in transportation engineering and systems within an R1 urban research university setting requiring an appropriate terminal degree. | Research Topics: Transportation Engineering, Transportation Systems, Transit Planning</t>
         </is>
       </c>
       <c r="M22" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-at-georgia-institute-of-technology-4467296351</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-associate-full-professor-transportation-engineering-and-systems-at-university-of-cincinnati-4416744025</t>
         </is>
       </c>
       <c r="N22" s="5" t="inlineStr">
@@ -2627,12 +2631,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Q22" s="7" t="inlineStr">
@@ -2641,54 +2645,54 @@
         </is>
       </c>
       <c r="R22" s="2" t="n">
-        <v>33.7756</v>
+        <v>39.1318888</v>
       </c>
       <c r="S22" s="2" t="n">
-        <v>-84.3963</v>
+        <v>-84.51578309999999</v>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1b7278bf60327029</t>
+          <t>6aa8ab000bc6f6c0</t>
         </is>
       </c>
     </row>
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Assistant or Associate Professor in Complex Systems and Urban &amp; Regional Modelling</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Maastricht University</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Faculty of Science and Engineering</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="n">
-        <v>7</v>
+          <t>School of City and Regional Planning</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="n">
+        <v>8</v>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>This Assistant or Associate Professor role in complex systems and urban and regional modelling aligns well with the candidate's strong computational and urban modelling expertise.</t>
+          <t>This is an Assistant Professor position within the School of City and Regional Planning, matching the candidate's background in urban planning and transportation mobility research.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Urban and Regional Modelling, Complex Systems Theory, Urban Sustainability, Spatial Modelling</t>
+          <t>Urban Planning and Spatial Analytics, Sustainable and Resilient Communities, Mobility Analytics</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Maastricht, Netherlands</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
@@ -2704,12 +2708,12 @@
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>Maastricht University seeks an Assistant or Associate Professor to build a new research line in urban and regional modelling, requiring a PhD in a relevant technical or computational field. | Research Topics: Urban and Regional Modelling, Complex Systems Theory, Urban Sustainability, Spatial Modelling</t>
+          <t>Georgia Institute of Technology seeks a tenure-track Assistant Professor in the School of City and Regional Planning to advance research and teaching in urban planning, spatial analytics, and sustainable communities. | Research Topics: Urban Planning and Spatial Analytics, Sustainable and Resilient Communities, Mobility Analytics</t>
         </is>
       </c>
       <c r="M23" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/assistant-or-associate-professor-in-complex-systems-and-urban-regional-modelling-at-maastricht-university-faculty-of-science-and-engineering-4452765174</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-at-georgia-institute-of-technology-4467296351</t>
         </is>
       </c>
       <c r="N23" s="5" t="inlineStr">
@@ -2719,12 +2723,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="Q23" s="7" t="inlineStr">
@@ -2733,31 +2737,31 @@
         </is>
       </c>
       <c r="R23" s="2" t="n">
-        <v>50.8472117</v>
+        <v>33.7756</v>
       </c>
       <c r="S23" s="2" t="n">
-        <v>5.6859518</v>
+        <v>-84.3963</v>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>321ee686ffad2403</t>
+          <t>1b7278bf60327029</t>
         </is>
       </c>
     </row>
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Tenure-track Assistant Professor – AI for Automotive and Mobility Systems</t>
+          <t>Assistant or Associate Professor in Complex Systems and Urban &amp; Regional Modelling</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>The Ohio State University</t>
+          <t>Maastricht University</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Department of Mechanical Engineering</t>
+          <t>Faculty of Science and Engineering</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
@@ -2765,22 +2769,22 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>The position focuses on AI and mobility systems, which aligns well with the candidate's background in machine learning applications and smart mobility, though situated within Mechanical Engineering.</t>
+          <t>This Assistant or Associate Professor role in complex systems and urban and regional modelling aligns well with the candidate's strong computational and urban modelling expertise.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>AI in Transportation and Mobility, Automotive and Mobility Systems, Smart Urban Mobility, Machine Learning Applications</t>
+          <t>Urban and Regional Modelling, Complex Systems Theory, Urban Sustainability, Spatial Modelling</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Unspecified</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Columbus, OH</t>
+          <t>Maastricht, Netherlands</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
@@ -2796,83 +2800,83 @@
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>The Ohio State University invites applications for a tenure-track Assistant Professor in Mechanical Engineering specializing in AI for automotive and mobility systems, requiring a Ph.D. in a related engineering discipline. | Research Topics: AI in Transportation and Mobility, Automotive and Mobility Systems, Smart Urban Mobility, Machine Learning Applications</t>
+          <t>Maastricht University seeks an Assistant or Associate Professor to build a new research line in urban and regional modelling, requiring a PhD in a relevant technical or computational field. | Research Topics: Urban and Regional Modelling, Complex Systems Theory, Urban Sustainability, Spatial Modelling</t>
         </is>
       </c>
       <c r="M24" s="6" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179558778&amp;Title=Tenure%2Dtrack%20Assistant%20Professor%20%E2%80%93%20AI%20for%20Automotive%20and%20Mobility%20Systems</t>
+          <t>https://nl.linkedin.com/jobs/view/assistant-or-associate-professor-in-complex-systems-and-urban-regional-modelling-at-maastricht-university-faculty-of-science-and-engineering-4452765174</t>
         </is>
       </c>
       <c r="N24" s="5" t="inlineStr">
         <is>
-          <t>HigherEdJobs</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
       <c r="Q24" s="7" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
       <c r="R24" s="2" t="n">
-        <v>40.0067</v>
+        <v>50.8472117</v>
       </c>
       <c r="S24" s="2" t="n">
-        <v>-83.0305</v>
+        <v>5.6859518</v>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4e4fa974f5d3f2a4</t>
+          <t>321ee686ffad2403</t>
         </is>
       </c>
     </row>
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Assistant/Associate Professor of Civil Engineering</t>
+          <t>Tenure-track Assistant Professor – AI for Automotive and Mobility Systems</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Cedarville University</t>
+          <t>The Ohio State University</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>School of Engineering and Computer Science</t>
+          <t>Department of Mechanical Engineering</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>This is a broad civil engineering faculty search where transportation is explicitly listed as one of the acceptable sub-disciplines.</t>
+          <t>The position focuses on AI and mobility systems, which aligns well with the candidate's background in machine learning applications and smart mobility, though situated within Mechanical Engineering.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Transportation Engineering, Civil Engineering Education, Undergraduate Mentoring</t>
+          <t>AI in Transportation and Mobility, Automotive and Mobility Systems, Smart Urban Mobility, Machine Learning Applications</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Cedarville, OH</t>
+          <t>Columbus, OH</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
@@ -2888,12 +2892,12 @@
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>This position seeks an Assistant or Associate Professor in Civil Engineering to teach undergraduate courses and mentor students across disciplines including transportation, requiring a Ph.D. in Civil Engineering or related field. | Research Topics: Transportation Engineering, Civil Engineering Education, Undergraduate Mentoring</t>
+          <t>The Ohio State University invites applications for a tenure-track Assistant Professor in Mechanical Engineering specializing in AI for automotive and mobility systems, requiring a Ph.D. in a related engineering discipline. | Research Topics: AI in Transportation and Mobility, Automotive and Mobility Systems, Smart Urban Mobility, Machine Learning Applications</t>
         </is>
       </c>
       <c r="M25" s="6" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179544290&amp;Title=Assistant%2FAssociate%20Professor%20of%20Civil%20Engineering</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179558778&amp;Title=Tenure%2Dtrack%20Assistant%20Professor%20%E2%80%93%20AI%20for%20Automotive%20and%20Mobility%20Systems</t>
         </is>
       </c>
       <c r="N25" s="5" t="inlineStr">
@@ -2903,12 +2907,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Q25" s="7" t="inlineStr">
@@ -2917,31 +2921,31 @@
         </is>
       </c>
       <c r="R25" s="2" t="n">
-        <v>39.7540491</v>
+        <v>40.0067</v>
       </c>
       <c r="S25" s="2" t="n">
-        <v>-83.8170518</v>
+        <v>-83.0305</v>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>751c7406865a2787</t>
+          <t>4e4fa974f5d3f2a4</t>
         </is>
       </c>
     </row>
     <row r="26" ht="26" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Civil Engineering</t>
+          <t>Assistant/Associate Professor of Civil Engineering</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>McNeese State University</t>
+          <t>Cedarville University</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Department of Engineering and Computer Science</t>
+          <t>School of Engineering and Computer Science</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
@@ -2949,22 +2953,22 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>This is a broad civil engineering faculty search that explicitly welcomes transportation engineering alongside other sub-disciplines.</t>
+          <t>This is a broad civil engineering faculty search where transportation is explicitly listed as one of the acceptable sub-disciplines.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Civil Engineering, Transportation Engineering, Water Resources and Hydraulic Engineering, Structural and Geotechnical Engineering</t>
+          <t>Transportation Engineering, Civil Engineering Education, Undergraduate Mentoring</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Unspecified</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Lake Charles, LA</t>
+          <t>Cedarville, OH</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
@@ -2975,17 +2979,17 @@
       <c r="J26" s="5" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>$76,000 per year</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>McNeese State University seeks a full-time, tenure-track Assistant Professor of Civil Engineering to teach, advise students, and conduct research, requiring a Ph.D. in Civil Engineering. | Research Topics: Civil Engineering, Transportation Engineering, Water Resources and Hydraulic Engineering, Structural and Geotechnical Engineering</t>
+          <t>This position seeks an Assistant or Associate Professor in Civil Engineering to teach undergraduate courses and mentor students across disciplines including transportation, requiring a Ph.D. in Civil Engineering or related field. | Research Topics: Transportation Engineering, Civil Engineering Education, Undergraduate Mentoring</t>
         </is>
       </c>
       <c r="M26" s="6" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179545361&amp;Title=Assistant%20Professor%20of%20Civil%20Engineering</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179544290&amp;Title=Assistant%2FAssociate%20Professor%20of%20Civil%20Engineering</t>
         </is>
       </c>
       <c r="N26" s="5" t="inlineStr">
@@ -2995,7 +2999,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3009,31 +3013,31 @@
         </is>
       </c>
       <c r="R26" s="2" t="n">
-        <v>30.1751363</v>
+        <v>39.7540491</v>
       </c>
       <c r="S26" s="2" t="n">
-        <v>-93.2112786</v>
+        <v>-83.8170518</v>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>bd292fb9f52ac2e9</t>
+          <t>751c7406865a2787</t>
         </is>
       </c>
     </row>
     <row r="27" ht="26" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor / Associate Professor in Civil and Environmental Engineering</t>
+          <t>Assistant Professor of Civil Engineering</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Nanyang Technological University Singapore</t>
+          <t>McNeese State University</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>School of Civil and Environmental Engineering</t>
+          <t>Department of Engineering and Computer Science</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
@@ -3041,12 +3045,12 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>This is an open-rank faculty search in Civil and Environmental Engineering where transportation is a potential fit among broader infrastructure domains.</t>
+          <t>This is a broad civil engineering faculty search that explicitly welcomes transportation engineering alongside other sub-disciplines.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Civil Engineering, Geospatial Technologies, Digital Construction, Infrastructure Systems</t>
+          <t>Civil Engineering, Transportation Engineering, Water Resources and Hydraulic Engineering, Structural and Geotechnical Engineering</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -3056,7 +3060,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Singapore, Singapore</t>
+          <t>Lake Charles, LA</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
@@ -3067,32 +3071,32 @@
       <c r="J27" s="5" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>Highly competitive</t>
+          <t>$76,000 per year</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>Nanyang Technological University seeks tenure-track faculty across all areas of Civil and Environmental Engineering requiring a Ph.D. in a relevant field. | Research Topics: Civil Engineering, Geospatial Technologies, Digital Construction, Infrastructure Systems</t>
+          <t>McNeese State University seeks a full-time, tenure-track Assistant Professor of Civil Engineering to teach, advise students, and conduct research, requiring a Ph.D. in Civil Engineering. | Research Topics: Civil Engineering, Transportation Engineering, Water Resources and Hydraulic Engineering, Structural and Geotechnical Engineering</t>
         </is>
       </c>
       <c r="M27" s="6" t="inlineStr">
         <is>
-          <t>https://sg.linkedin.com/jobs/view/assistant-professor-associate-professor-tenure-track-in-civil-and-environmental-engineering-at-nanyang-technological-university-singapore-4432357834</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179545361&amp;Title=Assistant%20Professor%20of%20Civil%20Engineering</t>
         </is>
       </c>
       <c r="N27" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="Q27" s="7" t="inlineStr">
@@ -3101,31 +3105,31 @@
         </is>
       </c>
       <c r="R27" s="2" t="n">
-        <v>1.3483</v>
+        <v>30.1751363</v>
       </c>
       <c r="S27" s="2" t="n">
-        <v>103.6831</v>
+        <v>-93.2112786</v>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>ce5f34eaef46b041</t>
+          <t>bd292fb9f52ac2e9</t>
         </is>
       </c>
     </row>
     <row r="28" ht="26" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Assistant/Associate Professor of Civil Engineering (Transportation)</t>
+          <t>Assistant Professor / Associate Professor in Civil and Environmental Engineering</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Trine University</t>
+          <t>Nanyang Technological University Singapore</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Reiners Department of Civil and Environmental Engineering</t>
+          <t>School of Civil and Environmental Engineering</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
@@ -3133,12 +3137,12 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>This is a broad Civil Engineering assistant/associate professor position at a teaching-focused institution where transportation engineering is explicitly listed as a primary teaching and curricular requirement.</t>
+          <t>This is an open-rank faculty search in Civil and Environmental Engineering where transportation is a potential fit among broader infrastructure domains.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Transportation Engineering, Undergraduate Engineering Education, Geographic Information Systems (GIS), Civil Engineering Curriculum</t>
+          <t>Civil Engineering, Geospatial Technologies, Digital Construction, Infrastructure Systems</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
@@ -3148,7 +3152,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Angola, IN</t>
+          <t>Singapore, Singapore</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
@@ -3159,32 +3163,32 @@
       <c r="J28" s="5" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Based on qualifications</t>
+          <t>Highly competitive</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>Trine University seeks a full-time Assistant or Associate Professor of Civil Engineering with a specialization in transportation to teach undergraduate courses, engage students in applied projects, and support program accreditation, requiring a Ph.D. in Civil Engineering or a closely related field. | Research Topics: Transportation Engineering, Undergraduate Engineering Education, Geographic Information Systems (GIS), Civil Engineering Curriculum</t>
+          <t>Nanyang Technological University seeks tenure-track faculty across all areas of Civil and Environmental Engineering requiring a Ph.D. in a relevant field. | Research Topics: Civil Engineering, Geospatial Technologies, Digital Construction, Infrastructure Systems</t>
         </is>
       </c>
       <c r="M28" s="6" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38028401/assistant-associate-professor-civil-engineering-transportation-/</t>
+          <t>https://sg.linkedin.com/jobs/view/assistant-professor-associate-professor-tenure-track-in-civil-and-environmental-engineering-at-nanyang-technological-university-singapore-4432357834</t>
         </is>
       </c>
       <c r="N28" s="5" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Q28" s="7" t="inlineStr">
@@ -3193,31 +3197,31 @@
         </is>
       </c>
       <c r="R28" s="2" t="n">
-        <v>41.6311141</v>
+        <v>1.3483</v>
       </c>
       <c r="S28" s="2" t="n">
-        <v>-85.0105982</v>
+        <v>103.6831</v>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9f9cc58aa59ccd96</t>
+          <t>ce5f34eaef46b041</t>
         </is>
       </c>
     </row>
     <row r="29" ht="26" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Faculty Position in Civil Engineering (Transportation and Traffic Engineering)</t>
+          <t>Assistant/Associate Professor of Civil Engineering (Transportation)</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>University of New Brunswick</t>
+          <t>Trine University</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Faculty of Engineering</t>
+          <t>Reiners Department of Civil and Environmental Engineering</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
@@ -3225,12 +3229,12 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>This is a broad Civil Engineering faculty position that explicitly covers traffic engineering and transportation operations, aligning with the candidate's core subfield.</t>
+          <t>This is a broad Civil Engineering assistant/associate professor position at a teaching-focused institution where transportation engineering is explicitly listed as a primary teaching and curricular requirement.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Traffic studies and analysis, Traffic control devices, Intersections and interchanges operations, Traffic accident studies</t>
+          <t>Transportation Engineering, Undergraduate Engineering Education, Geographic Information Systems (GIS), Civil Engineering Curriculum</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -3240,7 +3244,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Fredericton, New Brunswick</t>
+          <t>Angola, IN</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
@@ -3251,32 +3255,32 @@
       <c r="J29" s="5" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Based on qualifications</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>The University of New Brunswick seeks a faculty member in Civil Engineering specializing in traffic characteristics, traffic studies, and intersection operations, requiring a Master's or Ph.D. in Civil Engineering or a closely related area. | Research Topics: Traffic studies and analysis, Traffic control devices, Intersections and interchanges operations, Traffic accident studies</t>
+          <t>Trine University seeks a full-time Assistant or Associate Professor of Civil Engineering with a specialization in transportation to teach undergraduate courses, engage students in applied projects, and support program accreditation, requiring a Ph.D. in Civil Engineering or a closely related field. | Research Topics: Transportation Engineering, Undergraduate Engineering Education, Geographic Information Systems (GIS), Civil Engineering Curriculum</t>
         </is>
       </c>
       <c r="M29" s="6" t="inlineStr">
         <is>
-          <t>https://ca.linkedin.com/jobs/view/engineering-faculty-of-at-university-of-new-brunswick-4451582209</t>
+          <t>https://jobs.chronicle.com/job/38028401/assistant-associate-professor-civil-engineering-transportation-/</t>
         </is>
       </c>
       <c r="N29" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Q29" s="7" t="inlineStr">
@@ -3285,44 +3289,44 @@
         </is>
       </c>
       <c r="R29" s="2" t="n">
-        <v>45.9455202</v>
+        <v>41.6311141</v>
       </c>
       <c r="S29" s="2" t="n">
-        <v>-66.64018609999999</v>
+        <v>-85.0105982</v>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>77b43c5491345e72</t>
+          <t>9f9cc58aa59ccd96</t>
         </is>
       </c>
     </row>
     <row r="30" ht="26" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Assistant/Associate Professor of Civil, Architectural and Environmental Engineering</t>
+          <t>Faculty Position in Civil Engineering (Transportation and Traffic Engineering)</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Missouri University of Science and Technology</t>
+          <t>University of New Brunswick</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Department of Civil, Architectural and Environmental Engineering</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="n">
-        <v>4</v>
+          <t>Faculty of Engineering</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>This is a general Civil, Architectural and Environmental Engineering faculty opening without an explicitly stated specialization in transportation engineering or transit planning.</t>
+          <t>This is a broad Civil Engineering faculty position that explicitly covers traffic engineering and transportation operations, aligning with the candidate's core subfield.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Civil Engineering, Architectural Engineering, Environmental Engineering</t>
+          <t>Traffic studies and analysis, Traffic control devices, Intersections and interchanges operations, Traffic accident studies</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
@@ -3332,7 +3336,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Rolla, MO</t>
+          <t>Fredericton, New Brunswick</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
@@ -3348,12 +3352,12 @@
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>Missouri University of Science and Technology invites applications for an Assistant or Associate Professor position in Civil, Architectural, and Environmental Engineering requiring a relevant doctoral degree. | Research Topics: Civil Engineering, Architectural Engineering, Environmental Engineering</t>
+          <t>The University of New Brunswick seeks a faculty member in Civil Engineering specializing in traffic characteristics, traffic studies, and intersection operations, requiring a Master's or Ph.D. in Civil Engineering or a closely related area. | Research Topics: Traffic studies and analysis, Traffic control devices, Intersections and interchanges operations, Traffic accident studies</t>
         </is>
       </c>
       <c r="M30" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-associate-professor-civil-architectural-and-environmental-engineering-%2300096512-at-missouri-university-of-science-and-technology-4442271248</t>
+          <t>https://ca.linkedin.com/jobs/view/engineering-faculty-of-at-university-of-new-brunswick-4451582209</t>
         </is>
       </c>
       <c r="N30" s="5" t="inlineStr">
@@ -3368,7 +3372,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Q30" s="7" t="inlineStr">
@@ -3377,31 +3381,31 @@
         </is>
       </c>
       <c r="R30" s="2" t="n">
-        <v>37.9532435</v>
+        <v>45.9455202</v>
       </c>
       <c r="S30" s="2" t="n">
-        <v>-91.7742667</v>
+        <v>-66.64018609999999</v>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4fad8c46021c1243</t>
+          <t>77b43c5491345e72</t>
         </is>
       </c>
     </row>
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Public Policy</t>
+          <t>Assistant/Associate Professor of Civil, Architectural and Environmental Engineering</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>University of Texas at Arlington</t>
+          <t>Missouri University of Science and Technology</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Department of Public Affairs &amp; Planning</t>
+          <t>Department of Civil, Architectural and Environmental Engineering</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
@@ -3409,12 +3413,12 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>The position is for an Assistant Professor of Public Policy in a public affairs department, which falls outside the candidate's core expertise in transportation engineering, travel behavior, and mobility systems.</t>
+          <t>This is a general Civil, Architectural and Environmental Engineering faculty opening without an explicitly stated specialization in transportation engineering or transit planning.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Public Policy, Urban Studies, Public Infrastructure, Public Administration</t>
+          <t>Civil Engineering, Architectural Engineering, Environmental Engineering</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -3424,7 +3428,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Arlington, TX</t>
+          <t>Rolla, MO</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
@@ -3440,12 +3444,12 @@
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>The University of Texas at Arlington seeks a tenure-track Assistant Professor of Public Policy in the Department of Public Affairs and Planning requiring a Ph.D. in public policy or a related social science discipline. | Research Topics: Public Policy, Urban Studies, Public Infrastructure, Public Administration</t>
+          <t>Missouri University of Science and Technology invites applications for an Assistant or Associate Professor position in Civil, Architectural, and Environmental Engineering requiring a relevant doctoral degree. | Research Topics: Civil Engineering, Architectural Engineering, Environmental Engineering</t>
         </is>
       </c>
       <c r="M31" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-at-excel-campus-activities-4464851831</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-associate-professor-civil-architectural-and-environmental-engineering-%2300096512-at-missouri-university-of-science-and-technology-4442271248</t>
         </is>
       </c>
       <c r="N31" s="5" t="inlineStr">
@@ -3455,12 +3459,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Q31" s="7" t="inlineStr">
@@ -3469,44 +3473,44 @@
         </is>
       </c>
       <c r="R31" s="2" t="n">
-        <v>32.7315155</v>
+        <v>37.9532435</v>
       </c>
       <c r="S31" s="2" t="n">
-        <v>-97.1171533</v>
+        <v>-91.7742667</v>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>15704bb25858281c</t>
+          <t>4fad8c46021c1243</t>
         </is>
       </c>
     </row>
     <row r="32" ht="26" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor in Supply Chain Management</t>
+          <t>Assistant Professor of Public Policy</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Iowa State University</t>
+          <t>University of Texas at Arlington</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Department of Supply Chain Management, Ivy College of Business</t>
+          <t>Department of Public Affairs &amp; Planning</t>
         </is>
       </c>
       <c r="D32" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>This is a business school position focused on supply chain management rather than transportation engineering or urban mobility systems.</t>
+          <t>The position is for an Assistant Professor of Public Policy in a public affairs department, which falls outside the candidate's core expertise in transportation engineering, travel behavior, and mobility systems.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Management, Logistics, Operations</t>
+          <t>Public Policy, Urban Studies, Public Infrastructure, Public Administration</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
@@ -3516,7 +3520,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Ames, IA</t>
+          <t>Arlington, TX</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
@@ -3532,12 +3536,12 @@
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>Iowa State University seeks a tenure-track Assistant Professor in Supply Chain Management to conduct research and teach courses at the undergraduate, master's, and Ph.D. levels, requiring a doctorate in business administration, supply chain, transportation, logistics, operations, or a related field. | Research Topics: Supply Chain Management, Logistics, Operations</t>
+          <t>The University of Texas at Arlington seeks a tenure-track Assistant Professor of Public Policy in the Department of Public Affairs and Planning requiring a Ph.D. in public policy or a related social science discipline. | Research Topics: Public Policy, Urban Studies, Public Infrastructure, Public Administration</t>
         </is>
       </c>
       <c r="M32" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-in-supply-chain-management-at-iowa-state-university-ivy-college-of-business-4440811209</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-at-excel-campus-activities-4464851831</t>
         </is>
       </c>
       <c r="N32" s="5" t="inlineStr">
@@ -3547,12 +3551,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="Q32" s="7" t="inlineStr">
@@ -3561,31 +3565,31 @@
         </is>
       </c>
       <c r="R32" s="2" t="n">
-        <v>42.0267567</v>
+        <v>32.7315155</v>
       </c>
       <c r="S32" s="2" t="n">
-        <v>-93.6170448</v>
+        <v>-97.1171533</v>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>e994e392d38b77ce</t>
+          <t>15704bb25858281c</t>
         </is>
       </c>
     </row>
     <row r="33" ht="26" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor / Associate Professor (Tenure-Track) in Maritime Studies</t>
+          <t>Assistant Professor in Supply Chain Management</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Nanyang Technological University</t>
+          <t>Iowa State University</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>School of Civil and Environmental Engineering</t>
+          <t>Department of Supply Chain Management, Ivy College of Business</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
@@ -3593,12 +3597,12 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>While housed in the School of Civil and Environmental Engineering, this position specifically targets Maritime Studies, shipping decarbonization, and port logistics, diverging from the candidate's core expertise in urban public transit and travel behavior modeling.</t>
+          <t>This is a business school position focused on supply chain management rather than transportation engineering or urban mobility systems.</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Sustainable Shipping and Decarbonization, Port Operations and Logistics, Maritime Economics and Digitalisation, Supply Chain Resilience</t>
+          <t>Supply Chain Management, Logistics, Operations</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -3608,7 +3612,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Ames, IA</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
@@ -3624,12 +3628,12 @@
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>Nanyang Technological University seeks tenure-track faculty at all ranks in Maritime Studies within the School of Civil and Environmental Engineering, requiring a Ph.D. in Maritime Studies or a closely related field. | Research Topics: Sustainable Shipping and Decarbonization, Port Operations and Logistics, Maritime Economics and Digitalisation, Supply Chain Resilience</t>
+          <t>Iowa State University seeks a tenure-track Assistant Professor in Supply Chain Management to conduct research and teach courses at the undergraduate, master's, and Ph.D. levels, requiring a doctorate in business administration, supply chain, transportation, logistics, operations, or a related field. | Research Topics: Supply Chain Management, Logistics, Operations</t>
         </is>
       </c>
       <c r="M33" s="6" t="inlineStr">
         <is>
-          <t>https://sg.linkedin.com/jobs/view/assistant-professor-associate-professor-tenure-track-associate-professor-practice-track-in-maritime-studies-at-nanyang-technological-university-singapore-4432368242</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-in-supply-chain-management-at-iowa-state-university-ivy-college-of-business-4440811209</t>
         </is>
       </c>
       <c r="N33" s="5" t="inlineStr">
@@ -3639,12 +3643,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="Q33" s="7" t="inlineStr">
@@ -3653,31 +3657,31 @@
         </is>
       </c>
       <c r="R33" s="2" t="n">
-        <v>1.3483</v>
+        <v>42.0267567</v>
       </c>
       <c r="S33" s="2" t="n">
-        <v>103.6831</v>
+        <v>-93.6170448</v>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1e0a7536f9329af5</t>
+          <t>e994e392d38b77ce</t>
         </is>
       </c>
     </row>
     <row r="34" ht="26" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Faculty Openings in Engineering (Open Rank)</t>
+          <t>Assistant Professor / Associate Professor (Tenure-Track) in Maritime Studies</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Singapore Institute of Technology</t>
+          <t>Nanyang Technological University</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Engineering Cluster</t>
+          <t>School of Civil and Environmental Engineering</t>
         </is>
       </c>
       <c r="D34" s="5" t="n">
@@ -3685,17 +3689,17 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>While open rank and located in target Singapore, the engineering openings focus on construction materials, tunneling, infrastructure asset maintenance, and power systems rather than transportation planning or travel demand modeling.</t>
+          <t>While housed in the School of Civil and Environmental Engineering, this position specifically targets Maritime Studies, shipping decarbonization, and port logistics, diverging from the candidate's core expertise in urban public transit and travel behavior modeling.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Transport Infrastructure Asset Management, Tunnel Engineering, Construction Technologies, Power and Systems Engineering</t>
+          <t>Sustainable Shipping and Decarbonization, Port Operations and Logistics, Maritime Economics and Digitalisation, Supply Chain Resilience</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3716,12 +3720,12 @@
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>Singapore Institute of Technology is seeking faculty at all ranks across civil, electrical, mechanical, and systems engineering disciplines to support applied learning and translational industry research. | Research Topics: Transport Infrastructure Asset Management, Tunnel Engineering, Construction Technologies, Power and Systems Engineering</t>
+          <t>Nanyang Technological University seeks tenure-track faculty at all ranks in Maritime Studies within the School of Civil and Environmental Engineering, requiring a Ph.D. in Maritime Studies or a closely related field. | Research Topics: Sustainable Shipping and Decarbonization, Port Operations and Logistics, Maritime Economics and Digitalisation, Supply Chain Resilience</t>
         </is>
       </c>
       <c r="M34" s="6" t="inlineStr">
         <is>
-          <t>https://sg.linkedin.com/jobs/view/faculty-openings-in-engineering-at-singapore-institute-of-technology-4273859333</t>
+          <t>https://sg.linkedin.com/jobs/view/assistant-professor-associate-professor-tenure-track-associate-professor-practice-track-in-maritime-studies-at-nanyang-technological-university-singapore-4432368242</t>
         </is>
       </c>
       <c r="N34" s="5" t="inlineStr">
@@ -3736,7 +3740,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Q34" s="7" t="inlineStr">
@@ -3745,31 +3749,31 @@
         </is>
       </c>
       <c r="R34" s="2" t="n">
-        <v>1.4123197</v>
+        <v>1.3483</v>
       </c>
       <c r="S34" s="2" t="n">
-        <v>103.9094621</v>
+        <v>103.6831</v>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>f21dc0b6a181929c</t>
+          <t>1e0a7536f9329af5</t>
         </is>
       </c>
     </row>
     <row r="35" ht="26" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Assistant/Associate/Full Professor in Industrial and Systems Engineering</t>
+          <t>Assistant, Associate, or Full Professor of Mechanical and Industrial Engineering</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>University of Florida</t>
+          <t>Northeastern University</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Department of Industrial and Systems Engineering</t>
+          <t>Department of Mechanical and Industrial Engineering</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
@@ -3777,22 +3781,22 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Although transportation is mentioned as a potential application area, the primary focus of this Industrial and Systems Engineering position is on Industrialized Construction and 3D construction printing rather than core transportation engineering, mobility, or travel behavior.</t>
+          <t>The position is in Mechanical and Industrial Engineering without a stated focus on transportation engineering, making it a poor fit for the candidate's core profile.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Industrialized Construction, Artificial Intelligence, Digital Twins, Operations Research</t>
+          <t>Mechanical Engineering, Industrial Engineering</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Unspecified</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Gainesville, FL</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
@@ -3803,32 +3807,32 @@
       <c r="J35" s="5" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>Salary is commensurate with education and experience.</t>
+          <t>$101,000 - $215,000 per year</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>This full-time tenured or tenure-track faculty position in Industrial and Systems Engineering at the University of Florida seeks expertise in industrialized construction and related technologies, requiring a Ph.D. in ISE, Manufacturing Engineering, Civil Engineering, Mechanical Engineering, or a closely related field. | Research Topics: Industrialized Construction, Artificial Intelligence, Digital Twins, Operations Research</t>
+          <t>Open-rank faculty position in mechanical and industrial engineering focusing on general department research areas. | Research Topics: Mechanical Engineering, Industrial Engineering</t>
         </is>
       </c>
       <c r="M35" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-associate-full-professor-industrial-systems-engineering-at-university-of-florida-4323668785</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179560354&amp;Title=Assistant%2C%20Associate%2C%20Full%20Professor%20%2D%20College%20of%20Engineering%20%2D%20Mechanical%20and%20Industrial%20Engineering%20%2D%20Boston</t>
         </is>
       </c>
       <c r="N35" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Q35" s="7" t="inlineStr">
@@ -3837,94 +3841,90 @@
         </is>
       </c>
       <c r="R35" s="2" t="n">
-        <v>29.6436</v>
+        <v>42.3351065</v>
       </c>
       <c r="S35" s="2" t="n">
-        <v>-82.3549</v>
+        <v>-71.0892575</v>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>56d501f448e77e05</t>
+          <t>e1042bf3b6aa8057</t>
         </is>
       </c>
     </row>
     <row r="36" ht="26" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Assistant / Associate Professor of Industrial and Systems Engineering</t>
+          <t>Faculty Openings in Engineering (Open Rank)</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>University of Washington</t>
+          <t>Singapore Institute of Technology</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Industrial &amp; Systems Engineering</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="n">
-        <v>6</v>
+          <t>Engineering Cluster</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Assistant Professor position in Systems Engineering that aligns with the candidate's expertise in AI-enabled systems and smart mobility through the lens of cyber-physical and autonomous systems.</t>
+          <t>While open rank and located in target Singapore, the engineering openings focus on construction materials, tunneling, infrastructure asset maintenance, and power systems rather than transportation planning or travel demand modeling.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Systems Engineering, Autonomous Systems, Cyber-Physical Systems, AI-Enabled Systems Engineering</t>
+          <t>Transport Infrastructure Asset Management, Tunnel Engineering, Construction Technologies, Power and Systems Engineering</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Unspecified</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>Priority: 2026-09-15 / Open until filled</t>
-        </is>
-      </c>
-      <c r="J36" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>$12,000 – $17,000 per month (9-month service period)</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>The Department of Industrial and Systems Engineering at the University of Washington seeks an Assistant or Associate Professor specializing in Systems Engineering, requiring a Ph.D. in Systems Engineering, Industrial Engineering, or a related discipline. | Research Topics: Systems Engineering, Autonomous Systems, Cyber-Physical Systems, AI-Enabled Systems Engineering</t>
+          <t>Singapore Institute of Technology is seeking faculty at all ranks across civil, electrical, mechanical, and systems engineering disciplines to support applied learning and translational industry research. | Research Topics: Transport Infrastructure Asset Management, Tunnel Engineering, Construction Technologies, Power and Systems Engineering</t>
         </is>
       </c>
       <c r="M36" s="6" t="inlineStr">
         <is>
-          <t>https://engineering.academickeys.com/job/g4m97a60/AssistantAssociate-Professor-Industrial-and-Systems-Engineering-Systems-Engineering-Focus</t>
+          <t>https://sg.linkedin.com/jobs/view/faculty-openings-in-engineering-at-singapore-institute-of-technology-4273859333</t>
         </is>
       </c>
       <c r="N36" s="5" t="inlineStr">
         <is>
-          <t>AcademicKeys</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Q36" s="7" t="inlineStr">
@@ -3933,31 +3933,31 @@
         </is>
       </c>
       <c r="R36" s="2" t="n">
-        <v>47.6553</v>
+        <v>1.4123197</v>
       </c>
       <c r="S36" s="2" t="n">
-        <v>-122.3035</v>
+        <v>103.9094621</v>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>9d5682cf4dbca334</t>
+          <t>f21dc0b6a181929c</t>
         </is>
       </c>
     </row>
     <row r="37" ht="26" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Tenure-Track Assistant/Associate Professor of Air Transportation Systems</t>
+          <t>Assistant/Associate/Full Professor in Industrial and Systems Engineering</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Embry-Riddle Aeronautical University</t>
+          <t>University of Florida</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>School of Graduate Studies, College of Aviation</t>
+          <t>Department of Industrial and Systems Engineering</t>
         </is>
       </c>
       <c r="D37" s="5" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>The position focuses specifically on air transportation systems, advanced air mobility, and aviation, which falls outside the candidate's core background in ground-based transportation engineering and public transit planning.</t>
+          <t>Although transportation is mentioned as a potential application area, the primary focus of this Industrial and Systems Engineering position is on Industrialized Construction and 3D construction printing rather than core transportation engineering, mobility, or travel behavior.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Air Transportation Systems, Advanced Air Mobility, UAS Traffic Management, Machine Learning/AI in Aviation</t>
+          <t>Industrialized Construction, Artificial Intelligence, Digital Twins, Operations Research</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -3980,37 +3980,33 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL</t>
+          <t>Gainesville, FL</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>Priority: 2026-08-31 / Open until filled</t>
-        </is>
-      </c>
-      <c r="J37" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>Competitive Salary</t>
+          <t>Salary is commensurate with education and experience.</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>Embry-Riddle Aeronautical University seeks a tenure-track faculty member in air transportation systems and advanced air mobility requiring a doctorate and relevant experience. | Research Topics: Air Transportation Systems, Advanced Air Mobility, UAS Traffic Management, Machine Learning/AI in Aviation</t>
+          <t>This full-time tenured or tenure-track faculty position in Industrial and Systems Engineering at the University of Florida seeks expertise in industrialized construction and related technologies, requiring a Ph.D. in ISE, Manufacturing Engineering, Civil Engineering, Mechanical Engineering, or a closely related field. | Research Topics: Industrialized Construction, Artificial Intelligence, Digital Twins, Operations Research</t>
         </is>
       </c>
       <c r="M37" s="6" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38012134/tenure-track-faculty-position-with-a-focus-on-air-transportation-systems-daytona-beach-campus/</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-associate-full-professor-industrial-systems-engineering-at-university-of-florida-4323668785</t>
         </is>
       </c>
       <c r="N37" s="5" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
@@ -4020,7 +4016,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="Q37" s="7" t="inlineStr">
@@ -4029,44 +4025,44 @@
         </is>
       </c>
       <c r="R37" s="2" t="n">
-        <v>29.1895</v>
+        <v>29.6436</v>
       </c>
       <c r="S37" s="2" t="n">
-        <v>-81.04940000000001</v>
+        <v>-82.3549</v>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>52969a207999417a</t>
+          <t>56d501f448e77e05</t>
         </is>
       </c>
     </row>
     <row r="38" ht="26" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Transportation Engineering</t>
+          <t>Assistant / Associate Professor of Industrial and Systems Engineering</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>South Dakota State University</t>
+          <t>University of Washington</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Department of Civil and Environmental Engineering</t>
-        </is>
-      </c>
-      <c r="D38" s="8" t="n">
-        <v>9</v>
+          <t>Industrial &amp; Systems Engineering</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>This is a tenure-track Assistant Professor position in Transportation Engineering within a Civil and Environmental Engineering department, perfectly aligning with the candidate's core research profile.</t>
+          <t>Assistant Professor position in Systems Engineering that aligns with the candidate's expertise in AI-enabled systems and smart mobility through the lens of cyber-physical and autonomous systems.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Intelligent Transportation Systems, Transportation Data Analytics, Traffic Operations, Resilient Transportation Systems</t>
+          <t>Systems Engineering, Autonomous Systems, Cyber-Physical Systems, AI-Enabled Systems Engineering</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
@@ -4076,32 +4072,32 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Brookings, SD</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>Priority: 2026-09-15 / Open until filled</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>Starting at $92,000</t>
+          <t>$12,000 – $17,000 per month (9-month service period)</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>South Dakota State University seeks a tenure-track Assistant Professor in Transportation Engineering to teach undergraduate and graduate courses, advise students, and develop an externally funded research program requiring a Ph.D. in Civil Engineering or a closely related field. | Research Topics: Intelligent Transportation Systems, Transportation Data Analytics, Traffic Operations, Resilient Transportation Systems</t>
+          <t>The Department of Industrial and Systems Engineering at the University of Washington seeks an Assistant or Associate Professor specializing in Systems Engineering, requiring a Ph.D. in Systems Engineering, Industrial Engineering, or a related discipline. | Research Topics: Systems Engineering, Autonomous Systems, Cyber-Physical Systems, AI-Enabled Systems Engineering</t>
         </is>
       </c>
       <c r="M38" s="6" t="inlineStr">
         <is>
-          <t>https://engineering.academickeys.com/job/m4lk5asr/Assistant-Professor-of-Transportation-Engineering</t>
+          <t>https://engineering.academickeys.com/job/g4m97a60/AssistantAssociate-Professor-Industrial-and-Systems-Engineering-Systems-Engineering-Focus</t>
         </is>
       </c>
       <c r="N38" s="5" t="inlineStr">
@@ -4111,7 +4107,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4119,85 +4115,85 @@
           <t>2026-09-19</t>
         </is>
       </c>
-      <c r="Q38" s="9" t="inlineStr">
-        <is>
-          <t>Past Due</t>
+      <c r="Q38" s="7" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
       <c r="R38" s="2" t="n">
-        <v>44.344449</v>
+        <v>47.6553</v>
       </c>
       <c r="S38" s="2" t="n">
-        <v>-96.79823709999999</v>
+        <v>-122.3035</v>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>9b7d5de4753a514b</t>
+          <t>9d5682cf4dbca334</t>
         </is>
       </c>
     </row>
     <row r="39" ht="26" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Clinical Assistant Professor</t>
+          <t>Tenure-Track Assistant/Associate Professor of Air Transportation Systems</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Georgia State University</t>
+          <t>Embry-Riddle Aeronautical University</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Department of Public Management and Policy</t>
+          <t>School of Graduate Studies, College of Aviation</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>This is a non-tenure-track clinical position in public management and policy focusing on teaching data analytics and urban planning, which is a poor fit for a candidate targeting research-active tenure-track positions in transportation engineering.</t>
+          <t>The position focuses specifically on air transportation systems, advanced air mobility, and aviation, which falls outside the candidate's core background in ground-based transportation engineering and public transit planning.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Policy Analytics, Urban Planning, Data Visualization, GIS Applications</t>
+          <t>Air Transportation Systems, Advanced Air Mobility, UAS Traffic Management, Machine Learning/AI in Aviation</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>Non-Tenure Track</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Daytona Beach, FL</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>Priority: 2026-08-31 / Open until filled</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>$80,000-$90,000</t>
+          <t>Competitive Salary</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>A non-tenure-track clinical assistant professor position focusing on teaching policy analytics, urban planning, and GIS, requiring a Ph.D. in a related field and university teaching experience. | Research Topics: Policy Analytics, Urban Planning, Data Visualization, GIS Applications</t>
+          <t>Embry-Riddle Aeronautical University seeks a tenure-track faculty member in air transportation systems and advanced air mobility requiring a doctorate and relevant experience. | Research Topics: Air Transportation Systems, Advanced Air Mobility, UAS Traffic Management, Machine Learning/AI in Aviation</t>
         </is>
       </c>
       <c r="M39" s="6" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38022215/clinical-assistant-professor-non-tenure-tack/</t>
+          <t>https://jobs.chronicle.com/job/38012134/tenure-track-faculty-position-with-a-focus-on-air-transportation-systems-daytona-beach-campus/</t>
         </is>
       </c>
       <c r="N39" s="5" t="inlineStr">
@@ -4207,58 +4203,58 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="P39" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="Q39" s="9" t="inlineStr">
-        <is>
-          <t>Past Due</t>
+      <c r="Q39" s="7" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
       <c r="R39" s="2" t="n">
-        <v>33.7535889</v>
+        <v>29.1895</v>
       </c>
       <c r="S39" s="2" t="n">
-        <v>-84.3854209</v>
+        <v>-81.04940000000001</v>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>f39f14cbaaf9d6f7</t>
+          <t>52969a207999417a</t>
         </is>
       </c>
     </row>
     <row r="40" ht="26" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor in Transportation Policy</t>
+          <t>Assistant Professor of Transportation Engineering</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Hunter College</t>
+          <t>South Dakota State University</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Department of Urban Policy and Planning</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="n">
-        <v>7</v>
+          <t>Department of Civil and Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="n">
+        <v>9</v>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Strong interdisciplinary fit for an Assistant Professor position focusing on transportation policy and planning within an urban policy department.</t>
+          <t>This is a tenure-track Assistant Professor position in Transportation Engineering within a Civil and Environmental Engineering department, perfectly aligning with the candidate's core research profile.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Transportation Policy, Transportation Advocacy &amp; Accessibility, Community-Engaged Research, Urban Planning</t>
+          <t>Intelligent Transportation Systems, Transportation Data Analytics, Traffic Operations, Resilient Transportation Systems</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
@@ -4268,37 +4264,37 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Brookings, SD</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>Open until filled</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>$77,092 - $91,922</t>
+          <t>Starting at $92,000</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>Hunter College seeks a tenure-track Assistant Professor in transportation policy to teach graduate students and conduct community-engaged research, requiring a Ph.D. in policy, planning, or a related field specializing in transportation. | Research Topics: Transportation Policy, Transportation Advocacy &amp; Accessibility, Community-Engaged Research, Urban Planning</t>
+          <t>South Dakota State University seeks a tenure-track Assistant Professor in Transportation Engineering to teach undergraduate and graduate courses, advise students, and develop an externally funded research program requiring a Ph.D. in Civil Engineering or a closely related field. | Research Topics: Intelligent Transportation Systems, Transportation Data Analytics, Traffic Operations, Resilient Transportation Systems</t>
         </is>
       </c>
       <c r="M40" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-%E2%80%93-urban-policy-and-planning-dept-school-of-arts-and-sciences-hunter-college-at-hunter-college-4438624127</t>
+          <t>https://engineering.academickeys.com/job/m4lk5asr/Assistant-Professor-of-Transportation-Engineering</t>
         </is>
       </c>
       <c r="N40" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>AcademicKeys</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -4311,100 +4307,100 @@
           <t>2026-09-19</t>
         </is>
       </c>
-      <c r="Q40" s="7" t="inlineStr">
-        <is>
-          <t>Active</t>
+      <c r="Q40" s="9" t="inlineStr">
+        <is>
+          <t>Past Due</t>
         </is>
       </c>
       <c r="R40" s="2" t="n">
-        <v>40.7683107</v>
+        <v>44.344449</v>
       </c>
       <c r="S40" s="2" t="n">
-        <v>-73.964406</v>
+        <v>-96.79823709999999</v>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>e4e18ed629103a27</t>
+          <t>9b7d5de4753a514b</t>
         </is>
       </c>
     </row>
     <row r="41" ht="26" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Full/Associate/Assistant Professor in Modern Civil Engineering</t>
+          <t>Clinical Assistant Professor</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>University of Macau</t>
+          <t>Georgia State University</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Department of Civil and Environmental Engineering (CEE)</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>6</v>
+          <t>Department of Public Management and Policy</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>The posting is an open-rank faculty search in modern civil engineering which may encompass transportation, but lacks sufficient departmental subfield details in the short snippet.</t>
+          <t>This is a non-tenure-track clinical position in public management and policy focusing on teaching data analytics and urban planning, which is a poor fit for a candidate targeting research-active tenure-track positions in transportation engineering.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Modern Civil Engineering, Transportation Engineering, Urban Systems</t>
+          <t>Policy Analytics, Urban Planning, Data Visualization, GIS Applications</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Non-Tenure Track</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Macao</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>£87,465.51 to £127,834.20 starting salary</t>
+          <t>$80,000-$90,000</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>The University of Macau seeks a faculty member in modern civil engineering within the Department of Civil and Environmental Engineering. | Research Topics: Modern Civil Engineering, Transportation Engineering, Urban Systems</t>
+          <t>A non-tenure-track clinical assistant professor position focusing on teaching policy analytics, urban planning, and GIS, requiring a Ph.D. in a related field and university teaching experience. | Research Topics: Policy Analytics, Urban Planning, Data Visualization, GIS Applications</t>
         </is>
       </c>
       <c r="M41" s="6" t="inlineStr">
         <is>
-          <t>https://www.jobs.ac.uk/job/DSL575/full-associate-assistant-professor-in-modern-civil-engineering</t>
+          <t>https://jobs.chronicle.com/job/38022215/clinical-assistant-professor-non-tenure-tack/</t>
         </is>
       </c>
       <c r="N41" s="5" t="inlineStr">
         <is>
-          <t>Jobs.ac.uk</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Q41" s="9" t="inlineStr">
@@ -4413,44 +4409,44 @@
         </is>
       </c>
       <c r="R41" s="2" t="n">
-        <v>22.1285</v>
+        <v>33.7535889</v>
       </c>
       <c r="S41" s="2" t="n">
-        <v>113.5438</v>
+        <v>-84.3854209</v>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>600dff84e8f0a0b2</t>
+          <t>f39f14cbaaf9d6f7</t>
         </is>
       </c>
     </row>
     <row r="42" ht="26" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor in Low-Altitude Economy</t>
+          <t>Assistant Professor in Transportation Policy</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>The Hong Kong Polytechnic University</t>
+          <t>Hunter College</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Department of Aeronautical and Aviation Engineering</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="n">
-        <v>3</v>
+          <t>Department of Urban Policy and Planning</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>7</v>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Although located in Hong Kong, the position is in Aeronautical and Aviation Engineering focusing on the Low-Altitude Economy rather than traditional transportation engineering or public transit planning.</t>
+          <t>Strong interdisciplinary fit for an Assistant Professor position focusing on transportation policy and planning within an urban policy department.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Low-Altitude Economy, Aeronautical Engineering, Aviation Systems</t>
+          <t>Transportation Policy, Transportation Advocacy &amp; Accessibility, Community-Engaged Research, Urban Planning</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
@@ -4460,59 +4456,159 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="J42" s="5" t="inlineStr"/>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>$77,092 - $91,922</t>
         </is>
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>The role seeks an Assistant Professor in Low-Altitude Economy within the Department of Aeronautical and Aviation Engineering, requiring relevant expertise in aviation or aerospace systems. | Research Topics: Low-Altitude Economy, Aeronautical Engineering, Aviation Systems</t>
+          <t>Hunter College seeks a tenure-track Assistant Professor in transportation policy to teach graduate students and conduct community-engaged research, requiring a Ph.D. in policy, planning, or a related field specializing in transportation. | Research Topics: Transportation Policy, Transportation Advocacy &amp; Accessibility, Community-Engaged Research, Urban Planning</t>
         </is>
       </c>
       <c r="M42" s="6" t="inlineStr">
         <is>
-          <t>https://www.jobs.ac.uk/job/DSJ402/assistant-professor-in-low-altitude-economy</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-%E2%80%93-urban-policy-and-planning-dept-school-of-arts-and-sciences-hunter-college-at-hunter-college-4438624127</t>
         </is>
       </c>
       <c r="N42" s="5" t="inlineStr">
         <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Q42" s="7" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="n">
+        <v>40.7683107</v>
+      </c>
+      <c r="S42" s="2" t="n">
+        <v>-73.964406</v>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>e4e18ed629103a27</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="26" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Full/Associate/Assistant Professor in Modern Civil Engineering</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>University of Macau</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Department of Civil and Environmental Engineering (CEE)</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>The posting is an open-rank faculty search in modern civil engineering which may encompass transportation, but lacks sufficient departmental subfield details in the short snippet.</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Modern Civil Engineering, Transportation Engineering, Urban Systems</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Macao</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>£87,465.51 to £127,834.20 starting salary</t>
+        </is>
+      </c>
+      <c r="L43" s="4" t="inlineStr">
+        <is>
+          <t>The University of Macau seeks a faculty member in modern civil engineering within the Department of Civil and Environmental Engineering. | Research Topics: Modern Civil Engineering, Transportation Engineering, Urban Systems</t>
+        </is>
+      </c>
+      <c r="M43" s="6" t="inlineStr">
+        <is>
+          <t>https://www.jobs.ac.uk/job/DSL575/full-associate-assistant-professor-in-modern-civil-engineering</t>
+        </is>
+      </c>
+      <c r="N43" s="5" t="inlineStr">
+        <is>
           <t>Jobs.ac.uk</t>
         </is>
       </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="Q42" s="7" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="n">
-        <v>22.3045</v>
-      </c>
-      <c r="S42" s="2" t="n">
-        <v>114.1797</v>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t>ce4ae0a91b9988f7</t>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Q43" s="9" t="inlineStr">
+        <is>
+          <t>Past Due</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="n">
+        <v>22.1285</v>
+      </c>
+      <c r="S43" s="2" t="n">
+        <v>113.5438</v>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>600dff84e8f0a0b2</t>
         </is>
       </c>
     </row>
@@ -4559,6 +4655,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId42"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T43"/>
+  <dimension ref="A1:T47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -527,7 +527,7 @@
     <col width="32" customWidth="1" min="5" max="5"/>
     <col width="138" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="29" customWidth="1" min="8" max="8"/>
+    <col width="33" customWidth="1" min="8" max="8"/>
     <col width="50" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="78" customWidth="1" min="11" max="11"/>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="Q7" s="7" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="Q11" s="7" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="Q12" s="7" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="Q13" s="7" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="Q18" s="7" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="Q22" s="7" t="inlineStr">
@@ -2751,17 +2751,17 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Assistant or Associate Professor in Complex Systems and Urban &amp; Regional Modelling</t>
+          <t>Chair Professor / Professor / Associate Professor / Assistant Professor, Lingnan-60</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Maastricht University</t>
+          <t>Lingnan University</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Faculty of Science and Engineering</t>
+          <t>Lingnan-60 Global Talent Recruitment</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
@@ -2769,22 +2769,22 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>This Assistant or Associate Professor role in complex systems and urban and regional modelling aligns well with the candidate's strong computational and urban modelling expertise.</t>
+          <t>This is an open-rank cluster hire that explicitly includes smart city, data science, and AI areas aligning well with the candidate's interdisciplinary profile.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Urban and Regional Modelling, Complex Systems Theory, Urban Sustainability, Spatial Modelling</t>
+          <t>Smart City, Data Science and Artificial Intelligence, Smart Infrastructure, Social and Public Policy</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Maastricht, Netherlands</t>
+          <t>New Territories, Hong Kong SAR</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
@@ -2800,12 +2800,12 @@
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>Maastricht University seeks an Assistant or Associate Professor to build a new research line in urban and regional modelling, requiring a PhD in a relevant technical or computational field. | Research Topics: Urban and Regional Modelling, Complex Systems Theory, Urban Sustainability, Spatial Modelling</t>
+          <t>Lingnan University seeks open-rank scholars across interdisciplinary fields including smart infrastructure, data science, and AI, requiring a relevant PhD degree. | Research Topics: Smart City, Data Science and Artificial Intelligence, Smart Infrastructure, Social and Public Policy</t>
         </is>
       </c>
       <c r="M24" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/assistant-or-associate-professor-in-complex-systems-and-urban-regional-modelling-at-maastricht-university-faculty-of-science-and-engineering-4452765174</t>
+          <t>https://hk.linkedin.com/jobs/view/chair-professor-professor-associate-professor-assistant-professor-lingnan-60-at-lingnan-university-4386654192</t>
         </is>
       </c>
       <c r="N24" s="5" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="Q24" s="7" t="inlineStr">
@@ -2829,31 +2829,31 @@
         </is>
       </c>
       <c r="R24" s="2" t="n">
-        <v>50.8472117</v>
+        <v>22.4123588</v>
       </c>
       <c r="S24" s="2" t="n">
-        <v>5.6859518</v>
+        <v>113.9812776</v>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>321ee686ffad2403</t>
+          <t>0a5d257fc60d771a</t>
         </is>
       </c>
     </row>
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Tenure-track Assistant Professor – AI for Automotive and Mobility Systems</t>
+          <t>Assistant or Associate Professor in Complex Systems and Urban &amp; Regional Modelling</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>The Ohio State University</t>
+          <t>Maastricht University</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Department of Mechanical Engineering</t>
+          <t>Faculty of Science and Engineering</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
@@ -2861,22 +2861,22 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>The position focuses on AI and mobility systems, which aligns well with the candidate's background in machine learning applications and smart mobility, though situated within Mechanical Engineering.</t>
+          <t>This Assistant or Associate Professor role in complex systems and urban and regional modelling aligns well with the candidate's strong computational and urban modelling expertise.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>AI in Transportation and Mobility, Automotive and Mobility Systems, Smart Urban Mobility, Machine Learning Applications</t>
+          <t>Urban and Regional Modelling, Complex Systems Theory, Urban Sustainability, Spatial Modelling</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Unspecified</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Columbus, OH</t>
+          <t>Maastricht, Netherlands</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
@@ -2892,27 +2892,27 @@
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>The Ohio State University invites applications for a tenure-track Assistant Professor in Mechanical Engineering specializing in AI for automotive and mobility systems, requiring a Ph.D. in a related engineering discipline. | Research Topics: AI in Transportation and Mobility, Automotive and Mobility Systems, Smart Urban Mobility, Machine Learning Applications</t>
+          <t>Maastricht University seeks an Assistant or Associate Professor to build a new research line in urban and regional modelling, requiring a PhD in a relevant technical or computational field. | Research Topics: Urban and Regional Modelling, Complex Systems Theory, Urban Sustainability, Spatial Modelling</t>
         </is>
       </c>
       <c r="M25" s="6" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179558778&amp;Title=Tenure%2Dtrack%20Assistant%20Professor%20%E2%80%93%20AI%20for%20Automotive%20and%20Mobility%20Systems</t>
+          <t>https://nl.linkedin.com/jobs/view/assistant-or-associate-professor-in-complex-systems-and-urban-regional-modelling-at-maastricht-university-faculty-of-science-and-engineering-4452765174</t>
         </is>
       </c>
       <c r="N25" s="5" t="inlineStr">
         <is>
-          <t>HigherEdJobs</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="Q25" s="7" t="inlineStr">
@@ -2921,54 +2921,54 @@
         </is>
       </c>
       <c r="R25" s="2" t="n">
-        <v>40.0067</v>
+        <v>50.8472117</v>
       </c>
       <c r="S25" s="2" t="n">
-        <v>-83.0305</v>
+        <v>5.6859518</v>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4e4fa974f5d3f2a4</t>
+          <t>321ee686ffad2403</t>
         </is>
       </c>
     </row>
     <row r="26" ht="26" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Assistant/Associate Professor of Civil Engineering</t>
+          <t>Tenure-track Assistant Professor – AI for Automotive and Mobility Systems</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Cedarville University</t>
+          <t>The Ohio State University</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>School of Engineering and Computer Science</t>
+          <t>Department of Mechanical Engineering</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>This is a broad civil engineering faculty search where transportation is explicitly listed as one of the acceptable sub-disciplines.</t>
+          <t>The position focuses on AI and mobility systems, which aligns well with the candidate's background in machine learning applications and smart mobility, though situated within Mechanical Engineering.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Transportation Engineering, Civil Engineering Education, Undergraduate Mentoring</t>
+          <t>AI in Transportation and Mobility, Automotive and Mobility Systems, Smart Urban Mobility, Machine Learning Applications</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Cedarville, OH</t>
+          <t>Columbus, OH</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
@@ -2984,12 +2984,12 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>This position seeks an Assistant or Associate Professor in Civil Engineering to teach undergraduate courses and mentor students across disciplines including transportation, requiring a Ph.D. in Civil Engineering or related field. | Research Topics: Transportation Engineering, Civil Engineering Education, Undergraduate Mentoring</t>
+          <t>The Ohio State University invites applications for a tenure-track Assistant Professor in Mechanical Engineering specializing in AI for automotive and mobility systems, requiring a Ph.D. in a related engineering discipline. | Research Topics: AI in Transportation and Mobility, Automotive and Mobility Systems, Smart Urban Mobility, Machine Learning Applications</t>
         </is>
       </c>
       <c r="M26" s="6" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179544290&amp;Title=Assistant%2FAssociate%20Professor%20of%20Civil%20Engineering</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179558778&amp;Title=Tenure%2Dtrack%20Assistant%20Professor%20%E2%80%93%20AI%20for%20Automotive%20and%20Mobility%20Systems</t>
         </is>
       </c>
       <c r="N26" s="5" t="inlineStr">
@@ -2999,12 +2999,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Q26" s="7" t="inlineStr">
@@ -3013,44 +3013,44 @@
         </is>
       </c>
       <c r="R26" s="2" t="n">
-        <v>39.7540491</v>
+        <v>40.0067</v>
       </c>
       <c r="S26" s="2" t="n">
-        <v>-83.8170518</v>
+        <v>-83.0305</v>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>751c7406865a2787</t>
+          <t>4e4fa974f5d3f2a4</t>
         </is>
       </c>
     </row>
     <row r="27" ht="26" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Civil Engineering</t>
+          <t>Assistant Professor of Operations Research</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>McNeese State University</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Department of Engineering and Computer Science</t>
+          <t>Department of Industrial and Manufacturing Engineering</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>This is a broad civil engineering faculty search that explicitly welcomes transportation engineering alongside other sub-disciplines.</t>
+          <t>This is an Assistant Professor search in Industrial and Manufacturing Engineering focusing on Operations Research, which aligns well with the candidate's systems and operations specialty.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Civil Engineering, Transportation Engineering, Water Resources and Hydraulic Engineering, Structural and Geotechnical Engineering</t>
+          <t>Operations Research, Systems Engineering, Optimization, Data Analytics</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Lake Charles, LA</t>
+          <t>Blacksburg, VA</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
@@ -3071,17 +3071,17 @@
       <c r="J27" s="5" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>$76,000 per year</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>McNeese State University seeks a full-time, tenure-track Assistant Professor of Civil Engineering to teach, advise students, and conduct research, requiring a Ph.D. in Civil Engineering. | Research Topics: Civil Engineering, Transportation Engineering, Water Resources and Hydraulic Engineering, Structural and Geotechnical Engineering</t>
+          <t>This tenure-track Assistant Professor position in Industrial and Manufacturing Engineering seeks an expert in operations research and systems modeling requiring a Ph.D. | Research Topics: Operations Research, Systems Engineering, Optimization, Data Analytics</t>
         </is>
       </c>
       <c r="M27" s="6" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179545361&amp;Title=Assistant%20Professor%20of%20Civil%20Engineering</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179563591&amp;Title=Assistant%20Professor%20%2D%20Operations%20Research</t>
         </is>
       </c>
       <c r="N27" s="5" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="Q27" s="7" t="inlineStr">
@@ -3105,31 +3105,31 @@
         </is>
       </c>
       <c r="R27" s="2" t="n">
-        <v>30.1751363</v>
+        <v>37.2284</v>
       </c>
       <c r="S27" s="2" t="n">
-        <v>-93.2112786</v>
+        <v>-80.4234</v>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>bd292fb9f52ac2e9</t>
+          <t>ca8945afe4726788</t>
         </is>
       </c>
     </row>
     <row r="28" ht="26" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor / Associate Professor in Civil and Environmental Engineering</t>
+          <t>Assistant/Associate Professor of Civil Engineering</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Nanyang Technological University Singapore</t>
+          <t>Cedarville University</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>School of Civil and Environmental Engineering</t>
+          <t>School of Engineering and Computer Science</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
@@ -3137,22 +3137,22 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>This is an open-rank faculty search in Civil and Environmental Engineering where transportation is a potential fit among broader infrastructure domains.</t>
+          <t>This is a broad civil engineering faculty search where transportation is explicitly listed as one of the acceptable sub-disciplines.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Civil Engineering, Geospatial Technologies, Digital Construction, Infrastructure Systems</t>
+          <t>Transportation Engineering, Civil Engineering Education, Undergraduate Mentoring</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Unspecified</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Singapore, Singapore</t>
+          <t>Cedarville, OH</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
@@ -3163,32 +3163,32 @@
       <c r="J28" s="5" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Highly competitive</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>Nanyang Technological University seeks tenure-track faculty across all areas of Civil and Environmental Engineering requiring a Ph.D. in a relevant field. | Research Topics: Civil Engineering, Geospatial Technologies, Digital Construction, Infrastructure Systems</t>
+          <t>This position seeks an Assistant or Associate Professor in Civil Engineering to teach undergraduate courses and mentor students across disciplines including transportation, requiring a Ph.D. in Civil Engineering or related field. | Research Topics: Transportation Engineering, Civil Engineering Education, Undergraduate Mentoring</t>
         </is>
       </c>
       <c r="M28" s="6" t="inlineStr">
         <is>
-          <t>https://sg.linkedin.com/jobs/view/assistant-professor-associate-professor-tenure-track-in-civil-and-environmental-engineering-at-nanyang-technological-university-singapore-4432357834</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179544290&amp;Title=Assistant%2FAssociate%20Professor%20of%20Civil%20Engineering</t>
         </is>
       </c>
       <c r="N28" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="Q28" s="7" t="inlineStr">
@@ -3197,31 +3197,31 @@
         </is>
       </c>
       <c r="R28" s="2" t="n">
-        <v>1.3483</v>
+        <v>39.7540491</v>
       </c>
       <c r="S28" s="2" t="n">
-        <v>103.6831</v>
+        <v>-83.8170518</v>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>ce5f34eaef46b041</t>
+          <t>751c7406865a2787</t>
         </is>
       </c>
     </row>
     <row r="29" ht="26" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Assistant/Associate Professor of Civil Engineering (Transportation)</t>
+          <t>Assistant Professor of Civil Engineering</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Trine University</t>
+          <t>McNeese State University</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Reiners Department of Civil and Environmental Engineering</t>
+          <t>Department of Engineering and Computer Science</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>This is a broad Civil Engineering assistant/associate professor position at a teaching-focused institution where transportation engineering is explicitly listed as a primary teaching and curricular requirement.</t>
+          <t>This is a broad civil engineering faculty search that explicitly welcomes transportation engineering alongside other sub-disciplines.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Transportation Engineering, Undergraduate Engineering Education, Geographic Information Systems (GIS), Civil Engineering Curriculum</t>
+          <t>Civil Engineering, Transportation Engineering, Water Resources and Hydraulic Engineering, Structural and Geotechnical Engineering</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Angola, IN</t>
+          <t>Lake Charles, LA</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
@@ -3255,32 +3255,32 @@
       <c r="J29" s="5" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Based on qualifications</t>
+          <t>$76,000 per year</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>Trine University seeks a full-time Assistant or Associate Professor of Civil Engineering with a specialization in transportation to teach undergraduate courses, engage students in applied projects, and support program accreditation, requiring a Ph.D. in Civil Engineering or a closely related field. | Research Topics: Transportation Engineering, Undergraduate Engineering Education, Geographic Information Systems (GIS), Civil Engineering Curriculum</t>
+          <t>McNeese State University seeks a full-time, tenure-track Assistant Professor of Civil Engineering to teach, advise students, and conduct research, requiring a Ph.D. in Civil Engineering. | Research Topics: Civil Engineering, Transportation Engineering, Water Resources and Hydraulic Engineering, Structural and Geotechnical Engineering</t>
         </is>
       </c>
       <c r="M29" s="6" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38028401/assistant-associate-professor-civil-engineering-transportation-/</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179545361&amp;Title=Assistant%20Professor%20of%20Civil%20Engineering</t>
         </is>
       </c>
       <c r="N29" s="5" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="Q29" s="7" t="inlineStr">
@@ -3289,31 +3289,31 @@
         </is>
       </c>
       <c r="R29" s="2" t="n">
-        <v>41.6311141</v>
+        <v>30.1751363</v>
       </c>
       <c r="S29" s="2" t="n">
-        <v>-85.0105982</v>
+        <v>-93.2112786</v>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>9f9cc58aa59ccd96</t>
+          <t>bd292fb9f52ac2e9</t>
         </is>
       </c>
     </row>
     <row r="30" ht="26" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Faculty Position in Civil Engineering (Transportation and Traffic Engineering)</t>
+          <t>Assistant Professor / Associate Professor in Civil and Environmental Engineering</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>University of New Brunswick</t>
+          <t>Nanyang Technological University Singapore</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Faculty of Engineering</t>
+          <t>School of Civil and Environmental Engineering</t>
         </is>
       </c>
       <c r="D30" s="3" t="n">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>This is a broad Civil Engineering faculty position that explicitly covers traffic engineering and transportation operations, aligning with the candidate's core subfield.</t>
+          <t>This is an open-rank faculty search in Civil and Environmental Engineering where transportation is a potential fit among broader infrastructure domains.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Traffic studies and analysis, Traffic control devices, Intersections and interchanges operations, Traffic accident studies</t>
+          <t>Civil Engineering, Geospatial Technologies, Digital Construction, Infrastructure Systems</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Fredericton, New Brunswick</t>
+          <t>Singapore, Singapore</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
@@ -3347,17 +3347,17 @@
       <c r="J30" s="5" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Highly competitive</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>The University of New Brunswick seeks a faculty member in Civil Engineering specializing in traffic characteristics, traffic studies, and intersection operations, requiring a Master's or Ph.D. in Civil Engineering or a closely related area. | Research Topics: Traffic studies and analysis, Traffic control devices, Intersections and interchanges operations, Traffic accident studies</t>
+          <t>Nanyang Technological University seeks tenure-track faculty across all areas of Civil and Environmental Engineering requiring a Ph.D. in a relevant field. | Research Topics: Civil Engineering, Geospatial Technologies, Digital Construction, Infrastructure Systems</t>
         </is>
       </c>
       <c r="M30" s="6" t="inlineStr">
         <is>
-          <t>https://ca.linkedin.com/jobs/view/engineering-faculty-of-at-university-of-new-brunswick-4451582209</t>
+          <t>https://sg.linkedin.com/jobs/view/assistant-professor-associate-professor-tenure-track-in-civil-and-environmental-engineering-at-nanyang-technological-university-singapore-4432357834</t>
         </is>
       </c>
       <c r="N30" s="5" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="Q30" s="7" t="inlineStr">
@@ -3381,44 +3381,44 @@
         </is>
       </c>
       <c r="R30" s="2" t="n">
-        <v>45.9455202</v>
+        <v>1.3483</v>
       </c>
       <c r="S30" s="2" t="n">
-        <v>-66.64018609999999</v>
+        <v>103.6831</v>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>77b43c5491345e72</t>
+          <t>ce5f34eaef46b041</t>
         </is>
       </c>
     </row>
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Assistant/Associate Professor of Civil, Architectural and Environmental Engineering</t>
+          <t>Assistant/Associate Professor of Civil Engineering (Transportation)</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Missouri University of Science and Technology</t>
+          <t>Trine University</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Department of Civil, Architectural and Environmental Engineering</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>4</v>
+          <t>Reiners Department of Civil and Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>This is a general Civil, Architectural and Environmental Engineering faculty opening without an explicitly stated specialization in transportation engineering or transit planning.</t>
+          <t>This is a broad Civil Engineering assistant/associate professor position at a teaching-focused institution where transportation engineering is explicitly listed as a primary teaching and curricular requirement.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Civil Engineering, Architectural Engineering, Environmental Engineering</t>
+          <t>Transportation Engineering, Undergraduate Engineering Education, Geographic Information Systems (GIS), Civil Engineering Curriculum</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Rolla, MO</t>
+          <t>Angola, IN</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
@@ -3439,32 +3439,32 @@
       <c r="J31" s="5" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Based on qualifications</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>Missouri University of Science and Technology invites applications for an Assistant or Associate Professor position in Civil, Architectural, and Environmental Engineering requiring a relevant doctoral degree. | Research Topics: Civil Engineering, Architectural Engineering, Environmental Engineering</t>
+          <t>Trine University seeks a full-time Assistant or Associate Professor of Civil Engineering with a specialization in transportation to teach undergraduate courses, engage students in applied projects, and support program accreditation, requiring a Ph.D. in Civil Engineering or a closely related field. | Research Topics: Transportation Engineering, Undergraduate Engineering Education, Geographic Information Systems (GIS), Civil Engineering Curriculum</t>
         </is>
       </c>
       <c r="M31" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-associate-professor-civil-architectural-and-environmental-engineering-%2300096512-at-missouri-university-of-science-and-technology-4442271248</t>
+          <t>https://jobs.chronicle.com/job/38028401/assistant-associate-professor-civil-engineering-transportation-/</t>
         </is>
       </c>
       <c r="N31" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Q31" s="7" t="inlineStr">
@@ -3473,44 +3473,44 @@
         </is>
       </c>
       <c r="R31" s="2" t="n">
-        <v>37.9532435</v>
+        <v>41.6311141</v>
       </c>
       <c r="S31" s="2" t="n">
-        <v>-91.7742667</v>
+        <v>-85.0105982</v>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4fad8c46021c1243</t>
+          <t>9f9cc58aa59ccd96</t>
         </is>
       </c>
     </row>
     <row r="32" ht="26" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Public Policy</t>
+          <t>Assistant Professor, Associate Professor, or Professor, Transportation Engineering Systems</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>University of Texas at Arlington</t>
+          <t>University of Central Florida</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Department of Public Affairs &amp; Planning</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="n">
-        <v>4</v>
+          <t>Civil and Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>The position is for an Assistant Professor of Public Policy in a public affairs department, which falls outside the candidate's core expertise in transportation engineering, travel behavior, and mobility systems.</t>
+          <t>This is an open-rank faculty search in Civil and Environmental Engineering that includes transportation engineering systems, aligning with the candidate's core Ph.D. background.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Public Policy, Urban Studies, Public Infrastructure, Public Administration</t>
+          <t>Transportation Engineering Systems, Civil Engineering, Transportation Planning</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Arlington, TX</t>
+          <t>Orlando, FL</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
@@ -3536,27 +3536,27 @@
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>The University of Texas at Arlington seeks a tenure-track Assistant Professor of Public Policy in the Department of Public Affairs and Planning requiring a Ph.D. in public policy or a related social science discipline. | Research Topics: Public Policy, Urban Studies, Public Infrastructure, Public Administration</t>
+          <t>An open-rank faculty position in transportation engineering systems within the Department of Civil and Environmental Engineering requiring a relevant doctoral degree. | Research Topics: Transportation Engineering Systems, Civil Engineering, Transportation Planning</t>
         </is>
       </c>
       <c r="M32" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-at-excel-campus-activities-4464851831</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179562762&amp;Title=Assistant%20Professor%2C%20Associate%20Professor%2C%20or%20Professor%2C%20Transportation%20Engineering%20Systems</t>
         </is>
       </c>
       <c r="N32" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="Q32" s="7" t="inlineStr">
@@ -3565,44 +3565,44 @@
         </is>
       </c>
       <c r="R32" s="2" t="n">
-        <v>32.7315155</v>
+        <v>28.599591</v>
       </c>
       <c r="S32" s="2" t="n">
-        <v>-97.1171533</v>
+        <v>-81.1971284</v>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>15704bb25858281c</t>
+          <t>438fdcc800574f0c</t>
         </is>
       </c>
     </row>
     <row r="33" ht="26" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor in Supply Chain Management</t>
+          <t>Assistant Professor of Civil and Infrastructure Systems Engineering</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Iowa State University</t>
+          <t>University of Kentucky</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Department of Supply Chain Management, Ivy College of Business</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="n">
-        <v>3</v>
+          <t>Civil and Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>This is a business school position focused on supply chain management rather than transportation engineering or urban mobility systems.</t>
+          <t>The posting is for a broad Civil and Infrastructure Systems Engineering faculty position at the University of Kentucky where transportation is typically encompassed within the civil engineering department.</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Management, Logistics, Operations</t>
+          <t>Civil and Infrastructure Systems, Transportation Engineering, Infrastructure Systems</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Ames, IA</t>
+          <t>Lexington, KY</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
@@ -3628,27 +3628,27 @@
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>Iowa State University seeks a tenure-track Assistant Professor in Supply Chain Management to conduct research and teach courses at the undergraduate, master's, and Ph.D. levels, requiring a doctorate in business administration, supply chain, transportation, logistics, operations, or a related field. | Research Topics: Supply Chain Management, Logistics, Operations</t>
+          <t>The University of Kentucky seeks a tenure-track Assistant Professor in Civil and Infrastructure Systems Engineering within the Department of Civil and Environmental Engineering. | Research Topics: Civil and Infrastructure Systems, Transportation Engineering, Infrastructure Systems</t>
         </is>
       </c>
       <c r="M33" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-in-supply-chain-management-at-iowa-state-university-ivy-college-of-business-4440811209</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179563675&amp;Title=Assistant%20Professor%20of%20Civil%20and%20Infrastructure%20Systems%20Engineering</t>
         </is>
       </c>
       <c r="N33" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="Q33" s="7" t="inlineStr">
@@ -3657,44 +3657,44 @@
         </is>
       </c>
       <c r="R33" s="2" t="n">
-        <v>42.0267567</v>
+        <v>38.0266291</v>
       </c>
       <c r="S33" s="2" t="n">
-        <v>-93.6170448</v>
+        <v>-84.5047222</v>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>e994e392d38b77ce</t>
+          <t>6e03346773ae0b71</t>
         </is>
       </c>
     </row>
     <row r="34" ht="26" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor / Associate Professor (Tenure-Track) in Maritime Studies</t>
+          <t>Faculty Position in Civil Engineering (Transportation and Traffic Engineering)</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Nanyang Technological University</t>
+          <t>University of New Brunswick</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>School of Civil and Environmental Engineering</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="n">
-        <v>3</v>
+          <t>Faculty of Engineering</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>While housed in the School of Civil and Environmental Engineering, this position specifically targets Maritime Studies, shipping decarbonization, and port logistics, diverging from the candidate's core expertise in urban public transit and travel behavior modeling.</t>
+          <t>This is a broad Civil Engineering faculty position that explicitly covers traffic engineering and transportation operations, aligning with the candidate's core subfield.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Sustainable Shipping and Decarbonization, Port Operations and Logistics, Maritime Economics and Digitalisation, Supply Chain Resilience</t>
+          <t>Traffic studies and analysis, Traffic control devices, Intersections and interchanges operations, Traffic accident studies</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Fredericton, New Brunswick</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>Nanyang Technological University seeks tenure-track faculty at all ranks in Maritime Studies within the School of Civil and Environmental Engineering, requiring a Ph.D. in Maritime Studies or a closely related field. | Research Topics: Sustainable Shipping and Decarbonization, Port Operations and Logistics, Maritime Economics and Digitalisation, Supply Chain Resilience</t>
+          <t>The University of New Brunswick seeks a faculty member in Civil Engineering specializing in traffic characteristics, traffic studies, and intersection operations, requiring a Master's or Ph.D. in Civil Engineering or a closely related area. | Research Topics: Traffic studies and analysis, Traffic control devices, Intersections and interchanges operations, Traffic accident studies</t>
         </is>
       </c>
       <c r="M34" s="6" t="inlineStr">
         <is>
-          <t>https://sg.linkedin.com/jobs/view/assistant-professor-associate-professor-tenure-track-associate-professor-practice-track-in-maritime-studies-at-nanyang-technological-university-singapore-4432368242</t>
+          <t>https://ca.linkedin.com/jobs/view/engineering-faculty-of-at-university-of-new-brunswick-4451582209</t>
         </is>
       </c>
       <c r="N34" s="5" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="Q34" s="7" t="inlineStr">
@@ -3749,54 +3749,54 @@
         </is>
       </c>
       <c r="R34" s="2" t="n">
-        <v>1.3483</v>
+        <v>45.9455202</v>
       </c>
       <c r="S34" s="2" t="n">
-        <v>103.6831</v>
+        <v>-66.64018609999999</v>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1e0a7536f9329af5</t>
+          <t>77b43c5491345e72</t>
         </is>
       </c>
     </row>
     <row r="35" ht="26" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Assistant, Associate, or Full Professor of Mechanical and Industrial Engineering</t>
+          <t>Assistant/Associate Professor of Civil, Architectural and Environmental Engineering</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>Missouri University of Science and Technology</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Department of Mechanical and Industrial Engineering</t>
+          <t>Department of Civil, Architectural and Environmental Engineering</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>The position is in Mechanical and Industrial Engineering without a stated focus on transportation engineering, making it a poor fit for the candidate's core profile.</t>
+          <t>This is a general Civil, Architectural and Environmental Engineering faculty opening without an explicitly stated specialization in transportation engineering or transit planning.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Mechanical Engineering, Industrial Engineering</t>
+          <t>Civil Engineering, Architectural Engineering, Environmental Engineering</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>Rolla, MO</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
@@ -3807,32 +3807,32 @@
       <c r="J35" s="5" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>$101,000 - $215,000 per year</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>Open-rank faculty position in mechanical and industrial engineering focusing on general department research areas. | Research Topics: Mechanical Engineering, Industrial Engineering</t>
+          <t>Missouri University of Science and Technology invites applications for an Assistant or Associate Professor position in Civil, Architectural, and Environmental Engineering requiring a relevant doctoral degree. | Research Topics: Civil Engineering, Architectural Engineering, Environmental Engineering</t>
         </is>
       </c>
       <c r="M35" s="6" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179560354&amp;Title=Assistant%2C%20Associate%2C%20Full%20Professor%20%2D%20College%20of%20Engineering%20%2D%20Mechanical%20and%20Industrial%20Engineering%20%2D%20Boston</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-associate-professor-civil-architectural-and-environmental-engineering-%2300096512-at-missouri-university-of-science-and-technology-4442271248</t>
         </is>
       </c>
       <c r="N35" s="5" t="inlineStr">
         <is>
-          <t>HigherEdJobs</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="Q35" s="7" t="inlineStr">
@@ -3841,54 +3841,54 @@
         </is>
       </c>
       <c r="R35" s="2" t="n">
-        <v>42.3351065</v>
+        <v>37.9532435</v>
       </c>
       <c r="S35" s="2" t="n">
-        <v>-71.0892575</v>
+        <v>-91.7742667</v>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>e1042bf3b6aa8057</t>
+          <t>4fad8c46021c1243</t>
         </is>
       </c>
     </row>
     <row r="36" ht="26" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Faculty Openings in Engineering (Open Rank)</t>
+          <t>Assistant Professor of Public Policy</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Singapore Institute of Technology</t>
+          <t>University of Texas at Arlington</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Engineering Cluster</t>
+          <t>Department of Public Affairs &amp; Planning</t>
         </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>While open rank and located in target Singapore, the engineering openings focus on construction materials, tunneling, infrastructure asset maintenance, and power systems rather than transportation planning or travel demand modeling.</t>
+          <t>The position is for an Assistant Professor of Public Policy in a public affairs department, which falls outside the candidate's core expertise in transportation engineering, travel behavior, and mobility systems.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Transport Infrastructure Asset Management, Tunnel Engineering, Construction Technologies, Power and Systems Engineering</t>
+          <t>Public Policy, Urban Studies, Public Infrastructure, Public Administration</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Arlington, TX</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
@@ -3904,12 +3904,12 @@
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>Singapore Institute of Technology is seeking faculty at all ranks across civil, electrical, mechanical, and systems engineering disciplines to support applied learning and translational industry research. | Research Topics: Transport Infrastructure Asset Management, Tunnel Engineering, Construction Technologies, Power and Systems Engineering</t>
+          <t>The University of Texas at Arlington seeks a tenure-track Assistant Professor of Public Policy in the Department of Public Affairs and Planning requiring a Ph.D. in public policy or a related social science discipline. | Research Topics: Public Policy, Urban Studies, Public Infrastructure, Public Administration</t>
         </is>
       </c>
       <c r="M36" s="6" t="inlineStr">
         <is>
-          <t>https://sg.linkedin.com/jobs/view/faculty-openings-in-engineering-at-singapore-institute-of-technology-4273859333</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-at-excel-campus-activities-4464851831</t>
         </is>
       </c>
       <c r="N36" s="5" t="inlineStr">
@@ -3919,12 +3919,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="Q36" s="7" t="inlineStr">
@@ -3933,31 +3933,31 @@
         </is>
       </c>
       <c r="R36" s="2" t="n">
-        <v>1.4123197</v>
+        <v>32.7315155</v>
       </c>
       <c r="S36" s="2" t="n">
-        <v>103.9094621</v>
+        <v>-97.1171533</v>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>f21dc0b6a181929c</t>
+          <t>15704bb25858281c</t>
         </is>
       </c>
     </row>
     <row r="37" ht="26" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Assistant/Associate/Full Professor in Industrial and Systems Engineering</t>
+          <t>Assistant Professor in Supply Chain Management</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>University of Florida</t>
+          <t>Iowa State University</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Department of Industrial and Systems Engineering</t>
+          <t>Department of Supply Chain Management, Ivy College of Business</t>
         </is>
       </c>
       <c r="D37" s="5" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Although transportation is mentioned as a potential application area, the primary focus of this Industrial and Systems Engineering position is on Industrialized Construction and 3D construction printing rather than core transportation engineering, mobility, or travel behavior.</t>
+          <t>This is a business school position focused on supply chain management rather than transportation engineering or urban mobility systems.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Industrialized Construction, Artificial Intelligence, Digital Twins, Operations Research</t>
+          <t>Supply Chain Management, Logistics, Operations</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Gainesville, FL</t>
+          <t>Ames, IA</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
@@ -3991,17 +3991,17 @@
       <c r="J37" s="5" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>Salary is commensurate with education and experience.</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>This full-time tenured or tenure-track faculty position in Industrial and Systems Engineering at the University of Florida seeks expertise in industrialized construction and related technologies, requiring a Ph.D. in ISE, Manufacturing Engineering, Civil Engineering, Mechanical Engineering, or a closely related field. | Research Topics: Industrialized Construction, Artificial Intelligence, Digital Twins, Operations Research</t>
+          <t>Iowa State University seeks a tenure-track Assistant Professor in Supply Chain Management to conduct research and teach courses at the undergraduate, master's, and Ph.D. levels, requiring a doctorate in business administration, supply chain, transportation, logistics, operations, or a related field. | Research Topics: Supply Chain Management, Logistics, Operations</t>
         </is>
       </c>
       <c r="M37" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-associate-full-professor-industrial-systems-engineering-at-university-of-florida-4323668785</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-in-supply-chain-management-at-iowa-state-university-ivy-college-of-business-4440811209</t>
         </is>
       </c>
       <c r="N37" s="5" t="inlineStr">
@@ -4025,44 +4025,44 @@
         </is>
       </c>
       <c r="R37" s="2" t="n">
-        <v>29.6436</v>
+        <v>42.0267567</v>
       </c>
       <c r="S37" s="2" t="n">
-        <v>-82.3549</v>
+        <v>-93.6170448</v>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>56d501f448e77e05</t>
+          <t>e994e392d38b77ce</t>
         </is>
       </c>
     </row>
     <row r="38" ht="26" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Assistant / Associate Professor of Industrial and Systems Engineering</t>
+          <t>Assistant Professor / Associate Professor (Tenure-Track) in Maritime Studies</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>University of Washington</t>
+          <t>Nanyang Technological University</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Industrial &amp; Systems Engineering</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="n">
-        <v>6</v>
+          <t>School of Civil and Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Assistant Professor position in Systems Engineering that aligns with the candidate's expertise in AI-enabled systems and smart mobility through the lens of cyber-physical and autonomous systems.</t>
+          <t>While housed in the School of Civil and Environmental Engineering, this position specifically targets Maritime Studies, shipping decarbonization, and port logistics, diverging from the candidate's core expertise in urban public transit and travel behavior modeling.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Systems Engineering, Autonomous Systems, Cyber-Physical Systems, AI-Enabled Systems Engineering</t>
+          <t>Sustainable Shipping and Decarbonization, Port Operations and Logistics, Maritime Economics and Digitalisation, Supply Chain Resilience</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
@@ -4072,47 +4072,43 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>Priority: 2026-09-15 / Open until filled</t>
-        </is>
-      </c>
-      <c r="J38" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>$12,000 – $17,000 per month (9-month service period)</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>The Department of Industrial and Systems Engineering at the University of Washington seeks an Assistant or Associate Professor specializing in Systems Engineering, requiring a Ph.D. in Systems Engineering, Industrial Engineering, or a related discipline. | Research Topics: Systems Engineering, Autonomous Systems, Cyber-Physical Systems, AI-Enabled Systems Engineering</t>
+          <t>Nanyang Technological University seeks tenure-track faculty at all ranks in Maritime Studies within the School of Civil and Environmental Engineering, requiring a Ph.D. in Maritime Studies or a closely related field. | Research Topics: Sustainable Shipping and Decarbonization, Port Operations and Logistics, Maritime Economics and Digitalisation, Supply Chain Resilience</t>
         </is>
       </c>
       <c r="M38" s="6" t="inlineStr">
         <is>
-          <t>https://engineering.academickeys.com/job/g4m97a60/AssistantAssociate-Professor-Industrial-and-Systems-Engineering-Systems-Engineering-Focus</t>
+          <t>https://sg.linkedin.com/jobs/view/assistant-professor-associate-professor-tenure-track-associate-professor-practice-track-in-maritime-studies-at-nanyang-technological-university-singapore-4432368242</t>
         </is>
       </c>
       <c r="N38" s="5" t="inlineStr">
         <is>
-          <t>AcademicKeys</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="Q38" s="7" t="inlineStr">
@@ -4121,31 +4117,31 @@
         </is>
       </c>
       <c r="R38" s="2" t="n">
-        <v>47.6553</v>
+        <v>1.3483</v>
       </c>
       <c r="S38" s="2" t="n">
-        <v>-122.3035</v>
+        <v>103.6831</v>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>9d5682cf4dbca334</t>
+          <t>1e0a7536f9329af5</t>
         </is>
       </c>
     </row>
     <row r="39" ht="26" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Tenure-Track Assistant/Associate Professor of Air Transportation Systems</t>
+          <t>Assistant, Associate, or Full Professor of Mechanical and Industrial Engineering</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Embry-Riddle Aeronautical University</t>
+          <t>Northeastern University</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>School of Graduate Studies, College of Aviation</t>
+          <t>Department of Mechanical and Industrial Engineering</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
@@ -4153,62 +4149,58 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>The position focuses specifically on air transportation systems, advanced air mobility, and aviation, which falls outside the candidate's core background in ground-based transportation engineering and public transit planning.</t>
+          <t>The position is in Mechanical and Industrial Engineering without a stated focus on transportation engineering, making it a poor fit for the candidate's core profile.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Air Transportation Systems, Advanced Air Mobility, UAS Traffic Management, Machine Learning/AI in Aviation</t>
+          <t>Mechanical Engineering, Industrial Engineering</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Unspecified</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>Priority: 2026-08-31 / Open until filled</t>
-        </is>
-      </c>
-      <c r="J39" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>Competitive Salary</t>
+          <t>$101,000 - $215,000 per year</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>Embry-Riddle Aeronautical University seeks a tenure-track faculty member in air transportation systems and advanced air mobility requiring a doctorate and relevant experience. | Research Topics: Air Transportation Systems, Advanced Air Mobility, UAS Traffic Management, Machine Learning/AI in Aviation</t>
+          <t>Open-rank faculty position in mechanical and industrial engineering focusing on general department research areas. | Research Topics: Mechanical Engineering, Industrial Engineering</t>
         </is>
       </c>
       <c r="M39" s="6" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38012134/tenure-track-faculty-position-with-a-focus-on-air-transportation-systems-daytona-beach-campus/</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179560354&amp;Title=Assistant%2C%20Associate%2C%20Full%20Professor%20%2D%20College%20of%20Engineering%20%2D%20Mechanical%20and%20Industrial%20Engineering%20%2D%20Boston</t>
         </is>
       </c>
       <c r="N39" s="5" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Q39" s="7" t="inlineStr">
@@ -4217,236 +4209,228 @@
         </is>
       </c>
       <c r="R39" s="2" t="n">
-        <v>29.1895</v>
+        <v>42.3351065</v>
       </c>
       <c r="S39" s="2" t="n">
-        <v>-81.04940000000001</v>
+        <v>-71.0892575</v>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>52969a207999417a</t>
+          <t>e1042bf3b6aa8057</t>
         </is>
       </c>
     </row>
     <row r="40" ht="26" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Transportation Engineering</t>
+          <t>Faculty Openings in Engineering (Open Rank)</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>South Dakota State University</t>
+          <t>Singapore Institute of Technology</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Department of Civil and Environmental Engineering</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="n">
-        <v>9</v>
+          <t>Engineering Cluster</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>This is a tenure-track Assistant Professor position in Transportation Engineering within a Civil and Environmental Engineering department, perfectly aligning with the candidate's core research profile.</t>
+          <t>While open rank and located in target Singapore, the engineering openings focus on construction materials, tunneling, infrastructure asset maintenance, and power systems rather than transportation planning or travel demand modeling.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Intelligent Transportation Systems, Transportation Data Analytics, Traffic Operations, Resilient Transportation Systems</t>
+          <t>Transport Infrastructure Asset Management, Tunnel Engineering, Construction Technologies, Power and Systems Engineering</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Unspecified</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Brookings, SD</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="J40" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>Starting at $92,000</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>South Dakota State University seeks a tenure-track Assistant Professor in Transportation Engineering to teach undergraduate and graduate courses, advise students, and develop an externally funded research program requiring a Ph.D. in Civil Engineering or a closely related field. | Research Topics: Intelligent Transportation Systems, Transportation Data Analytics, Traffic Operations, Resilient Transportation Systems</t>
+          <t>Singapore Institute of Technology is seeking faculty at all ranks across civil, electrical, mechanical, and systems engineering disciplines to support applied learning and translational industry research. | Research Topics: Transport Infrastructure Asset Management, Tunnel Engineering, Construction Technologies, Power and Systems Engineering</t>
         </is>
       </c>
       <c r="M40" s="6" t="inlineStr">
         <is>
-          <t>https://engineering.academickeys.com/job/m4lk5asr/Assistant-Professor-of-Transportation-Engineering</t>
+          <t>https://sg.linkedin.com/jobs/view/faculty-openings-in-engineering-at-singapore-institute-of-technology-4273859333</t>
         </is>
       </c>
       <c r="N40" s="5" t="inlineStr">
         <is>
-          <t>AcademicKeys</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="Q40" s="9" t="inlineStr">
-        <is>
-          <t>Past Due</t>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="Q40" s="7" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
       <c r="R40" s="2" t="n">
-        <v>44.344449</v>
+        <v>1.4123197</v>
       </c>
       <c r="S40" s="2" t="n">
-        <v>-96.79823709999999</v>
+        <v>103.9094621</v>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>9b7d5de4753a514b</t>
+          <t>f21dc0b6a181929c</t>
         </is>
       </c>
     </row>
     <row r="41" ht="26" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Clinical Assistant Professor</t>
+          <t>Assistant/Associate/Full Professor in Industrial and Systems Engineering</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Georgia State University</t>
+          <t>University of Florida</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Department of Public Management and Policy</t>
+          <t>Department of Industrial and Systems Engineering</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>This is a non-tenure-track clinical position in public management and policy focusing on teaching data analytics and urban planning, which is a poor fit for a candidate targeting research-active tenure-track positions in transportation engineering.</t>
+          <t>Although transportation is mentioned as a potential application area, the primary focus of this Industrial and Systems Engineering position is on Industrialized Construction and 3D construction printing rather than core transportation engineering, mobility, or travel behavior.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Policy Analytics, Urban Planning, Data Visualization, GIS Applications</t>
+          <t>Industrialized Construction, Artificial Intelligence, Digital Twins, Operations Research</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Non-Tenure Track</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Gainesville, FL</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="J41" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>$80,000-$90,000</t>
+          <t>Salary is commensurate with education and experience.</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>A non-tenure-track clinical assistant professor position focusing on teaching policy analytics, urban planning, and GIS, requiring a Ph.D. in a related field and university teaching experience. | Research Topics: Policy Analytics, Urban Planning, Data Visualization, GIS Applications</t>
+          <t>This full-time tenured or tenure-track faculty position in Industrial and Systems Engineering at the University of Florida seeks expertise in industrialized construction and related technologies, requiring a Ph.D. in ISE, Manufacturing Engineering, Civil Engineering, Mechanical Engineering, or a closely related field. | Research Topics: Industrialized Construction, Artificial Intelligence, Digital Twins, Operations Research</t>
         </is>
       </c>
       <c r="M41" s="6" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38022215/clinical-assistant-professor-non-tenure-tack/</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-associate-full-professor-industrial-systems-engineering-at-university-of-florida-4323668785</t>
         </is>
       </c>
       <c r="N41" s="5" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="Q41" s="9" t="inlineStr">
-        <is>
-          <t>Past Due</t>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Q41" s="7" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
       <c r="R41" s="2" t="n">
-        <v>33.7535889</v>
+        <v>29.6436</v>
       </c>
       <c r="S41" s="2" t="n">
-        <v>-84.3854209</v>
+        <v>-82.3549</v>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>f39f14cbaaf9d6f7</t>
+          <t>56d501f448e77e05</t>
         </is>
       </c>
     </row>
     <row r="42" ht="26" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor in Transportation Policy</t>
+          <t>Assistant / Associate Professor of Industrial and Systems Engineering</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Hunter College</t>
+          <t>University of Washington</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Department of Urban Policy and Planning</t>
+          <t>Industrial &amp; Systems Engineering</t>
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Strong interdisciplinary fit for an Assistant Professor position focusing on transportation policy and planning within an urban policy department.</t>
+          <t>Assistant Professor position in Systems Engineering that aligns with the candidate's expertise in AI-enabled systems and smart mobility through the lens of cyber-physical and autonomous systems.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Transportation Policy, Transportation Advocacy &amp; Accessibility, Community-Engaged Research, Urban Planning</t>
+          <t>Systems Engineering, Autonomous Systems, Cyber-Physical Systems, AI-Enabled Systems Engineering</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
@@ -4456,42 +4440,42 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>Open until filled</t>
+          <t>Priority: 2026-09-15 / Open until filled</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>$77,092 - $91,922</t>
+          <t>$12,000 – $17,000 per month (9-month service period)</t>
         </is>
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>Hunter College seeks a tenure-track Assistant Professor in transportation policy to teach graduate students and conduct community-engaged research, requiring a Ph.D. in policy, planning, or a related field specializing in transportation. | Research Topics: Transportation Policy, Transportation Advocacy &amp; Accessibility, Community-Engaged Research, Urban Planning</t>
+          <t>The Department of Industrial and Systems Engineering at the University of Washington seeks an Assistant or Associate Professor specializing in Systems Engineering, requiring a Ph.D. in Systems Engineering, Industrial Engineering, or a related discipline. | Research Topics: Systems Engineering, Autonomous Systems, Cyber-Physical Systems, AI-Enabled Systems Engineering</t>
         </is>
       </c>
       <c r="M42" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-%E2%80%93-urban-policy-and-planning-dept-school-of-arts-and-sciences-hunter-college-at-hunter-college-4438624127</t>
+          <t>https://engineering.academickeys.com/job/g4m97a60/AssistantAssociate-Professor-Industrial-and-Systems-Engineering-Systems-Engineering-Focus</t>
         </is>
       </c>
       <c r="N42" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>AcademicKeys</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -4505,108 +4489,492 @@
         </is>
       </c>
       <c r="R42" s="2" t="n">
-        <v>40.7683107</v>
+        <v>47.6553</v>
       </c>
       <c r="S42" s="2" t="n">
-        <v>-73.964406</v>
+        <v>-122.3035</v>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>e4e18ed629103a27</t>
+          <t>9d5682cf4dbca334</t>
         </is>
       </c>
     </row>
     <row r="43" ht="26" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>Tenure-Track Assistant/Associate Professor of Air Transportation Systems</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Embry-Riddle Aeronautical University</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>School of Graduate Studies, College of Aviation</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>The position focuses specifically on air transportation systems, advanced air mobility, and aviation, which falls outside the candidate's core background in ground-based transportation engineering and public transit planning.</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Air Transportation Systems, Advanced Air Mobility, UAS Traffic Management, Machine Learning/AI in Aviation</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>Tenure-Track</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Daytona Beach, FL</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>Priority: 2026-08-31 / Open until filled</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>Competitive Salary</t>
+        </is>
+      </c>
+      <c r="L43" s="4" t="inlineStr">
+        <is>
+          <t>Embry-Riddle Aeronautical University seeks a tenure-track faculty member in air transportation systems and advanced air mobility requiring a doctorate and relevant experience. | Research Topics: Air Transportation Systems, Advanced Air Mobility, UAS Traffic Management, Machine Learning/AI in Aviation</t>
+        </is>
+      </c>
+      <c r="M43" s="6" t="inlineStr">
+        <is>
+          <t>https://jobs.chronicle.com/job/38012134/tenure-track-faculty-position-with-a-focus-on-air-transportation-systems-daytona-beach-campus/</t>
+        </is>
+      </c>
+      <c r="N43" s="5" t="inlineStr">
+        <is>
+          <t>Chronicle</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Q43" s="7" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="n">
+        <v>29.1895</v>
+      </c>
+      <c r="S43" s="2" t="n">
+        <v>-81.04940000000001</v>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>52969a207999417a</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="26" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Transportation Engineering</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>South Dakota State University</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Department of Civil and Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>This is a tenure-track Assistant Professor position in Transportation Engineering within a Civil and Environmental Engineering department, perfectly aligning with the candidate's core research profile.</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Intelligent Transportation Systems, Transportation Data Analytics, Traffic Operations, Resilient Transportation Systems</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>Tenure-Track</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Brookings, SD</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>Starting at $92,000</t>
+        </is>
+      </c>
+      <c r="L44" s="4" t="inlineStr">
+        <is>
+          <t>South Dakota State University seeks a tenure-track Assistant Professor in Transportation Engineering to teach undergraduate and graduate courses, advise students, and develop an externally funded research program requiring a Ph.D. in Civil Engineering or a closely related field. | Research Topics: Intelligent Transportation Systems, Transportation Data Analytics, Traffic Operations, Resilient Transportation Systems</t>
+        </is>
+      </c>
+      <c r="M44" s="6" t="inlineStr">
+        <is>
+          <t>https://engineering.academickeys.com/job/m4lk5asr/Assistant-Professor-of-Transportation-Engineering</t>
+        </is>
+      </c>
+      <c r="N44" s="5" t="inlineStr">
+        <is>
+          <t>AcademicKeys</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Q44" s="9" t="inlineStr">
+        <is>
+          <t>Past Due</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="n">
+        <v>44.344449</v>
+      </c>
+      <c r="S44" s="2" t="n">
+        <v>-96.79823709999999</v>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>9b7d5de4753a514b</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="26" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Clinical Assistant Professor</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Georgia State University</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Department of Public Management and Policy</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>This is a non-tenure-track clinical position in public management and policy focusing on teaching data analytics and urban planning, which is a poor fit for a candidate targeting research-active tenure-track positions in transportation engineering.</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Policy Analytics, Urban Planning, Data Visualization, GIS Applications</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>Non-Tenure Track</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>$80,000-$90,000</t>
+        </is>
+      </c>
+      <c r="L45" s="4" t="inlineStr">
+        <is>
+          <t>A non-tenure-track clinical assistant professor position focusing on teaching policy analytics, urban planning, and GIS, requiring a Ph.D. in a related field and university teaching experience. | Research Topics: Policy Analytics, Urban Planning, Data Visualization, GIS Applications</t>
+        </is>
+      </c>
+      <c r="M45" s="6" t="inlineStr">
+        <is>
+          <t>https://jobs.chronicle.com/job/38022215/clinical-assistant-professor-non-tenure-tack/</t>
+        </is>
+      </c>
+      <c r="N45" s="5" t="inlineStr">
+        <is>
+          <t>Chronicle</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Q45" s="9" t="inlineStr">
+        <is>
+          <t>Past Due</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="n">
+        <v>33.7535889</v>
+      </c>
+      <c r="S45" s="2" t="n">
+        <v>-84.3854209</v>
+      </c>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t>f39f14cbaaf9d6f7</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="26" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Professor in Transportation Policy</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Hunter College</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Department of Urban Policy and Planning</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>Strong interdisciplinary fit for an Assistant Professor position focusing on transportation policy and planning within an urban policy department.</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Transportation Policy, Transportation Advocacy &amp; Accessibility, Community-Engaged Research, Urban Planning</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>Tenure-Track</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>$77,092 - $91,922</t>
+        </is>
+      </c>
+      <c r="L46" s="4" t="inlineStr">
+        <is>
+          <t>Hunter College seeks a tenure-track Assistant Professor in transportation policy to teach graduate students and conduct community-engaged research, requiring a Ph.D. in policy, planning, or a related field specializing in transportation. | Research Topics: Transportation Policy, Transportation Advocacy &amp; Accessibility, Community-Engaged Research, Urban Planning</t>
+        </is>
+      </c>
+      <c r="M46" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-%E2%80%93-urban-policy-and-planning-dept-school-of-arts-and-sciences-hunter-college-at-hunter-college-4438624127</t>
+        </is>
+      </c>
+      <c r="N46" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Q46" s="7" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="n">
+        <v>40.7683107</v>
+      </c>
+      <c r="S46" s="2" t="n">
+        <v>-73.964406</v>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>e4e18ed629103a27</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="26" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
           <t>Full/Associate/Assistant Professor in Modern Civil Engineering</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>University of Macau</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>Department of Civil and Environmental Engineering (CEE)</t>
         </is>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="D47" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="E43" s="4" t="inlineStr">
+      <c r="E47" s="4" t="inlineStr">
         <is>
           <t>The posting is an open-rank faculty search in modern civil engineering which may encompass transportation, but lacks sufficient departmental subfield details in the short snippet.</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Modern Civil Engineering, Transportation Engineering, Urban Systems</t>
         </is>
       </c>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="G47" s="5" t="inlineStr">
         <is>
           <t>Unspecified</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>Macao</t>
         </is>
       </c>
-      <c r="I43" s="5" t="inlineStr">
+      <c r="I47" s="5" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="J43" s="5" t="inlineStr">
+      <c r="J47" s="5" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="K43" s="2" t="inlineStr">
+      <c r="K47" s="2" t="inlineStr">
         <is>
           <t>£87,465.51 to £127,834.20 starting salary</t>
         </is>
       </c>
-      <c r="L43" s="4" t="inlineStr">
+      <c r="L47" s="4" t="inlineStr">
         <is>
           <t>The University of Macau seeks a faculty member in modern civil engineering within the Department of Civil and Environmental Engineering. | Research Topics: Modern Civil Engineering, Transportation Engineering, Urban Systems</t>
         </is>
       </c>
-      <c r="M43" s="6" t="inlineStr">
+      <c r="M47" s="6" t="inlineStr">
         <is>
           <t>https://www.jobs.ac.uk/job/DSL575/full-associate-assistant-professor-in-modern-civil-engineering</t>
         </is>
       </c>
-      <c r="N43" s="5" t="inlineStr">
+      <c r="N47" s="5" t="inlineStr">
         <is>
           <t>Jobs.ac.uk</t>
         </is>
       </c>
-      <c r="O43" s="2" t="inlineStr">
+      <c r="O47" s="2" t="inlineStr">
         <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="Q43" s="9" t="inlineStr">
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="Q47" s="9" t="inlineStr">
         <is>
           <t>Past Due</t>
         </is>
       </c>
-      <c r="R43" s="2" t="n">
+      <c r="R47" s="2" t="n">
         <v>22.1285</v>
       </c>
-      <c r="S43" s="2" t="n">
+      <c r="S47" s="2" t="n">
         <v>113.5438</v>
       </c>
-      <c r="T43" s="2" t="inlineStr">
+      <c r="T47" s="2" t="inlineStr">
         <is>
           <t>600dff84e8f0a0b2</t>
         </is>
@@ -4656,6 +5024,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M47" r:id="rId46"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T47"/>
+  <dimension ref="A1:T48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Q7" s="7" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Q12" s="7" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Q13" s="7" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Q18" s="7" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Q22" s="7" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Q24" s="7" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Q25" s="7" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Q27" s="7" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Q30" s="7" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Q33" s="7" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Q34" s="7" t="inlineStr">
@@ -3832,7 +3832,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Q35" s="7" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Q38" s="7" t="inlineStr">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Q40" s="7" t="inlineStr">
@@ -4407,30 +4407,30 @@
     <row r="42" ht="26" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Assistant / Associate Professor of Industrial and Systems Engineering</t>
+          <t>Assistant Professor in Industrial and Systems Engineering - Quantum Optimization</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>University of Washington</t>
+          <t>University of Missouri</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Industrial &amp; Systems Engineering</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="n">
-        <v>6</v>
+          <t>Department of Industrial and Manufacturing Engineering</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Assistant Professor position in Systems Engineering that aligns with the candidate's expertise in AI-enabled systems and smart mobility through the lens of cyber-physical and autonomous systems.</t>
+          <t>Screened out due to an excessive focus on quantum optimization within industrial and systems engineering, which lacks a core transportation or mobility planning component.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Systems Engineering, Autonomous Systems, Cyber-Physical Systems, AI-Enabled Systems Engineering</t>
+          <t>Industrial and Systems Engineering, Quantum Optimization, Operations Research</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
@@ -4440,47 +4440,43 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Columbia, MO</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>Priority: 2026-09-15 / Open until filled</t>
-        </is>
-      </c>
-      <c r="J42" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>$12,000 – $17,000 per month (9-month service period)</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>The Department of Industrial and Systems Engineering at the University of Washington seeks an Assistant or Associate Professor specializing in Systems Engineering, requiring a Ph.D. in Systems Engineering, Industrial Engineering, or a related discipline. | Research Topics: Systems Engineering, Autonomous Systems, Cyber-Physical Systems, AI-Enabled Systems Engineering</t>
+          <t>This tenure-track assistant professor position focuses on quantum optimization within industrial and systems engineering, requiring a Ph.D. in a relevant engineering or scientific discipline. | Research Topics: Industrial and Systems Engineering, Quantum Optimization, Operations Research</t>
         </is>
       </c>
       <c r="M42" s="6" t="inlineStr">
         <is>
-          <t>https://engineering.academickeys.com/job/g4m97a60/AssistantAssociate-Professor-Industrial-and-Systems-Engineering-Systems-Engineering-Focus</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179565194&amp;Title=Assistant%20Professor%20in%20Industrial%20and%20Systems%20Engineering%20%2D%20Quantum%20Optimization</t>
         </is>
       </c>
       <c r="N42" s="5" t="inlineStr">
         <is>
-          <t>AcademicKeys</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Q42" s="7" t="inlineStr">
@@ -4489,44 +4485,44 @@
         </is>
       </c>
       <c r="R42" s="2" t="n">
-        <v>47.6553</v>
+        <v>38.9364147</v>
       </c>
       <c r="S42" s="2" t="n">
-        <v>-122.3035</v>
+        <v>-92.32970299999999</v>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>9d5682cf4dbca334</t>
+          <t>f13a6da0148df3dd</t>
         </is>
       </c>
     </row>
     <row r="43" ht="26" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Tenure-Track Assistant/Associate Professor of Air Transportation Systems</t>
+          <t>Assistant / Associate Professor of Industrial and Systems Engineering</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Embry-Riddle Aeronautical University</t>
+          <t>University of Washington</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>School of Graduate Studies, College of Aviation</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="n">
-        <v>3</v>
+          <t>Industrial &amp; Systems Engineering</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>The position focuses specifically on air transportation systems, advanced air mobility, and aviation, which falls outside the candidate's core background in ground-based transportation engineering and public transit planning.</t>
+          <t>Assistant Professor position in Systems Engineering that aligns with the candidate's expertise in AI-enabled systems and smart mobility through the lens of cyber-physical and autonomous systems.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Air Transportation Systems, Advanced Air Mobility, UAS Traffic Management, Machine Learning/AI in Aviation</t>
+          <t>Systems Engineering, Autonomous Systems, Cyber-Physical Systems, AI-Enabled Systems Engineering</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -4536,37 +4532,37 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>Priority: 2026-08-31 / Open until filled</t>
+          <t>Priority: 2026-09-15 / Open until filled</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>Competitive Salary</t>
+          <t>$12,000 – $17,000 per month (9-month service period)</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>Embry-Riddle Aeronautical University seeks a tenure-track faculty member in air transportation systems and advanced air mobility requiring a doctorate and relevant experience. | Research Topics: Air Transportation Systems, Advanced Air Mobility, UAS Traffic Management, Machine Learning/AI in Aviation</t>
+          <t>The Department of Industrial and Systems Engineering at the University of Washington seeks an Assistant or Associate Professor specializing in Systems Engineering, requiring a Ph.D. in Systems Engineering, Industrial Engineering, or a related discipline. | Research Topics: Systems Engineering, Autonomous Systems, Cyber-Physical Systems, AI-Enabled Systems Engineering</t>
         </is>
       </c>
       <c r="M43" s="6" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38012134/tenure-track-faculty-position-with-a-focus-on-air-transportation-systems-daytona-beach-campus/</t>
+          <t>https://engineering.academickeys.com/job/g4m97a60/AssistantAssociate-Professor-Industrial-and-Systems-Engineering-Systems-Engineering-Focus</t>
         </is>
       </c>
       <c r="N43" s="5" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>AcademicKeys</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
@@ -4576,7 +4572,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="Q43" s="7" t="inlineStr">
@@ -4585,44 +4581,44 @@
         </is>
       </c>
       <c r="R43" s="2" t="n">
-        <v>29.1895</v>
+        <v>47.6553</v>
       </c>
       <c r="S43" s="2" t="n">
-        <v>-81.04940000000001</v>
+        <v>-122.3035</v>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>52969a207999417a</t>
+          <t>9d5682cf4dbca334</t>
         </is>
       </c>
     </row>
     <row r="44" ht="26" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Transportation Engineering</t>
+          <t>Tenure-Track Assistant/Associate Professor of Air Transportation Systems</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>South Dakota State University</t>
+          <t>Embry-Riddle Aeronautical University</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Department of Civil and Environmental Engineering</t>
-        </is>
-      </c>
-      <c r="D44" s="8" t="n">
-        <v>9</v>
+          <t>School of Graduate Studies, College of Aviation</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>This is a tenure-track Assistant Professor position in Transportation Engineering within a Civil and Environmental Engineering department, perfectly aligning with the candidate's core research profile.</t>
+          <t>The position focuses specifically on air transportation systems, advanced air mobility, and aviation, which falls outside the candidate's core background in ground-based transportation engineering and public transit planning.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Intelligent Transportation Systems, Transportation Data Analytics, Traffic Operations, Resilient Transportation Systems</t>
+          <t>Air Transportation Systems, Advanced Air Mobility, UAS Traffic Management, Machine Learning/AI in Aviation</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
@@ -4632,143 +4628,143 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Brookings, SD</t>
+          <t>Daytona Beach, FL</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>Priority: 2026-08-31 / Open until filled</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>Starting at $92,000</t>
+          <t>Competitive Salary</t>
         </is>
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>South Dakota State University seeks a tenure-track Assistant Professor in Transportation Engineering to teach undergraduate and graduate courses, advise students, and develop an externally funded research program requiring a Ph.D. in Civil Engineering or a closely related field. | Research Topics: Intelligent Transportation Systems, Transportation Data Analytics, Traffic Operations, Resilient Transportation Systems</t>
+          <t>Embry-Riddle Aeronautical University seeks a tenure-track faculty member in air transportation systems and advanced air mobility requiring a doctorate and relevant experience. | Research Topics: Air Transportation Systems, Advanced Air Mobility, UAS Traffic Management, Machine Learning/AI in Aviation</t>
         </is>
       </c>
       <c r="M44" s="6" t="inlineStr">
         <is>
-          <t>https://engineering.academickeys.com/job/m4lk5asr/Assistant-Professor-of-Transportation-Engineering</t>
+          <t>https://jobs.chronicle.com/job/38012134/tenure-track-faculty-position-with-a-focus-on-air-transportation-systems-daytona-beach-campus/</t>
         </is>
       </c>
       <c r="N44" s="5" t="inlineStr">
         <is>
-          <t>AcademicKeys</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="Q44" s="9" t="inlineStr">
-        <is>
-          <t>Past Due</t>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Q44" s="7" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
       <c r="R44" s="2" t="n">
-        <v>44.344449</v>
+        <v>29.1895</v>
       </c>
       <c r="S44" s="2" t="n">
-        <v>-96.79823709999999</v>
+        <v>-81.04940000000001</v>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>9b7d5de4753a514b</t>
+          <t>52969a207999417a</t>
         </is>
       </c>
     </row>
     <row r="45" ht="26" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Clinical Assistant Professor</t>
+          <t>Assistant Professor of Transportation Engineering</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Georgia State University</t>
+          <t>South Dakota State University</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Department of Public Management and Policy</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="n">
-        <v>4</v>
+          <t>Department of Civil and Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="n">
+        <v>9</v>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>This is a non-tenure-track clinical position in public management and policy focusing on teaching data analytics and urban planning, which is a poor fit for a candidate targeting research-active tenure-track positions in transportation engineering.</t>
+          <t>This is a tenure-track Assistant Professor position in Transportation Engineering within a Civil and Environmental Engineering department, perfectly aligning with the candidate's core research profile.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Policy Analytics, Urban Planning, Data Visualization, GIS Applications</t>
+          <t>Intelligent Transportation Systems, Transportation Data Analytics, Traffic Operations, Resilient Transportation Systems</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>Non-Tenure Track</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Brookings, SD</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>$80,000-$90,000</t>
+          <t>Starting at $92,000</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>A non-tenure-track clinical assistant professor position focusing on teaching policy analytics, urban planning, and GIS, requiring a Ph.D. in a related field and university teaching experience. | Research Topics: Policy Analytics, Urban Planning, Data Visualization, GIS Applications</t>
+          <t>South Dakota State University seeks a tenure-track Assistant Professor in Transportation Engineering to teach undergraduate and graduate courses, advise students, and develop an externally funded research program requiring a Ph.D. in Civil Engineering or a closely related field. | Research Topics: Intelligent Transportation Systems, Transportation Data Analytics, Traffic Operations, Resilient Transportation Systems</t>
         </is>
       </c>
       <c r="M45" s="6" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38022215/clinical-assistant-professor-non-tenure-tack/</t>
+          <t>https://engineering.academickeys.com/job/m4lk5asr/Assistant-Professor-of-Transportation-Engineering</t>
         </is>
       </c>
       <c r="N45" s="5" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>AcademicKeys</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="Q45" s="9" t="inlineStr">
@@ -4777,204 +4773,300 @@
         </is>
       </c>
       <c r="R45" s="2" t="n">
-        <v>33.7535889</v>
+        <v>44.344449</v>
       </c>
       <c r="S45" s="2" t="n">
-        <v>-84.3854209</v>
+        <v>-96.79823709999999</v>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>f39f14cbaaf9d6f7</t>
+          <t>9b7d5de4753a514b</t>
         </is>
       </c>
     </row>
     <row r="46" ht="26" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor in Transportation Policy</t>
+          <t>Clinical Assistant Professor</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Hunter College</t>
+          <t>Georgia State University</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Department of Urban Policy and Planning</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="n">
-        <v>7</v>
+          <t>Department of Public Management and Policy</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>Strong interdisciplinary fit for an Assistant Professor position focusing on transportation policy and planning within an urban policy department.</t>
+          <t>This is a non-tenure-track clinical position in public management and policy focusing on teaching data analytics and urban planning, which is a poor fit for a candidate targeting research-active tenure-track positions in transportation engineering.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Transportation Policy, Transportation Advocacy &amp; Accessibility, Community-Engaged Research, Urban Planning</t>
+          <t>Policy Analytics, Urban Planning, Data Visualization, GIS Applications</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Non-Tenure Track</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>Open until filled</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>$77,092 - $91,922</t>
+          <t>$80,000-$90,000</t>
         </is>
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>Hunter College seeks a tenure-track Assistant Professor in transportation policy to teach graduate students and conduct community-engaged research, requiring a Ph.D. in policy, planning, or a related field specializing in transportation. | Research Topics: Transportation Policy, Transportation Advocacy &amp; Accessibility, Community-Engaged Research, Urban Planning</t>
+          <t>A non-tenure-track clinical assistant professor position focusing on teaching policy analytics, urban planning, and GIS, requiring a Ph.D. in a related field and university teaching experience. | Research Topics: Policy Analytics, Urban Planning, Data Visualization, GIS Applications</t>
         </is>
       </c>
       <c r="M46" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-%E2%80%93-urban-policy-and-planning-dept-school-of-arts-and-sciences-hunter-college-at-hunter-college-4438624127</t>
+          <t>https://jobs.chronicle.com/job/38022215/clinical-assistant-professor-non-tenure-tack/</t>
         </is>
       </c>
       <c r="N46" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="Q46" s="7" t="inlineStr">
-        <is>
-          <t>Active</t>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Q46" s="9" t="inlineStr">
+        <is>
+          <t>Past Due</t>
         </is>
       </c>
       <c r="R46" s="2" t="n">
-        <v>40.7683107</v>
+        <v>33.7535889</v>
       </c>
       <c r="S46" s="2" t="n">
-        <v>-73.964406</v>
+        <v>-84.3854209</v>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>e4e18ed629103a27</t>
+          <t>f39f14cbaaf9d6f7</t>
         </is>
       </c>
     </row>
     <row r="47" ht="26" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>Assistant Professor in Transportation Policy</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Hunter College</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Department of Urban Policy and Planning</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>Strong interdisciplinary fit for an Assistant Professor position focusing on transportation policy and planning within an urban policy department.</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Transportation Policy, Transportation Advocacy &amp; Accessibility, Community-Engaged Research, Urban Planning</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>Tenure-Track</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>$77,092 - $91,922</t>
+        </is>
+      </c>
+      <c r="L47" s="4" t="inlineStr">
+        <is>
+          <t>Hunter College seeks a tenure-track Assistant Professor in transportation policy to teach graduate students and conduct community-engaged research, requiring a Ph.D. in policy, planning, or a related field specializing in transportation. | Research Topics: Transportation Policy, Transportation Advocacy &amp; Accessibility, Community-Engaged Research, Urban Planning</t>
+        </is>
+      </c>
+      <c r="M47" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-%E2%80%93-urban-policy-and-planning-dept-school-of-arts-and-sciences-hunter-college-at-hunter-college-4438624127</t>
+        </is>
+      </c>
+      <c r="N47" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Q47" s="7" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="n">
+        <v>40.7683107</v>
+      </c>
+      <c r="S47" s="2" t="n">
+        <v>-73.964406</v>
+      </c>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>e4e18ed629103a27</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="26" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
           <t>Full/Associate/Assistant Professor in Modern Civil Engineering</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>University of Macau</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>Department of Civil and Environmental Engineering (CEE)</t>
         </is>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="D48" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="E47" s="4" t="inlineStr">
+      <c r="E48" s="4" t="inlineStr">
         <is>
           <t>The posting is an open-rank faculty search in modern civil engineering which may encompass transportation, but lacks sufficient departmental subfield details in the short snippet.</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Modern Civil Engineering, Transportation Engineering, Urban Systems</t>
         </is>
       </c>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="G48" s="5" t="inlineStr">
         <is>
           <t>Unspecified</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Macao</t>
         </is>
       </c>
-      <c r="I47" s="5" t="inlineStr">
+      <c r="I48" s="5" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="J47" s="5" t="inlineStr">
+      <c r="J48" s="5" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="K47" s="2" t="inlineStr">
+      <c r="K48" s="2" t="inlineStr">
         <is>
           <t>£87,465.51 to £127,834.20 starting salary</t>
         </is>
       </c>
-      <c r="L47" s="4" t="inlineStr">
+      <c r="L48" s="4" t="inlineStr">
         <is>
           <t>The University of Macau seeks a faculty member in modern civil engineering within the Department of Civil and Environmental Engineering. | Research Topics: Modern Civil Engineering, Transportation Engineering, Urban Systems</t>
         </is>
       </c>
-      <c r="M47" s="6" t="inlineStr">
+      <c r="M48" s="6" t="inlineStr">
         <is>
           <t>https://www.jobs.ac.uk/job/DSL575/full-associate-assistant-professor-in-modern-civil-engineering</t>
         </is>
       </c>
-      <c r="N47" s="5" t="inlineStr">
+      <c r="N48" s="5" t="inlineStr">
         <is>
           <t>Jobs.ac.uk</t>
         </is>
       </c>
-      <c r="O47" s="2" t="inlineStr">
+      <c r="O48" s="2" t="inlineStr">
         <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="P47" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="Q47" s="9" t="inlineStr">
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Q48" s="9" t="inlineStr">
         <is>
           <t>Past Due</t>
         </is>
       </c>
-      <c r="R47" s="2" t="n">
+      <c r="R48" s="2" t="n">
         <v>22.1285</v>
       </c>
-      <c r="S47" s="2" t="n">
+      <c r="S48" s="2" t="n">
         <v>113.5438</v>
       </c>
-      <c r="T47" s="2" t="inlineStr">
+      <c r="T48" s="2" t="inlineStr">
         <is>
           <t>600dff84e8f0a0b2</t>
         </is>
@@ -5028,6 +5120,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M45" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M48" r:id="rId47"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T48"/>
+  <dimension ref="A1:T49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="Q7" s="7" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="Q12" s="7" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="Q13" s="7" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="Q18" s="7" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="Q22" s="7" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="Q25" s="7" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="Q30" s="7" t="inlineStr">
@@ -3671,17 +3671,17 @@
     <row r="34" ht="26" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Faculty Position in Civil Engineering (Transportation and Traffic Engineering)</t>
+          <t>Assistant Professor in Urban Analytics</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>University of New Brunswick</t>
+          <t>University of Massachusetts - Boston</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Faculty of Engineering</t>
+          <t>Urban Studies and Planning</t>
         </is>
       </c>
       <c r="D34" s="3" t="n">
@@ -3689,12 +3689,12 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>This is a broad Civil Engineering faculty position that explicitly covers traffic engineering and transportation operations, aligning with the candidate's core subfield.</t>
+          <t>This Assistant Professor in Urban Analytics within Urban Studies and Planning offers a broad interdisciplinary fit for the candidate's travel behavior and spatial data analysis expertise.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Traffic studies and analysis, Traffic control devices, Intersections and interchanges operations, Traffic accident studies</t>
+          <t>Urban Analytics, Spatial Data Analysis, Travel Behavior, Urban Planning</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Fredericton, New Brunswick</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
@@ -3715,32 +3715,32 @@
       <c r="J34" s="5" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>$80,000 - $98,003 per year</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>The University of New Brunswick seeks a faculty member in Civil Engineering specializing in traffic characteristics, traffic studies, and intersection operations, requiring a Master's or Ph.D. in Civil Engineering or a closely related area. | Research Topics: Traffic studies and analysis, Traffic control devices, Intersections and interchanges operations, Traffic accident studies</t>
+          <t>This tenure-track Assistant Professor position in Urban Analytics seeks faculty expertise in urban data methods with a relevant doctoral degree. | Research Topics: Urban Analytics, Spatial Data Analysis, Travel Behavior, Urban Planning</t>
         </is>
       </c>
       <c r="M34" s="6" t="inlineStr">
         <is>
-          <t>https://ca.linkedin.com/jobs/view/engineering-faculty-of-at-university-of-new-brunswick-4451582209</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179566167&amp;Title=Assistant%20Professor%20%2D%20Urban%20Analytics</t>
         </is>
       </c>
       <c r="N34" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="Q34" s="7" t="inlineStr">
@@ -3749,44 +3749,44 @@
         </is>
       </c>
       <c r="R34" s="2" t="n">
-        <v>45.9455202</v>
+        <v>42.314068</v>
       </c>
       <c r="S34" s="2" t="n">
-        <v>-66.64018609999999</v>
+        <v>-71.0387132</v>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>77b43c5491345e72</t>
+          <t>b984f007b128f638</t>
         </is>
       </c>
     </row>
     <row r="35" ht="26" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Assistant/Associate Professor of Civil, Architectural and Environmental Engineering</t>
+          <t>Faculty Position in Civil Engineering (Transportation and Traffic Engineering)</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Missouri University of Science and Technology</t>
+          <t>University of New Brunswick</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Department of Civil, Architectural and Environmental Engineering</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>4</v>
+          <t>Faculty of Engineering</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>This is a general Civil, Architectural and Environmental Engineering faculty opening without an explicitly stated specialization in transportation engineering or transit planning.</t>
+          <t>This is a broad Civil Engineering faculty position that explicitly covers traffic engineering and transportation operations, aligning with the candidate's core subfield.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Civil Engineering, Architectural Engineering, Environmental Engineering</t>
+          <t>Traffic studies and analysis, Traffic control devices, Intersections and interchanges operations, Traffic accident studies</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Rolla, MO</t>
+          <t>Fredericton, New Brunswick</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>Missouri University of Science and Technology invites applications for an Assistant or Associate Professor position in Civil, Architectural, and Environmental Engineering requiring a relevant doctoral degree. | Research Topics: Civil Engineering, Architectural Engineering, Environmental Engineering</t>
+          <t>The University of New Brunswick seeks a faculty member in Civil Engineering specializing in traffic characteristics, traffic studies, and intersection operations, requiring a Master's or Ph.D. in Civil Engineering or a closely related area. | Research Topics: Traffic studies and analysis, Traffic control devices, Intersections and interchanges operations, Traffic accident studies</t>
         </is>
       </c>
       <c r="M35" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-associate-professor-civil-architectural-and-environmental-engineering-%2300096512-at-missouri-university-of-science-and-technology-4442271248</t>
+          <t>https://ca.linkedin.com/jobs/view/engineering-faculty-of-at-university-of-new-brunswick-4451582209</t>
         </is>
       </c>
       <c r="N35" s="5" t="inlineStr">
@@ -3832,7 +3832,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="Q35" s="7" t="inlineStr">
@@ -3841,31 +3841,31 @@
         </is>
       </c>
       <c r="R35" s="2" t="n">
-        <v>37.9532435</v>
+        <v>45.9455202</v>
       </c>
       <c r="S35" s="2" t="n">
-        <v>-91.7742667</v>
+        <v>-66.64018609999999</v>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>4fad8c46021c1243</t>
+          <t>77b43c5491345e72</t>
         </is>
       </c>
     </row>
     <row r="36" ht="26" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Public Policy</t>
+          <t>Assistant/Associate Professor of Civil, Architectural and Environmental Engineering</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>University of Texas at Arlington</t>
+          <t>Missouri University of Science and Technology</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Department of Public Affairs &amp; Planning</t>
+          <t>Department of Civil, Architectural and Environmental Engineering</t>
         </is>
       </c>
       <c r="D36" s="5" t="n">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>The position is for an Assistant Professor of Public Policy in a public affairs department, which falls outside the candidate's core expertise in transportation engineering, travel behavior, and mobility systems.</t>
+          <t>This is a general Civil, Architectural and Environmental Engineering faculty opening without an explicitly stated specialization in transportation engineering or transit planning.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Public Policy, Urban Studies, Public Infrastructure, Public Administration</t>
+          <t>Civil Engineering, Architectural Engineering, Environmental Engineering</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Arlington, TX</t>
+          <t>Rolla, MO</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
@@ -3904,12 +3904,12 @@
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>The University of Texas at Arlington seeks a tenure-track Assistant Professor of Public Policy in the Department of Public Affairs and Planning requiring a Ph.D. in public policy or a related social science discipline. | Research Topics: Public Policy, Urban Studies, Public Infrastructure, Public Administration</t>
+          <t>Missouri University of Science and Technology invites applications for an Assistant or Associate Professor position in Civil, Architectural, and Environmental Engineering requiring a relevant doctoral degree. | Research Topics: Civil Engineering, Architectural Engineering, Environmental Engineering</t>
         </is>
       </c>
       <c r="M36" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-at-excel-campus-activities-4464851831</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-associate-professor-civil-architectural-and-environmental-engineering-%2300096512-at-missouri-university-of-science-and-technology-4442271248</t>
         </is>
       </c>
       <c r="N36" s="5" t="inlineStr">
@@ -3919,12 +3919,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="Q36" s="7" t="inlineStr">
@@ -3933,44 +3933,44 @@
         </is>
       </c>
       <c r="R36" s="2" t="n">
-        <v>32.7315155</v>
+        <v>37.9532435</v>
       </c>
       <c r="S36" s="2" t="n">
-        <v>-97.1171533</v>
+        <v>-91.7742667</v>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>15704bb25858281c</t>
+          <t>4fad8c46021c1243</t>
         </is>
       </c>
     </row>
     <row r="37" ht="26" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor in Supply Chain Management</t>
+          <t>Assistant Professor of Public Policy</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Iowa State University</t>
+          <t>University of Texas at Arlington</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Department of Supply Chain Management, Ivy College of Business</t>
+          <t>Department of Public Affairs &amp; Planning</t>
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>This is a business school position focused on supply chain management rather than transportation engineering or urban mobility systems.</t>
+          <t>The position is for an Assistant Professor of Public Policy in a public affairs department, which falls outside the candidate's core expertise in transportation engineering, travel behavior, and mobility systems.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Management, Logistics, Operations</t>
+          <t>Public Policy, Urban Studies, Public Infrastructure, Public Administration</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Ames, IA</t>
+          <t>Arlington, TX</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>Iowa State University seeks a tenure-track Assistant Professor in Supply Chain Management to conduct research and teach courses at the undergraduate, master's, and Ph.D. levels, requiring a doctorate in business administration, supply chain, transportation, logistics, operations, or a related field. | Research Topics: Supply Chain Management, Logistics, Operations</t>
+          <t>The University of Texas at Arlington seeks a tenure-track Assistant Professor of Public Policy in the Department of Public Affairs and Planning requiring a Ph.D. in public policy or a related social science discipline. | Research Topics: Public Policy, Urban Studies, Public Infrastructure, Public Administration</t>
         </is>
       </c>
       <c r="M37" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-in-supply-chain-management-at-iowa-state-university-ivy-college-of-business-4440811209</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-at-excel-campus-activities-4464851831</t>
         </is>
       </c>
       <c r="N37" s="5" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="Q37" s="7" t="inlineStr">
@@ -4025,31 +4025,31 @@
         </is>
       </c>
       <c r="R37" s="2" t="n">
-        <v>42.0267567</v>
+        <v>32.7315155</v>
       </c>
       <c r="S37" s="2" t="n">
-        <v>-93.6170448</v>
+        <v>-97.1171533</v>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>e994e392d38b77ce</t>
+          <t>15704bb25858281c</t>
         </is>
       </c>
     </row>
     <row r="38" ht="26" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor / Associate Professor (Tenure-Track) in Maritime Studies</t>
+          <t>Assistant Professor in Supply Chain Management</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Nanyang Technological University</t>
+          <t>Iowa State University</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>School of Civil and Environmental Engineering</t>
+          <t>Department of Supply Chain Management, Ivy College of Business</t>
         </is>
       </c>
       <c r="D38" s="5" t="n">
@@ -4057,12 +4057,12 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>While housed in the School of Civil and Environmental Engineering, this position specifically targets Maritime Studies, shipping decarbonization, and port logistics, diverging from the candidate's core expertise in urban public transit and travel behavior modeling.</t>
+          <t>This is a business school position focused on supply chain management rather than transportation engineering or urban mobility systems.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Sustainable Shipping and Decarbonization, Port Operations and Logistics, Maritime Economics and Digitalisation, Supply Chain Resilience</t>
+          <t>Supply Chain Management, Logistics, Operations</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Ames, IA</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>Nanyang Technological University seeks tenure-track faculty at all ranks in Maritime Studies within the School of Civil and Environmental Engineering, requiring a Ph.D. in Maritime Studies or a closely related field. | Research Topics: Sustainable Shipping and Decarbonization, Port Operations and Logistics, Maritime Economics and Digitalisation, Supply Chain Resilience</t>
+          <t>Iowa State University seeks a tenure-track Assistant Professor in Supply Chain Management to conduct research and teach courses at the undergraduate, master's, and Ph.D. levels, requiring a doctorate in business administration, supply chain, transportation, logistics, operations, or a related field. | Research Topics: Supply Chain Management, Logistics, Operations</t>
         </is>
       </c>
       <c r="M38" s="6" t="inlineStr">
         <is>
-          <t>https://sg.linkedin.com/jobs/view/assistant-professor-associate-professor-tenure-track-associate-professor-practice-track-in-maritime-studies-at-nanyang-technological-university-singapore-4432368242</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-in-supply-chain-management-at-iowa-state-university-ivy-college-of-business-4440811209</t>
         </is>
       </c>
       <c r="N38" s="5" t="inlineStr">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="Q38" s="7" t="inlineStr">
@@ -4117,31 +4117,31 @@
         </is>
       </c>
       <c r="R38" s="2" t="n">
-        <v>1.3483</v>
+        <v>42.0267567</v>
       </c>
       <c r="S38" s="2" t="n">
-        <v>103.6831</v>
+        <v>-93.6170448</v>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1e0a7536f9329af5</t>
+          <t>e994e392d38b77ce</t>
         </is>
       </c>
     </row>
     <row r="39" ht="26" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Assistant, Associate, or Full Professor of Mechanical and Industrial Engineering</t>
+          <t>Assistant Professor / Associate Professor (Tenure-Track) in Maritime Studies</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>Nanyang Technological University</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Department of Mechanical and Industrial Engineering</t>
+          <t>School of Civil and Environmental Engineering</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
@@ -4149,22 +4149,22 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>The position is in Mechanical and Industrial Engineering without a stated focus on transportation engineering, making it a poor fit for the candidate's core profile.</t>
+          <t>While housed in the School of Civil and Environmental Engineering, this position specifically targets Maritime Studies, shipping decarbonization, and port logistics, diverging from the candidate's core expertise in urban public transit and travel behavior modeling.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Mechanical Engineering, Industrial Engineering</t>
+          <t>Sustainable Shipping and Decarbonization, Port Operations and Logistics, Maritime Economics and Digitalisation, Supply Chain Resilience</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
@@ -4175,32 +4175,32 @@
       <c r="J39" s="5" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>$101,000 - $215,000 per year</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>Open-rank faculty position in mechanical and industrial engineering focusing on general department research areas. | Research Topics: Mechanical Engineering, Industrial Engineering</t>
+          <t>Nanyang Technological University seeks tenure-track faculty at all ranks in Maritime Studies within the School of Civil and Environmental Engineering, requiring a Ph.D. in Maritime Studies or a closely related field. | Research Topics: Sustainable Shipping and Decarbonization, Port Operations and Logistics, Maritime Economics and Digitalisation, Supply Chain Resilience</t>
         </is>
       </c>
       <c r="M39" s="6" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179560354&amp;Title=Assistant%2C%20Associate%2C%20Full%20Professor%20%2D%20College%20of%20Engineering%20%2D%20Mechanical%20and%20Industrial%20Engineering%20%2D%20Boston</t>
+          <t>https://sg.linkedin.com/jobs/view/assistant-professor-associate-professor-tenure-track-associate-professor-practice-track-in-maritime-studies-at-nanyang-technological-university-singapore-4432368242</t>
         </is>
       </c>
       <c r="N39" s="5" t="inlineStr">
         <is>
-          <t>HigherEdJobs</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="Q39" s="7" t="inlineStr">
@@ -4209,31 +4209,31 @@
         </is>
       </c>
       <c r="R39" s="2" t="n">
-        <v>42.3351065</v>
+        <v>1.3483</v>
       </c>
       <c r="S39" s="2" t="n">
-        <v>-71.0892575</v>
+        <v>103.6831</v>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>e1042bf3b6aa8057</t>
+          <t>1e0a7536f9329af5</t>
         </is>
       </c>
     </row>
     <row r="40" ht="26" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Faculty Openings in Engineering (Open Rank)</t>
+          <t>Assistant, Associate, or Full Professor of Mechanical and Industrial Engineering</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Singapore Institute of Technology</t>
+          <t>Northeastern University</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Engineering Cluster</t>
+          <t>Department of Mechanical and Industrial Engineering</t>
         </is>
       </c>
       <c r="D40" s="5" t="n">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>While open rank and located in target Singapore, the engineering openings focus on construction materials, tunneling, infrastructure asset maintenance, and power systems rather than transportation planning or travel demand modeling.</t>
+          <t>The position is in Mechanical and Industrial Engineering without a stated focus on transportation engineering, making it a poor fit for the candidate's core profile.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Transport Infrastructure Asset Management, Tunnel Engineering, Construction Technologies, Power and Systems Engineering</t>
+          <t>Mechanical Engineering, Industrial Engineering</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
@@ -4267,32 +4267,32 @@
       <c r="J40" s="5" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>$101,000 - $215,000 per year</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>Singapore Institute of Technology is seeking faculty at all ranks across civil, electrical, mechanical, and systems engineering disciplines to support applied learning and translational industry research. | Research Topics: Transport Infrastructure Asset Management, Tunnel Engineering, Construction Technologies, Power and Systems Engineering</t>
+          <t>Open-rank faculty position in mechanical and industrial engineering focusing on general department research areas. | Research Topics: Mechanical Engineering, Industrial Engineering</t>
         </is>
       </c>
       <c r="M40" s="6" t="inlineStr">
         <is>
-          <t>https://sg.linkedin.com/jobs/view/faculty-openings-in-engineering-at-singapore-institute-of-technology-4273859333</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179560354&amp;Title=Assistant%2C%20Associate%2C%20Full%20Professor%20%2D%20College%20of%20Engineering%20%2D%20Mechanical%20and%20Industrial%20Engineering%20%2D%20Boston</t>
         </is>
       </c>
       <c r="N40" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Q40" s="7" t="inlineStr">
@@ -4301,31 +4301,31 @@
         </is>
       </c>
       <c r="R40" s="2" t="n">
-        <v>1.4123197</v>
+        <v>42.3351065</v>
       </c>
       <c r="S40" s="2" t="n">
-        <v>103.9094621</v>
+        <v>-71.0892575</v>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>f21dc0b6a181929c</t>
+          <t>e1042bf3b6aa8057</t>
         </is>
       </c>
     </row>
     <row r="41" ht="26" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Assistant/Associate/Full Professor in Industrial and Systems Engineering</t>
+          <t>Faculty Openings in Engineering (Open Rank)</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>University of Florida</t>
+          <t>Singapore Institute of Technology</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Department of Industrial and Systems Engineering</t>
+          <t>Engineering Cluster</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
@@ -4333,22 +4333,22 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Although transportation is mentioned as a potential application area, the primary focus of this Industrial and Systems Engineering position is on Industrialized Construction and 3D construction printing rather than core transportation engineering, mobility, or travel behavior.</t>
+          <t>While open rank and located in target Singapore, the engineering openings focus on construction materials, tunneling, infrastructure asset maintenance, and power systems rather than transportation planning or travel demand modeling.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Industrialized Construction, Artificial Intelligence, Digital Twins, Operations Research</t>
+          <t>Transport Infrastructure Asset Management, Tunnel Engineering, Construction Technologies, Power and Systems Engineering</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Unspecified</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Gainesville, FL</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
@@ -4359,17 +4359,17 @@
       <c r="J41" s="5" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>Salary is commensurate with education and experience.</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>This full-time tenured or tenure-track faculty position in Industrial and Systems Engineering at the University of Florida seeks expertise in industrialized construction and related technologies, requiring a Ph.D. in ISE, Manufacturing Engineering, Civil Engineering, Mechanical Engineering, or a closely related field. | Research Topics: Industrialized Construction, Artificial Intelligence, Digital Twins, Operations Research</t>
+          <t>Singapore Institute of Technology is seeking faculty at all ranks across civil, electrical, mechanical, and systems engineering disciplines to support applied learning and translational industry research. | Research Topics: Transport Infrastructure Asset Management, Tunnel Engineering, Construction Technologies, Power and Systems Engineering</t>
         </is>
       </c>
       <c r="M41" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-associate-full-professor-industrial-systems-engineering-at-university-of-florida-4323668785</t>
+          <t>https://sg.linkedin.com/jobs/view/faculty-openings-in-engineering-at-singapore-institute-of-technology-4273859333</t>
         </is>
       </c>
       <c r="N41" s="5" t="inlineStr">
@@ -4379,12 +4379,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="Q41" s="7" t="inlineStr">
@@ -4393,31 +4393,31 @@
         </is>
       </c>
       <c r="R41" s="2" t="n">
-        <v>29.6436</v>
+        <v>1.4123197</v>
       </c>
       <c r="S41" s="2" t="n">
-        <v>-82.3549</v>
+        <v>103.9094621</v>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>56d501f448e77e05</t>
+          <t>f21dc0b6a181929c</t>
         </is>
       </c>
     </row>
     <row r="42" ht="26" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor in Industrial and Systems Engineering - Quantum Optimization</t>
+          <t>Assistant/Associate/Full Professor in Industrial and Systems Engineering</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>University of Missouri</t>
+          <t>University of Florida</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Department of Industrial and Manufacturing Engineering</t>
+          <t>Department of Industrial and Systems Engineering</t>
         </is>
       </c>
       <c r="D42" s="5" t="n">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Screened out due to an excessive focus on quantum optimization within industrial and systems engineering, which lacks a core transportation or mobility planning component.</t>
+          <t>Although transportation is mentioned as a potential application area, the primary focus of this Industrial and Systems Engineering position is on Industrialized Construction and 3D construction printing rather than core transportation engineering, mobility, or travel behavior.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Industrial and Systems Engineering, Quantum Optimization, Operations Research</t>
+          <t>Industrialized Construction, Artificial Intelligence, Digital Twins, Operations Research</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Columbia, MO</t>
+          <t>Gainesville, FL</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr">
@@ -4451,32 +4451,32 @@
       <c r="J42" s="5" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Salary is commensurate with education and experience.</t>
         </is>
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>This tenure-track assistant professor position focuses on quantum optimization within industrial and systems engineering, requiring a Ph.D. in a relevant engineering or scientific discipline. | Research Topics: Industrial and Systems Engineering, Quantum Optimization, Operations Research</t>
+          <t>This full-time tenured or tenure-track faculty position in Industrial and Systems Engineering at the University of Florida seeks expertise in industrialized construction and related technologies, requiring a Ph.D. in ISE, Manufacturing Engineering, Civil Engineering, Mechanical Engineering, or a closely related field. | Research Topics: Industrialized Construction, Artificial Intelligence, Digital Twins, Operations Research</t>
         </is>
       </c>
       <c r="M42" s="6" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179565194&amp;Title=Assistant%20Professor%20in%20Industrial%20and%20Systems%20Engineering%20%2D%20Quantum%20Optimization</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-associate-full-professor-industrial-systems-engineering-at-university-of-florida-4323668785</t>
         </is>
       </c>
       <c r="N42" s="5" t="inlineStr">
         <is>
-          <t>HigherEdJobs</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="Q42" s="7" t="inlineStr">
@@ -4485,44 +4485,44 @@
         </is>
       </c>
       <c r="R42" s="2" t="n">
-        <v>38.9364147</v>
+        <v>29.6436</v>
       </c>
       <c r="S42" s="2" t="n">
-        <v>-92.32970299999999</v>
+        <v>-82.3549</v>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>f13a6da0148df3dd</t>
+          <t>56d501f448e77e05</t>
         </is>
       </c>
     </row>
     <row r="43" ht="26" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Assistant / Associate Professor of Industrial and Systems Engineering</t>
+          <t>Assistant Professor in Industrial and Systems Engineering - Quantum Optimization</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>University of Washington</t>
+          <t>University of Missouri</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Industrial &amp; Systems Engineering</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="n">
-        <v>6</v>
+          <t>Department of Industrial and Manufacturing Engineering</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Assistant Professor position in Systems Engineering that aligns with the candidate's expertise in AI-enabled systems and smart mobility through the lens of cyber-physical and autonomous systems.</t>
+          <t>Screened out due to an excessive focus on quantum optimization within industrial and systems engineering, which lacks a core transportation or mobility planning component.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Systems Engineering, Autonomous Systems, Cyber-Physical Systems, AI-Enabled Systems Engineering</t>
+          <t>Industrial and Systems Engineering, Quantum Optimization, Operations Research</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -4532,47 +4532,43 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Columbia, MO</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>Priority: 2026-09-15 / Open until filled</t>
-        </is>
-      </c>
-      <c r="J43" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>$12,000 – $17,000 per month (9-month service period)</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>The Department of Industrial and Systems Engineering at the University of Washington seeks an Assistant or Associate Professor specializing in Systems Engineering, requiring a Ph.D. in Systems Engineering, Industrial Engineering, or a related discipline. | Research Topics: Systems Engineering, Autonomous Systems, Cyber-Physical Systems, AI-Enabled Systems Engineering</t>
+          <t>This tenure-track assistant professor position focuses on quantum optimization within industrial and systems engineering, requiring a Ph.D. in a relevant engineering or scientific discipline. | Research Topics: Industrial and Systems Engineering, Quantum Optimization, Operations Research</t>
         </is>
       </c>
       <c r="M43" s="6" t="inlineStr">
         <is>
-          <t>https://engineering.academickeys.com/job/g4m97a60/AssistantAssociate-Professor-Industrial-and-Systems-Engineering-Systems-Engineering-Focus</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179565194&amp;Title=Assistant%20Professor%20in%20Industrial%20and%20Systems%20Engineering%20%2D%20Quantum%20Optimization</t>
         </is>
       </c>
       <c r="N43" s="5" t="inlineStr">
         <is>
-          <t>AcademicKeys</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="Q43" s="7" t="inlineStr">
@@ -4581,44 +4577,44 @@
         </is>
       </c>
       <c r="R43" s="2" t="n">
-        <v>47.6553</v>
+        <v>38.9364147</v>
       </c>
       <c r="S43" s="2" t="n">
-        <v>-122.3035</v>
+        <v>-92.32970299999999</v>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>9d5682cf4dbca334</t>
+          <t>f13a6da0148df3dd</t>
         </is>
       </c>
     </row>
     <row r="44" ht="26" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Tenure-Track Assistant/Associate Professor of Air Transportation Systems</t>
+          <t>Assistant / Associate Professor of Industrial and Systems Engineering</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Embry-Riddle Aeronautical University</t>
+          <t>University of Washington</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>School of Graduate Studies, College of Aviation</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="n">
-        <v>3</v>
+          <t>Industrial &amp; Systems Engineering</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>The position focuses specifically on air transportation systems, advanced air mobility, and aviation, which falls outside the candidate's core background in ground-based transportation engineering and public transit planning.</t>
+          <t>Assistant Professor position in Systems Engineering that aligns with the candidate's expertise in AI-enabled systems and smart mobility through the lens of cyber-physical and autonomous systems.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Air Transportation Systems, Advanced Air Mobility, UAS Traffic Management, Machine Learning/AI in Aviation</t>
+          <t>Systems Engineering, Autonomous Systems, Cyber-Physical Systems, AI-Enabled Systems Engineering</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
@@ -4628,37 +4624,37 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>Priority: 2026-08-31 / Open until filled</t>
+          <t>Priority: 2026-09-15 / Open until filled</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>Competitive Salary</t>
+          <t>$12,000 – $17,000 per month (9-month service period)</t>
         </is>
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>Embry-Riddle Aeronautical University seeks a tenure-track faculty member in air transportation systems and advanced air mobility requiring a doctorate and relevant experience. | Research Topics: Air Transportation Systems, Advanced Air Mobility, UAS Traffic Management, Machine Learning/AI in Aviation</t>
+          <t>The Department of Industrial and Systems Engineering at the University of Washington seeks an Assistant or Associate Professor specializing in Systems Engineering, requiring a Ph.D. in Systems Engineering, Industrial Engineering, or a related discipline. | Research Topics: Systems Engineering, Autonomous Systems, Cyber-Physical Systems, AI-Enabled Systems Engineering</t>
         </is>
       </c>
       <c r="M44" s="6" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38012134/tenure-track-faculty-position-with-a-focus-on-air-transportation-systems-daytona-beach-campus/</t>
+          <t>https://engineering.academickeys.com/job/g4m97a60/AssistantAssociate-Professor-Industrial-and-Systems-Engineering-Systems-Engineering-Focus</t>
         </is>
       </c>
       <c r="N44" s="5" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>AcademicKeys</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
@@ -4668,7 +4664,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="Q44" s="7" t="inlineStr">
@@ -4677,44 +4673,44 @@
         </is>
       </c>
       <c r="R44" s="2" t="n">
-        <v>29.1895</v>
+        <v>47.6553</v>
       </c>
       <c r="S44" s="2" t="n">
-        <v>-81.04940000000001</v>
+        <v>-122.3035</v>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>52969a207999417a</t>
+          <t>9d5682cf4dbca334</t>
         </is>
       </c>
     </row>
     <row r="45" ht="26" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Transportation Engineering</t>
+          <t>Tenure-Track Assistant/Associate Professor of Air Transportation Systems</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>South Dakota State University</t>
+          <t>Embry-Riddle Aeronautical University</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Department of Civil and Environmental Engineering</t>
-        </is>
-      </c>
-      <c r="D45" s="8" t="n">
-        <v>9</v>
+          <t>School of Graduate Studies, College of Aviation</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>This is a tenure-track Assistant Professor position in Transportation Engineering within a Civil and Environmental Engineering department, perfectly aligning with the candidate's core research profile.</t>
+          <t>The position focuses specifically on air transportation systems, advanced air mobility, and aviation, which falls outside the candidate's core background in ground-based transportation engineering and public transit planning.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Intelligent Transportation Systems, Transportation Data Analytics, Traffic Operations, Resilient Transportation Systems</t>
+          <t>Air Transportation Systems, Advanced Air Mobility, UAS Traffic Management, Machine Learning/AI in Aviation</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -4724,143 +4720,143 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Brookings, SD</t>
+          <t>Daytona Beach, FL</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>Priority: 2026-08-31 / Open until filled</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>Starting at $92,000</t>
+          <t>Competitive Salary</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>South Dakota State University seeks a tenure-track Assistant Professor in Transportation Engineering to teach undergraduate and graduate courses, advise students, and develop an externally funded research program requiring a Ph.D. in Civil Engineering or a closely related field. | Research Topics: Intelligent Transportation Systems, Transportation Data Analytics, Traffic Operations, Resilient Transportation Systems</t>
+          <t>Embry-Riddle Aeronautical University seeks a tenure-track faculty member in air transportation systems and advanced air mobility requiring a doctorate and relevant experience. | Research Topics: Air Transportation Systems, Advanced Air Mobility, UAS Traffic Management, Machine Learning/AI in Aviation</t>
         </is>
       </c>
       <c r="M45" s="6" t="inlineStr">
         <is>
-          <t>https://engineering.academickeys.com/job/m4lk5asr/Assistant-Professor-of-Transportation-Engineering</t>
+          <t>https://jobs.chronicle.com/job/38012134/tenure-track-faculty-position-with-a-focus-on-air-transportation-systems-daytona-beach-campus/</t>
         </is>
       </c>
       <c r="N45" s="5" t="inlineStr">
         <is>
-          <t>AcademicKeys</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="Q45" s="9" t="inlineStr">
-        <is>
-          <t>Past Due</t>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Q45" s="7" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
       <c r="R45" s="2" t="n">
-        <v>44.344449</v>
+        <v>29.1895</v>
       </c>
       <c r="S45" s="2" t="n">
-        <v>-96.79823709999999</v>
+        <v>-81.04940000000001</v>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>9b7d5de4753a514b</t>
+          <t>52969a207999417a</t>
         </is>
       </c>
     </row>
     <row r="46" ht="26" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Clinical Assistant Professor</t>
+          <t>Assistant Professor of Transportation Engineering</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Georgia State University</t>
+          <t>South Dakota State University</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Department of Public Management and Policy</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="n">
-        <v>4</v>
+          <t>Department of Civil and Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="n">
+        <v>9</v>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>This is a non-tenure-track clinical position in public management and policy focusing on teaching data analytics and urban planning, which is a poor fit for a candidate targeting research-active tenure-track positions in transportation engineering.</t>
+          <t>This is a tenure-track Assistant Professor position in Transportation Engineering within a Civil and Environmental Engineering department, perfectly aligning with the candidate's core research profile.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Policy Analytics, Urban Planning, Data Visualization, GIS Applications</t>
+          <t>Intelligent Transportation Systems, Transportation Data Analytics, Traffic Operations, Resilient Transportation Systems</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>Non-Tenure Track</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Brookings, SD</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>$80,000-$90,000</t>
+          <t>Starting at $92,000</t>
         </is>
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>A non-tenure-track clinical assistant professor position focusing on teaching policy analytics, urban planning, and GIS, requiring a Ph.D. in a related field and university teaching experience. | Research Topics: Policy Analytics, Urban Planning, Data Visualization, GIS Applications</t>
+          <t>South Dakota State University seeks a tenure-track Assistant Professor in Transportation Engineering to teach undergraduate and graduate courses, advise students, and develop an externally funded research program requiring a Ph.D. in Civil Engineering or a closely related field. | Research Topics: Intelligent Transportation Systems, Transportation Data Analytics, Traffic Operations, Resilient Transportation Systems</t>
         </is>
       </c>
       <c r="M46" s="6" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38022215/clinical-assistant-professor-non-tenure-tack/</t>
+          <t>https://engineering.academickeys.com/job/m4lk5asr/Assistant-Professor-of-Transportation-Engineering</t>
         </is>
       </c>
       <c r="N46" s="5" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>AcademicKeys</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="Q46" s="9" t="inlineStr">
@@ -4869,204 +4865,300 @@
         </is>
       </c>
       <c r="R46" s="2" t="n">
-        <v>33.7535889</v>
+        <v>44.344449</v>
       </c>
       <c r="S46" s="2" t="n">
-        <v>-84.3854209</v>
+        <v>-96.79823709999999</v>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>f39f14cbaaf9d6f7</t>
+          <t>9b7d5de4753a514b</t>
         </is>
       </c>
     </row>
     <row r="47" ht="26" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor in Transportation Policy</t>
+          <t>Clinical Assistant Professor</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Hunter College</t>
+          <t>Georgia State University</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Department of Urban Policy and Planning</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="n">
-        <v>7</v>
+          <t>Department of Public Management and Policy</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Strong interdisciplinary fit for an Assistant Professor position focusing on transportation policy and planning within an urban policy department.</t>
+          <t>This is a non-tenure-track clinical position in public management and policy focusing on teaching data analytics and urban planning, which is a poor fit for a candidate targeting research-active tenure-track positions in transportation engineering.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Transportation Policy, Transportation Advocacy &amp; Accessibility, Community-Engaged Research, Urban Planning</t>
+          <t>Policy Analytics, Urban Planning, Data Visualization, GIS Applications</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Non-Tenure Track</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>Open until filled</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>$77,092 - $91,922</t>
+          <t>$80,000-$90,000</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>Hunter College seeks a tenure-track Assistant Professor in transportation policy to teach graduate students and conduct community-engaged research, requiring a Ph.D. in policy, planning, or a related field specializing in transportation. | Research Topics: Transportation Policy, Transportation Advocacy &amp; Accessibility, Community-Engaged Research, Urban Planning</t>
+          <t>A non-tenure-track clinical assistant professor position focusing on teaching policy analytics, urban planning, and GIS, requiring a Ph.D. in a related field and university teaching experience. | Research Topics: Policy Analytics, Urban Planning, Data Visualization, GIS Applications</t>
         </is>
       </c>
       <c r="M47" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-%E2%80%93-urban-policy-and-planning-dept-school-of-arts-and-sciences-hunter-college-at-hunter-college-4438624127</t>
+          <t>https://jobs.chronicle.com/job/38022215/clinical-assistant-professor-non-tenure-tack/</t>
         </is>
       </c>
       <c r="N47" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="Q47" s="7" t="inlineStr">
-        <is>
-          <t>Active</t>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Q47" s="9" t="inlineStr">
+        <is>
+          <t>Past Due</t>
         </is>
       </c>
       <c r="R47" s="2" t="n">
-        <v>40.7683107</v>
+        <v>33.7535889</v>
       </c>
       <c r="S47" s="2" t="n">
-        <v>-73.964406</v>
+        <v>-84.3854209</v>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>e4e18ed629103a27</t>
+          <t>f39f14cbaaf9d6f7</t>
         </is>
       </c>
     </row>
     <row r="48" ht="26" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>Assistant Professor in Transportation Policy</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Hunter College</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Department of Urban Policy and Planning</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>Strong interdisciplinary fit for an Assistant Professor position focusing on transportation policy and planning within an urban policy department.</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Transportation Policy, Transportation Advocacy &amp; Accessibility, Community-Engaged Research, Urban Planning</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>Tenure-Track</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>$77,092 - $91,922</t>
+        </is>
+      </c>
+      <c r="L48" s="4" t="inlineStr">
+        <is>
+          <t>Hunter College seeks a tenure-track Assistant Professor in transportation policy to teach graduate students and conduct community-engaged research, requiring a Ph.D. in policy, planning, or a related field specializing in transportation. | Research Topics: Transportation Policy, Transportation Advocacy &amp; Accessibility, Community-Engaged Research, Urban Planning</t>
+        </is>
+      </c>
+      <c r="M48" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-%E2%80%93-urban-policy-and-planning-dept-school-of-arts-and-sciences-hunter-college-at-hunter-college-4438624127</t>
+        </is>
+      </c>
+      <c r="N48" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Q48" s="7" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="n">
+        <v>40.7683107</v>
+      </c>
+      <c r="S48" s="2" t="n">
+        <v>-73.964406</v>
+      </c>
+      <c r="T48" s="2" t="inlineStr">
+        <is>
+          <t>e4e18ed629103a27</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="26" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
           <t>Full/Associate/Assistant Professor in Modern Civil Engineering</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>University of Macau</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>Department of Civil and Environmental Engineering (CEE)</t>
         </is>
       </c>
-      <c r="D48" s="3" t="n">
+      <c r="D49" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="E48" s="4" t="inlineStr">
+      <c r="E49" s="4" t="inlineStr">
         <is>
           <t>The posting is an open-rank faculty search in modern civil engineering which may encompass transportation, but lacks sufficient departmental subfield details in the short snippet.</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Modern Civil Engineering, Transportation Engineering, Urban Systems</t>
         </is>
       </c>
-      <c r="G48" s="5" t="inlineStr">
+      <c r="G49" s="5" t="inlineStr">
         <is>
           <t>Unspecified</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>Macao</t>
         </is>
       </c>
-      <c r="I48" s="5" t="inlineStr">
+      <c r="I49" s="5" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="J48" s="5" t="inlineStr">
+      <c r="J49" s="5" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="K48" s="2" t="inlineStr">
+      <c r="K49" s="2" t="inlineStr">
         <is>
           <t>£87,465.51 to £127,834.20 starting salary</t>
         </is>
       </c>
-      <c r="L48" s="4" t="inlineStr">
+      <c r="L49" s="4" t="inlineStr">
         <is>
           <t>The University of Macau seeks a faculty member in modern civil engineering within the Department of Civil and Environmental Engineering. | Research Topics: Modern Civil Engineering, Transportation Engineering, Urban Systems</t>
         </is>
       </c>
-      <c r="M48" s="6" t="inlineStr">
+      <c r="M49" s="6" t="inlineStr">
         <is>
           <t>https://www.jobs.ac.uk/job/DSL575/full-associate-assistant-professor-in-modern-civil-engineering</t>
         </is>
       </c>
-      <c r="N48" s="5" t="inlineStr">
+      <c r="N49" s="5" t="inlineStr">
         <is>
           <t>Jobs.ac.uk</t>
         </is>
       </c>
-      <c r="O48" s="2" t="inlineStr">
+      <c r="O49" s="2" t="inlineStr">
         <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="P48" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="Q48" s="9" t="inlineStr">
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="Q49" s="9" t="inlineStr">
         <is>
           <t>Past Due</t>
         </is>
       </c>
-      <c r="R48" s="2" t="n">
+      <c r="R49" s="2" t="n">
         <v>22.1285</v>
       </c>
-      <c r="S48" s="2" t="n">
+      <c r="S49" s="2" t="n">
         <v>113.5438</v>
       </c>
-      <c r="T48" s="2" t="inlineStr">
+      <c r="T49" s="2" t="inlineStr">
         <is>
           <t>600dff84e8f0a0b2</t>
         </is>
@@ -5121,6 +5213,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M47" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M49" r:id="rId48"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -529,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T139"/>
+  <dimension ref="A1:T138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -555,102 +555,102 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Institution</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Field/Division</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Fit Score (1-10)</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Fit Reason</t>
         </is>
       </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Research Topics</t>
         </is>
       </c>
-      <c r="G1" s="10" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Tenure Track</t>
         </is>
       </c>
-      <c r="H1" s="10" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="I1" s="10" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Deadline</t>
         </is>
       </c>
-      <c r="J1" s="10" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Deadline Date</t>
         </is>
       </c>
-      <c r="K1" s="10" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Salary</t>
         </is>
       </c>
-      <c r="L1" s="10" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Summary (Gemini)</t>
         </is>
       </c>
-      <c r="M1" s="10" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Link</t>
         </is>
       </c>
-      <c r="N1" s="10" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="O1" s="10" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Date Added</t>
         </is>
       </c>
-      <c r="P1" s="10" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Last Verified</t>
         </is>
       </c>
-      <c r="Q1" s="10" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="R1" s="10" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Latitude</t>
         </is>
       </c>
-      <c r="S1" s="10" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Longitude</t>
         </is>
       </c>
-      <c r="T1" s="10" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
@@ -1074,7 +1074,11 @@
           <t>Priority: 2026-10-01 / Final: Open until filled</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
           <t>Not specified</t>
@@ -1780,9 +1784,8 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assistant Professor in Regional and Urban Planning UCD School of Architecture University College Dublin Location:
-            Dublin Salary: £57,454.37 to £90,980.66
-                                  </t>
+          <t>Assistant Professor in Regional and Urban Planning UCD School of Architecture University College Dublin Location:
+            Dublin Salary: £57,454.37 to £90,980.66</t>
         </is>
       </c>
       <c r="M14" s="5" t="inlineStr">
@@ -2181,30 +2184,40 @@
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Assistant or Associate Professor x2 (112030-0826)</t>
+          <t>Assistant Professor in Urban Analytics and Artificial Intelligence</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>University of Warwick</t>
+          <t>University of Massachusetts Boston</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Transportation Engineering</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr"/>
-      <c r="E19" s="4" t="inlineStr"/>
-      <c r="F19" s="2" t="inlineStr"/>
+          <t>Department of Urban Planning and Community Development</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>This tenure-track position in an Urban Planning department explicitly highlights Transportation and Mobility Systems alongside Urban Analytics and AI, creating a strong interdisciplinary match with the candidate's profile.</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Urban Analytics &amp; AI, Transportation and Mobility Systems, Accessibility &amp; Mobility Equity, Spatial Modeling</t>
+        </is>
+      </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Coventry, England, United Kingdom</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -2219,32 +2232,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>$80,000 - $98,003</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>About The Role Informal Queries For informal queries about the role, please contact Professor James Robinson (Head of Department, Mathematics) at J.C.Robinson@warwick.ac.uk or Professor Marie-Therese</t>
+          <t>The Department of Urban Planning and Community Development seeks a tenure-track Assistant Professor in Urban Analytics and AI with a interest in transportation and mobility systems; a Ph.D. in Urban Planning or a closely related field is required. | Research Topics: Urban Analytics &amp; AI, Transportation and Mobility Systems, Accessibility &amp; Mobility Equity, Spatial Modeling</t>
         </is>
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>https://uk.linkedin.com/jobs/view/assistant-or-associate-professor-x2-112030-0826-at-university-of-warwick-4459612809</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179566167&amp;Title=Assistant%20Professor%20%2D%20Urban%20Analytics</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q19" s="6" t="inlineStr">
@@ -2253,64 +2266,54 @@
         </is>
       </c>
       <c r="R19" s="2" t="n">
-        <v>52.3813073</v>
+        <v>42.314068</v>
       </c>
       <c r="S19" s="2" t="n">
-        <v>-1.5639569</v>
+        <v>-71.0387132</v>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7c1c15e77aa2d698</t>
+          <t>b984f007b128f638</t>
         </is>
       </c>
     </row>
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Assistant/Associate Professor of Public Administration &amp; MPA Coordinator</t>
+          <t>Assistant or Associate Professor x2 (112030-0826)</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>University of New Orleans</t>
+          <t>University of Warwick</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Department of Political Science / Division of Planning and Public Affairs</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>The position is for an Assistant/Associate Professor of Public Administration and MPA Coordinator in a political science and public affairs division, which does not align with the candidate's core transportation engineering and travel behavior research profile.</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Public Administration, Public Policy, Nonprofit Management, Emergency Management</t>
-        </is>
-      </c>
+          <t>Transportation Engineering</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr"/>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Unspecified</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>New Orleans, LA</t>
+          <t>Coventry, England, United Kingdom</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>Priority: 2026-10-19 / Final: Open until filled</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2320,12 +2323,12 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>The Department of Political Science seeks a tenure-track Assistant or Associate Professor of Public Administration to teach graduate MPA courses, serve as Program Coordinator, and maintain an active research agenda requiring a Ph.D. in Public Administration, Political Science, or a closely related field. | Research Topics: Public Administration, Public Policy, Nonprofit Management, Emergency Management</t>
+          <t>About The Role Informal Queries For informal queries about the role, please contact Professor James Robinson (Head of Department, Mathematics) at J.C.Robinson@warwick.ac.uk or Professor Marie-Therese</t>
         </is>
       </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-associate-professor-public-administration-master-of-public-administration-coordinator-at-uno-transportation-institute-4466545068</t>
+          <t>https://uk.linkedin.com/jobs/view/assistant-or-associate-professor-x2-112030-0826-at-university-of-warwick-4459612809</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -2335,12 +2338,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="Q20" s="6" t="inlineStr">
@@ -2349,56 +2352,66 @@
         </is>
       </c>
       <c r="R20" s="2" t="n">
-        <v>29.9561422</v>
+        <v>52.3813073</v>
       </c>
       <c r="S20" s="2" t="n">
-        <v>-90.0733934</v>
+        <v>-1.5639569</v>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>0bd357a7efab4a73</t>
+          <t>7c1c15e77aa2d698</t>
         </is>
       </c>
     </row>
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Professional-Practice Assistant Professor in Journalism</t>
+          <t>Assistant/Associate Professor of Public Administration &amp; MPA Coordinator</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>The Ohio State University School of Communication</t>
+          <t>University of New Orleans</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Transportation / Civil Engineering</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr"/>
-      <c r="E21" s="4" t="inlineStr"/>
-      <c r="F21" s="2" t="inlineStr"/>
+          <t>Department of Political Science / Division of Planning and Public Affairs</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>The position is for an Assistant/Associate Professor of Public Administration and MPA Coordinator in a political science and public affairs division, which does not align with the candidate's core transportation engineering and travel behavior research profile.</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Public Administration, Public Policy, Nonprofit Management, Emergency Management</t>
+        </is>
+      </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Columbus, Ohio, US</t>
+          <t>New Orleans, LA</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
+          <t>Priority: 2026-10-19 / Final: Open until filled</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
           <t>Not specified</t>
@@ -2406,27 +2419,27 @@
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>Professional-Practice Assistant Professor in Journalism Employer The Ohio State University School of Communication Location Columbus, Ohio (US) Salary Competitive Date posted Sep 23, 2026 View more ca</t>
+          <t>The Department of Political Science seeks a tenure-track Assistant or Associate Professor of Public Administration to teach graduate MPA courses, serve as Program Coordinator, and maintain an active research agenda requiring a Ph.D. in Public Administration, Political Science, or a closely related field. | Research Topics: Public Administration, Public Policy, Nonprofit Management, Emergency Management</t>
         </is>
       </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38042786/professional-practice-assistant-professor-in-journalism/</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-associate-professor-public-administration-master-of-public-administration-coordinator-at-uno-transportation-institute-4466545068</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="Q21" s="6" t="inlineStr">
@@ -2435,26 +2448,26 @@
         </is>
       </c>
       <c r="R21" s="2" t="n">
-        <v>40.0067</v>
+        <v>29.9561422</v>
       </c>
       <c r="S21" s="2" t="n">
-        <v>-83.0305</v>
+        <v>-90.0733934</v>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>699288a5d07436e5</t>
+          <t>0bd357a7efab4a73</t>
         </is>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>CCIS - Assistant Professor, Tenure-Track, Sports Media, Journalism and Creative Media - 530569</t>
+          <t>Professional-Practice Assistant Professor in Journalism</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>University of Alabama, College of Communication and Information Sciences</t>
+          <t>The Ohio State University School of Communication</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2472,7 +2485,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Tuscaloosa, Alabama, US</t>
+          <t>Columbus, Ohio, US</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
@@ -2492,12 +2505,12 @@
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>CCIS - Assistant Professor, Tenure-Track, Sports Media, Journalism and Creative Media - 530569 Employer University of Alabama, College of Communication and Information Sciences Location Tuscaloosa, Al</t>
+          <t>Professional-Practice Assistant Professor in Journalism Employer The Ohio State University School of Communication Location Columbus, Ohio (US) Salary Competitive Date posted Sep 23, 2026 View more ca</t>
         </is>
       </c>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38042317/ccis-assistant-professor-tenure-track-sports-media-journalism-and-creative-media-530569/</t>
+          <t>https://jobs.chronicle.com/job/38042786/professional-practice-assistant-professor-in-journalism/</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
@@ -2521,26 +2534,26 @@
         </is>
       </c>
       <c r="R22" s="2" t="n">
-        <v>33.2095614</v>
+        <v>40.0067</v>
       </c>
       <c r="S22" s="2" t="n">
-        <v>-87.5675258</v>
+        <v>-83.0305</v>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7910f26bbe0561d3</t>
+          <t>699288a5d07436e5</t>
         </is>
       </c>
     </row>
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Professor / Associate Professor / Assistant Professor</t>
+          <t>CCIS - Assistant Professor, Tenure-Track, Sports Media, Journalism and Creative Media - 530569</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>THE HONG KONG POLYTECHNIC UNIVERSITY</t>
+          <t>University of Alabama, College of Communication and Information Sciences</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2558,17 +2571,17 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>Tuscaloosa, Alabama, US</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2578,12 +2591,12 @@
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>Professor / Associate Professor / Assistant Professor Employer THE HONG KONG POLYTECHNIC UNIVERSITY Location Hong Kong Salary Competitive Date posted Aug 21, 2026 View more categories View less catego</t>
+          <t>CCIS - Assistant Professor, Tenure-Track, Sports Media, Journalism and Creative Media - 530569 Employer University of Alabama, College of Communication and Information Sciences Location Tuscaloosa, Al</t>
         </is>
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38028368/professor-associate-professor-assistant-professor/</t>
+          <t>https://jobs.chronicle.com/job/38042317/ccis-assistant-professor-tenure-track-sports-media-journalism-and-creative-media-530569/</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
@@ -2607,94 +2620,84 @@
         </is>
       </c>
       <c r="R23" s="2" t="n">
-        <v>22.3045</v>
+        <v>33.2095614</v>
       </c>
       <c r="S23" s="2" t="n">
-        <v>114.1797</v>
+        <v>-87.5675258</v>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>09d04da628fd08f9</t>
+          <t>7910f26bbe0561d3</t>
         </is>
       </c>
     </row>
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor (Tenure-Track)</t>
+          <t>Professor / Associate Professor / Assistant Professor</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Johns Hopkins University</t>
+          <t>THE HONG KONG POLYTECHNIC UNIVERSITY</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>School of Government and Policy</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>Strong interdisciplinary fit as JHU's new School of Government and Policy explicitly solicits candidates with civil engineering and urban planning backgrounds working on transportation and land use, smart city innovation, and AI governance.</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Transportation and Land Use, Urban Innovation and State Capacity, Frontier AI in Government, Public-Sector Technology Adoption</t>
-        </is>
-      </c>
+          <t>Transportation / Civil Engineering</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr"/>
+      <c r="E24" s="4" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Unspecified</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Washington, DC</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>$100,000 - $200,000 per year</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>Johns Hopkins University seeks multiple tenure-track Assistant Professors in civil engineering, urban planning, and related fields with research interests in transportation, land use, and AI policy, requiring a Ph.D. or J.D. by the start date. | Research Topics: Transportation and Land Use, Urban Innovation and State Capacity, Frontier AI in Government, Public-Sector Technology Adoption</t>
+          <t>Professor / Associate Professor / Assistant Professor Employer THE HONG KONG POLYTECHNIC UNIVERSITY Location Hong Kong Salary Competitive Date posted Aug 21, 2026 View more categories View less catego</t>
         </is>
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179560444&amp;Title=Assistant%20Professor</t>
+          <t>https://jobs.chronicle.com/job/38028368/professor-associate-professor-assistant-professor/</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>HigherEdJobs</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="Q24" s="6" t="inlineStr">
@@ -2703,84 +2706,94 @@
         </is>
       </c>
       <c r="R24" s="2" t="n">
-        <v>38.9086858</v>
+        <v>22.3045</v>
       </c>
       <c r="S24" s="2" t="n">
-        <v>-77.0395355</v>
+        <v>114.1797</v>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3e8b915493d9b1ef</t>
+          <t>09d04da628fd08f9</t>
         </is>
       </c>
     </row>
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Transportation Services Assistant Supervisor, Demand Response</t>
+          <t>Assistant Professor (Tenure-Track)</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>University of Wyoming</t>
+          <t>Johns Hopkins University</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Transportation / Civil Engineering</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr"/>
-      <c r="E25" s="4" t="inlineStr"/>
-      <c r="F25" s="2" t="inlineStr"/>
+          <t>School of Government and Policy</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Strong interdisciplinary fit as JHU's new School of Government and Policy explicitly solicits candidates with civil engineering and urban planning backgrounds working on transportation and land use, smart city innovation, and AI governance.</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Transportation and Land Use, Urban Innovation and State Capacity, Frontier AI in Government, Public-Sector Technology Adoption</t>
+        </is>
+      </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Laramie, Wyoming, US</t>
+          <t>Washington, DC</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>$100,000 - $200,000 per year</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Transportation Services Assistant Supervisor, Demand Response Employer University of Wyoming Location Wyoming, United States Salary Salary Not specified Date posted Aug 27, 2026 View m</t>
+          <t>Johns Hopkins University seeks multiple tenure-track Assistant Professors in civil engineering, urban planning, and related fields with research interests in transportation, land use, and AI policy, requiring a Ph.D. or J.D. by the start date. | Research Topics: Transportation and Land Use, Urban Innovation and State Capacity, Frontier AI in Government, Public-Sector Technology Adoption</t>
         </is>
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38030429/hourly-pooled-transportation-services-assistant-supervisor-demand-response/</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179560444&amp;Title=Assistant%20Professor</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="Q25" s="6" t="inlineStr">
@@ -2789,64 +2802,54 @@
         </is>
       </c>
       <c r="R25" s="2" t="n">
-        <v>41.314986</v>
+        <v>38.9086858</v>
       </c>
       <c r="S25" s="2" t="n">
-        <v>-105.5643222</v>
+        <v>-77.0395355</v>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>f024c4d9da93eb21</t>
+          <t>3e8b915493d9b1ef</t>
         </is>
       </c>
     </row>
     <row r="26" ht="26" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor (Canada Impact+ Emerging Leaders)</t>
+          <t>Hourly Pooled - Transportation Services Assistant Supervisor, Demand Response</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>McGill University</t>
+          <t>University of Wyoming</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Faculty of Engineering / Trottier Institute for Sustainability in Engineering and Design</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>This broad early-career initiative in the Faculty of Engineering targets clean technology and resource value chains rather than specifically prioritizing transportation engineering or mobility systems.</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Clean Technology, Resource Value Chains, Sustainable Engineering</t>
-        </is>
-      </c>
+          <t>Transportation / Civil Engineering</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr"/>
+      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Unspecified</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Montreal, QC</t>
+          <t>Laramie, Wyoming, US</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2856,17 +2859,17 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>McGill University seeks an internationally based early-career researcher for a tenure-track Assistant Professor position focused on clean technology and resource value chains, requiring a PhD. | Research Topics: Clean Technology, Resource Value Chains, Sustainable Engineering</t>
+          <t>Hourly Pooled - Transportation Services Assistant Supervisor, Demand Response Employer University of Wyoming Location Wyoming, United States Salary Salary Not specified Date posted Aug 27, 2026 View m</t>
         </is>
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>http://engineering.academickeys.com/job/ezohr835/Canada-Impact-Emerging-Leaders</t>
+          <t>https://jobs.chronicle.com/job/38030429/hourly-pooled-transportation-services-assistant-supervisor-demand-response/</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>AcademicKeys</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -2876,7 +2879,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="Q26" s="6" t="inlineStr">
@@ -2885,44 +2888,44 @@
         </is>
       </c>
       <c r="R26" s="2" t="n">
-        <v>45.5048</v>
+        <v>41.314986</v>
       </c>
       <c r="S26" s="2" t="n">
-        <v>-73.5772</v>
+        <v>-105.5643222</v>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>46b9360bc01a5ec3</t>
+          <t>f024c4d9da93eb21</t>
         </is>
       </c>
     </row>
     <row r="27" ht="26" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Associate Professor or DTU Tenure Track Assistant Professor in Sustainable Travel Behaviour</t>
+          <t>Assistant Professor (Canada Impact+ Emerging Leaders)</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Technical University of Denmark</t>
+          <t>McGill University</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>DTU Management</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="n">
-        <v>10</v>
+          <t>Faculty of Engineering / Trottier Institute for Sustainability in Engineering and Design</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>The position is a direct core match for an Assistant or Associate Professor in Sustainable Travel Behaviour, perfectly aligning with the candidate's core expertise in travel behavior analysis.</t>
+          <t>This broad early-career initiative in the Faculty of Engineering targets clean technology and resource value chains rather than specifically prioritizing transportation engineering or mobility systems.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Sustainable Travel Behaviour, Travel Behavior Analysis, Transportation Planning</t>
+          <t>Clean Technology, Resource Value Chains, Sustainable Engineering</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -2932,17 +2935,17 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Lyngby, Denmark</t>
+          <t>Montreal, QC</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2952,27 +2955,27 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>This faculty position at Technical University of Denmark focuses on sustainable travel behavior research and teaching within DTU Management. | Research Topics: Sustainable Travel Behaviour, Travel Behavior Analysis, Transportation Planning</t>
+          <t>McGill University seeks an internationally based early-career researcher for a tenure-track Assistant Professor position focused on clean technology and resource value chains, requiring a PhD. | Research Topics: Clean Technology, Resource Value Chains, Sustainable Engineering</t>
         </is>
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>https://www.jobs.ac.uk/job/DTA266/associate-professor-or-dtu-tenure-track-assistant-professor-in-sustainable-travel-behaviour</t>
+          <t>http://engineering.academickeys.com/job/ezohr835/Canada-Impact-Emerging-Leaders</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>Jobs.ac.uk</t>
+          <t>AcademicKeys</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="Q27" s="6" t="inlineStr">
@@ -2981,49 +2984,59 @@
         </is>
       </c>
       <c r="R27" s="2" t="n">
-        <v>55.7856</v>
+        <v>45.5048</v>
       </c>
       <c r="S27" s="2" t="n">
-        <v>12.5218</v>
+        <v>-73.5772</v>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>22581fb6f9f6fea0</t>
+          <t>46b9360bc01a5ec3</t>
         </is>
       </c>
     </row>
     <row r="28" ht="26" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Faculty Lecturer, Department of Bioengineering McGill University Bioengineering Posted Sep. 22, 2026</t>
+          <t>Associate Professor or DTU Tenure Track Assistant Professor in Sustainable Travel Behaviour</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Academic Institution</t>
+          <t>Technical University of Denmark</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>of Bioengineering University McGill University Montreal, QC, Canada Department Bioengineering</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr"/>
-      <c r="E28" s="4" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr"/>
+          <t>DTU Management</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>The position is a direct core match for an Assistant or Associate Professor in Sustainable Travel Behaviour, perfectly aligning with the candidate's core expertise in travel behavior analysis.</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Sustainable Travel Behaviour, Travel Behavior Analysis, Transportation Planning</t>
+        </is>
+      </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Lyngby, Denmark</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>October 31, 2026</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -3038,27 +3051,27 @@
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>University Job: Faculty Lecturer, Department of Bioengineering , McGill University Showing jobs in Engineering . Looking for other jobs? Academic Keys (home page) Adjuncts Agriculture Business Communi</t>
+          <t>This faculty position at Technical University of Denmark focuses on sustainable travel behavior research and teaching within DTU Management. | Research Topics: Sustainable Travel Behaviour, Travel Behavior Analysis, Transportation Planning</t>
         </is>
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>http://engineering.academickeys.com/job/e6fq7u53/Faculty-Lecturer-Department-of-Bioengineering</t>
+          <t>https://www.jobs.ac.uk/job/DTA266/associate-professor-or-dtu-tenure-track-assistant-professor-in-sustainable-travel-behaviour</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>AcademicKeys</t>
+          <t>Jobs.ac.uk</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="Q28" s="6" t="inlineStr">
@@ -3067,75 +3080,69 @@
         </is>
       </c>
       <c r="R28" s="2" t="n">
-        <v>7.1438798</v>
+        <v>55.7856</v>
       </c>
       <c r="S28" s="2" t="n">
-        <v>125.5990517</v>
+        <v>12.5218</v>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>c7fbb9b6bf0092a8</t>
+          <t>22581fb6f9f6fea0</t>
         </is>
       </c>
     </row>
     <row r="29" ht="26" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor, Associate Professor, or Professor, Transportation Engineering Systems</t>
+          <t>Faculty Lecturer, Department of Bioengineering McGill University Bioengineering Posted Sep. 22, 2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>University of Central Florida</t>
+          <t>Academic Institution</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Department of Civil, Environmental, and Construction Engineering</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>This open-rank, tenure-track position directly targets Transportation Engineering Systems and explicitly seeks expertise in traveler behavior modeling, big data, and smart mobility, which perfectly matches the candidate's core research specialties.</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>traveler behavior and demand modeling, smart mobility, data analytics and econometrics in transportation, connected and automated vehicles</t>
-        </is>
-      </c>
+          <t>of Bioengineering University McGill University Montreal, QC, Canada Department Bioengineering</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr"/>
+      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Unspecified</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Orlando, FL</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>Priority: 2026-11-01 / Final: Open until filled</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr"/>
+          <t>October 31, 2026</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Negotiable</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>The Department of Civil, Environmental, and Construction Engineering invites applications for a full-time tenure-track or tenured position in Transportation Engineering Systems requiring a PhD in Engineering, Computer Science, or a closely related field. | Research Topics: traveler behavior and demand modeling, smart mobility, data analytics and econometrics in transportation, connected and automated vehicles</t>
+          <t>University Job: Faculty Lecturer, Department of Bioengineering , McGill University Showing jobs in Engineering . Looking for other jobs? Academic Keys (home page) Adjuncts Agriculture Business Communi</t>
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>https://engineering.academickeys.com/job/q8tz2op9/Assistant-Professor-Associate-Professor-or-Professor-Transportation-Engineering-Systems</t>
+          <t>http://engineering.academickeys.com/job/e6fq7u53/Faculty-Lecturer-Department-of-Bioengineering</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
@@ -3145,12 +3152,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="Q29" s="6" t="inlineStr">
@@ -3159,44 +3166,44 @@
         </is>
       </c>
       <c r="R29" s="2" t="n">
-        <v>28.599591</v>
+        <v>7.1438798</v>
       </c>
       <c r="S29" s="2" t="n">
-        <v>-81.1971284</v>
+        <v>125.5990517</v>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>ae92e44a62c477f9</t>
+          <t>c7fbb9b6bf0092a8</t>
         </is>
       </c>
     </row>
     <row r="30" ht="26" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Teaching of Urban Planning</t>
+          <t>Assistant Professor, Associate Professor, or Professor, Transportation Engineering Systems</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>University of California, Los Angeles</t>
+          <t>University of Central Florida</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Department of Urban Planning, Luskin School of Public Affairs</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="n">
-        <v>6</v>
+          <t>Department of Civil, Environmental, and Construction Engineering</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="n">
+        <v>10</v>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>This is a career-track teaching faculty role in a target Urban Planning department listing transportation among eligible focus areas, but it prioritizes global public affairs contexts outside North America.</t>
+          <t>This open-rank, tenure-track position directly targets Transportation Engineering Systems and explicitly seeks expertise in traveler behavior modeling, big data, and smart mobility, which perfectly matches the candidate's core research specialties.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Global Public Affairs, Transportation and Infrastructure, Comparative Urbanization, International Urban Planning</t>
+          <t>traveler behavior and demand modeling, smart mobility, data analytics and econometrics in transportation, connected and automated vehicles</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -3206,12 +3213,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Los Angeles, CA</t>
+          <t>Orlando, FL</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>Open until filled</t>
+          <t>Priority: 2026-11-01 / Final: Open until filled</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -3221,32 +3228,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>DOE</t>
+          <t>Negotiable</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>The Department of Urban Planning seeks an Assistant Professor of Teaching with research and teaching interests in global public affairs and planning outside North America, requiring a Ph.D. in a related field. | Research Topics: Global Public Affairs, Transportation and Infrastructure, Comparative Urbanization, International Urban Planning</t>
+          <t>The Department of Civil, Environmental, and Construction Engineering invites applications for a full-time tenure-track or tenured position in Transportation Engineering Systems requiring a PhD in Engineering, Computer Science, or a closely related field. | Research Topics: traveler behavior and demand modeling, smart mobility, data analytics and econometrics in transportation, connected and automated vehicles</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38020965/assistant-professor-of-teaching-of-urban-planning/</t>
+          <t>https://engineering.academickeys.com/job/q8tz2op9/Assistant-Professor-Associate-Professor-or-Professor-Transportation-Engineering-Systems</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>AcademicKeys</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="Q30" s="6" t="inlineStr">
@@ -3255,44 +3262,44 @@
         </is>
       </c>
       <c r="R30" s="2" t="n">
-        <v>34.0536909</v>
+        <v>28.599591</v>
       </c>
       <c r="S30" s="2" t="n">
-        <v>-118.242766</v>
+        <v>-81.1971284</v>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>fb7ba0794bd02172</t>
+          <t>ae92e44a62c477f9</t>
         </is>
       </c>
     </row>
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Urban Economics</t>
+          <t>Assistant Professor of Teaching of Urban Planning</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Harvard University</t>
+          <t>University of California, Los Angeles</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Harvard Kennedy School of Government</t>
+          <t>Department of Urban Planning, Luskin School of Public Affairs</t>
         </is>
       </c>
       <c r="D31" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>While transportation is listed among the acceptable research areas, this is an urban economics position in a public policy school preferring junior economists rather than a core engineering or mobility planning appointment.</t>
+          <t>This is a career-track teaching faculty role in a target Urban Planning department listing transportation among eligible focus areas, but it prioritizes global public affairs contexts outside North America.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Urban Economics, Housing, Transportation, Infrastructure</t>
+          <t>Global Public Affairs, Transportation and Infrastructure, Comparative Urbanization, International Urban Planning</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -3302,32 +3309,32 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Cambridge, MA</t>
+          <t>Los Angeles, CA</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
+          <t>Open until filled</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
           <t>2026-11-01</t>
         </is>
       </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>2026-11-01</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>165k - 185k</t>
+          <t>DOE</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>The Harvard Kennedy School seeks a junior economist to study urban issues including housing, transportation, and infrastructure, requiring a Ph.D. by June 2027. | Research Topics: Urban Economics, Housing, Transportation, Infrastructure</t>
+          <t>The Department of Urban Planning seeks an Assistant Professor of Teaching with research and teaching interests in global public affairs and planning outside North America, requiring a Ph.D. in a related field. | Research Topics: Global Public Affairs, Transportation and Infrastructure, Comparative Urbanization, International Urban Planning</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38032116/assistant-professor-urban-economics-/</t>
+          <t>https://jobs.chronicle.com/job/38020965/assistant-professor-of-teaching-of-urban-planning/</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
@@ -3337,12 +3344,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="Q31" s="6" t="inlineStr">
@@ -3351,44 +3358,44 @@
         </is>
       </c>
       <c r="R31" s="2" t="n">
-        <v>42.3657432</v>
+        <v>34.0536909</v>
       </c>
       <c r="S31" s="2" t="n">
-        <v>-71.12221390000001</v>
+        <v>-118.242766</v>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>93251b0fa8170f49</t>
+          <t>fb7ba0794bd02172</t>
         </is>
       </c>
     </row>
     <row r="32" ht="26" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Assistant or Associate Professor in Supply Chain Management</t>
+          <t>Assistant Professor of Urban Economics</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>University of Arkansas</t>
+          <t>Harvard University</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Department of Supply Chain Management, Sam M. Walton College of Business</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>3</v>
+          <t>Harvard Kennedy School of Government</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>5</v>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>This tenure-track position is housed within a business school's Supply Chain Management department, which is peripheral to the candidate's core focus on passenger transit planning, travel behavior, and transportation engineering.</t>
+          <t>While transportation is listed among the acceptable research areas, this is an urban economics position in a public policy school preferring junior economists rather than a core engineering or mobility planning appointment.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Management, Logistics, Operations Management</t>
+          <t>Urban Economics, Housing, Transportation, Infrastructure</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -3398,7 +3405,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Fayetteville, AR</t>
+          <t>Cambridge, MA</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
@@ -3413,32 +3420,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>165k - 185k</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>Tenure-track Assistant or Associate Professor position in Supply Chain Management requiring an earned doctorate and a demonstrated record of peer-reviewed research. | Research Topics: Supply Chain Management, Logistics, Operations Management</t>
+          <t>The Harvard Kennedy School seeks a junior economist to study urban issues including housing, transportation, and infrastructure, requiring a Ph.D. by June 2027. | Research Topics: Urban Economics, Housing, Transportation, Infrastructure</t>
         </is>
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-or-associate-professor-open-rank-at-university-of-arkansas-%C2%AD-sam-m-walton-college-of-business-4460111187</t>
+          <t>https://jobs.chronicle.com/job/38032116/assistant-professor-urban-economics-/</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="Q32" s="6" t="inlineStr">
@@ -3447,31 +3454,31 @@
         </is>
       </c>
       <c r="R32" s="2" t="n">
-        <v>36.0970389</v>
+        <v>42.3657432</v>
       </c>
       <c r="S32" s="2" t="n">
-        <v>-94.1703322</v>
+        <v>-71.12221390000001</v>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>c16a694d5f7f68d4</t>
+          <t>93251b0fa8170f49</t>
         </is>
       </c>
     </row>
     <row r="33" ht="26" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Aerospace Engineering</t>
+          <t>Assistant or Associate Professor in Supply Chain Management</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>University of Arkansas</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Department of Aerospace Engineering and Engineering Mechanics</t>
+          <t>Department of Supply Chain Management, Sam M. Walton College of Business</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
@@ -3479,12 +3486,12 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>The position is within an Aerospace Engineering department focused on space discovery and advanced air mobility, presenting only peripheral overlap with the candidate's core expertise in surface transportation, travel behavior, and transit planning.</t>
+          <t>This tenure-track position is housed within a business school's Supply Chain Management department, which is peripheral to the candidate's core focus on passenger transit planning, travel behavior, and transportation engineering.</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Advanced Air Mobility Solutions, Space Discovery, Observations, and Connectivity</t>
+          <t>Supply Chain Management, Logistics, Operations Management</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -3494,12 +3501,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Fayetteville, AR</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>Priority: 2026-11-01 / Final: Open until filled</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -3514,27 +3521,27 @@
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>The Department of Aerospace Engineering and Engineering Mechanics invites applications for a tenure-track Assistant Professor specializing in space systems or advanced air mobility, requiring a Ph.D. in engineering or a related discipline. | Research Topics: Advanced Air Mobility Solutions, Space Discovery, Observations, and Connectivity</t>
+          <t>Tenure-track Assistant or Associate Professor position in Supply Chain Management requiring an earned doctorate and a demonstrated record of peer-reviewed research. | Research Topics: Supply Chain Management, Logistics, Operations Management</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>https://engineering.academickeys.com/job/fq6v1p8t/Assistant-Professor-Fall-2027--Aerospace-Engineering</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-or-associate-professor-open-rank-at-university-of-arkansas-%C2%AD-sam-m-walton-college-of-business-4460111187</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>AcademicKeys</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="Q33" s="6" t="inlineStr">
@@ -3543,56 +3550,66 @@
         </is>
       </c>
       <c r="R33" s="2" t="n">
-        <v>30.2849</v>
+        <v>36.0970389</v>
       </c>
       <c r="S33" s="2" t="n">
-        <v>-97.7341</v>
+        <v>-94.1703322</v>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>b762e241121d9f0d</t>
+          <t>c16a694d5f7f68d4</t>
         </is>
       </c>
     </row>
     <row r="34" ht="26" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Tenure-Track Faculty Position (Open Rank) - all areas</t>
+          <t>Assistant Professor of Aerospace Engineering</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>University of Notre Dame</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Transportation Engineering</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr"/>
-      <c r="E34" s="4" t="inlineStr"/>
-      <c r="F34" s="2" t="inlineStr"/>
+          <t>Department of Aerospace Engineering and Engineering Mechanics</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>The position is within an Aerospace Engineering department focused on space discovery and advanced air mobility, presenting only peripheral overlap with the candidate's core expertise in surface transportation, travel behavior, and transit planning.</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Advanced Air Mobility Solutions, Space Discovery, Observations, and Connectivity</t>
+        </is>
+      </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Notre Dame, New Brunswick, Canada</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
+          <t>Priority: 2026-11-01 / Final: Open until filled</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
           <t>2026-11-01</t>
         </is>
       </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>2026-11-01</t>
-        </is>
-      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
           <t>Not specified</t>
@@ -3600,60 +3617,60 @@
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>The Department of Aerospace and Mechanical Engineering at the University of Notre Dame invites applications for a tenure-track faculty position. Applications are welcome from all areas of aerospace an</t>
+          <t>The Department of Aerospace Engineering and Engineering Mechanics invites applications for a tenure-track Assistant Professor specializing in space systems or advanced air mobility, requiring a Ph.D. in engineering or a related discipline. | Research Topics: Advanced Air Mobility Solutions, Space Discovery, Observations, and Connectivity</t>
         </is>
       </c>
       <c r="M34" s="5" t="inlineStr">
         <is>
-          <t>https://ca.linkedin.com/jobs/view/tenure-track-faculty-position-open-rank-all-areas-at-university-of-notre-dame-4463103000</t>
+          <t>https://engineering.academickeys.com/job/fq6v1p8t/Assistant-Professor-Fall-2027--Aerospace-Engineering</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>AcademicKeys</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
       <c r="Q34" s="6" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
       <c r="R34" s="2" t="n">
-        <v>41.7045677</v>
+        <v>30.2849</v>
       </c>
       <c r="S34" s="2" t="n">
-        <v>-86.23822029999999</v>
+        <v>-97.7341</v>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>bf3ba3056fe418d9</t>
+          <t>b762e241121d9f0d</t>
         </is>
       </c>
     </row>
     <row r="35" ht="26" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Endowed Nursing Professorship in Health, Well-Being, and Chronic Conditions Innovation</t>
+          <t>Tenure-Track Faculty Position (Open Rank) - all areas</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>University of Massachusetts Dartmouth</t>
+          <t>University of Notre Dame</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Transportation / Civil Engineering</t>
+          <t>Transportation Engineering</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr"/>
@@ -3666,17 +3683,17 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Dartmouth, Massachusetts, US</t>
+          <t>Notre Dame, New Brunswick, Canada</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3686,17 +3703,17 @@
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>Endowed Nursing Professorship in Health, Well-Being, and Chronic Conditions Innovation Employer University of Massachusetts Dartmouth Location Dartmouth, Massachusetts (US) Salary Competitive Date pos</t>
+          <t>The Department of Aerospace and Mechanical Engineering at the University of Notre Dame invites applications for a tenure-track faculty position. Applications are welcome from all areas of aerospace an</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38034190/endowed-nursing-professorship-in-health-well-being-and-chronic-conditions-innovation/?LinkSource=PromotedJob</t>
+          <t>https://ca.linkedin.com/jobs/view/tenure-track-faculty-position-open-rank-all-areas-at-university-of-notre-dame-4463103000</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
@@ -3715,14 +3732,14 @@
         </is>
       </c>
       <c r="R35" s="2" t="n">
-        <v>41.6225037</v>
+        <v>41.7045677</v>
       </c>
       <c r="S35" s="2" t="n">
-        <v>-71.0073448</v>
+        <v>-86.23822029999999</v>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>6c74e41e0a146e26</t>
+          <t>bf3ba3056fe418d9</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4517,7 @@
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tenure-track Assistant Professor – AI for Automotive and Mobility Systems Employer The Ohio State University Location Columbus, Ohio Salary Not Specified Date posted Sep 16, 2026 View more categories </t>
+          <t>Tenure-track Assistant Professor – AI for Automotive and Mobility Systems Employer The Ohio State University Location Columbus, Ohio Salary Not Specified Date posted Sep 16, 2026 View more categories</t>
         </is>
       </c>
       <c r="M44" s="5" t="inlineStr">
@@ -9412,17 +9429,17 @@
     <row r="100" ht="26" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor - Urban Analytics</t>
+          <t>Assistant or Associate Professor of Mechanical Engineering (tenure-track)</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>University of Massachusetts - Boston</t>
+          <t>Virginia Military Institute</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Civil &amp; Environmental / Transportation Engineering</t>
+          <t>Mechanical Engineering</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr"/>
@@ -9435,7 +9452,7 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>Lexington, Virginia</t>
         </is>
       </c>
       <c r="I100" s="3" t="inlineStr">
@@ -9451,17 +9468,17 @@
       </c>
       <c r="L100" s="4" t="inlineStr">
         <is>
-          <t>Assistant Professor - Urban Analytics University of Massachusetts - Boston Boston, MA $80,000 - $98,003 per year Urban Studies and Planning Posted 5 days ago</t>
+          <t>University Job: Assistant or Associate Professor of Mechanical Engineering (tenure-track), Virginia Military Institute Showing jobs in Engineering . Looking for other jobs? Academic Keys (home page) A</t>
         </is>
       </c>
       <c r="M100" s="5" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179566167&amp;Title=Assistant%20Professor%20%2D%20Urban%20Analytics</t>
+          <t>https://engineering.academickeys.com/job/wyok0std/Assistant-or-Associate-Professor-of-Mechanical-Engineering-tenuretrack</t>
         </is>
       </c>
       <c r="N100" s="3" t="inlineStr">
         <is>
-          <t>HigherEdJobs</t>
+          <t>AcademicKeys</t>
         </is>
       </c>
       <c r="O100" s="2" t="inlineStr">
@@ -9471,7 +9488,7 @@
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="Q100" s="6" t="inlineStr">
@@ -9480,31 +9497,31 @@
         </is>
       </c>
       <c r="R100" s="2" t="n">
-        <v>42.314068</v>
+        <v>37.7913339</v>
       </c>
       <c r="S100" s="2" t="n">
-        <v>-71.0387132</v>
+        <v>-79.4355152</v>
       </c>
       <c r="T100" s="2" t="inlineStr">
         <is>
-          <t>b984f007b128f638</t>
+          <t>40d11d7f2b4d26eb</t>
         </is>
       </c>
     </row>
     <row r="101" ht="26" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Assistant or Associate Professor of Mechanical Engineering (tenure-track)</t>
+          <t>Assistant/Associate Professor</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Virginia Military Institute</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Mechanical Engineering</t>
+          <t>Civil &amp; Environmental / Transportation Engineering</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr"/>
@@ -9517,7 +9534,7 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>Lexington, Virginia</t>
+          <t>Blacksburg, VA</t>
         </is>
       </c>
       <c r="I101" s="3" t="inlineStr">
@@ -9533,17 +9550,17 @@
       </c>
       <c r="L101" s="4" t="inlineStr">
         <is>
-          <t>University Job: Assistant or Associate Professor of Mechanical Engineering (tenure-track), Virginia Military Institute Showing jobs in Engineering . Looking for other jobs? Academic Keys (home page) A</t>
+          <t>Assistant/Associate Professor Virginia Tech Blacksburg, VA $120,000 - $150,000 per year Biological and Biomedical Engineering Posted 5 days ago Military</t>
         </is>
       </c>
       <c r="M101" s="5" t="inlineStr">
         <is>
-          <t>https://engineering.academickeys.com/job/wyok0std/Assistant-or-Associate-Professor-of-Mechanical-Engineering-tenuretrack</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179566278&amp;Title=Assistant%2FAssociate%20Professor</t>
         </is>
       </c>
       <c r="N101" s="3" t="inlineStr">
         <is>
-          <t>AcademicKeys</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="O101" s="2" t="inlineStr">
@@ -9553,7 +9570,7 @@
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q101" s="6" t="inlineStr">
@@ -9562,26 +9579,26 @@
         </is>
       </c>
       <c r="R101" s="2" t="n">
-        <v>37.7913339</v>
+        <v>37.2284</v>
       </c>
       <c r="S101" s="2" t="n">
-        <v>-79.4355152</v>
+        <v>-80.4234</v>
       </c>
       <c r="T101" s="2" t="inlineStr">
         <is>
-          <t>40d11d7f2b4d26eb</t>
+          <t>205447314e3413c7</t>
         </is>
       </c>
     </row>
     <row r="102" ht="26" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Assistant/Associate Professor</t>
+          <t>Assistant Professor of Electrical Engineering</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>Wilkes University</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -9599,7 +9616,7 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>Blacksburg, VA</t>
+          <t>Wilkes-Barre, PA</t>
         </is>
       </c>
       <c r="I102" s="3" t="inlineStr">
@@ -9615,12 +9632,12 @@
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
-          <t>Assistant/Associate Professor Virginia Tech Blacksburg, VA $120,000 - $150,000 per year Biological and Biomedical Engineering Posted 5 days ago Military</t>
+          <t>Assistant Professor of Electrical Engineering Wilkes University Wilkes-Barre, PA Electrical Engineering Posted 4 days ago</t>
         </is>
       </c>
       <c r="M102" s="5" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179566278&amp;Title=Assistant%2FAssociate%20Professor</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179566665&amp;Title=Assistant%20Professor%20of%20Electrical%20Engineering</t>
         </is>
       </c>
       <c r="N102" s="3" t="inlineStr">
@@ -9635,7 +9652,7 @@
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="Q102" s="6" t="inlineStr">
@@ -9644,33 +9661,29 @@
         </is>
       </c>
       <c r="R102" s="2" t="n">
-        <v>37.2284</v>
+        <v>41.2444276</v>
       </c>
       <c r="S102" s="2" t="n">
-        <v>-80.4234</v>
+        <v>-75.8902922</v>
       </c>
       <c r="T102" s="2" t="inlineStr">
         <is>
-          <t>205447314e3413c7</t>
+          <t>4bed99aa9e0f2a8b</t>
         </is>
       </c>
     </row>
     <row r="103" ht="26" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Electrical Engineering</t>
+          <t>Open-rank Faculty Position in Computer Science and Engineering</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Wilkes University</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>Civil &amp; Environmental / Transportation Engineering</t>
-        </is>
-      </c>
+          <t>Zhejiang University-University of Illinois Urbana-Champaign Institute  (ZJU-UIUC)</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr"/>
       <c r="D103" s="3" t="inlineStr"/>
       <c r="E103" s="4" t="inlineStr"/>
       <c r="F103" s="2" t="inlineStr"/>
@@ -9681,7 +9694,7 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>Wilkes-Barre, PA</t>
+          <t>Haining</t>
         </is>
       </c>
       <c r="I103" s="3" t="inlineStr">
@@ -9697,27 +9710,28 @@
       </c>
       <c r="L103" s="4" t="inlineStr">
         <is>
-          <t>Assistant Professor of Electrical Engineering Wilkes University Wilkes-Barre, PA Electrical Engineering Posted 4 days ago</t>
+          <t>Open-rank Faculty Position in Computer Science and Engineering Zhejiang University-University of Illinois Urbana-Champaign Institute  (ZJU-UIUC) Location:
+            Haining Salary: Competitive Date</t>
         </is>
       </c>
       <c r="M103" s="5" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179566665&amp;Title=Assistant%20Professor%20of%20Electrical%20Engineering</t>
+          <t>https://www.jobs.ac.uk/job/DSS455/open-rank-faculty-position-in-computer-science-and-engineering</t>
         </is>
       </c>
       <c r="N103" s="3" t="inlineStr">
         <is>
-          <t>HigherEdJobs</t>
+          <t>Jobs.ac.uk</t>
         </is>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="Q103" s="6" t="inlineStr">
@@ -9726,21 +9740,21 @@
         </is>
       </c>
       <c r="R103" s="2" t="n">
-        <v>41.2444276</v>
+        <v>40.102</v>
       </c>
       <c r="S103" s="2" t="n">
-        <v>-75.8902922</v>
+        <v>-88.2272</v>
       </c>
       <c r="T103" s="2" t="inlineStr">
         <is>
-          <t>4bed99aa9e0f2a8b</t>
+          <t>00c8b8eab6347b33</t>
         </is>
       </c>
     </row>
     <row r="104" ht="26" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Open-rank Faculty Position in Computer Science and Engineering</t>
+          <t>Open-rank Faculty Position in Electrical and Electronic Engineering</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -9775,13 +9789,13 @@
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
-          <t>Open-rank Faculty Position in Computer Science and Engineering Zhejiang University-University of Illinois Urbana-Champaign Institute  (ZJU-UIUC) Location:
-            Haining Salary: Competitive Date</t>
+          <t>Open-rank Faculty Position in Electrical and Electronic Engineering Zhejiang University-University of Illinois Urbana-Champaign Institute  (ZJU-UIUC) Location:
+            Haining Salary: Competitive</t>
         </is>
       </c>
       <c r="M104" s="5" t="inlineStr">
         <is>
-          <t>https://www.jobs.ac.uk/job/DSS455/open-rank-faculty-position-in-computer-science-and-engineering</t>
+          <t>https://www.jobs.ac.uk/job/DSS464/open-rank-faculty-position-in-electrical-and-electronic-engineering</t>
         </is>
       </c>
       <c r="N104" s="3" t="inlineStr">
@@ -9812,14 +9826,14 @@
       </c>
       <c r="T104" s="2" t="inlineStr">
         <is>
-          <t>00c8b8eab6347b33</t>
+          <t>6a637601f90e960f</t>
         </is>
       </c>
     </row>
     <row r="105" ht="26" customHeight="1">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Open-rank Faculty Position in Electrical and Electronic Engineering</t>
+          <t>Open-rank Faculty Position in Mechanical Engineering</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -9854,13 +9868,13 @@
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
-          <t>Open-rank Faculty Position in Electrical and Electronic Engineering Zhejiang University-University of Illinois Urbana-Champaign Institute  (ZJU-UIUC) Location:
-            Haining Salary: Competitive</t>
+          <t>Open-rank Faculty Position in Mechanical Engineering Zhejiang University-University of Illinois Urbana-Champaign Institute  (ZJU-UIUC) Location:
+            Haining Salary: Competitive Date Placed: 26</t>
         </is>
       </c>
       <c r="M105" s="5" t="inlineStr">
         <is>
-          <t>https://www.jobs.ac.uk/job/DSS464/open-rank-faculty-position-in-electrical-and-electronic-engineering</t>
+          <t>https://www.jobs.ac.uk/job/DSS443/open-rank-faculty-position-in-mechanical-engineering</t>
         </is>
       </c>
       <c r="N105" s="3" t="inlineStr">
@@ -9891,22 +9905,26 @@
       </c>
       <c r="T105" s="2" t="inlineStr">
         <is>
-          <t>6a637601f90e960f</t>
+          <t>abe047e706c49df3</t>
         </is>
       </c>
     </row>
     <row r="106" ht="26" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Open-rank Faculty Position in Mechanical Engineering</t>
+          <t>Assistant Professor in Resilient Manufacturing Systems</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Zhejiang University-University of Illinois Urbana-Champaign Institute  (ZJU-UIUC)</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr"/>
+          <t>Aalborg University</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Transportation Engineering</t>
+        </is>
+      </c>
       <c r="D106" s="3" t="inlineStr"/>
       <c r="E106" s="4" t="inlineStr"/>
       <c r="F106" s="2" t="inlineStr"/>
@@ -9917,12 +9935,12 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>Haining</t>
+          <t>Aalborg, North Denmark Region, Denmark</t>
         </is>
       </c>
       <c r="I106" s="3" t="inlineStr">
         <is>
-          <t>Open until filled</t>
+          <t>Posted 3 months ago</t>
         </is>
       </c>
       <c r="J106" s="3" t="inlineStr"/>
@@ -9933,23 +9951,22 @@
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
-          <t>Open-rank Faculty Position in Mechanical Engineering Zhejiang University-University of Illinois Urbana-Champaign Institute  (ZJU-UIUC) Location:
-            Haining Salary: Competitive Date Placed: 26</t>
+          <t>Fixed-term, full-time position (3 years), starting 1 February 2027 or as soon as possible thereafter. Modern manufacturing is increasingly dependent on robust, adaptable, and data-driven production sy</t>
         </is>
       </c>
       <c r="M106" s="5" t="inlineStr">
         <is>
-          <t>https://www.jobs.ac.uk/job/DSS443/open-rank-faculty-position-in-mechanical-engineering</t>
+          <t>https://dk.linkedin.com/jobs/view/assistant-professor-in-resilient-manufacturing-systems-at-aalborg-university-4433319001</t>
         </is>
       </c>
       <c r="N106" s="3" t="inlineStr">
         <is>
-          <t>Jobs.ac.uk</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -9963,26 +9980,26 @@
         </is>
       </c>
       <c r="R106" s="2" t="n">
-        <v>40.102</v>
+        <v>57.0156429</v>
       </c>
       <c r="S106" s="2" t="n">
-        <v>-88.2272</v>
+        <v>9.975296200000001</v>
       </c>
       <c r="T106" s="2" t="inlineStr">
         <is>
-          <t>abe047e706c49df3</t>
+          <t>d6af8cfed15e21c1</t>
         </is>
       </c>
     </row>
     <row r="107" ht="26" customHeight="1">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor in Resilient Manufacturing Systems</t>
+          <t>Airbus Synthetic Flight Instructor (SFI)</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Aalborg University</t>
+          <t>Airbus</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -10000,12 +10017,12 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>Aalborg, North Denmark Region, Denmark</t>
+          <t>Seoul, Seoul, South Korea</t>
         </is>
       </c>
       <c r="I107" s="3" t="inlineStr">
         <is>
-          <t>Posted 3 months ago</t>
+          <t>Posted 1 week ago</t>
         </is>
       </c>
       <c r="J107" s="3" t="inlineStr"/>
@@ -10016,12 +10033,12 @@
       </c>
       <c r="L107" s="4" t="inlineStr">
         <is>
-          <t>Fixed-term, full-time position (3 years), starting 1 February 2027 or as soon as possible thereafter. Modern manufacturing is increasingly dependent on robust, adaptable, and data-driven production sy</t>
+          <t>Job Description: Airbus Korea | SFI Airbus Korea have open positions for Synthetic Flight Instructors to be employed directly with Airbus Korea, with flexible commuting options available such as 3/1,</t>
         </is>
       </c>
       <c r="M107" s="5" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/assistant-professor-in-resilient-manufacturing-systems-at-aalborg-university-4433319001</t>
+          <t>https://kr.linkedin.com/jobs/view/airbus-synthetic-flight-instructor-sfi-at-airbus-4192389555</t>
         </is>
       </c>
       <c r="N107" s="3" t="inlineStr">
@@ -10031,7 +10048,7 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
@@ -10045,26 +10062,26 @@
         </is>
       </c>
       <c r="R107" s="2" t="n">
-        <v>57.0156429</v>
+        <v>32.9101077</v>
       </c>
       <c r="S107" s="2" t="n">
-        <v>9.975296200000001</v>
+        <v>-97.38323629999999</v>
       </c>
       <c r="T107" s="2" t="inlineStr">
         <is>
-          <t>d6af8cfed15e21c1</t>
+          <t>9b6fb928277c1942</t>
         </is>
       </c>
     </row>
     <row r="108" ht="26" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Airbus Synthetic Flight Instructor (SFI)</t>
+          <t>Professor (x2), Associate Professor (x2) &amp; Assistant Professor | University of Tokyo, Japan</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Airbus</t>
+          <t>ALICE Collaboration</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -10082,12 +10099,12 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>Seoul, Seoul, South Korea</t>
+          <t>Greater Tokyo Area</t>
         </is>
       </c>
       <c r="I108" s="3" t="inlineStr">
         <is>
-          <t>Posted 1 week ago</t>
+          <t>Posted 2 months ago</t>
         </is>
       </c>
       <c r="J108" s="3" t="inlineStr"/>
@@ -10098,12 +10115,12 @@
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
-          <t>Job Description: Airbus Korea | SFI Airbus Korea have open positions for Synthetic Flight Instructors to be employed directly with Airbus Korea, with flexible commuting options available such as 3/1,</t>
+          <t>Submitted by tmillerd on Tue, 06/30/2026 - 10:41 Category non-alice job The Quark Nuclear Science Institute of the Graduate School of Science, The University of Tokyo, is inviting applications for two</t>
         </is>
       </c>
       <c r="M108" s="5" t="inlineStr">
         <is>
-          <t>https://kr.linkedin.com/jobs/view/airbus-synthetic-flight-instructor-sfi-at-airbus-4192389555</t>
+          <t>https://jp.linkedin.com/jobs/view/professor-x2-associate-professor-x2-assistant-professor-university-of-tokyo-japan-at-alice-collaboration-4455318954</t>
         </is>
       </c>
       <c r="N108" s="3" t="inlineStr">
@@ -10126,27 +10143,23 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="R108" s="2" t="n">
-        <v>32.9101077</v>
-      </c>
-      <c r="S108" s="2" t="n">
-        <v>-97.38323629999999</v>
-      </c>
+      <c r="R108" s="2" t="inlineStr"/>
+      <c r="S108" s="2" t="inlineStr"/>
       <c r="T108" s="2" t="inlineStr">
         <is>
-          <t>9b6fb928277c1942</t>
+          <t>a60b32b552e436a7</t>
         </is>
       </c>
     </row>
     <row r="109" ht="26" customHeight="1">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Professor (x2), Associate Professor (x2) &amp; Assistant Professor | University of Tokyo, Japan</t>
+          <t>Flight Simulator Instructor A320 / B737-EN</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>ALICE Collaboration</t>
+          <t>CAE</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -10164,12 +10177,12 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>Greater Tokyo Area</t>
+          <t>Seoul, Seoul, South Korea</t>
         </is>
       </c>
       <c r="I109" s="3" t="inlineStr">
         <is>
-          <t>Posted 2 months ago</t>
+          <t>Posted 1 week ago</t>
         </is>
       </c>
       <c r="J109" s="3" t="inlineStr"/>
@@ -10180,12 +10193,12 @@
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
-          <t>Submitted by tmillerd on Tue, 06/30/2026 - 10:41 Category non-alice job The Quark Nuclear Science Institute of the Graduate School of Science, The University of Tokyo, is inviting applications for two</t>
+          <t>The Simulator Instructor is responsible for all training activities being delivered in compliance with the authority approval, defined standards and processes and ensures that the highest standards of</t>
         </is>
       </c>
       <c r="M109" s="5" t="inlineStr">
         <is>
-          <t>https://jp.linkedin.com/jobs/view/professor-x2-associate-professor-x2-assistant-professor-university-of-tokyo-japan-at-alice-collaboration-4455318954</t>
+          <t>https://kr.linkedin.com/jobs/view/flight-simulator-instructor-a320-b737-en-at-cae-4411538607</t>
         </is>
       </c>
       <c r="N109" s="3" t="inlineStr">
@@ -10195,7 +10208,7 @@
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="P109" s="2" t="inlineStr">
@@ -10208,23 +10221,27 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="R109" s="2" t="inlineStr"/>
-      <c r="S109" s="2" t="inlineStr"/>
+      <c r="R109" s="2" t="n">
+        <v>33.9388631</v>
+      </c>
+      <c r="S109" s="2" t="n">
+        <v>-81.11397150000001</v>
+      </c>
       <c r="T109" s="2" t="inlineStr">
         <is>
-          <t>a60b32b552e436a7</t>
+          <t>3ec4840688af2db3</t>
         </is>
       </c>
     </row>
     <row r="110" ht="26" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Flight Simulator Instructor A320 / B737-EN</t>
+          <t>Associate Professor or DTU Tenure Track Assistant Professor in Sustainable Travel Behaviour - DTU Management</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>CAE</t>
+          <t>DTU - Technical University of Denmark</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -10242,7 +10259,7 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>Seoul, Seoul, South Korea</t>
+          <t>Kongens Lyngby, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
       <c r="I110" s="3" t="inlineStr">
@@ -10258,12 +10275,12 @@
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
-          <t>The Simulator Instructor is responsible for all training activities being delivered in compliance with the authority approval, defined standards and processes and ensures that the highest standards of</t>
+          <t>Job Description DTU Management is looking for an Associate Professor or Tenure Track Assistant Professor in Sustainable Travel Behaviour to join our Transportation Science Division. In this position,</t>
         </is>
       </c>
       <c r="M110" s="5" t="inlineStr">
         <is>
-          <t>https://kr.linkedin.com/jobs/view/flight-simulator-instructor-a320-b737-en-at-cae-4411538607</t>
+          <t>https://dk.linkedin.com/jobs/view/associate-professor-or-dtu-tenure-track-assistant-professor-in-sustainable-travel-behaviour-dtu-management-at-dtu-technical-university-of-denmark-4468634703</t>
         </is>
       </c>
       <c r="N110" s="3" t="inlineStr">
@@ -10273,40 +10290,40 @@
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="P110" s="2" t="inlineStr">
+        <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="P110" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
       <c r="Q110" s="6" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
       <c r="R110" s="2" t="n">
-        <v>33.9388631</v>
+        <v>55.7856</v>
       </c>
       <c r="S110" s="2" t="n">
-        <v>-81.11397150000001</v>
+        <v>12.5218</v>
       </c>
       <c r="T110" s="2" t="inlineStr">
         <is>
-          <t>3ec4840688af2db3</t>
+          <t>7e6d15e66f05eb1f</t>
         </is>
       </c>
     </row>
     <row r="111" ht="26" customHeight="1">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Associate Professor or DTU Tenure Track Assistant Professor in Sustainable Travel Behaviour - DTU Management</t>
+          <t>Assistant Professor In Control Systems Technology for Emerging Application Areas</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>DTU - Technical University of Denmark</t>
+          <t>Eindhoven University of Technology</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -10324,12 +10341,12 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>Kongens Lyngby, Capital Region of Denmark, Denmark</t>
+          <t>Eindhoven, North Brabant, Netherlands</t>
         </is>
       </c>
       <c r="I111" s="3" t="inlineStr">
         <is>
-          <t>Posted 1 week ago</t>
+          <t>Posted 3 weeks ago</t>
         </is>
       </c>
       <c r="J111" s="3" t="inlineStr"/>
@@ -10340,12 +10357,12 @@
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
-          <t>Job Description DTU Management is looking for an Associate Professor or Tenure Track Assistant Professor in Sustainable Travel Behaviour to join our Transportation Science Division. In this position,</t>
+          <t>Would you like to be part of a vibrant and collaborative academic community, contributing to real-world innovations? Join us in shaping the future of 'control systems technology' in the heart of the h</t>
         </is>
       </c>
       <c r="M111" s="5" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/associate-professor-or-dtu-tenure-track-assistant-professor-in-sustainable-travel-behaviour-dtu-management-at-dtu-technical-university-of-denmark-4468634703</t>
+          <t>https://nl.linkedin.com/jobs/view/assistant-professor-in-control-systems-technology-for-emerging-application-areas-at-eindhoven-university-of-technology-4449015225</t>
         </is>
       </c>
       <c r="N111" s="3" t="inlineStr">
@@ -10369,26 +10386,26 @@
         </is>
       </c>
       <c r="R111" s="2" t="n">
-        <v>55.7856</v>
+        <v>51.4486602</v>
       </c>
       <c r="S111" s="2" t="n">
-        <v>12.5218</v>
+        <v>5.4903996</v>
       </c>
       <c r="T111" s="2" t="inlineStr">
         <is>
-          <t>7e6d15e66f05eb1f</t>
+          <t>61c642450ddce455</t>
         </is>
       </c>
     </row>
     <row r="112" ht="26" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor In Control Systems Technology for Emerging Application Areas</t>
+          <t>Tenure-track Professor/ Associate Professor/ Assistant Professor in Global Health (several posts), School of Public Health</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Eindhoven University of Technology</t>
+          <t>HKUMed – The University of Hong Kong</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -10406,12 +10423,12 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>Eindhoven, North Brabant, Netherlands</t>
+          <t>Hong Kong SAR</t>
         </is>
       </c>
       <c r="I112" s="3" t="inlineStr">
         <is>
-          <t>Posted 3 weeks ago</t>
+          <t>Posted 2 weeks ago</t>
         </is>
       </c>
       <c r="J112" s="3" t="inlineStr"/>
@@ -10422,12 +10439,12 @@
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
-          <t>Would you like to be part of a vibrant and collaborative academic community, contributing to real-world innovations? Join us in shaping the future of 'control systems technology' in the heart of the h</t>
+          <t>Applications are invited for appointment as Tenure-track Professor/ Associate Professor/ Assistant Professor in Global Health (several posts), School of Public Health (Ref.: 536310), to commence as so</t>
         </is>
       </c>
       <c r="M112" s="5" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/assistant-professor-in-control-systems-technology-for-emerging-application-areas-at-eindhoven-university-of-technology-4449015225</t>
+          <t>https://hk.linkedin.com/jobs/view/tenure-track-professor-associate-professor-assistant-professor-in-global-health-several-posts-school-of-public-health-at-hkumed-%E2%80%93-the-university-of-hong-kong-4418123989</t>
         </is>
       </c>
       <c r="N112" s="3" t="inlineStr">
@@ -10437,12 +10454,12 @@
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="Q112" s="6" t="inlineStr">
@@ -10451,26 +10468,26 @@
         </is>
       </c>
       <c r="R112" s="2" t="n">
-        <v>51.4486602</v>
+        <v>22.3492361</v>
       </c>
       <c r="S112" s="2" t="n">
-        <v>5.4903996</v>
+        <v>114.1857778</v>
       </c>
       <c r="T112" s="2" t="inlineStr">
         <is>
-          <t>61c642450ddce455</t>
+          <t>6c0230e6f7f95d23</t>
         </is>
       </c>
     </row>
     <row r="113" ht="26" customHeight="1">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Tenure-track Professor/ Associate Professor/ Assistant Professor in Global Health (several posts), School of Public Health</t>
+          <t>Lecturer - Land Transport Engineering (Automotive) [ITE College West]</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>HKUMed – The University of Hong Kong</t>
+          <t>Institute of Technical Education</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -10488,12 +10505,12 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>Hong Kong SAR</t>
+          <t>Singapore, Singapore</t>
         </is>
       </c>
       <c r="I113" s="3" t="inlineStr">
         <is>
-          <t>Posted 2 weeks ago</t>
+          <t>Posted 6 days ago</t>
         </is>
       </c>
       <c r="J113" s="3" t="inlineStr"/>
@@ -10504,12 +10521,12 @@
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
-          <t>Applications are invited for appointment as Tenure-track Professor/ Associate Professor/ Assistant Professor in Global Health (several posts), School of Public Health (Ref.: 536310), to commence as so</t>
+          <t>[What the role is] As a Lecturer, your contributions go beyond teaching and facilitating learning. You will play a critical role in recognising and nurturing your students’ potential and their lifelon</t>
         </is>
       </c>
       <c r="M113" s="5" t="inlineStr">
         <is>
-          <t>https://hk.linkedin.com/jobs/view/tenure-track-professor-associate-professor-assistant-professor-in-global-health-several-posts-school-of-public-health-at-hkumed-%E2%80%93-the-university-of-hong-kong-4418123989</t>
+          <t>https://sg.linkedin.com/jobs/view/lecturer-land-transport-engineering-automotive-ite-college-west-at-institute-of-technical-education-4468133509</t>
         </is>
       </c>
       <c r="N113" s="3" t="inlineStr">
@@ -10519,12 +10536,12 @@
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="Q113" s="6" t="inlineStr">
@@ -10533,26 +10550,26 @@
         </is>
       </c>
       <c r="R113" s="2" t="n">
-        <v>22.3492361</v>
+        <v>4.6734345</v>
       </c>
       <c r="S113" s="2" t="n">
-        <v>114.1857778</v>
+        <v>-74.1436672</v>
       </c>
       <c r="T113" s="2" t="inlineStr">
         <is>
-          <t>6c0230e6f7f95d23</t>
+          <t>b0b079856b84fe41</t>
         </is>
       </c>
     </row>
     <row r="114" ht="26" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Lecturer - Land Transport Engineering (Automotive) [ITE College West]</t>
+          <t>[LTA-PP] DEPUTY/ASSISTANT MANAGER, POLICY (PRIVATE TRANSPORT)</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Institute of Technical Education</t>
+          <t>Land Transport Authority (LTA) Singapore</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -10575,7 +10592,7 @@
       </c>
       <c r="I114" s="3" t="inlineStr">
         <is>
-          <t>Posted 6 days ago</t>
+          <t>Posted 5 days ago</t>
         </is>
       </c>
       <c r="J114" s="3" t="inlineStr"/>
@@ -10586,12 +10603,12 @@
       </c>
       <c r="L114" s="4" t="inlineStr">
         <is>
-          <t>[What the role is] As a Lecturer, your contributions go beyond teaching and facilitating learning. You will play a critical role in recognising and nurturing your students’ potential and their lifelon</t>
+          <t>[What the role is] You will be part of LTA's Private Transport Policy Team, that develops and reviews policies that shape how Singaporeans own and use vehicles. The team is responsible for key policy</t>
         </is>
       </c>
       <c r="M114" s="5" t="inlineStr">
         <is>
-          <t>https://sg.linkedin.com/jobs/view/lecturer-land-transport-engineering-automotive-ite-college-west-at-institute-of-technical-education-4468133509</t>
+          <t>https://sg.linkedin.com/jobs/view/lta-pp-deputy-assistant-manager-policy-private-transport-at-land-transport-authority-lta-singapore-4470432609</t>
         </is>
       </c>
       <c r="N114" s="3" t="inlineStr">
@@ -10615,26 +10632,26 @@
         </is>
       </c>
       <c r="R114" s="2" t="n">
-        <v>4.6734345</v>
+        <v>1.2899175</v>
       </c>
       <c r="S114" s="2" t="n">
-        <v>-74.1436672</v>
+        <v>103.8519072</v>
       </c>
       <c r="T114" s="2" t="inlineStr">
         <is>
-          <t>b0b079856b84fe41</t>
+          <t>6eaba38b6bbbb1a2</t>
         </is>
       </c>
     </row>
     <row r="115" ht="26" customHeight="1">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>[LTA-PP] DEPUTY/ASSISTANT MANAGER, POLICY (PRIVATE TRANSPORT)</t>
+          <t>Assistant Professor / Associate Professor (Tenure-Track), Associate Professor (Practice-Track) in Maritime Studies</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Land Transport Authority (LTA) Singapore</t>
+          <t>Nanyang Technological University Singapore</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -10657,7 +10674,7 @@
       </c>
       <c r="I115" s="3" t="inlineStr">
         <is>
-          <t>Posted 5 days ago</t>
+          <t>Posted 2 months ago</t>
         </is>
       </c>
       <c r="J115" s="3" t="inlineStr"/>
@@ -10668,12 +10685,12 @@
       </c>
       <c r="L115" s="4" t="inlineStr">
         <is>
-          <t>[What the role is] You will be part of LTA's Private Transport Policy Team, that develops and reviews policies that shape how Singaporeans own and use vehicles. The team is responsible for key policy</t>
+          <t>NTU Singapore is in one of the world's most rapidly growing countries. As a beautiful and vibrant nation in Southeast Asia, Singapore attracts top talent from around the globe. NTU Singapore is one of</t>
         </is>
       </c>
       <c r="M115" s="5" t="inlineStr">
         <is>
-          <t>https://sg.linkedin.com/jobs/view/lta-pp-deputy-assistant-manager-policy-private-transport-at-land-transport-authority-lta-singapore-4470432609</t>
+          <t>https://sg.linkedin.com/jobs/view/assistant-professor-associate-professor-tenure-track-associate-professor-practice-track-in-maritime-studies-at-nanyang-technological-university-singapore-4432368242</t>
         </is>
       </c>
       <c r="N115" s="3" t="inlineStr">
@@ -10683,7 +10700,7 @@
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="P115" s="2" t="inlineStr">
@@ -10697,26 +10714,26 @@
         </is>
       </c>
       <c r="R115" s="2" t="n">
-        <v>1.2899175</v>
+        <v>1.3483</v>
       </c>
       <c r="S115" s="2" t="n">
-        <v>103.8519072</v>
+        <v>103.6831</v>
       </c>
       <c r="T115" s="2" t="inlineStr">
         <is>
-          <t>6eaba38b6bbbb1a2</t>
+          <t>1e0a7536f9329af5</t>
         </is>
       </c>
     </row>
     <row r="116" ht="26" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor / Associate Professor (Tenure-Track), Associate Professor (Practice-Track) in Maritime Studies</t>
+          <t>Assistant Professor (Biostatistics and Modelling), Saw Swee Hock School of Public Health, NUS</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Nanyang Technological University Singapore</t>
+          <t>National University of Singapore</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -10739,7 +10756,7 @@
       </c>
       <c r="I116" s="3" t="inlineStr">
         <is>
-          <t>Posted 2 months ago</t>
+          <t>Posted 3 months ago</t>
         </is>
       </c>
       <c r="J116" s="3" t="inlineStr"/>
@@ -10750,12 +10767,12 @@
       </c>
       <c r="L116" s="4" t="inlineStr">
         <is>
-          <t>NTU Singapore is in one of the world's most rapidly growing countries. As a beautiful and vibrant nation in Southeast Asia, Singapore attracts top talent from around the globe. NTU Singapore is one of</t>
+          <t>Job Title: Assistant Professor (Biostatistics and Modelling), Saw Swee Hock School of Public Health, NUS University-Level Unit: Saw Swee Hock School of Public Health Faculty/Department-Level Unit: Saw</t>
         </is>
       </c>
       <c r="M116" s="5" t="inlineStr">
         <is>
-          <t>https://sg.linkedin.com/jobs/view/assistant-professor-associate-professor-tenure-track-associate-professor-practice-track-in-maritime-studies-at-nanyang-technological-university-singapore-4432368242</t>
+          <t>https://sg.linkedin.com/jobs/view/assistant-professor-biostatistics-and-modelling-saw-swee-hock-school-of-public-health-nus-at-national-university-of-singapore-4433037029</t>
         </is>
       </c>
       <c r="N116" s="3" t="inlineStr">
@@ -10770,7 +10787,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="Q116" s="6" t="inlineStr">
@@ -10779,26 +10796,26 @@
         </is>
       </c>
       <c r="R116" s="2" t="n">
-        <v>1.3483</v>
+        <v>1.2966</v>
       </c>
       <c r="S116" s="2" t="n">
-        <v>103.6831</v>
+        <v>103.7764</v>
       </c>
       <c r="T116" s="2" t="inlineStr">
         <is>
-          <t>1e0a7536f9329af5</t>
+          <t>dcb75613dfdef163</t>
         </is>
       </c>
     </row>
     <row r="117" ht="26" customHeight="1">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor (Biostatistics and Modelling), Saw Swee Hock School of Public Health, NUS</t>
+          <t>Assistant Professor - Mechatronics and Mechanical Engineering</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>National University of Singapore</t>
+          <t>Ontario Tech University</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -10816,12 +10833,12 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>Singapore, Singapore</t>
+          <t>Oshawa, Ontario, Canada</t>
         </is>
       </c>
       <c r="I117" s="3" t="inlineStr">
         <is>
-          <t>Posted 3 months ago</t>
+          <t>Posted 2 days ago</t>
         </is>
       </c>
       <c r="J117" s="3" t="inlineStr"/>
@@ -10832,12 +10849,12 @@
       </c>
       <c r="L117" s="4" t="inlineStr">
         <is>
-          <t>Job Title: Assistant Professor (Biostatistics and Modelling), Saw Swee Hock School of Public Health, NUS University-Level Unit: Saw Swee Hock School of Public Health Faculty/Department-Level Unit: Saw</t>
+          <t>Tracking Code: req2248 Faculty/Department: Faculty of Engineering and Applied Science Appointment Type: Tenured and Tenure-Track, Full-time Continuing Number of Positions: 1 Salary Grade: Hiring Range</t>
         </is>
       </c>
       <c r="M117" s="5" t="inlineStr">
         <is>
-          <t>https://sg.linkedin.com/jobs/view/assistant-professor-biostatistics-and-modelling-saw-swee-hock-school-of-public-health-nus-at-national-university-of-singapore-4433037029</t>
+          <t>https://ca.linkedin.com/jobs/view/assistant-professor-mechatronics-and-mechanical-engineering-at-ontario-tech-university-4466293036</t>
         </is>
       </c>
       <c r="N117" s="3" t="inlineStr">
@@ -10847,12 +10864,12 @@
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="Q117" s="6" t="inlineStr">
@@ -10861,26 +10878,26 @@
         </is>
       </c>
       <c r="R117" s="2" t="n">
-        <v>1.2966</v>
+        <v>43.9483414</v>
       </c>
       <c r="S117" s="2" t="n">
-        <v>103.7764</v>
+        <v>-78.8982025</v>
       </c>
       <c r="T117" s="2" t="inlineStr">
         <is>
-          <t>dcb75613dfdef163</t>
+          <t>388fabc48392f309</t>
         </is>
       </c>
     </row>
     <row r="118" ht="26" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor - Mechatronics and Mechanical Engineering</t>
+          <t>Lecturer (Mobility &amp; Robotic Systems)</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Ontario Tech University</t>
+          <t>Republic Polytechnic</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -10898,12 +10915,12 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>Oshawa, Ontario, Canada</t>
+          <t>Singapore, Singapore</t>
         </is>
       </c>
       <c r="I118" s="3" t="inlineStr">
         <is>
-          <t>Posted 2 days ago</t>
+          <t>Posted 1 week ago</t>
         </is>
       </c>
       <c r="J118" s="3" t="inlineStr"/>
@@ -10914,12 +10931,12 @@
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
-          <t>Tracking Code: req2248 Faculty/Department: Faculty of Engineering and Applied Science Appointment Type: Tenured and Tenure-Track, Full-time Continuing Number of Positions: 1 Salary Grade: Hiring Range</t>
+          <t>Job Description: Curriculum development, course delivery and student project supervision in the areas of large mobility and smart robotic engineering systems. This includes, but is not limited to, aut</t>
         </is>
       </c>
       <c r="M118" s="5" t="inlineStr">
         <is>
-          <t>https://ca.linkedin.com/jobs/view/assistant-professor-mechatronics-and-mechanical-engineering-at-ontario-tech-university-4466293036</t>
+          <t>https://sg.linkedin.com/jobs/view/lecturer-mobility-robotic-systems-at-republic-polytechnic-4466503273</t>
         </is>
       </c>
       <c r="N118" s="3" t="inlineStr">
@@ -10943,26 +10960,26 @@
         </is>
       </c>
       <c r="R118" s="2" t="n">
-        <v>43.9483414</v>
+        <v>1.4443688</v>
       </c>
       <c r="S118" s="2" t="n">
-        <v>-78.8982025</v>
+        <v>103.7853712</v>
       </c>
       <c r="T118" s="2" t="inlineStr">
         <is>
-          <t>388fabc48392f309</t>
+          <t>00c292267aae717a</t>
         </is>
       </c>
     </row>
     <row r="119" ht="26" customHeight="1">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>Lecturer (Mobility &amp; Robotic Systems)</t>
+          <t>Teaching Assistant Professor</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Republic Polytechnic</t>
+          <t>State of South Carolina</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -10980,12 +10997,12 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>Singapore, Singapore</t>
+          <t>Columbia, SC</t>
         </is>
       </c>
       <c r="I119" s="3" t="inlineStr">
         <is>
-          <t>Posted 1 week ago</t>
+          <t>Posted 18 hours ago</t>
         </is>
       </c>
       <c r="J119" s="3" t="inlineStr"/>
@@ -10996,12 +11013,12 @@
       </c>
       <c r="L119" s="4" t="inlineStr">
         <is>
-          <t>Job Description: Curriculum development, course delivery and student project supervision in the areas of large mobility and smart robotic engineering systems. This includes, but is not limited to, aut</t>
+          <t>Job Responsibilities Teaching Assistant Professor Department: CEC Civil and Environmental Engineering Part/Full Time: Full Time Advertised Salary Range: To commensurate with qualifications About UofSC</t>
         </is>
       </c>
       <c r="M119" s="5" t="inlineStr">
         <is>
-          <t>https://sg.linkedin.com/jobs/view/lecturer-mobility-robotic-systems-at-republic-polytechnic-4466503273</t>
+          <t>https://www.linkedin.com/jobs/view/teaching-assistant-professor-at-state-of-south-carolina-4471523322</t>
         </is>
       </c>
       <c r="N119" s="3" t="inlineStr">
@@ -11011,7 +11028,7 @@
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="P119" s="2" t="inlineStr">
@@ -11025,26 +11042,26 @@
         </is>
       </c>
       <c r="R119" s="2" t="n">
-        <v>1.4443688</v>
+        <v>39.7978672</v>
       </c>
       <c r="S119" s="2" t="n">
-        <v>103.7853712</v>
+        <v>-77.255923</v>
       </c>
       <c r="T119" s="2" t="inlineStr">
         <is>
-          <t>00c292267aae717a</t>
+          <t>b9c68db81eb752b4</t>
         </is>
       </c>
     </row>
     <row r="120" ht="26" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Teaching Assistant Professor</t>
+          <t>Research Assistant Professor</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>State of South Carolina</t>
+          <t>The Chinese University of Hong Kong</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -11062,12 +11079,12 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>Columbia, SC</t>
+          <t>Hong Kong, Hong Kong SAR</t>
         </is>
       </c>
       <c r="I120" s="3" t="inlineStr">
         <is>
-          <t>Posted 18 hours ago</t>
+          <t>Posted 2 weeks ago</t>
         </is>
       </c>
       <c r="J120" s="3" t="inlineStr"/>
@@ -11078,12 +11095,12 @@
       </c>
       <c r="L120" s="4" t="inlineStr">
         <is>
-          <t>Job Responsibilities Teaching Assistant Professor Department: CEC Civil and Environmental Engineering Part/Full Time: Full Time Advertised Salary Range: To commensurate with qualifications About UofSC</t>
+          <t>Department of Electronic Engineering Research Assistant Professor (Ref.: 260001FH) (Closing Date: Until the post is filled) The Department of Electronic Engineering (EE) at the Chinese University of H</t>
         </is>
       </c>
       <c r="M120" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/teaching-assistant-professor-at-state-of-south-carolina-4471523322</t>
+          <t>https://hk.linkedin.com/jobs/view/research-assistant-professor-at-the-chinese-university-of-hong-kong-4466058445</t>
         </is>
       </c>
       <c r="N120" s="3" t="inlineStr">
@@ -11093,7 +11110,7 @@
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="P120" s="2" t="inlineStr">
@@ -11107,26 +11124,26 @@
         </is>
       </c>
       <c r="R120" s="2" t="n">
-        <v>39.7978672</v>
+        <v>22.4201838</v>
       </c>
       <c r="S120" s="2" t="n">
-        <v>-77.255923</v>
+        <v>114.2079145</v>
       </c>
       <c r="T120" s="2" t="inlineStr">
         <is>
-          <t>b9c68db81eb752b4</t>
+          <t>78a3531d318468ce</t>
         </is>
       </c>
     </row>
     <row r="121" ht="26" customHeight="1">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Research Assistant Professor</t>
+          <t>Assistant Professor (tenure-track)</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>The Chinese University of Hong Kong</t>
+          <t>The University of British Columbia</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -11144,12 +11161,12 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>Hong Kong, Hong Kong SAR</t>
+          <t>Vancouver, British Columbia, Canada</t>
         </is>
       </c>
       <c r="I121" s="3" t="inlineStr">
         <is>
-          <t>Posted 2 weeks ago</t>
+          <t>Posted 2 months ago</t>
         </is>
       </c>
       <c r="J121" s="3" t="inlineStr"/>
@@ -11160,12 +11177,12 @@
       </c>
       <c r="L121" s="4" t="inlineStr">
         <is>
-          <t>Department of Electronic Engineering Research Assistant Professor (Ref.: 260001FH) (Closing Date: Until the post is filled) The Department of Electronic Engineering (EE) at the Chinese University of H</t>
+          <t>Academic Job Category Faculty Bargaining Job Title Assistant Professor (tenure-track) Department Administrative Leadership | Department of Civil Engineering | Faculty of Applied Science (Bernard Laval</t>
         </is>
       </c>
       <c r="M121" s="5" t="inlineStr">
         <is>
-          <t>https://hk.linkedin.com/jobs/view/research-assistant-professor-at-the-chinese-university-of-hong-kong-4466058445</t>
+          <t>https://ca.linkedin.com/jobs/view/assistant-professor-tenure-track-at-the-university-of-british-columbia-4446163254</t>
         </is>
       </c>
       <c r="N121" s="3" t="inlineStr">
@@ -11175,40 +11192,40 @@
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="P121" s="2" t="inlineStr">
+        <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="P121" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
       <c r="Q121" s="6" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
       <c r="R121" s="2" t="n">
-        <v>22.4201838</v>
+        <v>49.2606</v>
       </c>
       <c r="S121" s="2" t="n">
-        <v>114.2079145</v>
+        <v>-123.246</v>
       </c>
       <c r="T121" s="2" t="inlineStr">
         <is>
-          <t>78a3531d318468ce</t>
+          <t>67496928d1d58372</t>
         </is>
       </c>
     </row>
     <row r="122" ht="26" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor (tenure-track)</t>
+          <t>Assistant or Associate Professor in Structural Engineering (Research and Education) - School of Engineering - 107706 - Grade 8 or 9</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>The University of British Columbia</t>
+          <t>University of Birmingham</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -11226,12 +11243,12 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>Vancouver, British Columbia, Canada</t>
+          <t>Birmingham, England, United Kingdom</t>
         </is>
       </c>
       <c r="I122" s="3" t="inlineStr">
         <is>
-          <t>Posted 2 months ago</t>
+          <t>Posted 1 month ago</t>
         </is>
       </c>
       <c r="J122" s="3" t="inlineStr"/>
@@ -11242,12 +11259,12 @@
       </c>
       <c r="L122" s="4" t="inlineStr">
         <is>
-          <t>Academic Job Category Faculty Bargaining Job Title Assistant Professor (tenure-track) Department Administrative Leadership | Department of Civil Engineering | Faculty of Applied Science (Bernard Laval</t>
+          <t>Job Description Position Details School of Engineering Location: University of Birmingham, Edgbaston, Birmingham UK Grade 8 Full time starting salary is normally in the range £47,389 to £56,535 with p</t>
         </is>
       </c>
       <c r="M122" s="5" t="inlineStr">
         <is>
-          <t>https://ca.linkedin.com/jobs/view/assistant-professor-tenure-track-at-the-university-of-british-columbia-4446163254</t>
+          <t>https://uk.linkedin.com/jobs/view/assistant-or-associate-professor-in-structural-engineering-research-and-education-school-of-engineering-107706-grade-8-or-9-at-university-of-birmingham-4456842407</t>
         </is>
       </c>
       <c r="N122" s="3" t="inlineStr">
@@ -11271,26 +11288,26 @@
         </is>
       </c>
       <c r="R122" s="2" t="n">
-        <v>49.2606</v>
+        <v>52.4508</v>
       </c>
       <c r="S122" s="2" t="n">
-        <v>-123.246</v>
+        <v>-1.9305</v>
       </c>
       <c r="T122" s="2" t="inlineStr">
         <is>
-          <t>67496928d1d58372</t>
+          <t>337b52e2521d491e</t>
         </is>
       </c>
     </row>
     <row r="123" ht="26" customHeight="1">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>Assistant or Associate Professor in Structural Engineering (Research and Education) - School of Engineering - 107706 - Grade 8 or 9</t>
+          <t>Assistant or Associate Professor in Supply Chain Management</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>University of Birmingham</t>
+          <t>University of Guelph</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -11308,12 +11325,12 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>Birmingham, England, United Kingdom</t>
+          <t>Guelph, Ontario, Canada</t>
         </is>
       </c>
       <c r="I123" s="3" t="inlineStr">
         <is>
-          <t>Posted 1 month ago</t>
+          <t>Posted 6 months ago</t>
         </is>
       </c>
       <c r="J123" s="3" t="inlineStr"/>
@@ -11324,12 +11341,12 @@
       </c>
       <c r="L123" s="4" t="inlineStr">
         <is>
-          <t>Job Description Position Details School of Engineering Location: University of Birmingham, Edgbaston, Birmingham UK Grade 8 Full time starting salary is normally in the range £47,389 to £56,535 with p</t>
+          <t>Location: Guelph, ON, CA, N1G 2W1 Primary Category Page: Faculty, Librarian and Veterinarian Division: Gordon S Lang School of Business and Economics Requisition ID: 2283 Position Title / Rank: Assist</t>
         </is>
       </c>
       <c r="M123" s="5" t="inlineStr">
         <is>
-          <t>https://uk.linkedin.com/jobs/view/assistant-or-associate-professor-in-structural-engineering-research-and-education-school-of-engineering-107706-grade-8-or-9-at-university-of-birmingham-4456842407</t>
+          <t>https://ca.linkedin.com/jobs/view/assistant-or-associate-professor-in-supply-chain-management-at-university-of-guelph-4397076267</t>
         </is>
       </c>
       <c r="N123" s="3" t="inlineStr">
@@ -11339,7 +11356,7 @@
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="P123" s="2" t="inlineStr">
@@ -11353,26 +11370,26 @@
         </is>
       </c>
       <c r="R123" s="2" t="n">
-        <v>52.4508</v>
+        <v>43.5327864</v>
       </c>
       <c r="S123" s="2" t="n">
-        <v>-1.9305</v>
+        <v>-80.22499740000001</v>
       </c>
       <c r="T123" s="2" t="inlineStr">
         <is>
-          <t>337b52e2521d491e</t>
+          <t>e9269b52adecc4bd</t>
         </is>
       </c>
     </row>
     <row r="124" ht="26" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Assistant or Associate Professor in Supply Chain Management</t>
+          <t>Department of Geodesy and Geomatics Engineering: Tenure-Track Assistant Professor in Positioning, Navigation, and Timing</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>University of Guelph</t>
+          <t>University of New Brunswick</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -11390,12 +11407,12 @@
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>Guelph, Ontario, Canada</t>
+          <t>Fredericton, New Brunswick, Canada</t>
         </is>
       </c>
       <c r="I124" s="3" t="inlineStr">
         <is>
-          <t>Posted 6 months ago</t>
+          <t>Posted 5 months ago</t>
         </is>
       </c>
       <c r="J124" s="3" t="inlineStr"/>
@@ -11406,12 +11423,12 @@
       </c>
       <c r="L124" s="4" t="inlineStr">
         <is>
-          <t>Location: Guelph, ON, CA, N1G 2W1 Primary Category Page: Faculty, Librarian and Veterinarian Division: Gordon S Lang School of Business and Economics Requisition ID: 2283 Position Title / Rank: Assist</t>
+          <t>The Department of Geodesy and Geomatics Engineering at the University of New Brunswick in Fredericton invites applications for a tenure-track position in Geodesy and Geomatics Engineering at the rank</t>
         </is>
       </c>
       <c r="M124" s="5" t="inlineStr">
         <is>
-          <t>https://ca.linkedin.com/jobs/view/assistant-or-associate-professor-in-supply-chain-management-at-university-of-guelph-4397076267</t>
+          <t>https://ca.linkedin.com/jobs/view/department-of-geodesy-and-geomatics-engineering-tenure-track-assistant-professor-in-positioning-navigation-and-timing-at-university-of-new-brunswick-4406141089</t>
         </is>
       </c>
       <c r="N124" s="3" t="inlineStr">
@@ -11421,40 +11438,40 @@
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="P124" s="2" t="inlineStr">
+        <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="P124" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
       <c r="Q124" s="6" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
       <c r="R124" s="2" t="n">
-        <v>43.5327864</v>
+        <v>45.9455202</v>
       </c>
       <c r="S124" s="2" t="n">
-        <v>-80.22499740000001</v>
+        <v>-66.64018609999999</v>
       </c>
       <c r="T124" s="2" t="inlineStr">
         <is>
-          <t>e9269b52adecc4bd</t>
+          <t>6f8958be6b7d9994</t>
         </is>
       </c>
     </row>
     <row r="125" ht="26" customHeight="1">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Department of Geodesy and Geomatics Engineering: Tenure-Track Assistant Professor in Positioning, Navigation, and Timing</t>
+          <t>Two Assistant Professorship Positions in Sustainability Studies</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>University of New Brunswick</t>
+          <t>University of Twente</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -11472,12 +11489,12 @@
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>Fredericton, New Brunswick, Canada</t>
+          <t>Enschede, Overijssel, Netherlands</t>
         </is>
       </c>
       <c r="I125" s="3" t="inlineStr">
         <is>
-          <t>Posted 5 months ago</t>
+          <t>Posted 1 week ago</t>
         </is>
       </c>
       <c r="J125" s="3" t="inlineStr"/>
@@ -11488,12 +11505,12 @@
       </c>
       <c r="L125" s="4" t="inlineStr">
         <is>
-          <t>The Department of Geodesy and Geomatics Engineering at the University of New Brunswick in Fredericton invites applications for a tenure-track position in Geodesy and Geomatics Engineering at the rank</t>
+          <t>Job Description We seek new enthusiastic colleagues whose academic training and research experience provide a clear foundation for contributing to: Position 1: Social science, quantitative and qualita</t>
         </is>
       </c>
       <c r="M125" s="5" t="inlineStr">
         <is>
-          <t>https://ca.linkedin.com/jobs/view/department-of-geodesy-and-geomatics-engineering-tenure-track-assistant-professor-in-positioning-navigation-and-timing-at-university-of-new-brunswick-4406141089</t>
+          <t>https://nl.linkedin.com/jobs/view/two-assistant-professorship-positions-in-sustainability-studies-at-university-of-twente-4463028013</t>
         </is>
       </c>
       <c r="N125" s="3" t="inlineStr">
@@ -11503,7 +11520,7 @@
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="P125" s="2" t="inlineStr">
@@ -11517,26 +11534,26 @@
         </is>
       </c>
       <c r="R125" s="2" t="n">
-        <v>45.9455202</v>
+        <v>52.2433268</v>
       </c>
       <c r="S125" s="2" t="n">
-        <v>-66.64018609999999</v>
+        <v>6.8509157</v>
       </c>
       <c r="T125" s="2" t="inlineStr">
         <is>
-          <t>6f8958be6b7d9994</t>
+          <t>bc3324541c93bcd3</t>
         </is>
       </c>
     </row>
     <row r="126" ht="26" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Two Assistant Professorship Positions in Sustainability Studies</t>
+          <t>WARSIM/JCATS Instructor Controller</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>University of Twente</t>
+          <t>Valiant Integrated Services</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -11554,12 +11571,12 @@
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>Enschede, Overijssel, Netherlands</t>
+          <t>Busan Metropolitan Area</t>
         </is>
       </c>
       <c r="I126" s="3" t="inlineStr">
         <is>
-          <t>Posted 1 week ago</t>
+          <t>Posted 2 months ago</t>
         </is>
       </c>
       <c r="J126" s="3" t="inlineStr"/>
@@ -11570,12 +11587,12 @@
       </c>
       <c r="L126" s="4" t="inlineStr">
         <is>
-          <t>Job Description We seek new enthusiastic colleagues whose academic training and research experience provide a clear foundation for contributing to: Position 1: Social science, quantitative and qualita</t>
+          <t>Valiant is looking for a WARSIM/JCATS Instructor Controller to join our team! Essential Duties And Responsibilities Support military training exercises for the Korea Battle Simulation Center. Responsi</t>
         </is>
       </c>
       <c r="M126" s="5" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/two-assistant-professorship-positions-in-sustainability-studies-at-university-of-twente-4463028013</t>
+          <t>https://kr.linkedin.com/jobs/view/warsim-jcats-instructor-controller-at-valiant-integrated-services-4430736441</t>
         </is>
       </c>
       <c r="N126" s="3" t="inlineStr">
@@ -11599,26 +11616,26 @@
         </is>
       </c>
       <c r="R126" s="2" t="n">
-        <v>52.2433268</v>
+        <v>35.1283054</v>
       </c>
       <c r="S126" s="2" t="n">
-        <v>6.8509157</v>
+        <v>129.0960519</v>
       </c>
       <c r="T126" s="2" t="inlineStr">
         <is>
-          <t>bc3324541c93bcd3</t>
+          <t>699310b717b5d28c</t>
         </is>
       </c>
     </row>
     <row r="127" ht="26" customHeight="1">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>WARSIM/JCATS Instructor Controller</t>
+          <t>Logistics Operations Planning Assistant Manager, Test Course Operations</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Valiant Integrated Services</t>
+          <t>Woven by Toyota</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -11636,12 +11653,12 @@
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>Busan Metropolitan Area</t>
+          <t>Susono, Shizuoka, Japan</t>
         </is>
       </c>
       <c r="I127" s="3" t="inlineStr">
         <is>
-          <t>Posted 2 months ago</t>
+          <t>Posted 3 weeks ago</t>
         </is>
       </c>
       <c r="J127" s="3" t="inlineStr"/>
@@ -11652,12 +11669,12 @@
       </c>
       <c r="L127" s="4" t="inlineStr">
         <is>
-          <t>Valiant is looking for a WARSIM/JCATS Instructor Controller to join our team! Essential Duties And Responsibilities Support military training exercises for the Korea Battle Simulation Center. Responsi</t>
+          <t>About Woven By Toyota Woven by Toyota is enabling Toyota’s once-in-a-century transformation into a mobility company. Inspired by a legacy of innovating for the benefit of others, our mission is to cha</t>
         </is>
       </c>
       <c r="M127" s="5" t="inlineStr">
         <is>
-          <t>https://kr.linkedin.com/jobs/view/warsim-jcats-instructor-controller-at-valiant-integrated-services-4430736441</t>
+          <t>https://jp.linkedin.com/jobs/view/logistics-operations-planning-assistant-manager-test-course-operations-at-woven-by-toyota-4441816215</t>
         </is>
       </c>
       <c r="N127" s="3" t="inlineStr">
@@ -11681,31 +11698,31 @@
         </is>
       </c>
       <c r="R127" s="2" t="n">
-        <v>35.1283054</v>
+        <v>40.7039729</v>
       </c>
       <c r="S127" s="2" t="n">
-        <v>129.0960519</v>
+        <v>-73.986845</v>
       </c>
       <c r="T127" s="2" t="inlineStr">
         <is>
-          <t>699310b717b5d28c</t>
+          <t>951e0a12877591f6</t>
         </is>
       </c>
     </row>
     <row r="128" ht="26" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Logistics Operations Planning Assistant Manager, Test Course Operations</t>
+          <t>Tenure-Track Assistant Professor of Statistics</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Woven by Toyota</t>
+          <t>Haverford College</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Transportation Engineering</t>
+          <t>Transportation / Civil Engineering</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr"/>
@@ -11718,15 +11735,19 @@
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>Susono, Shizuoka, Japan</t>
+          <t>Haverford, Pennsylvania, US</t>
         </is>
       </c>
       <c r="I128" s="3" t="inlineStr">
         <is>
-          <t>Posted 3 weeks ago</t>
-        </is>
-      </c>
-      <c r="J128" s="3" t="inlineStr"/>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="J128" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
           <t>Not specified</t>
@@ -11734,27 +11755,27 @@
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
-          <t>About Woven By Toyota Woven by Toyota is enabling Toyota’s once-in-a-century transformation into a mobility company. Inspired by a legacy of innovating for the benefit of others, our mission is to cha</t>
+          <t>Tenure-Track Assistant Professor of Statistics Employer Haverford College Location Haverford, Pennsylvania, United States Salary Competitive Salary Date posted Jul 30, 2026 View more categories View l</t>
         </is>
       </c>
       <c r="M128" s="5" t="inlineStr">
         <is>
-          <t>https://jp.linkedin.com/jobs/view/logistics-operations-planning-assistant-manager-test-course-operations-at-woven-by-toyota-4441816215</t>
+          <t>https://jobs.chronicle.com/job/38017766/tenure-track-assistant-professor-of-statistics/</t>
         </is>
       </c>
       <c r="N128" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q128" s="6" t="inlineStr">
@@ -11763,31 +11784,31 @@
         </is>
       </c>
       <c r="R128" s="2" t="n">
-        <v>40.7039729</v>
+        <v>40.0071506</v>
       </c>
       <c r="S128" s="2" t="n">
-        <v>-73.986845</v>
+        <v>-75.3069423</v>
       </c>
       <c r="T128" s="2" t="inlineStr">
         <is>
-          <t>951e0a12877591f6</t>
+          <t>139bc27f2f7867a0</t>
         </is>
       </c>
     </row>
     <row r="129" ht="26" customHeight="1">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>Tenure-Track Assistant Professor of Statistics</t>
+          <t>Research Assistant/Associate in Bacterial DNA Replication</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Haverford College</t>
+          <t>Newcastle University</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Transportation / Civil Engineering</t>
+          <t>Faculty Medical Sciences</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr"/>
@@ -11800,7 +11821,7 @@
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>Haverford, Pennsylvania, US</t>
+          <t>Newcastle upon Tyne</t>
         </is>
       </c>
       <c r="I129" s="3" t="inlineStr">
@@ -11820,27 +11841,28 @@
       </c>
       <c r="L129" s="4" t="inlineStr">
         <is>
-          <t>Tenure-Track Assistant Professor of Statistics Employer Haverford College Location Haverford, Pennsylvania, United States Salary Competitive Salary Date posted Jul 30, 2026 View more categories View l</t>
+          <t>Research Assistant/Associate in Bacterial DNA Replication Faculty Medical Sciences Newcastle University Location:
+            Newcastle upon Tyne Salary: £33,951 to £36,636</t>
         </is>
       </c>
       <c r="M129" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38017766/tenure-track-assistant-professor-of-statistics/</t>
+          <t>https://www.jobs.ac.uk/job/DSY021/research-assistant-associate-in-bacterial-dna-replication</t>
         </is>
       </c>
       <c r="N129" s="3" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>Jobs.ac.uk</t>
         </is>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="Q129" s="6" t="inlineStr">
@@ -11849,31 +11871,31 @@
         </is>
       </c>
       <c r="R129" s="2" t="n">
-        <v>40.0071506</v>
+        <v>54.9801751</v>
       </c>
       <c r="S129" s="2" t="n">
-        <v>-75.3069423</v>
+        <v>-1.6146802</v>
       </c>
       <c r="T129" s="2" t="inlineStr">
         <is>
-          <t>139bc27f2f7867a0</t>
+          <t>e92871acf5683165</t>
         </is>
       </c>
     </row>
     <row r="130" ht="26" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Research Assistant/Associate in Bacterial DNA Replication</t>
+          <t>Assistant Professor of Mechanical Engineering</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Newcastle University</t>
+          <t>Montana State University</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Faculty Medical Sciences</t>
+          <t>Mechanical and Industrial Engineering</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr"/>
@@ -11886,48 +11908,47 @@
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>Newcastle upon Tyne</t>
+          <t>Bozeman, Montana</t>
         </is>
       </c>
       <c r="I130" s="3" t="inlineStr">
         <is>
+          <t>Sep. 28, 2026</t>
+        </is>
+      </c>
+      <c r="J130" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="L130" s="4" t="inlineStr">
+        <is>
+          <t>University Job: Assistant Professor of Mechanical Engineering, Montana State University Showing jobs in Engineering . Looking for other jobs? Academic Keys (home page) Adjuncts Agriculture Business Co</t>
+        </is>
+      </c>
+      <c r="M130" s="5" t="inlineStr">
+        <is>
+          <t>https://engineering.academickeys.com/job/ruoe4wlz/Assistant-Professor-of-Mechanical-Engineering</t>
+        </is>
+      </c>
+      <c r="N130" s="3" t="inlineStr">
+        <is>
+          <t>AcademicKeys</t>
+        </is>
+      </c>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="J130" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="K130" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="L130" s="4" t="inlineStr">
-        <is>
-          <t>Research Assistant/Associate in Bacterial DNA Replication Faculty Medical Sciences Newcastle University Location:
-            Newcastle upon Tyne Salary: £33,951 to £36,636</t>
-        </is>
-      </c>
-      <c r="M130" s="5" t="inlineStr">
-        <is>
-          <t>https://www.jobs.ac.uk/job/DSY021/research-assistant-associate-in-bacterial-dna-replication</t>
-        </is>
-      </c>
-      <c r="N130" s="3" t="inlineStr">
-        <is>
-          <t>Jobs.ac.uk</t>
-        </is>
-      </c>
-      <c r="O130" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="Q130" s="6" t="inlineStr">
@@ -11936,69 +11957,79 @@
         </is>
       </c>
       <c r="R130" s="2" t="n">
-        <v>54.9801751</v>
+        <v>45.6639222</v>
       </c>
       <c r="S130" s="2" t="n">
-        <v>-1.6146802</v>
+        <v>-111.079277</v>
       </c>
       <c r="T130" s="2" t="inlineStr">
         <is>
-          <t>e92871acf5683165</t>
+          <t>735f106baf0ccc18</t>
         </is>
       </c>
     </row>
     <row r="131" ht="26" customHeight="1">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Mechanical Engineering</t>
+          <t>Assistant / Associate Professor of Industrial and Systems Engineering</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>Montana State University</t>
+          <t>University of Washington</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Mechanical and Industrial Engineering</t>
-        </is>
-      </c>
-      <c r="D131" s="3" t="inlineStr"/>
-      <c r="E131" s="4" t="inlineStr"/>
-      <c r="F131" s="2" t="inlineStr"/>
+          <t>Industrial &amp; Systems Engineering</t>
+        </is>
+      </c>
+      <c r="D131" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E131" s="4" t="inlineStr">
+        <is>
+          <t>Assistant Professor position in Systems Engineering that aligns with the candidate's expertise in AI-enabled systems and smart mobility through the lens of cyber-physical and autonomous systems.</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>Systems Engineering, Autonomous Systems, Cyber-Physical Systems, AI-Enabled Systems Engineering</t>
+        </is>
+      </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>Bozeman, Montana</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="I131" s="3" t="inlineStr">
         <is>
-          <t>Sep. 28, 2026</t>
+          <t>Priority: 2026-09-15 / Open until filled</t>
         </is>
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>$12,000 – $17,000 per month (9-month service period)</t>
         </is>
       </c>
       <c r="L131" s="4" t="inlineStr">
         <is>
-          <t>University Job: Assistant Professor of Mechanical Engineering, Montana State University Showing jobs in Engineering . Looking for other jobs? Academic Keys (home page) Adjuncts Agriculture Business Co</t>
+          <t>The Department of Industrial and Systems Engineering at the University of Washington seeks an Assistant or Associate Professor specializing in Systems Engineering, requiring a Ph.D. in Systems Engineering, Industrial Engineering, or a related discipline. | Research Topics: Systems Engineering, Autonomous Systems, Cyber-Physical Systems, AI-Enabled Systems Engineering</t>
         </is>
       </c>
       <c r="M131" s="5" t="inlineStr">
         <is>
-          <t>https://engineering.academickeys.com/job/ruoe4wlz/Assistant-Professor-of-Mechanical-Engineering</t>
+          <t>https://engineering.academickeys.com/job/g4m97a60/AssistantAssociate-Professor-Industrial-and-Systems-Engineering-Systems-Engineering-Focus</t>
         </is>
       </c>
       <c r="N131" s="3" t="inlineStr">
@@ -12008,7 +12039,7 @@
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="P131" s="2" t="inlineStr">
@@ -12022,44 +12053,44 @@
         </is>
       </c>
       <c r="R131" s="2" t="n">
-        <v>45.6639222</v>
+        <v>47.6553</v>
       </c>
       <c r="S131" s="2" t="n">
-        <v>-111.079277</v>
+        <v>-122.3035</v>
       </c>
       <c r="T131" s="2" t="inlineStr">
         <is>
-          <t>735f106baf0ccc18</t>
+          <t>9d5682cf4dbca334</t>
         </is>
       </c>
     </row>
     <row r="132" ht="26" customHeight="1">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>Assistant / Associate Professor of Industrial and Systems Engineering</t>
+          <t>Tenure-Track Assistant/Associate Professor of Air Transportation Systems</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>University of Washington</t>
+          <t>Embry-Riddle Aeronautical University</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Industrial &amp; Systems Engineering</t>
-        </is>
-      </c>
-      <c r="D132" s="7" t="n">
-        <v>6</v>
+          <t>School of Graduate Studies, College of Aviation</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>Assistant Professor position in Systems Engineering that aligns with the candidate's expertise in AI-enabled systems and smart mobility through the lens of cyber-physical and autonomous systems.</t>
+          <t>The position focuses specifically on air transportation systems, advanced air mobility, and aviation, which falls outside the candidate's core background in ground-based transportation engineering and public transit planning.</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>Systems Engineering, Autonomous Systems, Cyber-Physical Systems, AI-Enabled Systems Engineering</t>
+          <t>Air Transportation Systems, Advanced Air Mobility, UAS Traffic Management, Machine Learning/AI in Aviation</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
@@ -12069,37 +12100,37 @@
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Daytona Beach, FL</t>
         </is>
       </c>
       <c r="I132" s="3" t="inlineStr">
         <is>
-          <t>Priority: 2026-09-15 / Open until filled</t>
+          <t>Priority: 2026-08-31 / Open until filled</t>
         </is>
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>$12,000 – $17,000 per month (9-month service period)</t>
+          <t>Competitive Salary</t>
         </is>
       </c>
       <c r="L132" s="4" t="inlineStr">
         <is>
-          <t>The Department of Industrial and Systems Engineering at the University of Washington seeks an Assistant or Associate Professor specializing in Systems Engineering, requiring a Ph.D. in Systems Engineering, Industrial Engineering, or a related discipline. | Research Topics: Systems Engineering, Autonomous Systems, Cyber-Physical Systems, AI-Enabled Systems Engineering</t>
+          <t>Embry-Riddle Aeronautical University seeks a tenure-track faculty member in air transportation systems and advanced air mobility requiring a doctorate and relevant experience. | Research Topics: Air Transportation Systems, Advanced Air Mobility, UAS Traffic Management, Machine Learning/AI in Aviation</t>
         </is>
       </c>
       <c r="M132" s="5" t="inlineStr">
         <is>
-          <t>https://engineering.academickeys.com/job/g4m97a60/AssistantAssociate-Professor-Industrial-and-Systems-Engineering-Systems-Engineering-Focus</t>
+          <t>https://jobs.chronicle.com/job/38012134/tenure-track-faculty-position-with-a-focus-on-air-transportation-systems-daytona-beach-campus/</t>
         </is>
       </c>
       <c r="N132" s="3" t="inlineStr">
         <is>
-          <t>AcademicKeys</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="O132" s="2" t="inlineStr">
@@ -12109,7 +12140,7 @@
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="Q132" s="6" t="inlineStr">
@@ -12118,165 +12149,165 @@
         </is>
       </c>
       <c r="R132" s="2" t="n">
-        <v>47.6553</v>
+        <v>29.1895</v>
       </c>
       <c r="S132" s="2" t="n">
-        <v>-122.3035</v>
+        <v>-81.04940000000001</v>
       </c>
       <c r="T132" s="2" t="inlineStr">
         <is>
-          <t>9d5682cf4dbca334</t>
+          <t>52969a207999417a</t>
         </is>
       </c>
     </row>
     <row r="133" ht="26" customHeight="1">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>Tenure-Track Assistant/Associate Professor of Air Transportation Systems</t>
+          <t>Senior Lecturer (Biomedical Engineering) University of Western Australia School of Engineering Posted Jul. 28, 2026</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>Embry-Riddle Aeronautical University</t>
+          <t>Academic Institution</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>School of Graduate Studies, College of Aviation</t>
-        </is>
-      </c>
-      <c r="D133" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E133" s="4" t="inlineStr">
-        <is>
-          <t>The position focuses specifically on air transportation systems, advanced air mobility, and aviation, which falls outside the candidate's core background in ground-based transportation engineering and public transit planning.</t>
-        </is>
-      </c>
-      <c r="F133" s="2" t="inlineStr">
-        <is>
-          <t>Air Transportation Systems, Advanced Air Mobility, UAS Traffic Management, Machine Learning/AI in Aviation</t>
-        </is>
-      </c>
+          <t>School of Engineering</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr"/>
+      <c r="E133" s="4" t="inlineStr"/>
+      <c r="F133" s="2" t="inlineStr"/>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Unspecified</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="I133" s="3" t="inlineStr">
         <is>
-          <t>Priority: 2026-08-31 / Open until filled</t>
+          <t>Aug. 26, 2026</t>
         </is>
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
-          <t>Competitive Salary</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L133" s="4" t="inlineStr">
         <is>
-          <t>Embry-Riddle Aeronautical University seeks a tenure-track faculty member in air transportation systems and advanced air mobility requiring a doctorate and relevant experience. | Research Topics: Air Transportation Systems, Advanced Air Mobility, UAS Traffic Management, Machine Learning/AI in Aviation</t>
+          <t>University Job: Senior Lecturer (Biomedical Engineering), University of Western Australia Showing jobs in Engineering . Looking for other jobs? Academic Keys (home page) Adjuncts Agriculture Business</t>
         </is>
       </c>
       <c r="M133" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38012134/tenure-track-faculty-position-with-a-focus-on-air-transportation-systems-daytona-beach-campus/</t>
+          <t>http://engineering.academickeys.com/job/sxjqk9ic/Senior-Lecturer-Biomedical-Engineering</t>
         </is>
       </c>
       <c r="N133" s="3" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>AcademicKeys</t>
         </is>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="Q133" s="6" t="inlineStr">
-        <is>
-          <t>Active</t>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q133" s="9" t="inlineStr">
+        <is>
+          <t>Past Due</t>
         </is>
       </c>
       <c r="R133" s="2" t="n">
-        <v>29.1895</v>
+        <v>7.1438798</v>
       </c>
       <c r="S133" s="2" t="n">
-        <v>-81.04940000000001</v>
+        <v>125.5990517</v>
       </c>
       <c r="T133" s="2" t="inlineStr">
         <is>
-          <t>52969a207999417a</t>
+          <t>520bf89b522e2bfe</t>
         </is>
       </c>
     </row>
     <row r="134" ht="26" customHeight="1">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>Senior Lecturer (Biomedical Engineering) University of Western Australia School of Engineering Posted Jul. 28, 2026</t>
+          <t>Assistant Professor of Transportation Engineering</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Academic Institution</t>
+          <t>South Dakota State University</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>School of Engineering</t>
-        </is>
-      </c>
-      <c r="D134" s="3" t="inlineStr"/>
-      <c r="E134" s="4" t="inlineStr"/>
-      <c r="F134" s="2" t="inlineStr"/>
+          <t>Department of Civil and Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="D134" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="E134" s="4" t="inlineStr">
+        <is>
+          <t>This is a tenure-track Assistant Professor position in Transportation Engineering within a Civil and Environmental Engineering department, perfectly aligning with the candidate's core research profile.</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>Intelligent Transportation Systems, Transportation Data Analytics, Traffic Operations, Resilient Transportation Systems</t>
+        </is>
+      </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Brookings, SD</t>
         </is>
       </c>
       <c r="I134" s="3" t="inlineStr">
         <is>
-          <t>Aug. 26, 2026</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Starting at $92,000</t>
         </is>
       </c>
       <c r="L134" s="4" t="inlineStr">
         <is>
-          <t>University Job: Senior Lecturer (Biomedical Engineering), University of Western Australia Showing jobs in Engineering . Looking for other jobs? Academic Keys (home page) Adjuncts Agriculture Business</t>
+          <t>South Dakota State University seeks a tenure-track Assistant Professor in Transportation Engineering to teach undergraduate and graduate courses, advise students, and develop an externally funded research program requiring a Ph.D. in Civil Engineering or a closely related field. | Research Topics: Intelligent Transportation Systems, Transportation Data Analytics, Traffic Operations, Resilient Transportation Systems</t>
         </is>
       </c>
       <c r="M134" s="5" t="inlineStr">
         <is>
-          <t>http://engineering.academickeys.com/job/sxjqk9ic/Senior-Lecturer-Biomedical-Engineering</t>
+          <t>https://engineering.academickeys.com/job/m4lk5asr/Assistant-Professor-of-Transportation-Engineering</t>
         </is>
       </c>
       <c r="N134" s="3" t="inlineStr">
@@ -12286,12 +12317,12 @@
       </c>
       <c r="O134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="Q134" s="9" t="inlineStr">
@@ -12300,79 +12331,69 @@
         </is>
       </c>
       <c r="R134" s="2" t="n">
-        <v>7.1438798</v>
+        <v>44.344449</v>
       </c>
       <c r="S134" s="2" t="n">
-        <v>125.5990517</v>
+        <v>-96.79823709999999</v>
       </c>
       <c r="T134" s="2" t="inlineStr">
         <is>
-          <t>520bf89b522e2bfe</t>
+          <t>9b7d5de4753a514b</t>
         </is>
       </c>
     </row>
     <row r="135" ht="26" customHeight="1">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Transportation Engineering</t>
+          <t>Assistant Professor (Electrical Engineering &amp; Renewable Energy)</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>South Dakota State University</t>
+          <t>Oregon Institute of Technology</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Department of Civil and Environmental Engineering</t>
-        </is>
-      </c>
-      <c r="D135" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="E135" s="4" t="inlineStr">
-        <is>
-          <t>This is a tenure-track Assistant Professor position in Transportation Engineering within a Civil and Environmental Engineering department, perfectly aligning with the candidate's core research profile.</t>
-        </is>
-      </c>
-      <c r="F135" s="2" t="inlineStr">
-        <is>
-          <t>Intelligent Transportation Systems, Transportation Data Analytics, Traffic Operations, Resilient Transportation Systems</t>
-        </is>
-      </c>
+          <t>Electrical Engineering &amp; Renewable Energy</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr"/>
+      <c r="E135" s="4" t="inlineStr"/>
+      <c r="F135" s="2" t="inlineStr"/>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Unspecified</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>Brookings, SD</t>
+          <t>Klamath Falls, Oregon</t>
         </is>
       </c>
       <c r="I135" s="3" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>Aug. 5, 2026</t>
         </is>
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
-          <t>Starting at $92,000</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L135" s="4" t="inlineStr">
         <is>
-          <t>South Dakota State University seeks a tenure-track Assistant Professor in Transportation Engineering to teach undergraduate and graduate courses, advise students, and develop an externally funded research program requiring a Ph.D. in Civil Engineering or a closely related field. | Research Topics: Intelligent Transportation Systems, Transportation Data Analytics, Traffic Operations, Resilient Transportation Systems</t>
+          <t>University Job: Assistant Professor (Electrical Engineering &amp; Renewable Energy), Oregon Institute of Technology Showing jobs in Engineering . Looking for other jobs? Academic Keys (home page) Adjuncts</t>
         </is>
       </c>
       <c r="M135" s="5" t="inlineStr">
         <is>
-          <t>https://engineering.academickeys.com/job/m4lk5asr/Assistant-Professor-of-Transportation-Engineering</t>
+          <t>https://engineering.academickeys.com/job/fqg38d2a/Assistant-Professor-Electrical-Engineering--Renewable-Energy</t>
         </is>
       </c>
       <c r="N135" s="3" t="inlineStr">
@@ -12382,7 +12403,7 @@
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="P135" s="2" t="inlineStr">
@@ -12396,54 +12417,64 @@
         </is>
       </c>
       <c r="R135" s="2" t="n">
-        <v>44.344449</v>
+        <v>42.2583928</v>
       </c>
       <c r="S135" s="2" t="n">
-        <v>-96.79823709999999</v>
+        <v>-121.7853992</v>
       </c>
       <c r="T135" s="2" t="inlineStr">
         <is>
-          <t>9b7d5de4753a514b</t>
+          <t>6a822124d258ac07</t>
         </is>
       </c>
     </row>
     <row r="136" ht="26" customHeight="1">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor (Electrical Engineering &amp; Renewable Energy)</t>
+          <t>Teaching Faculty Position for First-Year Engineering</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Oregon Institute of Technology</t>
+          <t>Florida A&amp;M University - Florida State University College of Engineering</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Electrical Engineering &amp; Renewable Energy</t>
-        </is>
-      </c>
-      <c r="D136" s="3" t="inlineStr"/>
-      <c r="E136" s="4" t="inlineStr"/>
-      <c r="F136" s="2" t="inlineStr"/>
+          <t>Office of Student Services and Undergraduate Affairs</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E136" s="4" t="inlineStr">
+        <is>
+          <t>While the position is a permanent teaching faculty role, it focuses on general first-year engineering instruction and student affairs administration rather than transportation engineering or planning.</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Education, First-Year Engineering Programming, Student Retention and Advising</t>
+        </is>
+      </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Non-Tenure Track</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>Klamath Falls, Oregon</t>
+          <t>Tallahassee, FL</t>
         </is>
       </c>
       <c r="I136" s="3" t="inlineStr">
         <is>
-          <t>Aug. 5, 2026</t>
+          <t>Priority: 2026-07-06 / Final: Open until filled</t>
         </is>
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
@@ -12453,12 +12484,12 @@
       </c>
       <c r="L136" s="4" t="inlineStr">
         <is>
-          <t>University Job: Assistant Professor (Electrical Engineering &amp; Renewable Energy), Oregon Institute of Technology Showing jobs in Engineering . Looking for other jobs? Academic Keys (home page) Adjuncts</t>
+          <t>This full-time, non-tenure-track teaching position involves leading first-year engineering laboratories and directing the Engineering Living Learning Community, requiring a Ph.D. in an engineering discipline or engineering education. | Research Topics: Engineering Education, First-Year Engineering Programming, Student Retention and Advising</t>
         </is>
       </c>
       <c r="M136" s="5" t="inlineStr">
         <is>
-          <t>https://engineering.academickeys.com/job/fqg38d2a/Assistant-Professor-Electrical-Engineering--Renewable-Energy</t>
+          <t>http://engineering.academickeys.com/job/jvd3l79c/Teaching-Faculty-Position-for-FirstYear-Engineering</t>
         </is>
       </c>
       <c r="N136" s="3" t="inlineStr">
@@ -12468,12 +12499,12 @@
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="Q136" s="9" t="inlineStr">
@@ -12482,44 +12513,44 @@
         </is>
       </c>
       <c r="R136" s="2" t="n">
-        <v>42.2583928</v>
+        <v>30.4380832</v>
       </c>
       <c r="S136" s="2" t="n">
-        <v>-121.7853992</v>
+        <v>-84.28093320000001</v>
       </c>
       <c r="T136" s="2" t="inlineStr">
         <is>
-          <t>6a822124d258ac07</t>
+          <t>0249d5be9bd5a4a1</t>
         </is>
       </c>
     </row>
     <row r="137" ht="26" customHeight="1">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>Teaching Faculty Position for First-Year Engineering</t>
+          <t>Clinical Assistant Professor</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Florida A&amp;M University - Florida State University College of Engineering</t>
+          <t>Georgia State University</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>Office of Student Services and Undergraduate Affairs</t>
+          <t>Department of Public Management and Policy</t>
         </is>
       </c>
       <c r="D137" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>While the position is a permanent teaching faculty role, it focuses on general first-year engineering instruction and student affairs administration rather than transportation engineering or planning.</t>
+          <t>This is a non-tenure-track clinical position in public management and policy focusing on teaching data analytics and urban planning, which is a poor fit for a candidate targeting research-active tenure-track positions in transportation engineering.</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>Engineering Education, First-Year Engineering Programming, Student Retention and Advising</t>
+          <t>Policy Analytics, Urban Planning, Data Visualization, GIS Applications</t>
         </is>
       </c>
       <c r="G137" s="3" t="inlineStr">
@@ -12529,47 +12560,47 @@
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>Tallahassee, FL</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="I137" s="3" t="inlineStr">
         <is>
-          <t>Priority: 2026-07-06 / Final: Open until filled</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>$80,000-$90,000</t>
         </is>
       </c>
       <c r="L137" s="4" t="inlineStr">
         <is>
-          <t>This full-time, non-tenure-track teaching position involves leading first-year engineering laboratories and directing the Engineering Living Learning Community, requiring a Ph.D. in an engineering discipline or engineering education. | Research Topics: Engineering Education, First-Year Engineering Programming, Student Retention and Advising</t>
+          <t>A non-tenure-track clinical assistant professor position focusing on teaching policy analytics, urban planning, and GIS, requiring a Ph.D. in a related field and university teaching experience. | Research Topics: Policy Analytics, Urban Planning, Data Visualization, GIS Applications</t>
         </is>
       </c>
       <c r="M137" s="5" t="inlineStr">
         <is>
-          <t>http://engineering.academickeys.com/job/jvd3l79c/Teaching-Faculty-Position-for-FirstYear-Engineering</t>
+          <t>https://jobs.chronicle.com/job/38022215/clinical-assistant-professor-non-tenure-tack/</t>
         </is>
       </c>
       <c r="N137" s="3" t="inlineStr">
         <is>
-          <t>AcademicKeys</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="Q137" s="9" t="inlineStr">
@@ -12578,204 +12609,108 @@
         </is>
       </c>
       <c r="R137" s="2" t="n">
-        <v>30.4380832</v>
+        <v>33.7535889</v>
       </c>
       <c r="S137" s="2" t="n">
-        <v>-84.28093320000001</v>
+        <v>-84.3854209</v>
       </c>
       <c r="T137" s="2" t="inlineStr">
         <is>
-          <t>0249d5be9bd5a4a1</t>
+          <t>f39f14cbaaf9d6f7</t>
         </is>
       </c>
     </row>
     <row r="138" ht="26" customHeight="1">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>Clinical Assistant Professor</t>
+          <t>Assistant Professor in Transportation Policy</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Georgia State University</t>
+          <t>Hunter College</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Department of Public Management and Policy</t>
-        </is>
-      </c>
-      <c r="D138" s="3" t="n">
-        <v>4</v>
+          <t>Department of Urban Policy and Planning</t>
+        </is>
+      </c>
+      <c r="D138" s="7" t="n">
+        <v>7</v>
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>This is a non-tenure-track clinical position in public management and policy focusing on teaching data analytics and urban planning, which is a poor fit for a candidate targeting research-active tenure-track positions in transportation engineering.</t>
+          <t>Strong interdisciplinary fit for an Assistant Professor position focusing on transportation policy and planning within an urban policy department.</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>Policy Analytics, Urban Planning, Data Visualization, GIS Applications</t>
+          <t>Transportation Policy, Transportation Advocacy &amp; Accessibility, Community-Engaged Research, Urban Planning</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>Non-Tenure Track</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="I138" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>Open until filled</t>
         </is>
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>$80,000-$90,000</t>
+          <t>$77,092 - $91,922</t>
         </is>
       </c>
       <c r="L138" s="4" t="inlineStr">
         <is>
-          <t>A non-tenure-track clinical assistant professor position focusing on teaching policy analytics, urban planning, and GIS, requiring a Ph.D. in a related field and university teaching experience. | Research Topics: Policy Analytics, Urban Planning, Data Visualization, GIS Applications</t>
+          <t>Hunter College seeks a tenure-track Assistant Professor in transportation policy to teach graduate students and conduct community-engaged research, requiring a Ph.D. in policy, planning, or a related field specializing in transportation. | Research Topics: Transportation Policy, Transportation Advocacy &amp; Accessibility, Community-Engaged Research, Urban Planning</t>
         </is>
       </c>
       <c r="M138" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38022215/clinical-assistant-professor-non-tenure-tack/</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-%E2%80%93-urban-policy-and-planning-dept-school-of-arts-and-sciences-hunter-college-at-hunter-college-4438624127</t>
         </is>
       </c>
       <c r="N138" s="3" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="Q138" s="9" t="inlineStr">
-        <is>
-          <t>Past Due</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Q138" s="6" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
       <c r="R138" s="2" t="n">
-        <v>33.7535889</v>
+        <v>40.7683107</v>
       </c>
       <c r="S138" s="2" t="n">
-        <v>-84.3854209</v>
+        <v>-73.964406</v>
       </c>
       <c r="T138" s="2" t="inlineStr">
-        <is>
-          <t>f39f14cbaaf9d6f7</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="26" customHeight="1">
-      <c r="A139" s="2" t="inlineStr">
-        <is>
-          <t>Assistant Professor in Transportation Policy</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>Hunter College</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>Department of Urban Policy and Planning</t>
-        </is>
-      </c>
-      <c r="D139" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="E139" s="4" t="inlineStr">
-        <is>
-          <t>Strong interdisciplinary fit for an Assistant Professor position focusing on transportation policy and planning within an urban policy department.</t>
-        </is>
-      </c>
-      <c r="F139" s="2" t="inlineStr">
-        <is>
-          <t>Transportation Policy, Transportation Advocacy &amp; Accessibility, Community-Engaged Research, Urban Planning</t>
-        </is>
-      </c>
-      <c r="G139" s="3" t="inlineStr">
-        <is>
-          <t>Tenure-Track</t>
-        </is>
-      </c>
-      <c r="H139" s="2" t="inlineStr">
-        <is>
-          <t>New York, NY</t>
-        </is>
-      </c>
-      <c r="I139" s="3" t="inlineStr">
-        <is>
-          <t>Open until filled</t>
-        </is>
-      </c>
-      <c r="J139" s="3" t="inlineStr">
-        <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="K139" s="2" t="inlineStr">
-        <is>
-          <t>$77,092 - $91,922</t>
-        </is>
-      </c>
-      <c r="L139" s="4" t="inlineStr">
-        <is>
-          <t>Hunter College seeks a tenure-track Assistant Professor in transportation policy to teach graduate students and conduct community-engaged research, requiring a Ph.D. in policy, planning, or a related field specializing in transportation. | Research Topics: Transportation Policy, Transportation Advocacy &amp; Accessibility, Community-Engaged Research, Urban Planning</t>
-        </is>
-      </c>
-      <c r="M139" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-%E2%80%93-urban-policy-and-planning-dept-school-of-arts-and-sciences-hunter-college-at-hunter-college-4438624127</t>
-        </is>
-      </c>
-      <c r="N139" s="3" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="O139" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="P139" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="Q139" s="6" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="R139" s="2" t="n">
-        <v>40.7683107</v>
-      </c>
-      <c r="S139" s="2" t="n">
-        <v>-73.964406</v>
-      </c>
-      <c r="T139" s="2" t="inlineStr">
         <is>
           <t>e4e18ed629103a27</t>
         </is>
@@ -12920,7 +12855,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M136" r:id="rId135"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M137" r:id="rId136"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M138" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M139" r:id="rId138"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -530,7 +530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T126"/>
+  <dimension ref="A1:T122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1140,7 +1140,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Associate Professor or DTU Tenure Track Assistant Professor in Sustainable Travel Behaviour</t>
+          <t>DTU Tenure Track Assistant Professor in Sustainable Travel Behaviour</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>The position is a direct core match for an Assistant or Associate Professor in Sustainable Travel Behaviour, perfectly aligning with the candidate's core expertise in travel behavior analysis.</t>
+          <t>This is a direct tenure-track Assistant Professor match specifically focusing on sustainable travel behavior within the Transportation Science Division.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Sustainable Travel Behaviour, Travel Behavior Analysis, Transportation Planning</t>
+          <t>Sustainable Travel Behaviour, Transportation Science, Travel Demand Modeling</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Lyngby, Denmark</t>
+          <t>Kongens Lyngby</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -1193,17 +1193,17 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>This faculty position at Technical University of Denmark focuses on sustainable travel behavior research and teaching within DTU Management. | Research Topics: Sustainable Travel Behaviour, Travel Behavior Analysis, Transportation Planning</t>
+          <t>This is a tenure-track Assistant Professor position focusing on sustainable travel behavior research within the Transportation Science Division. | Research Topics: Sustainable Travel Behaviour, Transportation Science, Travel Demand Modeling</t>
         </is>
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>https://www.jobs.ac.uk/job/DTA266/associate-professor-or-dtu-tenure-track-assistant-professor-in-sustainable-travel-behaviour</t>
+          <t>https://dk.linkedin.com/jobs/view/associate-professor-or-dtu-tenure-track-assistant-professor-in-sustainable-travel-behaviour-dtu-management-at-dtu-technical-university-of-denmark-4468634703</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>Jobs.ac.uk</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22581fb6f9f6fea0</t>
+          <t>7e6d15e66f05eb1f</t>
         </is>
       </c>
     </row>
@@ -3444,30 +3444,30 @@
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>DTU Tenure Track Assistant Professor in Sustainable Travel Behaviour</t>
+          <t>Assistant Professor (tenure-track)</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>DTU - Technical University of Denmark</t>
+          <t>The University of British Columbia</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>DTU Management</t>
+          <t>Department of Civil Engineering</t>
         </is>
       </c>
       <c r="D31" s="8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>This is a direct tenure-track Assistant Professor match specifically focusing on sustainable travel behavior within the Transportation Science Division.</t>
+          <t>This is a core tenure-track Assistant Professor position in the Department of Civil Engineering, directly matching the candidate's primary field.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Sustainable Travel Behaviour, Transportation Science, Travel Demand Modeling</t>
+          <t>Civil Engineering, Transportation Engineering, Infrastructure Systems</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Kongens Lyngby</t>
+          <t>Vancouver, British Columbia</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>This is a tenure-track Assistant Professor position focusing on sustainable travel behavior research within the Transportation Science Division. | Research Topics: Sustainable Travel Behaviour, Transportation Science, Travel Demand Modeling</t>
+          <t>Tenure-track Assistant Professor in Civil Engineering requiring a Ph.D. and expertise in engineering education and research. | Research Topics: Civil Engineering, Transportation Engineering, Infrastructure Systems</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/associate-professor-or-dtu-tenure-track-assistant-professor-in-sustainable-travel-behaviour-dtu-management-at-dtu-technical-university-of-denmark-4468634703</t>
+          <t>https://ca.linkedin.com/jobs/view/assistant-professor-tenure-track-at-the-university-of-british-columbia-4446163254</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
@@ -3522,44 +3522,44 @@
         </is>
       </c>
       <c r="R31" s="2" t="n">
-        <v>55.7856</v>
+        <v>49.2606</v>
       </c>
       <c r="S31" s="2" t="n">
-        <v>12.5218</v>
+        <v>-123.246</v>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>7e6d15e66f05eb1f</t>
+          <t>67496928d1d58372</t>
         </is>
       </c>
     </row>
     <row r="32" ht="26" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Associate Professor or DTU Tenure Track Assistant Professor in Sustainable Travel Behaviour</t>
+          <t>Tenure-Track &amp; Tenured Faculty in Urban Design, Environmental Planning or Real Estate Finance</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>DTU Management</t>
+          <t>Massachusetts Institute of Technology</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>DTU Management</t>
+          <t>Department of Urban Studies and Planning</t>
         </is>
       </c>
       <c r="D32" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>This position focuses directly on sustainable travel behavior, perfectly aligning with the candidate's core research specialty.</t>
+          <t>This is a strong interdisciplinary faculty match in Environmental Planning and urban systems that closely aligns with the candidate's urban planning and mobility track.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Sustainable Travel Behaviour, Mobility Analysis, Transportation Planning</t>
+          <t>Urban Design, Environmental Planning, Urban Mobility, Real Estate Finance</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Copenhagen, Denmark</t>
+          <t>Cambridge, Massachusetts</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
@@ -3580,32 +3580,32 @@
       <c r="J32" s="3" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Commensurate with experience</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>This role seeks an expert in sustainable travel behaviour at the assistant or associate professor level, requiring a Ph.D. in a relevant discipline. | Research Topics: Sustainable Travel Behaviour, Mobility Analysis, Transportation Planning</t>
+          <t>Tenure-track or tenured faculty position in environmental planning and urban design requiring a Ph.D. or terminal degree. | Research Topics: Urban Design, Environmental Planning, Urban Mobility, Real Estate Finance</t>
         </is>
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179567818&amp;Title=Associate%20Professor%20or%20DTU%20Tenure%20Track%20Assistant%20Professor%20in%20Sustainable%20Travel%20Behaviour%20%2D%20DTU%20Management</t>
+          <t>https://jobs.chronicle.com/job/38029401/tenure-track-and-tenured-faculty-in-urban-design-environmental-planning-or-real-estate-finance/</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>HigherEdJobs</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Q32" s="6" t="inlineStr">
@@ -3614,44 +3614,44 @@
         </is>
       </c>
       <c r="R32" s="2" t="n">
-        <v>55.7856</v>
+        <v>42.3601</v>
       </c>
       <c r="S32" s="2" t="n">
-        <v>12.5218</v>
+        <v>-71.0942</v>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>dda1f4d97d7ed551</t>
+          <t>54a836f7760d9e03</t>
         </is>
       </c>
     </row>
     <row r="33" ht="26" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor (tenure-track)</t>
+          <t>Tenure-Track Assistant/Associate Professor of Urban Planning and Public Service</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>The University of British Columbia</t>
+          <t>New York University</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Department of Civil Engineering</t>
+          <t>Robert F. Wagner Graduate School of Public Service</t>
         </is>
       </c>
       <c r="D33" s="8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>This is a core tenure-track Assistant Professor position in the Department of Civil Engineering, directly matching the candidate's primary field.</t>
+          <t>This is a strong tenure-track appointment in urban planning which aligns with the candidate's mobility and urban planning track.</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Civil Engineering, Transportation Engineering, Infrastructure Systems</t>
+          <t>Urban Planning, Public Service, Mobility</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Vancouver, British Columbia</t>
+          <t>New York City, New York</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -3677,22 +3677,22 @@
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>Tenure-track Assistant Professor in Civil Engineering requiring a Ph.D. and expertise in engineering education and research. | Research Topics: Civil Engineering, Transportation Engineering, Infrastructure Systems</t>
+          <t>A tenure-track Assistant or Associate Professor position focusing on urban planning and public service. | Research Topics: Urban Planning, Public Service, Mobility</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>https://ca.linkedin.com/jobs/view/assistant-professor-tenure-track-at-the-university-of-british-columbia-4446163254</t>
+          <t>https://jobs.chronicle.com/job/38044497/tenure-track-assistant-associate-professor-of-urban-planning-and-public-service/</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -3706,31 +3706,31 @@
         </is>
       </c>
       <c r="R33" s="2" t="n">
-        <v>49.2606</v>
+        <v>40.7127281</v>
       </c>
       <c r="S33" s="2" t="n">
-        <v>-123.246</v>
+        <v>-74.00601519999999</v>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>67496928d1d58372</t>
+          <t>6aa29a307ed32c5e</t>
         </is>
       </c>
     </row>
     <row r="34" ht="26" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Tenure-Track &amp; Tenured Faculty in Urban Design, Environmental Planning or Real Estate Finance</t>
+          <t>Assistant/Associate/Full Professor of Civil and Environmental Engineering (Intelligent Infrastructure)</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Massachusetts Institute of Technology</t>
+          <t>Northeastern University</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Department of Urban Studies and Planning</t>
+          <t>Department of Civil and Environmental Engineering</t>
         </is>
       </c>
       <c r="D34" s="8" t="n">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>This is a strong interdisciplinary faculty match in Environmental Planning and urban systems that closely aligns with the candidate's urban planning and mobility track.</t>
+          <t>The tenure-track position in Civil and Environmental Engineering explicitly includes AI-enabled urban mobility systems, connected vehicles, and autonomous mobility as primary focus areas, strongly aligning with the candidate's profile.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Urban Design, Environmental Planning, Urban Mobility, Real Estate Finance</t>
+          <t>Autonomous Mobility, AI-Enabled Urban Mobility Systems, Intelligent Infrastructure, Connected Vehicles and Smart Transportation</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Cambridge, Massachusetts</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
@@ -3764,27 +3764,27 @@
       <c r="J34" s="3" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>Commensurate with experience</t>
+          <t>Assistant Professor: $106,000.00 - $121,000.00 | Associate Professor: $123,000.00 - $141,000.00 | Professor: $138,000.00 - $207,000.00</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>Tenure-track or tenured faculty position in environmental planning and urban design requiring a Ph.D. or terminal degree. | Research Topics: Urban Design, Environmental Planning, Urban Mobility, Real Estate Finance</t>
+          <t>Northeastern University seeks open-rank tenure-track faculty in Civil and Environmental Engineering focusing on intelligent infrastructure and autonomous mobility, requiring a Ph.D. in civil engineering or a related field. | Research Topics: Autonomous Mobility, AI-Enabled Urban Mobility Systems, Intelligent Infrastructure, Connected Vehicles and Smart Transportation</t>
         </is>
       </c>
       <c r="M34" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38029401/tenure-track-and-tenured-faculty-in-urban-design-environmental-planning-or-real-estate-finance/</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179568338&amp;Title=Assistant%2FAssociate%2FFull%20Professor%2D%20Khoury%20College%20of%20Computer%20Sciences</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -3798,31 +3798,31 @@
         </is>
       </c>
       <c r="R34" s="2" t="n">
-        <v>42.3601</v>
+        <v>42.3351065</v>
       </c>
       <c r="S34" s="2" t="n">
-        <v>-71.0942</v>
+        <v>-71.0892575</v>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>54a836f7760d9e03</t>
+          <t>ff41022f943a7cbe</t>
         </is>
       </c>
     </row>
     <row r="35" ht="26" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor / Associate Professor in Maritime Studies</t>
+          <t>Assistant/Associate Professor in Automotive Engineering &amp; Transportation</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Nanyang Technological University Singapore</t>
+          <t>Purdue University</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>School of Civil and Environmental Engineering / Maritime Studies</t>
+          <t>Department of Mechanical Engineering</t>
         </is>
       </c>
       <c r="D35" s="8" t="n">
@@ -3830,12 +3830,12 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>This tenure-track or practice-track position in Maritime Studies strongly aligns with transportation systems, transit planning, and mobility operations.</t>
+          <t>The position focuses on automotive engineering and transportation, aligning well with the candidate's research in intelligent transportation systems and mobility.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Maritime Studies, Port Operations, Transportation Systems, Supply Chain and Mobility</t>
+          <t>Automotive Engineering, Transportation Systems, Mobility</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>West Lafayette, Indiana</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
@@ -3856,32 +3856,32 @@
       <c r="J35" s="3" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>Highly competitive</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>This faculty position seeks scholars in maritime studies and transportation to conduct teaching and research, requiring a Ph.D. | Research Topics: Maritime Studies, Port Operations, Transportation Systems, Supply Chain and Mobility</t>
+          <t>An open-rank faculty appointment in automotive engineering and transportation requiring a Ph.D. in mechanical engineering or a related transportation field. | Research Topics: Automotive Engineering, Transportation Systems, Mobility</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>https://sg.linkedin.com/jobs/view/assistant-professor-associate-professor-tenure-track-associate-professor-practice-track-in-maritime-studies-at-nanyang-technological-university-singapore-4432368242</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179567748&amp;Title=Assistant%2FAssociate%20Professor%20in%20Automotive%20Engineering%20%26%20Transportation</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="Q35" s="6" t="inlineStr">
@@ -3890,31 +3890,31 @@
         </is>
       </c>
       <c r="R35" s="2" t="n">
-        <v>1.3483</v>
+        <v>40.4237</v>
       </c>
       <c r="S35" s="2" t="n">
-        <v>103.6831</v>
+        <v>-86.9212</v>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1e0a7536f9329af5</t>
+          <t>40bc1f3f13f9ded6</t>
         </is>
       </c>
     </row>
     <row r="36" ht="26" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Tenure-Track Assistant/Associate Professor of Urban Planning and Public Service</t>
+          <t>Assistant Professor - Urban Analytics</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>New York University</t>
+          <t>University of Massachusetts Boston</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Robert F. Wagner Graduate School of Public Service</t>
+          <t>Department of Urban Planning and Community Development</t>
         </is>
       </c>
       <c r="D36" s="8" t="n">
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>This is a strong tenure-track appointment in urban planning which aligns with the candidate's mobility and urban planning track.</t>
+          <t>This is a strong interdisciplinary match in Urban Planning and Community Development focusing on urban analytics, aligning well with the candidate's expertise in mobility and planning.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Urban Planning, Public Service, Mobility</t>
+          <t>Urban Analytics, Urban Planning, Community Development</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>New York City, New York</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
@@ -3948,22 +3948,22 @@
       <c r="J36" s="3" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>$80,000 - $98,003</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>A tenure-track Assistant or Associate Professor position focusing on urban planning and public service. | Research Topics: Urban Planning, Public Service, Mobility</t>
+          <t>Full-time tenure-track Assistant Professor in Urban Analytics requiring a Ph.D. in urban planning or a related field. | Research Topics: Urban Analytics, Urban Planning, Community Development</t>
         </is>
       </c>
       <c r="M36" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38044497/tenure-track-assistant-associate-professor-of-urban-planning-and-public-service/</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-urban-analytics-at-umass-boston-4469629227</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
@@ -3982,31 +3982,31 @@
         </is>
       </c>
       <c r="R36" s="2" t="n">
-        <v>40.7127281</v>
+        <v>42.314068</v>
       </c>
       <c r="S36" s="2" t="n">
-        <v>-74.00601519999999</v>
+        <v>-71.0387132</v>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6aa29a307ed32c5e</t>
+          <t>18d2edee77596e22</t>
         </is>
       </c>
     </row>
     <row r="37" ht="26" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Assistant/Associate/Full Professor of Civil and Environmental Engineering (Intelligent Infrastructure)</t>
+          <t>Tenure-Track Assistant Professor in Positioning, Navigation, and Timing</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>University of New Brunswick</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Department of Civil and Environmental Engineering</t>
+          <t>Department of Geodesy and Geomatics Engineering</t>
         </is>
       </c>
       <c r="D37" s="8" t="n">
@@ -4014,12 +4014,12 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>The tenure-track position in Civil and Environmental Engineering explicitly includes AI-enabled urban mobility systems, connected vehicles, and autonomous mobility as primary focus areas, strongly aligning with the candidate's profile.</t>
+          <t>Position in Positioning, Navigation, and Timing aligns closely with intelligent transportation systems, data fusion, and mobility research.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Autonomous Mobility, AI-Enabled Urban Mobility Systems, Intelligent Infrastructure, Connected Vehicles and Smart Transportation</t>
+          <t>Positioning, Navigation and Timing, Geomatics, Intelligent Transportation Systems</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>Fredericton, New Brunswick</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
@@ -4040,22 +4040,22 @@
       <c r="J37" s="3" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor: $106,000.00 - $121,000.00 | Associate Professor: $123,000.00 - $141,000.00 | Professor: $138,000.00 - $207,000.00</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>Northeastern University seeks open-rank tenure-track faculty in Civil and Environmental Engineering focusing on intelligent infrastructure and autonomous mobility, requiring a Ph.D. in civil engineering or a related field. | Research Topics: Autonomous Mobility, AI-Enabled Urban Mobility Systems, Intelligent Infrastructure, Connected Vehicles and Smart Transportation</t>
+          <t>Tenure-track assistant professor position in geomatics engineering focusing on positioning, navigation, and timing requiring a Ph.D. | Research Topics: Positioning, Navigation and Timing, Geomatics, Intelligent Transportation Systems</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179568338&amp;Title=Assistant%2FAssociate%2FFull%20Professor%2D%20Khoury%20College%20of%20Computer%20Sciences</t>
+          <t>https://ca.linkedin.com/jobs/view/department-of-geodesy-and-geomatics-engineering-tenure-track-assistant-professor-in-positioning-navigation-and-timing-at-university-of-new-brunswick-4406141089</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>HigherEdJobs</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
@@ -4074,54 +4074,54 @@
         </is>
       </c>
       <c r="R37" s="2" t="n">
-        <v>42.3351065</v>
+        <v>45.9455202</v>
       </c>
       <c r="S37" s="2" t="n">
-        <v>-71.0892575</v>
+        <v>-66.64018609999999</v>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>ff41022f943a7cbe</t>
+          <t>6f8958be6b7d9994</t>
         </is>
       </c>
     </row>
     <row r="38" ht="26" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Assistant/Associate Professor in Automotive Engineering &amp; Transportation</t>
+          <t>Assistant Teaching Professor – Urban Planning</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>Arizona State University</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Department of Mechanical Engineering</t>
-        </is>
-      </c>
-      <c r="D38" s="8" t="n">
-        <v>8</v>
+          <t>School of Geographical Sciences and Urban Planning</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>7</v>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>The position focuses on automotive engineering and transportation, aligning well with the candidate's research in intelligent transportation systems and mobility.</t>
+          <t>This is a career-track Assistant Teaching Professor position in Urban Planning that aligns well with the candidate's mobility and planning track.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Automotive Engineering, Transportation Systems, Mobility</t>
+          <t>Urban Planning, Mobility, Pedagogy</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Non-Tenure Track</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>West Lafayette, Indiana</t>
+          <t>Tempe, AZ</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
@@ -4137,27 +4137,27 @@
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>An open-rank faculty appointment in automotive engineering and transportation requiring a Ph.D. in mechanical engineering or a related transportation field. | Research Topics: Automotive Engineering, Transportation Systems, Mobility</t>
+          <t>This is an Assistant Teaching Professor role focusing on urban planning education and requires a relevant terminal degree. | Research Topics: Urban Planning, Mobility, Pedagogy</t>
         </is>
       </c>
       <c r="M38" s="5" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179567748&amp;Title=Assistant%2FAssociate%20Professor%20in%20Automotive%20Engineering%20%26%20Transportation</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-teaching-professor-%E2%80%93-urban-planning-arizona-state-university-at-arizona-state-university-4370180914</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>HigherEdJobs</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Q38" s="6" t="inlineStr">
@@ -4166,44 +4166,44 @@
         </is>
       </c>
       <c r="R38" s="2" t="n">
-        <v>40.4237</v>
+        <v>33.4242</v>
       </c>
       <c r="S38" s="2" t="n">
-        <v>-86.9212</v>
+        <v>-111.9281</v>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>40bc1f3f13f9ded6</t>
+          <t>0b4f9f3352865006</t>
         </is>
       </c>
     </row>
     <row r="39" ht="26" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor - Urban Analytics</t>
+          <t>Assistant Professor in Fair and Responsible Artificial Intelligence</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>University of Massachusetts Boston</t>
+          <t>Imperial College London</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Department of Urban Planning and Community Development</t>
-        </is>
-      </c>
-      <c r="D39" s="8" t="n">
-        <v>8</v>
+          <t>Dyson School of Design Engineering</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="n">
+        <v>7</v>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>This is a strong interdisciplinary match in Urban Planning and Community Development focusing on urban analytics, aligning well with the candidate's expertise in mobility and planning.</t>
+          <t>This design engineering role focuses on responsible artificial intelligence, offering strong interdisciplinary alignment with the candidate's AI-integrated mobility work.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Urban Analytics, Urban Planning, Community Development</t>
+          <t>Responsible AI, Design Engineering, Algorithmic Fairness</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>London, United Kingdom</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
@@ -4224,22 +4224,22 @@
       <c r="J39" s="3" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>$80,000 - $98,003</t>
+          <t>£73,194 to £82,954</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>Full-time tenure-track Assistant Professor in Urban Analytics requiring a Ph.D. in urban planning or a related field. | Research Topics: Urban Analytics, Urban Planning, Community Development</t>
+          <t>An assistant professor position in fair and responsible artificial intelligence within design engineering, requiring a Ph.D. in a relevant field. | Research Topics: Responsible AI, Design Engineering, Algorithmic Fairness</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-urban-analytics-at-umass-boston-4469629227</t>
+          <t>https://www.jobs.ac.uk/job/DSO564/assistant-professor-in-fair-and-responsible-artificial-intelligence</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Jobs.ac.uk</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
@@ -4258,44 +4258,44 @@
         </is>
       </c>
       <c r="R39" s="2" t="n">
-        <v>42.314068</v>
+        <v>51.4988</v>
       </c>
       <c r="S39" s="2" t="n">
-        <v>-71.0387132</v>
+        <v>-0.1749</v>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>18d2edee77596e22</t>
+          <t>cd73f7eb569f2263</t>
         </is>
       </c>
     </row>
     <row r="40" ht="26" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Tenure-Track Assistant Professor in Positioning, Navigation, and Timing</t>
+          <t>Assistant Professor in Regional &amp; Community Planning</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>University of New Brunswick</t>
+          <t>Kansas State University</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Department of Geodesy and Geomatics Engineering</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="n">
-        <v>8</v>
+          <t>Department of Regional &amp; Community Planning</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>7</v>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Position in Positioning, Navigation, and Timing aligns closely with intelligent transportation systems, data fusion, and mobility research.</t>
+          <t>This is a strong interdisciplinary match in regional and community planning which aligns well with the candidate's focus on urban planning and mobility track.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Positioning, Navigation and Timing, Geomatics, Intelligent Transportation Systems</t>
+          <t>Regional Planning, Community Planning, Urban Mobility</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -4305,7 +4305,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Fredericton, New Brunswick</t>
+          <t>Manhattan, KS</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>Tenure-track assistant professor position in geomatics engineering focusing on positioning, navigation, and timing requiring a Ph.D. | Research Topics: Positioning, Navigation and Timing, Geomatics, Intelligent Transportation Systems</t>
+          <t>A tenure-track assistant professor position in regional and community planning requiring a Ph.D. or terminal degree. | Research Topics: Regional Planning, Community Planning, Urban Mobility</t>
         </is>
       </c>
       <c r="M40" s="5" t="inlineStr">
         <is>
-          <t>https://ca.linkedin.com/jobs/view/department-of-geodesy-and-geomatics-engineering-tenure-track-assistant-professor-in-positioning-navigation-and-timing-at-university-of-new-brunswick-4406141089</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-in-regional-community-planning-at-kansas-state-university-4473289497</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -4350,31 +4350,31 @@
         </is>
       </c>
       <c r="R40" s="2" t="n">
-        <v>45.9455202</v>
+        <v>39.2086412</v>
       </c>
       <c r="S40" s="2" t="n">
-        <v>-66.64018609999999</v>
+        <v>-96.5884966</v>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>6f8958be6b7d9994</t>
+          <t>cc81a3a07169c7a2</t>
         </is>
       </c>
     </row>
     <row r="41" ht="26" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Assistant Teaching Professor – Urban Planning</t>
+          <t>Chair Professor / Professor / Associate Professor / Assistant Professor, Lingnan-60</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Lingnan University</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>School of Geographical Sciences and Urban Planning</t>
+          <t>Lingnan-60 Global Talent Recruitment</t>
         </is>
       </c>
       <c r="D41" s="7" t="n">
@@ -4382,22 +4382,22 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>This is a career-track Assistant Teaching Professor position in Urban Planning that aligns well with the candidate's mobility and planning track.</t>
+          <t>This is an open-rank cluster hire that explicitly includes smart city, data science, and AI areas aligning well with the candidate's interdisciplinary profile.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Urban Planning, Mobility, Pedagogy</t>
+          <t>Smart City, Data Science and Artificial Intelligence, Smart Infrastructure, Social and Public Policy</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>Non-Tenure Track</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Tempe, AZ</t>
+          <t>New Territories, Hong Kong SAR</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>This is an Assistant Teaching Professor role focusing on urban planning education and requires a relevant terminal degree. | Research Topics: Urban Planning, Mobility, Pedagogy</t>
+          <t>Lingnan University seeks open-rank scholars across interdisciplinary fields including smart infrastructure, data science, and AI, requiring a relevant PhD degree. | Research Topics: Smart City, Data Science and Artificial Intelligence, Smart Infrastructure, Social and Public Policy</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-teaching-professor-%E2%80%93-urban-planning-arizona-state-university-at-arizona-state-university-4370180914</t>
+          <t>https://hk.linkedin.com/jobs/view/chair-professor-professor-associate-professor-assistant-professor-lingnan-60-at-lingnan-university-4386654192</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="Q41" s="6" t="inlineStr">
@@ -4442,31 +4442,31 @@
         </is>
       </c>
       <c r="R41" s="2" t="n">
-        <v>33.4242</v>
+        <v>22.4123588</v>
       </c>
       <c r="S41" s="2" t="n">
-        <v>-111.9281</v>
+        <v>113.9812776</v>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>0b4f9f3352865006</t>
+          <t>0a5d257fc60d771a</t>
         </is>
       </c>
     </row>
     <row r="42" ht="26" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor in Fair and Responsible Artificial Intelligence</t>
+          <t>Assistant Professor in Urban and Regional Planning</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Imperial College London</t>
+          <t>Texas State University</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Dyson School of Design Engineering</t>
+          <t>Department of Geography and Environmental Studies</t>
         </is>
       </c>
       <c r="D42" s="7" t="n">
@@ -4474,12 +4474,12 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>This design engineering role focuses on responsible artificial intelligence, offering strong interdisciplinary alignment with the candidate's AI-integrated mobility work.</t>
+          <t>This tenure-track position in Urban and Regional Planning directly matches one of the candidate's target departments and aligns with their expertise in urban infrastructure systems, policy evaluation, and GIS applications.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Responsible AI, Design Engineering, Algorithmic Fairness</t>
+          <t>Urban Infrastructure Systems, Planning and Public Policy, GIScience, Urban Planning</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>London, United Kingdom</t>
+          <t>San Marcos, TX</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
@@ -4500,27 +4500,27 @@
       <c r="J42" s="3" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>£73,194 to £82,954</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>An assistant professor position in fair and responsible artificial intelligence within design engineering, requiring a Ph.D. in a relevant field. | Research Topics: Responsible AI, Design Engineering, Algorithmic Fairness</t>
+          <t>The Department of Geography and Environmental Studies invites applications for a tenure-track Assistant Professor in Urban and Regional Planning with a required Ph.D. in geography, urban planning, or urban studies. | Research Topics: Urban Infrastructure Systems, Planning and Public Policy, GIScience, Urban Planning</t>
         </is>
       </c>
       <c r="M42" s="5" t="inlineStr">
         <is>
-          <t>https://www.jobs.ac.uk/job/DSO564/assistant-professor-in-fair-and-responsible-artificial-intelligence</t>
+          <t>https://jobs.chronicle.com/job/38045925/assistant-professor-in-urban-and-regional-planning/</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>Jobs.ac.uk</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -4534,31 +4534,31 @@
         </is>
       </c>
       <c r="R42" s="2" t="n">
-        <v>51.4988</v>
+        <v>29.8910885</v>
       </c>
       <c r="S42" s="2" t="n">
-        <v>-0.1749</v>
+        <v>-97.9376214</v>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>cd73f7eb569f2263</t>
+          <t>79cdd18aa1e79ddb</t>
         </is>
       </c>
     </row>
     <row r="43" ht="26" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor in Regional &amp; Community Planning</t>
+          <t>Assistant Professor in Regional and Urban Planning</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Kansas State University</t>
+          <t>University College Dublin</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Department of Regional &amp; Community Planning</t>
+          <t>UCD School of Architecture, Planning and Environmental Policy</t>
         </is>
       </c>
       <c r="D43" s="7" t="n">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>This is a strong interdisciplinary match in regional and community planning which aligns well with the candidate's focus on urban planning and mobility track.</t>
+          <t>This Assistant Professor position in regional and urban planning aligns well with the candidate's research interests in urban planning and mobility track.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Regional Planning, Community Planning, Urban Mobility</t>
+          <t>Regional Planning, Urban Planning, Mobility, Spatial Development</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Manhattan, KS</t>
+          <t>Dublin, Ireland</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
@@ -4592,22 +4592,22 @@
       <c r="J43" s="3" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>£57,454.37 to £90,980.66</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>A tenure-track assistant professor position in regional and community planning requiring a Ph.D. or terminal degree. | Research Topics: Regional Planning, Community Planning, Urban Mobility</t>
+          <t>An assistant professor position focusing on regional and urban planning with a relevant doctoral degree required. | Research Topics: Regional Planning, Urban Planning, Mobility, Spatial Development</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-in-regional-community-planning-at-kansas-state-university-4473289497</t>
+          <t>https://www.jobs.ac.uk/job/DSY140/assistant-professor-in-regional-and-urban-planning</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Jobs.ac.uk</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
@@ -4626,31 +4626,31 @@
         </is>
       </c>
       <c r="R43" s="2" t="n">
-        <v>39.2086412</v>
+        <v>53.3082</v>
       </c>
       <c r="S43" s="2" t="n">
-        <v>-96.5884966</v>
+        <v>-6.2238</v>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>cc81a3a07169c7a2</t>
+          <t>d042d0e38cf2b00a</t>
         </is>
       </c>
     </row>
     <row r="44" ht="26" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Chair Professor / Professor / Associate Professor / Assistant Professor, Lingnan-60</t>
+          <t>LECTURER/Instructional Assistant Professor</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Lingnan University</t>
+          <t>University of Florida</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Lingnan-60 Global Talent Recruitment</t>
+          <t>Department of Urban and Regional Planning</t>
         </is>
       </c>
       <c r="D44" s="7" t="n">
@@ -4658,22 +4658,22 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>This is an open-rank cluster hire that explicitly includes smart city, data science, and AI areas aligning well with the candidate's interdisciplinary profile.</t>
+          <t>This instructional faculty role requires an advanced degree in urban and regional planning, closely aligning with the candidate's mobility track.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Smart City, Data Science and Artificial Intelligence, Smart Infrastructure, Social and Public Policy</t>
+          <t>Urban and Regional Planning, Landscape Architecture, Urban Analytics</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Non-Tenure Track</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>New Territories, Hong Kong SAR</t>
+          <t>Gainesville, FL</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>Lingnan University seeks open-rank scholars across interdisciplinary fields including smart infrastructure, data science, and AI, requiring a relevant PhD degree. | Research Topics: Smart City, Data Science and Artificial Intelligence, Smart Infrastructure, Social and Public Policy</t>
+          <t>Instructional Assistant Professor or Lecturer position requiring an advanced degree in urban and regional planning or related discipline. | Research Topics: Urban and Regional Planning, Landscape Architecture, Urban Analytics</t>
         </is>
       </c>
       <c r="M44" s="5" t="inlineStr">
         <is>
-          <t>https://hk.linkedin.com/jobs/view/chair-professor-professor-associate-professor-assistant-professor-lingnan-60-at-lingnan-university-4386654192</t>
+          <t>https://www.linkedin.com/jobs/view/lecturer-instructional-assistant-professor-at-university-of-florida-4467572007</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
@@ -4704,12 +4704,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Q44" s="6" t="inlineStr">
@@ -4718,31 +4718,31 @@
         </is>
       </c>
       <c r="R44" s="2" t="n">
-        <v>22.4123588</v>
+        <v>29.6436</v>
       </c>
       <c r="S44" s="2" t="n">
-        <v>113.9812776</v>
+        <v>-82.3549</v>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>0a5d257fc60d771a</t>
+          <t>9b6b271cd9e3d13c</t>
         </is>
       </c>
     </row>
     <row r="45" ht="26" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor in Urban and Regional Planning</t>
+          <t>Assistant / Associate / Full Professor in Land Use</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Texas State University</t>
+          <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Department of Geography and Environmental Studies</t>
+          <t>Department of Urban and Regional Planning</t>
         </is>
       </c>
       <c r="D45" s="7" t="n">
@@ -4750,12 +4750,12 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>This tenure-track position in Urban and Regional Planning directly matches one of the candidate's target departments and aligns with their expertise in urban infrastructure systems, policy evaluation, and GIS applications.</t>
+          <t>The open-rank urban planning position aligns well with the candidate's background in urban mobility and transportation planning.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Urban Infrastructure Systems, Planning and Public Policy, GIScience, Urban Planning</t>
+          <t>Land Use, Urban Planning, Transportation</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>San Marcos, TX</t>
+          <t>Urbana, IL</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
@@ -4781,22 +4781,22 @@
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>The Department of Geography and Environmental Studies invites applications for a tenure-track Assistant Professor in Urban and Regional Planning with a required Ph.D. in geography, urban planning, or urban studies. | Research Topics: Urban Infrastructure Systems, Planning and Public Policy, GIScience, Urban Planning</t>
+          <t>Open-rank tenure-track faculty position focusing on land use and urban planning requiring a Ph.D. | Research Topics: Land Use, Urban Planning, Transportation</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38045925/assistant-professor-in-urban-and-regional-planning/</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-associate-full-professor-land-use-tenure-track-urban-regional-planning-at-university-of-illinois-urbana-champaign-4464659038</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -4810,31 +4810,31 @@
         </is>
       </c>
       <c r="R45" s="2" t="n">
-        <v>29.8910885</v>
+        <v>40.102</v>
       </c>
       <c r="S45" s="2" t="n">
-        <v>-97.9376214</v>
+        <v>-88.2272</v>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>79cdd18aa1e79ddb</t>
+          <t>f854191688870ed4</t>
         </is>
       </c>
     </row>
     <row r="46" ht="26" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor in Regional and Urban Planning</t>
+          <t>Teaching Assistant Professor</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>University College Dublin</t>
+          <t>University of South Carolina</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>UCD School of Architecture, Planning and Environmental Policy</t>
+          <t>Department of Civil and Environmental Engineering</t>
         </is>
       </c>
       <c r="D46" s="7" t="n">
@@ -4842,22 +4842,22 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>This Assistant Professor position in regional and urban planning aligns well with the candidate's research interests in urban planning and mobility track.</t>
+          <t>This teaching faculty position is housed in Civil and Environmental Engineering, which aligns with the candidate's core department and background, though it focuses primarily on teaching.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Regional Planning, Urban Planning, Mobility, Spatial Development</t>
+          <t>Civil Engineering, Engineering Education, Environmental Engineering</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Non-Tenure Track</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Dublin, Ireland</t>
+          <t>Columbia, SC</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
@@ -4868,27 +4868,27 @@
       <c r="J46" s="3" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>£57,454.37 to £90,980.66</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>An assistant professor position focusing on regional and urban planning with a relevant doctoral degree required. | Research Topics: Regional Planning, Urban Planning, Mobility, Spatial Development</t>
+          <t>Full-time teaching assistant professor in civil and environmental engineering requiring a Ph.D. | Research Topics: Civil Engineering, Engineering Education, Environmental Engineering</t>
         </is>
       </c>
       <c r="M46" s="5" t="inlineStr">
         <is>
-          <t>https://www.jobs.ac.uk/job/DSY140/assistant-professor-in-regional-and-urban-planning</t>
+          <t>https://www.linkedin.com/jobs/view/teaching-assistant-professor-at-state-of-south-carolina-4471523322</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>Jobs.ac.uk</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -4902,31 +4902,31 @@
         </is>
       </c>
       <c r="R46" s="2" t="n">
-        <v>53.3082</v>
+        <v>33.9929</v>
       </c>
       <c r="S46" s="2" t="n">
-        <v>-6.2238</v>
+        <v>-81.0269</v>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>d042d0e38cf2b00a</t>
+          <t>b9c68db81eb752b4</t>
         </is>
       </c>
     </row>
     <row r="47" ht="26" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>LECTURER/Instructional Assistant Professor</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>University of Florida</t>
+          <t>University of Texas at Arlington</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Department of Urban and Regional Planning</t>
+          <t>Department of Civil Engineering</t>
         </is>
       </c>
       <c r="D47" s="7" t="n">
@@ -4934,22 +4934,22 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>This instructional faculty role requires an advanced degree in urban and regional planning, closely aligning with the candidate's mobility track.</t>
+          <t>This is a Civil Engineering department faculty search where transportation engineering track is a strong potential fit.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Urban and Regional Planning, Landscape Architecture, Urban Analytics</t>
+          <t>Civil Engineering, Infrastructure Systems, Transportation Engineering</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>Non-Tenure Track</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Gainesville, FL</t>
+          <t>Arlington, TX</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
@@ -4965,12 +4965,12 @@
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>Instructional Assistant Professor or Lecturer position requiring an advanced degree in urban and regional planning or related discipline. | Research Topics: Urban and Regional Planning, Landscape Architecture, Urban Analytics</t>
+          <t>Full-time tenure-track Assistant Professor in Civil Engineering requiring a Ph.D. in civil engineering or a closely related field. | Research Topics: Civil Engineering, Infrastructure Systems, Transportation Engineering</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/lecturer-instructional-assistant-professor-at-university-of-florida-4467572007</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-at-excel-campus-activities-4393887488</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr">
@@ -4994,54 +4994,54 @@
         </is>
       </c>
       <c r="R47" s="2" t="n">
-        <v>29.6436</v>
+        <v>32.7355816</v>
       </c>
       <c r="S47" s="2" t="n">
-        <v>-82.3549</v>
+        <v>-97.10711860000001</v>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>9b6b271cd9e3d13c</t>
+          <t>960518333ab86519</t>
         </is>
       </c>
     </row>
     <row r="48" ht="26" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Assistant / Associate / Full Professor in Land Use</t>
+          <t>Instructor of Urban Planning</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>University of Illinois Urbana-Champaign</t>
+          <t>Ball State University</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Department of Urban and Regional Planning</t>
+          <t>Department of Urban Planning</t>
         </is>
       </c>
       <c r="D48" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>The open-rank urban planning position aligns well with the candidate's background in urban mobility and transportation planning.</t>
+          <t>While an instructor position in urban planning, it aligns broadly with the candidate's urban planning and mobility track interests.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Land Use, Urban Planning, Transportation</t>
+          <t>Urban Planning, Mobility, City Design</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Non-Tenure Track</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Urbana, IL</t>
+          <t>Muncie, Indiana</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
@@ -5052,22 +5052,22 @@
       <c r="J48" s="3" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Competitive Salary</t>
         </is>
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>Open-rank tenure-track faculty position focusing on land use and urban planning requiring a Ph.D. | Research Topics: Land Use, Urban Planning, Transportation</t>
+          <t>Instructor position teaching urban planning courses within the planning department. | Research Topics: Urban Planning, Mobility, City Design</t>
         </is>
       </c>
       <c r="M48" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-associate-full-professor-land-use-tenure-track-urban-regional-planning-at-university-of-illinois-urbana-champaign-4464659038</t>
+          <t>https://jobs.chronicle.com/job/38044759/instructor-of-urban-planning/</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
@@ -5086,54 +5086,54 @@
         </is>
       </c>
       <c r="R48" s="2" t="n">
-        <v>40.102</v>
+        <v>40.2097296</v>
       </c>
       <c r="S48" s="2" t="n">
-        <v>-88.2272</v>
+        <v>-85.41121510000001</v>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>f854191688870ed4</t>
+          <t>2f5cc4d8a7818cba</t>
         </is>
       </c>
     </row>
     <row r="49" ht="26" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Teaching Assistant Professor</t>
+          <t>Assistant/Associate Professor of Civil Engineering</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>University of South Carolina</t>
+          <t>Cedarville University</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Department of Civil and Environmental Engineering</t>
+          <t>School of Engineering and Computer Science</t>
         </is>
       </c>
       <c r="D49" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>This teaching faculty position is housed in Civil and Environmental Engineering, which aligns with the candidate's core department and background, though it focuses primarily on teaching.</t>
+          <t>This is a broad civil engineering faculty search where transportation is explicitly listed as one of the acceptable sub-disciplines.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Civil Engineering, Engineering Education, Environmental Engineering</t>
+          <t>Transportation Engineering, Civil Engineering Education, Undergraduate Mentoring</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>Non-Tenure Track</t>
+          <t>Unspecified</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Columbia, SC</t>
+          <t>Cedarville, OH</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
@@ -5149,27 +5149,27 @@
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>Full-time teaching assistant professor in civil and environmental engineering requiring a Ph.D. | Research Topics: Civil Engineering, Engineering Education, Environmental Engineering</t>
+          <t>This position seeks an Assistant or Associate Professor in Civil Engineering to teach undergraduate courses and mentor students across disciplines including transportation, requiring a Ph.D. in Civil Engineering or related field. | Research Topics: Transportation Engineering, Civil Engineering Education, Undergraduate Mentoring</t>
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/teaching-assistant-professor-at-state-of-south-carolina-4471523322</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179544290&amp;Title=Assistant%2FAssociate%20Professor%20of%20Civil%20Engineering</t>
         </is>
       </c>
       <c r="N49" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="Q49" s="6" t="inlineStr">
@@ -5178,44 +5178,44 @@
         </is>
       </c>
       <c r="R49" s="2" t="n">
-        <v>39.7978672</v>
+        <v>39.7540491</v>
       </c>
       <c r="S49" s="2" t="n">
-        <v>-77.255923</v>
+        <v>-83.8170518</v>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>b9c68db81eb752b4</t>
+          <t>751c7406865a2787</t>
         </is>
       </c>
     </row>
     <row r="50" ht="26" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Tenure-Track Assistant Professor of Aeronautical Sciences</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>University of Texas at Arlington</t>
+          <t>Embry-Riddle Aeronautical University</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Department of Civil Engineering</t>
+          <t>College of Aviation</t>
         </is>
       </c>
       <c r="D50" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>This is a Civil Engineering department faculty search where transportation engineering track is a strong potential fit.</t>
+          <t>While in aeronautical sciences, the specific focus is on air transportation systems which offers some overlap with transportation planning.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Civil Engineering, Infrastructure Systems, Transportation Engineering</t>
+          <t>Air Transportation Systems, Aeronautical Sciences, Transportation Management</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Arlington, TX</t>
+          <t>Daytona Beach, FL</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
@@ -5236,17 +5236,17 @@
       <c r="J50" s="3" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Competitive Salary</t>
         </is>
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>Full-time tenure-track Assistant Professor in Civil Engineering requiring a Ph.D. in civil engineering or a closely related field. | Research Topics: Civil Engineering, Infrastructure Systems, Transportation Engineering</t>
+          <t>Tenure-track Assistant Professor focusing on air transportation systems requiring a Ph.D. in aviation or a related field. | Research Topics: Air Transportation Systems, Aeronautical Sciences, Transportation Management</t>
         </is>
       </c>
       <c r="M50" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-at-excel-campus-activities-4393887488</t>
+          <t>https://www.linkedin.com/jobs/view/tenure-track-assistant-professor-of-aeronautical-sciences-daytona-beach-campus-at-embry-riddle-aeronautical-university-4472944897</t>
         </is>
       </c>
       <c r="N50" s="3" t="inlineStr">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -5270,31 +5270,31 @@
         </is>
       </c>
       <c r="R50" s="2" t="n">
-        <v>32.7355816</v>
+        <v>29.1895</v>
       </c>
       <c r="S50" s="2" t="n">
-        <v>-97.10711860000001</v>
+        <v>-81.04940000000001</v>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>960518333ab86519</t>
+          <t>e5ba6a7cb0c600c1</t>
         </is>
       </c>
     </row>
     <row r="51" ht="26" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Instructor of Urban Planning</t>
+          <t>Assistant Professor of Civil Engineering</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Ball State University</t>
+          <t>McNeese State University</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Department of Urban Planning</t>
+          <t>Department of Engineering and Computer Science</t>
         </is>
       </c>
       <c r="D51" s="7" t="n">
@@ -5302,22 +5302,22 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>While an instructor position in urban planning, it aligns broadly with the candidate's urban planning and mobility track interests.</t>
+          <t>This is a broad civil engineering faculty search that explicitly welcomes transportation engineering alongside other sub-disciplines.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Urban Planning, Mobility, City Design</t>
+          <t>Civil Engineering, Transportation Engineering, Water Resources and Hydraulic Engineering, Structural and Geotechnical Engineering</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>Non-Tenure Track</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Muncie, Indiana</t>
+          <t>Lake Charles, LA</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
@@ -5328,32 +5328,32 @@
       <c r="J51" s="3" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>Competitive Salary</t>
+          <t>$76,000 per year</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>Instructor position teaching urban planning courses within the planning department. | Research Topics: Urban Planning, Mobility, City Design</t>
+          <t>McNeese State University seeks a full-time, tenure-track Assistant Professor of Civil Engineering to teach, advise students, and conduct research, requiring a Ph.D. in Civil Engineering. | Research Topics: Civil Engineering, Transportation Engineering, Water Resources and Hydraulic Engineering, Structural and Geotechnical Engineering</t>
         </is>
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38044759/instructor-of-urban-planning/</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179545361&amp;Title=Assistant%20Professor%20of%20Civil%20Engineering</t>
         </is>
       </c>
       <c r="N51" s="3" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="Q51" s="6" t="inlineStr">
@@ -5362,31 +5362,31 @@
         </is>
       </c>
       <c r="R51" s="2" t="n">
-        <v>40.2097296</v>
+        <v>30.1751363</v>
       </c>
       <c r="S51" s="2" t="n">
-        <v>-85.41121510000001</v>
+        <v>-93.2112786</v>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>2f5cc4d8a7818cba</t>
+          <t>bd292fb9f52ac2e9</t>
         </is>
       </c>
     </row>
     <row r="52" ht="26" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Assistant/Associate Professor of Civil Engineering</t>
+          <t>Assistant Professor / Associate Professor / Professor in Digital Supply Chain</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Cedarville University</t>
+          <t>Singapore Institute of Technology</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>School of Engineering and Computer Science</t>
+          <t>Engineering Division</t>
         </is>
       </c>
       <c r="D52" s="7" t="n">
@@ -5394,22 +5394,22 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>This is a broad civil engineering faculty search where transportation is explicitly listed as one of the acceptable sub-disciplines.</t>
+          <t>This open rank faculty position in digital supply chain offers some methodological overlap with logistics and mobility systems, though it is outside traditional transportation engineering.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Transportation Engineering, Civil Engineering Education, Undergraduate Mentoring</t>
+          <t>Digital Supply Chain, Logistics, Systems Engineering</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Non-Tenure Track</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Cedarville, OH</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
@@ -5425,27 +5425,27 @@
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>This position seeks an Assistant or Associate Professor in Civil Engineering to teach undergraduate courses and mentor students across disciplines including transportation, requiring a Ph.D. in Civil Engineering or related field. | Research Topics: Transportation Engineering, Civil Engineering Education, Undergraduate Mentoring</t>
+          <t>Open rank faculty position in digital supply chain management within the engineering division requiring a Ph.D. | Research Topics: Digital Supply Chain, Logistics, Systems Engineering</t>
         </is>
       </c>
       <c r="M52" s="5" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179544290&amp;Title=Assistant%2FAssociate%20Professor%20of%20Civil%20Engineering</t>
+          <t>https://sg.linkedin.com/jobs/view/assistant-professor-associate-professor-professor-in-digital-supply-chain-at-singapore-institute-of-technology-4278938030</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
-          <t>HigherEdJobs</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Q52" s="6" t="inlineStr">
@@ -5454,31 +5454,31 @@
         </is>
       </c>
       <c r="R52" s="2" t="n">
-        <v>39.7540491</v>
+        <v>1.4123197</v>
       </c>
       <c r="S52" s="2" t="n">
-        <v>-83.8170518</v>
+        <v>103.9094621</v>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>751c7406865a2787</t>
+          <t>dc9d59570835ff1a</t>
         </is>
       </c>
     </row>
     <row r="53" ht="26" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Tenure-Track Assistant Professor of Aeronautical Sciences</t>
+          <t>Assistant or Associate Professor of Professional Practice in Computer Science</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Embry-Riddle Aeronautical University</t>
+          <t>Texas Christian University</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>College of Aviation</t>
+          <t>Department of Computer Science</t>
         </is>
       </c>
       <c r="D53" s="7" t="n">
@@ -5486,22 +5486,22 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>While in aeronautical sciences, the specific focus is on air transportation systems which offers some overlap with transportation planning.</t>
+          <t>A professional practice position in computer science offers moderate applicability for candidates focused on mobility analytics and AI-integrated computing.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Air Transportation Systems, Aeronautical Sciences, Transportation Management</t>
+          <t>Computer Science, Software Engineering, Algorithms</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Non-Tenure Track</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL</t>
+          <t>Fort Worth, Texas</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
@@ -5512,27 +5512,27 @@
       <c r="J53" s="3" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>Competitive Salary</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>Tenure-track Assistant Professor focusing on air transportation systems requiring a Ph.D. in aviation or a related field. | Research Topics: Air Transportation Systems, Aeronautical Sciences, Transportation Management</t>
+          <t>A career-track faculty position of professional practice in computer science requiring a Ph.D. in computer science or related computing field. | Research Topics: Computer Science, Software Engineering, Algorithms</t>
         </is>
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/tenure-track-assistant-professor-of-aeronautical-sciences-daytona-beach-campus-at-embry-riddle-aeronautical-university-4472944897</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179571135&amp;Title=Assistant%20or%20Associate%20Professor%20of%20Professional%20Practice%20in%20Computer%20Science</t>
         </is>
       </c>
       <c r="N53" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -5546,31 +5546,31 @@
         </is>
       </c>
       <c r="R53" s="2" t="n">
-        <v>29.1895</v>
+        <v>32.7080148</v>
       </c>
       <c r="S53" s="2" t="n">
-        <v>-81.04940000000001</v>
+        <v>-97.3611939</v>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>e5ba6a7cb0c600c1</t>
+          <t>2ce3778a100bb83a</t>
         </is>
       </c>
     </row>
     <row r="54" ht="26" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Civil Engineering</t>
+          <t>Assistant, Associate, or Full Professor (Ladder Rank): Artificial Intelligence &amp; Public Policy</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>McNeese State University</t>
+          <t>University of California, San Diego</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Department of Engineering and Computer Science</t>
+          <t>Department / School of Public Policy</t>
         </is>
       </c>
       <c r="D54" s="7" t="n">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>This is a broad civil engineering faculty search that explicitly welcomes transportation engineering alongside other sub-disciplines.</t>
+          <t>This open rank faculty position focuses on Artificial Intelligence &amp; Public Policy, which has moderate interdisciplinary overlap with the candidate's AI-integrated mobility and policy work.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Civil Engineering, Transportation Engineering, Water Resources and Hydraulic Engineering, Structural and Geotechnical Engineering</t>
+          <t>Artificial Intelligence, Public Policy, Policy Analytics</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Lake Charles, LA</t>
+          <t>San Diego, CA</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
@@ -5604,32 +5604,32 @@
       <c r="J54" s="3" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>$76,000 per year</t>
+          <t>Reasonable range provided in posting</t>
         </is>
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>McNeese State University seeks a full-time, tenure-track Assistant Professor of Civil Engineering to teach, advise students, and conduct research, requiring a Ph.D. in Civil Engineering. | Research Topics: Civil Engineering, Transportation Engineering, Water Resources and Hydraulic Engineering, Structural and Geotechnical Engineering</t>
+          <t>Ladder-rank faculty position spanning Assistant to Full Professor levels focusing on Artificial Intelligence and Public Policy. | Research Topics: Artificial Intelligence, Public Policy, Policy Analytics</t>
         </is>
       </c>
       <c r="M54" s="5" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179545361&amp;Title=Assistant%20Professor%20of%20Civil%20Engineering</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-associate-or-full-professor-ladder-rank-artificial-intelligence-public-policy-at-uc-san-diego-academic-jobs-4436181013</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
         <is>
-          <t>HigherEdJobs</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Q54" s="6" t="inlineStr">
@@ -5638,31 +5638,31 @@
         </is>
       </c>
       <c r="R54" s="2" t="n">
-        <v>30.1751363</v>
+        <v>32.7157062</v>
       </c>
       <c r="S54" s="2" t="n">
-        <v>-93.2112786</v>
+        <v>-117.1638284</v>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>bd292fb9f52ac2e9</t>
+          <t>8bd030de26ce34cb</t>
         </is>
       </c>
     </row>
     <row r="55" ht="26" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor / Associate Professor / Professor in Digital Supply Chain</t>
+          <t>Full/Associate/Assistant Professor in Modern Civil Engineering</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Singapore Institute of Technology</t>
+          <t>University of Macau</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Engineering Division</t>
+          <t>Department of Civil and Environmental Engineering</t>
         </is>
       </c>
       <c r="D55" s="7" t="n">
@@ -5670,22 +5670,22 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>This open rank faculty position in digital supply chain offers some methodological overlap with logistics and mobility systems, though it is outside traditional transportation engineering.</t>
+          <t>Although the position matches the department of civil engineering, Macao is outside the candidate's target geographic regions.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Digital Supply Chain, Logistics, Systems Engineering</t>
+          <t>Civil Engineering, Infrastructure, Transportation</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>Non-Tenure Track</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Macao</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
@@ -5696,32 +5696,32 @@
       <c r="J55" s="3" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>£87,465.51 to £127,834.20</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
-          <t>Open rank faculty position in digital supply chain management within the engineering division requiring a Ph.D. | Research Topics: Digital Supply Chain, Logistics, Systems Engineering</t>
+          <t>An open-rank faculty position in civil engineering requiring a Ph.D. for teaching and research responsibilities. | Research Topics: Civil Engineering, Infrastructure, Transportation</t>
         </is>
       </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
-          <t>https://sg.linkedin.com/jobs/view/assistant-professor-associate-professor-professor-in-digital-supply-chain-at-singapore-institute-of-technology-4278938030</t>
+          <t>https://www.jobs.ac.uk/job/DSL575/full-associate-assistant-professor-in-modern-civil-engineering</t>
         </is>
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Jobs.ac.uk</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="Q55" s="6" t="inlineStr">
@@ -5730,31 +5730,31 @@
         </is>
       </c>
       <c r="R55" s="2" t="n">
-        <v>1.4123197</v>
+        <v>22.1285</v>
       </c>
       <c r="S55" s="2" t="n">
-        <v>103.9094621</v>
+        <v>113.5438</v>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>dc9d59570835ff1a</t>
+          <t>600dff84e8f0a0b2</t>
         </is>
       </c>
     </row>
     <row r="56" ht="26" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Assistant or Associate Professor of Professional Practice in Computer Science</t>
+          <t>Assistant Professor in Engineering Sciences</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Texas Christian University</t>
+          <t>Uppsala University</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Department of Computer Science</t>
+          <t>Department of Engineering Sciences</t>
         </is>
       </c>
       <c r="D56" s="7" t="n">
@@ -5762,22 +5762,22 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>A professional practice position in computer science offers moderate applicability for candidates focused on mobility analytics and AI-integrated computing.</t>
+          <t>The broad engineering sciences recruitment allows for potential alignment in mobility or systems engineering, but lacks a dedicated transportation department focus.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Computer Science, Software Engineering, Algorithms</t>
+          <t>Engineering Sciences, Technology, Innovation</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>Non-Tenure Track</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Fort Worth, Texas</t>
+          <t>Uppsala, Sweden</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
@@ -5793,22 +5793,22 @@
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>A career-track faculty position of professional practice in computer science requiring a Ph.D. in computer science or related computing field. | Research Topics: Computer Science, Software Engineering, Algorithms</t>
+          <t>Assistant professor position in engineering sciences seeking top talent in technology and innovation holding a Ph.D. | Research Topics: Engineering Sciences, Technology, Innovation</t>
         </is>
       </c>
       <c r="M56" s="5" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179571135&amp;Title=Assistant%20or%20Associate%20Professor%20of%20Professional%20Practice%20in%20Computer%20Science</t>
+          <t>https://se.linkedin.com/jobs/view/assistant-professor-in-engineering-sciences-at-uppsala-university-4469465117</t>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
-          <t>HigherEdJobs</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -5822,31 +5822,31 @@
         </is>
       </c>
       <c r="R56" s="2" t="n">
-        <v>32.7080148</v>
+        <v>59.8576363</v>
       </c>
       <c r="S56" s="2" t="n">
-        <v>-97.3611939</v>
+        <v>17.6294616</v>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>2ce3778a100bb83a</t>
+          <t>b15b03a481822584</t>
         </is>
       </c>
     </row>
     <row r="57" ht="26" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Assistant, Associate, or Full Professor (Ladder Rank): Artificial Intelligence &amp; Public Policy</t>
+          <t>Faculty - Tenure-Track, Transportation Technologies</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>University of California, San Diego</t>
+          <t>Utah Valley University</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Department / School of Public Policy</t>
+          <t>Department of Transportation Technologies</t>
         </is>
       </c>
       <c r="D57" s="7" t="n">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>This open rank faculty position focuses on Artificial Intelligence &amp; Public Policy, which has moderate interdisciplinary overlap with the candidate's AI-integrated mobility and policy work.</t>
+          <t>The position targets transportation technologies, offering a broad fit though potentially oriented toward technical/vocational or applied systems rather than core civil engineering transportation planning.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Artificial Intelligence, Public Policy, Policy Analytics</t>
+          <t>Transportation Technologies, Intelligent Transportation Systems, Vehicle Systems</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>San Diego, CA</t>
+          <t>Orem, Utah</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
@@ -5880,27 +5880,27 @@
       <c r="J57" s="3" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>Reasonable range provided in posting</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
-          <t>Ladder-rank faculty position spanning Assistant to Full Professor levels focusing on Artificial Intelligence and Public Policy. | Research Topics: Artificial Intelligence, Public Policy, Policy Analytics</t>
+          <t>Tenure-track faculty position focusing on transportation technologies and systems requiring an appropriate advanced degree. | Research Topics: Transportation Technologies, Intelligent Transportation Systems, Vehicle Systems</t>
         </is>
       </c>
       <c r="M57" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-associate-or-full-professor-ladder-rank-artificial-intelligence-public-policy-at-uc-san-diego-academic-jobs-4436181013</t>
+          <t>https://jobs.chronicle.com/job/38038164/faculty-tenure-track-transportation-technologies/</t>
         </is>
       </c>
       <c r="N57" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -5914,31 +5914,31 @@
         </is>
       </c>
       <c r="R57" s="2" t="n">
-        <v>32.7157062</v>
+        <v>40.2794106</v>
       </c>
       <c r="S57" s="2" t="n">
-        <v>-117.1638284</v>
+        <v>-111.7178868</v>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>8bd030de26ce34cb</t>
+          <t>2290e54d4bdd2bb2</t>
         </is>
       </c>
     </row>
     <row r="58" ht="26" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Full/Associate/Assistant Professor in Modern Civil Engineering</t>
+          <t>Open Rank - Research Faculty</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>University of Macau</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Department of Civil and Environmental Engineering</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="D58" s="7" t="n">
@@ -5946,22 +5946,22 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Although the position matches the department of civil engineering, Macao is outside the candidate's target geographic regions.</t>
+          <t>This is an open rank research faculty search at Virginia Tech, which offers potential alignment with transportation and mobility systems depending on the specific institute focus.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Civil Engineering, Infrastructure, Transportation</t>
+          <t>Research Faculty, Systems Engineering, Applied Research</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Non-Tenure Track</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Macao</t>
+          <t>Blacksburg, VA</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
@@ -5972,32 +5972,32 @@
       <c r="J58" s="3" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>£87,465.51 to £127,834.20</t>
+          <t>Competitive</t>
         </is>
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>An open-rank faculty position in civil engineering requiring a Ph.D. for teaching and research responsibilities. | Research Topics: Civil Engineering, Infrastructure, Transportation</t>
+          <t>An open rank research faculty appointment at Virginia Tech focused on advancing sponsored research programs. | Research Topics: Research Faculty, Systems Engineering, Applied Research</t>
         </is>
       </c>
       <c r="M58" s="5" t="inlineStr">
         <is>
-          <t>https://www.jobs.ac.uk/job/DSL575/full-associate-assistant-professor-in-modern-civil-engineering</t>
+          <t>https://www.linkedin.com/jobs/view/open-rank-research-faculty-at-virginia-tech-4436626390</t>
         </is>
       </c>
       <c r="N58" s="3" t="inlineStr">
         <is>
-          <t>Jobs.ac.uk</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Q58" s="6" t="inlineStr">
@@ -6006,54 +6006,54 @@
         </is>
       </c>
       <c r="R58" s="2" t="n">
-        <v>22.1285</v>
+        <v>37.2284</v>
       </c>
       <c r="S58" s="2" t="n">
-        <v>113.5438</v>
+        <v>-80.4234</v>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>600dff84e8f0a0b2</t>
+          <t>506a4da7eb130285</t>
         </is>
       </c>
     </row>
     <row r="59" ht="26" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor in Engineering Sciences</t>
+          <t>Assistant/Associate/Full Professor</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Uppsala University</t>
+          <t>Auburn University</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Department of Engineering Sciences</t>
+          <t>Unspecified Department</t>
         </is>
       </c>
       <c r="D59" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>The broad engineering sciences recruitment allows for potential alignment in mobility or systems engineering, but lacks a dedicated transportation department focus.</t>
+          <t>This is an open rank faculty search in an unspecified department at Auburn University, offering moderate potential for transportation engineering depending on the specific hiring unit.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Engineering Sciences, Technology, Innovation</t>
+          <t>Higher Education, Faculty Research, Academic Teaching</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Unspecified</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Uppsala, Sweden</t>
+          <t>Auburn, Alabama</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
@@ -6064,22 +6064,22 @@
       <c r="J59" s="3" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Competitive Salary</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
-          <t>Assistant professor position in engineering sciences seeking top talent in technology and innovation holding a Ph.D. | Research Topics: Engineering Sciences, Technology, Innovation</t>
+          <t>This open rank faculty position at Auburn University requires a terminal degree and focuses on teaching, research, and service across unspecified academic disciplines. | Research Topics: Higher Education, Faculty Research, Academic Teaching</t>
         </is>
       </c>
       <c r="M59" s="5" t="inlineStr">
         <is>
-          <t>https://se.linkedin.com/jobs/view/assistant-professor-in-engineering-sciences-at-uppsala-university-4469465117</t>
+          <t>https://jobs.chronicle.com/job/38006801/assistant-associate-full-professor/</t>
         </is>
       </c>
       <c r="N59" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
@@ -6098,54 +6098,54 @@
         </is>
       </c>
       <c r="R59" s="2" t="n">
-        <v>59.8576363</v>
+        <v>32.5919529</v>
       </c>
       <c r="S59" s="2" t="n">
-        <v>17.6294616</v>
+        <v>-85.4959775</v>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>b15b03a481822584</t>
+          <t>aa87d514aaef1b11</t>
         </is>
       </c>
     </row>
     <row r="60" ht="26" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Faculty - Tenure-Track, Transportation Technologies</t>
+          <t>Assistant Professor of Teaching</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Utah Valley University</t>
+          <t>Florida Atlantic University</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Department of Transportation Technologies</t>
+          <t>College of Engineering and Computer Science</t>
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>The position targets transportation technologies, offering a broad fit though potentially oriented toward technical/vocational or applied systems rather than core civil engineering transportation planning.</t>
+          <t>The posting is for a general teaching faculty position in an unspecified department, offering broad teaching opportunities.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Transportation Technologies, Intelligent Transportation Systems, Vehicle Systems</t>
+          <t>Engineering Education, Pedagogy, Curriculum Development</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Non-Tenure Track</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Orem, Utah</t>
+          <t>Boca Raton, FL</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
@@ -6161,22 +6161,22 @@
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
-          <t>Tenure-track faculty position focusing on transportation technologies and systems requiring an appropriate advanced degree. | Research Topics: Transportation Technologies, Intelligent Transportation Systems, Vehicle Systems</t>
+          <t>Assistant Professor of Teaching career-track appointment requiring a Ph.D. in engineering or a closely related discipline. | Research Topics: Engineering Education, Pedagogy, Curriculum Development</t>
         </is>
       </c>
       <c r="M60" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38038164/faculty-tenure-track-transportation-technologies/</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-of-teaching-at-florida-atlantic-university-4414964381</t>
         </is>
       </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -6190,44 +6190,44 @@
         </is>
       </c>
       <c r="R60" s="2" t="n">
-        <v>40.2794106</v>
+        <v>26.3743445</v>
       </c>
       <c r="S60" s="2" t="n">
-        <v>-111.7178868</v>
+        <v>-80.1027236</v>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>2290e54d4bdd2bb2</t>
+          <t>7bdaa996cf64d1f6</t>
         </is>
       </c>
     </row>
     <row r="61" ht="26" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Open Rank - Research Faculty</t>
+          <t>Lecturer (Mobility &amp; Robotic Systems)</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>Republic Polytechnic</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>School of Engineering</t>
         </is>
       </c>
       <c r="D61" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>This is an open rank research faculty search at Virginia Tech, which offers potential alignment with transportation and mobility systems depending on the specific institute focus.</t>
+          <t>While it deals with mobility and robotic systems, it is a teaching polytechnic lecturer position rather than a tenure-track research university faculty role.</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Research Faculty, Systems Engineering, Applied Research</t>
+          <t>Mobility Systems, Smart Robotics, Autonomous Systems</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
@@ -6237,7 +6237,7 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Blacksburg, VA</t>
+          <t>Singapore, Singapore</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
@@ -6248,17 +6248,17 @@
       <c r="J61" s="3" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>Competitive</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
-          <t>An open rank research faculty appointment at Virginia Tech focused on advancing sponsored research programs. | Research Topics: Research Faculty, Systems Engineering, Applied Research</t>
+          <t>This is a teaching and curriculum development role focusing on mobility and robotic engineering systems requiring a relevant degree. | Research Topics: Mobility Systems, Smart Robotics, Autonomous Systems</t>
         </is>
       </c>
       <c r="M61" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/open-rank-research-faculty-at-virginia-tech-4436626390</t>
+          <t>https://sg.linkedin.com/jobs/view/lecturer-mobility-robotic-systems-at-republic-polytechnic-4466503273</t>
         </is>
       </c>
       <c r="N61" s="3" t="inlineStr">
@@ -6268,12 +6268,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="Q61" s="6" t="inlineStr">
@@ -6282,31 +6282,31 @@
         </is>
       </c>
       <c r="R61" s="2" t="n">
-        <v>37.2284</v>
+        <v>1.4443688</v>
       </c>
       <c r="S61" s="2" t="n">
-        <v>-80.4234</v>
+        <v>103.7853712</v>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>506a4da7eb130285</t>
+          <t>00c292267aae717a</t>
         </is>
       </c>
     </row>
     <row r="62" ht="26" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Assistant/Associate/Full Professor</t>
+          <t>Assistant Professor of Economics - Urban/Regional Spatial Data Analysis</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Auburn University</t>
+          <t>The California State University</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Unspecified Department</t>
+          <t>Department of Economics</t>
         </is>
       </c>
       <c r="D62" s="7" t="n">
@@ -6314,22 +6314,22 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>This is an open rank faculty search in an unspecified department at Auburn University, offering moderate potential for transportation engineering depending on the specific hiring unit.</t>
+          <t>The position is in Economics focusing on urban and regional spatial data analysis, offering some interdisciplinary alignment with spatial mobility and urban planning.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Higher Education, Faculty Research, Academic Teaching</t>
+          <t>Urban Economics, Regional Spatial Data Analysis, Spatial Econometrics</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Auburn, Alabama</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
@@ -6340,22 +6340,22 @@
       <c r="J62" s="3" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>Competitive Salary</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
-          <t>This open rank faculty position at Auburn University requires a terminal degree and focuses on teaching, research, and service across unspecified academic disciplines. | Research Topics: Higher Education, Faculty Research, Academic Teaching</t>
+          <t>Tenure-track assistant professor in economics specializing in urban and regional spatial data analysis requiring a Ph.D. | Research Topics: Urban Economics, Regional Spatial Data Analysis, Spatial Econometrics</t>
         </is>
       </c>
       <c r="M62" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38006801/assistant-associate-full-professor/</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-of-economics-urban-regional-spatial-data-analysis-at-the-california-state-university-4453250485</t>
         </is>
       </c>
       <c r="N62" s="3" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
@@ -6374,31 +6374,31 @@
         </is>
       </c>
       <c r="R62" s="2" t="n">
-        <v>32.5919529</v>
+        <v>34.2455346</v>
       </c>
       <c r="S62" s="2" t="n">
-        <v>-85.4959775</v>
+        <v>-118.5263221</v>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>aa87d514aaef1b11</t>
+          <t>4e72794ba80f8d06</t>
         </is>
       </c>
     </row>
     <row r="63" ht="26" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Teaching</t>
+          <t>Professor / Associate Professor / Assistant Professor</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Florida Atlantic University</t>
+          <t>THE HONG KONG POLYTECHNIC UNIVERSITY</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>College of Engineering and Computer Science</t>
+          <t>Unspecified Department</t>
         </is>
       </c>
       <c r="D63" s="7" t="n">
@@ -6406,22 +6406,22 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>The posting is for a general teaching faculty position in an unspecified department, offering broad teaching opportunities.</t>
+          <t>The posting is an open rank faculty search at a major polytechnic university that could encompass transportation, though specific department details are unspecified.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Engineering Education, Pedagogy, Curriculum Development</t>
+          <t>Polytechnic Education, Engineering, Technology</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>Non-Tenure Track</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Boca Raton, FL</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
@@ -6432,65 +6432,65 @@
       <c r="J63" s="3" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Competitive</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
-          <t>Assistant Professor of Teaching career-track appointment requiring a Ph.D. in engineering or a closely related discipline. | Research Topics: Engineering Education, Pedagogy, Curriculum Development</t>
+          <t>Open rank faculty position at a polytechnic university requiring a Ph.D. in a relevant engineering or technology discipline. | Research Topics: Polytechnic Education, Engineering, Technology</t>
         </is>
       </c>
       <c r="M63" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-of-teaching-at-florida-atlantic-university-4414964381</t>
+          <t>https://jobs.chronicle.com/job/38028368/professor-associate-professor-assistant-professor/</t>
         </is>
       </c>
       <c r="N63" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="P63" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
       <c r="Q63" s="6" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
       <c r="R63" s="2" t="n">
-        <v>26.3743445</v>
+        <v>22.3045</v>
       </c>
       <c r="S63" s="2" t="n">
-        <v>-80.1027236</v>
+        <v>114.1797</v>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>7bdaa996cf64d1f6</t>
+          <t>09d04da628fd08f9</t>
         </is>
       </c>
     </row>
     <row r="64" ht="26" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Lecturer (Mobility &amp; Robotic Systems)</t>
+          <t>Professor / Associate Professor / Assistant Professor in AI/Robotics for Aircraft Maintenance / Low-Altitude Economy / Satellite and Space Engineering</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Republic Polytechnic</t>
+          <t>The Hong Kong Polytechnic University</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>School of Engineering</t>
+          <t>Department of Aeronautical and Aviation Engineering</t>
         </is>
       </c>
       <c r="D64" s="7" t="n">
@@ -6498,22 +6498,22 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>While it deals with mobility and robotic systems, it is a teaching polytechnic lecturer position rather than a tenure-track research university faculty role.</t>
+          <t>The position includes Assistant Professor level and focuses on AI/Robotics and the low-altitude economy, offering some alignment with mobility systems.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Mobility Systems, Smart Robotics, Autonomous Systems</t>
+          <t>Low-Altitude Economy, AI and Robotics, Aviation Systems</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>Non-Tenure Track</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Singapore, Singapore</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
@@ -6529,27 +6529,27 @@
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
-          <t>This is a teaching and curriculum development role focusing on mobility and robotic engineering systems requiring a relevant degree. | Research Topics: Mobility Systems, Smart Robotics, Autonomous Systems</t>
+          <t>Open rank faculty position focusing on AI and robotics for aviation and low-altitude economy applications requiring a Ph.D. | Research Topics: Low-Altitude Economy, AI and Robotics, Aviation Systems</t>
         </is>
       </c>
       <c r="M64" s="5" t="inlineStr">
         <is>
-          <t>https://sg.linkedin.com/jobs/view/lecturer-mobility-robotic-systems-at-republic-polytechnic-4466503273</t>
+          <t>https://www.jobs.ac.uk/job/DSR599/professor-associate-professor-assistant-professor-in-ai-robotics-for-aircraft-maintenance-low-altitude-economy-satellite-and-space-engineering-under-strategic-hiring-scheme</t>
         </is>
       </c>
       <c r="N64" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Jobs.ac.uk</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Q64" s="6" t="inlineStr">
@@ -6558,31 +6558,31 @@
         </is>
       </c>
       <c r="R64" s="2" t="n">
-        <v>1.4443688</v>
+        <v>22.3045</v>
       </c>
       <c r="S64" s="2" t="n">
-        <v>103.7853712</v>
+        <v>114.1797</v>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>00c292267aae717a</t>
+          <t>9f12038ffb75ebfb</t>
         </is>
       </c>
     </row>
     <row r="65" ht="26" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Economics - Urban/Regional Spatial Data Analysis</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>The California State University</t>
+          <t>University of Louisville</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Department of Economics</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="D65" s="7" t="n">
@@ -6590,12 +6590,12 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>The position is in Economics focusing on urban and regional spatial data analysis, offering some interdisciplinary alignment with spatial mobility and urban planning.</t>
+          <t>The posting is too generic to confirm a transportation focus, but it is an Assistant Professor role.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Urban Economics, Regional Spatial Data Analysis, Spatial Econometrics</t>
+          <t>General Faculty, Academic Research</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
@@ -6605,7 +6605,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>Louisville, Kentucky</t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
@@ -6616,22 +6616,22 @@
       <c r="J65" s="3" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Commensurate with qualifications and experience</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
-          <t>Tenure-track assistant professor in economics specializing in urban and regional spatial data analysis requiring a Ph.D. | Research Topics: Urban Economics, Regional Spatial Data Analysis, Spatial Econometrics</t>
+          <t>An unspecified Assistant Professor position at the University of Louisville. | Research Topics: General Faculty, Academic Research</t>
         </is>
       </c>
       <c r="M65" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-of-economics-urban-regional-spatial-data-analysis-at-the-california-state-university-4453250485</t>
+          <t>https://jobs.chronicle.com/job/38030999/assistant-professor/</t>
         </is>
       </c>
       <c r="N65" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
@@ -6650,31 +6650,31 @@
         </is>
       </c>
       <c r="R65" s="2" t="n">
-        <v>34.2455346</v>
+        <v>38.2133224</v>
       </c>
       <c r="S65" s="2" t="n">
-        <v>-118.5263221</v>
+        <v>-85.7577075</v>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>4e72794ba80f8d06</t>
+          <t>7d3d0a76d877bbe5</t>
         </is>
       </c>
     </row>
     <row r="66" ht="26" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Professor / Associate Professor / Assistant Professor</t>
+          <t>Assistant Professor in Sustainability Studies</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>THE HONG KONG POLYTECHNIC UNIVERSITY</t>
+          <t>University of Twente</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Unspecified Department</t>
+          <t>Faculty of Social Sciences / Sustainability Studies</t>
         </is>
       </c>
       <c r="D66" s="7" t="n">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>The posting is an open rank faculty search at a major polytechnic university that could encompass transportation, though specific department details are unspecified.</t>
+          <t>The position focuses broadly on sustainability studies with quantitative and qualitative methods, offering a modest interdisciplinary fit for mobility research.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Polytechnic Education, Engineering, Technology</t>
+          <t>Sustainability Studies, Social Science, Quantitative and Qualitative Methods</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
@@ -6697,7 +6697,7 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Enschede, Overijssel, Netherlands</t>
         </is>
       </c>
       <c r="I66" s="3" t="inlineStr">
@@ -6708,32 +6708,32 @@
       <c r="J66" s="3" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>Competitive</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
-          <t>Open rank faculty position at a polytechnic university requiring a Ph.D. in a relevant engineering or technology discipline. | Research Topics: Polytechnic Education, Engineering, Technology</t>
+          <t>Assistant professor position focusing on social science and quantitative sustainability research requiring a Ph.D. | Research Topics: Sustainability Studies, Social Science, Quantitative and Qualitative Methods</t>
         </is>
       </c>
       <c r="M66" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38028368/professor-associate-professor-assistant-professor/</t>
+          <t>https://nl.linkedin.com/jobs/view/two-assistant-professorship-positions-in-sustainability-studies-at-university-of-twente-4463028013</t>
         </is>
       </c>
       <c r="N66" s="3" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="Q66" s="6" t="inlineStr">
@@ -6742,31 +6742,31 @@
         </is>
       </c>
       <c r="R66" s="2" t="n">
-        <v>22.3045</v>
+        <v>52.2433268</v>
       </c>
       <c r="S66" s="2" t="n">
-        <v>114.1797</v>
+        <v>6.8509157</v>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>09d04da628fd08f9</t>
+          <t>bc3324541c93bcd3</t>
         </is>
       </c>
     </row>
     <row r="67" ht="26" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Professor / Associate Professor / Assistant Professor in AI/Robotics for Aircraft Maintenance / Low-Altitude Economy / Satellite and Space Engineering</t>
+          <t>Tenure-track Faculty Position in Data Analysis and Quantitative Methods</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>The Hong Kong Polytechnic University</t>
+          <t>Université Laval</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Department of Aeronautical and Aviation Engineering</t>
+          <t>Department of Quantitative Methods</t>
         </is>
       </c>
       <c r="D67" s="7" t="n">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>The position includes Assistant Professor level and focuses on AI/Robotics and the low-altitude economy, offering some alignment with mobility systems.</t>
+          <t>The general quantitative methods and data analysis focus offers a broad methodological alignment, though it lacks a specific transportation engineering context.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Low-Altitude Economy, AI and Robotics, Aviation Systems</t>
+          <t>Data Analysis, Quantitative Methods</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
@@ -6789,7 +6789,7 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Québec, Quebec, Canada</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
@@ -6805,22 +6805,22 @@
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
-          <t>Open rank faculty position focusing on AI and robotics for aviation and low-altitude economy applications requiring a Ph.D. | Research Topics: Low-Altitude Economy, AI and Robotics, Aviation Systems</t>
+          <t>Tenure-track position in data analysis and quantitative methods requiring a Ph.D. and a strong publication record. | Research Topics: Data Analysis, Quantitative Methods</t>
         </is>
       </c>
       <c r="M67" s="5" t="inlineStr">
         <is>
-          <t>https://www.jobs.ac.uk/job/DSR599/professor-associate-professor-assistant-professor-in-ai-robotics-for-aircraft-maintenance-low-altitude-economy-satellite-and-space-engineering-under-strategic-hiring-scheme</t>
+          <t>https://ca.linkedin.com/jobs/view/tenure-track-faculty-position-in-data-analysis-and-quantitative-methods-at-universit%C3%A9-laval-4445943132</t>
         </is>
       </c>
       <c r="N67" s="3" t="inlineStr">
         <is>
-          <t>Jobs.ac.uk</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -6834,44 +6834,44 @@
         </is>
       </c>
       <c r="R67" s="2" t="n">
-        <v>22.3045</v>
+        <v>46.7811677</v>
       </c>
       <c r="S67" s="2" t="n">
-        <v>114.1797</v>
+        <v>-71.27413610000001</v>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>9f12038ffb75ebfb</t>
+          <t>d3156802feb660c0</t>
         </is>
       </c>
     </row>
     <row r="68" ht="26" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Assistant/Associate Professor</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>University of Louisville</t>
+          <t>Brown University</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="D68" s="7" t="n">
-        <v>5</v>
+          <t>School of Engineering</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>The posting is too generic to confirm a transportation focus, but it is an Assistant Professor role.</t>
+          <t>The department focuses on chemical and environmental engineering, which has limited overlap with the candidate's transportation engineering profile.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>General Faculty, Academic Research</t>
+          <t>Chemical Engineering, Environmental Engineering, Materials Science</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Louisville, Kentucky</t>
+          <t>Providence, Rhode Island</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
@@ -6892,27 +6892,27 @@
       <c r="J68" s="3" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>Commensurate with qualifications and experience</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L68" s="4" t="inlineStr">
         <is>
-          <t>An unspecified Assistant Professor position at the University of Louisville. | Research Topics: General Faculty, Academic Research</t>
+          <t>This open-rank faculty position requires a Ph.D. in chemical engineering, environmental engineering, or materials science. | Research Topics: Chemical Engineering, Environmental Engineering, Materials Science</t>
         </is>
       </c>
       <c r="M68" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38030999/assistant-professor/</t>
+          <t>http://engineering.academickeys.com/job/ad8r6xb2/Chemical-Engineering-Environmental-Engineering-and-Materials-Science-and-Engineering-AssistantAssociate-Professor</t>
         </is>
       </c>
       <c r="N68" s="3" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>AcademicKeys</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -6926,44 +6926,44 @@
         </is>
       </c>
       <c r="R68" s="2" t="n">
-        <v>38.2133224</v>
+        <v>41.8268</v>
       </c>
       <c r="S68" s="2" t="n">
-        <v>-85.7577075</v>
+        <v>-71.4025</v>
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>7d3d0a76d877bbe5</t>
+          <t>6617a775b51412a6</t>
         </is>
       </c>
     </row>
     <row r="69" ht="26" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor in Sustainability Studies</t>
+          <t>Assistant Professor in Control Systems Technology for Emerging Application Areas</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>University of Twente</t>
+          <t>Eindhoven University of Technology</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Faculty of Social Sciences / Sustainability Studies</t>
-        </is>
-      </c>
-      <c r="D69" s="7" t="n">
-        <v>5</v>
+          <t>Department of Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>The position focuses broadly on sustainability studies with quantitative and qualitative methods, offering a modest interdisciplinary fit for mobility research.</t>
+          <t>The position focuses on general control systems technology rather than transportation engineering or mobility systems.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Sustainability Studies, Social Science, Quantitative and Qualitative Methods</t>
+          <t>Control Systems Technology, Emerging Applications, Systems Engineering</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
@@ -6973,7 +6973,7 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>Enschede, Overijssel, Netherlands</t>
+          <t>Eindhoven, North Brabant, Netherlands</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr">
@@ -6989,12 +6989,12 @@
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
-          <t>Assistant professor position focusing on social science and quantitative sustainability research requiring a Ph.D. | Research Topics: Sustainability Studies, Social Science, Quantitative and Qualitative Methods</t>
+          <t>Assistant Professor role focusing on control systems technology requiring a Ph.D. in a relevant engineering discipline. | Research Topics: Control Systems Technology, Emerging Applications, Systems Engineering</t>
         </is>
       </c>
       <c r="M69" s="5" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/two-assistant-professorship-positions-in-sustainability-studies-at-university-of-twente-4463028013</t>
+          <t>https://nl.linkedin.com/jobs/view/assistant-professor-in-control-systems-technology-for-emerging-application-areas-at-eindhoven-university-of-technology-4449015225</t>
         </is>
       </c>
       <c r="N69" s="3" t="inlineStr">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Q69" s="6" t="inlineStr">
@@ -7018,54 +7018,54 @@
         </is>
       </c>
       <c r="R69" s="2" t="n">
-        <v>52.2433268</v>
+        <v>51.4486602</v>
       </c>
       <c r="S69" s="2" t="n">
-        <v>6.8509157</v>
+        <v>5.4903996</v>
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>bc3324541c93bcd3</t>
+          <t>61c642450ddce455</t>
         </is>
       </c>
     </row>
     <row r="70" ht="26" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Tenure-track Faculty Position in Data Analysis and Quantitative Methods</t>
+          <t>Mathematician (Assistant Professor)</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Université Laval</t>
+          <t>Maritime Administration (MARAD)</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Department of Quantitative Methods</t>
-        </is>
-      </c>
-      <c r="D70" s="7" t="n">
-        <v>5</v>
+          <t>Department of Mathematics</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>The general quantitative methods and data analysis focus offers a broad methodological alignment, though it lacks a specific transportation engineering context.</t>
+          <t>The role involves teaching mathematics courses rather than transportation engineering or mobility systems.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Data Analysis, Quantitative Methods</t>
+          <t>Mathematics Education, Applied Mathematics, Maritime Education</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Non-Tenure Track</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Québec, Quebec, Canada</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="I70" s="3" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
-          <t>Tenure-track position in data analysis and quantitative methods requiring a Ph.D. and a strong publication record. | Research Topics: Data Analysis, Quantitative Methods</t>
+          <t>This role involves teaching mathematics courses and developing educational programs requiring a graduate degree. | Research Topics: Mathematics Education, Applied Mathematics, Maritime Education</t>
         </is>
       </c>
       <c r="M70" s="5" t="inlineStr">
         <is>
-          <t>https://ca.linkedin.com/jobs/view/tenure-track-faculty-position-in-data-analysis-and-quantitative-methods-at-universit%C3%A9-laval-4445943132</t>
+          <t>https://www.linkedin.com/jobs/view/mathematician-assistant-professor-excepted-service-at-maritime-administration-marad-4474153695</t>
         </is>
       </c>
       <c r="N70" s="3" t="inlineStr">
@@ -7110,31 +7110,31 @@
         </is>
       </c>
       <c r="R70" s="2" t="n">
-        <v>46.7811677</v>
+        <v>40.7127281</v>
       </c>
       <c r="S70" s="2" t="n">
-        <v>-71.27413610000001</v>
+        <v>-74.00601519999999</v>
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>d3156802feb660c0</t>
+          <t>00943bd3a153f1ac</t>
         </is>
       </c>
     </row>
     <row r="71" ht="26" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Assistant/Associate Professor</t>
+          <t>Assistant Professor of Mechanical Engineering</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Brown University</t>
+          <t>Montana State University</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>School of Engineering</t>
+          <t>Department of Mechanical and Industrial Engineering</t>
         </is>
       </c>
       <c r="D71" s="3" t="n">
@@ -7142,12 +7142,12 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>The department focuses on chemical and environmental engineering, which has limited overlap with the candidate's transportation engineering profile.</t>
+          <t>The position is in Mechanical Engineering rather than Civil or Transportation Engineering, offering only peripheral overlap.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Chemical Engineering, Environmental Engineering, Materials Science</t>
+          <t>Mechanical Engineering, Thermal-Fluids, Mechanics</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>Providence, Rhode Island</t>
+          <t>Bozeman, Montana</t>
         </is>
       </c>
       <c r="I71" s="3" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
-          <t>This open-rank faculty position requires a Ph.D. in chemical engineering, environmental engineering, or materials science. | Research Topics: Chemical Engineering, Environmental Engineering, Materials Science</t>
+          <t>Seeking an Assistant Professor of Mechanical Engineering requiring a Ph.D. in mechanical engineering or closely related field. | Research Topics: Mechanical Engineering, Thermal-Fluids, Mechanics</t>
         </is>
       </c>
       <c r="M71" s="5" t="inlineStr">
         <is>
-          <t>http://engineering.academickeys.com/job/ad8r6xb2/Chemical-Engineering-Environmental-Engineering-and-Materials-Science-and-Engineering-AssistantAssociate-Professor</t>
+          <t>https://engineering.academickeys.com/job/ruoe4wlz/Assistant-Professor-of-Mechanical-Engineering</t>
         </is>
       </c>
       <c r="N71" s="3" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -7202,31 +7202,31 @@
         </is>
       </c>
       <c r="R71" s="2" t="n">
-        <v>7.1438798</v>
+        <v>45.6639222</v>
       </c>
       <c r="S71" s="2" t="n">
-        <v>125.5990517</v>
+        <v>-111.079277</v>
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>6617a775b51412a6</t>
+          <t>735f106baf0ccc18</t>
         </is>
       </c>
     </row>
     <row r="72" ht="26" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor in Control Systems Technology for Emerging Application Areas</t>
+          <t>Assistant Professor of Economics - Urban/Regional Spatial Data Analysis</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Eindhoven University of Technology</t>
+          <t>San José State University</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Department of Mechanical Engineering</t>
+          <t>Department of Economics</t>
         </is>
       </c>
       <c r="D72" s="3" t="n">
@@ -7234,12 +7234,12 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>The position focuses on general control systems technology rather than transportation engineering or mobility systems.</t>
+          <t>Although the role involves spatial data analysis which intersects with mobility, it is based in an Economics department focusing on urban and regional economics rather than transportation engineering.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Control Systems Technology, Emerging Applications, Systems Engineering</t>
+          <t>Urban Economics, Spatial Data Analysis, Regional Economics</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
@@ -7249,7 +7249,7 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Eindhoven, North Brabant, Netherlands</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="I72" s="3" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
-          <t>Assistant Professor role focusing on control systems technology requiring a Ph.D. in a relevant engineering discipline. | Research Topics: Control Systems Technology, Emerging Applications, Systems Engineering</t>
+          <t>Tenure-track assistant professor in economics specializing in urban and regional spatial data analysis requiring a Ph.D. | Research Topics: Urban Economics, Spatial Data Analysis, Regional Economics</t>
         </is>
       </c>
       <c r="M72" s="5" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/assistant-professor-in-control-systems-technology-for-emerging-application-areas-at-eindhoven-university-of-technology-4449015225</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-of-economics-urban-regional-spatial-data-analysis-at-san-jos%C3%A9-state-university-4454304392</t>
         </is>
       </c>
       <c r="N72" s="3" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -7294,31 +7294,31 @@
         </is>
       </c>
       <c r="R72" s="2" t="n">
-        <v>51.4486602</v>
+        <v>37.3351902</v>
       </c>
       <c r="S72" s="2" t="n">
-        <v>5.4903996</v>
+        <v>-121.881225</v>
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>61c642450ddce455</t>
+          <t>8f931a7dcebc3de3</t>
         </is>
       </c>
     </row>
     <row r="73" ht="26" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Mathematician (Assistant Professor)</t>
+          <t>Assistant or Associate Professor in Management – Operations and Supply Chain Management</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Maritime Administration (MARAD)</t>
+          <t>The American College of Greece</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Department of Mathematics</t>
+          <t>Alba Graduate Business School</t>
         </is>
       </c>
       <c r="D73" s="3" t="n">
@@ -7326,22 +7326,22 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>The role involves teaching mathematics courses rather than transportation engineering or mobility systems.</t>
+          <t>While operations and supply chain management has methodological overlaps with logistics, the focus is within a business school rather than a transportation engineering or urban planning department.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Mathematics Education, Applied Mathematics, Maritime Education</t>
+          <t>Operations Management, Supply Chain Management, Business Analytics</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>Non-Tenure Track</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Athens, Greece</t>
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr">
@@ -7357,12 +7357,12 @@
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
-          <t>This role involves teaching mathematics courses and developing educational programs requiring a graduate degree. | Research Topics: Mathematics Education, Applied Mathematics, Maritime Education</t>
+          <t>Faculty position in operations and supply chain management at a graduate business school requiring a Ph.D. in a related field. | Research Topics: Operations Management, Supply Chain Management, Business Analytics</t>
         </is>
       </c>
       <c r="M73" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/mathematician-assistant-professor-excepted-service-at-maritime-administration-marad-4474153695</t>
+          <t>https://gr.linkedin.com/jobs/view/assistant-or-associate-professor-in-management-%E2%80%93-operations-and-supply-chain-management-at-the-american-college-of-greece-4471999873</t>
         </is>
       </c>
       <c r="N73" s="3" t="inlineStr">
@@ -7386,31 +7386,31 @@
         </is>
       </c>
       <c r="R73" s="2" t="n">
-        <v>40.7127281</v>
+        <v>38.003282</v>
       </c>
       <c r="S73" s="2" t="n">
-        <v>-74.00601519999999</v>
+        <v>23.8317208</v>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>00943bd3a153f1ac</t>
+          <t>154bc2d385933c45</t>
         </is>
       </c>
     </row>
     <row r="74" ht="26" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Mechanical Engineering</t>
+          <t>Assistant or Associate Professor in Supply Chain Management</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Montana State University</t>
+          <t>University of Guelph</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Department of Mechanical and Industrial Engineering</t>
+          <t>Gordon S. Lang School of Business and Economics</t>
         </is>
       </c>
       <c r="D74" s="3" t="n">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>The position is in Mechanical Engineering rather than Civil or Transportation Engineering, offering only peripheral overlap.</t>
+          <t>This is a supply chain management faculty position within a business school, offering only slight peripheral overlap with logistics.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Mechanical Engineering, Thermal-Fluids, Mechanics</t>
+          <t>Supply Chain Management, Logistics, Operations Management</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Bozeman, Montana</t>
+          <t>Guelph, Ontario</t>
         </is>
       </c>
       <c r="I74" s="3" t="inlineStr">
@@ -7449,22 +7449,22 @@
       </c>
       <c r="L74" s="4" t="inlineStr">
         <is>
-          <t>Seeking an Assistant Professor of Mechanical Engineering requiring a Ph.D. in mechanical engineering or closely related field. | Research Topics: Mechanical Engineering, Thermal-Fluids, Mechanics</t>
+          <t>Assistant or Associate Professor in Supply Chain Management requiring a Ph.D. in supply chain or a related business field. | Research Topics: Supply Chain Management, Logistics, Operations Management</t>
         </is>
       </c>
       <c r="M74" s="5" t="inlineStr">
         <is>
-          <t>https://engineering.academickeys.com/job/ruoe4wlz/Assistant-Professor-of-Mechanical-Engineering</t>
+          <t>https://ca.linkedin.com/jobs/view/assistant-or-associate-professor-in-supply-chain-management-at-university-of-guelph-4397076267</t>
         </is>
       </c>
       <c r="N74" s="3" t="inlineStr">
         <is>
-          <t>AcademicKeys</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -7478,31 +7478,31 @@
         </is>
       </c>
       <c r="R74" s="2" t="n">
-        <v>45.6639222</v>
+        <v>43.5327864</v>
       </c>
       <c r="S74" s="2" t="n">
-        <v>-111.079277</v>
+        <v>-80.22499740000001</v>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>735f106baf0ccc18</t>
+          <t>e9269b52adecc4bd</t>
         </is>
       </c>
     </row>
     <row r="75" ht="26" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Economics - Urban/Regional Spatial Data Analysis</t>
+          <t>Full/Associate/Assistant Professor in Computer Science</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>San José State University</t>
+          <t>University of Macau</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Department of Economics</t>
+          <t>Department of Computer Science</t>
         </is>
       </c>
       <c r="D75" s="3" t="n">
@@ -7510,12 +7510,12 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>Although the role involves spatial data analysis which intersects with mobility, it is based in an Economics department focusing on urban and regional economics rather than transportation engineering.</t>
+          <t>Open rank faculty position in Computer Science, which shares methodological overlap with data science for mobility but lacks a direct transportation focus.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Urban Economics, Spatial Data Analysis, Regional Economics</t>
+          <t>Computer Science, Algorithms, Data Systems</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>Macao</t>
         </is>
       </c>
       <c r="I75" s="3" t="inlineStr">
@@ -7536,27 +7536,27 @@
       <c r="J75" s="3" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>£87,465.51 to £127,834.20</t>
         </is>
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
-          <t>Tenure-track assistant professor in economics specializing in urban and regional spatial data analysis requiring a Ph.D. | Research Topics: Urban Economics, Spatial Data Analysis, Regional Economics</t>
+          <t>Open rank faculty position in computer science requiring a Ph.D. and a strong research record. | Research Topics: Computer Science, Algorithms, Data Systems</t>
         </is>
       </c>
       <c r="M75" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-of-economics-urban-regional-spatial-data-analysis-at-san-jos%C3%A9-state-university-4454304392</t>
+          <t>https://www.jobs.ac.uk/job/DSP580/full-associate-assistant-professor-in-computer-science</t>
         </is>
       </c>
       <c r="N75" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Jobs.ac.uk</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -7570,31 +7570,31 @@
         </is>
       </c>
       <c r="R75" s="2" t="n">
-        <v>37.3351902</v>
+        <v>22.1285</v>
       </c>
       <c r="S75" s="2" t="n">
-        <v>-121.881225</v>
+        <v>113.5438</v>
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>8f931a7dcebc3de3</t>
+          <t>af1fdedb3a4712b5</t>
         </is>
       </c>
     </row>
     <row r="76" ht="26" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Assistant or Associate Professor in Management – Operations and Supply Chain Management</t>
+          <t>Assistant Professor of Business Analytics</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>The American College of Greece</t>
+          <t>University of Puget Sound</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Alba Graduate Business School</t>
+          <t>School of Business / Business Analytics</t>
         </is>
       </c>
       <c r="D76" s="3" t="n">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>While operations and supply chain management has methodological overlaps with logistics, the focus is within a business school rather than a transportation engineering or urban planning department.</t>
+          <t>While business analytics shares data science methods with mobility, this general business analytics position lacks a specific transportation or mobility focus.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Operations Management, Supply Chain Management, Business Analytics</t>
+          <t>Business Analytics, Data Science, Quantitative Methods</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
@@ -7617,7 +7617,7 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Athens, Greece</t>
+          <t>Tacoma, Washington, US</t>
         </is>
       </c>
       <c r="I76" s="3" t="inlineStr">
@@ -7628,22 +7628,22 @@
       <c r="J76" s="3" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Commensurate with education and experience</t>
         </is>
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
-          <t>Faculty position in operations and supply chain management at a graduate business school requiring a Ph.D. in a related field. | Research Topics: Operations Management, Supply Chain Management, Business Analytics</t>
+          <t>An assistant professor position in business analytics requiring a Ph.D. in business analytics, operations research, or a related field. | Research Topics: Business Analytics, Data Science, Quantitative Methods</t>
         </is>
       </c>
       <c r="M76" s="5" t="inlineStr">
         <is>
-          <t>https://gr.linkedin.com/jobs/view/assistant-or-associate-professor-in-management-%E2%80%93-operations-and-supply-chain-management-at-the-american-college-of-greece-4471999873</t>
+          <t>https://jobs.chronicle.com/job/38033792/assistant-professor-of-business-analytics/</t>
         </is>
       </c>
       <c r="N76" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
@@ -7662,31 +7662,31 @@
         </is>
       </c>
       <c r="R76" s="2" t="n">
-        <v>38.003282</v>
+        <v>47.261437</v>
       </c>
       <c r="S76" s="2" t="n">
-        <v>23.8317208</v>
+        <v>-122.4809573</v>
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>154bc2d385933c45</t>
+          <t>61114277d3d1d45d</t>
         </is>
       </c>
     </row>
     <row r="77" ht="26" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Assistant or Associate Professor in Supply Chain Management</t>
+          <t>Assistant Professor in Applied Mathematics</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>University of Guelph</t>
+          <t>Utrecht University</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Gordon S. Lang School of Business and Economics</t>
+          <t>Mathematical Institute</t>
         </is>
       </c>
       <c r="D77" s="3" t="n">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>This is a supply chain management faculty position within a business school, offering only slight peripheral overlap with logistics.</t>
+          <t>This is an assistant professor position in applied mathematics which lacks a direct connection to transportation engineering or mobility research.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Management, Logistics, Operations Management</t>
+          <t>Applied Mathematics, Mathematical Modeling, Education</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Guelph, Ontario</t>
+          <t>Utrecht, Netherlands</t>
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr">
@@ -7725,12 +7725,12 @@
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
-          <t>Assistant or Associate Professor in Supply Chain Management requiring a Ph.D. in supply chain or a related business field. | Research Topics: Supply Chain Management, Logistics, Operations Management</t>
+          <t>An assistant professor role in applied mathematics dedicated to research and teaching within the Mathematical Institute. | Research Topics: Applied Mathematics, Mathematical Modeling, Education</t>
         </is>
       </c>
       <c r="M77" s="5" t="inlineStr">
         <is>
-          <t>https://ca.linkedin.com/jobs/view/assistant-or-associate-professor-in-supply-chain-management-at-university-of-guelph-4397076267</t>
+          <t>https://nl.linkedin.com/jobs/view/assistant-professor-in-applied-mathematics-at-utrecht-university-4471740837</t>
         </is>
       </c>
       <c r="N77" s="3" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -7754,31 +7754,31 @@
         </is>
       </c>
       <c r="R77" s="2" t="n">
-        <v>43.5327864</v>
+        <v>52.0942343</v>
       </c>
       <c r="S77" s="2" t="n">
-        <v>-80.22499740000001</v>
+        <v>5.1211881</v>
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>e9269b52adecc4bd</t>
+          <t>a114cd232ce97052</t>
         </is>
       </c>
     </row>
     <row r="78" ht="26" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Full/Associate/Assistant Professor in Computer Science</t>
+          <t>Faculty Openings</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>University of Macau</t>
+          <t>Worcester State University</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Department of Computer Science</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="D78" s="3" t="n">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>Open rank faculty position in Computer Science, which shares methodological overlap with data science for mobility but lacks a direct transportation focus.</t>
+          <t>This is a pooled general faculty opening announcement without a specified discipline or department.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Computer Science, Algorithms, Data Systems</t>
+          <t>Higher Education, General Teaching</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Macao</t>
+          <t>Worcester, Massachusetts</t>
         </is>
       </c>
       <c r="I78" s="3" t="inlineStr">
@@ -7812,27 +7812,27 @@
       <c r="J78" s="3" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>£87,465.51 to £127,834.20</t>
+          <t>Competitive</t>
         </is>
       </c>
       <c r="L78" s="4" t="inlineStr">
         <is>
-          <t>Open rank faculty position in computer science requiring a Ph.D. and a strong research record. | Research Topics: Computer Science, Algorithms, Data Systems</t>
+          <t>General faculty openings at Worcester State University across unspecified departments. | Research Topics: Higher Education, General Teaching</t>
         </is>
       </c>
       <c r="M78" s="5" t="inlineStr">
         <is>
-          <t>https://www.jobs.ac.uk/job/DSP580/full-associate-assistant-professor-in-computer-science</t>
+          <t>https://jobs.chronicle.com/job/38031758/faculty-openings/?LinkSource=PromotedJob</t>
         </is>
       </c>
       <c r="N78" s="3" t="inlineStr">
         <is>
-          <t>Jobs.ac.uk</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -7846,54 +7846,54 @@
         </is>
       </c>
       <c r="R78" s="2" t="n">
-        <v>22.1285</v>
+        <v>42.2677195</v>
       </c>
       <c r="S78" s="2" t="n">
-        <v>113.5438</v>
+        <v>-71.8427016</v>
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>af1fdedb3a4712b5</t>
+          <t>0abc7f3ac357dd0f</t>
         </is>
       </c>
     </row>
     <row r="79" ht="26" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Business Analytics</t>
+          <t>Assistant Professor in Resilient Manufacturing Systems</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>University of Puget Sound</t>
+          <t>Aalborg University</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>School of Business / Business Analytics</t>
+          <t>Department of Materials and Production</t>
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>While business analytics shares data science methods with mobility, this general business analytics position lacks a specific transportation or mobility focus.</t>
+          <t>The role focuses on Resilient Manufacturing Systems within Industrial/Production Engineering, lacking a direct connection to transportation or mobility.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Business Analytics, Data Science, Quantitative Methods</t>
+          <t>Manufacturing Systems, Production Engineering, Data-Driven Production</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Non-Tenure Track</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>Tacoma, Washington, US</t>
+          <t>Aalborg, Denmark</t>
         </is>
       </c>
       <c r="I79" s="3" t="inlineStr">
@@ -7904,32 +7904,32 @@
       <c r="J79" s="3" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>Commensurate with education and experience</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
-          <t>An assistant professor position in business analytics requiring a Ph.D. in business analytics, operations research, or a related field. | Research Topics: Business Analytics, Data Science, Quantitative Methods</t>
+          <t>A 3-year fixed-term assistant professorship in resilient manufacturing systems requiring a relevant doctoral degree. | Research Topics: Manufacturing Systems, Production Engineering, Data-Driven Production</t>
         </is>
       </c>
       <c r="M79" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38033792/assistant-professor-of-business-analytics/</t>
+          <t>https://dk.linkedin.com/jobs/view/assistant-professor-in-resilient-manufacturing-systems-at-aalborg-university-4433319001</t>
         </is>
       </c>
       <c r="N79" s="3" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="Q79" s="6" t="inlineStr">
@@ -7938,44 +7938,44 @@
         </is>
       </c>
       <c r="R79" s="2" t="n">
-        <v>47.261437</v>
+        <v>57.0156429</v>
       </c>
       <c r="S79" s="2" t="n">
-        <v>-122.4809573</v>
+        <v>9.975296200000001</v>
       </c>
       <c r="T79" s="2" t="inlineStr">
         <is>
-          <t>61114277d3d1d45d</t>
+          <t>d6af8cfed15e21c1</t>
         </is>
       </c>
     </row>
     <row r="80" ht="26" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor in Applied Mathematics</t>
+          <t>Tenure-Track Assistant Professor of Statistics</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Utrecht University</t>
+          <t>Haverford College</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Mathematical Institute</t>
+          <t>Department of Statistics</t>
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>This is an assistant professor position in applied mathematics which lacks a direct connection to transportation engineering or mobility research.</t>
+          <t>Although statistics involves data analysis, the department is pure Statistics rather than transportation data science or civil engineering.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Applied Mathematics, Mathematical Modeling, Education</t>
+          <t>Statistics, Data Analysis, Probability</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Utrecht, Netherlands</t>
+          <t>Haverford, Pennsylvania</t>
         </is>
       </c>
       <c r="I80" s="3" t="inlineStr">
@@ -7996,32 +7996,32 @@
       <c r="J80" s="3" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Competitive Salary</t>
         </is>
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
-          <t>An assistant professor role in applied mathematics dedicated to research and teaching within the Mathematical Institute. | Research Topics: Applied Mathematics, Mathematical Modeling, Education</t>
+          <t>Seeking a tenure-track Assistant Professor of Statistics requiring a Ph.D. in statistics or a closely related quantitative field. | Research Topics: Statistics, Data Analysis, Probability</t>
         </is>
       </c>
       <c r="M80" s="5" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/assistant-professor-in-applied-mathematics-at-utrecht-university-4471740837</t>
+          <t>https://jobs.chronicle.com/job/38017766/tenure-track-assistant-professor-of-statistics/</t>
         </is>
       </c>
       <c r="N80" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q80" s="6" t="inlineStr">
@@ -8030,44 +8030,44 @@
         </is>
       </c>
       <c r="R80" s="2" t="n">
-        <v>52.0942343</v>
+        <v>40.0071506</v>
       </c>
       <c r="S80" s="2" t="n">
-        <v>5.1211881</v>
+        <v>-75.3069423</v>
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>a114cd232ce97052</t>
+          <t>139bc27f2f7867a0</t>
         </is>
       </c>
     </row>
     <row r="81" ht="26" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Faculty Openings</t>
+          <t>Assistant Professors in Business Administration</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Worcester State University</t>
+          <t>Jönköping University</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Jönköping International Business School</t>
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>This is a pooled general faculty opening announcement without a specified discipline or department.</t>
+          <t>The position is in general Business Administration rather than transportation or mobility systems, resulting in a low fit.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Higher Education, General Teaching</t>
+          <t>Business Administration, Management, Business Analytics</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
@@ -8077,7 +8077,7 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Worcester, Massachusetts</t>
+          <t>Jönköping</t>
         </is>
       </c>
       <c r="I81" s="3" t="inlineStr">
@@ -8088,22 +8088,22 @@
       <c r="J81" s="3" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>Competitive</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L81" s="4" t="inlineStr">
         <is>
-          <t>General faculty openings at Worcester State University across unspecified departments. | Research Topics: Higher Education, General Teaching</t>
+          <t>A tenure-track assistant professor position in business administration requiring a Ph.D. in a relevant discipline. | Research Topics: Business Administration, Management, Business Analytics</t>
         </is>
       </c>
       <c r="M81" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38031758/faculty-openings/?LinkSource=PromotedJob</t>
+          <t>https://se.linkedin.com/jobs/view/assistant-professors-in-business-administration-at-j%C3%B6nk%C3%B6ping-university-4473966498</t>
         </is>
       </c>
       <c r="N81" s="3" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
@@ -8122,31 +8122,31 @@
         </is>
       </c>
       <c r="R81" s="2" t="n">
-        <v>42.2677195</v>
+        <v>57.7780222</v>
       </c>
       <c r="S81" s="2" t="n">
-        <v>-71.8427016</v>
+        <v>14.162141</v>
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>0abc7f3ac357dd0f</t>
+          <t>e274767183b1b68d</t>
         </is>
       </c>
     </row>
     <row r="82" ht="26" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor in Resilient Manufacturing Systems</t>
+          <t>Assistant/Associate Professor in Mechanical and Aerospace Engineering</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Aalborg University</t>
+          <t>Missouri University of Science and Technology</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Department of Materials and Production</t>
+          <t>Department of Mechanical and Aerospace Engineering</t>
         </is>
       </c>
       <c r="D82" s="3" t="n">
@@ -8154,22 +8154,22 @@
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>The role focuses on Resilient Manufacturing Systems within Industrial/Production Engineering, lacking a direct connection to transportation or mobility.</t>
+          <t>The position is situated in Mechanical and Aerospace Engineering, which falls outside the candidate's core civil and urban transportation fields.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Manufacturing Systems, Production Engineering, Data-Driven Production</t>
+          <t>Mechanical Engineering, Aerospace Systems, Thermal-Fluids or Dynamics</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>Non-Tenure Track</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Aalborg, Denmark</t>
+          <t>Rolla, MO</t>
         </is>
       </c>
       <c r="I82" s="3" t="inlineStr">
@@ -8185,12 +8185,12 @@
       </c>
       <c r="L82" s="4" t="inlineStr">
         <is>
-          <t>A 3-year fixed-term assistant professorship in resilient manufacturing systems requiring a relevant doctoral degree. | Research Topics: Manufacturing Systems, Production Engineering, Data-Driven Production</t>
+          <t>This is an open rank faculty position in mechanical and aerospace engineering requiring a Ph.D. in a relevant discipline. | Research Topics: Mechanical Engineering, Aerospace Systems, Thermal-Fluids or Dynamics</t>
         </is>
       </c>
       <c r="M82" s="5" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/assistant-professor-in-resilient-manufacturing-systems-at-aalborg-university-4433319001</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-associate-professor-mechanical-and-aerospace-engineering-%2300098258-at-missouri-university-of-science-and-technology-4464936601</t>
         </is>
       </c>
       <c r="N82" s="3" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="Q82" s="6" t="inlineStr">
@@ -8214,31 +8214,31 @@
         </is>
       </c>
       <c r="R82" s="2" t="n">
-        <v>57.0156429</v>
+        <v>37.9532435</v>
       </c>
       <c r="S82" s="2" t="n">
-        <v>9.975296200000001</v>
+        <v>-91.7742667</v>
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
-          <t>d6af8cfed15e21c1</t>
+          <t>664e10f5664e3e49</t>
         </is>
       </c>
     </row>
     <row r="83" ht="26" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Tenure-Track Assistant Professor of Statistics</t>
+          <t>Assistant Professor, Logistics &amp; Supply Chain Management</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Haverford College</t>
+          <t>Murray State University</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Department of Statistics</t>
+          <t>Department of Management</t>
         </is>
       </c>
       <c r="D83" s="3" t="n">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>Although statistics involves data analysis, the department is pure Statistics rather than transportation data science or civil engineering.</t>
+          <t>Although the position involves teaching transportation and logistics, it strictly requires a Ph.D. or DBA from an AACSB-accredited Business School, which diverges from the candidate's engineering doctoral background.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>Statistics, Data Analysis, Probability</t>
+          <t>Transportation &amp; Logistics, Supply Chain Management, Operations Management</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Haverford, Pennsylvania</t>
+          <t>Murray, KY</t>
         </is>
       </c>
       <c r="I83" s="3" t="inlineStr">
@@ -8272,32 +8272,32 @@
       <c r="J83" s="3" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>Competitive Salary</t>
+          <t>$92,159 per year</t>
         </is>
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
-          <t>Seeking a tenure-track Assistant Professor of Statistics requiring a Ph.D. in statistics or a closely related quantitative field. | Research Topics: Statistics, Data Analysis, Probability</t>
+          <t>This tenure-track Assistant Professor position focuses on teaching and conducting research in transportation, logistics, and supply chain management, requiring a Ph.D. or DBA from an AACSB-accredited Business School. | Research Topics: Transportation &amp; Logistics, Supply Chain Management, Operations Management</t>
         </is>
       </c>
       <c r="M83" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38017766/tenure-track-assistant-professor-of-statistics/</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179569817&amp;Title=Assistant%20Professor%2C%20Logistics%20%26amp%3B%20Supply%20Chain%20Management</t>
         </is>
       </c>
       <c r="N83" s="3" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Q83" s="6" t="inlineStr">
@@ -8306,31 +8306,31 @@
         </is>
       </c>
       <c r="R83" s="2" t="n">
-        <v>40.0071506</v>
+        <v>36.6129699</v>
       </c>
       <c r="S83" s="2" t="n">
-        <v>-75.3069423</v>
+        <v>-88.32208799999999</v>
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>139bc27f2f7867a0</t>
+          <t>324d2886190ffbc0</t>
         </is>
       </c>
     </row>
     <row r="84" ht="26" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professors in Business Administration</t>
+          <t>Assistant / Associate Professor (Tenure-Track) in Maritime Studies</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Jönköping University</t>
+          <t>Nanyang Technological University</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Jönköping International Business School</t>
+          <t>School of Civil and Environmental Engineering</t>
         </is>
       </c>
       <c r="D84" s="3" t="n">
@@ -8338,12 +8338,12 @@
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>The position is in general Business Administration rather than transportation or mobility systems, resulting in a low fit.</t>
+          <t>Although housed within Civil and Environmental Engineering, this position specifically focuses on maritime studies, shipping decarbonization, and port operations, which diverges from the candidate's core expertise in urban passenger transportation and travel behavior modeling.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>Business Administration, Management, Business Analytics</t>
+          <t>Sustainable Shipping &amp; Decarbonization, Port Operations &amp; Logistics, Maritime Economics &amp; Digitalisation, Supply Chain Resilience</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>Jönköping</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="I84" s="3" t="inlineStr">
@@ -8364,27 +8364,27 @@
       <c r="J84" s="3" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Highly competitive</t>
         </is>
       </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
-          <t>A tenure-track assistant professor position in business administration requiring a Ph.D. in a relevant discipline. | Research Topics: Business Administration, Management, Business Analytics</t>
+          <t>Nanyang Technological University invites applications for tenure-track faculty positions across all ranks in Maritime Studies within the School of Civil and Environmental Engineering, requiring a Ph.D. in Maritime Studies or a closely related field. | Research Topics: Sustainable Shipping &amp; Decarbonization, Port Operations &amp; Logistics, Maritime Economics &amp; Digitalisation, Supply Chain Resilience</t>
         </is>
       </c>
       <c r="M84" s="5" t="inlineStr">
         <is>
-          <t>https://se.linkedin.com/jobs/view/assistant-professors-in-business-administration-at-j%C3%B6nk%C3%B6ping-university-4473966498</t>
+          <t>https://engineering.academickeys.com/job/m80x7utf/Assistant-Professor--Associate-Professor-TenureTrack-Associate-Professor-PracticeTrack-in-Maritime-Studies</t>
         </is>
       </c>
       <c r="N84" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>AcademicKeys</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -8398,31 +8398,31 @@
         </is>
       </c>
       <c r="R84" s="2" t="n">
-        <v>57.7780222</v>
+        <v>1.3483</v>
       </c>
       <c r="S84" s="2" t="n">
-        <v>14.162141</v>
+        <v>103.6831</v>
       </c>
       <c r="T84" s="2" t="inlineStr">
         <is>
-          <t>e274767183b1b68d</t>
+          <t>6736da1a934c5c83</t>
         </is>
       </c>
     </row>
     <row r="85" ht="26" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Assistant/Associate Professor in Mechanical and Aerospace Engineering</t>
+          <t>Assistant, Associate, or Full Professor of Mechanical and Industrial Engineering</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Missouri University of Science and Technology</t>
+          <t>Northeastern University</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Department of Mechanical and Aerospace Engineering</t>
+          <t>Department of Mechanical and Industrial Engineering</t>
         </is>
       </c>
       <c r="D85" s="3" t="n">
@@ -8430,22 +8430,22 @@
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>The position is situated in Mechanical and Aerospace Engineering, which falls outside the candidate's core civil and urban transportation fields.</t>
+          <t>The position is in Mechanical and Industrial Engineering without a stated focus on transportation engineering, making it a poor fit for the candidate's core profile.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>Mechanical Engineering, Aerospace Systems, Thermal-Fluids or Dynamics</t>
+          <t>Mechanical Engineering, Industrial Engineering</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Unspecified</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>Rolla, MO</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="I85" s="3" t="inlineStr">
@@ -8456,32 +8456,32 @@
       <c r="J85" s="3" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>$101,000 - $215,000 per year</t>
         </is>
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
-          <t>This is an open rank faculty position in mechanical and aerospace engineering requiring a Ph.D. in a relevant discipline. | Research Topics: Mechanical Engineering, Aerospace Systems, Thermal-Fluids or Dynamics</t>
+          <t>Open-rank faculty position in mechanical and industrial engineering focusing on general department research areas. | Research Topics: Mechanical Engineering, Industrial Engineering</t>
         </is>
       </c>
       <c r="M85" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-associate-professor-mechanical-and-aerospace-engineering-%2300098258-at-missouri-university-of-science-and-technology-4464936601</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179560354&amp;Title=Assistant%2C%20Associate%2C%20Full%20Professor%20%2D%20College%20of%20Engineering%20%2D%20Mechanical%20and%20Industrial%20Engineering%20%2D%20Boston</t>
         </is>
       </c>
       <c r="N85" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Q85" s="6" t="inlineStr">
@@ -8490,31 +8490,31 @@
         </is>
       </c>
       <c r="R85" s="2" t="n">
-        <v>37.9532435</v>
+        <v>42.3351065</v>
       </c>
       <c r="S85" s="2" t="n">
-        <v>-91.7742667</v>
+        <v>-71.0892575</v>
       </c>
       <c r="T85" s="2" t="inlineStr">
         <is>
-          <t>664e10f5664e3e49</t>
+          <t>e1042bf3b6aa8057</t>
         </is>
       </c>
     </row>
     <row r="86" ht="26" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor, Logistics &amp; Supply Chain Management</t>
+          <t>Assistant Professor - Mechatronics and Mechanical Engineering</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Murray State University</t>
+          <t>Ontario Tech University</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Department of Management</t>
+          <t>Faculty of Engineering and Applied Science</t>
         </is>
       </c>
       <c r="D86" s="3" t="n">
@@ -8522,12 +8522,12 @@
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>Although the position involves teaching transportation and logistics, it strictly requires a Ph.D. or DBA from an AACSB-accredited Business School, which diverges from the candidate's engineering doctoral background.</t>
+          <t>The role is focused on mechatronics and mechanical engineering, which lacks a direct connection to transportation planning and mobility systems.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>Transportation &amp; Logistics, Supply Chain Management, Operations Management</t>
+          <t>Mechatronics, Mechanical Engineering, Robotics</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
@@ -8537,7 +8537,7 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Murray, KY</t>
+          <t>Oshawa, Ontario, Canada</t>
         </is>
       </c>
       <c r="I86" s="3" t="inlineStr">
@@ -8548,27 +8548,27 @@
       <c r="J86" s="3" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>$92,159 per year</t>
+          <t>Hiring Range not specified</t>
         </is>
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
-          <t>This tenure-track Assistant Professor position focuses on teaching and conducting research in transportation, logistics, and supply chain management, requiring a Ph.D. or DBA from an AACSB-accredited Business School. | Research Topics: Transportation &amp; Logistics, Supply Chain Management, Operations Management</t>
+          <t>This is a full-time tenure-track assistant professor position in mechatronics and mechanical engineering requiring a Ph.D. | Research Topics: Mechatronics, Mechanical Engineering, Robotics</t>
         </is>
       </c>
       <c r="M86" s="5" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179569817&amp;Title=Assistant%20Professor%2C%20Logistics%20%26amp%3B%20Supply%20Chain%20Management</t>
+          <t>https://ca.linkedin.com/jobs/view/assistant-professor-mechatronics-and-mechanical-engineering-at-ontario-tech-university-4466293036</t>
         </is>
       </c>
       <c r="N86" s="3" t="inlineStr">
         <is>
-          <t>HigherEdJobs</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -8582,31 +8582,31 @@
         </is>
       </c>
       <c r="R86" s="2" t="n">
-        <v>36.6129699</v>
+        <v>43.9483414</v>
       </c>
       <c r="S86" s="2" t="n">
-        <v>-88.32208799999999</v>
+        <v>-78.8982025</v>
       </c>
       <c r="T86" s="2" t="inlineStr">
         <is>
-          <t>324d2886190ffbc0</t>
+          <t>388fabc48392f309</t>
         </is>
       </c>
     </row>
     <row r="87" ht="26" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Assistant / Associate Professor (Tenure-Track) in Maritime Studies</t>
+          <t>Tenure-Track Assistant Professor of Mathematics</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Nanyang Technological University</t>
+          <t>Rutgers University</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>School of Civil and Environmental Engineering</t>
+          <t>Department of Mathematics</t>
         </is>
       </c>
       <c r="D87" s="3" t="n">
@@ -8614,12 +8614,12 @@
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>Although housed within Civil and Environmental Engineering, this position specifically focuses on maritime studies, shipping decarbonization, and port operations, which diverges from the candidate's core expertise in urban passenger transportation and travel behavior modeling.</t>
+          <t>Despite being hosted via Rutgers Transportation Services, the actual department hiring is Mathematics, which focuses on pure/applied math rather than transportation engineering.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Sustainable Shipping &amp; Decarbonization, Port Operations &amp; Logistics, Maritime Economics &amp; Digitalisation, Supply Chain Resilience</t>
+          <t>Mathematics, Applied Mathematics, Mathematical Modeling</t>
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr">
@@ -8629,7 +8629,7 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Piscataway, NJ</t>
         </is>
       </c>
       <c r="I87" s="3" t="inlineStr">
@@ -8640,22 +8640,22 @@
       <c r="J87" s="3" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Minimum $80,000</t>
         </is>
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
-          <t>Nanyang Technological University invites applications for tenure-track faculty positions across all ranks in Maritime Studies within the School of Civil and Environmental Engineering, requiring a Ph.D. in Maritime Studies or a closely related field. | Research Topics: Sustainable Shipping &amp; Decarbonization, Port Operations &amp; Logistics, Maritime Economics &amp; Digitalisation, Supply Chain Resilience</t>
+          <t>This is a tenure-track assistant professor position in the Department of Mathematics requiring a Ph.D. in mathematics or related fields. | Research Topics: Mathematics, Applied Mathematics, Mathematical Modeling</t>
         </is>
       </c>
       <c r="M87" s="5" t="inlineStr">
         <is>
-          <t>https://engineering.academickeys.com/job/m80x7utf/Assistant-Professor--Associate-Professor-TenureTrack-Associate-Professor-PracticeTrack-in-Maritime-Studies</t>
+          <t>https://www.linkedin.com/jobs/view/tenure-track-assistant-professor-of-mathematics-at-rutgers-transportation-services-4473983685</t>
         </is>
       </c>
       <c r="N87" s="3" t="inlineStr">
         <is>
-          <t>AcademicKeys</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
@@ -8674,31 +8674,31 @@
         </is>
       </c>
       <c r="R87" s="2" t="n">
-        <v>1.3483</v>
+        <v>40.5464326</v>
       </c>
       <c r="S87" s="2" t="n">
-        <v>103.6831</v>
+        <v>-74.4660542</v>
       </c>
       <c r="T87" s="2" t="inlineStr">
         <is>
-          <t>6736da1a934c5c83</t>
+          <t>c70af85c923c3087</t>
         </is>
       </c>
     </row>
     <row r="88" ht="26" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Assistant, Associate, or Full Professor of Mechanical and Industrial Engineering</t>
+          <t>Assistant Professor of Civil, Construction, and Environmental Engineering</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>San Diego State University</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Department of Mechanical and Industrial Engineering</t>
+          <t>Department of Civil, Construction and Environmental Engineering</t>
         </is>
       </c>
       <c r="D88" s="3" t="n">
@@ -8706,22 +8706,22 @@
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>The position is in Mechanical and Industrial Engineering without a stated focus on transportation engineering, making it a poor fit for the candidate's core profile.</t>
+          <t>While housed in Civil Engineering, this position specifically targets construction planning rather than transportation engineering or mobility systems.</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Mechanical Engineering, Industrial Engineering</t>
+          <t>Construction Planning, Construction Execution, Civil Engineering</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>San Diego, CA</t>
         </is>
       </c>
       <c r="I88" s="3" t="inlineStr">
@@ -8732,32 +8732,32 @@
       <c r="J88" s="3" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>$101,000 - $215,000 per year</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
-          <t>Open-rank faculty position in mechanical and industrial engineering focusing on general department research areas. | Research Topics: Mechanical Engineering, Industrial Engineering</t>
+          <t>Tenure-track assistant professor position in civil and construction engineering requiring a Ph.D. | Research Topics: Construction Planning, Construction Execution, Civil Engineering</t>
         </is>
       </c>
       <c r="M88" s="5" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179560354&amp;Title=Assistant%2C%20Associate%2C%20Full%20Professor%20%2D%20College%20of%20Engineering%20%2D%20Mechanical%20and%20Industrial%20Engineering%20%2D%20Boston</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-of-civil-construction-and-environmental-engineering-at-san-diego-state-university-4472340763</t>
         </is>
       </c>
       <c r="N88" s="3" t="inlineStr">
         <is>
-          <t>HigherEdJobs</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Q88" s="6" t="inlineStr">
@@ -8766,31 +8766,31 @@
         </is>
       </c>
       <c r="R88" s="2" t="n">
-        <v>42.3351065</v>
+        <v>32.7761529</v>
       </c>
       <c r="S88" s="2" t="n">
-        <v>-71.0892575</v>
+        <v>-117.0733037</v>
       </c>
       <c r="T88" s="2" t="inlineStr">
         <is>
-          <t>e1042bf3b6aa8057</t>
+          <t>8e10bc68b4d8034a</t>
         </is>
       </c>
     </row>
     <row r="89" ht="26" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor - Mechatronics and Mechanical Engineering</t>
+          <t>Faculty Openings in Engineering (Open Rank)</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Ontario Tech University</t>
+          <t>Singapore Institute of Technology</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Faculty of Engineering and Applied Science</t>
+          <t>Engineering Cluster</t>
         </is>
       </c>
       <c r="D89" s="3" t="n">
@@ -8798,22 +8798,22 @@
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>The role is focused on mechatronics and mechanical engineering, which lacks a direct connection to transportation planning and mobility systems.</t>
+          <t>While open rank and located in target Singapore, the engineering openings focus on construction materials, tunneling, infrastructure asset maintenance, and power systems rather than transportation planning or travel demand modeling.</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>Mechatronics, Mechanical Engineering, Robotics</t>
+          <t>Transport Infrastructure Asset Management, Tunnel Engineering, Construction Technologies, Power and Systems Engineering</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Unspecified</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>Oshawa, Ontario, Canada</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="I89" s="3" t="inlineStr">
@@ -8824,17 +8824,17 @@
       <c r="J89" s="3" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>Hiring Range not specified</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
-          <t>This is a full-time tenure-track assistant professor position in mechatronics and mechanical engineering requiring a Ph.D. | Research Topics: Mechatronics, Mechanical Engineering, Robotics</t>
+          <t>Singapore Institute of Technology is seeking faculty at all ranks across civil, electrical, mechanical, and systems engineering disciplines to support applied learning and translational industry research. | Research Topics: Transport Infrastructure Asset Management, Tunnel Engineering, Construction Technologies, Power and Systems Engineering</t>
         </is>
       </c>
       <c r="M89" s="5" t="inlineStr">
         <is>
-          <t>https://ca.linkedin.com/jobs/view/assistant-professor-mechatronics-and-mechanical-engineering-at-ontario-tech-university-4466293036</t>
+          <t>https://sg.linkedin.com/jobs/view/faculty-openings-in-engineering-at-singapore-institute-of-technology-4273859333</t>
         </is>
       </c>
       <c r="N89" s="3" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="Q89" s="6" t="inlineStr">
@@ -8858,31 +8858,31 @@
         </is>
       </c>
       <c r="R89" s="2" t="n">
-        <v>43.9483414</v>
+        <v>1.4123197</v>
       </c>
       <c r="S89" s="2" t="n">
-        <v>-78.8982025</v>
+        <v>103.9094621</v>
       </c>
       <c r="T89" s="2" t="inlineStr">
         <is>
-          <t>388fabc48392f309</t>
+          <t>f21dc0b6a181929c</t>
         </is>
       </c>
     </row>
     <row r="90" ht="26" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Tenure-Track Assistant Professor of Mathematics</t>
+          <t>Professor / Associate Professor / Assistant Professor</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Rutgers University</t>
+          <t>The Hong Kong University of Science and Technology</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Department of Mathematics</t>
+          <t>Department of Mechanical and Aerospace Engineering</t>
         </is>
       </c>
       <c r="D90" s="3" t="n">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>Despite being hosted via Rutgers Transportation Services, the actual department hiring is Mathematics, which focuses on pure/applied math rather than transportation engineering.</t>
+          <t>The role is in Mechanical and Aerospace Engineering, which falls outside the candidate's core transportation engineering and planning focus.</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Mathematics, Applied Mathematics, Mathematical Modeling</t>
+          <t>Mechanical Engineering, Aerospace Engineering</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
@@ -8905,7 +8905,7 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>Piscataway, NJ</t>
+          <t>Sai Kung District</t>
         </is>
       </c>
       <c r="I90" s="3" t="inlineStr">
@@ -8916,17 +8916,17 @@
       <c r="J90" s="3" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>Minimum $80,000</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
-          <t>This is a tenure-track assistant professor position in the Department of Mathematics requiring a Ph.D. in mathematics or related fields. | Research Topics: Mathematics, Applied Mathematics, Mathematical Modeling</t>
+          <t>This open-rank faculty position requires a Ph.D. in mechanical or aerospace engineering and an active research program in those fields. | Research Topics: Mechanical Engineering, Aerospace Engineering</t>
         </is>
       </c>
       <c r="M90" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/tenure-track-assistant-professor-of-mathematics-at-rutgers-transportation-services-4473983685</t>
+          <t>https://hk.linkedin.com/jobs/view/professor-associate-professor-assistant-professor-department-of-mechanical-and-aerospace-engineering-at-the-hong-kong-university-of-science-and-technology-4468352480</t>
         </is>
       </c>
       <c r="N90" s="3" t="inlineStr">
@@ -8936,12 +8936,12 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="Q90" s="6" t="inlineStr">
@@ -8950,31 +8950,31 @@
         </is>
       </c>
       <c r="R90" s="2" t="n">
-        <v>40.5464326</v>
+        <v>22.3360784</v>
       </c>
       <c r="S90" s="2" t="n">
-        <v>-74.4660542</v>
+        <v>114.2656774</v>
       </c>
       <c r="T90" s="2" t="inlineStr">
         <is>
-          <t>c70af85c923c3087</t>
+          <t>81c18021918cca1c</t>
         </is>
       </c>
     </row>
     <row r="91" ht="26" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Civil, Construction, and Environmental Engineering</t>
+          <t>Assistant Professor in International Development (Quantitative Social Science)</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>San Diego State University</t>
+          <t>The London School of Economics and Political Science (LSE)</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Department of Civil, Construction and Environmental Engineering</t>
+          <t>Department of International Development</t>
         </is>
       </c>
       <c r="D91" s="3" t="n">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>While housed in Civil Engineering, this position specifically targets construction planning rather than transportation engineering or mobility systems.</t>
+          <t>The position is in international development and quantitative social science, lacking direct alignment with transportation or mobility engineering.</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>Construction Planning, Construction Execution, Civil Engineering</t>
+          <t>International Development, Quantitative Social Science, Data Analysis</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
@@ -8997,7 +8997,7 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>San Diego, CA</t>
+          <t>London, United Kingdom</t>
         </is>
       </c>
       <c r="I91" s="3" t="inlineStr">
@@ -9013,12 +9013,12 @@
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
-          <t>Tenure-track assistant professor position in civil and construction engineering requiring a Ph.D. | Research Topics: Construction Planning, Construction Execution, Civil Engineering</t>
+          <t>Tenure-track Assistant Professor role focusing on international development and quantitative methods requiring a Ph.D. | Research Topics: International Development, Quantitative Social Science, Data Analysis</t>
         </is>
       </c>
       <c r="M91" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-of-civil-construction-and-environmental-engineering-at-san-diego-state-university-4472340763</t>
+          <t>https://uk.linkedin.com/jobs/view/assistant-professor-in-international-development-quantitative-social-science-at-the-london-school-of-economics-and-political-science-lse-4461566153</t>
         </is>
       </c>
       <c r="N91" s="3" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -9042,31 +9042,31 @@
         </is>
       </c>
       <c r="R91" s="2" t="n">
-        <v>32.7761529</v>
+        <v>51.5074456</v>
       </c>
       <c r="S91" s="2" t="n">
-        <v>-117.0733037</v>
+        <v>-0.1277653</v>
       </c>
       <c r="T91" s="2" t="inlineStr">
         <is>
-          <t>8e10bc68b4d8034a</t>
+          <t>69e89c6a307e9a14</t>
         </is>
       </c>
     </row>
     <row r="92" ht="26" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Faculty Openings in Engineering (Open Rank)</t>
+          <t>Assistant/Associate/Full Professor in Industrial and Systems Engineering</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Singapore Institute of Technology</t>
+          <t>University of Florida</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Engineering Cluster</t>
+          <t>Department of Industrial and Systems Engineering</t>
         </is>
       </c>
       <c r="D92" s="3" t="n">
@@ -9074,22 +9074,22 @@
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>While open rank and located in target Singapore, the engineering openings focus on construction materials, tunneling, infrastructure asset maintenance, and power systems rather than transportation planning or travel demand modeling.</t>
+          <t>Although transportation is mentioned as a potential application area, the primary focus of this Industrial and Systems Engineering position is on Industrialized Construction and 3D construction printing rather than core transportation engineering, mobility, or travel behavior.</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Transport Infrastructure Asset Management, Tunnel Engineering, Construction Technologies, Power and Systems Engineering</t>
+          <t>Industrialized Construction, Artificial Intelligence, Digital Twins, Operations Research</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Gainesville, FL</t>
         </is>
       </c>
       <c r="I92" s="3" t="inlineStr">
@@ -9100,17 +9100,17 @@
       <c r="J92" s="3" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Salary is commensurate with education and experience.</t>
         </is>
       </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
-          <t>Singapore Institute of Technology is seeking faculty at all ranks across civil, electrical, mechanical, and systems engineering disciplines to support applied learning and translational industry research. | Research Topics: Transport Infrastructure Asset Management, Tunnel Engineering, Construction Technologies, Power and Systems Engineering</t>
+          <t>This full-time tenured or tenure-track faculty position in Industrial and Systems Engineering at the University of Florida seeks expertise in industrialized construction and related technologies, requiring a Ph.D. in ISE, Manufacturing Engineering, Civil Engineering, Mechanical Engineering, or a closely related field. | Research Topics: Industrialized Construction, Artificial Intelligence, Digital Twins, Operations Research</t>
         </is>
       </c>
       <c r="M92" s="5" t="inlineStr">
         <is>
-          <t>https://sg.linkedin.com/jobs/view/faculty-openings-in-engineering-at-singapore-institute-of-technology-4273859333</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-associate-full-professor-industrial-systems-engineering-at-university-of-florida-4323668785</t>
         </is>
       </c>
       <c r="N92" s="3" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="Q92" s="6" t="inlineStr">
@@ -9134,31 +9134,31 @@
         </is>
       </c>
       <c r="R92" s="2" t="n">
-        <v>1.4123197</v>
+        <v>29.6436</v>
       </c>
       <c r="S92" s="2" t="n">
-        <v>103.9094621</v>
+        <v>-82.3549</v>
       </c>
       <c r="T92" s="2" t="inlineStr">
         <is>
-          <t>f21dc0b6a181929c</t>
+          <t>56d501f448e77e05</t>
         </is>
       </c>
     </row>
     <row r="93" ht="26" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Professor / Associate Professor / Assistant Professor</t>
+          <t>Assistant Professor (Tenure Track) – Biostatistics and Health Data Science</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>The Hong Kong University of Science and Technology</t>
+          <t>University of Minnesota</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Department of Mechanical and Aerospace Engineering</t>
+          <t>Division of Biostatistics and Health Data Science</t>
         </is>
       </c>
       <c r="D93" s="3" t="n">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>The role is in Mechanical and Aerospace Engineering, which falls outside the candidate's core transportation engineering and planning focus.</t>
+          <t>Although it involves data science, the focus is strictly on biostatistics and health data science rather than mobility data science.</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>Mechanical Engineering, Aerospace Engineering</t>
+          <t>Biostatistics, Health Data Science, Statistical Modeling</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
@@ -9181,7 +9181,7 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>Sai Kung District</t>
+          <t>Minneapolis, Minnesota</t>
         </is>
       </c>
       <c r="I93" s="3" t="inlineStr">
@@ -9192,32 +9192,32 @@
       <c r="J93" s="3" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Competitive Salary</t>
         </is>
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
-          <t>This open-rank faculty position requires a Ph.D. in mechanical or aerospace engineering and an active research program in those fields. | Research Topics: Mechanical Engineering, Aerospace Engineering</t>
+          <t>Tenure-track Assistant Professor position in biostatistics and health data science requiring a Ph.D. in statistics, biostatistics, or a related field. | Research Topics: Biostatistics, Health Data Science, Statistical Modeling</t>
         </is>
       </c>
       <c r="M93" s="5" t="inlineStr">
         <is>
-          <t>https://hk.linkedin.com/jobs/view/professor-associate-professor-assistant-professor-department-of-mechanical-and-aerospace-engineering-at-the-hong-kong-university-of-science-and-technology-4468352480</t>
+          <t>https://jobs.chronicle.com/job/38039489/assistant-professor-tenure-track-biostatistics-and-health-data-science/</t>
         </is>
       </c>
       <c r="N93" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Q93" s="6" t="inlineStr">
@@ -9226,31 +9226,31 @@
         </is>
       </c>
       <c r="R93" s="2" t="n">
-        <v>22.3360784</v>
+        <v>44.9863418</v>
       </c>
       <c r="S93" s="2" t="n">
-        <v>114.2656774</v>
+        <v>-93.1794451</v>
       </c>
       <c r="T93" s="2" t="inlineStr">
         <is>
-          <t>81c18021918cca1c</t>
+          <t>054f4f887d098cfa</t>
         </is>
       </c>
     </row>
     <row r="94" ht="26" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor in International Development (Quantitative Social Science)</t>
+          <t>Lee Assistant/Associate Professor of Economics, Real Estate and Urban Economics</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>The London School of Economics and Political Science (LSE)</t>
+          <t>University of Nevada-Las Vegas</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Department of International Development</t>
+          <t>Department of Economics</t>
         </is>
       </c>
       <c r="D94" s="3" t="n">
@@ -9258,12 +9258,12 @@
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>The position is in international development and quantitative social science, lacking direct alignment with transportation or mobility engineering.</t>
+          <t>The position is within Economics and Real Estate, lacking sufficient overlap with transportation engineering or mobility analytics.</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>International Development, Quantitative Social Science, Data Analysis</t>
+          <t>Economics, Real Estate, Urban Economics</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
@@ -9273,7 +9273,7 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>London, United Kingdom</t>
+          <t>Las Vegas, NV</t>
         </is>
       </c>
       <c r="I94" s="3" t="inlineStr">
@@ -9289,12 +9289,12 @@
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
-          <t>Tenure-track Assistant Professor role focusing on international development and quantitative methods requiring a Ph.D. | Research Topics: International Development, Quantitative Social Science, Data Analysis</t>
+          <t>Tenure-track assistant or associate professor position specializing in economics, real estate, and urban economics requiring a Ph.D. | Research Topics: Economics, Real Estate, Urban Economics</t>
         </is>
       </c>
       <c r="M94" s="5" t="inlineStr">
         <is>
-          <t>https://uk.linkedin.com/jobs/view/assistant-professor-in-international-development-quantitative-social-science-at-the-london-school-of-economics-and-political-science-lse-4461566153</t>
+          <t>https://www.linkedin.com/jobs/view/lee-assistant-associate-professor-of-economics-real-estate-and-urban-economics-r0153553-at-university-of-nevada-las-vegas-4467297476</t>
         </is>
       </c>
       <c r="N94" s="3" t="inlineStr">
@@ -9304,7 +9304,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -9318,31 +9318,31 @@
         </is>
       </c>
       <c r="R94" s="2" t="n">
-        <v>51.5074456</v>
+        <v>36.1079411</v>
       </c>
       <c r="S94" s="2" t="n">
-        <v>-0.1277653</v>
+        <v>-115.1439051</v>
       </c>
       <c r="T94" s="2" t="inlineStr">
         <is>
-          <t>69e89c6a307e9a14</t>
+          <t>2e04493c6bcebcfe</t>
         </is>
       </c>
     </row>
     <row r="95" ht="26" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Assistant/Associate/Full Professor in Industrial and Systems Engineering</t>
+          <t>Tenure-Track Faculty Position (Open Rank) - Robotics</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>University of Florida</t>
+          <t>University of Notre Dame</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Department of Industrial and Systems Engineering</t>
+          <t>Department of Engineering</t>
         </is>
       </c>
       <c r="D95" s="3" t="n">
@@ -9350,12 +9350,12 @@
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>Although transportation is mentioned as a potential application area, the primary focus of this Industrial and Systems Engineering position is on Industrialized Construction and 3D construction printing rather than core transportation engineering, mobility, or travel behavior.</t>
+          <t>The posting focuses specifically on robotics rather than transportation engineering, resulting in a low fit for the candidate's core profile.</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>Industrialized Construction, Artificial Intelligence, Digital Twins, Operations Research</t>
+          <t>Robotics, Engineering</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
@@ -9365,7 +9365,7 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>Gainesville, FL</t>
+          <t>Notre Dame, IN</t>
         </is>
       </c>
       <c r="I95" s="3" t="inlineStr">
@@ -9376,17 +9376,17 @@
       <c r="J95" s="3" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>Salary is commensurate with education and experience.</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
-          <t>This full-time tenured or tenure-track faculty position in Industrial and Systems Engineering at the University of Florida seeks expertise in industrialized construction and related technologies, requiring a Ph.D. in ISE, Manufacturing Engineering, Civil Engineering, Mechanical Engineering, or a closely related field. | Research Topics: Industrialized Construction, Artificial Intelligence, Digital Twins, Operations Research</t>
+          <t>Open rank tenure-track faculty position in robotics requiring a Ph.D. in engineering or a related discipline. | Research Topics: Robotics, Engineering</t>
         </is>
       </c>
       <c r="M95" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-associate-full-professor-industrial-systems-engineering-at-university-of-florida-4323668785</t>
+          <t>https://ca.linkedin.com/jobs/view/tenure-track-faculty-position-open-rank-all-areas-at-university-of-notre-dame-4463103000</t>
         </is>
       </c>
       <c r="N95" s="3" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Q95" s="6" t="inlineStr">
@@ -9410,31 +9410,31 @@
         </is>
       </c>
       <c r="R95" s="2" t="n">
-        <v>29.6436</v>
+        <v>41.7045677</v>
       </c>
       <c r="S95" s="2" t="n">
-        <v>-82.3549</v>
+        <v>-86.23822029999999</v>
       </c>
       <c r="T95" s="2" t="inlineStr">
         <is>
-          <t>56d501f448e77e05</t>
+          <t>bf3ba3056fe418d9</t>
         </is>
       </c>
     </row>
     <row r="96" ht="26" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor (Tenure Track) – Biostatistics and Health Data Science</t>
+          <t>Full Professor, Associate Professor, or Assistant Professor in Defense-related Technologies for Unmanned Aerial Systems Engineering for Defense</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>University of Minnesota</t>
+          <t>University of Southern Denmark</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Division of Biostatistics and Health Data Science</t>
+          <t>Department of Technology</t>
         </is>
       </c>
       <c r="D96" s="3" t="n">
@@ -9442,22 +9442,22 @@
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>Although it involves data science, the focus is strictly on biostatistics and health data science rather than mobility data science.</t>
+          <t>The position focuses on unmanned aerial systems engineering for defense, which is outside the candidate's core focus on ground transportation and mobility systems.</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>Biostatistics, Health Data Science, Statistical Modeling</t>
+          <t>Unmanned Aerial Systems, Defense Technologies, Aerospace Engineering</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Unspecified</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>Minneapolis, Minnesota</t>
+          <t>Greater Odense Area</t>
         </is>
       </c>
       <c r="I96" s="3" t="inlineStr">
@@ -9468,22 +9468,22 @@
       <c r="J96" s="3" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>Competitive Salary</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
-          <t>Tenure-track Assistant Professor position in biostatistics and health data science requiring a Ph.D. in statistics, biostatistics, or a related field. | Research Topics: Biostatistics, Health Data Science, Statistical Modeling</t>
+          <t>Open rank faculty position in unmanned aerial systems engineering for defense applications requiring a relevant doctorate. | Research Topics: Unmanned Aerial Systems, Defense Technologies, Aerospace Engineering</t>
         </is>
       </c>
       <c r="M96" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38039489/assistant-professor-tenure-track-biostatistics-and-health-data-science/</t>
+          <t>https://dk.linkedin.com/jobs/view/full-professor-associate-professor-or-assistant-professor-in-defense-related-technologies-for-unmanned-aerial-systems-engineering-for-defense-at-syddansk-universitet-university-of-southern-denmark-4466648729</t>
         </is>
       </c>
       <c r="N96" s="3" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
@@ -9502,31 +9502,31 @@
         </is>
       </c>
       <c r="R96" s="2" t="n">
-        <v>44.9863418</v>
+        <v>55.3678533</v>
       </c>
       <c r="S96" s="2" t="n">
-        <v>-93.1794451</v>
+        <v>10.4280534</v>
       </c>
       <c r="T96" s="2" t="inlineStr">
         <is>
-          <t>054f4f887d098cfa</t>
+          <t>a3c68961bb3746e6</t>
         </is>
       </c>
     </row>
     <row r="97" ht="26" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor in Industrial and Systems Engineering - Quantum Optimization</t>
+          <t>Assistant Professor – Statistical Learning Theory</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>University of Missouri</t>
+          <t>University of Toronto</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Department of Industrial and Manufacturing Engineering</t>
+          <t>Department of Statistical Sciences</t>
         </is>
       </c>
       <c r="D97" s="3" t="n">
@@ -9534,12 +9534,12 @@
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>Screened out due to an excessive focus on quantum optimization within industrial and systems engineering, which lacks a core transportation or mobility planning component.</t>
+          <t>While statistical learning is relevant to data science and modeling, this role is dedicated to Statistical Sciences rather than transportation engineering or mobility systems.</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>Industrial and Systems Engineering, Quantum Optimization, Operations Research</t>
+          <t>Statistical Learning Theory, Statistics, Data Science</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
@@ -9549,7 +9549,7 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>Columbia, MO</t>
+          <t>Toronto, Ontario</t>
         </is>
       </c>
       <c r="I97" s="3" t="inlineStr">
@@ -9565,27 +9565,27 @@
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
-          <t>This tenure-track assistant professor position focuses on quantum optimization within industrial and systems engineering, requiring a Ph.D. in a relevant engineering or scientific discipline. | Research Topics: Industrial and Systems Engineering, Quantum Optimization, Operations Research</t>
+          <t>Full-time tenure stream Assistant Professor position in Statistical Learning Theory requiring a Ph.D. | Research Topics: Statistical Learning Theory, Statistics, Data Science</t>
         </is>
       </c>
       <c r="M97" s="5" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179565194&amp;Title=Assistant%20Professor%20in%20Industrial%20and%20Systems%20Engineering%20%2D%20Quantum%20Optimization</t>
+          <t>https://ca.linkedin.com/jobs/view/assistant-professor-%E2%80%93-statistical-learning-theory-at-the-university-of-toronto-engineering-society-4439922753</t>
         </is>
       </c>
       <c r="N97" s="3" t="inlineStr">
         <is>
-          <t>HigherEdJobs</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Q97" s="6" t="inlineStr">
@@ -9594,31 +9594,31 @@
         </is>
       </c>
       <c r="R97" s="2" t="n">
-        <v>38.9364147</v>
+        <v>43.6629</v>
       </c>
       <c r="S97" s="2" t="n">
-        <v>-92.32970299999999</v>
+        <v>-79.39570000000001</v>
       </c>
       <c r="T97" s="2" t="inlineStr">
         <is>
-          <t>f13a6da0148df3dd</t>
+          <t>b8000dd39a2ffd80</t>
         </is>
       </c>
     </row>
     <row r="98" ht="26" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Lee Assistant/Associate Professor of Economics, Real Estate and Urban Economics</t>
+          <t>Professional Practice Assistant Professor - Air Traffic Control</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>University of Nevada-Las Vegas</t>
+          <t>Utah State University</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Department of Economics</t>
+          <t>Department of Aviation Technology</t>
         </is>
       </c>
       <c r="D98" s="3" t="n">
@@ -9626,22 +9626,22 @@
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>The position is within Economics and Real Estate, lacking sufficient overlap with transportation engineering or mobility analytics.</t>
+          <t>While it is an assistant professor role, the focus is strictly on teaching Air Traffic Control within aviation technology rather than transportation engineering research.</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>Economics, Real Estate, Urban Economics</t>
+          <t>Air Traffic Control, Aviation Technology, Professional Practice Teaching</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Non-Tenure Track</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>Las Vegas, NV</t>
+          <t>Logan, UT</t>
         </is>
       </c>
       <c r="I98" s="3" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
-          <t>Tenure-track assistant or associate professor position specializing in economics, real estate, and urban economics requiring a Ph.D. | Research Topics: Economics, Real Estate, Urban Economics</t>
+          <t>This is a teaching-focused professional practice assistant professor position focusing primarily on air traffic control instruction. | Research Topics: Air Traffic Control, Aviation Technology, Professional Practice Teaching</t>
         </is>
       </c>
       <c r="M98" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/lee-assistant-associate-professor-of-economics-real-estate-and-urban-economics-r0153553-at-university-of-nevada-las-vegas-4467297476</t>
+          <t>https://www.linkedin.com/jobs/view/professional-practice-assistant-professor-air-traffic-control-at-utah-state-university-4462897860</t>
         </is>
       </c>
       <c r="N98" s="3" t="inlineStr">
@@ -9672,7 +9672,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -9686,31 +9686,31 @@
         </is>
       </c>
       <c r="R98" s="2" t="n">
-        <v>36.1079411</v>
+        <v>41.7526959</v>
       </c>
       <c r="S98" s="2" t="n">
-        <v>-115.1439051</v>
+        <v>-111.808733</v>
       </c>
       <c r="T98" s="2" t="inlineStr">
         <is>
-          <t>2e04493c6bcebcfe</t>
+          <t>02b944bc9d0177ba</t>
         </is>
       </c>
     </row>
     <row r="99" ht="26" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Tenure-Track Faculty Position (Open Rank) - Robotics</t>
+          <t>Assistant Professor of AI in Mechatronics and Controls</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>University of Notre Dame</t>
+          <t>Worcester Polytechnic Institute</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Department of Engineering</t>
+          <t>Department of Mechanical &amp; Materials Engineering</t>
         </is>
       </c>
       <c r="D99" s="3" t="n">
@@ -9718,12 +9718,12 @@
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>The posting focuses specifically on robotics rather than transportation engineering, resulting in a low fit for the candidate's core profile.</t>
+          <t>The position is housed within Mechanical and Robotics Engineering focusing on mechatronics, controls, and cyber-physical systems, which lacks direct alignment with the candidate's civil engineering-based travel behavior and transit planning profile.</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>Robotics, Engineering</t>
+          <t>Mechatronics and Controls, Applied Artificial Intelligence, Cyber-Physical Systems, Autonomous Systems and Mobility</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
@@ -9733,7 +9733,7 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>Notre Dame, New Brunswick, Canada</t>
+          <t>Worcester, MA</t>
         </is>
       </c>
       <c r="I99" s="3" t="inlineStr">
@@ -9744,27 +9744,27 @@
       <c r="J99" s="3" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>$105,000 - $118,000 per year</t>
         </is>
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
-          <t>Open rank tenure-track faculty position in robotics requiring a Ph.D. in engineering or a related discipline. | Research Topics: Robotics, Engineering</t>
+          <t>The position seeks candidates for a tenure-track Assistant Professor role in Applied AI for Mechatronics and Controls, requiring a Ph.D. in mechanical engineering, robotics engineering, or a relevant discipline. | Research Topics: Mechatronics and Controls, Applied Artificial Intelligence, Cyber-Physical Systems, Autonomous Systems and Mobility</t>
         </is>
       </c>
       <c r="M99" s="5" t="inlineStr">
         <is>
-          <t>https://ca.linkedin.com/jobs/view/tenure-track-faculty-position-open-rank-all-areas-at-university-of-notre-dame-4463103000</t>
+          <t>https://engineering.academickeys.com/job/scf48oah/Assistant-Professor-of-AI-in-Mechatronics-and-Controls</t>
         </is>
       </c>
       <c r="N99" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>AcademicKeys</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -9778,59 +9778,59 @@
         </is>
       </c>
       <c r="R99" s="2" t="n">
-        <v>41.7045677</v>
+        <v>42.274315</v>
       </c>
       <c r="S99" s="2" t="n">
-        <v>-86.23822029999999</v>
+        <v>-71.80845669999999</v>
       </c>
       <c r="T99" s="2" t="inlineStr">
         <is>
-          <t>bf3ba3056fe418d9</t>
+          <t>f63e745090046255</t>
         </is>
       </c>
     </row>
     <row r="100" ht="26" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Full Professor, Associate Professor, or Assistant Professor in Defense-related Technologies for Unmanned Aerial Systems Engineering for Defense</t>
+          <t>Assistant/Associate/Full Professor, Transportation Engineering and Systems</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>University of Southern Denmark</t>
+          <t>University of Cincinnati</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Department of Technology</t>
-        </is>
-      </c>
-      <c r="D100" s="3" t="n">
-        <v>3</v>
+          <t>Department of Civil and Architectural Engineering and Construction Management (CAECM)</t>
+        </is>
+      </c>
+      <c r="D100" s="8" t="n">
+        <v>9</v>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>The position focuses on unmanned aerial systems engineering for defense, which is outside the candidate's core focus on ground transportation and mobility systems.</t>
+          <t>This is a dedicated Assistant/Associate/Full Professor position in Transportation Engineering and Systems perfectly aligned with the candidate's core research profile.</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>Unmanned Aerial Systems, Defense Technologies, Aerospace Engineering</t>
+          <t>Transportation Engineering, Transportation Systems, Transit Planning</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>Greater Odense Area</t>
+          <t>Cincinnati, OH</t>
         </is>
       </c>
       <c r="I100" s="3" t="inlineStr">
         <is>
-          <t>Open until filled</t>
+          <t>Posted 4 months ago</t>
         </is>
       </c>
       <c r="J100" s="3" t="inlineStr"/>
@@ -9841,12 +9841,12 @@
       </c>
       <c r="L100" s="4" t="inlineStr">
         <is>
-          <t>Open rank faculty position in unmanned aerial systems engineering for defense applications requiring a relevant doctorate. | Research Topics: Unmanned Aerial Systems, Defense Technologies, Aerospace Engineering</t>
+          <t>This role seeks a faculty member in transportation engineering and systems within an R1 urban research university setting requiring an appropriate terminal degree. | Research Topics: Transportation Engineering, Transportation Systems, Transit Planning</t>
         </is>
       </c>
       <c r="M100" s="5" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/full-professor-associate-professor-or-assistant-professor-in-defense-related-technologies-for-unmanned-aerial-systems-engineering-for-defense-at-syddansk-universitet-university-of-southern-denmark-4466648729</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-associate-full-professor-transportation-engineering-and-systems-at-university-of-cincinnati-4416744025</t>
         </is>
       </c>
       <c r="N100" s="3" t="inlineStr">
@@ -9856,7 +9856,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -9870,44 +9870,44 @@
         </is>
       </c>
       <c r="R100" s="2" t="n">
-        <v>55.3678533</v>
+        <v>39.1318888</v>
       </c>
       <c r="S100" s="2" t="n">
-        <v>10.4280534</v>
+        <v>-84.51578309999999</v>
       </c>
       <c r="T100" s="2" t="inlineStr">
         <is>
-          <t>a3c68961bb3746e6</t>
+          <t>6aa8ab000bc6f6c0</t>
         </is>
       </c>
     </row>
     <row r="101" ht="26" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor – Statistical Learning Theory</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>University of Toronto</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Department of Statistical Sciences</t>
-        </is>
-      </c>
-      <c r="D101" s="3" t="n">
-        <v>3</v>
+          <t>School of City and Regional Planning</t>
+        </is>
+      </c>
+      <c r="D101" s="8" t="n">
+        <v>8</v>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>While statistical learning is relevant to data science and modeling, this role is dedicated to Statistical Sciences rather than transportation engineering or mobility systems.</t>
+          <t>This is an Assistant Professor position within the School of City and Regional Planning, matching the candidate's background in urban planning and transportation mobility research.</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>Statistical Learning Theory, Statistics, Data Science</t>
+          <t>Urban Planning and Spatial Analytics, Sustainable and Resilient Communities, Mobility Analytics</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>Toronto, Ontario</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="I101" s="3" t="inlineStr">
         <is>
-          <t>Open until filled</t>
+          <t>Posted 6 days ago</t>
         </is>
       </c>
       <c r="J101" s="3" t="inlineStr"/>
@@ -9933,12 +9933,12 @@
       </c>
       <c r="L101" s="4" t="inlineStr">
         <is>
-          <t>Full-time tenure stream Assistant Professor position in Statistical Learning Theory requiring a Ph.D. | Research Topics: Statistical Learning Theory, Statistics, Data Science</t>
+          <t>Georgia Institute of Technology seeks a tenure-track Assistant Professor in the School of City and Regional Planning to advance research and teaching in urban planning, spatial analytics, and sustainable communities. | Research Topics: Urban Planning and Spatial Analytics, Sustainable and Resilient Communities, Mobility Analytics</t>
         </is>
       </c>
       <c r="M101" s="5" t="inlineStr">
         <is>
-          <t>https://ca.linkedin.com/jobs/view/assistant-professor-%E2%80%93-statistical-learning-theory-at-the-university-of-toronto-engineering-society-4439922753</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-at-georgia-institute-of-technology-4467296351</t>
         </is>
       </c>
       <c r="N101" s="3" t="inlineStr">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -9962,59 +9962,59 @@
         </is>
       </c>
       <c r="R101" s="2" t="n">
-        <v>43.6629</v>
+        <v>33.7756</v>
       </c>
       <c r="S101" s="2" t="n">
-        <v>-79.39570000000001</v>
+        <v>-84.3963</v>
       </c>
       <c r="T101" s="2" t="inlineStr">
         <is>
-          <t>b8000dd39a2ffd80</t>
+          <t>1b7278bf60327029</t>
         </is>
       </c>
     </row>
     <row r="102" ht="26" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Professional Practice Assistant Professor - Air Traffic Control</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Utah State University</t>
+          <t>The University of North Carolina at Chapel Hill</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Department of Aviation Technology</t>
-        </is>
-      </c>
-      <c r="D102" s="3" t="n">
-        <v>3</v>
+          <t>City and Regional Planning</t>
+        </is>
+      </c>
+      <c r="D102" s="8" t="n">
+        <v>8</v>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>While it is an assistant professor role, the focus is strictly on teaching Air Traffic Control within aviation technology rather than transportation engineering research.</t>
+          <t>This is a direct fit in a City and Regional Planning department which aligns strongly with the candidate's urban planning and mobility research track.</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>Air Traffic Control, Aviation Technology, Professional Practice Teaching</t>
+          <t>City and Regional Planning, Urban Mobility, Transportation Policy</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>Non-Tenure Track</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>Logan, UT</t>
+          <t>Chapel Hill, North Carolina</t>
         </is>
       </c>
       <c r="I102" s="3" t="inlineStr">
         <is>
-          <t>Open until filled</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J102" s="3" t="inlineStr"/>
@@ -10025,12 +10025,12 @@
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
-          <t>This is a teaching-focused professional practice assistant professor position focusing primarily on air traffic control instruction. | Research Topics: Air Traffic Control, Aviation Technology, Professional Practice Teaching</t>
+          <t>Permanent tenure-track faculty position in City and Regional Planning requiring a Ph.D. in planning, transportation, or a related discipline. | Research Topics: City and Regional Planning, Urban Mobility, Transportation Policy</t>
         </is>
       </c>
       <c r="M102" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/professional-practice-assistant-professor-air-traffic-control-at-utah-state-university-4462897860</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-at-the-university-of-north-carolina-at-chapel-hill-4466858895</t>
         </is>
       </c>
       <c r="N102" s="3" t="inlineStr">
@@ -10040,7 +10040,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -10054,44 +10054,44 @@
         </is>
       </c>
       <c r="R102" s="2" t="n">
-        <v>41.7526959</v>
+        <v>35.6729639</v>
       </c>
       <c r="S102" s="2" t="n">
-        <v>-111.808733</v>
+        <v>-79.03929189999999</v>
       </c>
       <c r="T102" s="2" t="inlineStr">
         <is>
-          <t>02b944bc9d0177ba</t>
+          <t>6136ec813df183f2</t>
         </is>
       </c>
     </row>
     <row r="103" ht="26" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of AI in Mechatronics and Controls</t>
+          <t>Assistant Professor in Transportation Policy</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Worcester Polytechnic Institute</t>
+          <t>Hunter College</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Department of Mechanical &amp; Materials Engineering</t>
-        </is>
-      </c>
-      <c r="D103" s="3" t="n">
-        <v>3</v>
+          <t>Department of Urban Policy and Planning</t>
+        </is>
+      </c>
+      <c r="D103" s="7" t="n">
+        <v>7</v>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>The position is housed within Mechanical and Robotics Engineering focusing on mechatronics, controls, and cyber-physical systems, which lacks direct alignment with the candidate's civil engineering-based travel behavior and transit planning profile.</t>
+          <t>Strong interdisciplinary fit for an Assistant Professor position focusing on transportation policy and planning within an urban policy department.</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>Mechatronics and Controls, Applied Artificial Intelligence, Cyber-Physical Systems, Autonomous Systems and Mobility</t>
+          <t>Transportation Policy, Transportation Advocacy &amp; Accessibility, Community-Engaged Research, Urban Planning</t>
         </is>
       </c>
       <c r="G103" s="3" t="inlineStr">
@@ -10101,38 +10101,38 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>Worcester, MA</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="I103" s="3" t="inlineStr">
         <is>
-          <t>Open until filled</t>
+          <t>Posted 2 months ago</t>
         </is>
       </c>
       <c r="J103" s="3" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>$105,000 - $118,000 per year</t>
+          <t>$77,092 - $91,922</t>
         </is>
       </c>
       <c r="L103" s="4" t="inlineStr">
         <is>
-          <t>The position seeks candidates for a tenure-track Assistant Professor role in Applied AI for Mechatronics and Controls, requiring a Ph.D. in mechanical engineering, robotics engineering, or a relevant discipline. | Research Topics: Mechatronics and Controls, Applied Artificial Intelligence, Cyber-Physical Systems, Autonomous Systems and Mobility</t>
+          <t>Hunter College seeks a tenure-track Assistant Professor in transportation policy to teach graduate students and conduct community-engaged research, requiring a Ph.D. in policy, planning, or a related field specializing in transportation. | Research Topics: Transportation Policy, Transportation Advocacy &amp; Accessibility, Community-Engaged Research, Urban Planning</t>
         </is>
       </c>
       <c r="M103" s="5" t="inlineStr">
         <is>
-          <t>https://engineering.academickeys.com/job/scf48oah/Assistant-Professor-of-AI-in-Mechatronics-and-Controls</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-%E2%80%93-urban-policy-and-planning-dept-school-of-arts-and-sciences-hunter-college-at-hunter-college-4438624127</t>
         </is>
       </c>
       <c r="N103" s="3" t="inlineStr">
         <is>
-          <t>AcademicKeys</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -10146,59 +10146,59 @@
         </is>
       </c>
       <c r="R103" s="2" t="n">
-        <v>42.274315</v>
+        <v>40.7683107</v>
       </c>
       <c r="S103" s="2" t="n">
-        <v>-71.80845669999999</v>
+        <v>-73.964406</v>
       </c>
       <c r="T103" s="2" t="inlineStr">
         <is>
-          <t>f63e745090046255</t>
+          <t>e4e18ed629103a27</t>
         </is>
       </c>
     </row>
     <row r="104" ht="26" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Assistant/Associate/Full Professor, Transportation Engineering and Systems</t>
+          <t>Assistant or Associate Professor in Complex Systems and Urban &amp; Regional Modelling</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>University of Cincinnati</t>
+          <t>Maastricht University</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Department of Civil and Architectural Engineering and Construction Management (CAECM)</t>
-        </is>
-      </c>
-      <c r="D104" s="8" t="n">
-        <v>9</v>
+          <t>Faculty of Science and Engineering</t>
+        </is>
+      </c>
+      <c r="D104" s="7" t="n">
+        <v>7</v>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>This is a dedicated Assistant/Associate/Full Professor position in Transportation Engineering and Systems perfectly aligned with the candidate's core research profile.</t>
+          <t>This Assistant or Associate Professor role in complex systems and urban and regional modelling aligns well with the candidate's strong computational and urban modelling expertise.</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>Transportation Engineering, Transportation Systems, Transit Planning</t>
+          <t>Urban and Regional Modelling, Complex Systems Theory, Urban Sustainability, Spatial Modelling</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Unspecified</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>Cincinnati, OH</t>
+          <t>Maastricht, Netherlands</t>
         </is>
       </c>
       <c r="I104" s="3" t="inlineStr">
         <is>
-          <t>Posted 4 months ago</t>
+          <t>Posted 1 month ago</t>
         </is>
       </c>
       <c r="J104" s="3" t="inlineStr"/>
@@ -10209,12 +10209,12 @@
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
-          <t>This role seeks a faculty member in transportation engineering and systems within an R1 urban research university setting requiring an appropriate terminal degree. | Research Topics: Transportation Engineering, Transportation Systems, Transit Planning</t>
+          <t>Maastricht University seeks an Assistant or Associate Professor to build a new research line in urban and regional modelling, requiring a PhD in a relevant technical or computational field. | Research Topics: Urban and Regional Modelling, Complex Systems Theory, Urban Sustainability, Spatial Modelling</t>
         </is>
       </c>
       <c r="M104" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-associate-full-professor-transportation-engineering-and-systems-at-university-of-cincinnati-4416744025</t>
+          <t>https://nl.linkedin.com/jobs/view/assistant-or-associate-professor-in-complex-systems-and-urban-regional-modelling-at-maastricht-university-faculty-of-science-and-engineering-4452765174</t>
         </is>
       </c>
       <c r="N104" s="3" t="inlineStr">
@@ -10224,7 +10224,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -10238,14 +10238,14 @@
         </is>
       </c>
       <c r="R104" s="2" t="n">
-        <v>39.1318888</v>
+        <v>50.8472117</v>
       </c>
       <c r="S104" s="2" t="n">
-        <v>-84.51578309999999</v>
+        <v>5.6859518</v>
       </c>
       <c r="T104" s="2" t="inlineStr">
         <is>
-          <t>6aa8ab000bc6f6c0</t>
+          <t>321ee686ffad2403</t>
         </is>
       </c>
     </row>
@@ -10257,25 +10257,25 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>The University of Texas at Arlington</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>School of City and Regional Planning</t>
-        </is>
-      </c>
-      <c r="D105" s="8" t="n">
-        <v>8</v>
+          <t>Department of Public Affairs and Planning</t>
+        </is>
+      </c>
+      <c r="D105" s="7" t="n">
+        <v>7</v>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>This is an Assistant Professor position within the School of City and Regional Planning, matching the candidate's background in urban planning and transportation mobility research.</t>
+          <t>The position is within public affairs and urban planning, offering a strong interdisciplinary match for the candidate's urban mobility and transportation equity research.</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>Urban Planning and Spatial Analytics, Sustainable and Resilient Communities, Mobility Analytics</t>
+          <t>Public Affairs, Urban Planning, Transportation Policy</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
@@ -10285,12 +10285,12 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Arlington, TX</t>
         </is>
       </c>
       <c r="I105" s="3" t="inlineStr">
         <is>
-          <t>Posted 6 days ago</t>
+          <t>Posted 2 weeks ago</t>
         </is>
       </c>
       <c r="J105" s="3" t="inlineStr"/>
@@ -10301,12 +10301,12 @@
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology seeks a tenure-track Assistant Professor in the School of City and Regional Planning to advance research and teaching in urban planning, spatial analytics, and sustainable communities. | Research Topics: Urban Planning and Spatial Analytics, Sustainable and Resilient Communities, Mobility Analytics</t>
+          <t>Tenure-track Assistant Professor in Public Affairs and Planning requiring a Ph.D. in urban planning or a closely related field. | Research Topics: Public Affairs, Urban Planning, Transportation Policy</t>
         </is>
       </c>
       <c r="M105" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-at-georgia-institute-of-technology-4467296351</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-at-the-university-of-texas-at-arlington-4465888489</t>
         </is>
       </c>
       <c r="N105" s="3" t="inlineStr">
@@ -10316,7 +10316,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -10330,44 +10330,44 @@
         </is>
       </c>
       <c r="R105" s="2" t="n">
-        <v>33.7756</v>
+        <v>32.7284713</v>
       </c>
       <c r="S105" s="2" t="n">
-        <v>-84.3963</v>
+        <v>-97.11202129999999</v>
       </c>
       <c r="T105" s="2" t="inlineStr">
         <is>
-          <t>1b7278bf60327029</t>
+          <t>786d8625d3eb7f22</t>
         </is>
       </c>
     </row>
     <row r="106" ht="26" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Faculty Position in Civil Engineering (Transportation and Traffic Engineering)</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>The University of North Carolina at Chapel Hill</t>
+          <t>University of New Brunswick</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>City and Regional Planning</t>
-        </is>
-      </c>
-      <c r="D106" s="8" t="n">
-        <v>8</v>
+          <t>Faculty of Engineering</t>
+        </is>
+      </c>
+      <c r="D106" s="7" t="n">
+        <v>6</v>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>This is a direct fit in a City and Regional Planning department which aligns strongly with the candidate's urban planning and mobility research track.</t>
+          <t>This is a broad Civil Engineering faculty position that explicitly covers traffic engineering and transportation operations, aligning with the candidate's core subfield.</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>City and Regional Planning, Urban Mobility, Transportation Policy</t>
+          <t>Traffic studies and analysis, Traffic control devices, Intersections and interchanges operations, Traffic accident studies</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
@@ -10377,12 +10377,12 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>Chapel Hill, North Carolina</t>
+          <t>Fredericton, New Brunswick</t>
         </is>
       </c>
       <c r="I106" s="3" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>Posted 1 month ago</t>
         </is>
       </c>
       <c r="J106" s="3" t="inlineStr"/>
@@ -10393,12 +10393,12 @@
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
-          <t>Permanent tenure-track faculty position in City and Regional Planning requiring a Ph.D. in planning, transportation, or a related discipline. | Research Topics: City and Regional Planning, Urban Mobility, Transportation Policy</t>
+          <t>The University of New Brunswick seeks a faculty member in Civil Engineering specializing in traffic characteristics, traffic studies, and intersection operations, requiring a Master's or Ph.D. in Civil Engineering or a closely related area. | Research Topics: Traffic studies and analysis, Traffic control devices, Intersections and interchanges operations, Traffic accident studies</t>
         </is>
       </c>
       <c r="M106" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-at-the-university-of-north-carolina-at-chapel-hill-4466858895</t>
+          <t>https://ca.linkedin.com/jobs/view/engineering-faculty-of-at-university-of-new-brunswick-4451582209</t>
         </is>
       </c>
       <c r="N106" s="3" t="inlineStr">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -10422,75 +10422,75 @@
         </is>
       </c>
       <c r="R106" s="2" t="n">
-        <v>35.6729639</v>
+        <v>45.9455202</v>
       </c>
       <c r="S106" s="2" t="n">
-        <v>-79.03929189999999</v>
+        <v>-66.64018609999999</v>
       </c>
       <c r="T106" s="2" t="inlineStr">
         <is>
-          <t>6136ec813df183f2</t>
+          <t>77b43c5491345e72</t>
         </is>
       </c>
     </row>
     <row r="107" ht="26" customHeight="1">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor in Transportation Policy</t>
+          <t>Assistant Lecturer in Human Geography</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Hunter College</t>
+          <t>Maynooth University</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Department of Urban Policy and Planning</t>
+          <t>Department of Geography</t>
         </is>
       </c>
       <c r="D107" s="7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>Strong interdisciplinary fit for an Assistant Professor position focusing on transportation policy and planning within an urban policy department.</t>
+          <t>While in human geography, it lacks specific focus on transportation engineering, planning, or mobility modeling.</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>Transportation Policy, Transportation Advocacy &amp; Accessibility, Community-Engaged Research, Urban Planning</t>
+          <t>Human Geography, Spatial Analysis, Social Sciences</t>
         </is>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Non-Tenure Track</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Maynooth, County Kildare</t>
         </is>
       </c>
       <c r="I107" s="3" t="inlineStr">
         <is>
-          <t>Posted 2 months ago</t>
+          <t>18-Oct-2026</t>
         </is>
       </c>
       <c r="J107" s="3" t="inlineStr"/>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>$77,092 - $91,922</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L107" s="4" t="inlineStr">
         <is>
-          <t>Hunter College seeks a tenure-track Assistant Professor in transportation policy to teach graduate students and conduct community-engaged research, requiring a Ph.D. in policy, planning, or a related field specializing in transportation. | Research Topics: Transportation Policy, Transportation Advocacy &amp; Accessibility, Community-Engaged Research, Urban Planning</t>
+          <t>This is an assistant lecturer position in human geography requiring a relevant postgraduate degree. | Research Topics: Human Geography, Spatial Analysis, Social Sciences</t>
         </is>
       </c>
       <c r="M107" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-%E2%80%93-urban-policy-and-planning-dept-school-of-arts-and-sciences-hunter-college-at-hunter-college-4438624127</t>
+          <t>https://ie.linkedin.com/jobs/view/assistant-lecturer-in-human-geography-at-maynooth-university-4473587700</t>
         </is>
       </c>
       <c r="N107" s="3" t="inlineStr">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
@@ -10514,85 +10514,85 @@
         </is>
       </c>
       <c r="R107" s="2" t="n">
-        <v>40.7683107</v>
+        <v>53.3820615</v>
       </c>
       <c r="S107" s="2" t="n">
-        <v>-73.964406</v>
+        <v>-6.5988074</v>
       </c>
       <c r="T107" s="2" t="inlineStr">
         <is>
-          <t>e4e18ed629103a27</t>
+          <t>5e152077721b65ac</t>
         </is>
       </c>
     </row>
     <row r="108" ht="26" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Assistant or Associate Professor in Complex Systems and Urban &amp; Regional Modelling</t>
+          <t>Assistant Professor in Industrial and Systems Engineering – Quantum Optimization</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Maastricht University</t>
+          <t>University of Missouri - Columbia</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Faculty of Science and Engineering</t>
+          <t>Department of Industrial and Systems Engineering</t>
         </is>
       </c>
       <c r="D108" s="7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>This Assistant or Associate Professor role in complex systems and urban and regional modelling aligns well with the candidate's strong computational and urban modelling expertise.</t>
+          <t>While in Industrial and Systems Engineering, the specific focus on quantum optimization has only peripheral overlap with the candidate's mobility systems expertise.</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>Urban and Regional Modelling, Complex Systems Theory, Urban Sustainability, Spatial Modelling</t>
+          <t>Industrial Engineering, Quantum Optimization, Systems Engineering</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>Maastricht, Netherlands</t>
+          <t>Columbia, Missouri</t>
         </is>
       </c>
       <c r="I108" s="3" t="inlineStr">
         <is>
-          <t>Posted 1 month ago</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="J108" s="3" t="inlineStr"/>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Competitive Salary</t>
         </is>
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
-          <t>Maastricht University seeks an Assistant or Associate Professor to build a new research line in urban and regional modelling, requiring a PhD in a relevant technical or computational field. | Research Topics: Urban and Regional Modelling, Complex Systems Theory, Urban Sustainability, Spatial Modelling</t>
+          <t>Tenure-track Assistant Professor role in Industrial and Systems Engineering focusing on quantum optimization requiring a Ph.D. | Research Topics: Industrial Engineering, Quantum Optimization, Systems Engineering</t>
         </is>
       </c>
       <c r="M108" s="5" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/assistant-or-associate-professor-in-complex-systems-and-urban-regional-modelling-at-maastricht-university-faculty-of-science-and-engineering-4452765174</t>
+          <t>https://jobs.chronicle.com/job/38042575/assistant-professor-in-industrial-and-systems-engineering-quantum-optimization/</t>
         </is>
       </c>
       <c r="N108" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
@@ -10606,44 +10606,44 @@
         </is>
       </c>
       <c r="R108" s="2" t="n">
-        <v>50.8472117</v>
+        <v>38.9364147</v>
       </c>
       <c r="S108" s="2" t="n">
-        <v>5.6859518</v>
+        <v>-92.32970299999999</v>
       </c>
       <c r="T108" s="2" t="inlineStr">
         <is>
-          <t>321ee686ffad2403</t>
+          <t>250d4a7e8de8baa9</t>
         </is>
       </c>
     </row>
     <row r="109" ht="26" customHeight="1">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Assistant/Associate Professor of Civil, Architectural and Environmental Engineering</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>The University of Texas at Arlington</t>
+          <t>Missouri University of Science and Technology</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Department of Public Affairs and Planning</t>
-        </is>
-      </c>
-      <c r="D109" s="7" t="n">
-        <v>7</v>
+          <t>Department of Civil, Architectural and Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>The position is within public affairs and urban planning, offering a strong interdisciplinary match for the candidate's urban mobility and transportation equity research.</t>
+          <t>This is a general Civil, Architectural and Environmental Engineering faculty opening without an explicitly stated specialization in transportation engineering or transit planning.</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>Public Affairs, Urban Planning, Transportation Policy</t>
+          <t>Civil Engineering, Architectural Engineering, Environmental Engineering</t>
         </is>
       </c>
       <c r="G109" s="3" t="inlineStr">
@@ -10653,12 +10653,12 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>Arlington, TX</t>
+          <t>Rolla, MO</t>
         </is>
       </c>
       <c r="I109" s="3" t="inlineStr">
         <is>
-          <t>Posted 2 weeks ago</t>
+          <t>Posted 1 week ago</t>
         </is>
       </c>
       <c r="J109" s="3" t="inlineStr"/>
@@ -10669,12 +10669,12 @@
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
-          <t>Tenure-track Assistant Professor in Public Affairs and Planning requiring a Ph.D. in urban planning or a closely related field. | Research Topics: Public Affairs, Urban Planning, Transportation Policy</t>
+          <t>Missouri University of Science and Technology invites applications for an Assistant or Associate Professor position in Civil, Architectural, and Environmental Engineering requiring a relevant doctoral degree. | Research Topics: Civil Engineering, Architectural Engineering, Environmental Engineering</t>
         </is>
       </c>
       <c r="M109" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-at-the-university-of-texas-at-arlington-4465888489</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-associate-professor-civil-architectural-and-environmental-engineering-%2300096512-at-missouri-university-of-science-and-technology-4442271248</t>
         </is>
       </c>
       <c r="N109" s="3" t="inlineStr">
@@ -10684,7 +10684,7 @@
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="P109" s="2" t="inlineStr">
@@ -10698,44 +10698,44 @@
         </is>
       </c>
       <c r="R109" s="2" t="n">
-        <v>32.7284713</v>
+        <v>37.9532435</v>
       </c>
       <c r="S109" s="2" t="n">
-        <v>-97.11202129999999</v>
+        <v>-91.7742667</v>
       </c>
       <c r="T109" s="2" t="inlineStr">
         <is>
-          <t>786d8625d3eb7f22</t>
+          <t>4fad8c46021c1243</t>
         </is>
       </c>
     </row>
     <row r="110" ht="26" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Faculty Position in Civil Engineering (Transportation and Traffic Engineering)</t>
+          <t>Assistant Professor in Supply Chain Management</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>University of New Brunswick</t>
+          <t>Iowa State University</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Faculty of Engineering</t>
-        </is>
-      </c>
-      <c r="D110" s="7" t="n">
-        <v>6</v>
+          <t>Department of Supply Chain Management, Ivy College of Business</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>This is a broad Civil Engineering faculty position that explicitly covers traffic engineering and transportation operations, aligning with the candidate's core subfield.</t>
+          <t>This is a business school position focused on supply chain management rather than transportation engineering or urban mobility systems.</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>Traffic studies and analysis, Traffic control devices, Intersections and interchanges operations, Traffic accident studies</t>
+          <t>Supply Chain Management, Logistics, Operations</t>
         </is>
       </c>
       <c r="G110" s="3" t="inlineStr">
@@ -10745,12 +10745,12 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>Fredericton, New Brunswick</t>
+          <t>Ames, IA</t>
         </is>
       </c>
       <c r="I110" s="3" t="inlineStr">
         <is>
-          <t>Posted 1 month ago</t>
+          <t>Posted 2 months ago</t>
         </is>
       </c>
       <c r="J110" s="3" t="inlineStr"/>
@@ -10761,12 +10761,12 @@
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
-          <t>The University of New Brunswick seeks a faculty member in Civil Engineering specializing in traffic characteristics, traffic studies, and intersection operations, requiring a Master's or Ph.D. in Civil Engineering or a closely related area. | Research Topics: Traffic studies and analysis, Traffic control devices, Intersections and interchanges operations, Traffic accident studies</t>
+          <t>Iowa State University seeks a tenure-track Assistant Professor in Supply Chain Management to conduct research and teach courses at the undergraduate, master's, and Ph.D. levels, requiring a doctorate in business administration, supply chain, transportation, logistics, operations, or a related field. | Research Topics: Supply Chain Management, Logistics, Operations</t>
         </is>
       </c>
       <c r="M110" s="5" t="inlineStr">
         <is>
-          <t>https://ca.linkedin.com/jobs/view/engineering-faculty-of-at-university-of-new-brunswick-4451582209</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-in-supply-chain-management-at-iowa-state-university-ivy-college-of-business-4440811209</t>
         </is>
       </c>
       <c r="N110" s="3" t="inlineStr">
@@ -10776,7 +10776,7 @@
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="P110" s="2" t="inlineStr">
@@ -10790,85 +10790,89 @@
         </is>
       </c>
       <c r="R110" s="2" t="n">
-        <v>45.9455202</v>
+        <v>42.0267567</v>
       </c>
       <c r="S110" s="2" t="n">
-        <v>-66.64018609999999</v>
+        <v>-93.6170448</v>
       </c>
       <c r="T110" s="2" t="inlineStr">
         <is>
-          <t>77b43c5491345e72</t>
+          <t>e994e392d38b77ce</t>
         </is>
       </c>
     </row>
     <row r="111" ht="26" customHeight="1">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Assistant Lecturer in Human Geography</t>
+          <t>Assistant Professor in Urban and Regional Planning</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Maynooth University</t>
+          <t>Louisiana State University New Orleans</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Department of Geography</t>
-        </is>
-      </c>
-      <c r="D111" s="7" t="n">
-        <v>5</v>
+          <t>Department of Planning and Urban Studies</t>
+        </is>
+      </c>
+      <c r="D111" s="8" t="n">
+        <v>8</v>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>While in human geography, it lacks specific focus on transportation engineering, planning, or mobility modeling.</t>
+          <t>Strong interdisciplinary fit for an Assistant Professor in Urban and Regional Planning with a specific interest in transportation planning, GIS, and spatial analytics.</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>Human Geography, Spatial Analysis, Social Sciences</t>
+          <t>Urban and Regional Planning, Transportation Planning, GIS and Spatial Analytics, Climate Adaptation and Environmental Planning</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>Non-Tenure Track</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>Maynooth, County Kildare</t>
+          <t>New Orleans, LA</t>
         </is>
       </c>
       <c r="I111" s="3" t="inlineStr">
         <is>
-          <t>18-Oct-2026</t>
-        </is>
-      </c>
-      <c r="J111" s="3" t="inlineStr"/>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="J111" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>DOE</t>
         </is>
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
-          <t>This is an assistant lecturer position in human geography requiring a relevant postgraduate degree. | Research Topics: Human Geography, Spatial Analysis, Social Sciences</t>
+          <t>LSU New Orleans seeks a tenure-track Assistant Professor in Urban and Regional Planning to teach graduate courses in the MURP program, mentor students, and maintain an active research agenda requiring a Ph.D. in Urban and Regional Planning or a closely related field. | Research Topics: Urban and Regional Planning, Transportation Planning, GIS and Spatial Analytics, Climate Adaptation and Environmental Planning</t>
         </is>
       </c>
       <c r="M111" s="5" t="inlineStr">
         <is>
-          <t>https://ie.linkedin.com/jobs/view/assistant-lecturer-in-human-geography-at-maynooth-university-4473587700</t>
+          <t>https://jobs.chronicle.com/job/38025681/assistant-professor-planning-and-urban-studies-/</t>
         </is>
       </c>
       <c r="N111" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="P111" s="2" t="inlineStr">
@@ -10882,44 +10886,44 @@
         </is>
       </c>
       <c r="R111" s="2" t="n">
-        <v>53.3820615</v>
+        <v>29.9911944</v>
       </c>
       <c r="S111" s="2" t="n">
-        <v>-6.5988074</v>
+        <v>-90.0835067</v>
       </c>
       <c r="T111" s="2" t="inlineStr">
         <is>
-          <t>5e152077721b65ac</t>
+          <t>f373f0209d1c2577</t>
         </is>
       </c>
     </row>
     <row r="112" ht="26" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor in Industrial and Systems Engineering – Quantum Optimization</t>
+          <t>Assistant Professor of Civil, Construction and Environmental Engineering (Transportation Engineering)</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>University of Missouri - Columbia</t>
+          <t>University of Alabama</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Department of Industrial and Systems Engineering</t>
-        </is>
-      </c>
-      <c r="D112" s="7" t="n">
-        <v>5</v>
+          <t>Department of Civil, Construction and Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="D112" s="8" t="n">
+        <v>8</v>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>While in Industrial and Systems Engineering, the specific focus on quantum optimization has only peripheral overlap with the candidate's mobility systems expertise.</t>
+          <t>Tenure-track Assistant Professor position in Civil Engineering explicitly recruiting in Transportation Engineering with focus areas including public transportation, network analysis, data science, and transportation planning.</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>Industrial Engineering, Quantum Optimization, Systems Engineering</t>
+          <t>Transportation Systems &amp; Planning, Public Transportation, Network Analysis &amp; Big Data in Transportation, Multimodal Transportation Safety &amp; Operations</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
@@ -10929,38 +10933,42 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>Columbia, Missouri</t>
+          <t>Tuscaloosa, AL</t>
         </is>
       </c>
       <c r="I112" s="3" t="inlineStr">
         <is>
+          <t>Priority: 2026-10-01 / Final: Open until filled</t>
+        </is>
+      </c>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="J112" s="3" t="inlineStr"/>
-      <c r="K112" s="2" t="inlineStr">
-        <is>
-          <t>Competitive Salary</t>
-        </is>
-      </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
-          <t>Tenure-track Assistant Professor role in Industrial and Systems Engineering focusing on quantum optimization requiring a Ph.D. | Research Topics: Industrial Engineering, Quantum Optimization, Systems Engineering</t>
+          <t>The Department of Civil, Construction and Environmental Engineering seeks a tenure-track Assistant Professor in Transportation Engineering and related civil disciplines with an earned Ph.D. in Civil Engineering or a closely related field. | Research Topics: Transportation Systems &amp; Planning, Public Transportation, Network Analysis &amp; Big Data in Transportation, Multimodal Transportation Safety &amp; Operations</t>
         </is>
       </c>
       <c r="M112" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38042575/assistant-professor-in-industrial-and-systems-engineering-quantum-optimization/</t>
+          <t>https://engineering.academickeys.com/job/02ixzgls/Civil-Construction-and-Environmental-Engineering--Assistant-Professor</t>
         </is>
       </c>
       <c r="N112" s="3" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>AcademicKeys</t>
         </is>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="P112" s="2" t="inlineStr">
@@ -10974,31 +10982,31 @@
         </is>
       </c>
       <c r="R112" s="2" t="n">
-        <v>38.9364147</v>
+        <v>33.2120822</v>
       </c>
       <c r="S112" s="2" t="n">
-        <v>-92.32970299999999</v>
+        <v>-87.53967350000001</v>
       </c>
       <c r="T112" s="2" t="inlineStr">
         <is>
-          <t>250d4a7e8de8baa9</t>
+          <t>f80ad2336a210f82</t>
         </is>
       </c>
     </row>
     <row r="113" ht="26" customHeight="1">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Assistant/Associate Professor of Civil, Architectural and Environmental Engineering</t>
+          <t>Tenure-track Assistant Professor – AI for Automotive and Mobility Systems</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Missouri University of Science and Technology</t>
+          <t>The Ohio State University</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Department of Civil, Architectural and Environmental Engineering</t>
+          <t>Department of Mechanical and Aerospace Engineering</t>
         </is>
       </c>
       <c r="D113" s="3" t="n">
@@ -11006,12 +11014,12 @@
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>This is a general Civil, Architectural and Environmental Engineering faculty opening without an explicitly stated specialization in transportation engineering or transit planning.</t>
+          <t>While the position focuses on AI for ground transportation and mobility, it is based in Mechanical and Aerospace Engineering with a primary focus on automotive engineering, control, and vehicle dynamics rather than transportation planning and systems engineering.</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>Civil Engineering, Architectural Engineering, Environmental Engineering</t>
+          <t>AI for Ground Transportation, Automotive and Mobility Systems, Vehicle Control and Optimization, Intelligent Infrastructure</t>
         </is>
       </c>
       <c r="G113" s="3" t="inlineStr">
@@ -11021,15 +11029,19 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>Rolla, MO</t>
+          <t>Columbus, OH</t>
         </is>
       </c>
       <c r="I113" s="3" t="inlineStr">
         <is>
-          <t>Posted 1 week ago</t>
-        </is>
-      </c>
-      <c r="J113" s="3" t="inlineStr"/>
+          <t>Priority: 2026-10-01 / Final: Open until filled</t>
+        </is>
+      </c>
+      <c r="J113" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
           <t>Not specified</t>
@@ -11037,22 +11049,22 @@
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
-          <t>Missouri University of Science and Technology invites applications for an Assistant or Associate Professor position in Civil, Architectural, and Environmental Engineering requiring a relevant doctoral degree. | Research Topics: Civil Engineering, Architectural Engineering, Environmental Engineering</t>
+          <t>The Department of Mechanical and Aerospace Engineering seeks a tenure-track assistant professor applying AI/ML to automotive and ground mobility systems, requiring a doctorate in mechanical engineering or a closely related discipline. | Research Topics: AI for Ground Transportation, Automotive and Mobility Systems, Vehicle Control and Optimization, Intelligent Infrastructure</t>
         </is>
       </c>
       <c r="M113" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-associate-professor-civil-architectural-and-environmental-engineering-%2300096512-at-missouri-university-of-science-and-technology-4442271248</t>
+          <t>https://jobs.chronicle.com/job/38039154/tenure-track-assistant-professor-ai-for-automotive-and-mobility-systems/</t>
         </is>
       </c>
       <c r="N113" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="P113" s="2" t="inlineStr">
@@ -11066,31 +11078,31 @@
         </is>
       </c>
       <c r="R113" s="2" t="n">
-        <v>37.9532435</v>
+        <v>40.0067</v>
       </c>
       <c r="S113" s="2" t="n">
-        <v>-91.7742667</v>
+        <v>-83.0305</v>
       </c>
       <c r="T113" s="2" t="inlineStr">
         <is>
-          <t>4fad8c46021c1243</t>
+          <t>b5690754b2f4d69a</t>
         </is>
       </c>
     </row>
     <row r="114" ht="26" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor in Supply Chain Management</t>
+          <t>Tenure Track Assistant Professor of Industrial and Manufacturing Engineering</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Iowa State University</t>
+          <t>California State Polytechnic University, Pomona</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Department of Supply Chain Management, Ivy College of Business</t>
+          <t>Industrial and Manufacturing Engineering Department</t>
         </is>
       </c>
       <c r="D114" s="3" t="n">
@@ -11098,12 +11110,12 @@
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>This is a business school position focused on supply chain management rather than transportation engineering or urban mobility systems.</t>
+          <t>This is an Industrial and Manufacturing Engineering position focusing on human-system integration and ergonomics, which does not align with the candidate's core expertise in transportation engineering and planning.</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Management, Logistics, Operations</t>
+          <t>Human-System Integration, Human Factors and Ergonomics, Intelligent Systems, Decision Sciences</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
@@ -11113,15 +11125,19 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>Ames, IA</t>
+          <t>Pomona, CA</t>
         </is>
       </c>
       <c r="I114" s="3" t="inlineStr">
         <is>
-          <t>Posted 2 months ago</t>
-        </is>
-      </c>
-      <c r="J114" s="3" t="inlineStr"/>
+          <t>Priority: 2026-10-01 / Final: Open until filled</t>
+        </is>
+      </c>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
           <t>Not specified</t>
@@ -11129,22 +11145,22 @@
       </c>
       <c r="L114" s="4" t="inlineStr">
         <is>
-          <t>Iowa State University seeks a tenure-track Assistant Professor in Supply Chain Management to conduct research and teach courses at the undergraduate, master's, and Ph.D. levels, requiring a doctorate in business administration, supply chain, transportation, logistics, operations, or a related field. | Research Topics: Supply Chain Management, Logistics, Operations</t>
+          <t>The position seeks a tenure-track Assistant Professor with expertise in human-system integration and decision sciences, requiring a Ph.D. in Industrial Engineering, Manufacturing Engineering, or a closely related field. | Research Topics: Human-System Integration, Human Factors and Ergonomics, Intelligent Systems, Decision Sciences</t>
         </is>
       </c>
       <c r="M114" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-in-supply-chain-management-at-iowa-state-university-ivy-college-of-business-4440811209</t>
+          <t>https://engineering.academickeys.com/job/v0ih9zfg/Tenure-Track-Faculty-Position</t>
         </is>
       </c>
       <c r="N114" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>AcademicKeys</t>
         </is>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="P114" s="2" t="inlineStr">
@@ -11158,44 +11174,44 @@
         </is>
       </c>
       <c r="R114" s="2" t="n">
-        <v>42.0267567</v>
+        <v>34.0556686</v>
       </c>
       <c r="S114" s="2" t="n">
-        <v>-93.6170448</v>
+        <v>-117.8239282</v>
       </c>
       <c r="T114" s="2" t="inlineStr">
         <is>
-          <t>e994e392d38b77ce</t>
+          <t>f2c11f1e74c28de6</t>
         </is>
       </c>
     </row>
     <row r="115" ht="26" customHeight="1">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor in Urban and Regional Planning</t>
+          <t>Assistant Professor of Mechanical Engineering</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Louisiana State University New Orleans</t>
+          <t>University of Alabama</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Department of Planning and Urban Studies</t>
-        </is>
-      </c>
-      <c r="D115" s="8" t="n">
-        <v>8</v>
+          <t>Department of Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>Strong interdisciplinary fit for an Assistant Professor in Urban and Regional Planning with a specific interest in transportation planning, GIS, and spatial analytics.</t>
+          <t>The position is in Mechanical Engineering requiring a Ph.D. in ME or IE, offering only incidental overlap with the candidate's core background in transportation engineering and travel behavior analysis.</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>Urban and Regional Planning, Transportation Planning, GIS and Spatial Analytics, Climate Adaptation and Environmental Planning</t>
+          <t>Future Mobility, Autonomous Transportation, Smart Infrastructure, Operations Research and Data Analytics</t>
         </is>
       </c>
       <c r="G115" s="3" t="inlineStr">
@@ -11205,12 +11221,12 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>New Orleans, LA</t>
+          <t>Tuscaloosa, AL</t>
         </is>
       </c>
       <c r="I115" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>Priority: 2026-10-01 / Open until filled</t>
         </is>
       </c>
       <c r="J115" s="3" t="inlineStr">
@@ -11220,27 +11236,27 @@
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>DOE</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L115" s="4" t="inlineStr">
         <is>
-          <t>LSU New Orleans seeks a tenure-track Assistant Professor in Urban and Regional Planning to teach graduate courses in the MURP program, mentor students, and maintain an active research agenda requiring a Ph.D. in Urban and Regional Planning or a closely related field. | Research Topics: Urban and Regional Planning, Transportation Planning, GIS and Spatial Analytics, Climate Adaptation and Environmental Planning</t>
+          <t>The Department of Mechanical Engineering at the University of Alabama seeks tenure-track Assistant Professor candidates with a Ph.D. in Mechanical Engineering, Industrial Engineering, or a closely related discipline. | Research Topics: Future Mobility, Autonomous Transportation, Smart Infrastructure, Operations Research and Data Analytics</t>
         </is>
       </c>
       <c r="M115" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38025681/assistant-professor-planning-and-urban-studies-/</t>
+          <t>https://engineering.academickeys.com/job/7tojey4s/Mechanical-Engineering--Assistant-Professor</t>
         </is>
       </c>
       <c r="N115" s="3" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>AcademicKeys</t>
         </is>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="P115" s="2" t="inlineStr">
@@ -11254,44 +11270,44 @@
         </is>
       </c>
       <c r="R115" s="2" t="n">
-        <v>29.9911944</v>
+        <v>33.2120822</v>
       </c>
       <c r="S115" s="2" t="n">
-        <v>-90.0835067</v>
+        <v>-87.53967350000001</v>
       </c>
       <c r="T115" s="2" t="inlineStr">
         <is>
-          <t>f373f0209d1c2577</t>
+          <t>7c4b58541d6f5578</t>
         </is>
       </c>
     </row>
     <row r="116" ht="26" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Civil, Construction and Environmental Engineering (Transportation Engineering)</t>
+          <t>Assistant Professor in Industrial Engineering</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>University of Alabama</t>
+          <t>California Polytechnic State University - San Luis Obispo</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Department of Civil, Construction and Environmental Engineering</t>
-        </is>
-      </c>
-      <c r="D116" s="8" t="n">
-        <v>8</v>
+          <t>Industrial and Manufacturing Engineering (IME) Department</t>
+        </is>
+      </c>
+      <c r="D116" s="7" t="n">
+        <v>7</v>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>Tenure-track Assistant Professor position in Civil Engineering explicitly recruiting in Transportation Engineering with focus areas including public transportation, network analysis, data science, and transportation planning.</t>
+          <t>This is an Industrial Engineering Assistant Professor position seeking AI and data analytics specialization with explicitly listed application areas including transportation, aligning with the candidate's interdisciplinary mobility expertise.</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>Transportation Systems &amp; Planning, Public Transportation, Network Analysis &amp; Big Data in Transportation, Multimodal Transportation Safety &amp; Operations</t>
+          <t>Data Analytics, Artificial Intelligence, Transportation Systems, Operations Research</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
@@ -11301,47 +11317,47 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>Tuscaloosa, AL</t>
+          <t>San Luis Obispo, CA</t>
         </is>
       </c>
       <c r="I116" s="3" t="inlineStr">
         <is>
-          <t>Priority: 2026-10-01 / Final: Open until filled</t>
+          <t>Priority: 2026-09-30</t>
         </is>
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>$106,000 - $117,000 per year</t>
         </is>
       </c>
       <c r="L116" s="4" t="inlineStr">
         <is>
-          <t>The Department of Civil, Construction and Environmental Engineering seeks a tenure-track Assistant Professor in Transportation Engineering and related civil disciplines with an earned Ph.D. in Civil Engineering or a closely related field. | Research Topics: Transportation Systems &amp; Planning, Public Transportation, Network Analysis &amp; Big Data in Transportation, Multimodal Transportation Safety &amp; Operations</t>
+          <t>This is a tenure-track Assistant Professor role in Industrial Engineering focusing on data analytics and AI with application areas including transportation, requiring a Ph.D. in industrial engineering, operations research, or a closely related field. | Research Topics: Data Analytics, Artificial Intelligence, Transportation Systems, Operations Research</t>
         </is>
       </c>
       <c r="M116" s="5" t="inlineStr">
         <is>
-          <t>https://engineering.academickeys.com/job/02ixzgls/Civil-Construction-and-Environmental-Engineering--Assistant-Professor</t>
+          <t>https://jobs.chronicle.com/job/38018328/assistant-professor-industrial-engineering/</t>
         </is>
       </c>
       <c r="N116" s="3" t="inlineStr">
         <is>
-          <t>AcademicKeys</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Q116" s="6" t="inlineStr">
@@ -11350,44 +11366,44 @@
         </is>
       </c>
       <c r="R116" s="2" t="n">
-        <v>33.2120822</v>
+        <v>35.3074623</v>
       </c>
       <c r="S116" s="2" t="n">
-        <v>-87.53967350000001</v>
+        <v>-120.6646483</v>
       </c>
       <c r="T116" s="2" t="inlineStr">
         <is>
-          <t>f80ad2336a210f82</t>
+          <t>78cbe3317d3f9c95</t>
         </is>
       </c>
     </row>
     <row r="117" ht="26" customHeight="1">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Tenure-track Assistant Professor – AI for Automotive and Mobility Systems</t>
+          <t>Assistant or Associate Professor of Urban Planning/Geography</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>The Ohio State University</t>
+          <t>Loyola Marymount University</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Department of Mechanical and Aerospace Engineering</t>
-        </is>
-      </c>
-      <c r="D117" s="3" t="n">
-        <v>4</v>
+          <t>Department of Urban and Environmental Studies</t>
+        </is>
+      </c>
+      <c r="D117" s="7" t="n">
+        <v>7</v>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>While the position focuses on AI for ground transportation and mobility, it is based in Mechanical and Aerospace Engineering with a primary focus on automotive engineering, control, and vehicle dynamics rather than transportation planning and systems engineering.</t>
+          <t>This tenure-track position in urban planning and urban geography strongly matches the candidate's M.S. and B.S. background in urban planning and explicitly encourages transportation and land use specializations.</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>AI for Ground Transportation, Automotive and Mobility Systems, Vehicle Control and Optimization, Intelligent Infrastructure</t>
+          <t>Transportation and Land Use, Urban Planning, Sustainable Urbanism, Racial and Environmental Justice</t>
         </is>
       </c>
       <c r="G117" s="3" t="inlineStr">
@@ -11397,32 +11413,32 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>Columbus, OH</t>
+          <t>Los Angeles, CA</t>
         </is>
       </c>
       <c r="I117" s="3" t="inlineStr">
         <is>
-          <t>Priority: 2026-10-01 / Final: Open until filled</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>$92,000</t>
         </is>
       </c>
       <c r="L117" s="4" t="inlineStr">
         <is>
-          <t>The Department of Mechanical and Aerospace Engineering seeks a tenure-track assistant professor applying AI/ML to automotive and ground mobility systems, requiring a doctorate in mechanical engineering or a closely related discipline. | Research Topics: AI for Ground Transportation, Automotive and Mobility Systems, Vehicle Control and Optimization, Intelligent Infrastructure</t>
+          <t>This tenure-line position seeks an emerging scholar in urban planning or urban geography with expertise in areas including transportation and land use, requiring a Ph.D. in urban studies, planning, geography, or a closely related field by August 2027. | Research Topics: Transportation and Land Use, Urban Planning, Sustainable Urbanism, Racial and Environmental Justice</t>
         </is>
       </c>
       <c r="M117" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38039154/tenure-track-assistant-professor-ai-for-automotive-and-mobility-systems/</t>
+          <t>https://jobs.chronicle.com/job/38031694/assistant-professor-of-urban-planning-geography/</t>
         </is>
       </c>
       <c r="N117" s="3" t="inlineStr">
@@ -11432,7 +11448,7 @@
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="P117" s="2" t="inlineStr">
@@ -11446,44 +11462,44 @@
         </is>
       </c>
       <c r="R117" s="2" t="n">
-        <v>40.0067</v>
+        <v>33.9687824</v>
       </c>
       <c r="S117" s="2" t="n">
-        <v>-83.0305</v>
+        <v>-118.4182021</v>
       </c>
       <c r="T117" s="2" t="inlineStr">
         <is>
-          <t>b5690754b2f4d69a</t>
+          <t>c13b0c3f0cf09a9e</t>
         </is>
       </c>
     </row>
     <row r="118" ht="26" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Tenure Track Assistant Professor of Industrial and Manufacturing Engineering</t>
+          <t>Assistant / Associate Professor of Industrial and Systems Engineering</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>California State Polytechnic University, Pomona</t>
+          <t>University of Washington</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Industrial and Manufacturing Engineering Department</t>
-        </is>
-      </c>
-      <c r="D118" s="3" t="n">
-        <v>3</v>
+          <t>Industrial &amp; Systems Engineering</t>
+        </is>
+      </c>
+      <c r="D118" s="7" t="n">
+        <v>6</v>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>This is an Industrial and Manufacturing Engineering position focusing on human-system integration and ergonomics, which does not align with the candidate's core expertise in transportation engineering and planning.</t>
+          <t>Assistant Professor position in Systems Engineering that aligns with the candidate's expertise in AI-enabled systems and smart mobility through the lens of cyber-physical and autonomous systems.</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>Human-System Integration, Human Factors and Ergonomics, Intelligent Systems, Decision Sciences</t>
+          <t>Systems Engineering, Autonomous Systems, Cyber-Physical Systems, AI-Enabled Systems Engineering</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
@@ -11493,32 +11509,32 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>Pomona, CA</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="I118" s="3" t="inlineStr">
         <is>
-          <t>Priority: 2026-10-01 / Final: Open until filled</t>
+          <t>Priority: 2026-09-15 / Open until filled</t>
         </is>
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>$12,000 – $17,000 per month (9-month service period)</t>
         </is>
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
-          <t>The position seeks a tenure-track Assistant Professor with expertise in human-system integration and decision sciences, requiring a Ph.D. in Industrial Engineering, Manufacturing Engineering, or a closely related field. | Research Topics: Human-System Integration, Human Factors and Ergonomics, Intelligent Systems, Decision Sciences</t>
+          <t>The Department of Industrial and Systems Engineering at the University of Washington seeks an Assistant or Associate Professor specializing in Systems Engineering, requiring a Ph.D. in Systems Engineering, Industrial Engineering, or a related discipline. | Research Topics: Systems Engineering, Autonomous Systems, Cyber-Physical Systems, AI-Enabled Systems Engineering</t>
         </is>
       </c>
       <c r="M118" s="5" t="inlineStr">
         <is>
-          <t>https://engineering.academickeys.com/job/v0ih9zfg/Tenure-Track-Faculty-Position</t>
+          <t>https://engineering.academickeys.com/job/g4m97a60/AssistantAssociate-Professor-Industrial-and-Systems-Engineering-Systems-Engineering-Focus</t>
         </is>
       </c>
       <c r="N118" s="3" t="inlineStr">
@@ -11528,7 +11544,7 @@
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="P118" s="2" t="inlineStr">
@@ -11542,31 +11558,31 @@
         </is>
       </c>
       <c r="R118" s="2" t="n">
-        <v>34.0556686</v>
+        <v>47.6553</v>
       </c>
       <c r="S118" s="2" t="n">
-        <v>-117.8239282</v>
+        <v>-122.3035</v>
       </c>
       <c r="T118" s="2" t="inlineStr">
         <is>
-          <t>f2c11f1e74c28de6</t>
+          <t>9d5682cf4dbca334</t>
         </is>
       </c>
     </row>
     <row r="119" ht="26" customHeight="1">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Mechanical Engineering</t>
+          <t>Assistant Professor of Information Systems</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>University of Alabama</t>
+          <t>California State University, Long Beach</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Department of Mechanical Engineering</t>
+          <t>Department of Information Systems, College of Business</t>
         </is>
       </c>
       <c r="D119" s="3" t="n">
@@ -11574,12 +11590,12 @@
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>The position is in Mechanical Engineering requiring a Ph.D. in ME or IE, offering only incidental overlap with the candidate's core background in transportation engineering and travel behavior analysis.</t>
+          <t>The position is housed within a Business School's Information Systems department with a focus on business analytics and cybersecurity, offering very low alignment with the candidate's core specialization in transportation systems engineering.</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>Future Mobility, Autonomous Transportation, Smart Infrastructure, Operations Research and Data Analytics</t>
+          <t>Artificial Intelligence, Business Analytics, Information Systems</t>
         </is>
       </c>
       <c r="G119" s="3" t="inlineStr">
@@ -11589,42 +11605,42 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>Tuscaloosa, AL</t>
+          <t>Long Beach, CA</t>
         </is>
       </c>
       <c r="I119" s="3" t="inlineStr">
         <is>
-          <t>Priority: 2026-10-01 / Open until filled</t>
+          <t>Priority: 2026-08-17 / Final: Open until filled</t>
         </is>
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>$10,916 to $11,750 per month (anticipated hiring range)</t>
         </is>
       </c>
       <c r="L119" s="4" t="inlineStr">
         <is>
-          <t>The Department of Mechanical Engineering at the University of Alabama seeks tenure-track Assistant Professor candidates with a Ph.D. in Mechanical Engineering, Industrial Engineering, or a closely related discipline. | Research Topics: Future Mobility, Autonomous Transportation, Smart Infrastructure, Operations Research and Data Analytics</t>
+          <t>This tenure-track position seeks an Assistant Professor to teach and conduct research in artificial intelligence, business analytics, and cybersecurity, requiring a Ph.D. in business, engineering, or a related science field. | Research Topics: Artificial Intelligence, Business Analytics, Information Systems</t>
         </is>
       </c>
       <c r="M119" s="5" t="inlineStr">
         <is>
-          <t>https://engineering.academickeys.com/job/7tojey4s/Mechanical-Engineering--Assistant-Professor</t>
+          <t>https://jobs.chronicle.com/job/38037935/assistant-professor-of-information-systems-2-open-positions-/</t>
         </is>
       </c>
       <c r="N119" s="3" t="inlineStr">
         <is>
-          <t>AcademicKeys</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="P119" s="2" t="inlineStr">
@@ -11632,50 +11648,50 @@
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="Q119" s="6" t="inlineStr">
-        <is>
-          <t>Active</t>
+      <c r="Q119" s="9" t="inlineStr">
+        <is>
+          <t>Past Due</t>
         </is>
       </c>
       <c r="R119" s="2" t="n">
-        <v>33.2120822</v>
+        <v>33.7817709</v>
       </c>
       <c r="S119" s="2" t="n">
-        <v>-87.53967350000001</v>
+        <v>-118.1152001</v>
       </c>
       <c r="T119" s="2" t="inlineStr">
         <is>
-          <t>7c4b58541d6f5578</t>
+          <t>3d6c2762d8d6386a</t>
         </is>
       </c>
     </row>
     <row r="120" ht="26" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor in Industrial Engineering</t>
+          <t>Assistant Professor of Transportation Engineering</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>California Polytechnic State University - San Luis Obispo</t>
+          <t>South Dakota State University</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Industrial and Manufacturing Engineering (IME) Department</t>
-        </is>
-      </c>
-      <c r="D120" s="7" t="n">
-        <v>7</v>
+          <t>Department of Civil and Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="D120" s="8" t="n">
+        <v>9</v>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>This is an Industrial Engineering Assistant Professor position seeking AI and data analytics specialization with explicitly listed application areas including transportation, aligning with the candidate's interdisciplinary mobility expertise.</t>
+          <t>This is a tenure-track Assistant Professor position in Transportation Engineering within a Civil and Environmental Engineering department, perfectly aligning with the candidate's core research profile.</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>Data Analytics, Artificial Intelligence, Transportation Systems, Operations Research</t>
+          <t>Intelligent Transportation Systems, Transportation Data Analytics, Traffic Operations, Resilient Transportation Systems</t>
         </is>
       </c>
       <c r="G120" s="3" t="inlineStr">
@@ -11685,138 +11701,138 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>San Luis Obispo, CA</t>
+          <t>Brookings, SD</t>
         </is>
       </c>
       <c r="I120" s="3" t="inlineStr">
         <is>
-          <t>Priority: 2026-09-30</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>$106,000 - $117,000 per year</t>
+          <t>Starting at $92,000</t>
         </is>
       </c>
       <c r="L120" s="4" t="inlineStr">
         <is>
-          <t>This is a tenure-track Assistant Professor role in Industrial Engineering focusing on data analytics and AI with application areas including transportation, requiring a Ph.D. in industrial engineering, operations research, or a closely related field. | Research Topics: Data Analytics, Artificial Intelligence, Transportation Systems, Operations Research</t>
+          <t>South Dakota State University seeks a tenure-track Assistant Professor in Transportation Engineering to teach undergraduate and graduate courses, advise students, and develop an externally funded research program requiring a Ph.D. in Civil Engineering or a closely related field. | Research Topics: Intelligent Transportation Systems, Transportation Data Analytics, Traffic Operations, Resilient Transportation Systems</t>
         </is>
       </c>
       <c r="M120" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38018328/assistant-professor-industrial-engineering/</t>
+          <t>https://engineering.academickeys.com/job/m4lk5asr/Assistant-Professor-of-Transportation-Engineering</t>
         </is>
       </c>
       <c r="N120" s="3" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>AcademicKeys</t>
         </is>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="Q120" s="6" t="inlineStr">
-        <is>
-          <t>Active</t>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Q120" s="9" t="inlineStr">
+        <is>
+          <t>Past Due</t>
         </is>
       </c>
       <c r="R120" s="2" t="n">
-        <v>35.3074623</v>
+        <v>44.344449</v>
       </c>
       <c r="S120" s="2" t="n">
-        <v>-120.6646483</v>
+        <v>-96.79823709999999</v>
       </c>
       <c r="T120" s="2" t="inlineStr">
         <is>
-          <t>78cbe3317d3f9c95</t>
+          <t>9b7d5de4753a514b</t>
         </is>
       </c>
     </row>
     <row r="121" ht="26" customHeight="1">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Assistant or Associate Professor of Urban Planning/Geography</t>
+          <t>Teaching Faculty Position for First-Year Engineering</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Loyola Marymount University</t>
+          <t>Florida A&amp;M University - Florida State University College of Engineering</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Department of Urban and Environmental Studies</t>
-        </is>
-      </c>
-      <c r="D121" s="7" t="n">
-        <v>7</v>
+          <t>Office of Student Services and Undergraduate Affairs</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>This tenure-track position in urban planning and urban geography strongly matches the candidate's M.S. and B.S. background in urban planning and explicitly encourages transportation and land use specializations.</t>
+          <t>While the position is a permanent teaching faculty role, it focuses on general first-year engineering instruction and student affairs administration rather than transportation engineering or planning.</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>Transportation and Land Use, Urban Planning, Sustainable Urbanism, Racial and Environmental Justice</t>
+          <t>Engineering Education, First-Year Engineering Programming, Student Retention and Advising</t>
         </is>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Non-Tenure Track</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>Los Angeles, CA</t>
+          <t>Tallahassee, FL</t>
         </is>
       </c>
       <c r="I121" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>Priority: 2026-07-06 / Final: Open until filled</t>
         </is>
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>$92,000</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L121" s="4" t="inlineStr">
         <is>
-          <t>This tenure-line position seeks an emerging scholar in urban planning or urban geography with expertise in areas including transportation and land use, requiring a Ph.D. in urban studies, planning, geography, or a closely related field by August 2027. | Research Topics: Transportation and Land Use, Urban Planning, Sustainable Urbanism, Racial and Environmental Justice</t>
+          <t>This full-time, non-tenure-track teaching position involves leading first-year engineering laboratories and directing the Engineering Living Learning Community, requiring a Ph.D. in an engineering discipline or engineering education. | Research Topics: Engineering Education, First-Year Engineering Programming, Student Retention and Advising</t>
         </is>
       </c>
       <c r="M121" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38031694/assistant-professor-of-urban-planning-geography/</t>
+          <t>http://engineering.academickeys.com/job/jvd3l79c/Teaching-Faculty-Position-for-FirstYear-Engineering</t>
         </is>
       </c>
       <c r="N121" s="3" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>AcademicKeys</t>
         </is>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="P121" s="2" t="inlineStr">
@@ -11824,95 +11840,95 @@
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="Q121" s="6" t="inlineStr">
-        <is>
-          <t>Active</t>
+      <c r="Q121" s="9" t="inlineStr">
+        <is>
+          <t>Past Due</t>
         </is>
       </c>
       <c r="R121" s="2" t="n">
-        <v>33.9687824</v>
+        <v>30.4380832</v>
       </c>
       <c r="S121" s="2" t="n">
-        <v>-118.4182021</v>
+        <v>-84.28093320000001</v>
       </c>
       <c r="T121" s="2" t="inlineStr">
         <is>
-          <t>c13b0c3f0cf09a9e</t>
+          <t>0249d5be9bd5a4a1</t>
         </is>
       </c>
     </row>
     <row r="122" ht="26" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Assistant / Associate Professor of Industrial and Systems Engineering</t>
+          <t>Clinical Assistant Professor</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>University of Washington</t>
+          <t>Georgia State University</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Industrial &amp; Systems Engineering</t>
-        </is>
-      </c>
-      <c r="D122" s="7" t="n">
-        <v>6</v>
+          <t>Department of Public Management and Policy</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>Assistant Professor position in Systems Engineering that aligns with the candidate's expertise in AI-enabled systems and smart mobility through the lens of cyber-physical and autonomous systems.</t>
+          <t>This is a non-tenure-track clinical position in public management and policy focusing on teaching data analytics and urban planning, which is a poor fit for a candidate targeting research-active tenure-track positions in transportation engineering.</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>Systems Engineering, Autonomous Systems, Cyber-Physical Systems, AI-Enabled Systems Engineering</t>
+          <t>Policy Analytics, Urban Planning, Data Visualization, GIS Applications</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Non-Tenure Track</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="I122" s="3" t="inlineStr">
         <is>
-          <t>Priority: 2026-09-15 / Open until filled</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>$12,000 – $17,000 per month (9-month service period)</t>
+          <t>$80,000-$90,000</t>
         </is>
       </c>
       <c r="L122" s="4" t="inlineStr">
         <is>
-          <t>The Department of Industrial and Systems Engineering at the University of Washington seeks an Assistant or Associate Professor specializing in Systems Engineering, requiring a Ph.D. in Systems Engineering, Industrial Engineering, or a related discipline. | Research Topics: Systems Engineering, Autonomous Systems, Cyber-Physical Systems, AI-Enabled Systems Engineering</t>
+          <t>A non-tenure-track clinical assistant professor position focusing on teaching policy analytics, urban planning, and GIS, requiring a Ph.D. in a related field and university teaching experience. | Research Topics: Policy Analytics, Urban Planning, Data Visualization, GIS Applications</t>
         </is>
       </c>
       <c r="M122" s="5" t="inlineStr">
         <is>
-          <t>https://engineering.academickeys.com/job/g4m97a60/AssistantAssociate-Professor-Industrial-and-Systems-Engineering-Systems-Engineering-Focus</t>
+          <t>https://jobs.chronicle.com/job/38022215/clinical-assistant-professor-non-tenure-tack/</t>
         </is>
       </c>
       <c r="N122" s="3" t="inlineStr">
         <is>
-          <t>AcademicKeys</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="P122" s="2" t="inlineStr">
@@ -11920,402 +11936,18 @@
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="Q122" s="6" t="inlineStr">
-        <is>
-          <t>Active</t>
+      <c r="Q122" s="9" t="inlineStr">
+        <is>
+          <t>Past Due</t>
         </is>
       </c>
       <c r="R122" s="2" t="n">
-        <v>47.6553</v>
+        <v>33.7535889</v>
       </c>
       <c r="S122" s="2" t="n">
-        <v>-122.3035</v>
+        <v>-84.3854209</v>
       </c>
       <c r="T122" s="2" t="inlineStr">
-        <is>
-          <t>9d5682cf4dbca334</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="26" customHeight="1">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t>Assistant Professor of Information Systems</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>California State University, Long Beach</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>Department of Information Systems, College of Business</t>
-        </is>
-      </c>
-      <c r="D123" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E123" s="4" t="inlineStr">
-        <is>
-          <t>The position is housed within a Business School's Information Systems department with a focus on business analytics and cybersecurity, offering very low alignment with the candidate's core specialization in transportation systems engineering.</t>
-        </is>
-      </c>
-      <c r="F123" s="2" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence, Business Analytics, Information Systems</t>
-        </is>
-      </c>
-      <c r="G123" s="3" t="inlineStr">
-        <is>
-          <t>Tenure-Track</t>
-        </is>
-      </c>
-      <c r="H123" s="2" t="inlineStr">
-        <is>
-          <t>Long Beach, CA</t>
-        </is>
-      </c>
-      <c r="I123" s="3" t="inlineStr">
-        <is>
-          <t>Priority: 2026-08-17 / Final: Open until filled</t>
-        </is>
-      </c>
-      <c r="J123" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="K123" s="2" t="inlineStr">
-        <is>
-          <t>$10,916 to $11,750 per month (anticipated hiring range)</t>
-        </is>
-      </c>
-      <c r="L123" s="4" t="inlineStr">
-        <is>
-          <t>This tenure-track position seeks an Assistant Professor to teach and conduct research in artificial intelligence, business analytics, and cybersecurity, requiring a Ph.D. in business, engineering, or a related science field. | Research Topics: Artificial Intelligence, Business Analytics, Information Systems</t>
-        </is>
-      </c>
-      <c r="M123" s="5" t="inlineStr">
-        <is>
-          <t>https://jobs.chronicle.com/job/38037935/assistant-professor-of-information-systems-2-open-positions-/</t>
-        </is>
-      </c>
-      <c r="N123" s="3" t="inlineStr">
-        <is>
-          <t>Chronicle</t>
-        </is>
-      </c>
-      <c r="O123" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="P123" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="Q123" s="9" t="inlineStr">
-        <is>
-          <t>Past Due</t>
-        </is>
-      </c>
-      <c r="R123" s="2" t="n">
-        <v>33.7817709</v>
-      </c>
-      <c r="S123" s="2" t="n">
-        <v>-118.1152001</v>
-      </c>
-      <c r="T123" s="2" t="inlineStr">
-        <is>
-          <t>3d6c2762d8d6386a</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="26" customHeight="1">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>Assistant Professor of Transportation Engineering</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>South Dakota State University</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>Department of Civil and Environmental Engineering</t>
-        </is>
-      </c>
-      <c r="D124" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="E124" s="4" t="inlineStr">
-        <is>
-          <t>This is a tenure-track Assistant Professor position in Transportation Engineering within a Civil and Environmental Engineering department, perfectly aligning with the candidate's core research profile.</t>
-        </is>
-      </c>
-      <c r="F124" s="2" t="inlineStr">
-        <is>
-          <t>Intelligent Transportation Systems, Transportation Data Analytics, Traffic Operations, Resilient Transportation Systems</t>
-        </is>
-      </c>
-      <c r="G124" s="3" t="inlineStr">
-        <is>
-          <t>Tenure-Track</t>
-        </is>
-      </c>
-      <c r="H124" s="2" t="inlineStr">
-        <is>
-          <t>Brookings, SD</t>
-        </is>
-      </c>
-      <c r="I124" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="J124" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="K124" s="2" t="inlineStr">
-        <is>
-          <t>Starting at $92,000</t>
-        </is>
-      </c>
-      <c r="L124" s="4" t="inlineStr">
-        <is>
-          <t>South Dakota State University seeks a tenure-track Assistant Professor in Transportation Engineering to teach undergraduate and graduate courses, advise students, and develop an externally funded research program requiring a Ph.D. in Civil Engineering or a closely related field. | Research Topics: Intelligent Transportation Systems, Transportation Data Analytics, Traffic Operations, Resilient Transportation Systems</t>
-        </is>
-      </c>
-      <c r="M124" s="5" t="inlineStr">
-        <is>
-          <t>https://engineering.academickeys.com/job/m4lk5asr/Assistant-Professor-of-Transportation-Engineering</t>
-        </is>
-      </c>
-      <c r="N124" s="3" t="inlineStr">
-        <is>
-          <t>AcademicKeys</t>
-        </is>
-      </c>
-      <c r="O124" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="P124" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="Q124" s="9" t="inlineStr">
-        <is>
-          <t>Past Due</t>
-        </is>
-      </c>
-      <c r="R124" s="2" t="n">
-        <v>44.344449</v>
-      </c>
-      <c r="S124" s="2" t="n">
-        <v>-96.79823709999999</v>
-      </c>
-      <c r="T124" s="2" t="inlineStr">
-        <is>
-          <t>9b7d5de4753a514b</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="26" customHeight="1">
-      <c r="A125" s="2" t="inlineStr">
-        <is>
-          <t>Teaching Faculty Position for First-Year Engineering</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>Florida A&amp;M University - Florida State University College of Engineering</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>Office of Student Services and Undergraduate Affairs</t>
-        </is>
-      </c>
-      <c r="D125" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E125" s="4" t="inlineStr">
-        <is>
-          <t>While the position is a permanent teaching faculty role, it focuses on general first-year engineering instruction and student affairs administration rather than transportation engineering or planning.</t>
-        </is>
-      </c>
-      <c r="F125" s="2" t="inlineStr">
-        <is>
-          <t>Engineering Education, First-Year Engineering Programming, Student Retention and Advising</t>
-        </is>
-      </c>
-      <c r="G125" s="3" t="inlineStr">
-        <is>
-          <t>Non-Tenure Track</t>
-        </is>
-      </c>
-      <c r="H125" s="2" t="inlineStr">
-        <is>
-          <t>Tallahassee, FL</t>
-        </is>
-      </c>
-      <c r="I125" s="3" t="inlineStr">
-        <is>
-          <t>Priority: 2026-07-06 / Final: Open until filled</t>
-        </is>
-      </c>
-      <c r="J125" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="K125" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="L125" s="4" t="inlineStr">
-        <is>
-          <t>This full-time, non-tenure-track teaching position involves leading first-year engineering laboratories and directing the Engineering Living Learning Community, requiring a Ph.D. in an engineering discipline or engineering education. | Research Topics: Engineering Education, First-Year Engineering Programming, Student Retention and Advising</t>
-        </is>
-      </c>
-      <c r="M125" s="5" t="inlineStr">
-        <is>
-          <t>http://engineering.academickeys.com/job/jvd3l79c/Teaching-Faculty-Position-for-FirstYear-Engineering</t>
-        </is>
-      </c>
-      <c r="N125" s="3" t="inlineStr">
-        <is>
-          <t>AcademicKeys</t>
-        </is>
-      </c>
-      <c r="O125" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="P125" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="Q125" s="9" t="inlineStr">
-        <is>
-          <t>Past Due</t>
-        </is>
-      </c>
-      <c r="R125" s="2" t="n">
-        <v>30.4380832</v>
-      </c>
-      <c r="S125" s="2" t="n">
-        <v>-84.28093320000001</v>
-      </c>
-      <c r="T125" s="2" t="inlineStr">
-        <is>
-          <t>0249d5be9bd5a4a1</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="26" customHeight="1">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t>Clinical Assistant Professor</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>Georgia State University</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>Department of Public Management and Policy</t>
-        </is>
-      </c>
-      <c r="D126" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E126" s="4" t="inlineStr">
-        <is>
-          <t>This is a non-tenure-track clinical position in public management and policy focusing on teaching data analytics and urban planning, which is a poor fit for a candidate targeting research-active tenure-track positions in transportation engineering.</t>
-        </is>
-      </c>
-      <c r="F126" s="2" t="inlineStr">
-        <is>
-          <t>Policy Analytics, Urban Planning, Data Visualization, GIS Applications</t>
-        </is>
-      </c>
-      <c r="G126" s="3" t="inlineStr">
-        <is>
-          <t>Non-Tenure Track</t>
-        </is>
-      </c>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t>Atlanta, GA</t>
-        </is>
-      </c>
-      <c r="I126" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="J126" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="K126" s="2" t="inlineStr">
-        <is>
-          <t>$80,000-$90,000</t>
-        </is>
-      </c>
-      <c r="L126" s="4" t="inlineStr">
-        <is>
-          <t>A non-tenure-track clinical assistant professor position focusing on teaching policy analytics, urban planning, and GIS, requiring a Ph.D. in a related field and university teaching experience. | Research Topics: Policy Analytics, Urban Planning, Data Visualization, GIS Applications</t>
-        </is>
-      </c>
-      <c r="M126" s="5" t="inlineStr">
-        <is>
-          <t>https://jobs.chronicle.com/job/38022215/clinical-assistant-professor-non-tenure-tack/</t>
-        </is>
-      </c>
-      <c r="N126" s="3" t="inlineStr">
-        <is>
-          <t>Chronicle</t>
-        </is>
-      </c>
-      <c r="O126" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="P126" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="Q126" s="9" t="inlineStr">
-        <is>
-          <t>Past Due</t>
-        </is>
-      </c>
-      <c r="R126" s="2" t="n">
-        <v>33.7535889</v>
-      </c>
-      <c r="S126" s="2" t="n">
-        <v>-84.3854209</v>
-      </c>
-      <c r="T126" s="2" t="inlineStr">
         <is>
           <t>f39f14cbaaf9d6f7</t>
         </is>
@@ -12444,10 +12076,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M120" r:id="rId119"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M121" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M122" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M123" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M124" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M125" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M126" r:id="rId125"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -834,7 +834,7 @@
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R3" s="6" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R5" s="6" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R7" s="6" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R9" s="6" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R10" s="6" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R15" s="6" t="inlineStr">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R17" s="6" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R18" s="6" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R19" s="6" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R20" s="6" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R21" s="6" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R23" s="6" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R24" s="6" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R27" s="6" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R28" s="6" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R29" s="6" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R30" s="6" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R31" s="6" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R32" s="6" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R33" s="6" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R34" s="6" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R35" s="6" t="inlineStr">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R37" s="6" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R39" s="6" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R41" s="6" t="inlineStr">
@@ -4770,7 +4770,7 @@
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R44" s="6" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R45" s="6" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="Q47" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R47" s="6" t="inlineStr">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R48" s="6" t="inlineStr">
@@ -5250,7 +5250,7 @@
       </c>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R49" s="6" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R50" s="6" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="Q56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R56" s="6" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="Q57" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R57" s="6" t="inlineStr">
@@ -6114,7 +6114,7 @@
       </c>
       <c r="Q58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="Q59" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R59" s="6" t="inlineStr">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R60" s="6" t="inlineStr">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="Q61" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R61" s="6" t="inlineStr">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R62" s="6" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="Q63" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R63" s="6" t="inlineStr">
@@ -6690,7 +6690,7 @@
       </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R64" s="6" t="inlineStr">
@@ -6882,7 +6882,7 @@
       </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R66" s="6" t="inlineStr">
@@ -7458,7 +7458,7 @@
       </c>
       <c r="Q72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R72" s="6" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="Q73" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R73" s="6" t="inlineStr">
@@ -7650,7 +7650,7 @@
       </c>
       <c r="Q74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R74" s="6" t="inlineStr">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="Q75" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R75" s="6" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="Q76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R76" s="6" t="inlineStr">
@@ -7938,7 +7938,7 @@
       </c>
       <c r="Q77" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R77" s="6" t="inlineStr">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="Q78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R78" s="6" t="inlineStr">
@@ -8130,7 +8130,7 @@
       </c>
       <c r="Q79" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R79" s="6" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="Q80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R80" s="6" t="inlineStr">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="Q84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R84" s="6" t="inlineStr">
@@ -8702,7 +8702,7 @@
       </c>
       <c r="Q85" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R85" s="6" t="inlineStr">
@@ -8794,7 +8794,7 @@
       </c>
       <c r="Q86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R86" s="6" t="inlineStr">
@@ -8978,7 +8978,7 @@
       </c>
       <c r="Q88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R88" s="6" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="Q89" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R89" s="6" t="inlineStr">
@@ -10358,7 +10358,7 @@
       </c>
       <c r="Q103" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R103" s="6" t="inlineStr">
@@ -11186,7 +11186,7 @@
       </c>
       <c r="Q112" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R112" s="6" t="inlineStr">
@@ -11738,7 +11738,7 @@
       </c>
       <c r="Q118" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R118" s="6" t="inlineStr">
@@ -11922,7 +11922,7 @@
       </c>
       <c r="Q120" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R120" s="6" t="inlineStr">
@@ -12106,7 +12106,7 @@
       </c>
       <c r="Q122" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R122" s="6" t="inlineStr">
@@ -12216,22 +12216,22 @@
     <row r="124" ht="26" customHeight="1">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>d5a49d24514fc7df</t>
+          <t>1d556090a8d4016a</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Open Rank Faculty Position in Computer Science</t>
+          <t>Assistant Professor of Electrical and Computer Engineering</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>The University of Texas at Dallas</t>
+          <t>The University of Memphis</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Department of Computer Science</t>
+          <t>Electrical and Computer Engineering (EECE)</t>
         </is>
       </c>
       <c r="E124" s="3" t="n">
@@ -12239,12 +12239,12 @@
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>General Computer Science faculty search lacking a dedicated transportation or travel behavior focus.</t>
+          <t>The position is in Electrical and Computer Engineering with peripheral overlap in electric transportation, but lacks a primary focus on transportation systems engineering.</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>Computer Science, Algorithms, Software Systems</t>
+          <t>Electric Transportation, Smart Grids and Microgrids, Cyber-Physical Systems</t>
         </is>
       </c>
       <c r="H124" s="3" t="inlineStr">
@@ -12254,7 +12254,7 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>Dallas, TX</t>
+          <t>Memphis, TN</t>
         </is>
       </c>
       <c r="J124" s="3" t="inlineStr">
@@ -12265,17 +12265,17 @@
       <c r="K124" s="3" t="inlineStr"/>
       <c r="L124" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Commensurate with education and experience</t>
         </is>
       </c>
       <c r="M124" s="4" t="inlineStr">
         <is>
-          <t>This open-rank faculty position in Computer Science seeks qualified researchers and educators with a Ph.D. in computer science or a closely related field. | Research Topics: Computer Science, Algorithms, Software Systems</t>
+          <t>The Department of Electrical and Computer Engineering at the University of Memphis invites applications for a tenure-track Assistant Professor position requiring a Ph.D. in electrical and computer engineering or a closely related discipline. | Research Topics: Electric Transportation, Smart Grids and Microgrids, Cyber-Physical Systems</t>
         </is>
       </c>
       <c r="N124" s="5" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179594704&amp;Title=Open%20Rank%20Faculty%20Position%20in%20Computer%20Science</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179603273&amp;Title=Assistant%20Professor</t>
         </is>
       </c>
       <c r="O124" s="3" t="inlineStr">
@@ -12285,12 +12285,12 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R124" s="6" t="inlineStr">
@@ -12299,31 +12299,31 @@
         </is>
       </c>
       <c r="S124" s="2" t="n">
-        <v>32.9785262</v>
+        <v>35.1189387</v>
       </c>
       <c r="T124" s="2" t="n">
-        <v>-96.7553288</v>
+        <v>-89.93721960000001</v>
       </c>
     </row>
     <row r="125" ht="26" customHeight="1">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>8220b83ca4262093</t>
+          <t>d5a49d24514fc7df</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor - Fintech and Cyber Risk</t>
+          <t>Open Rank Faculty Position in Computer Science</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>University of California, Berkeley</t>
+          <t>The University of Texas at Dallas</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Industrial Engineering &amp; Operations Research</t>
+          <t>Department of Computer Science</t>
         </is>
       </c>
       <c r="E125" s="3" t="n">
@@ -12331,12 +12331,12 @@
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>Low fit: The position is in Industrial Engineering and Operations Research focusing on fintech and cyber risk, lacking a direct focus on passenger transportation or mobility.</t>
+          <t>General Computer Science faculty search lacking a dedicated transportation or travel behavior focus.</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Fintech, Cyber Risk, Operations Research</t>
+          <t>Computer Science, Algorithms, Software Systems</t>
         </is>
       </c>
       <c r="H125" s="3" t="inlineStr">
@@ -12346,7 +12346,7 @@
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>Berkeley, CA</t>
+          <t>Dallas, TX</t>
         </is>
       </c>
       <c r="J125" s="3" t="inlineStr">
@@ -12357,17 +12357,17 @@
       <c r="K125" s="3" t="inlineStr"/>
       <c r="L125" s="2" t="inlineStr">
         <is>
-          <t>$111,400 - $163,200 per year</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="M125" s="4" t="inlineStr">
         <is>
-          <t>The Department of Industrial Engineering &amp; Operations Research at UC Berkeley invites applications for a tenure-track Assistant Professor position focusing on fintech and cyber risk, requiring an earned Ph.D. | Research Topics: Fintech, Cyber Risk, Operations Research</t>
+          <t>This open-rank faculty position in Computer Science seeks qualified researchers and educators with a Ph.D. in computer science or a closely related field. | Research Topics: Computer Science, Algorithms, Software Systems</t>
         </is>
       </c>
       <c r="N125" s="5" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179595173&amp;Title=Assistant%20Professor%20%2D%20Fintech%20and%20Cyber%20Risk%20%2D%20Industrial%20Engineering%20%26amp%3B%20Operations%20Research</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179594704&amp;Title=Open%20Rank%20Faculty%20Position%20in%20Computer%20Science</t>
         </is>
       </c>
       <c r="O125" s="3" t="inlineStr">
@@ -12377,12 +12377,12 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="R125" s="6" t="inlineStr">
@@ -12391,31 +12391,31 @@
         </is>
       </c>
       <c r="S125" s="2" t="n">
-        <v>37.8719</v>
+        <v>32.9785262</v>
       </c>
       <c r="T125" s="2" t="n">
-        <v>-122.2585</v>
+        <v>-96.7553288</v>
       </c>
     </row>
     <row r="126" ht="26" customHeight="1">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>56d501f448e77e05</t>
+          <t>8220b83ca4262093</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Assistant/Associate/Full Professor in Industrial and Systems Engineering</t>
+          <t>Assistant Professor - Fintech and Cyber Risk</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>University of Florida</t>
+          <t>University of California, Berkeley</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Department of Industrial and Systems Engineering</t>
+          <t>Industrial Engineering &amp; Operations Research</t>
         </is>
       </c>
       <c r="E126" s="3" t="n">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>Low fit: Position is housed in Industrial and Systems Engineering with a heavy focus on industrial construction and manufacturing rather than transit planning.</t>
+          <t>Low fit: The position is in Industrial Engineering and Operations Research focusing on fintech and cyber risk, lacking a direct focus on passenger transportation or mobility.</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Industrialized Construction, Artificial Intelligence, Digital Twins, Operations Research</t>
+          <t>Fintech, Cyber Risk, Operations Research</t>
         </is>
       </c>
       <c r="H126" s="3" t="inlineStr">
@@ -12438,7 +12438,7 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>Gainesville, FL</t>
+          <t>Berkeley, CA</t>
         </is>
       </c>
       <c r="J126" s="3" t="inlineStr">
@@ -12449,32 +12449,32 @@
       <c r="K126" s="3" t="inlineStr"/>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t>Salary is commensurate with education and experience.</t>
+          <t>$111,400 - $163,200 per year</t>
         </is>
       </c>
       <c r="M126" s="4" t="inlineStr">
         <is>
-          <t>The University of Florida seeks an open-rank faculty member in Industrial and Systems Engineering specializing in industrialized construction and systems methods, requiring a Ph.D. in ISE or a related field. | Research Topics: Industrialized Construction, Artificial Intelligence, Digital Twins, Operations Research</t>
+          <t>The Department of Industrial Engineering &amp; Operations Research at UC Berkeley invites applications for a tenure-track Assistant Professor position focusing on fintech and cyber risk, requiring an earned Ph.D. | Research Topics: Fintech, Cyber Risk, Operations Research</t>
         </is>
       </c>
       <c r="N126" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-associate-full-professor-industrial-systems-engineering-at-university-of-florida-4323668785</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179595173&amp;Title=Assistant%20Professor%20%2D%20Fintech%20and%20Cyber%20Risk%20%2D%20Industrial%20Engineering%20%26amp%3B%20Operations%20Research</t>
         </is>
       </c>
       <c r="O126" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="R126" s="6" t="inlineStr">
@@ -12483,31 +12483,31 @@
         </is>
       </c>
       <c r="S126" s="2" t="n">
-        <v>29.6436</v>
+        <v>37.8719</v>
       </c>
       <c r="T126" s="2" t="n">
-        <v>-82.3549</v>
+        <v>-122.2585</v>
       </c>
     </row>
     <row r="127" ht="26" customHeight="1">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>439ae704bb50bcf9</t>
+          <t>56d501f448e77e05</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor (Geomatics/Civil Engineering)</t>
+          <t>Assistant/Associate/Full Professor in Industrial and Systems Engineering</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>University of Hawaii at Manoa</t>
+          <t>University of Florida</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Civil, Environmental, and Construction Engineering</t>
+          <t>Department of Industrial and Systems Engineering</t>
         </is>
       </c>
       <c r="E127" s="3" t="n">
@@ -12515,12 +12515,12 @@
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>Low fit: While housed in Civil and Environmental Engineering, the search specifically prioritizes geomatics and geospatial science rather than transportation systems engineering.</t>
+          <t>Low fit: Position is housed in Industrial and Systems Engineering with a heavy focus on industrial construction and manufacturing rather than transit planning.</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Geospatial Science, Geodesy, Geographic Information Systems (GIS)</t>
+          <t>Industrialized Construction, Artificial Intelligence, Digital Twins, Operations Research</t>
         </is>
       </c>
       <c r="H127" s="3" t="inlineStr">
@@ -12530,7 +12530,7 @@
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>Honolulu, HI</t>
+          <t>Gainesville, FL</t>
         </is>
       </c>
       <c r="J127" s="3" t="inlineStr">
@@ -12541,32 +12541,32 @@
       <c r="K127" s="3" t="inlineStr"/>
       <c r="L127" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Salary is commensurate with education and experience.</t>
         </is>
       </c>
       <c r="M127" s="4" t="inlineStr">
         <is>
-          <t>The Department of Civil, Environmental, and Construction Engineering at the University of Hawaii at Manoa invites applications for a tenure-track faculty position focusing on advanced geospatial science and geomatics applications, requiring an earned doctorate. | Research Topics: Geospatial Science, Geodesy, Geographic Information Systems (GIS)</t>
+          <t>The University of Florida seeks an open-rank faculty member in Industrial and Systems Engineering specializing in industrialized construction and systems methods, requiring a Ph.D. in ISE or a related field. | Research Topics: Industrialized Construction, Artificial Intelligence, Digital Twins, Operations Research</t>
         </is>
       </c>
       <c r="N127" s="5" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179597929&amp;Title=Assistant%20Professor%20%28Geomatics%2FCivil%20Engineering%29</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-associate-full-professor-industrial-systems-engineering-at-university-of-florida-4323668785</t>
         </is>
       </c>
       <c r="O127" s="3" t="inlineStr">
         <is>
-          <t>HigherEdJobs</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="R127" s="6" t="inlineStr">
@@ -12575,31 +12575,31 @@
         </is>
       </c>
       <c r="S127" s="2" t="n">
-        <v>21.2982795</v>
+        <v>29.6436</v>
       </c>
       <c r="T127" s="2" t="n">
-        <v>-157.8186932</v>
+        <v>-82.3549</v>
       </c>
     </row>
     <row r="128" ht="26" customHeight="1">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>11c29a3e3943ebc1</t>
+          <t>439ae704bb50bcf9</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor (Tenure Track) in Systems Engineering</t>
+          <t>Assistant Professor (Geomatics/Civil Engineering)</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>University of South Alabama</t>
+          <t>University of Hawaii at Manoa</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Systems Engineering</t>
+          <t>Civil, Environmental, and Construction Engineering</t>
         </is>
       </c>
       <c r="E128" s="3" t="n">
@@ -12607,12 +12607,12 @@
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>This systems engineering position focuses on industrial systems and Model-Based Systems Engineering without a primary application in transportation.</t>
+          <t>Low fit: While housed in Civil and Environmental Engineering, the search specifically prioritizes geomatics and geospatial science rather than transportation systems engineering.</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>Systems Engineering, Model-Based Systems Engineering, Complex Systems Design</t>
+          <t>Geospatial Science, Geodesy, Geographic Information Systems (GIS)</t>
         </is>
       </c>
       <c r="H128" s="3" t="inlineStr">
@@ -12622,7 +12622,7 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>Mobile, AL</t>
+          <t>Honolulu, HI</t>
         </is>
       </c>
       <c r="J128" s="3" t="inlineStr">
@@ -12638,27 +12638,27 @@
       </c>
       <c r="M128" s="4" t="inlineStr">
         <is>
-          <t>This tenure-track assistant professor position requires an earned doctorate in systems engineering or a closely related discipline to conduct research and graduate teaching. | Research Topics: Systems Engineering, Model-Based Systems Engineering, Complex Systems Design</t>
+          <t>The Department of Civil, Environmental, and Construction Engineering at the University of Hawaii at Manoa invites applications for a tenure-track faculty position focusing on advanced geospatial science and geomatics applications, requiring an earned doctorate. | Research Topics: Geospatial Science, Geodesy, Geographic Information Systems (GIS)</t>
         </is>
       </c>
       <c r="N128" s="5" t="inlineStr">
         <is>
-          <t>http://engineering.academickeys.com/job/unxy6gj3/Assistant-Professor-Tenure-Track</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179597929&amp;Title=Assistant%20Professor%20%28Geomatics%2FCivil%20Engineering%29</t>
         </is>
       </c>
       <c r="O128" s="3" t="inlineStr">
         <is>
-          <t>AcademicKeys</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R128" s="6" t="inlineStr">
@@ -12667,31 +12667,31 @@
         </is>
       </c>
       <c r="S128" s="2" t="n">
-        <v>30.6972412</v>
+        <v>21.2982795</v>
       </c>
       <c r="T128" s="2" t="n">
-        <v>-88.18923340000001</v>
+        <v>-157.8186932</v>
       </c>
     </row>
     <row r="129" ht="26" customHeight="1">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>17a24780d19e1cb4</t>
+          <t>11c29a3e3943ebc1</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Open Rank Professor of Industrial Engineering</t>
+          <t>Assistant Professor (Tenure Track) in Systems Engineering</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>University of South Carolina</t>
+          <t>University of South Alabama</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Department of Mechanical Engineering</t>
+          <t>Systems Engineering</t>
         </is>
       </c>
       <c r="E129" s="3" t="n">
@@ -12699,12 +12699,12 @@
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>Industrial engineering position focused on manufacturing and advanced production systems rather than transportation planning, travel behavior, or mobility systems.</t>
+          <t>This systems engineering position focuses on industrial systems and Model-Based Systems Engineering without a primary application in transportation.</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>Advanced Manufacturing, Digital Twins and XR, Applied AI and Physical AI, Human-Robot Interaction</t>
+          <t>Systems Engineering, Model-Based Systems Engineering, Complex Systems Design</t>
         </is>
       </c>
       <c r="H129" s="3" t="inlineStr">
@@ -12714,7 +12714,7 @@
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>Columbia, SC</t>
+          <t>Mobile, AL</t>
         </is>
       </c>
       <c r="J129" s="3" t="inlineStr">
@@ -12730,12 +12730,12 @@
       </c>
       <c r="M129" s="4" t="inlineStr">
         <is>
-          <t>Open-rank faculty position in industrial engineering requiring a Ph.D. to support a new manufacturing-focused IE program. | Research Topics: Advanced Manufacturing, Digital Twins and XR, Applied AI and Physical AI, Human-Robot Interaction</t>
+          <t>This tenure-track assistant professor position requires an earned doctorate in systems engineering or a closely related discipline to conduct research and graduate teaching. | Research Topics: Systems Engineering, Model-Based Systems Engineering, Complex Systems Design</t>
         </is>
       </c>
       <c r="N129" s="5" t="inlineStr">
         <is>
-          <t>http://engineering.academickeys.com/job/3bckf2gv/Open-Rank-ProfessorTenure-TrackIndustrial-Engineering</t>
+          <t>http://engineering.academickeys.com/job/unxy6gj3/Assistant-Professor-Tenure-Track</t>
         </is>
       </c>
       <c r="O129" s="3" t="inlineStr">
@@ -12745,12 +12745,12 @@
       </c>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="Q129" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R129" s="6" t="inlineStr">
@@ -12759,31 +12759,31 @@
         </is>
       </c>
       <c r="S129" s="2" t="n">
-        <v>33.9928841</v>
+        <v>30.6972412</v>
       </c>
       <c r="T129" s="2" t="n">
-        <v>-81.0268676</v>
+        <v>-88.18923340000001</v>
       </c>
     </row>
     <row r="130" ht="26" customHeight="1">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>9d5682cf4dbca334</t>
+          <t>17a24780d19e1cb4</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Assistant / Associate Professor of Industrial and Systems Engineering</t>
+          <t>Open Rank Professor of Industrial Engineering</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>University of Washington</t>
+          <t>University of South Carolina</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Industrial &amp; Systems Engineering</t>
+          <t>Department of Mechanical Engineering</t>
         </is>
       </c>
       <c r="E130" s="3" t="n">
@@ -12791,12 +12791,12 @@
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>This industrial and systems engineering position focuses on generalized cyber-physical and autonomous systems without a dedicated transportation focus.</t>
+          <t>Industrial engineering position focused on manufacturing and advanced production systems rather than transportation planning, travel behavior, or mobility systems.</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>Systems Engineering, Model-Based Systems Engineering, Cyber-Physical Systems, Autonomous Systems</t>
+          <t>Advanced Manufacturing, Digital Twins and XR, Applied AI and Physical AI, Human-Robot Interaction</t>
         </is>
       </c>
       <c r="H130" s="3" t="inlineStr">
@@ -12806,7 +12806,7 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Columbia, SC</t>
         </is>
       </c>
       <c r="J130" s="3" t="inlineStr">
@@ -12817,17 +12817,17 @@
       <c r="K130" s="3" t="inlineStr"/>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>$12,000 – $17,000 per month (9-month service period)</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="M130" s="4" t="inlineStr">
         <is>
-          <t>Tenure-track faculty position in systems engineering requiring a Ph.D. to teach and establish an externally funded research program. | Research Topics: Systems Engineering, Model-Based Systems Engineering, Cyber-Physical Systems, Autonomous Systems</t>
+          <t>Open-rank faculty position in industrial engineering requiring a Ph.D. to support a new manufacturing-focused IE program. | Research Topics: Advanced Manufacturing, Digital Twins and XR, Applied AI and Physical AI, Human-Robot Interaction</t>
         </is>
       </c>
       <c r="N130" s="5" t="inlineStr">
         <is>
-          <t>https://engineering.academickeys.com/job/g4m97a60/AssistantAssociate-Professor-Industrial-and-Systems-Engineering-Systems-Engineering-Focus</t>
+          <t>http://engineering.academickeys.com/job/3bckf2gv/Open-Rank-ProfessorTenure-TrackIndustrial-Engineering</t>
         </is>
       </c>
       <c r="O130" s="3" t="inlineStr">
@@ -12837,12 +12837,12 @@
       </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="Q130" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="R130" s="6" t="inlineStr">
@@ -12851,31 +12851,31 @@
         </is>
       </c>
       <c r="S130" s="2" t="n">
-        <v>47.6553</v>
+        <v>33.9928841</v>
       </c>
       <c r="T130" s="2" t="n">
-        <v>-122.3035</v>
+        <v>-81.0268676</v>
       </c>
     </row>
     <row r="131" ht="26" customHeight="1">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>66ca5c4cd344d29b</t>
+          <t>9d5682cf4dbca334</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>Assistant/Associate/Full Professor in Mechanical Engineering (Robotics)</t>
+          <t>Assistant / Associate Professor of Industrial and Systems Engineering</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>University of Wisconsin - Madison</t>
+          <t>University of Washington</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Department of Mechanical Engineering</t>
+          <t>Industrial &amp; Systems Engineering</t>
         </is>
       </c>
       <c r="E131" s="3" t="n">
@@ -12883,12 +12883,12 @@
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>The position focuses on mechanical robotics and embodied AI rather than transportation planning or travel behavior analysis.</t>
+          <t>This industrial and systems engineering position focuses on generalized cyber-physical and autonomous systems without a dedicated transportation focus.</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>Robotics, Autonomous Systems, Embodied AI, Control Systems</t>
+          <t>Systems Engineering, Model-Based Systems Engineering, Cyber-Physical Systems, Autonomous Systems</t>
         </is>
       </c>
       <c r="H131" s="3" t="inlineStr">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>Madison, WI</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="J131" s="3" t="inlineStr">
@@ -12909,27 +12909,27 @@
       <c r="K131" s="3" t="inlineStr"/>
       <c r="L131" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>$12,000 – $17,000 per month (9-month service period)</t>
         </is>
       </c>
       <c r="M131" s="4" t="inlineStr">
         <is>
-          <t>This tenure-track position seeks faculty in robotics, automation, and embodied AI requiring a Ph.D. in mechanical engineering or a related discipline. | Research Topics: Robotics, Autonomous Systems, Embodied AI, Control Systems</t>
+          <t>Tenure-track faculty position in systems engineering requiring a Ph.D. to teach and establish an externally funded research program. | Research Topics: Systems Engineering, Model-Based Systems Engineering, Cyber-Physical Systems, Autonomous Systems</t>
         </is>
       </c>
       <c r="N131" s="5" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179584825&amp;Title=Assistant%2FAssociate%2FFull%20Professor%20in%20Mechanical%20Engineering%20%28Robotics%29</t>
+          <t>https://engineering.academickeys.com/job/g4m97a60/AssistantAssociate-Professor-Industrial-and-Systems-Engineering-Systems-Engineering-Focus</t>
         </is>
       </c>
       <c r="O131" s="3" t="inlineStr">
         <is>
-          <t>HigherEdJobs</t>
+          <t>AcademicKeys</t>
         </is>
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="Q131" s="2" t="inlineStr">
@@ -12943,44 +12943,44 @@
         </is>
       </c>
       <c r="S131" s="2" t="n">
-        <v>43.0802745</v>
+        <v>47.6553</v>
       </c>
       <c r="T131" s="2" t="n">
-        <v>-89.43095870000001</v>
+        <v>-122.3035</v>
       </c>
     </row>
     <row r="132" ht="26" customHeight="1">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>6617a775b51412a6</t>
+          <t>66ca5c4cd344d29b</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Assistant/Associate Professor</t>
+          <t>Assistant/Associate/Full Professor in Mechanical Engineering (Robotics)</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Brown University</t>
+          <t>University of Wisconsin - Madison</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>School of Engineering</t>
+          <t>Department of Mechanical Engineering</t>
         </is>
       </c>
       <c r="E132" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>The position is in environmental and chemical engineering rather than transportation engineering or urban mobility systems.</t>
+          <t>The position focuses on mechanical robotics and embodied AI rather than transportation planning or travel behavior analysis.</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>Environmental Engineering, Chemical Engineering, Materials Science</t>
+          <t>Robotics, Autonomous Systems, Embodied AI, Control Systems</t>
         </is>
       </c>
       <c r="H132" s="3" t="inlineStr">
@@ -12990,7 +12990,7 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>Providence, Rhode Island</t>
+          <t>Madison, WI</t>
         </is>
       </c>
       <c r="J132" s="3" t="inlineStr">
@@ -13006,27 +13006,27 @@
       </c>
       <c r="M132" s="4" t="inlineStr">
         <is>
-          <t>This role seeks faculty in chemical, environmental, or materials engineering with a Ph.D. to build independent research programs. | Research Topics: Environmental Engineering, Chemical Engineering, Materials Science</t>
+          <t>This tenure-track position seeks faculty in robotics, automation, and embodied AI requiring a Ph.D. in mechanical engineering or a related discipline. | Research Topics: Robotics, Autonomous Systems, Embodied AI, Control Systems</t>
         </is>
       </c>
       <c r="N132" s="5" t="inlineStr">
         <is>
-          <t>http://engineering.academickeys.com/job/ad8r6xb2/Chemical-Engineering-Environmental-Engineering-and-Materials-Science-and-Engineering-AssistantAssociate-Professor</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179584825&amp;Title=Assistant%2FAssociate%2FFull%20Professor%20in%20Mechanical%20Engineering%20%28Robotics%29</t>
         </is>
       </c>
       <c r="O132" s="3" t="inlineStr">
         <is>
-          <t>AcademicKeys</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="R132" s="6" t="inlineStr">
@@ -13035,31 +13035,31 @@
         </is>
       </c>
       <c r="S132" s="2" t="n">
-        <v>41.8268</v>
+        <v>43.0802745</v>
       </c>
       <c r="T132" s="2" t="n">
-        <v>-71.4025</v>
+        <v>-89.43095870000001</v>
       </c>
     </row>
     <row r="133" ht="26" customHeight="1">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>b82c1f87b1eab5ab</t>
+          <t>6617a775b51412a6</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor for Public Policy and Administration</t>
+          <t>Assistant/Associate Professor</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>California State University, Bakersfield</t>
+          <t>Brown University</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Department of Public Administration and Policy</t>
+          <t>School of Engineering</t>
         </is>
       </c>
       <c r="E133" s="3" t="n">
@@ -13067,12 +13067,12 @@
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>Low fit due to a focus on public administration and policy without a direct transportation or travel behavior specialization.</t>
+          <t>The position is in environmental and chemical engineering rather than transportation engineering or urban mobility systems.</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Public Policy, Public Administration</t>
+          <t>Environmental Engineering, Chemical Engineering, Materials Science</t>
         </is>
       </c>
       <c r="H133" s="3" t="inlineStr">
@@ -13082,7 +13082,7 @@
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>Bakersfield, CA</t>
+          <t>Providence, Rhode Island</t>
         </is>
       </c>
       <c r="J133" s="3" t="inlineStr">
@@ -13093,32 +13093,32 @@
       <c r="K133" s="3" t="inlineStr"/>
       <c r="L133" s="2" t="inlineStr">
         <is>
-          <t>$75,000 - $85,000 per year</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="M133" s="4" t="inlineStr">
         <is>
-          <t>California State University, Bakersfield invites applications for a tenure-track Assistant Professor in Public Policy and Administration requiring an earned doctorate. | Research Topics: Public Policy, Public Administration</t>
+          <t>This role seeks faculty in chemical, environmental, or materials engineering with a Ph.D. to build independent research programs. | Research Topics: Environmental Engineering, Chemical Engineering, Materials Science</t>
         </is>
       </c>
       <c r="N133" s="5" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179597599&amp;Title=Assistant%20Professor%20for%20Public%20Policy%20and%20Administration</t>
+          <t>http://engineering.academickeys.com/job/ad8r6xb2/Chemical-Engineering-Environmental-Engineering-and-Materials-Science-and-Engineering-AssistantAssociate-Professor</t>
         </is>
       </c>
       <c r="O133" s="3" t="inlineStr">
         <is>
-          <t>HigherEdJobs</t>
+          <t>AcademicKeys</t>
         </is>
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="Q133" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="R133" s="6" t="inlineStr">
@@ -13127,31 +13127,31 @@
         </is>
       </c>
       <c r="S133" s="2" t="n">
-        <v>35.3493892</v>
+        <v>41.8268</v>
       </c>
       <c r="T133" s="2" t="n">
-        <v>-119.1033969</v>
+        <v>-71.4025</v>
       </c>
     </row>
     <row r="134" ht="26" customHeight="1">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>9e6dd7d9c84a89d0</t>
+          <t>b82c1f87b1eab5ab</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor- Civil Engineering (Tenure-track)</t>
+          <t>Assistant Professor for Public Policy and Administration</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>City College of New York</t>
+          <t>California State University, Bakersfield</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Department of Civil Engineering</t>
+          <t>Department of Public Administration and Policy</t>
         </is>
       </c>
       <c r="E134" s="3" t="n">
@@ -13159,12 +13159,12 @@
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>The position is specifically dedicated to Geotechnical Engineering and Geomechanics rather than transportation systems engineering.</t>
+          <t>Low fit due to a focus on public administration and policy without a direct transportation or travel behavior specialization.</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>Geotechnical Engineering, Geomechanics, Soil-Structure Interaction, Geo-hazard Analysis and Mitigation</t>
+          <t>Public Policy, Public Administration</t>
         </is>
       </c>
       <c r="H134" s="3" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>New York City, NY</t>
+          <t>Bakersfield, CA</t>
         </is>
       </c>
       <c r="J134" s="3" t="inlineStr">
@@ -13185,17 +13185,17 @@
       <c r="K134" s="3" t="inlineStr"/>
       <c r="L134" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>$75,000 - $85,000 per year</t>
         </is>
       </c>
       <c r="M134" s="4" t="inlineStr">
         <is>
-          <t>[Geotechnical Engineering] The City College of New York invites applications for a tenure-track Assistant Professor in Civil Engineering with expertise in Geotechnical Engineering and Geomechanics, requiring a Ph.D. in Civil Engineering. | Research Topics: Geotechnical Engineering, Geomechanics, Soil-Structure Interaction, Geo-hazard Analysis and Mitigation</t>
+          <t>California State University, Bakersfield invites applications for a tenure-track Assistant Professor in Public Policy and Administration requiring an earned doctorate. | Research Topics: Public Policy, Public Administration</t>
         </is>
       </c>
       <c r="N134" s="5" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179601465&amp;Title=Assistant%20Professor%2D%20Civil%20Engineering%20%28Tenure%2Dtrack%29</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179597599&amp;Title=Assistant%20Professor%20for%20Public%20Policy%20and%20Administration</t>
         </is>
       </c>
       <c r="O134" s="3" t="inlineStr">
@@ -13205,12 +13205,12 @@
       </c>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q134" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="R134" s="6" t="inlineStr">
@@ -13219,31 +13219,31 @@
         </is>
       </c>
       <c r="S134" s="2" t="n">
-        <v>40.8181098</v>
+        <v>35.3493892</v>
       </c>
       <c r="T134" s="2" t="n">
-        <v>-73.950886</v>
+        <v>-119.1033969</v>
       </c>
     </row>
     <row r="135" ht="26" customHeight="1">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>0249d5be9bd5a4a1</t>
+          <t>9e6dd7d9c84a89d0</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Teaching Faculty Position for First-Year Engineering</t>
+          <t>Assistant Professor- Civil Engineering (Tenure-track)</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Florida A&amp;M University - Florida State University College of Engineering</t>
+          <t>City College of New York</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Office of Student Services and Undergraduate Affairs</t>
+          <t>Department of Civil Engineering</t>
         </is>
       </c>
       <c r="E135" s="3" t="n">
@@ -13251,22 +13251,22 @@
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>This is a non-tenure-track teaching position focused on general first-year engineering programming rather than transportation research.</t>
+          <t>The position is specifically dedicated to Geotechnical Engineering and Geomechanics rather than transportation systems engineering.</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>Engineering Education, First-Year Engineering Programming, Student Retention and Advising</t>
+          <t>Geotechnical Engineering, Geomechanics, Soil-Structure Interaction, Geo-hazard Analysis and Mitigation</t>
         </is>
       </c>
       <c r="H135" s="3" t="inlineStr">
         <is>
-          <t>Non-Tenure Track</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>Tallahassee, FL</t>
+          <t>New York City, NY</t>
         </is>
       </c>
       <c r="J135" s="3" t="inlineStr">
@@ -13282,27 +13282,27 @@
       </c>
       <c r="M135" s="4" t="inlineStr">
         <is>
-          <t>Full-time non-tenure track teaching faculty position focusing on undergraduate instruction and academic support in first-year engineering. | Research Topics: Engineering Education, First-Year Engineering Programming, Student Retention and Advising</t>
+          <t>[Geotechnical Engineering] The City College of New York invites applications for a tenure-track Assistant Professor in Civil Engineering with expertise in Geotechnical Engineering and Geomechanics, requiring a Ph.D. in Civil Engineering. | Research Topics: Geotechnical Engineering, Geomechanics, Soil-Structure Interaction, Geo-hazard Analysis and Mitigation</t>
         </is>
       </c>
       <c r="N135" s="5" t="inlineStr">
         <is>
-          <t>http://engineering.academickeys.com/job/jvd3l79c/Teaching-Faculty-Position-for-FirstYear-Engineering</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179601465&amp;Title=Assistant%20Professor%2D%20Civil%20Engineering%20%28Tenure%2Dtrack%29</t>
         </is>
       </c>
       <c r="O135" s="3" t="inlineStr">
         <is>
-          <t>AcademicKeys</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R135" s="6" t="inlineStr">
@@ -13311,31 +13311,31 @@
         </is>
       </c>
       <c r="S135" s="2" t="n">
-        <v>30.4380832</v>
+        <v>40.8181098</v>
       </c>
       <c r="T135" s="2" t="n">
-        <v>-84.28093320000001</v>
+        <v>-73.950886</v>
       </c>
     </row>
     <row r="136" ht="26" customHeight="1">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>c5bb5fe2141c1376</t>
+          <t>0249d5be9bd5a4a1</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Business (Supply Chain and Logistics)</t>
+          <t>Teaching Faculty Position for First-Year Engineering</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Georgia Military College</t>
+          <t>Florida A&amp;M University - Florida State University College of Engineering</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Department of Business Administration</t>
+          <t>Office of Student Services and Undergraduate Affairs</t>
         </is>
       </c>
       <c r="E136" s="3" t="n">
@@ -13343,12 +13343,12 @@
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>The position focuses on undergraduate business teaching in supply chain management and logistics rather than transportation systems engineering or urban mobility research.</t>
+          <t>This is a non-tenure-track teaching position focused on general first-year engineering programming rather than transportation research.</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Management, Logistics, Operations Management</t>
+          <t>Engineering Education, First-Year Engineering Programming, Student Retention and Advising</t>
         </is>
       </c>
       <c r="H136" s="3" t="inlineStr">
@@ -13358,7 +13358,7 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>Milledgeville, Georgia</t>
+          <t>Tallahassee, FL</t>
         </is>
       </c>
       <c r="J136" s="3" t="inlineStr">
@@ -13369,32 +13369,32 @@
       <c r="K136" s="3" t="inlineStr"/>
       <c r="L136" s="2" t="inlineStr">
         <is>
-          <t>$45,000 - $48,900 per year</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="M136" s="4" t="inlineStr">
         <is>
-          <t>Teaches full-time business coursework in supply chain, logistics, and operations management requiring at least a master's degree in a business-related field. | Research Topics: Supply Chain Management, Logistics, Operations Management</t>
+          <t>Full-time non-tenure track teaching faculty position focusing on undergraduate instruction and academic support in first-year engineering. | Research Topics: Engineering Education, First-Year Engineering Programming, Student Retention and Advising</t>
         </is>
       </c>
       <c r="N136" s="5" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179592179&amp;Title=College%20Faculty%3A%20Business%2FSupply%20Chain%20Logistics%3A%20Main%20%28In%2DPerson%29</t>
+          <t>http://engineering.academickeys.com/job/jvd3l79c/Teaching-Faculty-Position-for-FirstYear-Engineering</t>
         </is>
       </c>
       <c r="O136" s="3" t="inlineStr">
         <is>
-          <t>HigherEdJobs</t>
+          <t>AcademicKeys</t>
         </is>
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="Q136" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="R136" s="6" t="inlineStr">
@@ -13403,31 +13403,31 @@
         </is>
       </c>
       <c r="S136" s="2" t="n">
-        <v>33.0787182</v>
+        <v>30.4380832</v>
       </c>
       <c r="T136" s="2" t="n">
-        <v>-83.2245922</v>
+        <v>-84.28093320000001</v>
       </c>
     </row>
     <row r="137" ht="26" customHeight="1">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>c7dc0797cfd5822a</t>
+          <t>c5bb5fe2141c1376</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor Public History, Historic Preservation, and Museum Studies</t>
+          <t>Assistant Professor of Business (Supply Chain and Logistics)</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>Georgia Southern University</t>
+          <t>Georgia Military College</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Department of History</t>
+          <t>Department of Business Administration</t>
         </is>
       </c>
       <c r="E137" s="3" t="n">
@@ -13435,22 +13435,22 @@
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>Screened out: Position is in Public History and Historic Preservation, which is outside the candidate's transportation engineering focus.</t>
+          <t>The position focuses on undergraduate business teaching in supply chain management and logistics rather than transportation systems engineering or urban mobility research.</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>Public History, Historic Preservation, Museum Studies</t>
+          <t>Supply Chain Management, Logistics, Operations Management</t>
         </is>
       </c>
       <c r="H137" s="3" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Non-Tenure Track</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>Statesboro, Georgia</t>
+          <t>Milledgeville, Georgia</t>
         </is>
       </c>
       <c r="J137" s="3" t="inlineStr">
@@ -13461,32 +13461,32 @@
       <c r="K137" s="3" t="inlineStr"/>
       <c r="L137" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>$45,000 - $48,900 per year</t>
         </is>
       </c>
       <c r="M137" s="4" t="inlineStr">
         <is>
-          <t>This is a tenure-track Assistant Professor position focusing on public history, historic preservation, and museum studies. | Research Topics: Public History, Historic Preservation, Museum Studies</t>
+          <t>Teaches full-time business coursework in supply chain, logistics, and operations management requiring at least a master's degree in a business-related field. | Research Topics: Supply Chain Management, Logistics, Operations Management</t>
         </is>
       </c>
       <c r="N137" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38047641/assistant-professor-public-history-historic-preservation-and-museum-studies/</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179592179&amp;Title=College%20Faculty%3A%20Business%2FSupply%20Chain%20Logistics%3A%20Main%20%28In%2DPerson%29</t>
         </is>
       </c>
       <c r="O137" s="3" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="Q137" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="R137" s="6" t="inlineStr">
@@ -13495,31 +13495,31 @@
         </is>
       </c>
       <c r="S137" s="2" t="n">
-        <v>32.4214381</v>
+        <v>33.0787182</v>
       </c>
       <c r="T137" s="2" t="n">
-        <v>-81.78450530000001</v>
+        <v>-83.2245922</v>
       </c>
     </row>
     <row r="138" ht="26" customHeight="1">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>aa8f4632bbdd2759</t>
+          <t>c22550cf5a370cf7</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Assistant/Associate/Full Professor of Computer Science</t>
+          <t>Assistant Professor Public Administration</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Grove City College</t>
+          <t>Georgia Southern University</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Computer Science</t>
+          <t>College of Behavioral and Social Sciences</t>
         </is>
       </c>
       <c r="E138" s="3" t="n">
@@ -13527,22 +13527,22 @@
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>The position is in Computer Science focusing on general CS and data science undergraduate teaching rather than transportation engineering.</t>
+          <t>Low fit: Public Administration faculty position without any indication of a transportation planning, urban mobility, or infrastructure policy focus.</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Computer Science, Data Science, Computer Engineering, Computer Programming</t>
+          <t>Public Administration, Public Policy, Governance</t>
         </is>
       </c>
       <c r="H138" s="3" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Non-Tenure Track</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>Grove City, PA</t>
+          <t>Statesboro, GA</t>
         </is>
       </c>
       <c r="J138" s="3" t="inlineStr">
@@ -13558,27 +13558,27 @@
       </c>
       <c r="M138" s="4" t="inlineStr">
         <is>
-          <t>Grove City College invites applications for an Assistant/Associate/Full Professor of Computer Science to teach undergraduate courses and guide student research, preferring a Ph.D. in Computer Science or a closely related field. | Research Topics: Computer Science, Data Science, Computer Engineering, Computer Programming</t>
+          <t>Full-time assistant professor appointment in public administration focused on teaching and public management, requiring a terminal degree in Public Administration, Public Policy, or a related discipline. | Research Topics: Public Administration, Public Policy, Governance</t>
         </is>
       </c>
       <c r="N138" s="5" t="inlineStr">
         <is>
-          <t>http://engineering.academickeys.com/job/21qwyg60/AssistantAssociateFull-Professor-of-Computer-Science</t>
+          <t>https://jobs.chronicle.com/job/38051869/assistant-professor-public-administration/</t>
         </is>
       </c>
       <c r="O138" s="3" t="inlineStr">
         <is>
-          <t>AcademicKeys</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R138" s="6" t="inlineStr">
@@ -13587,31 +13587,31 @@
         </is>
       </c>
       <c r="S138" s="2" t="n">
-        <v>41.1553489</v>
+        <v>32.4214381</v>
       </c>
       <c r="T138" s="2" t="n">
-        <v>-80.0787486</v>
+        <v>-81.78450530000001</v>
       </c>
     </row>
     <row r="139" ht="26" customHeight="1">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>cd73f7eb569f2263</t>
+          <t>c7dc0797cfd5822a</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor in Fair and Responsible Artificial Intelligence</t>
+          <t>Assistant Professor Public History, Historic Preservation, and Museum Studies</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Imperial College London</t>
+          <t>Georgia Southern University</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Dyson School of Design Engineering</t>
+          <t>Department of History</t>
         </is>
       </c>
       <c r="E139" s="3" t="n">
@@ -13619,12 +13619,12 @@
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>This Assistant Professor position focuses specifically on fair and responsible artificial intelligence and algorithmic fairness rather than transportation engineering or travel behavior analysis.</t>
+          <t>Screened out: Position is in Public History and Historic Preservation, which is outside the candidate's transportation engineering focus.</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>Responsible AI, Algorithmic Fairness, Design Engineering, Human-AI Interaction</t>
+          <t>Public History, Historic Preservation, Museum Studies</t>
         </is>
       </c>
       <c r="H139" s="3" t="inlineStr">
@@ -13634,7 +13634,7 @@
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Statesboro, Georgia</t>
         </is>
       </c>
       <c r="J139" s="3" t="inlineStr">
@@ -13645,32 +13645,32 @@
       <c r="K139" s="3" t="inlineStr"/>
       <c r="L139" s="2" t="inlineStr">
         <is>
-          <t>£73,194 to £82,954</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="M139" s="4" t="inlineStr">
         <is>
-          <t>Assistant Professor role requiring a Ph.D. to conduct foundational research in fair, trustworthy, and responsible artificial intelligence methods. | Research Topics: Responsible AI, Algorithmic Fairness, Design Engineering, Human-AI Interaction</t>
+          <t>This is a tenure-track Assistant Professor position focusing on public history, historic preservation, and museum studies. | Research Topics: Public History, Historic Preservation, Museum Studies</t>
         </is>
       </c>
       <c r="N139" s="5" t="inlineStr">
         <is>
-          <t>https://www.jobs.ac.uk/job/DSO564/assistant-professor-in-fair-and-responsible-artificial-intelligence</t>
+          <t>https://jobs.chronicle.com/job/38047641/assistant-professor-public-history-historic-preservation-and-museum-studies/</t>
         </is>
       </c>
       <c r="O139" s="3" t="inlineStr">
         <is>
-          <t>Jobs.ac.uk</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="Q139" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R139" s="6" t="inlineStr">
@@ -13679,31 +13679,31 @@
         </is>
       </c>
       <c r="S139" s="2" t="n">
-        <v>51.4988</v>
+        <v>32.4214381</v>
       </c>
       <c r="T139" s="2" t="n">
-        <v>-0.1749</v>
+        <v>-81.78450530000001</v>
       </c>
     </row>
     <row r="140" ht="26" customHeight="1">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>8abe626fa2075a40</t>
+          <t>aa8f4632bbdd2759</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor: Land-Use &amp; Resilience Planning</t>
+          <t>Assistant/Associate/Full Professor of Computer Science</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Iowa State University</t>
+          <t>Grove City College</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Department of Community and Regional Planning</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E140" s="3" t="n">
@@ -13711,12 +13711,12 @@
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>Focuses on land-use and resilience planning without a dedicated focus on passenger transportation, public transit, or travel demand modeling.</t>
+          <t>The position is in Computer Science focusing on general CS and data science undergraduate teaching rather than transportation engineering.</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>Land-Use Planning, Resilience Planning, Urban Planning</t>
+          <t>Computer Science, Data Science, Computer Engineering, Computer Programming</t>
         </is>
       </c>
       <c r="H140" s="3" t="inlineStr">
@@ -13726,7 +13726,7 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>Ames, IA</t>
+          <t>Grove City, PA</t>
         </is>
       </c>
       <c r="J140" s="3" t="inlineStr">
@@ -13742,17 +13742,17 @@
       </c>
       <c r="M140" s="4" t="inlineStr">
         <is>
-          <t>Iowa State University invites applications for an Assistant Professor position specializing in land-use and resilience planning, requiring an earned doctorate in urban planning or a related field. | Research Topics: Land-Use Planning, Resilience Planning, Urban Planning</t>
+          <t>Grove City College invites applications for an Assistant/Associate/Full Professor of Computer Science to teach undergraduate courses and guide student research, preferring a Ph.D. in Computer Science or a closely related field. | Research Topics: Computer Science, Data Science, Computer Engineering, Computer Programming</t>
         </is>
       </c>
       <c r="N140" s="5" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179600207&amp;Title=Assistant%20Professor%3A%20Land%2DUse%20%26%20Resilience%20Planning</t>
+          <t>http://engineering.academickeys.com/job/21qwyg60/AssistantAssociateFull-Professor-of-Computer-Science</t>
         </is>
       </c>
       <c r="O140" s="3" t="inlineStr">
         <is>
-          <t>HigherEdJobs</t>
+          <t>AcademicKeys</t>
         </is>
       </c>
       <c r="P140" s="2" t="inlineStr">
@@ -13771,31 +13771,31 @@
         </is>
       </c>
       <c r="S140" s="2" t="n">
-        <v>42.0279608</v>
+        <v>41.1553489</v>
       </c>
       <c r="T140" s="2" t="n">
-        <v>-93.64473750000001</v>
+        <v>-80.0787486</v>
       </c>
     </row>
     <row r="141" ht="26" customHeight="1">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>3051e6754632b1be</t>
+          <t>cd73f7eb569f2263</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor - Department of Mathematics and Computer Science</t>
+          <t>Assistant Professor in Fair and Responsible Artificial Intelligence</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>John Jay College of Criminal Justice, CUNY</t>
+          <t>Imperial College London</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>Department of Mathematics and Computer Science</t>
+          <t>Dyson School of Design Engineering</t>
         </is>
       </c>
       <c r="E141" s="3" t="n">
@@ -13803,12 +13803,12 @@
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>Irrelevant subfield focusing on computer science, cybersecurity, and artificial intelligence without a transportation systems or mobility component.</t>
+          <t>This Assistant Professor position focuses specifically on fair and responsible artificial intelligence and algorithmic fairness rather than transportation engineering or travel behavior analysis.</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>Cybersecurity, Artificial Intelligence, Cloud Computing, Digital Forensics</t>
+          <t>Responsible AI, Algorithmic Fairness, Design Engineering, Human-AI Interaction</t>
         </is>
       </c>
       <c r="H141" s="3" t="inlineStr">
@@ -13818,7 +13818,7 @@
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>New York City, NY</t>
+          <t>London</t>
         </is>
       </c>
       <c r="J141" s="3" t="inlineStr">
@@ -13829,32 +13829,32 @@
       <c r="K141" s="3" t="inlineStr"/>
       <c r="L141" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>£73,194 to £82,954</t>
         </is>
       </c>
       <c r="M141" s="4" t="inlineStr">
         <is>
-          <t>John Jay College seeks a tenure-track Assistant Professor in Computer Science focusing on the intersection of cybersecurity and AI, requiring a relevant doctorate. | Research Topics: Cybersecurity, Artificial Intelligence, Cloud Computing, Digital Forensics</t>
+          <t>Assistant Professor role requiring a Ph.D. to conduct foundational research in fair, trustworthy, and responsible artificial intelligence methods. | Research Topics: Responsible AI, Algorithmic Fairness, Design Engineering, Human-AI Interaction</t>
         </is>
       </c>
       <c r="N141" s="5" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179585101&amp;Title=Assistant%20Professor%20%2D%20Department%20of%20Mathematics%20and%20Computer%20Science</t>
+          <t>https://www.jobs.ac.uk/job/DSO564/assistant-professor-in-fair-and-responsible-artificial-intelligence</t>
         </is>
       </c>
       <c r="O141" s="3" t="inlineStr">
         <is>
-          <t>HigherEdJobs</t>
+          <t>Jobs.ac.uk</t>
         </is>
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="Q141" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="R141" s="6" t="inlineStr">
@@ -13863,31 +13863,31 @@
         </is>
       </c>
       <c r="S141" s="2" t="n">
-        <v>40.7127281</v>
+        <v>51.4988</v>
       </c>
       <c r="T141" s="2" t="n">
-        <v>-74.00601519999999</v>
+        <v>-0.1749</v>
       </c>
     </row>
     <row r="142" ht="26" customHeight="1">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>783c7e538dfbb9cb</t>
+          <t>8abe626fa2075a40</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor - Computer Science</t>
+          <t>Assistant Professor: Land-Use &amp; Resilience Planning</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Lehman College</t>
+          <t>Iowa State University</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Department of Computer Science</t>
+          <t>Department of Community and Regional Planning</t>
         </is>
       </c>
       <c r="E142" s="3" t="n">
@@ -13895,12 +13895,12 @@
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>Screened out due to computer science department focus without a transportation or mobility specialization.</t>
+          <t>Focuses on land-use and resilience planning without a dedicated focus on passenger transportation, public transit, or travel demand modeling.</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>Computer Science, Algorithms, Computing</t>
+          <t>Land-Use Planning, Resilience Planning, Urban Planning</t>
         </is>
       </c>
       <c r="H142" s="3" t="inlineStr">
@@ -13910,7 +13910,7 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>Bronx, NY</t>
+          <t>Ames, IA</t>
         </is>
       </c>
       <c r="J142" s="3" t="inlineStr">
@@ -13921,17 +13921,17 @@
       <c r="K142" s="3" t="inlineStr"/>
       <c r="L142" s="2" t="inlineStr">
         <is>
-          <t>$112,841 per year</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="M142" s="4" t="inlineStr">
         <is>
-          <t>Lehman College invites applications for a tenure-track Assistant Professor position in Computer Science, requiring an earned doctorate. | Research Topics: Computer Science, Algorithms, Computing</t>
+          <t>Iowa State University invites applications for an Assistant Professor position specializing in land-use and resilience planning, requiring an earned doctorate in urban planning or a related field. | Research Topics: Land-Use Planning, Resilience Planning, Urban Planning</t>
         </is>
       </c>
       <c r="N142" s="5" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179592779&amp;Title=Assistant%20Professor%20%2D%20Computer%20Science</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179600207&amp;Title=Assistant%20Professor%3A%20Land%2DUse%20%26%20Resilience%20Planning</t>
         </is>
       </c>
       <c r="O142" s="3" t="inlineStr">
@@ -13941,12 +13941,12 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R142" s="6" t="inlineStr">
@@ -13955,31 +13955,31 @@
         </is>
       </c>
       <c r="S142" s="2" t="n">
-        <v>40.8722825</v>
+        <v>42.0279608</v>
       </c>
       <c r="T142" s="2" t="n">
-        <v>-73.8948917</v>
+        <v>-93.64473750000001</v>
       </c>
     </row>
     <row r="143" ht="26" customHeight="1">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>664e10f5664e3e49</t>
+          <t>3051e6754632b1be</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Assistant/Associate Professor in Mechanical and Aerospace Engineering</t>
+          <t>Assistant Professor - Department of Mathematics and Computer Science</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>Missouri University of Science and Technology</t>
+          <t>John Jay College of Criminal Justice, CUNY</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>Department of Mechanical and Aerospace Engineering</t>
+          <t>Department of Mathematics and Computer Science</t>
         </is>
       </c>
       <c r="E143" s="3" t="n">
@@ -13987,12 +13987,12 @@
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>This mechanical and aerospace engineering position focuses on thermal-fluids and dynamics, lacking any transportation engineering or mobility focus.</t>
+          <t>Irrelevant subfield focusing on computer science, cybersecurity, and artificial intelligence without a transportation systems or mobility component.</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>Mechanical Engineering, Aerospace Systems, Thermal-Fluids, Dynamics</t>
+          <t>Cybersecurity, Artificial Intelligence, Cloud Computing, Digital Forensics</t>
         </is>
       </c>
       <c r="H143" s="3" t="inlineStr">
@@ -14002,7 +14002,7 @@
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>Rolla, MO</t>
+          <t>New York City, NY</t>
         </is>
       </c>
       <c r="J143" s="3" t="inlineStr">
@@ -14018,27 +14018,27 @@
       </c>
       <c r="M143" s="4" t="inlineStr">
         <is>
-          <t>An open rank faculty position in mechanical and aerospace engineering requiring a Ph.D. in a relevant discipline. | Research Topics: Mechanical Engineering, Aerospace Systems, Thermal-Fluids, Dynamics</t>
+          <t>John Jay College seeks a tenure-track Assistant Professor in Computer Science focusing on the intersection of cybersecurity and AI, requiring a relevant doctorate. | Research Topics: Cybersecurity, Artificial Intelligence, Cloud Computing, Digital Forensics</t>
         </is>
       </c>
       <c r="N143" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-associate-professor-mechanical-and-aerospace-engineering-%2300098258-at-missouri-university-of-science-and-technology-4464936601</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179585101&amp;Title=Assistant%20Professor%20%2D%20Department%20of%20Mathematics%20and%20Computer%20Science</t>
         </is>
       </c>
       <c r="O143" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="R143" s="6" t="inlineStr">
@@ -14047,31 +14047,31 @@
         </is>
       </c>
       <c r="S143" s="2" t="n">
-        <v>37.9532435</v>
+        <v>40.7127281</v>
       </c>
       <c r="T143" s="2" t="n">
-        <v>-91.7742667</v>
+        <v>-74.00601519999999</v>
       </c>
     </row>
     <row r="144" ht="26" customHeight="1">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>1e0a7536f9329af5</t>
+          <t>783c7e538dfbb9cb</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor / Associate Professor (Tenure-Track) in Maritime Studies</t>
+          <t>Assistant Professor - Computer Science</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Nanyang Technological University</t>
+          <t>Lehman College</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Maritime Studies</t>
+          <t>Department of Computer Science</t>
         </is>
       </c>
       <c r="E144" s="3" t="n">
@@ -14079,12 +14079,12 @@
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>Snippet lacks detailed departmental and research specifics beyond maritime studies, which diverges from passenger transportation and urban transit modeling.</t>
+          <t>Screened out due to computer science department focus without a transportation or mobility specialization.</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>Maritime Studies, Maritime Logistics, Shipping Operations</t>
+          <t>Computer Science, Algorithms, Computing</t>
         </is>
       </c>
       <c r="H144" s="3" t="inlineStr">
@@ -14094,7 +14094,7 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Bronx, NY</t>
         </is>
       </c>
       <c r="J144" s="3" t="inlineStr">
@@ -14105,32 +14105,32 @@
       <c r="K144" s="3" t="inlineStr"/>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>$112,841 per year</t>
         </is>
       </c>
       <c r="M144" s="4" t="inlineStr">
         <is>
-          <t>Nanyang Technological University invites applications for a tenure-track faculty position in Maritime Studies, requiring a relevant doctorate. | Research Topics: Maritime Studies, Maritime Logistics, Shipping Operations</t>
+          <t>Lehman College invites applications for a tenure-track Assistant Professor position in Computer Science, requiring an earned doctorate. | Research Topics: Computer Science, Algorithms, Computing</t>
         </is>
       </c>
       <c r="N144" s="5" t="inlineStr">
         <is>
-          <t>https://sg.linkedin.com/jobs/view/assistant-professor-associate-professor-tenure-track-associate-professor-practice-track-in-maritime-studies-at-nanyang-technological-university-singapore-4432368242</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179592779&amp;Title=Assistant%20Professor%20%2D%20Computer%20Science</t>
         </is>
       </c>
       <c r="O144" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="R144" s="6" t="inlineStr">
@@ -14139,31 +14139,31 @@
         </is>
       </c>
       <c r="S144" s="2" t="n">
-        <v>1.3483</v>
+        <v>40.8722825</v>
       </c>
       <c r="T144" s="2" t="n">
-        <v>103.6831</v>
+        <v>-73.8948917</v>
       </c>
     </row>
     <row r="145" ht="26" customHeight="1">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>56a58b3515dd9d01</t>
+          <t>664e10f5664e3e49</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>Lecturer, Civil Engineering</t>
+          <t>Assistant/Associate Professor in Mechanical and Aerospace Engineering</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Ngee Ann Polytechnic</t>
+          <t>Missouri University of Science and Technology</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>School of Design &amp; Environment</t>
+          <t>Department of Mechanical and Aerospace Engineering</t>
         </is>
       </c>
       <c r="E145" s="3" t="n">
@@ -14171,22 +14171,22 @@
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>Low fit: This is a polytechnic teaching lecturer role focused on civil engineering, structural design, and construction management rather than advanced transportation systems or demand modeling.</t>
+          <t>This mechanical and aerospace engineering position focuses on thermal-fluids and dynamics, lacking any transportation engineering or mobility focus.</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Civil Engineering, Structural Design, Construction Management, Building Information Modeling</t>
+          <t>Mechanical Engineering, Aerospace Systems, Thermal-Fluids, Dynamics</t>
         </is>
       </c>
       <c r="H145" s="3" t="inlineStr">
         <is>
-          <t>Non-Tenure Track</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Rolla, MO</t>
         </is>
       </c>
       <c r="J145" s="3" t="inlineStr">
@@ -14202,12 +14202,12 @@
       </c>
       <c r="M145" s="4" t="inlineStr">
         <is>
-          <t>Ngee Ann Polytechnic invites applications for a 2-year contract Lecturer position in Civil Engineering to deliver classroom instruction, curriculum development, and student mentorship. | Research Topics: Civil Engineering, Structural Design, Construction Management, Building Information Modeling</t>
+          <t>An open rank faculty position in mechanical and aerospace engineering requiring a Ph.D. in a relevant discipline. | Research Topics: Mechanical Engineering, Aerospace Systems, Thermal-Fluids, Dynamics</t>
         </is>
       </c>
       <c r="N145" s="5" t="inlineStr">
         <is>
-          <t>https://sg.linkedin.com/jobs/view/lecturer-civil-engineering-school-of-design-environment-at-ngee-ann-polytechnic-4484026926</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-associate-professor-mechanical-and-aerospace-engineering-%2300098258-at-missouri-university-of-science-and-technology-4464936601</t>
         </is>
       </c>
       <c r="O145" s="3" t="inlineStr">
@@ -14217,12 +14217,12 @@
       </c>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="Q145" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="R145" s="6" t="inlineStr">
@@ -14231,31 +14231,31 @@
         </is>
       </c>
       <c r="S145" s="2" t="n">
-        <v>1.3331884</v>
+        <v>37.9532435</v>
       </c>
       <c r="T145" s="2" t="n">
-        <v>103.7746123</v>
+        <v>-91.7742667</v>
       </c>
     </row>
     <row r="146" ht="26" customHeight="1">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>ae0e53bec258ab23</t>
+          <t>56a58b3515dd9d01</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Open-Rank Tenure-Track/Tenured Faculty</t>
+          <t>Lecturer, Civil Engineering</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Oklahoma State University</t>
+          <t>Ngee Ann Polytechnic</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>School of Electrical and Computer Engineering</t>
+          <t>School of Design &amp; Environment</t>
         </is>
       </c>
       <c r="E146" s="3" t="n">
@@ -14263,22 +14263,22 @@
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>Focuses on electrical and computer engineering topics like hardware and machine learning algorithms rather than transportation planning or travel behavior.</t>
+          <t>Low fit: This is a polytechnic teaching lecturer role focused on civil engineering, structural design, and construction management rather than advanced transportation systems or demand modeling.</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Computer Architecture, Machine Learning, Embedded Systems, Cyber-Physical Systems</t>
+          <t>Civil Engineering, Structural Design, Construction Management, Building Information Modeling</t>
         </is>
       </c>
       <c r="H146" s="3" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Non-Tenure Track</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>Stillwater, OK</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="J146" s="3" t="inlineStr">
@@ -14294,27 +14294,27 @@
       </c>
       <c r="M146" s="4" t="inlineStr">
         <is>
-          <t>Open-rank faculty position in electrical and computer engineering requiring a Ph.D. with a focus on computer architecture, machine learning, and embedded systems. | Research Topics: Computer Architecture, Machine Learning, Embedded Systems, Cyber-Physical Systems</t>
+          <t>Ngee Ann Polytechnic invites applications for a 2-year contract Lecturer position in Civil Engineering to deliver classroom instruction, curriculum development, and student mentorship. | Research Topics: Civil Engineering, Structural Design, Construction Management, Building Information Modeling</t>
         </is>
       </c>
       <c r="N146" s="5" t="inlineStr">
         <is>
-          <t>https://engineering.academickeys.com/job/b4h5qge7/OpenRank-TenureTrackTenured-Faculty</t>
+          <t>https://sg.linkedin.com/jobs/view/lecturer-civil-engineering-school-of-design-environment-at-ngee-ann-polytechnic-4484026926</t>
         </is>
       </c>
       <c r="O146" s="3" t="inlineStr">
         <is>
-          <t>AcademicKeys</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="Q146" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R146" s="6" t="inlineStr">
@@ -14323,31 +14323,31 @@
         </is>
       </c>
       <c r="S146" s="2" t="n">
-        <v>36.1313523</v>
+        <v>1.3331884</v>
       </c>
       <c r="T146" s="2" t="n">
-        <v>-97.0890651</v>
+        <v>103.7746123</v>
       </c>
     </row>
     <row r="147" ht="26" customHeight="1">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>12e23ba45b1d6094</t>
+          <t>ae0e53bec258ab23</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>Lecturer of Civil Engineering Technology</t>
+          <t>Open-Rank Tenure-Track/Tenured Faculty</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Old Dominion University</t>
+          <t>Oklahoma State University</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>Department of Engineering Technology</t>
+          <t>School of Electrical and Computer Engineering</t>
         </is>
       </c>
       <c r="E147" s="3" t="n">
@@ -14355,22 +14355,22 @@
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>This non-tenure-track teaching position focuses on civil engineering technology courses in structural design and construction management rather than transportation planning.</t>
+          <t>Focuses on electrical and computer engineering topics like hardware and machine learning algorithms rather than transportation planning or travel behavior.</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>Civil Engineering Technology, Structural Design, Construction Management</t>
+          <t>Computer Architecture, Machine Learning, Embedded Systems, Cyber-Physical Systems</t>
         </is>
       </c>
       <c r="H147" s="3" t="inlineStr">
         <is>
-          <t>Non-Tenure Track</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>Norfolk, VA</t>
+          <t>Stillwater, OK</t>
         </is>
       </c>
       <c r="J147" s="3" t="inlineStr">
@@ -14386,12 +14386,12 @@
       </c>
       <c r="M147" s="4" t="inlineStr">
         <is>
-          <t>Full-time Lecturer position teaching undergraduate courses in civil engineering technology, requiring a minimum of a Master's degree (Ph.D. preferred) in Civil Engineering or related field. | Research Topics: Civil Engineering Technology, Structural Design, Construction Management</t>
+          <t>Open-rank faculty position in electrical and computer engineering requiring a Ph.D. with a focus on computer architecture, machine learning, and embedded systems. | Research Topics: Computer Architecture, Machine Learning, Embedded Systems, Cyber-Physical Systems</t>
         </is>
       </c>
       <c r="N147" s="5" t="inlineStr">
         <is>
-          <t>https://engineering.academickeys.com/job/k7s56az4/Lecturer-of-Civil-Engineering-Technology-NonTenure-Track</t>
+          <t>https://engineering.academickeys.com/job/b4h5qge7/OpenRank-TenureTrackTenured-Faculty</t>
         </is>
       </c>
       <c r="O147" s="3" t="inlineStr">
@@ -14401,12 +14401,12 @@
       </c>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q147" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="R147" s="6" t="inlineStr">
@@ -14415,31 +14415,31 @@
         </is>
       </c>
       <c r="S147" s="2" t="n">
-        <v>36.8862699</v>
+        <v>36.1313523</v>
       </c>
       <c r="T147" s="2" t="n">
-        <v>-76.3097248</v>
+        <v>-97.0890651</v>
       </c>
     </row>
     <row r="148" ht="26" customHeight="1">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>af2244e91d790700</t>
+          <t>12e23ba45b1d6094</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Instructor or Assistant Professor of Engineering</t>
+          <t>Lecturer of Civil Engineering Technology</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Perimeter College</t>
+          <t>Old Dominion University</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Department of Computer Science &amp; Engineering</t>
+          <t>Department of Engineering Technology</t>
         </is>
       </c>
       <c r="E148" s="3" t="n">
@@ -14447,22 +14447,22 @@
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>General engineering education faculty position without any specific focus on transportation engineering or mobility systems.</t>
+          <t>This non-tenure-track teaching position focuses on civil engineering technology courses in structural design and construction management rather than transportation planning.</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Engineering Education, Computer Science, Undergraduate Instruction</t>
+          <t>Civil Engineering Technology, Structural Design, Construction Management</t>
         </is>
       </c>
       <c r="H148" s="3" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Non-Tenure Track</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>Atlanta Area, GA</t>
+          <t>Norfolk, VA</t>
         </is>
       </c>
       <c r="J148" s="3" t="inlineStr">
@@ -14473,32 +14473,32 @@
       <c r="K148" s="3" t="inlineStr"/>
       <c r="L148" s="2" t="inlineStr">
         <is>
-          <t>$53,350 - $65,000 per year</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="M148" s="4" t="inlineStr">
         <is>
-          <t>Perimeter College at Georgia State University seeks an open-rank tenure-track engineering faculty member to teach undergraduate courses, requiring an appropriate graduate degree. | Research Topics: Engineering Education, Computer Science, Undergraduate Instruction</t>
+          <t>Full-time Lecturer position teaching undergraduate courses in civil engineering technology, requiring a minimum of a Master's degree (Ph.D. preferred) in Civil Engineering or related field. | Research Topics: Civil Engineering Technology, Structural Design, Construction Management</t>
         </is>
       </c>
       <c r="N148" s="5" t="inlineStr">
         <is>
-          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179578121&amp;Title=Instructor%20Or%20Assistant%20Professor%20Of%20Engineering</t>
+          <t>https://engineering.academickeys.com/job/k7s56az4/Lecturer-of-Civil-Engineering-Technology-NonTenure-Track</t>
         </is>
       </c>
       <c r="O148" s="3" t="inlineStr">
         <is>
-          <t>HigherEdJobs</t>
+          <t>AcademicKeys</t>
         </is>
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="Q148" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R148" s="6" t="inlineStr">
@@ -14507,31 +14507,31 @@
         </is>
       </c>
       <c r="S148" s="2" t="n">
-        <v>33.6667</v>
+        <v>36.8862699</v>
       </c>
       <c r="T148" s="2" t="n">
-        <v>-84.02889999999999</v>
+        <v>-76.3097248</v>
       </c>
     </row>
     <row r="149" ht="26" customHeight="1">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>251aaee2eeef6a4a</t>
+          <t>af2244e91d790700</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Lecturer (Mobility &amp; Robotic Systems)</t>
+          <t>Instructor or Assistant Professor of Engineering</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Republic Polytechnic</t>
+          <t>Perimeter College</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>School of Engineering</t>
+          <t>Department of Computer Science &amp; Engineering</t>
         </is>
       </c>
       <c r="E149" s="3" t="n">
@@ -14539,22 +14539,22 @@
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>The role focuses on vocational robotics, mechatronic hardware, ROS programming, and manufacturing automation rather than transportation systems planning or travel behavior.</t>
+          <t>General engineering education faculty position without any specific focus on transportation engineering or mobility systems.</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Robotic Systems, Intelligent Transport Systems, Autonomous Vehicles, Mechatronics and Automation</t>
+          <t>Engineering Education, Computer Science, Undergraduate Instruction</t>
         </is>
       </c>
       <c r="H149" s="3" t="inlineStr">
         <is>
-          <t>Non-Tenure Track</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Atlanta Area, GA</t>
         </is>
       </c>
       <c r="J149" s="3" t="inlineStr">
@@ -14565,32 +14565,32 @@
       <c r="K149" s="3" t="inlineStr"/>
       <c r="L149" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>$53,350 - $65,000 per year</t>
         </is>
       </c>
       <c r="M149" s="4" t="inlineStr">
         <is>
-          <t>Republic Polytechnic invites applications for a Lecturer in Mobility &amp; Robotic Systems to teach and supervise projects in automation, ROS, and smart robotics, requiring a qualification in electrical, mechanical, or mechatronic engineering. | Research Topics: Robotic Systems, Intelligent Transport Systems, Autonomous Vehicles, Mechatronics and Automation</t>
+          <t>Perimeter College at Georgia State University seeks an open-rank tenure-track engineering faculty member to teach undergraduate courses, requiring an appropriate graduate degree. | Research Topics: Engineering Education, Computer Science, Undergraduate Instruction</t>
         </is>
       </c>
       <c r="N149" s="5" t="inlineStr">
         <is>
-          <t>https://sg.linkedin.com/jobs/view/school-of-engineering-lecturer-mobility-robotic-systems-at-republic-polytechnic-4445058133</t>
+          <t>https://www.higheredjobs.com/search/details.cfm?JobCode=179578121&amp;Title=Instructor%20Or%20Assistant%20Professor%20Of%20Engineering</t>
         </is>
       </c>
       <c r="O149" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>HigherEdJobs</t>
         </is>
       </c>
       <c r="P149" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="Q149" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="R149" s="6" t="inlineStr">
@@ -14599,31 +14599,31 @@
         </is>
       </c>
       <c r="S149" s="2" t="n">
-        <v>1.4443688</v>
+        <v>33.6667</v>
       </c>
       <c r="T149" s="2" t="n">
-        <v>103.7853712</v>
+        <v>-84.02889999999999</v>
       </c>
     </row>
     <row r="150" ht="26" customHeight="1">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>d2d4a383081033c9</t>
+          <t>251aaee2eeef6a4a</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor (Tenure-Track), Supply Chain, Project &amp; Operations Management</t>
+          <t>Lecturer (Mobility &amp; Robotic Systems)</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Rochester Institute of Technology</t>
+          <t>Republic Polytechnic</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Management Department, Saunders College of Business</t>
+          <t>School of Engineering</t>
         </is>
       </c>
       <c r="E150" s="3" t="n">
@@ -14631,22 +14631,22 @@
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>Screened out: Position is focused on commercial supply chain and operations management rather than transportation engineering or travel behavior.</t>
+          <t>The role focuses on vocational robotics, mechatronic hardware, ROS programming, and manufacturing automation rather than transportation systems planning or travel behavior.</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Analytics, Logistics Management, Operations Research</t>
+          <t>Robotic Systems, Intelligent Transport Systems, Autonomous Vehicles, Mechatronics and Automation</t>
         </is>
       </c>
       <c r="H150" s="3" t="inlineStr">
         <is>
-          <t>Tenure-Track</t>
+          <t>Non-Tenure Track</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>Rochester, NY</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="J150" s="3" t="inlineStr">
@@ -14662,12 +14662,12 @@
       </c>
       <c r="M150" s="4" t="inlineStr">
         <is>
-          <t>Tenure-track assistant professor position in supply chain and operations management requiring a doctoral degree. | Research Topics: Supply Chain Analytics, Logistics Management, Operations Research</t>
+          <t>Republic Polytechnic invites applications for a Lecturer in Mobility &amp; Robotic Systems to teach and supervise projects in automation, ROS, and smart robotics, requiring a qualification in electrical, mechanical, or mechatronic engineering. | Research Topics: Robotic Systems, Intelligent Transport Systems, Autonomous Vehicles, Mechatronics and Automation</t>
         </is>
       </c>
       <c r="N150" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assistant-professor-tenure-track-supply-chain-proj-oper-mgt-quant-meth-at-rochester-institute-of-technology-4475485517</t>
+          <t>https://sg.linkedin.com/jobs/view/school-of-engineering-lecturer-mobility-robotic-systems-at-republic-polytechnic-4445058133</t>
         </is>
       </c>
       <c r="O150" s="3" t="inlineStr">
@@ -14677,12 +14677,12 @@
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="Q150" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R150" s="6" t="inlineStr">
@@ -14691,31 +14691,31 @@
         </is>
       </c>
       <c r="S150" s="2" t="n">
-        <v>43.0826701</v>
+        <v>1.4443688</v>
       </c>
       <c r="T150" s="2" t="n">
-        <v>-77.67293220000001</v>
+        <v>103.7853712</v>
       </c>
     </row>
     <row r="151" ht="26" customHeight="1">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>e40a4f6993abbbb7</t>
+          <t>d2d4a383081033c9</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Environmental and Geosciences</t>
+          <t>Assistant Professor (Tenure-Track), Supply Chain, Project &amp; Operations Management</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Sam Houston State University</t>
+          <t>Rochester Institute of Technology</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>Department of Environmental and Geosciences</t>
+          <t>Management Department, Saunders College of Business</t>
         </is>
       </c>
       <c r="E151" s="3" t="n">
@@ -14723,12 +14723,12 @@
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>Screened out due to focusing on environmental geoscience and GIS rather than transportation engineering or planning.</t>
+          <t>Screened out: Position is focused on commercial supply chain and operations management rather than transportation engineering or travel behavior.</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Geospatial Approaches, Environmental Geosciences, GIS and Remote Sensing</t>
+          <t>Supply Chain Analytics, Logistics Management, Operations Research</t>
         </is>
       </c>
       <c r="H151" s="3" t="inlineStr">
@@ -14738,7 +14738,7 @@
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>Huntsville, Texas</t>
+          <t>Rochester, NY</t>
         </is>
       </c>
       <c r="J151" s="3" t="inlineStr">
@@ -14749,32 +14749,32 @@
       <c r="K151" s="3" t="inlineStr"/>
       <c r="L151" s="2" t="inlineStr">
         <is>
-          <t>Commensurate with education and experience</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="M151" s="4" t="inlineStr">
         <is>
-          <t>Assistant Professor position focusing on environmental geoscience, GIS, and remote sensing requiring a relevant doctoral degree. | Research Topics: Geospatial Approaches, Environmental Geosciences, GIS and Remote Sensing</t>
+          <t>Tenure-track assistant professor position in supply chain and operations management requiring a doctoral degree. | Research Topics: Supply Chain Analytics, Logistics Management, Operations Research</t>
         </is>
       </c>
       <c r="N151" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.chronicle.com/job/38053979/assistant-professor-of-environmental-and-geosciences/</t>
+          <t>https://www.linkedin.com/jobs/view/assistant-professor-tenure-track-supply-chain-proj-oper-mgt-quant-meth-at-rochester-institute-of-technology-4475485517</t>
         </is>
       </c>
       <c r="O151" s="3" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="Q151" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="R151" s="6" t="inlineStr">
@@ -14783,31 +14783,31 @@
         </is>
       </c>
       <c r="S151" s="2" t="n">
-        <v>30.7133471</v>
+        <v>43.0826701</v>
       </c>
       <c r="T151" s="2" t="n">
-        <v>-95.5449136</v>
+        <v>-77.67293220000001</v>
       </c>
     </row>
     <row r="152" ht="26" customHeight="1">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>1aa41f4b13b25948</t>
+          <t>e40a4f6993abbbb7</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor in Public Policy and/or Public Governance</t>
+          <t>Assistant Professor of Environmental and Geosciences</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Singapore Management University</t>
+          <t>Sam Houston State University</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>School of Social Sciences</t>
+          <t>Department of Environmental and Geosciences</t>
         </is>
       </c>
       <c r="E152" s="3" t="n">
@@ -14815,12 +14815,12 @@
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>Screened out: Public policy position lacks any focus on transportation engineering, mobility analytics, or travel behavior.</t>
+          <t>Screened out due to focusing on environmental geoscience and GIS rather than transportation engineering or planning.</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>Public Policy, Policy Analysis, Public Administration, Global Governance</t>
+          <t>Geospatial Approaches, Environmental Geosciences, GIS and Remote Sensing</t>
         </is>
       </c>
       <c r="H152" s="3" t="inlineStr">
@@ -14830,7 +14830,7 @@
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>Singapore, Singapore</t>
+          <t>Huntsville, Texas</t>
         </is>
       </c>
       <c r="J152" s="3" t="inlineStr">
@@ -14841,32 +14841,32 @@
       <c r="K152" s="3" t="inlineStr"/>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Commensurate with education and experience</t>
         </is>
       </c>
       <c r="M152" s="4" t="inlineStr">
         <is>
-          <t>The School of Social Sciences seeks a tenure-track Assistant Professor in Public Policy and/or Public Governance requiring a Ph.D. | Research Topics: Public Policy, Policy Analysis, Public Administration, Global Governance</t>
+          <t>Assistant Professor position focusing on environmental geoscience, GIS, and remote sensing requiring a relevant doctoral degree. | Research Topics: Geospatial Approaches, Environmental Geosciences, GIS and Remote Sensing</t>
         </is>
       </c>
       <c r="N152" s="5" t="inlineStr">
         <is>
-          <t>https://sg.linkedin.com/jobs/view/soss-full-time-faculty-assistant-professor-in-public-policy-and-or-public-governance-term-or-tenure-track-at-singapore-management-university-4475952665</t>
+          <t>https://jobs.chronicle.com/job/38053979/assistant-professor-of-environmental-and-geosciences/</t>
         </is>
       </c>
       <c r="O152" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="Q152" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="R152" s="6" t="inlineStr">
@@ -14875,31 +14875,31 @@
         </is>
       </c>
       <c r="S152" s="2" t="n">
-        <v>1.2961099</v>
+        <v>30.7133471</v>
       </c>
       <c r="T152" s="2" t="n">
-        <v>103.8499494</v>
+        <v>-95.5449136</v>
       </c>
     </row>
     <row r="153" 